--- a/Spanish Dictionary.xlsx
+++ b/Spanish Dictionary.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="438">
   <si>
     <t>Word / Expression</t>
   </si>
@@ -823,6 +823,513 @@
   </si>
   <si>
     <t>unit 3</t>
+  </si>
+  <si>
+    <t>and you?</t>
+  </si>
+  <si>
+    <t>and</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>ee</t>
+  </si>
+  <si>
+    <t>¿y usted?</t>
+  </si>
+  <si>
+    <t>ee ostéd?</t>
+  </si>
+  <si>
+    <t>I am not North American</t>
+  </si>
+  <si>
+    <t>no soy norteamericana</t>
+  </si>
+  <si>
+    <t>no soy norté-américana</t>
+  </si>
+  <si>
+    <t>I am</t>
+  </si>
+  <si>
+    <t>soy</t>
+  </si>
+  <si>
+    <t>I am not North American (f)</t>
+  </si>
+  <si>
+    <t>I am North American</t>
+  </si>
+  <si>
+    <t>soy norteamericano</t>
+  </si>
+  <si>
+    <t>soy norté-américano</t>
+  </si>
+  <si>
+    <t>no soy norteamericano</t>
+  </si>
+  <si>
+    <t>no soy norté-américano</t>
+  </si>
+  <si>
+    <t>I am from Chicago</t>
+  </si>
+  <si>
+    <t>soy de chicago</t>
+  </si>
+  <si>
+    <t>soy dé-tchi-kago</t>
+  </si>
+  <si>
+    <t>from</t>
+  </si>
+  <si>
+    <t>de</t>
+  </si>
+  <si>
+    <t>dé</t>
+  </si>
+  <si>
+    <t>from Chicago</t>
+  </si>
+  <si>
+    <t>de chicago</t>
+  </si>
+  <si>
+    <t>dé-tchi-kago</t>
+  </si>
+  <si>
+    <t>I am from Washington</t>
+  </si>
+  <si>
+    <t>soy de washington</t>
+  </si>
+  <si>
+    <t>soy dé washinton</t>
+  </si>
+  <si>
+    <t>from where?</t>
+  </si>
+  <si>
+    <t>dé dondé?</t>
+  </si>
+  <si>
+    <t>where</t>
+  </si>
+  <si>
+    <t>dondé</t>
+  </si>
+  <si>
+    <t>dé dondé eso-stéd?</t>
+  </si>
+  <si>
+    <t>from where are you? / where are you from?</t>
+  </si>
+  <si>
+    <t>I am from Los Angeles</t>
+  </si>
+  <si>
+    <t>soy de los angeles</t>
+  </si>
+  <si>
+    <t>soy dé-los ankhélés</t>
+  </si>
+  <si>
+    <t>good afternoon</t>
+  </si>
+  <si>
+    <t>buenas tardes</t>
+  </si>
+  <si>
+    <t>buénas tardés</t>
+  </si>
+  <si>
+    <t>the afternoon</t>
+  </si>
+  <si>
+    <t>la tarde</t>
+  </si>
+  <si>
+    <t>là tardé</t>
+  </si>
+  <si>
+    <t>el señor</t>
+  </si>
+  <si>
+    <t>el sénior</t>
+  </si>
+  <si>
+    <t>the man / the gentleman</t>
+  </si>
+  <si>
+    <t>la señora</t>
+  </si>
+  <si>
+    <t>the lady</t>
+  </si>
+  <si>
+    <t>là séniora</t>
+  </si>
+  <si>
+    <t>the day</t>
+  </si>
+  <si>
+    <t>el dee-yah</t>
+  </si>
+  <si>
+    <t>el dia</t>
+  </si>
+  <si>
+    <t>do you speak English? (full)</t>
+  </si>
+  <si>
+    <t>¿habla usted inglés?</t>
+  </si>
+  <si>
+    <t>ablah ostéd in-glés?</t>
+  </si>
+  <si>
+    <t>Good afternoon Ms.</t>
+  </si>
+  <si>
+    <t>buenas tardes señorita</t>
+  </si>
+  <si>
+    <t>buénas tardés séniorita</t>
+  </si>
+  <si>
+    <t>buenas noches</t>
+  </si>
+  <si>
+    <t>buénas notchés</t>
+  </si>
+  <si>
+    <t>good evening / good night</t>
+  </si>
+  <si>
+    <t>night</t>
+  </si>
+  <si>
+    <t>noche</t>
+  </si>
+  <si>
+    <t>notché</t>
+  </si>
+  <si>
+    <t>the night</t>
+  </si>
+  <si>
+    <t>la noche</t>
+  </si>
+  <si>
+    <t>là notché</t>
+  </si>
+  <si>
+    <t>from Mexico</t>
+  </si>
+  <si>
+    <t>de México</t>
+  </si>
+  <si>
+    <t>dé méhiko</t>
+  </si>
+  <si>
+    <t>I am from Mexico</t>
+  </si>
+  <si>
+    <t>soy de México</t>
+  </si>
+  <si>
+    <t>soy dé méhiko</t>
+  </si>
+  <si>
+    <t>you are from Mexico</t>
+  </si>
+  <si>
+    <t>ustedes de México</t>
+  </si>
+  <si>
+    <t>ostédés dé méhiko</t>
+  </si>
+  <si>
+    <t>and you understand very well</t>
+  </si>
+  <si>
+    <t>y entiende muy bien</t>
+  </si>
+  <si>
+    <t>ee en-tiéndé mooyy bee-yan</t>
+  </si>
+  <si>
+    <t>no muy bien</t>
+  </si>
+  <si>
+    <t>no mooyy bee-yan</t>
+  </si>
+  <si>
+    <t>not very well</t>
+  </si>
+  <si>
+    <t>I am from North America</t>
+  </si>
+  <si>
+    <t>soy dé norté-américa</t>
+  </si>
+  <si>
+    <t>soy de Norteamérica</t>
+  </si>
+  <si>
+    <t>from Bolivia</t>
+  </si>
+  <si>
+    <t>dé bolivia</t>
+  </si>
+  <si>
+    <t>de Bolivia</t>
+  </si>
+  <si>
+    <t>I am from Bolivia</t>
+  </si>
+  <si>
+    <t>soy de Bolivia</t>
+  </si>
+  <si>
+    <t>soy dé bolivia</t>
+  </si>
+  <si>
+    <t>I am Miss Garcia</t>
+  </si>
+  <si>
+    <t>soy la señora Garcia</t>
+  </si>
+  <si>
+    <t>soy la séniora garcia</t>
+  </si>
+  <si>
+    <t>I am Mr. Jones</t>
+  </si>
+  <si>
+    <t>soy el señor Jones</t>
+  </si>
+  <si>
+    <t>soy el sénior jonz</t>
+  </si>
+  <si>
+    <t>I am not from Los Angeles</t>
+  </si>
+  <si>
+    <t>no soy de los angeles</t>
+  </si>
+  <si>
+    <t>no soy dé-los ankhélés</t>
+  </si>
+  <si>
+    <t>delante</t>
+  </si>
+  <si>
+    <t>in front of</t>
+  </si>
+  <si>
+    <t>délanté</t>
+  </si>
+  <si>
+    <t>damas</t>
+  </si>
+  <si>
+    <t>dahmas</t>
+  </si>
+  <si>
+    <t>ladies</t>
+  </si>
+  <si>
+    <t>la dama</t>
+  </si>
+  <si>
+    <t>the lady / the miss</t>
+  </si>
+  <si>
+    <t>là damah</t>
+  </si>
+  <si>
+    <t>por favor</t>
+  </si>
+  <si>
+    <t>please</t>
+  </si>
+  <si>
+    <t>el papel</t>
+  </si>
+  <si>
+    <t>the paper</t>
+  </si>
+  <si>
+    <t>el papél</t>
+  </si>
+  <si>
+    <t>¡canta!</t>
+  </si>
+  <si>
+    <t>kanta</t>
+  </si>
+  <si>
+    <t>sing!</t>
+  </si>
+  <si>
+    <t>calor</t>
+  </si>
+  <si>
+    <t>heat</t>
+  </si>
+  <si>
+    <t>kalor</t>
+  </si>
+  <si>
+    <t>baño</t>
+  </si>
+  <si>
+    <t>bathroom</t>
+  </si>
+  <si>
+    <t>banio</t>
+  </si>
+  <si>
+    <t>comer</t>
+  </si>
+  <si>
+    <t>to eat</t>
+  </si>
+  <si>
+    <t>komér</t>
+  </si>
+  <si>
+    <t>ella</t>
+  </si>
+  <si>
+    <t>she</t>
+  </si>
+  <si>
+    <t>eih-yah</t>
+  </si>
+  <si>
+    <t>la niña</t>
+  </si>
+  <si>
+    <t>the girl</t>
+  </si>
+  <si>
+    <t>là neen-yah</t>
+  </si>
+  <si>
+    <t>comprar</t>
+  </si>
+  <si>
+    <t>to buy</t>
+  </si>
+  <si>
+    <t>komprar</t>
+  </si>
+  <si>
+    <t>entender</t>
+  </si>
+  <si>
+    <t>to understand</t>
+  </si>
+  <si>
+    <t>enténdér</t>
+  </si>
+  <si>
+    <t>España</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
+    <t>eih-spaniah</t>
+  </si>
+  <si>
+    <t>Ud.</t>
+  </si>
+  <si>
+    <t>you (abbreviation of usted)</t>
+  </si>
+  <si>
+    <t>americano</t>
+  </si>
+  <si>
+    <t>American</t>
+  </si>
+  <si>
+    <t>américano</t>
+  </si>
+  <si>
+    <t>¿es Ud. americano?</t>
+  </si>
+  <si>
+    <t>eso-stéd américano?</t>
+  </si>
+  <si>
+    <t>Are you American?</t>
+  </si>
+  <si>
+    <t>si, soy americano</t>
+  </si>
+  <si>
+    <t>yes, I am American</t>
+  </si>
+  <si>
+    <t>cee soy américano</t>
+  </si>
+  <si>
+    <t>¿de dónde?</t>
+  </si>
+  <si>
+    <t>dónde</t>
+  </si>
+  <si>
+    <t>¿de dónde es usted?</t>
+  </si>
+  <si>
+    <t>saber</t>
+  </si>
+  <si>
+    <t>to know</t>
+  </si>
+  <si>
+    <t>sabér</t>
+  </si>
+  <si>
+    <t>norte</t>
+  </si>
+  <si>
+    <t>norté</t>
+  </si>
+  <si>
+    <t>North</t>
+  </si>
+  <si>
+    <t>bañar</t>
+  </si>
+  <si>
+    <t>baniar</t>
+  </si>
+  <si>
+    <t>to bathe</t>
+  </si>
+  <si>
+    <t>lloro</t>
+  </si>
+  <si>
+    <t>yoh-roh</t>
+  </si>
+  <si>
+    <t>I cry</t>
+  </si>
+  <si>
+    <t>unit 4</t>
   </si>
 </sst>
 </file>
@@ -870,7 +1377,67 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1508">
+  <dxfs count="1514">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -16248,7 +16815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:D446"/>
+  <dimension ref="B1:D445"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="1" customWidth="1"/>
@@ -17259,4475 +17826,5176 @@
       </c>
     </row>
     <row r="93" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C93" s="2"/>
+      <c r="B93" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>269</v>
+      </c>
     </row>
-    <row r="441" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B441" s="2"/>
+    <row r="94" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B94" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>270</v>
+      </c>
     </row>
-    <row r="446" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B446" s="2"/>
+    <row r="95" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B95" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="96" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B96" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="97" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B97" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="98" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B98" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="99" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B99" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="100" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B100" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="101" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B101" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="102" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B102" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="103" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B103" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="104" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B104" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="105" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B105" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="106" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B106" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="107" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B107" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="108" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B108" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="109" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B109" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="110" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B110" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="111" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B111" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="112" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B112" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="113" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B113" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B114" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B115" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B116" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="117" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B117" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B118" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="119" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B119" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="120" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B120" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="121" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B121" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="122" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B122" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="123" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B123" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="124" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B124" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="125" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B125" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B126" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="127" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B127" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B128" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="129" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B129" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="130" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B130" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B131" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="132" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B132" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="133" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B133" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="134" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B134" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="135" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B135" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="136" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B136" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="137" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B137" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="138" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B138" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="139" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B139" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="140" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B140" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="141" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B141" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="142" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B142" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="143" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B143" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="144" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B144" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B145" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="146" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B146" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B147" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B148" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B149" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="150" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B150" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="440" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B440" s="2"/>
+    </row>
+    <row r="445" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B445" s="2"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B108">
-    <cfRule type="duplicateValues" dxfId="1507" priority="2186"/>
+    <cfRule type="duplicateValues" dxfId="1510" priority="2216"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B125">
-    <cfRule type="duplicateValues" dxfId="1506" priority="2185"/>
+    <cfRule type="duplicateValues" dxfId="1509" priority="2215"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B132">
+    <cfRule type="duplicateValues" dxfId="1508" priority="2214"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B128">
-    <cfRule type="duplicateValues" dxfId="1505" priority="2184"/>
+    <cfRule type="duplicateValues" dxfId="1507" priority="2213"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B129">
-    <cfRule type="duplicateValues" dxfId="1504" priority="2183"/>
+    <cfRule type="duplicateValues" dxfId="1506" priority="2212"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B130">
-    <cfRule type="duplicateValues" dxfId="1503" priority="2182"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B131">
-    <cfRule type="duplicateValues" dxfId="1502" priority="2181"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B134">
-    <cfRule type="duplicateValues" dxfId="1501" priority="2180"/>
+    <cfRule type="duplicateValues" dxfId="1505" priority="2211"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B133">
+    <cfRule type="duplicateValues" dxfId="1504" priority="2210"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B135">
+    <cfRule type="duplicateValues" dxfId="1503" priority="2209"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B136">
-    <cfRule type="duplicateValues" dxfId="1500" priority="2179"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B137">
-    <cfRule type="duplicateValues" dxfId="1499" priority="2178"/>
+    <cfRule type="duplicateValues" dxfId="1502" priority="2208"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B138">
+    <cfRule type="duplicateValues" dxfId="1501" priority="2207"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B139">
-    <cfRule type="duplicateValues" dxfId="1498" priority="2177"/>
+    <cfRule type="duplicateValues" dxfId="1500" priority="2206"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B140">
-    <cfRule type="duplicateValues" dxfId="1497" priority="2176"/>
+    <cfRule type="duplicateValues" dxfId="1499" priority="2205"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B141">
-    <cfRule type="duplicateValues" dxfId="1496" priority="2175"/>
+    <cfRule type="duplicateValues" dxfId="1498" priority="2204"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B142">
-    <cfRule type="duplicateValues" dxfId="1495" priority="2174"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B143">
-    <cfRule type="duplicateValues" dxfId="1494" priority="2173"/>
+    <cfRule type="duplicateValues" dxfId="1497" priority="2203"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B148">
+    <cfRule type="duplicateValues" dxfId="1496" priority="2202"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B149">
-    <cfRule type="duplicateValues" dxfId="1493" priority="2172"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B150">
-    <cfRule type="duplicateValues" dxfId="1492" priority="2171"/>
+    <cfRule type="duplicateValues" dxfId="1495" priority="2201"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B153">
+    <cfRule type="duplicateValues" dxfId="1494" priority="2200"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B154">
-    <cfRule type="duplicateValues" dxfId="1491" priority="2170"/>
+    <cfRule type="duplicateValues" dxfId="1493" priority="2199"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B155">
-    <cfRule type="duplicateValues" dxfId="1490" priority="2169"/>
+    <cfRule type="duplicateValues" dxfId="1492" priority="2198"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B156">
-    <cfRule type="duplicateValues" dxfId="1489" priority="2168"/>
+    <cfRule type="duplicateValues" dxfId="1491" priority="2197"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B157">
-    <cfRule type="duplicateValues" dxfId="1488" priority="2167"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B158">
-    <cfRule type="duplicateValues" dxfId="1487" priority="2166"/>
+    <cfRule type="duplicateValues" dxfId="1490" priority="2196"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B161">
+    <cfRule type="duplicateValues" dxfId="1489" priority="2195"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B162">
-    <cfRule type="duplicateValues" dxfId="1486" priority="2165"/>
+    <cfRule type="duplicateValues" dxfId="1488" priority="2194"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B163">
-    <cfRule type="duplicateValues" dxfId="1485" priority="2164"/>
+    <cfRule type="duplicateValues" dxfId="1487" priority="2193"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B164">
-    <cfRule type="duplicateValues" dxfId="1484" priority="2163"/>
+    <cfRule type="duplicateValues" dxfId="1486" priority="2192"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B165">
-    <cfRule type="duplicateValues" dxfId="1483" priority="2162"/>
+    <cfRule type="duplicateValues" dxfId="1485" priority="2191"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B166">
-    <cfRule type="duplicateValues" dxfId="1482" priority="2161"/>
+    <cfRule type="duplicateValues" dxfId="1484" priority="2190"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B167">
-    <cfRule type="duplicateValues" dxfId="1481" priority="2160"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B168">
-    <cfRule type="duplicateValues" dxfId="1480" priority="2159"/>
+    <cfRule type="duplicateValues" dxfId="1483" priority="2189"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B170">
+    <cfRule type="duplicateValues" dxfId="1482" priority="2188"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171">
-    <cfRule type="duplicateValues" dxfId="1479" priority="2158"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B172">
-    <cfRule type="duplicateValues" dxfId="1478" priority="2157"/>
+    <cfRule type="duplicateValues" dxfId="1481" priority="2187"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B173">
+    <cfRule type="duplicateValues" dxfId="1480" priority="2186"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B174">
-    <cfRule type="duplicateValues" dxfId="1477" priority="2156"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B175">
-    <cfRule type="duplicateValues" dxfId="1476" priority="2155"/>
+    <cfRule type="duplicateValues" dxfId="1479" priority="2185"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B176">
+    <cfRule type="duplicateValues" dxfId="1478" priority="2184"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B177">
-    <cfRule type="duplicateValues" dxfId="1475" priority="2154"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B178">
-    <cfRule type="duplicateValues" dxfId="1474" priority="2153"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B180">
-    <cfRule type="duplicateValues" dxfId="1473" priority="2152"/>
+    <cfRule type="duplicateValues" dxfId="1477" priority="2183"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B179">
+    <cfRule type="duplicateValues" dxfId="1476" priority="2182"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B186">
+    <cfRule type="duplicateValues" dxfId="1475" priority="2181"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B187">
-    <cfRule type="duplicateValues" dxfId="1472" priority="2151"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B188">
-    <cfRule type="duplicateValues" dxfId="1471" priority="2150"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B190">
-    <cfRule type="duplicateValues" dxfId="1470" priority="2149"/>
+    <cfRule type="duplicateValues" dxfId="1474" priority="2180"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B189">
+    <cfRule type="duplicateValues" dxfId="1473" priority="2179"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B191">
+    <cfRule type="duplicateValues" dxfId="1472" priority="2178"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B192">
-    <cfRule type="duplicateValues" dxfId="1469" priority="2148"/>
+    <cfRule type="duplicateValues" dxfId="1471" priority="2177"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B193">
-    <cfRule type="duplicateValues" dxfId="1468" priority="2147"/>
+    <cfRule type="duplicateValues" dxfId="1470" priority="2176"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B194">
-    <cfRule type="duplicateValues" dxfId="1467" priority="2146"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B195">
-    <cfRule type="duplicateValues" dxfId="1466" priority="2145"/>
+    <cfRule type="duplicateValues" dxfId="1469" priority="2175"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B196">
+    <cfRule type="duplicateValues" dxfId="1468" priority="2174"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B197">
-    <cfRule type="duplicateValues" dxfId="1465" priority="2144"/>
+    <cfRule type="duplicateValues" dxfId="1467" priority="2173"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B198">
-    <cfRule type="duplicateValues" dxfId="1464" priority="2143"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B199">
-    <cfRule type="duplicateValues" dxfId="1463" priority="2142"/>
+    <cfRule type="duplicateValues" dxfId="1466" priority="2172"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B200">
+    <cfRule type="duplicateValues" dxfId="1465" priority="2171"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B201">
-    <cfRule type="duplicateValues" dxfId="1462" priority="2141"/>
+    <cfRule type="duplicateValues" dxfId="1464" priority="2170"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B202">
-    <cfRule type="duplicateValues" dxfId="1461" priority="2140"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B203">
-    <cfRule type="duplicateValues" dxfId="1460" priority="2139"/>
+    <cfRule type="duplicateValues" dxfId="1463" priority="2169"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B204">
+    <cfRule type="duplicateValues" dxfId="1462" priority="2168"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B205">
-    <cfRule type="duplicateValues" dxfId="1459" priority="2138"/>
+    <cfRule type="duplicateValues" dxfId="1461" priority="2167"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B206">
-    <cfRule type="duplicateValues" dxfId="1458" priority="2137"/>
+    <cfRule type="duplicateValues" dxfId="1460" priority="2166"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B207">
-    <cfRule type="duplicateValues" dxfId="1457" priority="2136"/>
+    <cfRule type="duplicateValues" dxfId="1459" priority="2165"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B208">
-    <cfRule type="duplicateValues" dxfId="1456" priority="2135"/>
+    <cfRule type="duplicateValues" dxfId="1458" priority="2164"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B209">
-    <cfRule type="duplicateValues" dxfId="1455" priority="2134"/>
+    <cfRule type="duplicateValues" dxfId="1457" priority="2163"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B210">
-    <cfRule type="duplicateValues" dxfId="1454" priority="2133"/>
+    <cfRule type="duplicateValues" dxfId="1456" priority="2162"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B211">
-    <cfRule type="duplicateValues" dxfId="1453" priority="2132"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B212">
-    <cfRule type="duplicateValues" dxfId="1452" priority="2131"/>
+    <cfRule type="duplicateValues" dxfId="1455" priority="2161"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B214">
+    <cfRule type="duplicateValues" dxfId="1454" priority="2160"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B215">
-    <cfRule type="duplicateValues" dxfId="1451" priority="2130"/>
+    <cfRule type="duplicateValues" dxfId="1453" priority="2159"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B216">
-    <cfRule type="duplicateValues" dxfId="1450" priority="2129"/>
+    <cfRule type="duplicateValues" dxfId="1452" priority="2158"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B217">
-    <cfRule type="duplicateValues" dxfId="1449" priority="2128"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B218">
-    <cfRule type="duplicateValues" dxfId="1448" priority="2127"/>
+    <cfRule type="duplicateValues" dxfId="1451" priority="2157"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B219">
+    <cfRule type="duplicateValues" dxfId="1450" priority="2156"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B220">
-    <cfRule type="duplicateValues" dxfId="1447" priority="2126"/>
+    <cfRule type="duplicateValues" dxfId="1449" priority="2155"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B221">
-    <cfRule type="duplicateValues" dxfId="1446" priority="2125"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B222">
-    <cfRule type="duplicateValues" dxfId="1445" priority="2124"/>
+    <cfRule type="duplicateValues" dxfId="1448" priority="2154"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B225">
+    <cfRule type="duplicateValues" dxfId="1447" priority="2153"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B226">
-    <cfRule type="duplicateValues" dxfId="1444" priority="2123"/>
+    <cfRule type="duplicateValues" dxfId="1446" priority="2152"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B227">
-    <cfRule type="duplicateValues" dxfId="1443" priority="2122"/>
+    <cfRule type="duplicateValues" dxfId="1445" priority="2151"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B228">
-    <cfRule type="duplicateValues" dxfId="1442" priority="2121"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B229">
-    <cfRule type="duplicateValues" dxfId="1441" priority="2120"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B231">
-    <cfRule type="duplicateValues" dxfId="1440" priority="2118"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B231">
-    <cfRule type="duplicateValues" dxfId="1439" priority="2117"/>
+    <cfRule type="duplicateValues" dxfId="1444" priority="2150"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B230">
+    <cfRule type="duplicateValues" dxfId="1443" priority="2148"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B230">
+    <cfRule type="duplicateValues" dxfId="1442" priority="2147"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B233">
+    <cfRule type="duplicateValues" dxfId="1441" priority="2146"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B233">
+    <cfRule type="duplicateValues" dxfId="1440" priority="2145"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B234">
-    <cfRule type="duplicateValues" dxfId="1438" priority="2116"/>
+    <cfRule type="duplicateValues" dxfId="1439" priority="2144"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B234">
-    <cfRule type="duplicateValues" dxfId="1437" priority="2115"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B235">
-    <cfRule type="duplicateValues" dxfId="1436" priority="2114"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B235">
-    <cfRule type="duplicateValues" dxfId="1435" priority="2113"/>
+    <cfRule type="duplicateValues" dxfId="1438" priority="2143"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B236">
+    <cfRule type="duplicateValues" dxfId="1437" priority="2142"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B236">
+    <cfRule type="duplicateValues" dxfId="1436" priority="2141"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B237">
-    <cfRule type="duplicateValues" dxfId="1434" priority="2112"/>
+    <cfRule type="duplicateValues" dxfId="1435" priority="2140"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B237">
-    <cfRule type="duplicateValues" dxfId="1433" priority="2111"/>
+    <cfRule type="duplicateValues" dxfId="1434" priority="2139"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B238">
-    <cfRule type="duplicateValues" dxfId="1432" priority="2110"/>
+    <cfRule type="duplicateValues" dxfId="1433" priority="2138"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B238">
-    <cfRule type="duplicateValues" dxfId="1431" priority="2109"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B239">
-    <cfRule type="duplicateValues" dxfId="1430" priority="2108"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B239">
-    <cfRule type="duplicateValues" dxfId="1429" priority="2107"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B242">
-    <cfRule type="duplicateValues" dxfId="1428" priority="2106"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B242">
-    <cfRule type="duplicateValues" dxfId="1427" priority="2105"/>
+    <cfRule type="duplicateValues" dxfId="1432" priority="2137"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B241">
+    <cfRule type="duplicateValues" dxfId="1431" priority="2136"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B241">
+    <cfRule type="duplicateValues" dxfId="1430" priority="2135"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B245">
+    <cfRule type="duplicateValues" dxfId="1429" priority="2134"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B245">
+    <cfRule type="duplicateValues" dxfId="1428" priority="2133"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B246">
-    <cfRule type="duplicateValues" dxfId="1426" priority="2104"/>
+    <cfRule type="duplicateValues" dxfId="1427" priority="2132"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B246">
-    <cfRule type="duplicateValues" dxfId="1425" priority="2103"/>
+    <cfRule type="duplicateValues" dxfId="1426" priority="2131"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B247">
-    <cfRule type="duplicateValues" dxfId="1424" priority="2102"/>
+    <cfRule type="duplicateValues" dxfId="1425" priority="2130"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B247">
-    <cfRule type="duplicateValues" dxfId="1423" priority="2101"/>
+    <cfRule type="duplicateValues" dxfId="1424" priority="2129"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B248">
-    <cfRule type="duplicateValues" dxfId="1422" priority="2100"/>
+    <cfRule type="duplicateValues" dxfId="1423" priority="2128"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B248">
-    <cfRule type="duplicateValues" dxfId="1421" priority="2099"/>
+    <cfRule type="duplicateValues" dxfId="1422" priority="2127"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B249">
-    <cfRule type="duplicateValues" dxfId="1420" priority="2098"/>
+    <cfRule type="duplicateValues" dxfId="1421" priority="2126"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B249">
-    <cfRule type="duplicateValues" dxfId="1419" priority="2097"/>
+    <cfRule type="duplicateValues" dxfId="1420" priority="2125"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B250">
-    <cfRule type="duplicateValues" dxfId="1418" priority="2096"/>
+    <cfRule type="duplicateValues" dxfId="1419" priority="2124"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B250">
-    <cfRule type="duplicateValues" dxfId="1417" priority="2095"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B251">
-    <cfRule type="duplicateValues" dxfId="1416" priority="2094"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B251">
-    <cfRule type="duplicateValues" dxfId="1415" priority="2093"/>
+    <cfRule type="duplicateValues" dxfId="1418" priority="2123"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B252">
+    <cfRule type="duplicateValues" dxfId="1417" priority="2120"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B252">
+    <cfRule type="duplicateValues" dxfId="1416" priority="2119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B253">
-    <cfRule type="duplicateValues" dxfId="1414" priority="2090"/>
+    <cfRule type="duplicateValues" dxfId="1415" priority="2118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B253">
-    <cfRule type="duplicateValues" dxfId="1413" priority="2089"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B254">
-    <cfRule type="duplicateValues" dxfId="1412" priority="2088"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B254">
-    <cfRule type="duplicateValues" dxfId="1411" priority="2087"/>
+    <cfRule type="duplicateValues" dxfId="1414" priority="2117"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B255">
+    <cfRule type="duplicateValues" dxfId="1413" priority="2116"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B255">
+    <cfRule type="duplicateValues" dxfId="1412" priority="2115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B256">
-    <cfRule type="duplicateValues" dxfId="1410" priority="2086"/>
+    <cfRule type="duplicateValues" dxfId="1411" priority="2114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B256">
-    <cfRule type="duplicateValues" dxfId="1409" priority="2085"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B257">
-    <cfRule type="duplicateValues" dxfId="1408" priority="2084"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B257">
-    <cfRule type="duplicateValues" dxfId="1407" priority="2083"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B264">
-    <cfRule type="duplicateValues" dxfId="1406" priority="2082"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B264">
-    <cfRule type="duplicateValues" dxfId="1405" priority="2081"/>
+    <cfRule type="duplicateValues" dxfId="1410" priority="2113"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B263">
+    <cfRule type="duplicateValues" dxfId="1409" priority="2112"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B263">
+    <cfRule type="duplicateValues" dxfId="1408" priority="2111"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B270">
+    <cfRule type="duplicateValues" dxfId="1407" priority="2110"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B270">
+    <cfRule type="duplicateValues" dxfId="1406" priority="2109"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B271">
-    <cfRule type="duplicateValues" dxfId="1404" priority="2080"/>
+    <cfRule type="duplicateValues" dxfId="1405" priority="2108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B271">
-    <cfRule type="duplicateValues" dxfId="1403" priority="2079"/>
+    <cfRule type="duplicateValues" dxfId="1404" priority="2107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B272">
-    <cfRule type="duplicateValues" dxfId="1402" priority="2078"/>
+    <cfRule type="duplicateValues" dxfId="1403" priority="2106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B272">
-    <cfRule type="duplicateValues" dxfId="1401" priority="2077"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B273">
-    <cfRule type="duplicateValues" dxfId="1400" priority="2076"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B273">
-    <cfRule type="duplicateValues" dxfId="1399" priority="2075"/>
+    <cfRule type="duplicateValues" dxfId="1402" priority="2105"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B274">
+    <cfRule type="duplicateValues" dxfId="1401" priority="2104"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B274">
+    <cfRule type="duplicateValues" dxfId="1400" priority="2103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B275">
-    <cfRule type="duplicateValues" dxfId="1398" priority="2074"/>
+    <cfRule type="duplicateValues" dxfId="1399" priority="2102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B275">
-    <cfRule type="duplicateValues" dxfId="1397" priority="2073"/>
+    <cfRule type="duplicateValues" dxfId="1398" priority="2101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B276">
-    <cfRule type="duplicateValues" dxfId="1396" priority="2072"/>
+    <cfRule type="duplicateValues" dxfId="1397" priority="2100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B276">
-    <cfRule type="duplicateValues" dxfId="1395" priority="2071"/>
+    <cfRule type="duplicateValues" dxfId="1396" priority="2099"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B277">
-    <cfRule type="duplicateValues" dxfId="1394" priority="2070"/>
+    <cfRule type="duplicateValues" dxfId="1395" priority="2096"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B277">
-    <cfRule type="duplicateValues" dxfId="1393" priority="2069"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B278">
-    <cfRule type="duplicateValues" dxfId="1392" priority="2066"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B278">
-    <cfRule type="duplicateValues" dxfId="1391" priority="2065"/>
+    <cfRule type="duplicateValues" dxfId="1394" priority="2095"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B279">
+    <cfRule type="duplicateValues" dxfId="1393" priority="2094"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B279">
+    <cfRule type="duplicateValues" dxfId="1392" priority="2093"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B280">
-    <cfRule type="duplicateValues" dxfId="1390" priority="2064"/>
+    <cfRule type="duplicateValues" dxfId="1391" priority="2092"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B280">
-    <cfRule type="duplicateValues" dxfId="1389" priority="2063"/>
+    <cfRule type="duplicateValues" dxfId="1390" priority="2091"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B281">
-    <cfRule type="duplicateValues" dxfId="1388" priority="2062"/>
+    <cfRule type="duplicateValues" dxfId="1389" priority="2088"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B281">
-    <cfRule type="duplicateValues" dxfId="1387" priority="2061"/>
+    <cfRule type="duplicateValues" dxfId="1388" priority="2087"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B282">
-    <cfRule type="duplicateValues" dxfId="1386" priority="2058"/>
+    <cfRule type="duplicateValues" dxfId="1387" priority="2086"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B282">
-    <cfRule type="duplicateValues" dxfId="1385" priority="2057"/>
+    <cfRule type="duplicateValues" dxfId="1386" priority="2085"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B283">
-    <cfRule type="duplicateValues" dxfId="1384" priority="2056"/>
+    <cfRule type="duplicateValues" dxfId="1385" priority="2084"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B283">
-    <cfRule type="duplicateValues" dxfId="1383" priority="2055"/>
+    <cfRule type="duplicateValues" dxfId="1384" priority="2083"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B284">
-    <cfRule type="duplicateValues" dxfId="1382" priority="2054"/>
+    <cfRule type="duplicateValues" dxfId="1383" priority="2082"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B284">
-    <cfRule type="duplicateValues" dxfId="1381" priority="2053"/>
+    <cfRule type="duplicateValues" dxfId="1382" priority="2081"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B285">
-    <cfRule type="duplicateValues" dxfId="1380" priority="2052"/>
+    <cfRule type="duplicateValues" dxfId="1381" priority="2080"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B285">
-    <cfRule type="duplicateValues" dxfId="1379" priority="2051"/>
+    <cfRule type="duplicateValues" dxfId="1380" priority="2079"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B286">
-    <cfRule type="duplicateValues" dxfId="1378" priority="2050"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B286">
-    <cfRule type="duplicateValues" dxfId="1377" priority="2049"/>
+    <cfRule type="duplicateValues" dxfId="1379" priority="2078"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B287">
-    <cfRule type="duplicateValues" dxfId="1376" priority="2048"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B288">
-    <cfRule type="duplicateValues" dxfId="1375" priority="2045"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B288">
-    <cfRule type="duplicateValues" dxfId="1374" priority="2044"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B291">
-    <cfRule type="duplicateValues" dxfId="1373" priority="2043"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B291">
-    <cfRule type="duplicateValues" dxfId="1372" priority="2042"/>
+    <cfRule type="duplicateValues" dxfId="1378" priority="2075"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B287">
+    <cfRule type="duplicateValues" dxfId="1377" priority="2074"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B290">
+    <cfRule type="duplicateValues" dxfId="1376" priority="2073"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B290">
+    <cfRule type="duplicateValues" dxfId="1375" priority="2072"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B292">
+    <cfRule type="duplicateValues" dxfId="1374" priority="2071"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B292">
+    <cfRule type="duplicateValues" dxfId="1373" priority="2070"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B293">
-    <cfRule type="duplicateValues" dxfId="1371" priority="2041"/>
+    <cfRule type="duplicateValues" dxfId="1372" priority="2067"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B293">
-    <cfRule type="duplicateValues" dxfId="1370" priority="2040"/>
+    <cfRule type="duplicateValues" dxfId="1371" priority="2066"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B294">
-    <cfRule type="duplicateValues" dxfId="1369" priority="2037"/>
+    <cfRule type="duplicateValues" dxfId="1370" priority="2065"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B294">
-    <cfRule type="duplicateValues" dxfId="1368" priority="2036"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B295">
-    <cfRule type="duplicateValues" dxfId="1367" priority="2035"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B295">
-    <cfRule type="duplicateValues" dxfId="1366" priority="2034"/>
+    <cfRule type="duplicateValues" dxfId="1369" priority="2064"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B300">
+    <cfRule type="duplicateValues" dxfId="1368" priority="2063"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B300">
+    <cfRule type="duplicateValues" dxfId="1367" priority="2062"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B301">
-    <cfRule type="duplicateValues" dxfId="1365" priority="2033"/>
+    <cfRule type="duplicateValues" dxfId="1366" priority="2061"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B301">
-    <cfRule type="duplicateValues" dxfId="1364" priority="2032"/>
+    <cfRule type="duplicateValues" dxfId="1365" priority="2060"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B302">
-    <cfRule type="duplicateValues" dxfId="1363" priority="2031"/>
+    <cfRule type="duplicateValues" dxfId="1364" priority="2057"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B302">
-    <cfRule type="duplicateValues" dxfId="1362" priority="2030"/>
+    <cfRule type="duplicateValues" dxfId="1363" priority="2056"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B303">
-    <cfRule type="duplicateValues" dxfId="1361" priority="2027"/>
+    <cfRule type="duplicateValues" dxfId="1362" priority="2055"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B303">
-    <cfRule type="duplicateValues" dxfId="1360" priority="2026"/>
+    <cfRule type="duplicateValues" dxfId="1361" priority="2054"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B304">
-    <cfRule type="duplicateValues" dxfId="1359" priority="2025"/>
+    <cfRule type="duplicateValues" dxfId="1360" priority="2053"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B304">
-    <cfRule type="duplicateValues" dxfId="1358" priority="2024"/>
+    <cfRule type="duplicateValues" dxfId="1359" priority="2052"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B305">
-    <cfRule type="duplicateValues" dxfId="1357" priority="2023"/>
+    <cfRule type="duplicateValues" dxfId="1358" priority="2051"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B305">
-    <cfRule type="duplicateValues" dxfId="1356" priority="2022"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B306">
-    <cfRule type="duplicateValues" dxfId="1355" priority="2021"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B306">
-    <cfRule type="duplicateValues" dxfId="1354" priority="2020"/>
+    <cfRule type="duplicateValues" dxfId="1357" priority="2050"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B308">
+    <cfRule type="duplicateValues" dxfId="1356" priority="2046"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B308">
+    <cfRule type="duplicateValues" dxfId="1355" priority="2045"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B309">
-    <cfRule type="duplicateValues" dxfId="1353" priority="2016"/>
+    <cfRule type="duplicateValues" dxfId="1354" priority="2044"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B309">
-    <cfRule type="duplicateValues" dxfId="1352" priority="2015"/>
+    <cfRule type="duplicateValues" dxfId="1353" priority="2043"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B310">
-    <cfRule type="duplicateValues" dxfId="1351" priority="2014"/>
+    <cfRule type="duplicateValues" dxfId="1352" priority="2042"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B310">
-    <cfRule type="duplicateValues" dxfId="1350" priority="2013"/>
+    <cfRule type="duplicateValues" dxfId="1351" priority="2041"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B311">
-    <cfRule type="duplicateValues" dxfId="1349" priority="2012"/>
+    <cfRule type="duplicateValues" dxfId="1350" priority="2040"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B311">
-    <cfRule type="duplicateValues" dxfId="1348" priority="2011"/>
+    <cfRule type="duplicateValues" dxfId="1349" priority="2039"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B312">
-    <cfRule type="duplicateValues" dxfId="1347" priority="2010"/>
+    <cfRule type="duplicateValues" dxfId="1348" priority="2036"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B312">
-    <cfRule type="duplicateValues" dxfId="1346" priority="2009"/>
+    <cfRule type="duplicateValues" dxfId="1347" priority="2035"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B313">
-    <cfRule type="duplicateValues" dxfId="1345" priority="2006"/>
+    <cfRule type="duplicateValues" dxfId="1346" priority="2032"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B313">
-    <cfRule type="duplicateValues" dxfId="1344" priority="2005"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B314">
-    <cfRule type="duplicateValues" dxfId="1343" priority="2002"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B314">
-    <cfRule type="duplicateValues" dxfId="1342" priority="2001"/>
+    <cfRule type="duplicateValues" dxfId="1345" priority="2031"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B315">
+    <cfRule type="duplicateValues" dxfId="1344" priority="2028"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B315">
+    <cfRule type="duplicateValues" dxfId="1343" priority="2027"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B316">
-    <cfRule type="duplicateValues" dxfId="1341" priority="1998"/>
+    <cfRule type="duplicateValues" dxfId="1342" priority="2024"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B316">
-    <cfRule type="duplicateValues" dxfId="1340" priority="1997"/>
+    <cfRule type="duplicateValues" dxfId="1341" priority="2023"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B317">
-    <cfRule type="duplicateValues" dxfId="1339" priority="1994"/>
+    <cfRule type="duplicateValues" dxfId="1340" priority="2020"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B317">
-    <cfRule type="duplicateValues" dxfId="1338" priority="1993"/>
+    <cfRule type="duplicateValues" dxfId="1339" priority="2019"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B318">
-    <cfRule type="duplicateValues" dxfId="1337" priority="1990"/>
+    <cfRule type="duplicateValues" dxfId="1338" priority="2018"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B318">
-    <cfRule type="duplicateValues" dxfId="1336" priority="1989"/>
+    <cfRule type="duplicateValues" dxfId="1337" priority="2017"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B319">
-    <cfRule type="duplicateValues" dxfId="1335" priority="1988"/>
+    <cfRule type="duplicateValues" dxfId="1336" priority="2012"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B319">
-    <cfRule type="duplicateValues" dxfId="1334" priority="1987"/>
+    <cfRule type="duplicateValues" dxfId="1335" priority="2011"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B320">
-    <cfRule type="duplicateValues" dxfId="1333" priority="1982"/>
+    <cfRule type="duplicateValues" dxfId="1334" priority="2010"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B320">
-    <cfRule type="duplicateValues" dxfId="1332" priority="1981"/>
+    <cfRule type="duplicateValues" dxfId="1333" priority="2009"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B321">
-    <cfRule type="duplicateValues" dxfId="1331" priority="1980"/>
+    <cfRule type="duplicateValues" dxfId="1332" priority="2008"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B321">
-    <cfRule type="duplicateValues" dxfId="1330" priority="1979"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B322">
-    <cfRule type="duplicateValues" dxfId="1329" priority="1978"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B322">
-    <cfRule type="duplicateValues" dxfId="1328" priority="1977"/>
+    <cfRule type="duplicateValues" dxfId="1331" priority="2007"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B325">
+    <cfRule type="duplicateValues" dxfId="1330" priority="1998"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B325">
+    <cfRule type="duplicateValues" dxfId="1329" priority="1997"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B326">
-    <cfRule type="duplicateValues" dxfId="1327" priority="1968"/>
+    <cfRule type="duplicateValues" dxfId="1328" priority="1996"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B326">
-    <cfRule type="duplicateValues" dxfId="1326" priority="1967"/>
+    <cfRule type="duplicateValues" dxfId="1327" priority="1995"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B327">
-    <cfRule type="duplicateValues" dxfId="1325" priority="1966"/>
+    <cfRule type="duplicateValues" dxfId="1326" priority="1994"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B327">
-    <cfRule type="duplicateValues" dxfId="1324" priority="1965"/>
+    <cfRule type="duplicateValues" dxfId="1325" priority="1993"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B328">
-    <cfRule type="duplicateValues" dxfId="1323" priority="1964"/>
+    <cfRule type="duplicateValues" dxfId="1324" priority="1992"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B328">
-    <cfRule type="duplicateValues" dxfId="1322" priority="1963"/>
+    <cfRule type="duplicateValues" dxfId="1323" priority="1991"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B329">
-    <cfRule type="duplicateValues" dxfId="1321" priority="1962"/>
+    <cfRule type="duplicateValues" dxfId="1322" priority="1988"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B329">
-    <cfRule type="duplicateValues" dxfId="1320" priority="1961"/>
+    <cfRule type="duplicateValues" dxfId="1321" priority="1987"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B330">
-    <cfRule type="duplicateValues" dxfId="1319" priority="1958"/>
+    <cfRule type="duplicateValues" dxfId="1320" priority="1984"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B330">
-    <cfRule type="duplicateValues" dxfId="1318" priority="1957"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B331">
-    <cfRule type="duplicateValues" dxfId="1317" priority="1954"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B331">
-    <cfRule type="duplicateValues" dxfId="1316" priority="1953"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B333">
-    <cfRule type="duplicateValues" dxfId="1315" priority="1952"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B333">
-    <cfRule type="duplicateValues" dxfId="1314" priority="1951"/>
+    <cfRule type="duplicateValues" dxfId="1319" priority="1983"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B332">
+    <cfRule type="duplicateValues" dxfId="1318" priority="1982"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B332">
+    <cfRule type="duplicateValues" dxfId="1317" priority="1981"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B334">
+    <cfRule type="duplicateValues" dxfId="1316" priority="1980"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B334">
+    <cfRule type="duplicateValues" dxfId="1315" priority="1979"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B335">
-    <cfRule type="duplicateValues" dxfId="1313" priority="1950"/>
+    <cfRule type="duplicateValues" dxfId="1314" priority="1978"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B335">
-    <cfRule type="duplicateValues" dxfId="1312" priority="1949"/>
+    <cfRule type="duplicateValues" dxfId="1313" priority="1977"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B336">
-    <cfRule type="duplicateValues" dxfId="1311" priority="1948"/>
+    <cfRule type="duplicateValues" dxfId="1312" priority="1974"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B336">
-    <cfRule type="duplicateValues" dxfId="1310" priority="1947"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B337">
-    <cfRule type="duplicateValues" dxfId="1309" priority="1944"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B337">
-    <cfRule type="duplicateValues" dxfId="1308" priority="1943"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B340">
-    <cfRule type="duplicateValues" dxfId="1307" priority="1942"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B340">
-    <cfRule type="duplicateValues" dxfId="1306" priority="1941"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B343">
-    <cfRule type="duplicateValues" dxfId="1305" priority="1938"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B343">
-    <cfRule type="duplicateValues" dxfId="1304" priority="1937"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B345">
-    <cfRule type="duplicateValues" dxfId="1303" priority="1932"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B345">
-    <cfRule type="duplicateValues" dxfId="1302" priority="1931"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B348">
-    <cfRule type="duplicateValues" dxfId="1301" priority="1930"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B348">
-    <cfRule type="duplicateValues" dxfId="1300" priority="1929"/>
+    <cfRule type="duplicateValues" dxfId="1311" priority="1973"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B339">
+    <cfRule type="duplicateValues" dxfId="1310" priority="1972"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B339">
+    <cfRule type="duplicateValues" dxfId="1309" priority="1971"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B342">
+    <cfRule type="duplicateValues" dxfId="1308" priority="1968"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B342">
+    <cfRule type="duplicateValues" dxfId="1307" priority="1967"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B344">
+    <cfRule type="duplicateValues" dxfId="1306" priority="1962"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B344">
+    <cfRule type="duplicateValues" dxfId="1305" priority="1961"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B347">
+    <cfRule type="duplicateValues" dxfId="1304" priority="1960"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B347">
+    <cfRule type="duplicateValues" dxfId="1303" priority="1959"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B349">
+    <cfRule type="duplicateValues" dxfId="1302" priority="1958"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B349">
+    <cfRule type="duplicateValues" dxfId="1301" priority="1957"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B350">
-    <cfRule type="duplicateValues" dxfId="1299" priority="1928"/>
+    <cfRule type="duplicateValues" dxfId="1300" priority="1954"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B350">
-    <cfRule type="duplicateValues" dxfId="1298" priority="1927"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B351">
-    <cfRule type="duplicateValues" dxfId="1297" priority="1924"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B351">
-    <cfRule type="duplicateValues" dxfId="1296" priority="1923"/>
+    <cfRule type="duplicateValues" dxfId="1299" priority="1953"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B352">
+    <cfRule type="duplicateValues" dxfId="1298" priority="1950"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B352">
+    <cfRule type="duplicateValues" dxfId="1297" priority="1949"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B353">
-    <cfRule type="duplicateValues" dxfId="1295" priority="1920"/>
+    <cfRule type="duplicateValues" dxfId="1296" priority="1946"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B353">
-    <cfRule type="duplicateValues" dxfId="1294" priority="1919"/>
+    <cfRule type="duplicateValues" dxfId="1295" priority="1945"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B354">
-    <cfRule type="duplicateValues" dxfId="1293" priority="1916"/>
+    <cfRule type="duplicateValues" dxfId="1294" priority="1944"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B354">
-    <cfRule type="duplicateValues" dxfId="1292" priority="1915"/>
+    <cfRule type="duplicateValues" dxfId="1293" priority="1943"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B355">
-    <cfRule type="duplicateValues" dxfId="1291" priority="1914"/>
+    <cfRule type="duplicateValues" dxfId="1292" priority="1942"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B355">
-    <cfRule type="duplicateValues" dxfId="1290" priority="1913"/>
+    <cfRule type="duplicateValues" dxfId="1291" priority="1941"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B356">
-    <cfRule type="duplicateValues" dxfId="1289" priority="1912"/>
+    <cfRule type="duplicateValues" dxfId="1290" priority="1940"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B356">
-    <cfRule type="duplicateValues" dxfId="1288" priority="1911"/>
+    <cfRule type="duplicateValues" dxfId="1289" priority="1939"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B357">
-    <cfRule type="duplicateValues" dxfId="1287" priority="1910"/>
+    <cfRule type="duplicateValues" dxfId="1288" priority="1938"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B357">
-    <cfRule type="duplicateValues" dxfId="1286" priority="1909"/>
+    <cfRule type="duplicateValues" dxfId="1287" priority="1937"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B358">
-    <cfRule type="duplicateValues" dxfId="1285" priority="1908"/>
+    <cfRule type="duplicateValues" dxfId="1286" priority="1934"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B358">
-    <cfRule type="duplicateValues" dxfId="1284" priority="1907"/>
+    <cfRule type="duplicateValues" dxfId="1285" priority="1933"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B359">
-    <cfRule type="duplicateValues" dxfId="1283" priority="1904"/>
+    <cfRule type="duplicateValues" dxfId="1284" priority="1932"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B359">
-    <cfRule type="duplicateValues" dxfId="1282" priority="1903"/>
+    <cfRule type="duplicateValues" dxfId="1283" priority="1931"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B360">
-    <cfRule type="duplicateValues" dxfId="1281" priority="1902"/>
+    <cfRule type="duplicateValues" dxfId="1282" priority="1930"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B360">
-    <cfRule type="duplicateValues" dxfId="1280" priority="1901"/>
+    <cfRule type="duplicateValues" dxfId="1281" priority="1929"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B361">
-    <cfRule type="duplicateValues" dxfId="1279" priority="1900"/>
+    <cfRule type="duplicateValues" dxfId="1280" priority="1928"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B361">
-    <cfRule type="duplicateValues" dxfId="1278" priority="1899"/>
+    <cfRule type="duplicateValues" dxfId="1279" priority="1927"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B362">
-    <cfRule type="duplicateValues" dxfId="1277" priority="1898"/>
+    <cfRule type="duplicateValues" dxfId="1278" priority="1926"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B362">
-    <cfRule type="duplicateValues" dxfId="1276" priority="1897"/>
+    <cfRule type="duplicateValues" dxfId="1277" priority="1925"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B363">
-    <cfRule type="duplicateValues" dxfId="1275" priority="1896"/>
+    <cfRule type="duplicateValues" dxfId="1276" priority="1924"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B363">
-    <cfRule type="duplicateValues" dxfId="1274" priority="1895"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B364">
-    <cfRule type="duplicateValues" dxfId="1273" priority="1894"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B364">
-    <cfRule type="duplicateValues" dxfId="1272" priority="1893"/>
+    <cfRule type="duplicateValues" dxfId="1275" priority="1923"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B365">
+    <cfRule type="duplicateValues" dxfId="1274" priority="1918"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B365">
+    <cfRule type="duplicateValues" dxfId="1273" priority="1917"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B366">
-    <cfRule type="duplicateValues" dxfId="1271" priority="1888"/>
+    <cfRule type="duplicateValues" dxfId="1272" priority="1914"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B366">
-    <cfRule type="duplicateValues" dxfId="1270" priority="1887"/>
+    <cfRule type="duplicateValues" dxfId="1271" priority="1913"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B367">
-    <cfRule type="duplicateValues" dxfId="1269" priority="1884"/>
+    <cfRule type="duplicateValues" dxfId="1270" priority="1910"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B367">
-    <cfRule type="duplicateValues" dxfId="1268" priority="1883"/>
+    <cfRule type="duplicateValues" dxfId="1269" priority="1909"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B368">
-    <cfRule type="duplicateValues" dxfId="1267" priority="1880"/>
+    <cfRule type="duplicateValues" dxfId="1268" priority="1908"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B368">
-    <cfRule type="duplicateValues" dxfId="1266" priority="1879"/>
+    <cfRule type="duplicateValues" dxfId="1267" priority="1907"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B369">
-    <cfRule type="duplicateValues" dxfId="1265" priority="1878"/>
+    <cfRule type="duplicateValues" dxfId="1266" priority="1904"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B369">
-    <cfRule type="duplicateValues" dxfId="1264" priority="1877"/>
+    <cfRule type="duplicateValues" dxfId="1265" priority="1903"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B370">
-    <cfRule type="duplicateValues" dxfId="1263" priority="1874"/>
+    <cfRule type="duplicateValues" dxfId="1264" priority="1902"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B370">
-    <cfRule type="duplicateValues" dxfId="1262" priority="1873"/>
+    <cfRule type="duplicateValues" dxfId="1263" priority="1901"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B371">
-    <cfRule type="duplicateValues" dxfId="1261" priority="1872"/>
+    <cfRule type="duplicateValues" dxfId="1262" priority="1900"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B371">
-    <cfRule type="duplicateValues" dxfId="1260" priority="1871"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B372">
-    <cfRule type="duplicateValues" dxfId="1259" priority="1870"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B372">
-    <cfRule type="duplicateValues" dxfId="1258" priority="1869"/>
+    <cfRule type="duplicateValues" dxfId="1261" priority="1899"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B374">
+    <cfRule type="duplicateValues" dxfId="1260" priority="1894"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B374">
+    <cfRule type="duplicateValues" dxfId="1259" priority="1893"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B375">
-    <cfRule type="duplicateValues" dxfId="1257" priority="1864"/>
+    <cfRule type="duplicateValues" dxfId="1258" priority="1892"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B375">
-    <cfRule type="duplicateValues" dxfId="1256" priority="1863"/>
+    <cfRule type="duplicateValues" dxfId="1257" priority="1891"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B376">
-    <cfRule type="duplicateValues" dxfId="1255" priority="1862"/>
+    <cfRule type="duplicateValues" dxfId="1256" priority="1888"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B376">
-    <cfRule type="duplicateValues" dxfId="1254" priority="1861"/>
+    <cfRule type="duplicateValues" dxfId="1255" priority="1887"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B377">
-    <cfRule type="duplicateValues" dxfId="1253" priority="1858"/>
+    <cfRule type="duplicateValues" dxfId="1254" priority="1884"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B377">
-    <cfRule type="duplicateValues" dxfId="1252" priority="1857"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B378">
-    <cfRule type="duplicateValues" dxfId="1251" priority="1854"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B378">
-    <cfRule type="duplicateValues" dxfId="1250" priority="1853"/>
+    <cfRule type="duplicateValues" dxfId="1253" priority="1883"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B381">
+    <cfRule type="duplicateValues" dxfId="1252" priority="1882"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B381">
+    <cfRule type="duplicateValues" dxfId="1251" priority="1881"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B382">
-    <cfRule type="duplicateValues" dxfId="1249" priority="1852"/>
+    <cfRule type="duplicateValues" dxfId="1250" priority="1878"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B382">
-    <cfRule type="duplicateValues" dxfId="1248" priority="1851"/>
+    <cfRule type="duplicateValues" dxfId="1249" priority="1877"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B383">
-    <cfRule type="duplicateValues" dxfId="1247" priority="1848"/>
+    <cfRule type="duplicateValues" dxfId="1248" priority="1874"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B383">
-    <cfRule type="duplicateValues" dxfId="1246" priority="1847"/>
+    <cfRule type="duplicateValues" dxfId="1247" priority="1873"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B384">
-    <cfRule type="duplicateValues" dxfId="1245" priority="1844"/>
+    <cfRule type="duplicateValues" dxfId="1246" priority="1872"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B384">
-    <cfRule type="duplicateValues" dxfId="1244" priority="1843"/>
+    <cfRule type="duplicateValues" dxfId="1245" priority="1871"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B385">
-    <cfRule type="duplicateValues" dxfId="1243" priority="1842"/>
+    <cfRule type="duplicateValues" dxfId="1244" priority="1870"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B385">
-    <cfRule type="duplicateValues" dxfId="1242" priority="1841"/>
+    <cfRule type="duplicateValues" dxfId="1243" priority="1869"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B386">
-    <cfRule type="duplicateValues" dxfId="1241" priority="1840"/>
+    <cfRule type="duplicateValues" dxfId="1242" priority="1864"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B386">
-    <cfRule type="duplicateValues" dxfId="1240" priority="1839"/>
+    <cfRule type="duplicateValues" dxfId="1241" priority="1863"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B387">
-    <cfRule type="duplicateValues" dxfId="1239" priority="1834"/>
+    <cfRule type="duplicateValues" dxfId="1240" priority="1858"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B387">
-    <cfRule type="duplicateValues" dxfId="1238" priority="1833"/>
+    <cfRule type="duplicateValues" dxfId="1239" priority="1857"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B388">
-    <cfRule type="duplicateValues" dxfId="1237" priority="1828"/>
+    <cfRule type="duplicateValues" dxfId="1238" priority="1856"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B388">
-    <cfRule type="duplicateValues" dxfId="1236" priority="1827"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B389">
-    <cfRule type="duplicateValues" dxfId="1235" priority="1826"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B389">
-    <cfRule type="duplicateValues" dxfId="1234" priority="1825"/>
+    <cfRule type="duplicateValues" dxfId="1237" priority="1855"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B391">
+    <cfRule type="duplicateValues" dxfId="1236" priority="1854"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B391">
+    <cfRule type="duplicateValues" dxfId="1235" priority="1853"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B392">
-    <cfRule type="duplicateValues" dxfId="1233" priority="1824"/>
+    <cfRule type="duplicateValues" dxfId="1234" priority="1852"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B392">
-    <cfRule type="duplicateValues" dxfId="1232" priority="1823"/>
+    <cfRule type="duplicateValues" dxfId="1233" priority="1851"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B393">
-    <cfRule type="duplicateValues" dxfId="1231" priority="1822"/>
+    <cfRule type="duplicateValues" dxfId="1232" priority="1850"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B393">
-    <cfRule type="duplicateValues" dxfId="1230" priority="1821"/>
+    <cfRule type="duplicateValues" dxfId="1231" priority="1849"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B394">
-    <cfRule type="duplicateValues" dxfId="1229" priority="1820"/>
+    <cfRule type="duplicateValues" dxfId="1230" priority="1846"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B394">
-    <cfRule type="duplicateValues" dxfId="1228" priority="1819"/>
+    <cfRule type="duplicateValues" dxfId="1229" priority="1845"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B395">
-    <cfRule type="duplicateValues" dxfId="1227" priority="1816"/>
+    <cfRule type="duplicateValues" dxfId="1228" priority="1844"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B395">
-    <cfRule type="duplicateValues" dxfId="1226" priority="1815"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B396">
-    <cfRule type="duplicateValues" dxfId="1225" priority="1814"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B396">
-    <cfRule type="duplicateValues" dxfId="1224" priority="1813"/>
+    <cfRule type="duplicateValues" dxfId="1227" priority="1843"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B398">
+    <cfRule type="duplicateValues" dxfId="1226" priority="1842"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B398">
+    <cfRule type="duplicateValues" dxfId="1225" priority="1841"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B399">
-    <cfRule type="duplicateValues" dxfId="1223" priority="1812"/>
+    <cfRule type="duplicateValues" dxfId="1224" priority="1840"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B399">
-    <cfRule type="duplicateValues" dxfId="1222" priority="1811"/>
+    <cfRule type="duplicateValues" dxfId="1223" priority="1839"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B400">
-    <cfRule type="duplicateValues" dxfId="1221" priority="1810"/>
+    <cfRule type="duplicateValues" dxfId="1222" priority="1836"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B400">
-    <cfRule type="duplicateValues" dxfId="1220" priority="1809"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B401">
-    <cfRule type="duplicateValues" dxfId="1219" priority="1806"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B401">
-    <cfRule type="duplicateValues" dxfId="1218" priority="1805"/>
+    <cfRule type="duplicateValues" dxfId="1221" priority="1835"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B402">
+    <cfRule type="duplicateValues" dxfId="1220" priority="1834"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B402">
+    <cfRule type="duplicateValues" dxfId="1219" priority="1833"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B403">
-    <cfRule type="duplicateValues" dxfId="1217" priority="1804"/>
+    <cfRule type="duplicateValues" dxfId="1218" priority="1832"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B403">
-    <cfRule type="duplicateValues" dxfId="1216" priority="1803"/>
+    <cfRule type="duplicateValues" dxfId="1217" priority="1831"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B404">
-    <cfRule type="duplicateValues" dxfId="1215" priority="1802"/>
+    <cfRule type="duplicateValues" dxfId="1216" priority="1830"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B404">
-    <cfRule type="duplicateValues" dxfId="1214" priority="1801"/>
+    <cfRule type="duplicateValues" dxfId="1215" priority="1829"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B405">
-    <cfRule type="duplicateValues" dxfId="1213" priority="1800"/>
+    <cfRule type="duplicateValues" dxfId="1214" priority="1828"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B405">
-    <cfRule type="duplicateValues" dxfId="1212" priority="1799"/>
+    <cfRule type="duplicateValues" dxfId="1213" priority="1827"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B406">
-    <cfRule type="duplicateValues" dxfId="1211" priority="1798"/>
+    <cfRule type="duplicateValues" dxfId="1212" priority="1826"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B406">
-    <cfRule type="duplicateValues" dxfId="1210" priority="1797"/>
+    <cfRule type="duplicateValues" dxfId="1211" priority="1825"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B407">
-    <cfRule type="duplicateValues" dxfId="1209" priority="1796"/>
+    <cfRule type="duplicateValues" dxfId="1210" priority="1824"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B407">
-    <cfRule type="duplicateValues" dxfId="1208" priority="1795"/>
+    <cfRule type="duplicateValues" dxfId="1209" priority="1823"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B408">
-    <cfRule type="duplicateValues" dxfId="1207" priority="1794"/>
+    <cfRule type="duplicateValues" dxfId="1208" priority="1822"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B408">
-    <cfRule type="duplicateValues" dxfId="1206" priority="1793"/>
+    <cfRule type="duplicateValues" dxfId="1207" priority="1821"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B409">
-    <cfRule type="duplicateValues" dxfId="1205" priority="1792"/>
+    <cfRule type="duplicateValues" dxfId="1206" priority="1820"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B409">
-    <cfRule type="duplicateValues" dxfId="1204" priority="1791"/>
+    <cfRule type="duplicateValues" dxfId="1205" priority="1819"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B410">
-    <cfRule type="duplicateValues" dxfId="1203" priority="1790"/>
+    <cfRule type="duplicateValues" dxfId="1204" priority="1818"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B410">
-    <cfRule type="duplicateValues" dxfId="1202" priority="1789"/>
+    <cfRule type="duplicateValues" dxfId="1203" priority="1817"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B411">
-    <cfRule type="duplicateValues" dxfId="1201" priority="1788"/>
+    <cfRule type="duplicateValues" dxfId="1202" priority="1816"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B411">
-    <cfRule type="duplicateValues" dxfId="1200" priority="1787"/>
+    <cfRule type="duplicateValues" dxfId="1201" priority="1815"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B412">
-    <cfRule type="duplicateValues" dxfId="1199" priority="1786"/>
+    <cfRule type="duplicateValues" dxfId="1200" priority="1812"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B412">
-    <cfRule type="duplicateValues" dxfId="1198" priority="1785"/>
+    <cfRule type="duplicateValues" dxfId="1199" priority="1811"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B413">
-    <cfRule type="duplicateValues" dxfId="1197" priority="1782"/>
+    <cfRule type="duplicateValues" dxfId="1198" priority="1808"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B413">
-    <cfRule type="duplicateValues" dxfId="1196" priority="1781"/>
+    <cfRule type="duplicateValues" dxfId="1197" priority="1807"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B414">
-    <cfRule type="duplicateValues" dxfId="1195" priority="1778"/>
+    <cfRule type="duplicateValues" dxfId="1196" priority="1806"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B414">
-    <cfRule type="duplicateValues" dxfId="1194" priority="1777"/>
+    <cfRule type="duplicateValues" dxfId="1195" priority="1805"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B415">
-    <cfRule type="duplicateValues" dxfId="1193" priority="1776"/>
+    <cfRule type="duplicateValues" dxfId="1194" priority="1800"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B415">
-    <cfRule type="duplicateValues" dxfId="1192" priority="1775"/>
+    <cfRule type="duplicateValues" dxfId="1193" priority="1799"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B416">
-    <cfRule type="duplicateValues" dxfId="1191" priority="1770"/>
+    <cfRule type="duplicateValues" dxfId="1192" priority="1796"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B416">
-    <cfRule type="duplicateValues" dxfId="1190" priority="1769"/>
+    <cfRule type="duplicateValues" dxfId="1191" priority="1795"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B417">
-    <cfRule type="duplicateValues" dxfId="1189" priority="1766"/>
+    <cfRule type="duplicateValues" dxfId="1190" priority="1794"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B417">
-    <cfRule type="duplicateValues" dxfId="1188" priority="1765"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B418">
-    <cfRule type="duplicateValues" dxfId="1187" priority="1764"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B418">
-    <cfRule type="duplicateValues" dxfId="1186" priority="1763"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B420">
-    <cfRule type="duplicateValues" dxfId="1185" priority="1762"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B420">
-    <cfRule type="duplicateValues" dxfId="1184" priority="1761"/>
+    <cfRule type="duplicateValues" dxfId="1189" priority="1793"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B419">
+    <cfRule type="duplicateValues" dxfId="1188" priority="1792"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B419">
+    <cfRule type="duplicateValues" dxfId="1187" priority="1791"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B422">
+    <cfRule type="duplicateValues" dxfId="1186" priority="1790"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B422">
+    <cfRule type="duplicateValues" dxfId="1185" priority="1789"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B421">
+    <cfRule type="duplicateValues" dxfId="1184" priority="1788"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B421">
+    <cfRule type="duplicateValues" dxfId="1183" priority="1787"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B423">
-    <cfRule type="duplicateValues" dxfId="1183" priority="1760"/>
+    <cfRule type="duplicateValues" dxfId="1182" priority="1784"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B423">
-    <cfRule type="duplicateValues" dxfId="1182" priority="1759"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B422">
-    <cfRule type="duplicateValues" dxfId="1181" priority="1758"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B422">
-    <cfRule type="duplicateValues" dxfId="1180" priority="1757"/>
+    <cfRule type="duplicateValues" dxfId="1181" priority="1783"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B424">
-    <cfRule type="duplicateValues" dxfId="1179" priority="1754"/>
+    <cfRule type="duplicateValues" dxfId="1180" priority="1782"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B424">
-    <cfRule type="duplicateValues" dxfId="1178" priority="1753"/>
+    <cfRule type="duplicateValues" dxfId="1179" priority="1781"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B425">
-    <cfRule type="duplicateValues" dxfId="1177" priority="1752"/>
+    <cfRule type="duplicateValues" dxfId="1178" priority="1780"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B425">
-    <cfRule type="duplicateValues" dxfId="1176" priority="1751"/>
+    <cfRule type="duplicateValues" dxfId="1177" priority="1779"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B426">
-    <cfRule type="duplicateValues" dxfId="1175" priority="1750"/>
+    <cfRule type="duplicateValues" dxfId="1176" priority="1778"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B426">
-    <cfRule type="duplicateValues" dxfId="1174" priority="1749"/>
+    <cfRule type="duplicateValues" dxfId="1175" priority="1777"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B427">
-    <cfRule type="duplicateValues" dxfId="1173" priority="1748"/>
+    <cfRule type="duplicateValues" dxfId="1174" priority="1776"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B427">
-    <cfRule type="duplicateValues" dxfId="1172" priority="1747"/>
+    <cfRule type="duplicateValues" dxfId="1173" priority="1775"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B428">
-    <cfRule type="duplicateValues" dxfId="1171" priority="1746"/>
+    <cfRule type="duplicateValues" dxfId="1172" priority="1774"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B428">
-    <cfRule type="duplicateValues" dxfId="1170" priority="1745"/>
+    <cfRule type="duplicateValues" dxfId="1171" priority="1773"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B429">
-    <cfRule type="duplicateValues" dxfId="1169" priority="1744"/>
+    <cfRule type="duplicateValues" dxfId="1170" priority="1772"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B429">
-    <cfRule type="duplicateValues" dxfId="1168" priority="1743"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B430">
-    <cfRule type="duplicateValues" dxfId="1167" priority="1742"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B430">
-    <cfRule type="duplicateValues" dxfId="1166" priority="1741"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B433">
-    <cfRule type="duplicateValues" dxfId="1165" priority="1738"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B433">
-    <cfRule type="duplicateValues" dxfId="1164" priority="1737"/>
+    <cfRule type="duplicateValues" dxfId="1169" priority="1771"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B432">
-    <cfRule type="duplicateValues" dxfId="1163" priority="1736"/>
+    <cfRule type="duplicateValues" dxfId="1168" priority="1768"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B432">
-    <cfRule type="duplicateValues" dxfId="1162" priority="1735"/>
+    <cfRule type="duplicateValues" dxfId="1167" priority="1767"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B431">
+    <cfRule type="duplicateValues" dxfId="1166" priority="1766"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B431">
+    <cfRule type="duplicateValues" dxfId="1165" priority="1765"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B434">
+    <cfRule type="duplicateValues" dxfId="1164" priority="1764"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B434">
+    <cfRule type="duplicateValues" dxfId="1163" priority="1763"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B435">
-    <cfRule type="duplicateValues" dxfId="1161" priority="1734"/>
+    <cfRule type="duplicateValues" dxfId="1162" priority="1760"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B435">
-    <cfRule type="duplicateValues" dxfId="1160" priority="1733"/>
+    <cfRule type="duplicateValues" dxfId="1161" priority="1759"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B437">
+    <cfRule type="duplicateValues" dxfId="1160" priority="1756"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B437">
+    <cfRule type="duplicateValues" dxfId="1159" priority="1755"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B436">
-    <cfRule type="duplicateValues" dxfId="1159" priority="1730"/>
+    <cfRule type="duplicateValues" dxfId="1158" priority="1754"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B436">
-    <cfRule type="duplicateValues" dxfId="1158" priority="1729"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B438">
-    <cfRule type="duplicateValues" dxfId="1157" priority="1726"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B438">
-    <cfRule type="duplicateValues" dxfId="1156" priority="1725"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B437">
-    <cfRule type="duplicateValues" dxfId="1155" priority="1724"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B437">
-    <cfRule type="duplicateValues" dxfId="1154" priority="1723"/>
+    <cfRule type="duplicateValues" dxfId="1157" priority="1753"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B440">
+    <cfRule type="duplicateValues" dxfId="1156" priority="1752"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B440">
+    <cfRule type="duplicateValues" dxfId="1155" priority="1751"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B441">
-    <cfRule type="duplicateValues" dxfId="1153" priority="1722"/>
+    <cfRule type="duplicateValues" dxfId="1154" priority="1750"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B441">
-    <cfRule type="duplicateValues" dxfId="1152" priority="1721"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B442">
-    <cfRule type="duplicateValues" dxfId="1151" priority="1720"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B442">
-    <cfRule type="duplicateValues" dxfId="1150" priority="1719"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B444">
-    <cfRule type="duplicateValues" dxfId="1149" priority="1718"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B444">
-    <cfRule type="duplicateValues" dxfId="1148" priority="1717"/>
+    <cfRule type="duplicateValues" dxfId="1153" priority="1749"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B443">
+    <cfRule type="duplicateValues" dxfId="1152" priority="1748"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B443">
+    <cfRule type="duplicateValues" dxfId="1151" priority="1747"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B445">
+    <cfRule type="duplicateValues" dxfId="1150" priority="1746"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B445">
+    <cfRule type="duplicateValues" dxfId="1149" priority="1745"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B446">
-    <cfRule type="duplicateValues" dxfId="1147" priority="1716"/>
+    <cfRule type="duplicateValues" dxfId="1148" priority="1742"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B446">
-    <cfRule type="duplicateValues" dxfId="1146" priority="1715"/>
+    <cfRule type="duplicateValues" dxfId="1147" priority="1741"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B447">
-    <cfRule type="duplicateValues" dxfId="1145" priority="1712"/>
+    <cfRule type="duplicateValues" dxfId="1146" priority="1740"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B447">
-    <cfRule type="duplicateValues" dxfId="1144" priority="1711"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B448">
-    <cfRule type="duplicateValues" dxfId="1143" priority="1710"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B448">
-    <cfRule type="duplicateValues" dxfId="1142" priority="1709"/>
+    <cfRule type="duplicateValues" dxfId="1145" priority="1739"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B449">
+    <cfRule type="duplicateValues" dxfId="1144" priority="1738"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B449">
+    <cfRule type="duplicateValues" dxfId="1143" priority="1737"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B450">
-    <cfRule type="duplicateValues" dxfId="1141" priority="1708"/>
+    <cfRule type="duplicateValues" dxfId="1142" priority="1736"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B450">
-    <cfRule type="duplicateValues" dxfId="1140" priority="1707"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B451">
-    <cfRule type="duplicateValues" dxfId="1139" priority="1706"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B451">
-    <cfRule type="duplicateValues" dxfId="1138" priority="1705"/>
+    <cfRule type="duplicateValues" dxfId="1141" priority="1735"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B452">
+    <cfRule type="duplicateValues" dxfId="1140" priority="1734"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B452">
+    <cfRule type="duplicateValues" dxfId="1139" priority="1733"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B453">
-    <cfRule type="duplicateValues" dxfId="1137" priority="1704"/>
+    <cfRule type="duplicateValues" dxfId="1138" priority="1730"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B453">
-    <cfRule type="duplicateValues" dxfId="1136" priority="1703"/>
+    <cfRule type="duplicateValues" dxfId="1137" priority="1729"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B454">
-    <cfRule type="duplicateValues" dxfId="1135" priority="1700"/>
+    <cfRule type="duplicateValues" dxfId="1136" priority="1724"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B454">
-    <cfRule type="duplicateValues" dxfId="1134" priority="1699"/>
+    <cfRule type="duplicateValues" dxfId="1135" priority="1723"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B455">
-    <cfRule type="duplicateValues" dxfId="1133" priority="1694"/>
+    <cfRule type="duplicateValues" dxfId="1134" priority="1722"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B455">
-    <cfRule type="duplicateValues" dxfId="1132" priority="1693"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B456">
-    <cfRule type="duplicateValues" dxfId="1131" priority="1692"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B456">
-    <cfRule type="duplicateValues" dxfId="1130" priority="1691"/>
+    <cfRule type="duplicateValues" dxfId="1133" priority="1721"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B457">
+    <cfRule type="duplicateValues" dxfId="1132" priority="1718"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B457">
+    <cfRule type="duplicateValues" dxfId="1131" priority="1717"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B458">
-    <cfRule type="duplicateValues" dxfId="1129" priority="1688"/>
+    <cfRule type="duplicateValues" dxfId="1130" priority="1716"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B458">
-    <cfRule type="duplicateValues" dxfId="1128" priority="1687"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B459">
-    <cfRule type="duplicateValues" dxfId="1127" priority="1686"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B459">
-    <cfRule type="duplicateValues" dxfId="1126" priority="1685"/>
+    <cfRule type="duplicateValues" dxfId="1129" priority="1715"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B460">
+    <cfRule type="duplicateValues" dxfId="1128" priority="1714"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B460">
+    <cfRule type="duplicateValues" dxfId="1127" priority="1713"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B461">
-    <cfRule type="duplicateValues" dxfId="1125" priority="1684"/>
+    <cfRule type="duplicateValues" dxfId="1126" priority="1712"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B461">
-    <cfRule type="duplicateValues" dxfId="1124" priority="1683"/>
+    <cfRule type="duplicateValues" dxfId="1125" priority="1711"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B462">
-    <cfRule type="duplicateValues" dxfId="1123" priority="1682"/>
+    <cfRule type="duplicateValues" dxfId="1124" priority="1708"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B462">
-    <cfRule type="duplicateValues" dxfId="1122" priority="1681"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B463">
-    <cfRule type="duplicateValues" dxfId="1121" priority="1678"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B463">
-    <cfRule type="duplicateValues" dxfId="1120" priority="1677"/>
+    <cfRule type="duplicateValues" dxfId="1123" priority="1707"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B464">
+    <cfRule type="duplicateValues" dxfId="1122" priority="1706"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B464">
+    <cfRule type="duplicateValues" dxfId="1121" priority="1705"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B465">
-    <cfRule type="duplicateValues" dxfId="1119" priority="1676"/>
+    <cfRule type="duplicateValues" dxfId="1120" priority="1704"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B465">
-    <cfRule type="duplicateValues" dxfId="1118" priority="1675"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B466">
-    <cfRule type="duplicateValues" dxfId="1117" priority="1674"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B466">
-    <cfRule type="duplicateValues" dxfId="1116" priority="1673"/>
+    <cfRule type="duplicateValues" dxfId="1119" priority="1703"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B469">
+    <cfRule type="duplicateValues" dxfId="1118" priority="1702"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B469">
+    <cfRule type="duplicateValues" dxfId="1117" priority="1701"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B470">
-    <cfRule type="duplicateValues" dxfId="1115" priority="1672"/>
+    <cfRule type="duplicateValues" dxfId="1116" priority="1700"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B470">
-    <cfRule type="duplicateValues" dxfId="1114" priority="1671"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B471">
-    <cfRule type="duplicateValues" dxfId="1113" priority="1670"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B471">
-    <cfRule type="duplicateValues" dxfId="1112" priority="1669"/>
+    <cfRule type="duplicateValues" dxfId="1115" priority="1699"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B473">
+    <cfRule type="duplicateValues" dxfId="1114" priority="1696"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B473">
+    <cfRule type="duplicateValues" dxfId="1113" priority="1695"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B474">
-    <cfRule type="duplicateValues" dxfId="1111" priority="1666"/>
+    <cfRule type="duplicateValues" dxfId="1112" priority="1694"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B474">
-    <cfRule type="duplicateValues" dxfId="1110" priority="1665"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B475">
-    <cfRule type="duplicateValues" dxfId="1109" priority="1664"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B475">
-    <cfRule type="duplicateValues" dxfId="1108" priority="1663"/>
+    <cfRule type="duplicateValues" dxfId="1111" priority="1693"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B477">
+    <cfRule type="duplicateValues" dxfId="1110" priority="1692"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B477">
+    <cfRule type="duplicateValues" dxfId="1109" priority="1691"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B478">
-    <cfRule type="duplicateValues" dxfId="1107" priority="1662"/>
+    <cfRule type="duplicateValues" dxfId="1108" priority="1688"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B478">
-    <cfRule type="duplicateValues" dxfId="1106" priority="1661"/>
+    <cfRule type="duplicateValues" dxfId="1107" priority="1687"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B479">
-    <cfRule type="duplicateValues" dxfId="1105" priority="1658"/>
+    <cfRule type="duplicateValues" dxfId="1106" priority="1684"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B479">
-    <cfRule type="duplicateValues" dxfId="1104" priority="1657"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B480">
-    <cfRule type="duplicateValues" dxfId="1103" priority="1654"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B480">
-    <cfRule type="duplicateValues" dxfId="1102" priority="1653"/>
+    <cfRule type="duplicateValues" dxfId="1105" priority="1683"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B481">
+    <cfRule type="duplicateValues" dxfId="1104" priority="1676"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B481">
+    <cfRule type="duplicateValues" dxfId="1103" priority="1675"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B482">
-    <cfRule type="duplicateValues" dxfId="1101" priority="1646"/>
+    <cfRule type="duplicateValues" dxfId="1102" priority="1674"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B482">
-    <cfRule type="duplicateValues" dxfId="1100" priority="1645"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B483">
-    <cfRule type="duplicateValues" dxfId="1099" priority="1644"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B483">
-    <cfRule type="duplicateValues" dxfId="1098" priority="1643"/>
+    <cfRule type="duplicateValues" dxfId="1101" priority="1673"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B484">
+    <cfRule type="duplicateValues" dxfId="1100" priority="1672"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B484">
+    <cfRule type="duplicateValues" dxfId="1099" priority="1671"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B485">
-    <cfRule type="duplicateValues" dxfId="1097" priority="1642"/>
+    <cfRule type="duplicateValues" dxfId="1098" priority="1668"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B485">
-    <cfRule type="duplicateValues" dxfId="1096" priority="1641"/>
+    <cfRule type="duplicateValues" dxfId="1097" priority="1667"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B487">
+    <cfRule type="duplicateValues" dxfId="1096" priority="1664"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B487">
+    <cfRule type="duplicateValues" dxfId="1095" priority="1663"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B486">
-    <cfRule type="duplicateValues" dxfId="1095" priority="1638"/>
+    <cfRule type="duplicateValues" dxfId="1094" priority="1662"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B486">
-    <cfRule type="duplicateValues" dxfId="1094" priority="1637"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B488">
-    <cfRule type="duplicateValues" dxfId="1093" priority="1634"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B488">
-    <cfRule type="duplicateValues" dxfId="1092" priority="1633"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B487">
-    <cfRule type="duplicateValues" dxfId="1091" priority="1632"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B487">
-    <cfRule type="duplicateValues" dxfId="1090" priority="1631"/>
+    <cfRule type="duplicateValues" dxfId="1093" priority="1661"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B489">
+    <cfRule type="duplicateValues" dxfId="1092" priority="1658"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B489">
+    <cfRule type="duplicateValues" dxfId="1091" priority="1657"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B490">
-    <cfRule type="duplicateValues" dxfId="1089" priority="1628"/>
+    <cfRule type="duplicateValues" dxfId="1090" priority="1656"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B490">
-    <cfRule type="duplicateValues" dxfId="1088" priority="1627"/>
+    <cfRule type="duplicateValues" dxfId="1089" priority="1655"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B491">
-    <cfRule type="duplicateValues" dxfId="1087" priority="1626"/>
+    <cfRule type="duplicateValues" dxfId="1088" priority="1650"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B491">
-    <cfRule type="duplicateValues" dxfId="1086" priority="1625"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B492">
-    <cfRule type="duplicateValues" dxfId="1085" priority="1620"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B492">
-    <cfRule type="duplicateValues" dxfId="1084" priority="1619"/>
+    <cfRule type="duplicateValues" dxfId="1087" priority="1649"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B496">
+    <cfRule type="duplicateValues" dxfId="1086" priority="1640"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B496">
+    <cfRule type="duplicateValues" dxfId="1085" priority="1639"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B497">
-    <cfRule type="duplicateValues" dxfId="1083" priority="1610"/>
+    <cfRule type="duplicateValues" dxfId="1084" priority="1638"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B497">
-    <cfRule type="duplicateValues" dxfId="1082" priority="1609"/>
+    <cfRule type="duplicateValues" dxfId="1083" priority="1637"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B499">
+    <cfRule type="duplicateValues" dxfId="1082" priority="1636"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B499">
+    <cfRule type="duplicateValues" dxfId="1081" priority="1635"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B498">
-    <cfRule type="duplicateValues" dxfId="1081" priority="1608"/>
+    <cfRule type="duplicateValues" dxfId="1080" priority="1634"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B498">
-    <cfRule type="duplicateValues" dxfId="1080" priority="1607"/>
+    <cfRule type="duplicateValues" dxfId="1079" priority="1633"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B500">
-    <cfRule type="duplicateValues" dxfId="1079" priority="1606"/>
+    <cfRule type="duplicateValues" dxfId="1078" priority="1630"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B500">
-    <cfRule type="duplicateValues" dxfId="1078" priority="1605"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B499">
-    <cfRule type="duplicateValues" dxfId="1077" priority="1604"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B499">
-    <cfRule type="duplicateValues" dxfId="1076" priority="1603"/>
+    <cfRule type="duplicateValues" dxfId="1077" priority="1629"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B501">
-    <cfRule type="duplicateValues" dxfId="1075" priority="1600"/>
+    <cfRule type="duplicateValues" dxfId="1076" priority="1628"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B501">
-    <cfRule type="duplicateValues" dxfId="1074" priority="1599"/>
+    <cfRule type="duplicateValues" dxfId="1075" priority="1627"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B502">
-    <cfRule type="duplicateValues" dxfId="1073" priority="1598"/>
+    <cfRule type="duplicateValues" dxfId="1074" priority="1626"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B502">
-    <cfRule type="duplicateValues" dxfId="1072" priority="1597"/>
+    <cfRule type="duplicateValues" dxfId="1073" priority="1625"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B503">
-    <cfRule type="duplicateValues" dxfId="1071" priority="1596"/>
+    <cfRule type="duplicateValues" dxfId="1072" priority="1624"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B503">
-    <cfRule type="duplicateValues" dxfId="1070" priority="1595"/>
+    <cfRule type="duplicateValues" dxfId="1071" priority="1623"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B504">
-    <cfRule type="duplicateValues" dxfId="1069" priority="1594"/>
+    <cfRule type="duplicateValues" dxfId="1070" priority="1622"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B504">
-    <cfRule type="duplicateValues" dxfId="1068" priority="1593"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B505">
-    <cfRule type="duplicateValues" dxfId="1067" priority="1592"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B505">
-    <cfRule type="duplicateValues" dxfId="1066" priority="1591"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B507">
-    <cfRule type="duplicateValues" dxfId="1065" priority="1588"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B507">
-    <cfRule type="duplicateValues" dxfId="1064" priority="1587"/>
+    <cfRule type="duplicateValues" dxfId="1069" priority="1621"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B506">
+    <cfRule type="duplicateValues" dxfId="1068" priority="1618"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B506">
+    <cfRule type="duplicateValues" dxfId="1067" priority="1617"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B508">
+    <cfRule type="duplicateValues" dxfId="1066" priority="1612"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B508">
+    <cfRule type="duplicateValues" dxfId="1065" priority="1611"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B509">
-    <cfRule type="duplicateValues" dxfId="1063" priority="1582"/>
+    <cfRule type="duplicateValues" dxfId="1064" priority="1610"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B509">
-    <cfRule type="duplicateValues" dxfId="1062" priority="1581"/>
+    <cfRule type="duplicateValues" dxfId="1063" priority="1609"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B510">
-    <cfRule type="duplicateValues" dxfId="1061" priority="1580"/>
+    <cfRule type="duplicateValues" dxfId="1062" priority="1608"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B510">
-    <cfRule type="duplicateValues" dxfId="1060" priority="1579"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B511">
-    <cfRule type="duplicateValues" dxfId="1059" priority="1578"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B511">
-    <cfRule type="duplicateValues" dxfId="1058" priority="1577"/>
+    <cfRule type="duplicateValues" dxfId="1061" priority="1607"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B512">
+    <cfRule type="duplicateValues" dxfId="1060" priority="1604"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B512">
+    <cfRule type="duplicateValues" dxfId="1059" priority="1603"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B513">
-    <cfRule type="duplicateValues" dxfId="1057" priority="1574"/>
+    <cfRule type="duplicateValues" dxfId="1058" priority="1602"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B513">
-    <cfRule type="duplicateValues" dxfId="1056" priority="1573"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B514">
-    <cfRule type="duplicateValues" dxfId="1055" priority="1572"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B514">
-    <cfRule type="duplicateValues" dxfId="1054" priority="1571"/>
+    <cfRule type="duplicateValues" dxfId="1057" priority="1601"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B515">
+    <cfRule type="duplicateValues" dxfId="1056" priority="1600"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B515">
+    <cfRule type="duplicateValues" dxfId="1055" priority="1599"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B516">
-    <cfRule type="duplicateValues" dxfId="1053" priority="1570"/>
+    <cfRule type="duplicateValues" dxfId="1054" priority="1592"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B516">
-    <cfRule type="duplicateValues" dxfId="1052" priority="1569"/>
+    <cfRule type="duplicateValues" dxfId="1053" priority="1591"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B517">
-    <cfRule type="duplicateValues" dxfId="1051" priority="1562"/>
+    <cfRule type="duplicateValues" dxfId="1052" priority="1588"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B517">
-    <cfRule type="duplicateValues" dxfId="1050" priority="1561"/>
+    <cfRule type="duplicateValues" dxfId="1051" priority="1587"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B518">
-    <cfRule type="duplicateValues" dxfId="1049" priority="1558"/>
+    <cfRule type="duplicateValues" dxfId="1050" priority="1584"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B518">
-    <cfRule type="duplicateValues" dxfId="1048" priority="1557"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B519">
-    <cfRule type="duplicateValues" dxfId="1047" priority="1554"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B519">
-    <cfRule type="duplicateValues" dxfId="1046" priority="1553"/>
+    <cfRule type="duplicateValues" dxfId="1049" priority="1583"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B522">
+    <cfRule type="duplicateValues" dxfId="1048" priority="1580"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B522">
+    <cfRule type="duplicateValues" dxfId="1047" priority="1579"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B520">
+    <cfRule type="duplicateValues" dxfId="1046" priority="1578"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B520">
+    <cfRule type="duplicateValues" dxfId="1045" priority="1577"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B521">
+    <cfRule type="duplicateValues" dxfId="1044" priority="1574"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B521">
+    <cfRule type="duplicateValues" dxfId="1043" priority="1573"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B523">
-    <cfRule type="duplicateValues" dxfId="1045" priority="1550"/>
+    <cfRule type="duplicateValues" dxfId="1042" priority="1568"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B523">
-    <cfRule type="duplicateValues" dxfId="1044" priority="1549"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B521">
-    <cfRule type="duplicateValues" dxfId="1043" priority="1548"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B521">
-    <cfRule type="duplicateValues" dxfId="1042" priority="1547"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B522">
-    <cfRule type="duplicateValues" dxfId="1041" priority="1544"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B522">
-    <cfRule type="duplicateValues" dxfId="1040" priority="1543"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B524">
-    <cfRule type="duplicateValues" dxfId="1039" priority="1538"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B524">
-    <cfRule type="duplicateValues" dxfId="1038" priority="1537"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B528">
-    <cfRule type="duplicateValues" dxfId="1037" priority="1532"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B528">
-    <cfRule type="duplicateValues" dxfId="1036" priority="1531"/>
+    <cfRule type="duplicateValues" dxfId="1041" priority="1567"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B527">
-    <cfRule type="duplicateValues" dxfId="1035" priority="1530"/>
+    <cfRule type="duplicateValues" dxfId="1040" priority="1562"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B527">
-    <cfRule type="duplicateValues" dxfId="1034" priority="1529"/>
+    <cfRule type="duplicateValues" dxfId="1039" priority="1561"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B526">
-    <cfRule type="duplicateValues" dxfId="1033" priority="1528"/>
+    <cfRule type="duplicateValues" dxfId="1038" priority="1560"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B526">
-    <cfRule type="duplicateValues" dxfId="1032" priority="1527"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B531">
-    <cfRule type="duplicateValues" dxfId="1031" priority="1526"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B531">
-    <cfRule type="duplicateValues" dxfId="1030" priority="1525"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B537">
-    <cfRule type="duplicateValues" dxfId="1029" priority="1524"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B537">
-    <cfRule type="duplicateValues" dxfId="1028" priority="1523"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B539">
-    <cfRule type="duplicateValues" dxfId="1027" priority="1522"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B539">
-    <cfRule type="duplicateValues" dxfId="1026" priority="1521"/>
+    <cfRule type="duplicateValues" dxfId="1037" priority="1559"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B525">
+    <cfRule type="duplicateValues" dxfId="1036" priority="1558"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B525">
+    <cfRule type="duplicateValues" dxfId="1035" priority="1557"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B530">
+    <cfRule type="duplicateValues" dxfId="1034" priority="1556"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B530">
+    <cfRule type="duplicateValues" dxfId="1033" priority="1555"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B536">
+    <cfRule type="duplicateValues" dxfId="1032" priority="1554"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B536">
+    <cfRule type="duplicateValues" dxfId="1031" priority="1553"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B538">
+    <cfRule type="duplicateValues" dxfId="1030" priority="1552"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B538">
+    <cfRule type="duplicateValues" dxfId="1029" priority="1551"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B540">
+    <cfRule type="duplicateValues" dxfId="1028" priority="1548"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B540">
+    <cfRule type="duplicateValues" dxfId="1027" priority="1547"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B543">
+    <cfRule type="duplicateValues" dxfId="1026" priority="1544"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B543">
+    <cfRule type="duplicateValues" dxfId="1025" priority="1543"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B541">
-    <cfRule type="duplicateValues" dxfId="1025" priority="1518"/>
+    <cfRule type="duplicateValues" dxfId="1024" priority="1542"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B541">
-    <cfRule type="duplicateValues" dxfId="1024" priority="1517"/>
+    <cfRule type="duplicateValues" dxfId="1023" priority="1541"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B542">
+    <cfRule type="duplicateValues" dxfId="1022" priority="1536"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B542">
+    <cfRule type="duplicateValues" dxfId="1021" priority="1535"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B544">
-    <cfRule type="duplicateValues" dxfId="1023" priority="1514"/>
+    <cfRule type="duplicateValues" dxfId="1020" priority="1532"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B544">
-    <cfRule type="duplicateValues" dxfId="1022" priority="1513"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B542">
-    <cfRule type="duplicateValues" dxfId="1021" priority="1512"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B542">
-    <cfRule type="duplicateValues" dxfId="1020" priority="1511"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B543">
-    <cfRule type="duplicateValues" dxfId="1019" priority="1506"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B543">
-    <cfRule type="duplicateValues" dxfId="1018" priority="1505"/>
+    <cfRule type="duplicateValues" dxfId="1019" priority="1531"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B545">
-    <cfRule type="duplicateValues" dxfId="1017" priority="1502"/>
+    <cfRule type="duplicateValues" dxfId="1018" priority="1528"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B545">
-    <cfRule type="duplicateValues" dxfId="1016" priority="1501"/>
+    <cfRule type="duplicateValues" dxfId="1017" priority="1527"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B546">
-    <cfRule type="duplicateValues" dxfId="1015" priority="1498"/>
+    <cfRule type="duplicateValues" dxfId="1016" priority="1526"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B546">
-    <cfRule type="duplicateValues" dxfId="1014" priority="1497"/>
+    <cfRule type="duplicateValues" dxfId="1015" priority="1525"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B548">
+    <cfRule type="duplicateValues" dxfId="1014" priority="1524"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B548">
+    <cfRule type="duplicateValues" dxfId="1013" priority="1523"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B547">
-    <cfRule type="duplicateValues" dxfId="1013" priority="1496"/>
+    <cfRule type="duplicateValues" dxfId="1012" priority="1522"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B547">
-    <cfRule type="duplicateValues" dxfId="1012" priority="1495"/>
+    <cfRule type="duplicateValues" dxfId="1011" priority="1521"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B549">
-    <cfRule type="duplicateValues" dxfId="1011" priority="1494"/>
+    <cfRule type="duplicateValues" dxfId="1010" priority="1520"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B549">
-    <cfRule type="duplicateValues" dxfId="1010" priority="1493"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B548">
-    <cfRule type="duplicateValues" dxfId="1009" priority="1492"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B548">
-    <cfRule type="duplicateValues" dxfId="1008" priority="1491"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B550">
-    <cfRule type="duplicateValues" dxfId="1007" priority="1490"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B550">
-    <cfRule type="duplicateValues" dxfId="1006" priority="1489"/>
+    <cfRule type="duplicateValues" dxfId="1009" priority="1519"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B551">
+    <cfRule type="duplicateValues" dxfId="1008" priority="1516"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B551">
+    <cfRule type="duplicateValues" dxfId="1007" priority="1515"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B552">
-    <cfRule type="duplicateValues" dxfId="1005" priority="1486"/>
+    <cfRule type="duplicateValues" dxfId="1006" priority="1514"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B552">
-    <cfRule type="duplicateValues" dxfId="1004" priority="1485"/>
+    <cfRule type="duplicateValues" dxfId="1005" priority="1513"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B553">
-    <cfRule type="duplicateValues" dxfId="1003" priority="1484"/>
+    <cfRule type="duplicateValues" dxfId="1004" priority="1508"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B553">
-    <cfRule type="duplicateValues" dxfId="1002" priority="1483"/>
+    <cfRule type="duplicateValues" dxfId="1003" priority="1507"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B554">
-    <cfRule type="duplicateValues" dxfId="1001" priority="1478"/>
+    <cfRule type="duplicateValues" dxfId="1002" priority="1506"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B554">
-    <cfRule type="duplicateValues" dxfId="1000" priority="1477"/>
+    <cfRule type="duplicateValues" dxfId="1001" priority="1505"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B555">
-    <cfRule type="duplicateValues" dxfId="999" priority="1476"/>
+    <cfRule type="duplicateValues" dxfId="1000" priority="1500"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B555">
-    <cfRule type="duplicateValues" dxfId="998" priority="1475"/>
+    <cfRule type="duplicateValues" dxfId="999" priority="1499"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B556">
-    <cfRule type="duplicateValues" dxfId="997" priority="1470"/>
+    <cfRule type="duplicateValues" dxfId="998" priority="1498"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B556">
-    <cfRule type="duplicateValues" dxfId="996" priority="1469"/>
+    <cfRule type="duplicateValues" dxfId="997" priority="1497"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B557">
-    <cfRule type="duplicateValues" dxfId="995" priority="1468"/>
+    <cfRule type="duplicateValues" dxfId="996" priority="1494"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B557">
-    <cfRule type="duplicateValues" dxfId="994" priority="1467"/>
+    <cfRule type="duplicateValues" dxfId="995" priority="1493"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B558">
-    <cfRule type="duplicateValues" dxfId="993" priority="1464"/>
+    <cfRule type="duplicateValues" dxfId="994" priority="1492"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B558">
-    <cfRule type="duplicateValues" dxfId="992" priority="1463"/>
+    <cfRule type="duplicateValues" dxfId="993" priority="1491"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B559">
-    <cfRule type="duplicateValues" dxfId="991" priority="1462"/>
+    <cfRule type="duplicateValues" dxfId="992" priority="1488"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B559">
-    <cfRule type="duplicateValues" dxfId="990" priority="1461"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B560">
-    <cfRule type="duplicateValues" dxfId="989" priority="1458"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B560">
-    <cfRule type="duplicateValues" dxfId="988" priority="1457"/>
+    <cfRule type="duplicateValues" dxfId="991" priority="1487"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B561">
+    <cfRule type="duplicateValues" dxfId="990" priority="1486"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B561">
+    <cfRule type="duplicateValues" dxfId="989" priority="1485"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B562">
-    <cfRule type="duplicateValues" dxfId="987" priority="1456"/>
+    <cfRule type="duplicateValues" dxfId="988" priority="1482"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B562">
-    <cfRule type="duplicateValues" dxfId="986" priority="1455"/>
+    <cfRule type="duplicateValues" dxfId="987" priority="1481"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B564">
+    <cfRule type="duplicateValues" dxfId="986" priority="1480"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B564">
+    <cfRule type="duplicateValues" dxfId="985" priority="1479"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B563">
-    <cfRule type="duplicateValues" dxfId="985" priority="1452"/>
+    <cfRule type="duplicateValues" dxfId="984" priority="1478"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B563">
-    <cfRule type="duplicateValues" dxfId="984" priority="1451"/>
+    <cfRule type="duplicateValues" dxfId="983" priority="1477"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B565">
-    <cfRule type="duplicateValues" dxfId="983" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="982" priority="1476"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B565">
-    <cfRule type="duplicateValues" dxfId="982" priority="1449"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B564">
-    <cfRule type="duplicateValues" dxfId="981" priority="1448"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B564">
-    <cfRule type="duplicateValues" dxfId="980" priority="1447"/>
+    <cfRule type="duplicateValues" dxfId="981" priority="1475"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B566">
-    <cfRule type="duplicateValues" dxfId="979" priority="1446"/>
+    <cfRule type="duplicateValues" dxfId="980" priority="1468"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B566">
-    <cfRule type="duplicateValues" dxfId="978" priority="1445"/>
+    <cfRule type="duplicateValues" dxfId="979" priority="1467"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B569">
+    <cfRule type="duplicateValues" dxfId="978" priority="1466"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B569">
+    <cfRule type="duplicateValues" dxfId="977" priority="1465"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B567">
-    <cfRule type="duplicateValues" dxfId="977" priority="1438"/>
+    <cfRule type="duplicateValues" dxfId="976" priority="1462"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B567">
-    <cfRule type="duplicateValues" dxfId="976" priority="1437"/>
+    <cfRule type="duplicateValues" dxfId="975" priority="1461"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B568">
+    <cfRule type="duplicateValues" dxfId="974" priority="1458"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B568">
+    <cfRule type="duplicateValues" dxfId="973" priority="1457"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B570">
-    <cfRule type="duplicateValues" dxfId="975" priority="1436"/>
+    <cfRule type="duplicateValues" dxfId="972" priority="1453"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B570">
-    <cfRule type="duplicateValues" dxfId="974" priority="1435"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B568">
-    <cfRule type="duplicateValues" dxfId="973" priority="1432"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B568">
-    <cfRule type="duplicateValues" dxfId="972" priority="1431"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B569">
-    <cfRule type="duplicateValues" dxfId="971" priority="1428"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B569">
-    <cfRule type="duplicateValues" dxfId="970" priority="1427"/>
+    <cfRule type="duplicateValues" dxfId="971" priority="1454"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B571">
-    <cfRule type="duplicateValues" dxfId="969" priority="1423"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B571">
-    <cfRule type="duplicateValues" dxfId="968" priority="1424"/>
+    <cfRule type="duplicateValues" dxfId="970" priority="1448"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B572">
-    <cfRule type="duplicateValues" dxfId="967" priority="1418"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B573">
-    <cfRule type="duplicateValues" dxfId="966" priority="1415"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B573">
-    <cfRule type="duplicateValues" dxfId="965" priority="1414"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B576">
-    <cfRule type="duplicateValues" dxfId="964" priority="1412"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B576">
-    <cfRule type="duplicateValues" dxfId="963" priority="1413"/>
+    <cfRule type="duplicateValues" dxfId="969" priority="1445"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B572">
+    <cfRule type="duplicateValues" dxfId="968" priority="1444"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B575">
+    <cfRule type="duplicateValues" dxfId="967" priority="1442"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B575">
+    <cfRule type="duplicateValues" dxfId="966" priority="1443"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B577">
+    <cfRule type="duplicateValues" dxfId="965" priority="1441"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B577">
+    <cfRule type="duplicateValues" dxfId="964" priority="1440"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B578">
-    <cfRule type="duplicateValues" dxfId="962" priority="1411"/>
+    <cfRule type="duplicateValues" dxfId="963" priority="1430"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B578">
-    <cfRule type="duplicateValues" dxfId="961" priority="1410"/>
+    <cfRule type="duplicateValues" dxfId="962" priority="1431"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B579">
-    <cfRule type="duplicateValues" dxfId="960" priority="1400"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B579">
-    <cfRule type="duplicateValues" dxfId="959" priority="1401"/>
+    <cfRule type="duplicateValues" dxfId="961" priority="1427"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B580">
-    <cfRule type="duplicateValues" dxfId="958" priority="1397"/>
+    <cfRule type="duplicateValues" dxfId="960" priority="1424"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B581">
-    <cfRule type="duplicateValues" dxfId="957" priority="1394"/>
+    <cfRule type="duplicateValues" dxfId="959" priority="1421"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B581">
+    <cfRule type="duplicateValues" dxfId="958" priority="1420"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B582">
-    <cfRule type="duplicateValues" dxfId="956" priority="1391"/>
+    <cfRule type="duplicateValues" dxfId="957" priority="1419"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B582">
-    <cfRule type="duplicateValues" dxfId="955" priority="1390"/>
+    <cfRule type="duplicateValues" dxfId="956" priority="1418"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B583">
-    <cfRule type="duplicateValues" dxfId="954" priority="1389"/>
+    <cfRule type="duplicateValues" dxfId="955" priority="1417"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B583">
-    <cfRule type="duplicateValues" dxfId="953" priority="1388"/>
+    <cfRule type="duplicateValues" dxfId="954" priority="1416"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B584">
-    <cfRule type="duplicateValues" dxfId="952" priority="1387"/>
+    <cfRule type="duplicateValues" dxfId="953" priority="1415"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B584">
-    <cfRule type="duplicateValues" dxfId="951" priority="1386"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B585">
-    <cfRule type="duplicateValues" dxfId="950" priority="1385"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B585">
-    <cfRule type="duplicateValues" dxfId="949" priority="1384"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B588">
-    <cfRule type="duplicateValues" dxfId="948" priority="1382"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B588">
-    <cfRule type="duplicateValues" dxfId="947" priority="1383"/>
+    <cfRule type="duplicateValues" dxfId="952" priority="1414"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B587">
-    <cfRule type="duplicateValues" dxfId="946" priority="1380"/>
+    <cfRule type="duplicateValues" dxfId="951" priority="1412"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B587">
-    <cfRule type="duplicateValues" dxfId="945" priority="1381"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B590">
-    <cfRule type="duplicateValues" dxfId="944" priority="1374"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B590">
-    <cfRule type="duplicateValues" dxfId="943" priority="1375"/>
+    <cfRule type="duplicateValues" dxfId="950" priority="1413"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B586">
+    <cfRule type="duplicateValues" dxfId="949" priority="1410"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B586">
+    <cfRule type="duplicateValues" dxfId="948" priority="1411"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B589">
+    <cfRule type="duplicateValues" dxfId="947" priority="1404"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B589">
+    <cfRule type="duplicateValues" dxfId="946" priority="1405"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B591">
+    <cfRule type="duplicateValues" dxfId="945" priority="1400"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B591">
+    <cfRule type="duplicateValues" dxfId="944" priority="1401"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B592">
-    <cfRule type="duplicateValues" dxfId="942" priority="1370"/>
+    <cfRule type="duplicateValues" dxfId="943" priority="1398"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B592">
-    <cfRule type="duplicateValues" dxfId="941" priority="1371"/>
+    <cfRule type="duplicateValues" dxfId="942" priority="1399"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B593">
-    <cfRule type="duplicateValues" dxfId="940" priority="1368"/>
+    <cfRule type="duplicateValues" dxfId="941" priority="1396"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B593">
-    <cfRule type="duplicateValues" dxfId="939" priority="1369"/>
+    <cfRule type="duplicateValues" dxfId="940" priority="1397"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B594">
-    <cfRule type="duplicateValues" dxfId="938" priority="1366"/>
+    <cfRule type="duplicateValues" dxfId="939" priority="1392"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B594">
-    <cfRule type="duplicateValues" dxfId="937" priority="1367"/>
+    <cfRule type="duplicateValues" dxfId="938" priority="1393"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B595">
-    <cfRule type="duplicateValues" dxfId="936" priority="1362"/>
+    <cfRule type="duplicateValues" dxfId="937" priority="1388"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B595">
-    <cfRule type="duplicateValues" dxfId="935" priority="1363"/>
+    <cfRule type="duplicateValues" dxfId="936" priority="1389"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B596">
-    <cfRule type="duplicateValues" dxfId="934" priority="1358"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B596">
-    <cfRule type="duplicateValues" dxfId="933" priority="1359"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B597">
-    <cfRule type="duplicateValues" dxfId="932" priority="1357"/>
+    <cfRule type="duplicateValues" dxfId="935" priority="1387"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B601">
+    <cfRule type="duplicateValues" dxfId="934" priority="1384"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B602">
-    <cfRule type="duplicateValues" dxfId="931" priority="1354"/>
+    <cfRule type="duplicateValues" dxfId="933" priority="1382"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B602">
+    <cfRule type="duplicateValues" dxfId="932" priority="1383"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B604">
+    <cfRule type="duplicateValues" dxfId="931" priority="1380"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B604">
+    <cfRule type="duplicateValues" dxfId="930" priority="1381"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B603">
-    <cfRule type="duplicateValues" dxfId="930" priority="1352"/>
+    <cfRule type="duplicateValues" dxfId="929" priority="1378"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B603">
-    <cfRule type="duplicateValues" dxfId="929" priority="1353"/>
+    <cfRule type="duplicateValues" dxfId="928" priority="1379"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B605">
-    <cfRule type="duplicateValues" dxfId="928" priority="1350"/>
+    <cfRule type="duplicateValues" dxfId="927" priority="1376"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B605">
-    <cfRule type="duplicateValues" dxfId="927" priority="1351"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B604">
-    <cfRule type="duplicateValues" dxfId="926" priority="1348"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B604">
-    <cfRule type="duplicateValues" dxfId="925" priority="1349"/>
+    <cfRule type="duplicateValues" dxfId="926" priority="1377"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B606">
-    <cfRule type="duplicateValues" dxfId="924" priority="1346"/>
+    <cfRule type="duplicateValues" dxfId="925" priority="1374"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B606">
-    <cfRule type="duplicateValues" dxfId="923" priority="1347"/>
+    <cfRule type="duplicateValues" dxfId="924" priority="1375"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B607">
-    <cfRule type="duplicateValues" dxfId="922" priority="1344"/>
+    <cfRule type="duplicateValues" dxfId="923" priority="1368"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B607">
-    <cfRule type="duplicateValues" dxfId="921" priority="1345"/>
+    <cfRule type="duplicateValues" dxfId="922" priority="1369"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B608">
-    <cfRule type="duplicateValues" dxfId="920" priority="1338"/>
+    <cfRule type="duplicateValues" dxfId="921" priority="1367"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B608">
-    <cfRule type="duplicateValues" dxfId="919" priority="1339"/>
+    <cfRule type="duplicateValues" dxfId="920" priority="1366"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B609">
-    <cfRule type="duplicateValues" dxfId="918" priority="1337"/>
+    <cfRule type="duplicateValues" dxfId="919" priority="1364"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B609">
-    <cfRule type="duplicateValues" dxfId="917" priority="1336"/>
+    <cfRule type="duplicateValues" dxfId="918" priority="1365"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B610">
-    <cfRule type="duplicateValues" dxfId="916" priority="1334"/>
+    <cfRule type="duplicateValues" dxfId="917" priority="1358"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B610">
-    <cfRule type="duplicateValues" dxfId="915" priority="1335"/>
+    <cfRule type="duplicateValues" dxfId="916" priority="1359"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B611">
-    <cfRule type="duplicateValues" dxfId="914" priority="1328"/>
+    <cfRule type="duplicateValues" dxfId="915" priority="1356"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B611">
-    <cfRule type="duplicateValues" dxfId="913" priority="1329"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B612">
-    <cfRule type="duplicateValues" dxfId="912" priority="1326"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B612">
-    <cfRule type="duplicateValues" dxfId="911" priority="1327"/>
+    <cfRule type="duplicateValues" dxfId="914" priority="1357"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B613">
+    <cfRule type="duplicateValues" dxfId="913" priority="1354"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B613">
+    <cfRule type="duplicateValues" dxfId="912" priority="1355"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B614">
-    <cfRule type="duplicateValues" dxfId="910" priority="1324"/>
+    <cfRule type="duplicateValues" dxfId="911" priority="1349"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B614">
-    <cfRule type="duplicateValues" dxfId="909" priority="1325"/>
+    <cfRule type="duplicateValues" dxfId="910" priority="1348"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B615">
-    <cfRule type="duplicateValues" dxfId="908" priority="1319"/>
+    <cfRule type="duplicateValues" dxfId="909" priority="1345"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B615">
-    <cfRule type="duplicateValues" dxfId="907" priority="1318"/>
+    <cfRule type="duplicateValues" dxfId="908" priority="1344"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B616">
-    <cfRule type="duplicateValues" dxfId="906" priority="1315"/>
+    <cfRule type="duplicateValues" dxfId="907" priority="1341"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B616">
-    <cfRule type="duplicateValues" dxfId="905" priority="1314"/>
+    <cfRule type="duplicateValues" dxfId="906" priority="1340"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B617">
-    <cfRule type="duplicateValues" dxfId="904" priority="1311"/>
+    <cfRule type="duplicateValues" dxfId="905" priority="1338"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B617">
-    <cfRule type="duplicateValues" dxfId="903" priority="1310"/>
+    <cfRule type="duplicateValues" dxfId="904" priority="1339"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B618">
-    <cfRule type="duplicateValues" dxfId="902" priority="1308"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B618">
-    <cfRule type="duplicateValues" dxfId="901" priority="1309"/>
+    <cfRule type="duplicateValues" dxfId="903" priority="1335"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B619">
-    <cfRule type="duplicateValues" dxfId="900" priority="1305"/>
+    <cfRule type="duplicateValues" dxfId="902" priority="1333"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B619">
+    <cfRule type="duplicateValues" dxfId="901" priority="1334"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B620">
-    <cfRule type="duplicateValues" dxfId="899" priority="1303"/>
+    <cfRule type="duplicateValues" dxfId="900" priority="1331"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B620">
-    <cfRule type="duplicateValues" dxfId="898" priority="1304"/>
+    <cfRule type="duplicateValues" dxfId="899" priority="1332"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D621">
+    <cfRule type="duplicateValues" dxfId="898" priority="1329"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D621">
+    <cfRule type="duplicateValues" dxfId="897" priority="1330"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B621">
-    <cfRule type="duplicateValues" dxfId="897" priority="1301"/>
+    <cfRule type="duplicateValues" dxfId="896" priority="1325"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B621">
-    <cfRule type="duplicateValues" dxfId="896" priority="1302"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D622">
-    <cfRule type="duplicateValues" dxfId="895" priority="1299"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D622">
-    <cfRule type="duplicateValues" dxfId="894" priority="1300"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B622">
-    <cfRule type="duplicateValues" dxfId="893" priority="1295"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B622">
-    <cfRule type="duplicateValues" dxfId="892" priority="1296"/>
+    <cfRule type="duplicateValues" dxfId="895" priority="1326"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B625">
+    <cfRule type="duplicateValues" dxfId="894" priority="1323"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B625">
+    <cfRule type="duplicateValues" dxfId="893" priority="1324"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B627">
+    <cfRule type="duplicateValues" dxfId="892" priority="1321"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B627">
+    <cfRule type="duplicateValues" dxfId="891" priority="1322"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B626">
-    <cfRule type="duplicateValues" dxfId="891" priority="1293"/>
+    <cfRule type="duplicateValues" dxfId="890" priority="1320"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B626">
-    <cfRule type="duplicateValues" dxfId="890" priority="1294"/>
+    <cfRule type="duplicateValues" dxfId="889" priority="1319"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B628">
-    <cfRule type="duplicateValues" dxfId="889" priority="1291"/>
+    <cfRule type="duplicateValues" dxfId="888" priority="1318"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B628">
-    <cfRule type="duplicateValues" dxfId="888" priority="1292"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B627">
-    <cfRule type="duplicateValues" dxfId="887" priority="1290"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B627">
-    <cfRule type="duplicateValues" dxfId="886" priority="1289"/>
+    <cfRule type="duplicateValues" dxfId="887" priority="1317"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B629">
-    <cfRule type="duplicateValues" dxfId="885" priority="1288"/>
+    <cfRule type="duplicateValues" dxfId="886" priority="1314"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B629">
-    <cfRule type="duplicateValues" dxfId="884" priority="1287"/>
+    <cfRule type="duplicateValues" dxfId="885" priority="1313"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B630">
-    <cfRule type="duplicateValues" dxfId="883" priority="1284"/>
+    <cfRule type="duplicateValues" dxfId="884" priority="1310"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B630">
-    <cfRule type="duplicateValues" dxfId="882" priority="1283"/>
+    <cfRule type="duplicateValues" dxfId="883" priority="1309"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B631">
-    <cfRule type="duplicateValues" dxfId="881" priority="1280"/>
+    <cfRule type="duplicateValues" dxfId="882" priority="1306"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B631">
-    <cfRule type="duplicateValues" dxfId="880" priority="1279"/>
+    <cfRule type="duplicateValues" dxfId="881" priority="1305"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B632">
-    <cfRule type="duplicateValues" dxfId="879" priority="1276"/>
+    <cfRule type="duplicateValues" dxfId="880" priority="1301"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B632">
-    <cfRule type="duplicateValues" dxfId="878" priority="1275"/>
+    <cfRule type="duplicateValues" dxfId="879" priority="1302"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B633">
-    <cfRule type="duplicateValues" dxfId="877" priority="1271"/>
+    <cfRule type="duplicateValues" dxfId="878" priority="1297"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B633">
-    <cfRule type="duplicateValues" dxfId="876" priority="1272"/>
+    <cfRule type="duplicateValues" dxfId="877" priority="1298"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B634">
-    <cfRule type="duplicateValues" dxfId="875" priority="1267"/>
+    <cfRule type="duplicateValues" dxfId="876" priority="1293"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B634">
-    <cfRule type="duplicateValues" dxfId="874" priority="1268"/>
+    <cfRule type="duplicateValues" dxfId="875" priority="1294"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B635">
-    <cfRule type="duplicateValues" dxfId="873" priority="1263"/>
+    <cfRule type="duplicateValues" dxfId="874" priority="1291"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B635">
-    <cfRule type="duplicateValues" dxfId="872" priority="1264"/>
+    <cfRule type="duplicateValues" dxfId="873" priority="1292"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B637">
+    <cfRule type="duplicateValues" dxfId="872" priority="1289"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B637">
+    <cfRule type="duplicateValues" dxfId="871" priority="1290"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B636">
-    <cfRule type="duplicateValues" dxfId="871" priority="1261"/>
+    <cfRule type="duplicateValues" dxfId="870" priority="1287"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B636">
-    <cfRule type="duplicateValues" dxfId="870" priority="1262"/>
+    <cfRule type="duplicateValues" dxfId="869" priority="1288"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B638">
-    <cfRule type="duplicateValues" dxfId="869" priority="1259"/>
+    <cfRule type="duplicateValues" dxfId="868" priority="1285"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B638">
-    <cfRule type="duplicateValues" dxfId="868" priority="1260"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B637">
-    <cfRule type="duplicateValues" dxfId="867" priority="1257"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B637">
-    <cfRule type="duplicateValues" dxfId="866" priority="1258"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B639">
-    <cfRule type="duplicateValues" dxfId="865" priority="1255"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B639">
-    <cfRule type="duplicateValues" dxfId="864" priority="1256"/>
+    <cfRule type="duplicateValues" dxfId="867" priority="1286"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B640">
+    <cfRule type="duplicateValues" dxfId="866" priority="1283"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B640">
+    <cfRule type="duplicateValues" dxfId="865" priority="1284"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B641">
-    <cfRule type="duplicateValues" dxfId="863" priority="1253"/>
+    <cfRule type="duplicateValues" dxfId="864" priority="1279"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B641">
-    <cfRule type="duplicateValues" dxfId="862" priority="1254"/>
+    <cfRule type="duplicateValues" dxfId="863" priority="1280"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B642">
-    <cfRule type="duplicateValues" dxfId="861" priority="1249"/>
+    <cfRule type="duplicateValues" dxfId="862" priority="1277"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B642">
-    <cfRule type="duplicateValues" dxfId="860" priority="1250"/>
+    <cfRule type="duplicateValues" dxfId="861" priority="1278"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B644">
+    <cfRule type="duplicateValues" dxfId="860" priority="1274"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B644">
+    <cfRule type="duplicateValues" dxfId="859" priority="1273"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B643">
-    <cfRule type="duplicateValues" dxfId="859" priority="1247"/>
+    <cfRule type="duplicateValues" dxfId="858" priority="1271"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B643">
-    <cfRule type="duplicateValues" dxfId="858" priority="1248"/>
+    <cfRule type="duplicateValues" dxfId="857" priority="1272"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B645">
-    <cfRule type="duplicateValues" dxfId="857" priority="1244"/>
+    <cfRule type="duplicateValues" dxfId="856" priority="1268"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B645">
-    <cfRule type="duplicateValues" dxfId="856" priority="1243"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B644">
-    <cfRule type="duplicateValues" dxfId="855" priority="1241"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B644">
-    <cfRule type="duplicateValues" dxfId="854" priority="1242"/>
+    <cfRule type="duplicateValues" dxfId="855" priority="1267"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B646">
-    <cfRule type="duplicateValues" dxfId="853" priority="1238"/>
+    <cfRule type="duplicateValues" dxfId="854" priority="1265"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B646">
-    <cfRule type="duplicateValues" dxfId="852" priority="1237"/>
+    <cfRule type="duplicateValues" dxfId="853" priority="1266"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B647">
-    <cfRule type="duplicateValues" dxfId="851" priority="1235"/>
+    <cfRule type="duplicateValues" dxfId="852" priority="1260"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B647">
-    <cfRule type="duplicateValues" dxfId="850" priority="1236"/>
+    <cfRule type="duplicateValues" dxfId="851" priority="1259"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B648">
-    <cfRule type="duplicateValues" dxfId="849" priority="1230"/>
+    <cfRule type="duplicateValues" dxfId="850" priority="1255"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B648">
-    <cfRule type="duplicateValues" dxfId="848" priority="1229"/>
+    <cfRule type="duplicateValues" dxfId="849" priority="1256"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B649">
-    <cfRule type="duplicateValues" dxfId="847" priority="1225"/>
+    <cfRule type="duplicateValues" dxfId="848" priority="1254"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B649">
-    <cfRule type="duplicateValues" dxfId="846" priority="1226"/>
+    <cfRule type="duplicateValues" dxfId="847" priority="1253"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B650">
-    <cfRule type="duplicateValues" dxfId="845" priority="1224"/>
+    <cfRule type="duplicateValues" dxfId="846" priority="1251"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B650">
-    <cfRule type="duplicateValues" dxfId="844" priority="1223"/>
+    <cfRule type="duplicateValues" dxfId="845" priority="1252"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B651">
-    <cfRule type="duplicateValues" dxfId="843" priority="1221"/>
+    <cfRule type="duplicateValues" dxfId="844" priority="1249"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B651">
-    <cfRule type="duplicateValues" dxfId="842" priority="1222"/>
+    <cfRule type="duplicateValues" dxfId="843" priority="1250"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B652">
-    <cfRule type="duplicateValues" dxfId="841" priority="1219"/>
+    <cfRule type="duplicateValues" dxfId="842" priority="1247"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B652">
-    <cfRule type="duplicateValues" dxfId="840" priority="1220"/>
+    <cfRule type="duplicateValues" dxfId="841" priority="1248"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B653">
-    <cfRule type="duplicateValues" dxfId="839" priority="1217"/>
+    <cfRule type="duplicateValues" dxfId="840" priority="1245"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B653">
-    <cfRule type="duplicateValues" dxfId="838" priority="1218"/>
+    <cfRule type="duplicateValues" dxfId="839" priority="1246"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B654">
-    <cfRule type="duplicateValues" dxfId="837" priority="1215"/>
+    <cfRule type="duplicateValues" dxfId="838" priority="1239"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B654">
-    <cfRule type="duplicateValues" dxfId="836" priority="1216"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B655">
-    <cfRule type="duplicateValues" dxfId="835" priority="1209"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B655">
-    <cfRule type="duplicateValues" dxfId="834" priority="1210"/>
+    <cfRule type="duplicateValues" dxfId="837" priority="1240"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B656">
+    <cfRule type="duplicateValues" dxfId="836" priority="1235"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B656">
+    <cfRule type="duplicateValues" dxfId="835" priority="1236"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B657">
-    <cfRule type="duplicateValues" dxfId="833" priority="1205"/>
+    <cfRule type="duplicateValues" dxfId="834" priority="1233"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B657">
-    <cfRule type="duplicateValues" dxfId="832" priority="1206"/>
+    <cfRule type="duplicateValues" dxfId="833" priority="1234"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B658">
-    <cfRule type="duplicateValues" dxfId="831" priority="1203"/>
+    <cfRule type="duplicateValues" dxfId="832" priority="1231"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B658">
-    <cfRule type="duplicateValues" dxfId="830" priority="1204"/>
+    <cfRule type="duplicateValues" dxfId="831" priority="1232"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B659">
-    <cfRule type="duplicateValues" dxfId="829" priority="1201"/>
+    <cfRule type="duplicateValues" dxfId="830" priority="1230"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B659">
-    <cfRule type="duplicateValues" dxfId="828" priority="1202"/>
+    <cfRule type="duplicateValues" dxfId="829" priority="1229"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B660">
-    <cfRule type="duplicateValues" dxfId="827" priority="1200"/>
+    <cfRule type="duplicateValues" dxfId="828" priority="1227"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B660">
-    <cfRule type="duplicateValues" dxfId="826" priority="1199"/>
+    <cfRule type="duplicateValues" dxfId="827" priority="1228"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B661">
-    <cfRule type="duplicateValues" dxfId="825" priority="1197"/>
+    <cfRule type="duplicateValues" dxfId="826" priority="1225"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B661">
-    <cfRule type="duplicateValues" dxfId="824" priority="1198"/>
+    <cfRule type="duplicateValues" dxfId="825" priority="1226"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B662">
-    <cfRule type="duplicateValues" dxfId="823" priority="1195"/>
+    <cfRule type="duplicateValues" dxfId="824" priority="1224"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B662">
-    <cfRule type="duplicateValues" dxfId="822" priority="1196"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B663">
-    <cfRule type="duplicateValues" dxfId="821" priority="1194"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B663">
-    <cfRule type="duplicateValues" dxfId="820" priority="1193"/>
+    <cfRule type="duplicateValues" dxfId="823" priority="1223"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B666">
+    <cfRule type="duplicateValues" dxfId="822" priority="1219"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B666">
+    <cfRule type="duplicateValues" dxfId="821" priority="1220"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B667">
-    <cfRule type="duplicateValues" dxfId="819" priority="1189"/>
+    <cfRule type="duplicateValues" dxfId="820" priority="1217"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B667">
-    <cfRule type="duplicateValues" dxfId="818" priority="1190"/>
+    <cfRule type="duplicateValues" dxfId="819" priority="1218"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B668">
-    <cfRule type="duplicateValues" dxfId="817" priority="1187"/>
+    <cfRule type="duplicateValues" dxfId="818" priority="1213"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B668">
-    <cfRule type="duplicateValues" dxfId="816" priority="1188"/>
+    <cfRule type="duplicateValues" dxfId="817" priority="1214"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B669">
-    <cfRule type="duplicateValues" dxfId="815" priority="1183"/>
+    <cfRule type="duplicateValues" dxfId="816" priority="1210"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B669">
-    <cfRule type="duplicateValues" dxfId="814" priority="1184"/>
+    <cfRule type="duplicateValues" dxfId="815" priority="1209"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B670">
-    <cfRule type="duplicateValues" dxfId="813" priority="1180"/>
+    <cfRule type="duplicateValues" dxfId="814" priority="1206"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B670">
-    <cfRule type="duplicateValues" dxfId="812" priority="1179"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B671">
-    <cfRule type="duplicateValues" dxfId="811" priority="1176"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B671">
-    <cfRule type="duplicateValues" dxfId="810" priority="1175"/>
+    <cfRule type="duplicateValues" dxfId="813" priority="1205"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B672">
+    <cfRule type="duplicateValues" dxfId="812" priority="1203"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B672">
+    <cfRule type="duplicateValues" dxfId="811" priority="1204"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B673">
-    <cfRule type="duplicateValues" dxfId="809" priority="1173"/>
+    <cfRule type="duplicateValues" dxfId="810" priority="1199"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B673">
-    <cfRule type="duplicateValues" dxfId="808" priority="1174"/>
+    <cfRule type="duplicateValues" dxfId="809" priority="1200"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B674">
-    <cfRule type="duplicateValues" dxfId="807" priority="1169"/>
+    <cfRule type="duplicateValues" dxfId="808" priority="1193"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B674">
-    <cfRule type="duplicateValues" dxfId="806" priority="1170"/>
+    <cfRule type="duplicateValues" dxfId="807" priority="1194"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B675">
-    <cfRule type="duplicateValues" dxfId="805" priority="1163"/>
+    <cfRule type="duplicateValues" dxfId="806" priority="1190"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B675">
-    <cfRule type="duplicateValues" dxfId="804" priority="1164"/>
+    <cfRule type="duplicateValues" dxfId="805" priority="1191"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B675">
+    <cfRule type="duplicateValues" dxfId="804" priority="1189"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B676">
-    <cfRule type="duplicateValues" dxfId="803" priority="1160"/>
+    <cfRule type="duplicateValues" dxfId="803" priority="1184"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B676">
-    <cfRule type="duplicateValues" dxfId="802" priority="1161"/>
+    <cfRule type="duplicateValues" dxfId="802" priority="1185"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B676">
-    <cfRule type="duplicateValues" dxfId="801" priority="1159"/>
+    <cfRule type="duplicateValues" dxfId="801" priority="1183"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677">
-    <cfRule type="duplicateValues" dxfId="800" priority="1154"/>
+    <cfRule type="duplicateValues" dxfId="800" priority="1181"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677">
-    <cfRule type="duplicateValues" dxfId="799" priority="1155"/>
+    <cfRule type="duplicateValues" dxfId="799" priority="1182"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677">
-    <cfRule type="duplicateValues" dxfId="798" priority="1153"/>
+    <cfRule type="duplicateValues" dxfId="798" priority="1180"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B678">
-    <cfRule type="duplicateValues" dxfId="797" priority="1151"/>
+    <cfRule type="duplicateValues" dxfId="797" priority="1178"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B678">
-    <cfRule type="duplicateValues" dxfId="796" priority="1152"/>
+    <cfRule type="duplicateValues" dxfId="796" priority="1179"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B678">
-    <cfRule type="duplicateValues" dxfId="795" priority="1150"/>
+    <cfRule type="duplicateValues" dxfId="795" priority="1177"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B679">
-    <cfRule type="duplicateValues" dxfId="794" priority="1148"/>
+    <cfRule type="duplicateValues" dxfId="794" priority="1175"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B679">
-    <cfRule type="duplicateValues" dxfId="793" priority="1149"/>
+    <cfRule type="duplicateValues" dxfId="793" priority="1176"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B679">
-    <cfRule type="duplicateValues" dxfId="792" priority="1147"/>
+    <cfRule type="duplicateValues" dxfId="792" priority="1174"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B680">
-    <cfRule type="duplicateValues" dxfId="791" priority="1145"/>
+    <cfRule type="duplicateValues" dxfId="791" priority="1169"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B680">
-    <cfRule type="duplicateValues" dxfId="790" priority="1146"/>
+    <cfRule type="duplicateValues" dxfId="790" priority="1170"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B680">
-    <cfRule type="duplicateValues" dxfId="789" priority="1144"/>
+    <cfRule type="duplicateValues" dxfId="789" priority="1168"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B681">
-    <cfRule type="duplicateValues" dxfId="788" priority="1139"/>
+    <cfRule type="duplicateValues" dxfId="788" priority="1164"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B681">
-    <cfRule type="duplicateValues" dxfId="787" priority="1140"/>
+    <cfRule type="duplicateValues" dxfId="787" priority="1163"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B681">
-    <cfRule type="duplicateValues" dxfId="786" priority="1138"/>
+    <cfRule type="duplicateValues" dxfId="786" priority="1162"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B682">
-    <cfRule type="duplicateValues" dxfId="785" priority="1134"/>
+    <cfRule type="duplicateValues" dxfId="785" priority="1158"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B682">
-    <cfRule type="duplicateValues" dxfId="784" priority="1133"/>
+    <cfRule type="duplicateValues" dxfId="784" priority="1157"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B682">
-    <cfRule type="duplicateValues" dxfId="783" priority="1132"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B683">
-    <cfRule type="duplicateValues" dxfId="782" priority="1128"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B683">
-    <cfRule type="duplicateValues" dxfId="781" priority="1127"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B683">
-    <cfRule type="duplicateValues" dxfId="780" priority="1126"/>
+    <cfRule type="duplicateValues" dxfId="783" priority="1156"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B684">
+    <cfRule type="duplicateValues" dxfId="782" priority="1145"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B684">
+    <cfRule type="duplicateValues" dxfId="781" priority="1146"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B684">
+    <cfRule type="duplicateValues" dxfId="780" priority="1144"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B685">
-    <cfRule type="duplicateValues" dxfId="779" priority="1115"/>
+    <cfRule type="duplicateValues" dxfId="779" priority="1142"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B685">
-    <cfRule type="duplicateValues" dxfId="778" priority="1116"/>
+    <cfRule type="duplicateValues" dxfId="778" priority="1143"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B685">
-    <cfRule type="duplicateValues" dxfId="777" priority="1114"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B686">
-    <cfRule type="duplicateValues" dxfId="776" priority="1112"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B686">
-    <cfRule type="duplicateValues" dxfId="775" priority="1113"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B686">
-    <cfRule type="duplicateValues" dxfId="774" priority="1111"/>
+    <cfRule type="duplicateValues" dxfId="777" priority="1141"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B687">
+    <cfRule type="duplicateValues" dxfId="776" priority="1139"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B687">
+    <cfRule type="duplicateValues" dxfId="775" priority="1140"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B687">
+    <cfRule type="duplicateValues" dxfId="774" priority="1138"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B688">
-    <cfRule type="duplicateValues" dxfId="773" priority="1109"/>
+    <cfRule type="duplicateValues" dxfId="773" priority="1136"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B688">
-    <cfRule type="duplicateValues" dxfId="772" priority="1110"/>
+    <cfRule type="duplicateValues" dxfId="772" priority="1137"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B688">
-    <cfRule type="duplicateValues" dxfId="771" priority="1108"/>
+    <cfRule type="duplicateValues" dxfId="771" priority="1135"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B689">
-    <cfRule type="duplicateValues" dxfId="770" priority="1106"/>
+    <cfRule type="duplicateValues" dxfId="770" priority="1127"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B689">
-    <cfRule type="duplicateValues" dxfId="769" priority="1107"/>
+    <cfRule type="duplicateValues" dxfId="769" priority="1128"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B689">
-    <cfRule type="duplicateValues" dxfId="768" priority="1105"/>
+    <cfRule type="duplicateValues" dxfId="768" priority="1126"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B690">
-    <cfRule type="duplicateValues" dxfId="767" priority="1097"/>
+    <cfRule type="duplicateValues" dxfId="767" priority="1124"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B690">
-    <cfRule type="duplicateValues" dxfId="766" priority="1098"/>
+    <cfRule type="duplicateValues" dxfId="766" priority="1125"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B690">
-    <cfRule type="duplicateValues" dxfId="765" priority="1096"/>
+    <cfRule type="duplicateValues" dxfId="765" priority="1123"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B691">
-    <cfRule type="duplicateValues" dxfId="764" priority="1094"/>
+    <cfRule type="duplicateValues" dxfId="764" priority="1119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B691">
-    <cfRule type="duplicateValues" dxfId="763" priority="1095"/>
+    <cfRule type="duplicateValues" dxfId="763" priority="1118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B691">
-    <cfRule type="duplicateValues" dxfId="762" priority="1093"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B692">
-    <cfRule type="duplicateValues" dxfId="761" priority="1089"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B692">
-    <cfRule type="duplicateValues" dxfId="760" priority="1088"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B692">
-    <cfRule type="duplicateValues" dxfId="759" priority="1087"/>
+    <cfRule type="duplicateValues" dxfId="762" priority="1117"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B693">
+    <cfRule type="duplicateValues" dxfId="761" priority="1116"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B693">
+    <cfRule type="duplicateValues" dxfId="760" priority="1115"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B693">
+    <cfRule type="duplicateValues" dxfId="759" priority="1114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B694">
-    <cfRule type="duplicateValues" dxfId="758" priority="1086"/>
+    <cfRule type="duplicateValues" dxfId="758" priority="1110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B694">
-    <cfRule type="duplicateValues" dxfId="757" priority="1085"/>
+    <cfRule type="duplicateValues" dxfId="757" priority="1109"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B694">
-    <cfRule type="duplicateValues" dxfId="756" priority="1084"/>
+    <cfRule type="duplicateValues" dxfId="756" priority="1108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B695">
-    <cfRule type="duplicateValues" dxfId="755" priority="1080"/>
+    <cfRule type="duplicateValues" dxfId="755" priority="1101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B695">
-    <cfRule type="duplicateValues" dxfId="754" priority="1079"/>
+    <cfRule type="duplicateValues" dxfId="754" priority="1100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B695">
-    <cfRule type="duplicateValues" dxfId="753" priority="1078"/>
+    <cfRule type="duplicateValues" dxfId="753" priority="1099"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B696">
-    <cfRule type="duplicateValues" dxfId="752" priority="1071"/>
+    <cfRule type="duplicateValues" dxfId="752" priority="1097"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B696">
-    <cfRule type="duplicateValues" dxfId="751" priority="1070"/>
+    <cfRule type="duplicateValues" dxfId="751" priority="1098"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B696">
-    <cfRule type="duplicateValues" dxfId="750" priority="1069"/>
+    <cfRule type="duplicateValues" dxfId="750" priority="1096"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B697">
-    <cfRule type="duplicateValues" dxfId="749" priority="1067"/>
+    <cfRule type="duplicateValues" dxfId="749" priority="1094"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B697">
-    <cfRule type="duplicateValues" dxfId="748" priority="1068"/>
+    <cfRule type="duplicateValues" dxfId="748" priority="1095"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B697">
-    <cfRule type="duplicateValues" dxfId="747" priority="1066"/>
+    <cfRule type="duplicateValues" dxfId="747" priority="1093"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B698">
-    <cfRule type="duplicateValues" dxfId="746" priority="1064"/>
+    <cfRule type="duplicateValues" dxfId="746" priority="1085"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B698">
-    <cfRule type="duplicateValues" dxfId="745" priority="1065"/>
+    <cfRule type="duplicateValues" dxfId="745" priority="1086"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B698">
-    <cfRule type="duplicateValues" dxfId="744" priority="1063"/>
+    <cfRule type="duplicateValues" dxfId="744" priority="1084"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B699">
-    <cfRule type="duplicateValues" dxfId="743" priority="1055"/>
+    <cfRule type="duplicateValues" dxfId="743" priority="1082"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B699">
-    <cfRule type="duplicateValues" dxfId="742" priority="1056"/>
+    <cfRule type="duplicateValues" dxfId="742" priority="1083"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B699">
-    <cfRule type="duplicateValues" dxfId="741" priority="1054"/>
+    <cfRule type="duplicateValues" dxfId="741" priority="1081"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B701">
+    <cfRule type="duplicateValues" dxfId="740" priority="1076"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B701">
+    <cfRule type="duplicateValues" dxfId="739" priority="1077"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B701">
+    <cfRule type="duplicateValues" dxfId="738" priority="1075"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B700">
-    <cfRule type="duplicateValues" dxfId="740" priority="1052"/>
+    <cfRule type="duplicateValues" dxfId="737" priority="1074"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B700">
-    <cfRule type="duplicateValues" dxfId="739" priority="1053"/>
+    <cfRule type="duplicateValues" dxfId="736" priority="1073"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B700">
-    <cfRule type="duplicateValues" dxfId="738" priority="1051"/>
+    <cfRule type="duplicateValues" dxfId="735" priority="1072"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B702">
-    <cfRule type="duplicateValues" dxfId="737" priority="1046"/>
+    <cfRule type="duplicateValues" dxfId="734" priority="1070"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B702">
-    <cfRule type="duplicateValues" dxfId="736" priority="1047"/>
+    <cfRule type="duplicateValues" dxfId="733" priority="1071"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B702">
-    <cfRule type="duplicateValues" dxfId="735" priority="1045"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B701">
-    <cfRule type="duplicateValues" dxfId="734" priority="1044"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B701">
-    <cfRule type="duplicateValues" dxfId="733" priority="1043"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B701">
-    <cfRule type="duplicateValues" dxfId="732" priority="1042"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B703">
-    <cfRule type="duplicateValues" dxfId="731" priority="1040"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B703">
-    <cfRule type="duplicateValues" dxfId="730" priority="1041"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B703">
-    <cfRule type="duplicateValues" dxfId="729" priority="1039"/>
+    <cfRule type="duplicateValues" dxfId="732" priority="1069"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B704">
+    <cfRule type="duplicateValues" dxfId="731" priority="1067"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B704">
+    <cfRule type="duplicateValues" dxfId="730" priority="1068"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B704">
+    <cfRule type="duplicateValues" dxfId="729" priority="1066"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B705">
-    <cfRule type="duplicateValues" dxfId="728" priority="1037"/>
+    <cfRule type="duplicateValues" dxfId="728" priority="1064"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B705">
-    <cfRule type="duplicateValues" dxfId="727" priority="1038"/>
+    <cfRule type="duplicateValues" dxfId="727" priority="1065"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B705">
-    <cfRule type="duplicateValues" dxfId="726" priority="1036"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B706">
-    <cfRule type="duplicateValues" dxfId="725" priority="1034"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B706">
-    <cfRule type="duplicateValues" dxfId="724" priority="1035"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B706">
-    <cfRule type="duplicateValues" dxfId="723" priority="1033"/>
+    <cfRule type="duplicateValues" dxfId="726" priority="1063"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B707">
+    <cfRule type="duplicateValues" dxfId="725" priority="1062"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B707">
+    <cfRule type="duplicateValues" dxfId="724" priority="1061"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B707">
+    <cfRule type="duplicateValues" dxfId="723" priority="1060"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B708">
-    <cfRule type="duplicateValues" dxfId="722" priority="1032"/>
+    <cfRule type="duplicateValues" dxfId="722" priority="1058"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B708">
-    <cfRule type="duplicateValues" dxfId="721" priority="1031"/>
+    <cfRule type="duplicateValues" dxfId="721" priority="1059"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B708">
-    <cfRule type="duplicateValues" dxfId="720" priority="1030"/>
+    <cfRule type="duplicateValues" dxfId="720" priority="1057"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B709">
-    <cfRule type="duplicateValues" dxfId="719" priority="1028"/>
+    <cfRule type="duplicateValues" dxfId="719" priority="1055"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B709">
-    <cfRule type="duplicateValues" dxfId="718" priority="1029"/>
+    <cfRule type="duplicateValues" dxfId="718" priority="1056"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B709">
-    <cfRule type="duplicateValues" dxfId="717" priority="1027"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B710">
-    <cfRule type="duplicateValues" dxfId="716" priority="1025"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B710">
-    <cfRule type="duplicateValues" dxfId="715" priority="1026"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B710">
-    <cfRule type="duplicateValues" dxfId="714" priority="1024"/>
+    <cfRule type="duplicateValues" dxfId="717" priority="1054"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B711">
+    <cfRule type="duplicateValues" dxfId="716" priority="1052"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B711">
+    <cfRule type="duplicateValues" dxfId="715" priority="1053"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B711">
+    <cfRule type="duplicateValues" dxfId="714" priority="1051"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B712">
-    <cfRule type="duplicateValues" dxfId="713" priority="1022"/>
+    <cfRule type="duplicateValues" dxfId="713" priority="1046"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B712">
-    <cfRule type="duplicateValues" dxfId="712" priority="1023"/>
+    <cfRule type="duplicateValues" dxfId="712" priority="1047"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B712">
-    <cfRule type="duplicateValues" dxfId="711" priority="1021"/>
+    <cfRule type="duplicateValues" dxfId="711" priority="1045"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B713">
-    <cfRule type="duplicateValues" dxfId="710" priority="1016"/>
+    <cfRule type="duplicateValues" dxfId="710" priority="1043"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B713">
-    <cfRule type="duplicateValues" dxfId="709" priority="1017"/>
+    <cfRule type="duplicateValues" dxfId="709" priority="1044"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B713">
-    <cfRule type="duplicateValues" dxfId="708" priority="1015"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B714">
-    <cfRule type="duplicateValues" dxfId="707" priority="1013"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B714">
-    <cfRule type="duplicateValues" dxfId="706" priority="1014"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B714">
-    <cfRule type="duplicateValues" dxfId="705" priority="1012"/>
+    <cfRule type="duplicateValues" dxfId="708" priority="1042"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B715">
+    <cfRule type="duplicateValues" dxfId="707" priority="1040"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B715">
+    <cfRule type="duplicateValues" dxfId="706" priority="1041"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B715">
+    <cfRule type="duplicateValues" dxfId="705" priority="1039"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B716">
-    <cfRule type="duplicateValues" dxfId="704" priority="1010"/>
+    <cfRule type="duplicateValues" dxfId="704" priority="1034"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B716">
-    <cfRule type="duplicateValues" dxfId="703" priority="1011"/>
+    <cfRule type="duplicateValues" dxfId="703" priority="1035"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B716">
-    <cfRule type="duplicateValues" dxfId="702" priority="1009"/>
+    <cfRule type="duplicateValues" dxfId="702" priority="1033"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B717">
-    <cfRule type="duplicateValues" dxfId="701" priority="1004"/>
+    <cfRule type="duplicateValues" dxfId="701" priority="1026"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B717">
-    <cfRule type="duplicateValues" dxfId="700" priority="1005"/>
+    <cfRule type="duplicateValues" dxfId="700" priority="1025"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B717">
-    <cfRule type="duplicateValues" dxfId="699" priority="1003"/>
+    <cfRule type="duplicateValues" dxfId="699" priority="1024"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B718">
-    <cfRule type="duplicateValues" dxfId="698" priority="996"/>
+    <cfRule type="duplicateValues" dxfId="698" priority="1023"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B718">
-    <cfRule type="duplicateValues" dxfId="697" priority="995"/>
+    <cfRule type="duplicateValues" dxfId="697" priority="1022"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B718">
-    <cfRule type="duplicateValues" dxfId="696" priority="994"/>
+    <cfRule type="duplicateValues" dxfId="696" priority="1021"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B720">
+    <cfRule type="duplicateValues" dxfId="695" priority="1020"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B720">
+    <cfRule type="duplicateValues" dxfId="694" priority="1019"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B720">
+    <cfRule type="duplicateValues" dxfId="693" priority="1018"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B719">
-    <cfRule type="duplicateValues" dxfId="695" priority="993"/>
+    <cfRule type="duplicateValues" dxfId="692" priority="1017"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B719">
-    <cfRule type="duplicateValues" dxfId="694" priority="992"/>
+    <cfRule type="duplicateValues" dxfId="691" priority="1016"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B719">
-    <cfRule type="duplicateValues" dxfId="693" priority="991"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B721">
-    <cfRule type="duplicateValues" dxfId="692" priority="990"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B721">
-    <cfRule type="duplicateValues" dxfId="691" priority="989"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B721">
-    <cfRule type="duplicateValues" dxfId="690" priority="988"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B720">
-    <cfRule type="duplicateValues" dxfId="689" priority="987"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B720">
-    <cfRule type="duplicateValues" dxfId="688" priority="986"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B720">
-    <cfRule type="duplicateValues" dxfId="687" priority="985"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B723">
-    <cfRule type="duplicateValues" dxfId="686" priority="983"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B723">
-    <cfRule type="duplicateValues" dxfId="685" priority="984"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B723">
-    <cfRule type="duplicateValues" dxfId="684" priority="982"/>
+    <cfRule type="duplicateValues" dxfId="690" priority="1015"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B722">
+    <cfRule type="duplicateValues" dxfId="689" priority="1013"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B722">
+    <cfRule type="duplicateValues" dxfId="688" priority="1014"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B722">
+    <cfRule type="duplicateValues" dxfId="687" priority="1012"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B724">
+    <cfRule type="duplicateValues" dxfId="686" priority="1004"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B724">
+    <cfRule type="duplicateValues" dxfId="685" priority="1005"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B724">
+    <cfRule type="duplicateValues" dxfId="684" priority="1003"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B725">
-    <cfRule type="duplicateValues" dxfId="683" priority="974"/>
+    <cfRule type="duplicateValues" dxfId="683" priority="998"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B725">
-    <cfRule type="duplicateValues" dxfId="682" priority="975"/>
+    <cfRule type="duplicateValues" dxfId="682" priority="999"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B725">
-    <cfRule type="duplicateValues" dxfId="681" priority="973"/>
+    <cfRule type="duplicateValues" dxfId="681" priority="997"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B727">
+    <cfRule type="duplicateValues" dxfId="680" priority="992"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B727">
+    <cfRule type="duplicateValues" dxfId="679" priority="993"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B727">
+    <cfRule type="duplicateValues" dxfId="678" priority="991"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B726">
-    <cfRule type="duplicateValues" dxfId="680" priority="968"/>
+    <cfRule type="duplicateValues" dxfId="677" priority="990"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B726">
-    <cfRule type="duplicateValues" dxfId="679" priority="969"/>
+    <cfRule type="duplicateValues" dxfId="676" priority="989"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B726">
-    <cfRule type="duplicateValues" dxfId="678" priority="967"/>
+    <cfRule type="duplicateValues" dxfId="675" priority="988"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B728">
-    <cfRule type="duplicateValues" dxfId="677" priority="962"/>
+    <cfRule type="duplicateValues" dxfId="674" priority="983"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B728">
-    <cfRule type="duplicateValues" dxfId="676" priority="963"/>
+    <cfRule type="duplicateValues" dxfId="673" priority="984"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B728">
-    <cfRule type="duplicateValues" dxfId="675" priority="961"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B727">
-    <cfRule type="duplicateValues" dxfId="674" priority="960"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B727">
-    <cfRule type="duplicateValues" dxfId="673" priority="959"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B727">
-    <cfRule type="duplicateValues" dxfId="672" priority="958"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B729">
-    <cfRule type="duplicateValues" dxfId="671" priority="953"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B729">
-    <cfRule type="duplicateValues" dxfId="670" priority="954"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B729">
-    <cfRule type="duplicateValues" dxfId="669" priority="952"/>
+    <cfRule type="duplicateValues" dxfId="672" priority="982"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B730">
+    <cfRule type="duplicateValues" dxfId="671" priority="981"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B730">
+    <cfRule type="duplicateValues" dxfId="670" priority="980"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B730">
+    <cfRule type="duplicateValues" dxfId="669" priority="979"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B731">
-    <cfRule type="duplicateValues" dxfId="668" priority="951"/>
+    <cfRule type="duplicateValues" dxfId="668" priority="977"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B731">
-    <cfRule type="duplicateValues" dxfId="667" priority="950"/>
+    <cfRule type="duplicateValues" dxfId="667" priority="978"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B731">
-    <cfRule type="duplicateValues" dxfId="666" priority="949"/>
+    <cfRule type="duplicateValues" dxfId="666" priority="976"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B732">
-    <cfRule type="duplicateValues" dxfId="665" priority="947"/>
+    <cfRule type="duplicateValues" dxfId="665" priority="968"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B732">
-    <cfRule type="duplicateValues" dxfId="664" priority="948"/>
+    <cfRule type="duplicateValues" dxfId="664" priority="969"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B732">
-    <cfRule type="duplicateValues" dxfId="663" priority="946"/>
+    <cfRule type="duplicateValues" dxfId="663" priority="967"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B683 D46 B573:B574 B505 B46 B104:B106 B109:B111 B126 B131 B134 B137 B143:B147 B150:B152 B158:B160 D154 B168:B169 B172 B175 B178 B180:B185 B188 B190 B199 D195 B203 B212:B213 B218 B222:B224 B229 B231:B232 B235 B239:B240 B242:B244 B251 B254 B257:B262 B264:B269 B273 B278 B288:B289 B291 B295:B299 B306:B307 B314 B322:B324 B331 B333 B337:B338 B340:B341 B343 B348 B345:B346 B351 B364 B372:B373 B378:B380 B389:B390 B396:B397 B401 B418 B420 B430 B433 B438:B439 B442 B444 B448 B451 B456 B459 B463 B466:B468 B471:B472 B475:B476 B480 B483 B488 B492:B495 B507 B511 B514 B519 B524 B528:B529 B531:B535 B537 B539 B550 B560 B576 B585 B588 B590 B597:B600 B612 B622:B624 B639 B655 B663:B665 B671 B686 B692 B703 B706 B710 B714 B721 B723 B729 B739 B755 B758 B766 B768:B769 B775:B776 B781:B783 B805 B808 B811 B824:B827 B838 B840 B842:B843 B847 B850 B855:B856 B860 B862 B864:B865 B876 B878 B897 B911 B927:B928 B930 B932:B933 B942 B950:B1048576 B1:B8 B11:B15 B18:B19 B22 B24 B30:B31 B34 B39:B41 B43 B48:B50 B53 B56:B58 B62:B64 B74:B94 B96:B102 B114:B119 B122 B124">
+    <cfRule type="duplicateValues" dxfId="662" priority="2309"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B683 B573:B574 B505 B231:B232 B235 B239:B240 B242:B244 B251 B254 B257:B262 B264:B269 B273 B278 B288:B289 B291 B295:B299 B306:B307 B314 B322:B324 B331 B333 B337:B338 B340:B341 B343 B348 B345:B346 B351 B364 B372:B373 B378:B380 B389:B390 B396:B397 B401 B418 B420 B430 B433 B438:B439 B442 B444 B448 B451 B456 B459 B463 B466:B468 B471:B472 B475:B476 B480 B483 B488 B492:B495 B507 B511 B514 B519 B524 B528:B529 B531:B535 B537 B539 B550 B560 B576 B585 B588 B590 B597:B600 B612 B622:B624 B639 B655 B663:B665 B671 B686 B692 B703 B706 B710 B714 B721 B723 B729 B739 B755 B758 B766 B768:B769 B775:B776 B781:B783 B805 B808 B811 B824:B827 B838 B840 B842:B843 B847 B850 B855:B856 B860 B862 B864:B865 B876 B878 B897 B911 B927:B928 B930 B932:B933 B942 B950:B1048576 B1:B8 B11:B15 B18:B19 B22 B24 B30:B31 B34 B39:B41 B43 B46 B48:B50 B53 B56:B58 B62:B64 B74:B94 B96:B106 B108:B111 B114:B119 B122 B124:B126 B128:B229">
+    <cfRule type="duplicateValues" dxfId="661" priority="2421"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B683 B686 B692 B703 B706 B710 B714 B721 B723 B729 B739 B755 B758 B766 B768:B769 B775:B776 B781:B783 B805 B808 B811 B824:B827 B838 B840 B842:B843 B847 B850 B855:B856 B860 B862 B864:B865 B876 B878 B897 B911 B927:B928 B930 B932:B933 B942 B950:B1048576 B1:B8 B11:B15 B18:B19 B22 B24 B30:B31 B34 B39:B41 B43 B46 B48:B50 B53 B56:B58 B62:B64 B74:B94 B96:B106 B108:B111 B114:B119 B122 B124:B126 B128:B674">
+    <cfRule type="duplicateValues" dxfId="660" priority="2507"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B733">
-    <cfRule type="duplicateValues" dxfId="662" priority="938"/>
+    <cfRule type="duplicateValues" dxfId="659" priority="961"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B733">
-    <cfRule type="duplicateValues" dxfId="661" priority="939"/>
+    <cfRule type="duplicateValues" dxfId="658" priority="962"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B733">
-    <cfRule type="duplicateValues" dxfId="660" priority="937"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B684 D46 B574:B575 B506 B46 B104:B107 B109:B124 B126:B127 B132:B133 B135 B138 B144:B148 B151:B153 B159:B161 D155 B169:B170 B173 B176 B179 B181:B186 B189 B191 B200 D196 B204 B213:B214 B219 B223:B225 B230 B232:B233 B236 B240:B241 B243:B245 B252 B255 B258:B263 B265:B270 B274 B279 B289:B290 B292 B296:B300 B307:B308 B315 B323:B325 B332 B334 B338:B339 B341:B342 B344 B349 B346:B347 B352 B365 B373:B374 B379:B381 B390:B391 B397:B398 B402 B419 B421 B431 B434 B439:B440 B443 B445 B449 B452 B457 B460 B464 B467:B469 B472:B473 B476:B477 B481 B484 B489 B493:B496 B508 B512 B515 B520 B525 B529:B530 B532:B536 B538 B540 B551 B561 B577 B586 B589 B591 B598:B601 B613 B623:B625 B640 B656 B664:B666 B672 B687 B693 B704 B707 B711 B715 B722 B724 B730 B740 B756 B759 B767 B769:B770 B776:B777 B782:B784 B806 B809 B812 B825:B828 B839 B841 B843:B844 B848 B851 B856:B857 B861 B863 B865:B866 B877 B879 B898 B912 B928:B929 B931 B933:B934 B943 B951:B1048576 B1:B8 B11:B15 B18:B19 B22 B24 B30:B31 B34 B39:B41 B43 B48:B50 B53 B56:B58 B62:B64 B74:B102">
-    <cfRule type="duplicateValues" dxfId="659" priority="2279"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B684 B574:B575 B506 B232:B233 B236 B240:B241 B243:B245 B252 B255 B258:B263 B265:B270 B274 B279 B289:B290 B292 B296:B300 B307:B308 B315 B323:B325 B332 B334 B338:B339 B341:B342 B344 B349 B346:B347 B352 B365 B373:B374 B379:B381 B390:B391 B397:B398 B402 B419 B421 B431 B434 B439:B440 B443 B445 B449 B452 B457 B460 B464 B467:B469 B472:B473 B476:B477 B481 B484 B489 B493:B496 B508 B512 B515 B520 B525 B529:B530 B532:B536 B538 B540 B551 B561 B577 B586 B589 B591 B598:B601 B613 B623:B625 B640 B656 B664:B666 B672 B687 B693 B704 B707 B711 B715 B722 B724 B730 B740 B756 B759 B767 B769:B770 B776:B777 B782:B784 B806 B809 B812 B825:B828 B839 B841 B843:B844 B848 B851 B856:B857 B861 B863 B865:B866 B877 B879 B898 B912 B928:B929 B931 B933:B934 B943 B951:B1048576 B1:B8 B11:B15 B18:B19 B22 B24 B30:B31 B34 B39:B41 B43 B46 B48:B50 B53 B56:B58 B62:B64 B74:B230">
-    <cfRule type="duplicateValues" dxfId="658" priority="2391"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B684 B687 B693 B704 B707 B711 B715 B722 B724 B730 B740 B756 B759 B767 B769:B770 B776:B777 B782:B784 B806 B809 B812 B825:B828 B839 B841 B843:B844 B848 B851 B856:B857 B861 B863 B865:B866 B877 B879 B898 B912 B928:B929 B931 B933:B934 B943 B951:B1048576 B1:B8 B11:B15 B18:B19 B22 B24 B30:B31 B34 B39:B41 B43 B46 B48:B50 B53 B56:B58 B62:B64 B74:B675">
-    <cfRule type="duplicateValues" dxfId="657" priority="2477"/>
+    <cfRule type="duplicateValues" dxfId="657" priority="963"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B734">
-    <cfRule type="duplicateValues" dxfId="656" priority="931"/>
+    <cfRule type="duplicateValues" dxfId="656" priority="956"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B734">
-    <cfRule type="duplicateValues" dxfId="655" priority="932"/>
+    <cfRule type="duplicateValues" dxfId="655" priority="955"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B734">
-    <cfRule type="duplicateValues" dxfId="654" priority="933"/>
+    <cfRule type="duplicateValues" dxfId="654" priority="957"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B735">
-    <cfRule type="duplicateValues" dxfId="653" priority="926"/>
+    <cfRule type="duplicateValues" dxfId="653" priority="952"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B735">
-    <cfRule type="duplicateValues" dxfId="652" priority="925"/>
+    <cfRule type="duplicateValues" dxfId="652" priority="953"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B735">
-    <cfRule type="duplicateValues" dxfId="651" priority="927"/>
+    <cfRule type="duplicateValues" dxfId="651" priority="954"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B736">
-    <cfRule type="duplicateValues" dxfId="650" priority="922"/>
+    <cfRule type="duplicateValues" dxfId="650" priority="947"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B736">
-    <cfRule type="duplicateValues" dxfId="649" priority="923"/>
+    <cfRule type="duplicateValues" dxfId="649" priority="948"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B736">
-    <cfRule type="duplicateValues" dxfId="648" priority="924"/>
+    <cfRule type="duplicateValues" dxfId="648" priority="946"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B737">
-    <cfRule type="duplicateValues" dxfId="647" priority="917"/>
+    <cfRule type="duplicateValues" dxfId="647" priority="940"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B737">
-    <cfRule type="duplicateValues" dxfId="646" priority="918"/>
+    <cfRule type="duplicateValues" dxfId="646" priority="941"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B737">
-    <cfRule type="duplicateValues" dxfId="645" priority="916"/>
+    <cfRule type="duplicateValues" dxfId="645" priority="942"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B738">
-    <cfRule type="duplicateValues" dxfId="644" priority="910"/>
+    <cfRule type="duplicateValues" dxfId="644" priority="938"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B738">
-    <cfRule type="duplicateValues" dxfId="643" priority="911"/>
+    <cfRule type="duplicateValues" dxfId="643" priority="939"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B738">
-    <cfRule type="duplicateValues" dxfId="642" priority="912"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B739">
-    <cfRule type="duplicateValues" dxfId="641" priority="908"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B739">
-    <cfRule type="duplicateValues" dxfId="640" priority="909"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B739">
-    <cfRule type="duplicateValues" dxfId="639" priority="907"/>
+    <cfRule type="duplicateValues" dxfId="642" priority="937"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B740">
+    <cfRule type="duplicateValues" dxfId="641" priority="932"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B740">
+    <cfRule type="duplicateValues" dxfId="640" priority="933"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B741">
-    <cfRule type="duplicateValues" dxfId="638" priority="902"/>
+    <cfRule type="duplicateValues" dxfId="639" priority="930"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B741">
-    <cfRule type="duplicateValues" dxfId="637" priority="903"/>
+    <cfRule type="duplicateValues" dxfId="638" priority="929"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B741">
+    <cfRule type="duplicateValues" dxfId="637" priority="931"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B742">
-    <cfRule type="duplicateValues" dxfId="636" priority="900"/>
+    <cfRule type="duplicateValues" dxfId="636" priority="923"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B742">
-    <cfRule type="duplicateValues" dxfId="635" priority="899"/>
+    <cfRule type="duplicateValues" dxfId="635" priority="924"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B742">
-    <cfRule type="duplicateValues" dxfId="634" priority="901"/>
+    <cfRule type="duplicateValues" dxfId="634" priority="925"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B743">
-    <cfRule type="duplicateValues" dxfId="633" priority="893"/>
+    <cfRule type="duplicateValues" dxfId="633" priority="920"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B743">
-    <cfRule type="duplicateValues" dxfId="632" priority="894"/>
+    <cfRule type="duplicateValues" dxfId="632" priority="921"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B743">
-    <cfRule type="duplicateValues" dxfId="631" priority="895"/>
+    <cfRule type="duplicateValues" dxfId="631" priority="922"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B744">
-    <cfRule type="duplicateValues" dxfId="630" priority="890"/>
+    <cfRule type="duplicateValues" dxfId="630" priority="914"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B744">
-    <cfRule type="duplicateValues" dxfId="629" priority="891"/>
+    <cfRule type="duplicateValues" dxfId="629" priority="915"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B744">
-    <cfRule type="duplicateValues" dxfId="628" priority="892"/>
+    <cfRule type="duplicateValues" dxfId="628" priority="916"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B745">
-    <cfRule type="duplicateValues" dxfId="627" priority="884"/>
+    <cfRule type="duplicateValues" dxfId="627" priority="899"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B745">
-    <cfRule type="duplicateValues" dxfId="626" priority="885"/>
+    <cfRule type="duplicateValues" dxfId="626" priority="900"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B745">
-    <cfRule type="duplicateValues" dxfId="625" priority="886"/>
+    <cfRule type="duplicateValues" dxfId="625" priority="901"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B746">
-    <cfRule type="duplicateValues" dxfId="624" priority="869"/>
+    <cfRule type="duplicateValues" dxfId="624" priority="893"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B746">
-    <cfRule type="duplicateValues" dxfId="623" priority="870"/>
+    <cfRule type="duplicateValues" dxfId="623" priority="894"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B746">
-    <cfRule type="duplicateValues" dxfId="622" priority="871"/>
+    <cfRule type="duplicateValues" dxfId="622" priority="895"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B747">
-    <cfRule type="duplicateValues" dxfId="621" priority="863"/>
+    <cfRule type="duplicateValues" dxfId="621" priority="887"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B747">
-    <cfRule type="duplicateValues" dxfId="620" priority="864"/>
+    <cfRule type="duplicateValues" dxfId="620" priority="888"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B747">
-    <cfRule type="duplicateValues" dxfId="619" priority="865"/>
+    <cfRule type="duplicateValues" dxfId="619" priority="889"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B748">
-    <cfRule type="duplicateValues" dxfId="618" priority="857"/>
+    <cfRule type="duplicateValues" dxfId="618" priority="885"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B748">
-    <cfRule type="duplicateValues" dxfId="617" priority="858"/>
+    <cfRule type="duplicateValues" dxfId="617" priority="886"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B748">
-    <cfRule type="duplicateValues" dxfId="616" priority="859"/>
+    <cfRule type="duplicateValues" dxfId="616" priority="884"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B749">
-    <cfRule type="duplicateValues" dxfId="615" priority="855"/>
+    <cfRule type="duplicateValues" dxfId="615" priority="875"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B749">
-    <cfRule type="duplicateValues" dxfId="614" priority="856"/>
+    <cfRule type="duplicateValues" dxfId="614" priority="876"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B749">
-    <cfRule type="duplicateValues" dxfId="613" priority="854"/>
+    <cfRule type="duplicateValues" dxfId="613" priority="877"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B750">
-    <cfRule type="duplicateValues" dxfId="612" priority="845"/>
+    <cfRule type="duplicateValues" dxfId="612" priority="867"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B750">
-    <cfRule type="duplicateValues" dxfId="611" priority="846"/>
+    <cfRule type="duplicateValues" dxfId="611" priority="866"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B750">
-    <cfRule type="duplicateValues" dxfId="610" priority="847"/>
+    <cfRule type="duplicateValues" dxfId="610" priority="868"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B751">
-    <cfRule type="duplicateValues" dxfId="609" priority="837"/>
+    <cfRule type="duplicateValues" dxfId="609" priority="864"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B751">
-    <cfRule type="duplicateValues" dxfId="608" priority="836"/>
+    <cfRule type="duplicateValues" dxfId="608" priority="863"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B751">
-    <cfRule type="duplicateValues" dxfId="607" priority="838"/>
+    <cfRule type="duplicateValues" dxfId="607" priority="865"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B752">
-    <cfRule type="duplicateValues" dxfId="606" priority="834"/>
+    <cfRule type="duplicateValues" dxfId="606" priority="858"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B752">
-    <cfRule type="duplicateValues" dxfId="605" priority="833"/>
+    <cfRule type="duplicateValues" dxfId="605" priority="859"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B752">
-    <cfRule type="duplicateValues" dxfId="604" priority="835"/>
+    <cfRule type="duplicateValues" dxfId="604" priority="857"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B753">
-    <cfRule type="duplicateValues" dxfId="603" priority="828"/>
+    <cfRule type="duplicateValues" dxfId="603" priority="851"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B753">
-    <cfRule type="duplicateValues" dxfId="602" priority="829"/>
+    <cfRule type="duplicateValues" dxfId="602" priority="852"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B753">
-    <cfRule type="duplicateValues" dxfId="601" priority="827"/>
+    <cfRule type="duplicateValues" dxfId="601" priority="853"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B754">
-    <cfRule type="duplicateValues" dxfId="600" priority="821"/>
+    <cfRule type="duplicateValues" dxfId="600" priority="848"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B754">
-    <cfRule type="duplicateValues" dxfId="599" priority="822"/>
+    <cfRule type="duplicateValues" dxfId="599" priority="849"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B754">
-    <cfRule type="duplicateValues" dxfId="598" priority="823"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B755">
-    <cfRule type="duplicateValues" dxfId="597" priority="818"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B755">
-    <cfRule type="duplicateValues" dxfId="596" priority="819"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B755">
-    <cfRule type="duplicateValues" dxfId="595" priority="820"/>
+    <cfRule type="duplicateValues" dxfId="598" priority="850"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B756">
+    <cfRule type="duplicateValues" dxfId="597" priority="845"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B756">
+    <cfRule type="duplicateValues" dxfId="596" priority="846"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B756">
+    <cfRule type="duplicateValues" dxfId="595" priority="847"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B757">
-    <cfRule type="duplicateValues" dxfId="594" priority="815"/>
+    <cfRule type="duplicateValues" dxfId="594" priority="842"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B757">
-    <cfRule type="duplicateValues" dxfId="593" priority="816"/>
+    <cfRule type="duplicateValues" dxfId="593" priority="843"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B757">
-    <cfRule type="duplicateValues" dxfId="592" priority="817"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B758">
-    <cfRule type="duplicateValues" dxfId="591" priority="812"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B758">
-    <cfRule type="duplicateValues" dxfId="590" priority="813"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B758">
-    <cfRule type="duplicateValues" dxfId="589" priority="814"/>
+    <cfRule type="duplicateValues" dxfId="592" priority="844"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B759">
+    <cfRule type="duplicateValues" dxfId="591" priority="841"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B759">
+    <cfRule type="duplicateValues" dxfId="590" priority="840"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B759">
+    <cfRule type="duplicateValues" dxfId="589" priority="839"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B760">
-    <cfRule type="duplicateValues" dxfId="588" priority="811"/>
+    <cfRule type="duplicateValues" dxfId="588" priority="836"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B760">
-    <cfRule type="duplicateValues" dxfId="587" priority="810"/>
+    <cfRule type="duplicateValues" dxfId="587" priority="837"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B760">
-    <cfRule type="duplicateValues" dxfId="586" priority="809"/>
+    <cfRule type="duplicateValues" dxfId="586" priority="838"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B761">
-    <cfRule type="duplicateValues" dxfId="585" priority="806"/>
+    <cfRule type="duplicateValues" dxfId="585" priority="833"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B761">
-    <cfRule type="duplicateValues" dxfId="584" priority="807"/>
+    <cfRule type="duplicateValues" dxfId="584" priority="834"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B761">
-    <cfRule type="duplicateValues" dxfId="583" priority="808"/>
+    <cfRule type="duplicateValues" dxfId="583" priority="835"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B764">
+    <cfRule type="duplicateValues" dxfId="582" priority="831"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B764">
+    <cfRule type="duplicateValues" dxfId="581" priority="832"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B764">
+    <cfRule type="duplicateValues" dxfId="580" priority="830"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B762">
-    <cfRule type="duplicateValues" dxfId="582" priority="803"/>
+    <cfRule type="duplicateValues" dxfId="579" priority="828"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B762">
-    <cfRule type="duplicateValues" dxfId="581" priority="804"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B762">
-    <cfRule type="duplicateValues" dxfId="580" priority="805"/>
+    <cfRule type="duplicateValues" dxfId="578" priority="829"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B763">
+    <cfRule type="duplicateValues" dxfId="577" priority="823"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B763">
+    <cfRule type="duplicateValues" dxfId="576" priority="824"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B765">
-    <cfRule type="duplicateValues" dxfId="579" priority="801"/>
+    <cfRule type="duplicateValues" dxfId="575" priority="818"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B765">
-    <cfRule type="duplicateValues" dxfId="578" priority="802"/>
+    <cfRule type="duplicateValues" dxfId="574" priority="819"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B765">
-    <cfRule type="duplicateValues" dxfId="577" priority="800"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B763">
-    <cfRule type="duplicateValues" dxfId="576" priority="798"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B763">
-    <cfRule type="duplicateValues" dxfId="575" priority="799"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B764">
-    <cfRule type="duplicateValues" dxfId="574" priority="793"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B764">
-    <cfRule type="duplicateValues" dxfId="573" priority="794"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B766">
-    <cfRule type="duplicateValues" dxfId="572" priority="788"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B766">
-    <cfRule type="duplicateValues" dxfId="571" priority="789"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B766">
-    <cfRule type="duplicateValues" dxfId="570" priority="787"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B768">
-    <cfRule type="duplicateValues" dxfId="569" priority="784"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B768">
-    <cfRule type="duplicateValues" dxfId="568" priority="785"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B768">
-    <cfRule type="duplicateValues" dxfId="567" priority="786"/>
+    <cfRule type="duplicateValues" dxfId="573" priority="817"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B767">
+    <cfRule type="duplicateValues" dxfId="572" priority="814"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B767">
+    <cfRule type="duplicateValues" dxfId="571" priority="815"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B767">
+    <cfRule type="duplicateValues" dxfId="570" priority="816"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B770">
+    <cfRule type="duplicateValues" dxfId="569" priority="811"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B770">
+    <cfRule type="duplicateValues" dxfId="568" priority="812"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B770">
+    <cfRule type="duplicateValues" dxfId="567" priority="813"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B771">
-    <cfRule type="duplicateValues" dxfId="566" priority="781"/>
+    <cfRule type="duplicateValues" dxfId="566" priority="808"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B771">
-    <cfRule type="duplicateValues" dxfId="565" priority="782"/>
+    <cfRule type="duplicateValues" dxfId="565" priority="809"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B771">
-    <cfRule type="duplicateValues" dxfId="564" priority="783"/>
+    <cfRule type="duplicateValues" dxfId="564" priority="810"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B772">
-    <cfRule type="duplicateValues" dxfId="563" priority="778"/>
+    <cfRule type="duplicateValues" dxfId="563" priority="805"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B772">
-    <cfRule type="duplicateValues" dxfId="562" priority="779"/>
+    <cfRule type="duplicateValues" dxfId="562" priority="806"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B772">
-    <cfRule type="duplicateValues" dxfId="561" priority="780"/>
+    <cfRule type="duplicateValues" dxfId="561" priority="807"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B773">
-    <cfRule type="duplicateValues" dxfId="560" priority="775"/>
+    <cfRule type="duplicateValues" dxfId="560" priority="793"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B773">
-    <cfRule type="duplicateValues" dxfId="559" priority="776"/>
+    <cfRule type="duplicateValues" dxfId="559" priority="794"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B773">
-    <cfRule type="duplicateValues" dxfId="558" priority="777"/>
+    <cfRule type="duplicateValues" dxfId="558" priority="795"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B774">
-    <cfRule type="duplicateValues" dxfId="557" priority="763"/>
+    <cfRule type="duplicateValues" dxfId="557" priority="788"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B774">
-    <cfRule type="duplicateValues" dxfId="556" priority="764"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B774">
-    <cfRule type="duplicateValues" dxfId="555" priority="765"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B775">
-    <cfRule type="duplicateValues" dxfId="554" priority="758"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B775">
-    <cfRule type="duplicateValues" dxfId="553" priority="759"/>
+    <cfRule type="duplicateValues" dxfId="556" priority="789"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B777">
+    <cfRule type="duplicateValues" dxfId="555" priority="782"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B777">
+    <cfRule type="duplicateValues" dxfId="554" priority="783"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B777">
+    <cfRule type="duplicateValues" dxfId="553" priority="784"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B778">
-    <cfRule type="duplicateValues" dxfId="552" priority="752"/>
+    <cfRule type="duplicateValues" dxfId="552" priority="776"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B778">
-    <cfRule type="duplicateValues" dxfId="551" priority="753"/>
+    <cfRule type="duplicateValues" dxfId="551" priority="777"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B778">
-    <cfRule type="duplicateValues" dxfId="550" priority="754"/>
+    <cfRule type="duplicateValues" dxfId="550" priority="778"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B779">
-    <cfRule type="duplicateValues" dxfId="549" priority="746"/>
+    <cfRule type="duplicateValues" dxfId="549" priority="773"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B779">
-    <cfRule type="duplicateValues" dxfId="548" priority="747"/>
+    <cfRule type="duplicateValues" dxfId="548" priority="774"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B779">
-    <cfRule type="duplicateValues" dxfId="547" priority="748"/>
+    <cfRule type="duplicateValues" dxfId="547" priority="775"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B780">
-    <cfRule type="duplicateValues" dxfId="546" priority="743"/>
+    <cfRule type="duplicateValues" dxfId="546" priority="767"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B780">
-    <cfRule type="duplicateValues" dxfId="545" priority="744"/>
+    <cfRule type="duplicateValues" dxfId="545" priority="768"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B780">
-    <cfRule type="duplicateValues" dxfId="544" priority="745"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B781">
-    <cfRule type="duplicateValues" dxfId="543" priority="737"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B781">
-    <cfRule type="duplicateValues" dxfId="542" priority="738"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B781">
-    <cfRule type="duplicateValues" dxfId="541" priority="739"/>
+    <cfRule type="duplicateValues" dxfId="544" priority="769"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B784">
+    <cfRule type="duplicateValues" dxfId="543" priority="758"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B784">
+    <cfRule type="duplicateValues" dxfId="542" priority="759"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B784">
+    <cfRule type="duplicateValues" dxfId="541" priority="760"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B785">
-    <cfRule type="duplicateValues" dxfId="540" priority="728"/>
+    <cfRule type="duplicateValues" dxfId="540" priority="755"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B785">
-    <cfRule type="duplicateValues" dxfId="539" priority="729"/>
+    <cfRule type="duplicateValues" dxfId="539" priority="756"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B785">
-    <cfRule type="duplicateValues" dxfId="538" priority="730"/>
+    <cfRule type="duplicateValues" dxfId="538" priority="757"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B786">
-    <cfRule type="duplicateValues" dxfId="537" priority="725"/>
+    <cfRule type="duplicateValues" dxfId="537" priority="749"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B786">
-    <cfRule type="duplicateValues" dxfId="536" priority="726"/>
+    <cfRule type="duplicateValues" dxfId="536" priority="750"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B786">
-    <cfRule type="duplicateValues" dxfId="535" priority="727"/>
+    <cfRule type="duplicateValues" dxfId="535" priority="751"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B787">
-    <cfRule type="duplicateValues" dxfId="534" priority="719"/>
+    <cfRule type="duplicateValues" dxfId="534" priority="740"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B787">
-    <cfRule type="duplicateValues" dxfId="533" priority="720"/>
+    <cfRule type="duplicateValues" dxfId="533" priority="741"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B787">
-    <cfRule type="duplicateValues" dxfId="532" priority="721"/>
+    <cfRule type="duplicateValues" dxfId="532" priority="742"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B788">
-    <cfRule type="duplicateValues" dxfId="531" priority="710"/>
+    <cfRule type="duplicateValues" dxfId="531" priority="737"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B788">
-    <cfRule type="duplicateValues" dxfId="530" priority="711"/>
+    <cfRule type="duplicateValues" dxfId="530" priority="738"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B788">
-    <cfRule type="duplicateValues" dxfId="529" priority="712"/>
+    <cfRule type="duplicateValues" dxfId="529" priority="739"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B789">
-    <cfRule type="duplicateValues" dxfId="528" priority="707"/>
+    <cfRule type="duplicateValues" dxfId="528" priority="731"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B789">
-    <cfRule type="duplicateValues" dxfId="527" priority="708"/>
+    <cfRule type="duplicateValues" dxfId="527" priority="732"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B789">
-    <cfRule type="duplicateValues" dxfId="526" priority="709"/>
+    <cfRule type="duplicateValues" dxfId="526" priority="733"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B790">
-    <cfRule type="duplicateValues" dxfId="525" priority="701"/>
+    <cfRule type="duplicateValues" dxfId="525" priority="729"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B790">
-    <cfRule type="duplicateValues" dxfId="524" priority="702"/>
+    <cfRule type="duplicateValues" dxfId="524" priority="730"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B790">
-    <cfRule type="duplicateValues" dxfId="523" priority="703"/>
+    <cfRule type="duplicateValues" dxfId="523" priority="728"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B791">
-    <cfRule type="duplicateValues" dxfId="522" priority="699"/>
+    <cfRule type="duplicateValues" dxfId="522" priority="725"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B791">
-    <cfRule type="duplicateValues" dxfId="521" priority="700"/>
+    <cfRule type="duplicateValues" dxfId="521" priority="726"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B791">
-    <cfRule type="duplicateValues" dxfId="520" priority="698"/>
+    <cfRule type="duplicateValues" dxfId="520" priority="727"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B792">
-    <cfRule type="duplicateValues" dxfId="519" priority="695"/>
+    <cfRule type="duplicateValues" dxfId="519" priority="723"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B792">
-    <cfRule type="duplicateValues" dxfId="518" priority="696"/>
+    <cfRule type="duplicateValues" dxfId="518" priority="722"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B792">
-    <cfRule type="duplicateValues" dxfId="517" priority="697"/>
+    <cfRule type="duplicateValues" dxfId="517" priority="724"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B793">
-    <cfRule type="duplicateValues" dxfId="516" priority="693"/>
+    <cfRule type="duplicateValues" dxfId="516" priority="713"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B793">
-    <cfRule type="duplicateValues" dxfId="515" priority="692"/>
+    <cfRule type="duplicateValues" dxfId="515" priority="714"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B793">
-    <cfRule type="duplicateValues" dxfId="514" priority="694"/>
+    <cfRule type="duplicateValues" dxfId="514" priority="715"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B794">
-    <cfRule type="duplicateValues" dxfId="513" priority="683"/>
+    <cfRule type="duplicateValues" dxfId="513" priority="710"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B794">
-    <cfRule type="duplicateValues" dxfId="512" priority="684"/>
+    <cfRule type="duplicateValues" dxfId="512" priority="711"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B794">
-    <cfRule type="duplicateValues" dxfId="511" priority="685"/>
+    <cfRule type="duplicateValues" dxfId="511" priority="712"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B795">
-    <cfRule type="duplicateValues" dxfId="510" priority="680"/>
+    <cfRule type="duplicateValues" dxfId="510" priority="707"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B795">
-    <cfRule type="duplicateValues" dxfId="509" priority="681"/>
+    <cfRule type="duplicateValues" dxfId="509" priority="708"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B795">
-    <cfRule type="duplicateValues" dxfId="508" priority="682"/>
+    <cfRule type="duplicateValues" dxfId="508" priority="709"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B796">
-    <cfRule type="duplicateValues" dxfId="507" priority="677"/>
+    <cfRule type="duplicateValues" dxfId="507" priority="704"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B796">
-    <cfRule type="duplicateValues" dxfId="506" priority="678"/>
+    <cfRule type="duplicateValues" dxfId="506" priority="705"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B796">
-    <cfRule type="duplicateValues" dxfId="505" priority="679"/>
+    <cfRule type="duplicateValues" dxfId="505" priority="706"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B797">
-    <cfRule type="duplicateValues" dxfId="504" priority="674"/>
+    <cfRule type="duplicateValues" dxfId="504" priority="701"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B797">
-    <cfRule type="duplicateValues" dxfId="503" priority="675"/>
+    <cfRule type="duplicateValues" dxfId="503" priority="702"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B797">
-    <cfRule type="duplicateValues" dxfId="502" priority="676"/>
+    <cfRule type="duplicateValues" dxfId="502" priority="703"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B798">
-    <cfRule type="duplicateValues" dxfId="501" priority="671"/>
+    <cfRule type="duplicateValues" dxfId="501" priority="698"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B798">
-    <cfRule type="duplicateValues" dxfId="500" priority="672"/>
+    <cfRule type="duplicateValues" dxfId="500" priority="699"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B798">
-    <cfRule type="duplicateValues" dxfId="499" priority="673"/>
+    <cfRule type="duplicateValues" dxfId="499" priority="700"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B799">
-    <cfRule type="duplicateValues" dxfId="498" priority="668"/>
+    <cfRule type="duplicateValues" dxfId="498" priority="692"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B799">
-    <cfRule type="duplicateValues" dxfId="497" priority="669"/>
+    <cfRule type="duplicateValues" dxfId="497" priority="693"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B799">
-    <cfRule type="duplicateValues" dxfId="496" priority="670"/>
+    <cfRule type="duplicateValues" dxfId="496" priority="694"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B800">
-    <cfRule type="duplicateValues" dxfId="495" priority="662"/>
+    <cfRule type="duplicateValues" dxfId="495" priority="689"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B800">
-    <cfRule type="duplicateValues" dxfId="494" priority="663"/>
+    <cfRule type="duplicateValues" dxfId="494" priority="690"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B800">
-    <cfRule type="duplicateValues" dxfId="493" priority="664"/>
+    <cfRule type="duplicateValues" dxfId="493" priority="691"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B801">
-    <cfRule type="duplicateValues" dxfId="492" priority="659"/>
+    <cfRule type="duplicateValues" dxfId="492" priority="681"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B801">
-    <cfRule type="duplicateValues" dxfId="491" priority="660"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B801">
-    <cfRule type="duplicateValues" dxfId="490" priority="661"/>
+    <cfRule type="duplicateValues" dxfId="491" priority="682"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B802">
-    <cfRule type="duplicateValues" dxfId="489" priority="651"/>
+    <cfRule type="duplicateValues" dxfId="490" priority="676"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B802">
-    <cfRule type="duplicateValues" dxfId="488" priority="652"/>
+    <cfRule type="duplicateValues" dxfId="489" priority="677"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B803">
-    <cfRule type="duplicateValues" dxfId="487" priority="646"/>
+    <cfRule type="duplicateValues" dxfId="488" priority="674"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B803">
-    <cfRule type="duplicateValues" dxfId="486" priority="647"/>
+    <cfRule type="duplicateValues" dxfId="487" priority="673"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B803">
+    <cfRule type="duplicateValues" dxfId="486" priority="675"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B804">
-    <cfRule type="duplicateValues" dxfId="485" priority="644"/>
+    <cfRule type="duplicateValues" dxfId="485" priority="664"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B804">
-    <cfRule type="duplicateValues" dxfId="484" priority="643"/>
+    <cfRule type="duplicateValues" dxfId="484" priority="665"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B804">
-    <cfRule type="duplicateValues" dxfId="483" priority="645"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B805">
-    <cfRule type="duplicateValues" dxfId="482" priority="634"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B805">
-    <cfRule type="duplicateValues" dxfId="481" priority="635"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B805">
-    <cfRule type="duplicateValues" dxfId="480" priority="636"/>
+    <cfRule type="duplicateValues" dxfId="483" priority="666"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B806">
+    <cfRule type="duplicateValues" dxfId="482" priority="661"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B806">
+    <cfRule type="duplicateValues" dxfId="481" priority="662"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B806">
+    <cfRule type="duplicateValues" dxfId="480" priority="663"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B807">
-    <cfRule type="duplicateValues" dxfId="479" priority="631"/>
+    <cfRule type="duplicateValues" dxfId="479" priority="658"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B807">
-    <cfRule type="duplicateValues" dxfId="478" priority="632"/>
+    <cfRule type="duplicateValues" dxfId="478" priority="659"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B807">
-    <cfRule type="duplicateValues" dxfId="477" priority="633"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B808">
-    <cfRule type="duplicateValues" dxfId="476" priority="628"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B808">
-    <cfRule type="duplicateValues" dxfId="475" priority="629"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B808">
-    <cfRule type="duplicateValues" dxfId="474" priority="630"/>
+    <cfRule type="duplicateValues" dxfId="477" priority="660"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B809">
+    <cfRule type="duplicateValues" dxfId="476" priority="655"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B809">
+    <cfRule type="duplicateValues" dxfId="475" priority="656"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B809">
+    <cfRule type="duplicateValues" dxfId="474" priority="657"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B810">
-    <cfRule type="duplicateValues" dxfId="473" priority="625"/>
+    <cfRule type="duplicateValues" dxfId="473" priority="653"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B810">
-    <cfRule type="duplicateValues" dxfId="472" priority="626"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B810">
-    <cfRule type="duplicateValues" dxfId="471" priority="627"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B811">
-    <cfRule type="duplicateValues" dxfId="470" priority="623"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B811">
-    <cfRule type="duplicateValues" dxfId="469" priority="624"/>
+    <cfRule type="duplicateValues" dxfId="472" priority="654"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B812">
+    <cfRule type="duplicateValues" dxfId="471" priority="645"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B812">
+    <cfRule type="duplicateValues" dxfId="470" priority="644"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B812">
+    <cfRule type="duplicateValues" dxfId="469" priority="646"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B813">
-    <cfRule type="duplicateValues" dxfId="468" priority="615"/>
+    <cfRule type="duplicateValues" dxfId="468" priority="638"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B813">
-    <cfRule type="duplicateValues" dxfId="467" priority="614"/>
+    <cfRule type="duplicateValues" dxfId="467" priority="639"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B813">
-    <cfRule type="duplicateValues" dxfId="466" priority="616"/>
+    <cfRule type="duplicateValues" dxfId="466" priority="640"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B814">
-    <cfRule type="duplicateValues" dxfId="465" priority="608"/>
+    <cfRule type="duplicateValues" dxfId="465" priority="635"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B814">
-    <cfRule type="duplicateValues" dxfId="464" priority="609"/>
+    <cfRule type="duplicateValues" dxfId="464" priority="636"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B814">
-    <cfRule type="duplicateValues" dxfId="463" priority="610"/>
+    <cfRule type="duplicateValues" dxfId="463" priority="637"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B815">
-    <cfRule type="duplicateValues" dxfId="462" priority="605"/>
+    <cfRule type="duplicateValues" dxfId="462" priority="632"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B815">
-    <cfRule type="duplicateValues" dxfId="461" priority="606"/>
+    <cfRule type="duplicateValues" dxfId="461" priority="633"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B815">
-    <cfRule type="duplicateValues" dxfId="460" priority="607"/>
+    <cfRule type="duplicateValues" dxfId="460" priority="634"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B816">
-    <cfRule type="duplicateValues" dxfId="459" priority="602"/>
+    <cfRule type="duplicateValues" dxfId="459" priority="629"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B816">
-    <cfRule type="duplicateValues" dxfId="458" priority="603"/>
+    <cfRule type="duplicateValues" dxfId="458" priority="630"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B816">
-    <cfRule type="duplicateValues" dxfId="457" priority="604"/>
+    <cfRule type="duplicateValues" dxfId="457" priority="631"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B817">
-    <cfRule type="duplicateValues" dxfId="456" priority="599"/>
+    <cfRule type="duplicateValues" dxfId="456" priority="626"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B817">
-    <cfRule type="duplicateValues" dxfId="455" priority="600"/>
+    <cfRule type="duplicateValues" dxfId="455" priority="627"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B817">
-    <cfRule type="duplicateValues" dxfId="454" priority="601"/>
+    <cfRule type="duplicateValues" dxfId="454" priority="628"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B818">
-    <cfRule type="duplicateValues" dxfId="453" priority="596"/>
+    <cfRule type="duplicateValues" dxfId="453" priority="623"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B818">
-    <cfRule type="duplicateValues" dxfId="452" priority="597"/>
+    <cfRule type="duplicateValues" dxfId="452" priority="624"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B818">
-    <cfRule type="duplicateValues" dxfId="451" priority="598"/>
+    <cfRule type="duplicateValues" dxfId="451" priority="625"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B819">
-    <cfRule type="duplicateValues" dxfId="450" priority="593"/>
+    <cfRule type="duplicateValues" dxfId="450" priority="617"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B819">
-    <cfRule type="duplicateValues" dxfId="449" priority="594"/>
+    <cfRule type="duplicateValues" dxfId="449" priority="618"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B819">
-    <cfRule type="duplicateValues" dxfId="448" priority="595"/>
+    <cfRule type="duplicateValues" dxfId="448" priority="619"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B820">
-    <cfRule type="duplicateValues" dxfId="447" priority="587"/>
+    <cfRule type="duplicateValues" dxfId="447" priority="614"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B820">
-    <cfRule type="duplicateValues" dxfId="446" priority="588"/>
+    <cfRule type="duplicateValues" dxfId="446" priority="615"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B820">
-    <cfRule type="duplicateValues" dxfId="445" priority="589"/>
+    <cfRule type="duplicateValues" dxfId="445" priority="616"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B821">
-    <cfRule type="duplicateValues" dxfId="444" priority="584"/>
+    <cfRule type="duplicateValues" dxfId="444" priority="611"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B821">
-    <cfRule type="duplicateValues" dxfId="443" priority="585"/>
+    <cfRule type="duplicateValues" dxfId="443" priority="612"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B821">
-    <cfRule type="duplicateValues" dxfId="442" priority="586"/>
+    <cfRule type="duplicateValues" dxfId="442" priority="613"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B822">
-    <cfRule type="duplicateValues" dxfId="441" priority="581"/>
+    <cfRule type="duplicateValues" dxfId="441" priority="609"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B822">
-    <cfRule type="duplicateValues" dxfId="440" priority="582"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B822">
-    <cfRule type="duplicateValues" dxfId="439" priority="583"/>
+    <cfRule type="duplicateValues" dxfId="440" priority="610"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B823">
-    <cfRule type="duplicateValues" dxfId="438" priority="579"/>
+    <cfRule type="duplicateValues" dxfId="439" priority="606"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B823">
-    <cfRule type="duplicateValues" dxfId="437" priority="580"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B824">
-    <cfRule type="duplicateValues" dxfId="436" priority="576"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B824">
-    <cfRule type="duplicateValues" dxfId="435" priority="577"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B824">
-    <cfRule type="duplicateValues" dxfId="434" priority="578"/>
+    <cfRule type="duplicateValues" dxfId="438" priority="607"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B823">
+    <cfRule type="duplicateValues" dxfId="437" priority="608"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B828">
+    <cfRule type="duplicateValues" dxfId="436" priority="603"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B828">
+    <cfRule type="duplicateValues" dxfId="435" priority="604"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B828">
+    <cfRule type="duplicateValues" dxfId="434" priority="605"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B829">
-    <cfRule type="duplicateValues" dxfId="433" priority="573"/>
+    <cfRule type="duplicateValues" dxfId="433" priority="594"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B829">
-    <cfRule type="duplicateValues" dxfId="432" priority="574"/>
+    <cfRule type="duplicateValues" dxfId="432" priority="595"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B829">
-    <cfRule type="duplicateValues" dxfId="431" priority="575"/>
+    <cfRule type="duplicateValues" dxfId="431" priority="596"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B830">
-    <cfRule type="duplicateValues" dxfId="430" priority="564"/>
+    <cfRule type="duplicateValues" dxfId="430" priority="591"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B830">
-    <cfRule type="duplicateValues" dxfId="429" priority="565"/>
+    <cfRule type="duplicateValues" dxfId="429" priority="592"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B830">
-    <cfRule type="duplicateValues" dxfId="428" priority="566"/>
+    <cfRule type="duplicateValues" dxfId="428" priority="593"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B831">
-    <cfRule type="duplicateValues" dxfId="427" priority="561"/>
+    <cfRule type="duplicateValues" dxfId="427" priority="588"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B831">
-    <cfRule type="duplicateValues" dxfId="426" priority="562"/>
+    <cfRule type="duplicateValues" dxfId="426" priority="589"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B831">
-    <cfRule type="duplicateValues" dxfId="425" priority="563"/>
+    <cfRule type="duplicateValues" dxfId="425" priority="590"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B832">
-    <cfRule type="duplicateValues" dxfId="424" priority="558"/>
+    <cfRule type="duplicateValues" dxfId="424" priority="585"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B832">
-    <cfRule type="duplicateValues" dxfId="423" priority="559"/>
+    <cfRule type="duplicateValues" dxfId="423" priority="586"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B832">
-    <cfRule type="duplicateValues" dxfId="422" priority="560"/>
+    <cfRule type="duplicateValues" dxfId="422" priority="587"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B833">
-    <cfRule type="duplicateValues" dxfId="421" priority="555"/>
+    <cfRule type="duplicateValues" dxfId="421" priority="582"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B833">
-    <cfRule type="duplicateValues" dxfId="420" priority="556"/>
+    <cfRule type="duplicateValues" dxfId="420" priority="583"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B833">
-    <cfRule type="duplicateValues" dxfId="419" priority="557"/>
+    <cfRule type="duplicateValues" dxfId="419" priority="584"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B834">
-    <cfRule type="duplicateValues" dxfId="418" priority="552"/>
+    <cfRule type="duplicateValues" dxfId="418" priority="580"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B834">
-    <cfRule type="duplicateValues" dxfId="417" priority="553"/>
+    <cfRule type="duplicateValues" dxfId="417" priority="579"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B834">
-    <cfRule type="duplicateValues" dxfId="416" priority="554"/>
+    <cfRule type="duplicateValues" dxfId="416" priority="581"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B835">
-    <cfRule type="duplicateValues" dxfId="415" priority="550"/>
+    <cfRule type="duplicateValues" dxfId="415" priority="576"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B835">
-    <cfRule type="duplicateValues" dxfId="414" priority="549"/>
+    <cfRule type="duplicateValues" dxfId="414" priority="577"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B835">
-    <cfRule type="duplicateValues" dxfId="413" priority="551"/>
+    <cfRule type="duplicateValues" dxfId="413" priority="578"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B836">
-    <cfRule type="duplicateValues" dxfId="412" priority="546"/>
+    <cfRule type="duplicateValues" dxfId="412" priority="573"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B836">
-    <cfRule type="duplicateValues" dxfId="411" priority="547"/>
+    <cfRule type="duplicateValues" dxfId="411" priority="574"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B836">
-    <cfRule type="duplicateValues" dxfId="410" priority="548"/>
+    <cfRule type="duplicateValues" dxfId="410" priority="575"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B837">
-    <cfRule type="duplicateValues" dxfId="409" priority="543"/>
+    <cfRule type="duplicateValues" dxfId="409" priority="567"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B837">
-    <cfRule type="duplicateValues" dxfId="408" priority="544"/>
+    <cfRule type="duplicateValues" dxfId="408" priority="568"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B837">
-    <cfRule type="duplicateValues" dxfId="407" priority="545"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B838">
-    <cfRule type="duplicateValues" dxfId="406" priority="537"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B838">
-    <cfRule type="duplicateValues" dxfId="405" priority="538"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B838">
-    <cfRule type="duplicateValues" dxfId="404" priority="539"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B840">
-    <cfRule type="duplicateValues" dxfId="403" priority="534"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B840">
-    <cfRule type="duplicateValues" dxfId="402" priority="535"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B840">
-    <cfRule type="duplicateValues" dxfId="401" priority="536"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B842">
-    <cfRule type="duplicateValues" dxfId="400" priority="531"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B842">
-    <cfRule type="duplicateValues" dxfId="399" priority="532"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B842">
-    <cfRule type="duplicateValues" dxfId="398" priority="533"/>
+    <cfRule type="duplicateValues" dxfId="407" priority="569"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B839">
+    <cfRule type="duplicateValues" dxfId="406" priority="564"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B839">
+    <cfRule type="duplicateValues" dxfId="405" priority="565"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B839">
+    <cfRule type="duplicateValues" dxfId="404" priority="566"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B841">
+    <cfRule type="duplicateValues" dxfId="403" priority="561"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B841">
+    <cfRule type="duplicateValues" dxfId="402" priority="562"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B841">
+    <cfRule type="duplicateValues" dxfId="401" priority="563"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B844">
+    <cfRule type="duplicateValues" dxfId="400" priority="558"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B844">
+    <cfRule type="duplicateValues" dxfId="399" priority="559"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B844">
+    <cfRule type="duplicateValues" dxfId="398" priority="560"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B845">
-    <cfRule type="duplicateValues" dxfId="397" priority="528"/>
+    <cfRule type="duplicateValues" dxfId="397" priority="555"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B845">
-    <cfRule type="duplicateValues" dxfId="396" priority="529"/>
+    <cfRule type="duplicateValues" dxfId="396" priority="556"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B845">
-    <cfRule type="duplicateValues" dxfId="395" priority="530"/>
+    <cfRule type="duplicateValues" dxfId="395" priority="557"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B846">
-    <cfRule type="duplicateValues" dxfId="394" priority="525"/>
+    <cfRule type="duplicateValues" dxfId="394" priority="552"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B846">
-    <cfRule type="duplicateValues" dxfId="393" priority="526"/>
+    <cfRule type="duplicateValues" dxfId="393" priority="553"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B846">
-    <cfRule type="duplicateValues" dxfId="392" priority="527"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B847">
-    <cfRule type="duplicateValues" dxfId="391" priority="522"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B847">
-    <cfRule type="duplicateValues" dxfId="390" priority="523"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B847">
-    <cfRule type="duplicateValues" dxfId="389" priority="524"/>
+    <cfRule type="duplicateValues" dxfId="392" priority="554"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B848">
+    <cfRule type="duplicateValues" dxfId="391" priority="546"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B848">
+    <cfRule type="duplicateValues" dxfId="390" priority="547"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B848">
+    <cfRule type="duplicateValues" dxfId="389" priority="548"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B849">
-    <cfRule type="duplicateValues" dxfId="388" priority="516"/>
+    <cfRule type="duplicateValues" dxfId="388" priority="540"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B849">
-    <cfRule type="duplicateValues" dxfId="387" priority="517"/>
+    <cfRule type="duplicateValues" dxfId="387" priority="541"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B849">
-    <cfRule type="duplicateValues" dxfId="386" priority="518"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B850">
-    <cfRule type="duplicateValues" dxfId="385" priority="510"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B850">
-    <cfRule type="duplicateValues" dxfId="384" priority="511"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B850">
-    <cfRule type="duplicateValues" dxfId="383" priority="512"/>
+    <cfRule type="duplicateValues" dxfId="386" priority="542"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B851">
+    <cfRule type="duplicateValues" dxfId="385" priority="537"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B851">
+    <cfRule type="duplicateValues" dxfId="384" priority="538"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B851">
+    <cfRule type="duplicateValues" dxfId="383" priority="539"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B852">
-    <cfRule type="duplicateValues" dxfId="382" priority="507"/>
+    <cfRule type="duplicateValues" dxfId="382" priority="528"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B852">
-    <cfRule type="duplicateValues" dxfId="381" priority="508"/>
+    <cfRule type="duplicateValues" dxfId="381" priority="529"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B852">
-    <cfRule type="duplicateValues" dxfId="380" priority="509"/>
+    <cfRule type="duplicateValues" dxfId="380" priority="530"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B853">
-    <cfRule type="duplicateValues" dxfId="379" priority="498"/>
+    <cfRule type="duplicateValues" dxfId="379" priority="522"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B853">
-    <cfRule type="duplicateValues" dxfId="378" priority="499"/>
+    <cfRule type="duplicateValues" dxfId="378" priority="523"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B853">
-    <cfRule type="duplicateValues" dxfId="377" priority="500"/>
+    <cfRule type="duplicateValues" dxfId="377" priority="524"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B854">
-    <cfRule type="duplicateValues" dxfId="376" priority="492"/>
+    <cfRule type="duplicateValues" dxfId="376" priority="519"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B854">
-    <cfRule type="duplicateValues" dxfId="375" priority="493"/>
+    <cfRule type="duplicateValues" dxfId="375" priority="520"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B854">
-    <cfRule type="duplicateValues" dxfId="374" priority="494"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B855">
-    <cfRule type="duplicateValues" dxfId="373" priority="489"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B855">
-    <cfRule type="duplicateValues" dxfId="372" priority="490"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B855">
-    <cfRule type="duplicateValues" dxfId="371" priority="491"/>
+    <cfRule type="duplicateValues" dxfId="374" priority="521"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B857">
+    <cfRule type="duplicateValues" dxfId="373" priority="516"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B857">
+    <cfRule type="duplicateValues" dxfId="372" priority="517"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B857">
+    <cfRule type="duplicateValues" dxfId="371" priority="518"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B858">
-    <cfRule type="duplicateValues" dxfId="370" priority="486"/>
+    <cfRule type="duplicateValues" dxfId="370" priority="513"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B858">
-    <cfRule type="duplicateValues" dxfId="369" priority="487"/>
+    <cfRule type="duplicateValues" dxfId="369" priority="514"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B858">
-    <cfRule type="duplicateValues" dxfId="368" priority="488"/>
+    <cfRule type="duplicateValues" dxfId="368" priority="515"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B859">
-    <cfRule type="duplicateValues" dxfId="367" priority="483"/>
+    <cfRule type="duplicateValues" dxfId="367" priority="510"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B859">
-    <cfRule type="duplicateValues" dxfId="366" priority="484"/>
+    <cfRule type="duplicateValues" dxfId="366" priority="511"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B859">
-    <cfRule type="duplicateValues" dxfId="365" priority="485"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B860">
-    <cfRule type="duplicateValues" dxfId="364" priority="480"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B860">
-    <cfRule type="duplicateValues" dxfId="363" priority="481"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B860">
-    <cfRule type="duplicateValues" dxfId="362" priority="482"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B862">
-    <cfRule type="duplicateValues" dxfId="361" priority="477"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B862">
-    <cfRule type="duplicateValues" dxfId="360" priority="476"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B862">
-    <cfRule type="duplicateValues" dxfId="359" priority="475"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B864">
-    <cfRule type="duplicateValues" dxfId="358" priority="466"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B864">
-    <cfRule type="duplicateValues" dxfId="357" priority="467"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B864">
-    <cfRule type="duplicateValues" dxfId="356" priority="468"/>
+    <cfRule type="duplicateValues" dxfId="365" priority="512"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B861">
+    <cfRule type="duplicateValues" dxfId="364" priority="507"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B861">
+    <cfRule type="duplicateValues" dxfId="363" priority="506"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B861">
+    <cfRule type="duplicateValues" dxfId="362" priority="505"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B863">
+    <cfRule type="duplicateValues" dxfId="361" priority="496"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B863">
+    <cfRule type="duplicateValues" dxfId="360" priority="497"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B863">
+    <cfRule type="duplicateValues" dxfId="359" priority="498"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B868">
+    <cfRule type="duplicateValues" dxfId="358" priority="485"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B868">
+    <cfRule type="duplicateValues" dxfId="357" priority="486"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B868">
+    <cfRule type="duplicateValues" dxfId="356" priority="487"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B866">
+    <cfRule type="duplicateValues" dxfId="355" priority="482"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B866">
+    <cfRule type="duplicateValues" dxfId="354" priority="483"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B866">
+    <cfRule type="duplicateValues" dxfId="353" priority="484"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B867">
+    <cfRule type="duplicateValues" dxfId="352" priority="479"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B867">
+    <cfRule type="duplicateValues" dxfId="351" priority="480"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B867">
+    <cfRule type="duplicateValues" dxfId="350" priority="481"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B869">
-    <cfRule type="duplicateValues" dxfId="355" priority="455"/>
+    <cfRule type="duplicateValues" dxfId="349" priority="477"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B869">
-    <cfRule type="duplicateValues" dxfId="354" priority="456"/>
+    <cfRule type="duplicateValues" dxfId="348" priority="476"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B869">
-    <cfRule type="duplicateValues" dxfId="353" priority="457"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B867">
-    <cfRule type="duplicateValues" dxfId="352" priority="452"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B867">
-    <cfRule type="duplicateValues" dxfId="351" priority="453"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B867">
-    <cfRule type="duplicateValues" dxfId="350" priority="454"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B868">
-    <cfRule type="duplicateValues" dxfId="349" priority="449"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B868">
-    <cfRule type="duplicateValues" dxfId="348" priority="450"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B868">
-    <cfRule type="duplicateValues" dxfId="347" priority="451"/>
+    <cfRule type="duplicateValues" dxfId="347" priority="478"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B870">
-    <cfRule type="duplicateValues" dxfId="346" priority="447"/>
+    <cfRule type="duplicateValues" dxfId="346" priority="470"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B870">
-    <cfRule type="duplicateValues" dxfId="345" priority="446"/>
+    <cfRule type="duplicateValues" dxfId="345" priority="471"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B870">
-    <cfRule type="duplicateValues" dxfId="344" priority="448"/>
+    <cfRule type="duplicateValues" dxfId="344" priority="472"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B871">
-    <cfRule type="duplicateValues" dxfId="343" priority="440"/>
+    <cfRule type="duplicateValues" dxfId="343" priority="464"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B871">
-    <cfRule type="duplicateValues" dxfId="342" priority="441"/>
+    <cfRule type="duplicateValues" dxfId="342" priority="465"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B871">
-    <cfRule type="duplicateValues" dxfId="341" priority="442"/>
+    <cfRule type="duplicateValues" dxfId="341" priority="466"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B873">
+    <cfRule type="duplicateValues" dxfId="340" priority="461"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B873">
+    <cfRule type="duplicateValues" dxfId="339" priority="462"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B873">
+    <cfRule type="duplicateValues" dxfId="338" priority="463"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B872">
-    <cfRule type="duplicateValues" dxfId="340" priority="434"/>
+    <cfRule type="duplicateValues" dxfId="337" priority="455"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B872">
-    <cfRule type="duplicateValues" dxfId="339" priority="435"/>
+    <cfRule type="duplicateValues" dxfId="336" priority="456"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B872">
-    <cfRule type="duplicateValues" dxfId="338" priority="436"/>
+    <cfRule type="duplicateValues" dxfId="335" priority="457"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B874">
-    <cfRule type="duplicateValues" dxfId="337" priority="431"/>
+    <cfRule type="duplicateValues" dxfId="334" priority="449"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B874">
-    <cfRule type="duplicateValues" dxfId="336" priority="432"/>
+    <cfRule type="duplicateValues" dxfId="333" priority="450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B874">
-    <cfRule type="duplicateValues" dxfId="335" priority="433"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B873">
-    <cfRule type="duplicateValues" dxfId="334" priority="425"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B873">
-    <cfRule type="duplicateValues" dxfId="333" priority="426"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B873">
-    <cfRule type="duplicateValues" dxfId="332" priority="427"/>
+    <cfRule type="duplicateValues" dxfId="332" priority="451"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B875">
-    <cfRule type="duplicateValues" dxfId="331" priority="419"/>
+    <cfRule type="duplicateValues" dxfId="331" priority="446"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B875">
-    <cfRule type="duplicateValues" dxfId="330" priority="420"/>
+    <cfRule type="duplicateValues" dxfId="330" priority="447"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B875">
-    <cfRule type="duplicateValues" dxfId="329" priority="421"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B876">
-    <cfRule type="duplicateValues" dxfId="328" priority="416"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B876">
-    <cfRule type="duplicateValues" dxfId="327" priority="417"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B876">
-    <cfRule type="duplicateValues" dxfId="326" priority="418"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B878">
-    <cfRule type="duplicateValues" dxfId="325" priority="413"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B878">
-    <cfRule type="duplicateValues" dxfId="324" priority="414"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B878">
-    <cfRule type="duplicateValues" dxfId="323" priority="415"/>
+    <cfRule type="duplicateValues" dxfId="329" priority="448"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B877">
+    <cfRule type="duplicateValues" dxfId="328" priority="443"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B877">
+    <cfRule type="duplicateValues" dxfId="327" priority="444"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B877">
+    <cfRule type="duplicateValues" dxfId="326" priority="445"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B879">
+    <cfRule type="duplicateValues" dxfId="325" priority="440"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B879">
+    <cfRule type="duplicateValues" dxfId="324" priority="441"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B879">
+    <cfRule type="duplicateValues" dxfId="323" priority="442"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B881">
+    <cfRule type="duplicateValues" dxfId="322" priority="437"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B881">
+    <cfRule type="duplicateValues" dxfId="321" priority="438"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B881">
+    <cfRule type="duplicateValues" dxfId="320" priority="439"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B882">
+    <cfRule type="duplicateValues" dxfId="319" priority="435"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B882">
+    <cfRule type="duplicateValues" dxfId="318" priority="434"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B882">
+    <cfRule type="duplicateValues" dxfId="317" priority="436"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B884">
+    <cfRule type="duplicateValues" dxfId="316" priority="431"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B884">
+    <cfRule type="duplicateValues" dxfId="315" priority="432"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B884">
+    <cfRule type="duplicateValues" dxfId="314" priority="433"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B883">
+    <cfRule type="duplicateValues" dxfId="313" priority="428"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B883">
+    <cfRule type="duplicateValues" dxfId="312" priority="429"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B883">
+    <cfRule type="duplicateValues" dxfId="311" priority="430"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B885">
+    <cfRule type="duplicateValues" dxfId="310" priority="425"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B885">
+    <cfRule type="duplicateValues" dxfId="309" priority="426"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B885">
+    <cfRule type="duplicateValues" dxfId="308" priority="427"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B886">
+    <cfRule type="duplicateValues" dxfId="307" priority="422"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B886">
+    <cfRule type="duplicateValues" dxfId="306" priority="423"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B886">
+    <cfRule type="duplicateValues" dxfId="305" priority="424"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B887">
+    <cfRule type="duplicateValues" dxfId="304" priority="416"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B887">
+    <cfRule type="duplicateValues" dxfId="303" priority="417"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B887">
+    <cfRule type="duplicateValues" dxfId="302" priority="418"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B888">
+    <cfRule type="duplicateValues" dxfId="301" priority="410"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B888">
+    <cfRule type="duplicateValues" dxfId="300" priority="411"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B888">
+    <cfRule type="duplicateValues" dxfId="299" priority="412"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B889">
+    <cfRule type="duplicateValues" dxfId="298" priority="407"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B889">
+    <cfRule type="duplicateValues" dxfId="297" priority="408"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B889">
+    <cfRule type="duplicateValues" dxfId="296" priority="409"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B890">
+    <cfRule type="duplicateValues" dxfId="295" priority="398"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B890">
+    <cfRule type="duplicateValues" dxfId="294" priority="399"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B890">
+    <cfRule type="duplicateValues" dxfId="293" priority="400"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B891">
+    <cfRule type="duplicateValues" dxfId="292" priority="395"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B891">
+    <cfRule type="duplicateValues" dxfId="291" priority="396"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B891">
+    <cfRule type="duplicateValues" dxfId="290" priority="397"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B892">
+    <cfRule type="duplicateValues" dxfId="289" priority="394"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B892">
+    <cfRule type="duplicateValues" dxfId="288" priority="393"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B892">
+    <cfRule type="duplicateValues" dxfId="287" priority="392"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B893">
+    <cfRule type="duplicateValues" dxfId="286" priority="383"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B893">
+    <cfRule type="duplicateValues" dxfId="285" priority="384"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B893">
+    <cfRule type="duplicateValues" dxfId="284" priority="385"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B894">
+    <cfRule type="duplicateValues" dxfId="283" priority="374"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B894">
+    <cfRule type="duplicateValues" dxfId="282" priority="375"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B894">
+    <cfRule type="duplicateValues" dxfId="281" priority="376"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B895">
+    <cfRule type="duplicateValues" dxfId="280" priority="371"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B895">
+    <cfRule type="duplicateValues" dxfId="279" priority="372"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B895">
+    <cfRule type="duplicateValues" dxfId="278" priority="373"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B896">
+    <cfRule type="duplicateValues" dxfId="277" priority="369"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B896">
+    <cfRule type="duplicateValues" dxfId="276" priority="368"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B896">
+    <cfRule type="duplicateValues" dxfId="275" priority="370"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B880">
-    <cfRule type="duplicateValues" dxfId="322" priority="410"/>
+    <cfRule type="duplicateValues" dxfId="274" priority="365"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B880">
-    <cfRule type="duplicateValues" dxfId="321" priority="411"/>
+    <cfRule type="duplicateValues" dxfId="273" priority="366"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B880">
-    <cfRule type="duplicateValues" dxfId="320" priority="412"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B882">
-    <cfRule type="duplicateValues" dxfId="319" priority="407"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B882">
-    <cfRule type="duplicateValues" dxfId="318" priority="408"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B882">
-    <cfRule type="duplicateValues" dxfId="317" priority="409"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B883">
-    <cfRule type="duplicateValues" dxfId="316" priority="405"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B883">
-    <cfRule type="duplicateValues" dxfId="315" priority="404"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B883">
-    <cfRule type="duplicateValues" dxfId="314" priority="406"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B885">
-    <cfRule type="duplicateValues" dxfId="313" priority="401"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B885">
-    <cfRule type="duplicateValues" dxfId="312" priority="402"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B885">
-    <cfRule type="duplicateValues" dxfId="311" priority="403"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B884">
-    <cfRule type="duplicateValues" dxfId="310" priority="398"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B884">
-    <cfRule type="duplicateValues" dxfId="309" priority="399"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B884">
-    <cfRule type="duplicateValues" dxfId="308" priority="400"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B886">
-    <cfRule type="duplicateValues" dxfId="307" priority="395"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B886">
-    <cfRule type="duplicateValues" dxfId="306" priority="396"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B886">
-    <cfRule type="duplicateValues" dxfId="305" priority="397"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B887">
-    <cfRule type="duplicateValues" dxfId="304" priority="392"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B887">
-    <cfRule type="duplicateValues" dxfId="303" priority="393"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B887">
-    <cfRule type="duplicateValues" dxfId="302" priority="394"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B888">
-    <cfRule type="duplicateValues" dxfId="301" priority="386"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B888">
-    <cfRule type="duplicateValues" dxfId="300" priority="387"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B888">
-    <cfRule type="duplicateValues" dxfId="299" priority="388"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B889">
-    <cfRule type="duplicateValues" dxfId="298" priority="380"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B889">
-    <cfRule type="duplicateValues" dxfId="297" priority="381"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B889">
-    <cfRule type="duplicateValues" dxfId="296" priority="382"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B890">
-    <cfRule type="duplicateValues" dxfId="295" priority="377"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B890">
-    <cfRule type="duplicateValues" dxfId="294" priority="378"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B890">
-    <cfRule type="duplicateValues" dxfId="293" priority="379"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B891">
-    <cfRule type="duplicateValues" dxfId="292" priority="368"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B891">
-    <cfRule type="duplicateValues" dxfId="291" priority="369"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B891">
-    <cfRule type="duplicateValues" dxfId="290" priority="370"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B892">
-    <cfRule type="duplicateValues" dxfId="289" priority="365"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B892">
-    <cfRule type="duplicateValues" dxfId="288" priority="366"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B892">
-    <cfRule type="duplicateValues" dxfId="287" priority="367"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B893">
-    <cfRule type="duplicateValues" dxfId="286" priority="364"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B893">
-    <cfRule type="duplicateValues" dxfId="285" priority="363"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B893">
-    <cfRule type="duplicateValues" dxfId="284" priority="362"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B894">
-    <cfRule type="duplicateValues" dxfId="283" priority="353"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B894">
-    <cfRule type="duplicateValues" dxfId="282" priority="354"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B894">
-    <cfRule type="duplicateValues" dxfId="281" priority="355"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B895">
-    <cfRule type="duplicateValues" dxfId="280" priority="344"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B895">
-    <cfRule type="duplicateValues" dxfId="279" priority="345"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B895">
-    <cfRule type="duplicateValues" dxfId="278" priority="346"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B896">
-    <cfRule type="duplicateValues" dxfId="277" priority="341"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B896">
-    <cfRule type="duplicateValues" dxfId="276" priority="342"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B896">
-    <cfRule type="duplicateValues" dxfId="275" priority="343"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B897">
-    <cfRule type="duplicateValues" dxfId="274" priority="339"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B897">
-    <cfRule type="duplicateValues" dxfId="273" priority="338"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B897">
-    <cfRule type="duplicateValues" dxfId="272" priority="340"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B881">
-    <cfRule type="duplicateValues" dxfId="271" priority="335"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B881">
-    <cfRule type="duplicateValues" dxfId="270" priority="336"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B881">
-    <cfRule type="duplicateValues" dxfId="269" priority="337"/>
+    <cfRule type="duplicateValues" dxfId="272" priority="367"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B898">
+    <cfRule type="duplicateValues" dxfId="271" priority="360"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B898">
+    <cfRule type="duplicateValues" dxfId="270" priority="359"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B898">
+    <cfRule type="duplicateValues" dxfId="269" priority="361"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B899">
-    <cfRule type="duplicateValues" dxfId="268" priority="330"/>
+    <cfRule type="duplicateValues" dxfId="268" priority="356"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B899">
-    <cfRule type="duplicateValues" dxfId="267" priority="329"/>
+    <cfRule type="duplicateValues" dxfId="267" priority="357"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B899">
-    <cfRule type="duplicateValues" dxfId="266" priority="331"/>
+    <cfRule type="duplicateValues" dxfId="266" priority="358"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B900">
-    <cfRule type="duplicateValues" dxfId="265" priority="326"/>
+    <cfRule type="duplicateValues" dxfId="265" priority="347"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B900">
-    <cfRule type="duplicateValues" dxfId="264" priority="327"/>
+    <cfRule type="duplicateValues" dxfId="264" priority="348"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B900">
-    <cfRule type="duplicateValues" dxfId="263" priority="328"/>
+    <cfRule type="duplicateValues" dxfId="263" priority="349"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B901">
-    <cfRule type="duplicateValues" dxfId="262" priority="317"/>
+    <cfRule type="duplicateValues" dxfId="262" priority="344"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B901">
-    <cfRule type="duplicateValues" dxfId="261" priority="318"/>
+    <cfRule type="duplicateValues" dxfId="261" priority="345"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B901">
-    <cfRule type="duplicateValues" dxfId="260" priority="319"/>
+    <cfRule type="duplicateValues" dxfId="260" priority="346"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B902">
-    <cfRule type="duplicateValues" dxfId="259" priority="314"/>
+    <cfRule type="duplicateValues" dxfId="259" priority="339"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B902">
-    <cfRule type="duplicateValues" dxfId="258" priority="315"/>
+    <cfRule type="duplicateValues" dxfId="258" priority="340"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B902">
-    <cfRule type="duplicateValues" dxfId="257" priority="316"/>
+    <cfRule type="duplicateValues" dxfId="257" priority="341"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B903">
-    <cfRule type="duplicateValues" dxfId="256" priority="309"/>
+    <cfRule type="duplicateValues" dxfId="256" priority="336"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B903">
-    <cfRule type="duplicateValues" dxfId="255" priority="310"/>
+    <cfRule type="duplicateValues" dxfId="255" priority="337"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B903">
-    <cfRule type="duplicateValues" dxfId="254" priority="311"/>
+    <cfRule type="duplicateValues" dxfId="254" priority="338"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B904">
-    <cfRule type="duplicateValues" dxfId="253" priority="306"/>
+    <cfRule type="duplicateValues" dxfId="253" priority="330"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B904">
-    <cfRule type="duplicateValues" dxfId="252" priority="307"/>
+    <cfRule type="duplicateValues" dxfId="252" priority="331"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B904">
-    <cfRule type="duplicateValues" dxfId="251" priority="308"/>
+    <cfRule type="duplicateValues" dxfId="251" priority="332"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B905">
-    <cfRule type="duplicateValues" dxfId="250" priority="300"/>
+    <cfRule type="duplicateValues" dxfId="250" priority="324"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B905">
-    <cfRule type="duplicateValues" dxfId="249" priority="301"/>
+    <cfRule type="duplicateValues" dxfId="249" priority="325"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B905">
-    <cfRule type="duplicateValues" dxfId="248" priority="302"/>
+    <cfRule type="duplicateValues" dxfId="248" priority="326"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B907">
+    <cfRule type="duplicateValues" dxfId="247" priority="321"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B907">
+    <cfRule type="duplicateValues" dxfId="246" priority="322"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B907">
+    <cfRule type="duplicateValues" dxfId="245" priority="323"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B906">
-    <cfRule type="duplicateValues" dxfId="247" priority="294"/>
+    <cfRule type="duplicateValues" dxfId="244" priority="318"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B906">
-    <cfRule type="duplicateValues" dxfId="246" priority="295"/>
+    <cfRule type="duplicateValues" dxfId="243" priority="319"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B906">
-    <cfRule type="duplicateValues" dxfId="245" priority="296"/>
+    <cfRule type="duplicateValues" dxfId="242" priority="320"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B909">
+    <cfRule type="duplicateValues" dxfId="241" priority="315"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B909">
+    <cfRule type="duplicateValues" dxfId="240" priority="316"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B909">
+    <cfRule type="duplicateValues" dxfId="239" priority="317"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B908">
-    <cfRule type="duplicateValues" dxfId="244" priority="291"/>
+    <cfRule type="duplicateValues" dxfId="238" priority="312"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B908">
-    <cfRule type="duplicateValues" dxfId="243" priority="292"/>
+    <cfRule type="duplicateValues" dxfId="237" priority="313"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B908">
-    <cfRule type="duplicateValues" dxfId="242" priority="293"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B907">
-    <cfRule type="duplicateValues" dxfId="241" priority="288"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B907">
-    <cfRule type="duplicateValues" dxfId="240" priority="289"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B907">
-    <cfRule type="duplicateValues" dxfId="239" priority="290"/>
+    <cfRule type="duplicateValues" dxfId="236" priority="314"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B910">
-    <cfRule type="duplicateValues" dxfId="238" priority="285"/>
+    <cfRule type="duplicateValues" dxfId="235" priority="303"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B910">
-    <cfRule type="duplicateValues" dxfId="237" priority="286"/>
+    <cfRule type="duplicateValues" dxfId="234" priority="304"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B910">
-    <cfRule type="duplicateValues" dxfId="236" priority="287"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B909">
-    <cfRule type="duplicateValues" dxfId="235" priority="282"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B909">
-    <cfRule type="duplicateValues" dxfId="234" priority="283"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B909">
-    <cfRule type="duplicateValues" dxfId="233" priority="284"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B911">
-    <cfRule type="duplicateValues" dxfId="232" priority="273"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B911">
-    <cfRule type="duplicateValues" dxfId="231" priority="274"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B911">
-    <cfRule type="duplicateValues" dxfId="230" priority="275"/>
+    <cfRule type="duplicateValues" dxfId="233" priority="305"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B912">
+    <cfRule type="duplicateValues" dxfId="232" priority="300"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B912">
+    <cfRule type="duplicateValues" dxfId="231" priority="301"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B912">
+    <cfRule type="duplicateValues" dxfId="230" priority="302"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B913">
-    <cfRule type="duplicateValues" dxfId="229" priority="270"/>
+    <cfRule type="duplicateValues" dxfId="229" priority="297"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B913">
-    <cfRule type="duplicateValues" dxfId="228" priority="271"/>
+    <cfRule type="duplicateValues" dxfId="228" priority="298"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B913">
-    <cfRule type="duplicateValues" dxfId="227" priority="272"/>
+    <cfRule type="duplicateValues" dxfId="227" priority="299"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B914">
-    <cfRule type="duplicateValues" dxfId="226" priority="267"/>
+    <cfRule type="duplicateValues" dxfId="226" priority="294"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B914">
-    <cfRule type="duplicateValues" dxfId="225" priority="268"/>
+    <cfRule type="duplicateValues" dxfId="225" priority="295"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B914">
-    <cfRule type="duplicateValues" dxfId="224" priority="269"/>
+    <cfRule type="duplicateValues" dxfId="224" priority="296"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B915">
-    <cfRule type="duplicateValues" dxfId="223" priority="264"/>
+    <cfRule type="duplicateValues" dxfId="223" priority="288"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B915">
-    <cfRule type="duplicateValues" dxfId="222" priority="265"/>
+    <cfRule type="duplicateValues" dxfId="222" priority="289"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B915">
-    <cfRule type="duplicateValues" dxfId="221" priority="266"/>
+    <cfRule type="duplicateValues" dxfId="221" priority="290"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B916">
-    <cfRule type="duplicateValues" dxfId="220" priority="258"/>
+    <cfRule type="duplicateValues" dxfId="220" priority="285"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B916">
-    <cfRule type="duplicateValues" dxfId="219" priority="259"/>
+    <cfRule type="duplicateValues" dxfId="219" priority="286"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B916">
-    <cfRule type="duplicateValues" dxfId="218" priority="260"/>
+    <cfRule type="duplicateValues" dxfId="218" priority="287"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B917">
-    <cfRule type="duplicateValues" dxfId="217" priority="255"/>
+    <cfRule type="duplicateValues" dxfId="217" priority="283"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B917">
-    <cfRule type="duplicateValues" dxfId="216" priority="256"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B917">
-    <cfRule type="duplicateValues" dxfId="215" priority="257"/>
+    <cfRule type="duplicateValues" dxfId="216" priority="284"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B918">
-    <cfRule type="duplicateValues" dxfId="214" priority="253"/>
+    <cfRule type="duplicateValues" dxfId="215" priority="280"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B918">
-    <cfRule type="duplicateValues" dxfId="213" priority="254"/>
+    <cfRule type="duplicateValues" dxfId="214" priority="281"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B918">
+    <cfRule type="duplicateValues" dxfId="213" priority="282"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B919">
-    <cfRule type="duplicateValues" dxfId="212" priority="250"/>
+    <cfRule type="duplicateValues" dxfId="212" priority="277"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B919">
-    <cfRule type="duplicateValues" dxfId="211" priority="251"/>
+    <cfRule type="duplicateValues" dxfId="211" priority="278"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B919">
-    <cfRule type="duplicateValues" dxfId="210" priority="252"/>
+    <cfRule type="duplicateValues" dxfId="210" priority="279"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B920">
-    <cfRule type="duplicateValues" dxfId="209" priority="247"/>
+    <cfRule type="duplicateValues" dxfId="209" priority="268"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B920">
-    <cfRule type="duplicateValues" dxfId="208" priority="248"/>
+    <cfRule type="duplicateValues" dxfId="208" priority="269"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B920">
-    <cfRule type="duplicateValues" dxfId="207" priority="249"/>
+    <cfRule type="duplicateValues" dxfId="207" priority="270"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B922">
+    <cfRule type="duplicateValues" dxfId="206" priority="267"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B922">
+    <cfRule type="duplicateValues" dxfId="205" priority="266"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B922">
+    <cfRule type="duplicateValues" dxfId="204" priority="265"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B921">
-    <cfRule type="duplicateValues" dxfId="206" priority="238"/>
+    <cfRule type="duplicateValues" dxfId="203" priority="256"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B921">
-    <cfRule type="duplicateValues" dxfId="205" priority="239"/>
+    <cfRule type="duplicateValues" dxfId="202" priority="257"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B921">
-    <cfRule type="duplicateValues" dxfId="204" priority="240"/>
+    <cfRule type="duplicateValues" dxfId="201" priority="258"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B923">
-    <cfRule type="duplicateValues" dxfId="203" priority="237"/>
+    <cfRule type="duplicateValues" dxfId="200" priority="253"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B923">
-    <cfRule type="duplicateValues" dxfId="202" priority="236"/>
+    <cfRule type="duplicateValues" dxfId="199" priority="254"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B923">
-    <cfRule type="duplicateValues" dxfId="201" priority="235"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B922">
-    <cfRule type="duplicateValues" dxfId="200" priority="226"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B922">
-    <cfRule type="duplicateValues" dxfId="199" priority="227"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B922">
-    <cfRule type="duplicateValues" dxfId="198" priority="228"/>
+    <cfRule type="duplicateValues" dxfId="198" priority="255"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B924">
-    <cfRule type="duplicateValues" dxfId="197" priority="223"/>
+    <cfRule type="duplicateValues" dxfId="197" priority="247"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B924">
-    <cfRule type="duplicateValues" dxfId="196" priority="224"/>
+    <cfRule type="duplicateValues" dxfId="196" priority="248"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B924">
-    <cfRule type="duplicateValues" dxfId="195" priority="225"/>
+    <cfRule type="duplicateValues" dxfId="195" priority="249"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B925">
-    <cfRule type="duplicateValues" dxfId="194" priority="217"/>
+    <cfRule type="duplicateValues" dxfId="194" priority="238"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B925">
-    <cfRule type="duplicateValues" dxfId="193" priority="218"/>
+    <cfRule type="duplicateValues" dxfId="193" priority="239"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B925">
-    <cfRule type="duplicateValues" dxfId="192" priority="219"/>
+    <cfRule type="duplicateValues" dxfId="192" priority="240"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B926">
-    <cfRule type="duplicateValues" dxfId="191" priority="208"/>
+    <cfRule type="duplicateValues" dxfId="191" priority="235"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B926">
-    <cfRule type="duplicateValues" dxfId="190" priority="209"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="236"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B926">
-    <cfRule type="duplicateValues" dxfId="189" priority="210"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B927">
-    <cfRule type="duplicateValues" dxfId="188" priority="205"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B927">
-    <cfRule type="duplicateValues" dxfId="187" priority="206"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B927">
-    <cfRule type="duplicateValues" dxfId="186" priority="207"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B930">
-    <cfRule type="duplicateValues" dxfId="185" priority="202"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B930">
-    <cfRule type="duplicateValues" dxfId="184" priority="203"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B930">
-    <cfRule type="duplicateValues" dxfId="183" priority="204"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B932">
-    <cfRule type="duplicateValues" dxfId="182" priority="199"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B932">
-    <cfRule type="duplicateValues" dxfId="181" priority="200"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B932">
-    <cfRule type="duplicateValues" dxfId="180" priority="201"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="237"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B929">
+    <cfRule type="duplicateValues" dxfId="188" priority="232"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B929">
+    <cfRule type="duplicateValues" dxfId="187" priority="233"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B929">
+    <cfRule type="duplicateValues" dxfId="186" priority="234"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B931">
+    <cfRule type="duplicateValues" dxfId="185" priority="229"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B931">
+    <cfRule type="duplicateValues" dxfId="184" priority="230"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B931">
+    <cfRule type="duplicateValues" dxfId="183" priority="231"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B934">
+    <cfRule type="duplicateValues" dxfId="182" priority="226"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B934">
+    <cfRule type="duplicateValues" dxfId="181" priority="227"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B934">
+    <cfRule type="duplicateValues" dxfId="180" priority="228"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B935">
-    <cfRule type="duplicateValues" dxfId="179" priority="196"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="220"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B935">
-    <cfRule type="duplicateValues" dxfId="178" priority="197"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="221"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B935">
-    <cfRule type="duplicateValues" dxfId="177" priority="198"/>
+    <cfRule type="duplicateValues" dxfId="177" priority="222"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B937">
+    <cfRule type="duplicateValues" dxfId="176" priority="217"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B937">
+    <cfRule type="duplicateValues" dxfId="175" priority="218"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B937">
+    <cfRule type="duplicateValues" dxfId="174" priority="219"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B936">
-    <cfRule type="duplicateValues" dxfId="176" priority="190"/>
+    <cfRule type="duplicateValues" dxfId="173" priority="211"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B936">
-    <cfRule type="duplicateValues" dxfId="175" priority="191"/>
+    <cfRule type="duplicateValues" dxfId="172" priority="212"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B936">
-    <cfRule type="duplicateValues" dxfId="174" priority="192"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="213"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B938">
-    <cfRule type="duplicateValues" dxfId="173" priority="187"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="205"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B938">
-    <cfRule type="duplicateValues" dxfId="172" priority="188"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="206"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B938">
-    <cfRule type="duplicateValues" dxfId="171" priority="189"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B937">
-    <cfRule type="duplicateValues" dxfId="170" priority="181"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B937">
-    <cfRule type="duplicateValues" dxfId="169" priority="182"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B937">
-    <cfRule type="duplicateValues" dxfId="168" priority="183"/>
+    <cfRule type="duplicateValues" dxfId="168" priority="207"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B939">
-    <cfRule type="duplicateValues" dxfId="167" priority="175"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="199"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B939">
-    <cfRule type="duplicateValues" dxfId="166" priority="176"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="200"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B939">
-    <cfRule type="duplicateValues" dxfId="165" priority="177"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="201"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B940">
-    <cfRule type="duplicateValues" dxfId="164" priority="169"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="190"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B940">
-    <cfRule type="duplicateValues" dxfId="163" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="191"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B940">
-    <cfRule type="duplicateValues" dxfId="162" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="192"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B941">
-    <cfRule type="duplicateValues" dxfId="161" priority="160"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="185"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B941">
-    <cfRule type="duplicateValues" dxfId="160" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="184"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B941">
-    <cfRule type="duplicateValues" dxfId="159" priority="162"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B942">
-    <cfRule type="duplicateValues" dxfId="158" priority="155"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B942">
-    <cfRule type="duplicateValues" dxfId="157" priority="154"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B942">
-    <cfRule type="duplicateValues" dxfId="156" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="186"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B943">
+    <cfRule type="duplicateValues" dxfId="158" priority="175"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B943">
+    <cfRule type="duplicateValues" dxfId="157" priority="176"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B943">
+    <cfRule type="duplicateValues" dxfId="156" priority="177"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B944">
-    <cfRule type="duplicateValues" dxfId="155" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="169"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B944">
-    <cfRule type="duplicateValues" dxfId="154" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="170"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B944">
-    <cfRule type="duplicateValues" dxfId="153" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="171"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B945">
-    <cfRule type="duplicateValues" dxfId="152" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="166"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B945">
-    <cfRule type="duplicateValues" dxfId="151" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="167"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B945">
-    <cfRule type="duplicateValues" dxfId="150" priority="141"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="168"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B946">
-    <cfRule type="duplicateValues" dxfId="149" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="163"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B946">
-    <cfRule type="duplicateValues" dxfId="148" priority="137"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="164"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B946">
-    <cfRule type="duplicateValues" dxfId="147" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="165"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B947">
-    <cfRule type="duplicateValues" dxfId="146" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="159"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B947">
-    <cfRule type="duplicateValues" dxfId="145" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="158"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B947">
-    <cfRule type="duplicateValues" dxfId="144" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="157"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B948">
-    <cfRule type="duplicateValues" dxfId="143" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="155"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B948">
-    <cfRule type="duplicateValues" dxfId="142" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="154"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B948">
-    <cfRule type="duplicateValues" dxfId="141" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="156"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B949">
-    <cfRule type="duplicateValues" dxfId="140" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="151"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B949">
-    <cfRule type="duplicateValues" dxfId="139" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="152"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B949">
-    <cfRule type="duplicateValues" dxfId="138" priority="126"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B950">
-    <cfRule type="duplicateValues" dxfId="137" priority="121"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B950">
-    <cfRule type="duplicateValues" dxfId="136" priority="122"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B950">
-    <cfRule type="duplicateValues" dxfId="135" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="153"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9">
-    <cfRule type="duplicateValues" dxfId="134" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="148"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9">
-    <cfRule type="duplicateValues" dxfId="133" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="149"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9">
-    <cfRule type="duplicateValues" dxfId="132" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="150"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10">
-    <cfRule type="duplicateValues" dxfId="131" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="145"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10">
-    <cfRule type="duplicateValues" dxfId="130" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="146"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10">
-    <cfRule type="duplicateValues" dxfId="129" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="147"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
-    <cfRule type="duplicateValues" dxfId="128" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="142"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
-    <cfRule type="duplicateValues" dxfId="127" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="143"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
-    <cfRule type="duplicateValues" dxfId="126" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="144"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="125" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="139"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="124" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="140"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="123" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="141"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20">
-    <cfRule type="duplicateValues" dxfId="122" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="136"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20">
-    <cfRule type="duplicateValues" dxfId="121" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="137"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20">
-    <cfRule type="duplicateValues" dxfId="120" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="138"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="duplicateValues" dxfId="119" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="133"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="duplicateValues" dxfId="118" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="134"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="duplicateValues" dxfId="117" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="135"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="duplicateValues" dxfId="116" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="130"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="duplicateValues" dxfId="115" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="131"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="duplicateValues" dxfId="114" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="132"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="duplicateValues" dxfId="113" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="127"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="duplicateValues" dxfId="112" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="128"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="duplicateValues" dxfId="111" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="129"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="110" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="124"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="109" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="125"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="108" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="126"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27">
-    <cfRule type="duplicateValues" dxfId="107" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="121"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27">
-    <cfRule type="duplicateValues" dxfId="106" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="122"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27">
-    <cfRule type="duplicateValues" dxfId="105" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="123"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28">
-    <cfRule type="duplicateValues" dxfId="104" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28">
-    <cfRule type="duplicateValues" dxfId="103" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28">
-    <cfRule type="duplicateValues" dxfId="102" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="120"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29">
-    <cfRule type="duplicateValues" dxfId="101" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29">
-    <cfRule type="duplicateValues" dxfId="100" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="116"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29">
-    <cfRule type="duplicateValues" dxfId="99" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="117"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="98" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="112"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="97" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="96" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="95" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="109"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="94" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="93" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="111"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="92" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="91" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="90" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="89" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="88" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="87" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="105"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="86" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="85" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="84" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="83" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="97"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="82" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="98"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="81" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="99"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="80" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="94"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="79" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="95"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="78" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="77" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="76" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="92"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="75" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="93"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="74" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="73" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="89"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="72" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="90"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47">
-    <cfRule type="duplicateValues" dxfId="71" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47">
-    <cfRule type="duplicateValues" dxfId="70" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47">
-    <cfRule type="duplicateValues" dxfId="69" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="68" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="67" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="66" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="65" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="64" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="63" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="62" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="61" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="60" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55">
-    <cfRule type="duplicateValues" dxfId="59" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55">
-    <cfRule type="duplicateValues" dxfId="58" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55">
-    <cfRule type="duplicateValues" dxfId="57" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="56" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="55" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="54" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B60">
-    <cfRule type="duplicateValues" dxfId="53" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B60">
-    <cfRule type="duplicateValues" dxfId="52" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B60">
-    <cfRule type="duplicateValues" dxfId="51" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B61">
-    <cfRule type="duplicateValues" dxfId="50" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B61">
-    <cfRule type="duplicateValues" dxfId="49" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B61">
-    <cfRule type="duplicateValues" dxfId="48" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B65">
-    <cfRule type="duplicateValues" dxfId="47" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B65">
-    <cfRule type="duplicateValues" dxfId="46" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B65">
-    <cfRule type="duplicateValues" dxfId="45" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B66">
-    <cfRule type="duplicateValues" dxfId="44" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B66">
-    <cfRule type="duplicateValues" dxfId="43" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B66">
-    <cfRule type="duplicateValues" dxfId="42" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="41" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="40" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="39" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68">
-    <cfRule type="duplicateValues" dxfId="38" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68">
-    <cfRule type="duplicateValues" dxfId="37" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68">
-    <cfRule type="duplicateValues" dxfId="36" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="35" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="33" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="31" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70">
-    <cfRule type="duplicateValues" dxfId="23" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70">
-    <cfRule type="duplicateValues" dxfId="21" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70">
-    <cfRule type="duplicateValues" dxfId="19" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="17" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="15" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="13" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72">
-    <cfRule type="duplicateValues" dxfId="11" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72">
-    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72">
-    <cfRule type="duplicateValues" dxfId="7" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B73">
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B73">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B73">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B95">
+    <cfRule type="duplicateValues" dxfId="23" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B95">
+    <cfRule type="duplicateValues" dxfId="22" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B95">
+    <cfRule type="duplicateValues" dxfId="21" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B107">
+    <cfRule type="duplicateValues" dxfId="20" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B107">
+    <cfRule type="duplicateValues" dxfId="19" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B107">
+    <cfRule type="duplicateValues" dxfId="18" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B112">
+    <cfRule type="duplicateValues" dxfId="17" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B112">
+    <cfRule type="duplicateValues" dxfId="16" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B112">
+    <cfRule type="duplicateValues" dxfId="15" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B113">
+    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B113">
+    <cfRule type="duplicateValues" dxfId="13" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B113">
+    <cfRule type="duplicateValues" dxfId="12" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B120">
+    <cfRule type="duplicateValues" dxfId="11" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B120">
+    <cfRule type="duplicateValues" dxfId="10" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B120">
+    <cfRule type="duplicateValues" dxfId="9" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B121">
+    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B121">
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B121">
+    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B123">
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B123">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B123">
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B127">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B127">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B127">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Spanish Dictionary.xlsx
+++ b/Spanish Dictionary.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="1775">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1929" uniqueCount="1920">
   <si>
     <t>Word / Expression</t>
   </si>
@@ -5341,6 +5341,441 @@
   </si>
   <si>
     <t>unit 12</t>
+  </si>
+  <si>
+    <t>Morad - De Nada</t>
+  </si>
+  <si>
+    <t>Si tú quieres te enseño a hacerlo</t>
+  </si>
+  <si>
+    <t>If you want, I can teach you how to do it.</t>
+  </si>
+  <si>
+    <t>cee to kiérés té énsényoh ah asérlo</t>
+  </si>
+  <si>
+    <t>El que habla se le da pa'l pelo</t>
+  </si>
+  <si>
+    <t>The one who speaks is getting a beating</t>
+  </si>
+  <si>
+    <t>éhl kéh ablah sélé dah pal péloh</t>
+  </si>
+  <si>
+    <t>El que habla se le manda pa'l cielo</t>
+  </si>
+  <si>
+    <t>The one who speaks is sent to heaven</t>
+  </si>
+  <si>
+    <t>éhl kéh ablah sélé mandah pal ciélo</t>
+  </si>
+  <si>
+    <t>Obligatory, that's the first thing</t>
+  </si>
+  <si>
+    <t>Obligado, es lo primero</t>
+  </si>
+  <si>
+    <t>obligadoh és loh priméroh</t>
+  </si>
+  <si>
+    <t>Si te conviertes en un traicionero</t>
+  </si>
+  <si>
+    <t>If you become a traitor</t>
+  </si>
+  <si>
+    <t>cee téh conbiérté-séh-nun-trais-yonéroh</t>
+  </si>
+  <si>
+    <t>O le faltas a todo' tus valores</t>
+  </si>
+  <si>
+    <t>Or you lack all your values</t>
+  </si>
+  <si>
+    <t>oh léh faltas ah todoh tus bahloréhs</t>
+  </si>
+  <si>
+    <t>No hay dinero que lo recupere</t>
+  </si>
+  <si>
+    <t>No amount of money can bring him back</t>
+  </si>
+  <si>
+    <t>noh ahyy dinéroh kéh lo récupéréh</t>
+  </si>
+  <si>
+    <t>No hay dinero que a ti te ayude</t>
+  </si>
+  <si>
+    <t>There is no amount of money that will help you</t>
+  </si>
+  <si>
+    <t>noh ahyy dinéroh kéh ah te téh ayudéh</t>
+  </si>
+  <si>
+    <t>Lo buscaban haciendo regates</t>
+  </si>
+  <si>
+    <t>They were looking for him by dribbling</t>
+  </si>
+  <si>
+    <t>loh buscaban ahsiéndoh régatés</t>
+  </si>
+  <si>
+    <t>Se buscaba hasta que llegue al tope</t>
+  </si>
+  <si>
+    <t>The search continued until I reached the top</t>
+  </si>
+  <si>
+    <t>séh buscabah astah kéh yégéh al topéh</t>
+  </si>
+  <si>
+    <t>No se piensa nunca en los escotes</t>
+  </si>
+  <si>
+    <t>They never think about low-cut necklines</t>
+  </si>
+  <si>
+    <t>noh séh piénsah nuncah én los éscotés</t>
+  </si>
+  <si>
+    <t>Solo money, nunca los pegotes</t>
+  </si>
+  <si>
+    <t>Just money, never the sticky bits</t>
+  </si>
+  <si>
+    <t>soloh money nunca los pégotés</t>
+  </si>
+  <si>
+    <t>They throw away the bundles of 100s and 20s</t>
+  </si>
+  <si>
+    <t>Let them throw away the bundles but in 50-dollar stacks</t>
+  </si>
+  <si>
+    <t>Que botan los fajos pero de cincuenta</t>
+  </si>
+  <si>
+    <t>kéh botan los fakhos péroh dé cinquéntah</t>
+  </si>
+  <si>
+    <t>Que botan los fajos de cien y de veinte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kéh botan los fakhos déh siéhn ee dé véintéh </t>
+  </si>
+  <si>
+    <t>Que botan, que botan</t>
+  </si>
+  <si>
+    <t>kéh botan kéh botan</t>
+  </si>
+  <si>
+    <t>Let them throw, let them throw</t>
+  </si>
+  <si>
+    <t>Se busca solo pa' la mama</t>
+  </si>
+  <si>
+    <t>Looking for mom only</t>
+  </si>
+  <si>
+    <t>séh buscah soloh pah lah mama</t>
+  </si>
+  <si>
+    <t>Ella se merece todo lo que gane</t>
+  </si>
+  <si>
+    <t>She deserves everything she earns</t>
+  </si>
+  <si>
+    <t>éhyah sé méréséh todoh loh kéh ganéh</t>
+  </si>
+  <si>
+    <t>No creo en gente que venga en tiempo y me lo mame</t>
+  </si>
+  <si>
+    <t>noh kréoh én khénté kéh véngah én tiémpoh ee mé loh mamé</t>
+  </si>
+  <si>
+    <t>I don't believe in people who come along on time and suck me off</t>
+  </si>
+  <si>
+    <t>No debo a ninguno, yo no debo nada</t>
+  </si>
+  <si>
+    <t>I don't owe anyone, I don't owe anything</t>
+  </si>
+  <si>
+    <t>noh déboh ah nengunoh yph noh déboh nadah</t>
+  </si>
+  <si>
+    <t>Te vendes solo por la fama</t>
+  </si>
+  <si>
+    <t>You sell yourself just for fame</t>
+  </si>
+  <si>
+    <t>téh véndéh soloh por lah famah</t>
+  </si>
+  <si>
+    <t>A ninguno yo le debo de nada</t>
+  </si>
+  <si>
+    <t>I don't owe any of them anything</t>
+  </si>
+  <si>
+    <t>ah nengunoh yoh léh déboh déh nadah</t>
+  </si>
+  <si>
+    <t>Empecé yo solo de la nada</t>
+  </si>
+  <si>
+    <t>I started all by myself from nothing</t>
+  </si>
+  <si>
+    <t>émpécéh yoh soloh déh lah nadah</t>
+  </si>
+  <si>
+    <t>El que envidia a mí me deseaba</t>
+  </si>
+  <si>
+    <t>He who envied me desired me</t>
+  </si>
+  <si>
+    <t>éhl kéh-énbidiah ah me mé déséabah</t>
+  </si>
+  <si>
+    <t>Veía como me elevaba</t>
+  </si>
+  <si>
+    <t>I watched myself rise</t>
+  </si>
+  <si>
+    <t>véiah komoh mé élébabah</t>
+  </si>
+  <si>
+    <t>Veía como yo subia</t>
+  </si>
+  <si>
+    <t>He watched me go up</t>
+  </si>
+  <si>
+    <t>véiah komoh yoh subiah</t>
+  </si>
+  <si>
+    <t>Veía que nunca cambiaba</t>
+  </si>
+  <si>
+    <t>I saw that he never changed</t>
+  </si>
+  <si>
+    <t>véiah kéh nunkah kambiabah</t>
+  </si>
+  <si>
+    <t>Y que siempre tengo yo la calle metia'</t>
+  </si>
+  <si>
+    <t>And that I always have the street involved</t>
+  </si>
+  <si>
+    <t>ee kéh siémpréh téngoh yoh lah kayéh métiah</t>
+  </si>
+  <si>
+    <t>Veian que me la sudaba</t>
+  </si>
+  <si>
+    <t>They could see I didn't give a damn</t>
+  </si>
+  <si>
+    <t>véian kéh méh lah sudabah</t>
+  </si>
+  <si>
+    <t>Que ganase lo que fuera al día</t>
+  </si>
+  <si>
+    <t>That he earned whatever he earned each day</t>
+  </si>
+  <si>
+    <t>kéh ganaséh loh kéh fuérah al deeyah</t>
+  </si>
+  <si>
+    <t>Veian que nunca llamaba</t>
+  </si>
+  <si>
+    <t>They saw that he never called</t>
+  </si>
+  <si>
+    <t>véian kéh nunkah yahmabah</t>
+  </si>
+  <si>
+    <t>Pase lo que pasaria</t>
+  </si>
+  <si>
+    <t>whatever happened</t>
+  </si>
+  <si>
+    <t>paséh loh kéh pasariah</t>
+  </si>
+  <si>
+    <t>Y siempre he sido un hombre en la calle</t>
+  </si>
+  <si>
+    <t>And I've always been a man of the streets</t>
+  </si>
+  <si>
+    <t>ee siémpréh éh sidoh own-ombré én la kayéh</t>
+  </si>
+  <si>
+    <t>Como también en comisaria</t>
+  </si>
+  <si>
+    <t>As well as at the police station</t>
+  </si>
+  <si>
+    <t>komoh también én komisariah</t>
+  </si>
+  <si>
+    <t>Nunca me escondo</t>
+  </si>
+  <si>
+    <t>I never hide</t>
+  </si>
+  <si>
+    <t>nunkah méh éskondoh</t>
+  </si>
+  <si>
+    <t>Aunque a veces escucho que alguno de estos matarían</t>
+  </si>
+  <si>
+    <t>Although I sometimes hear that some of these would kill</t>
+  </si>
+  <si>
+    <t>ah-ownkéh  ah véséhs éskoutchoh kéh algunoh déh éstos matarian</t>
+  </si>
+  <si>
+    <t>La vida es una</t>
+  </si>
+  <si>
+    <t>life is one</t>
+  </si>
+  <si>
+    <t>la vidah éhs ownah</t>
+  </si>
+  <si>
+    <t>Tengo la lista por si algún día</t>
+  </si>
+  <si>
+    <t>téngoh lah listah por cee algun diah</t>
+  </si>
+  <si>
+    <t>I have the list just in case someday</t>
+  </si>
+  <si>
+    <t>Me toca irme primero</t>
+  </si>
+  <si>
+    <t>It's my turn to go first</t>
+  </si>
+  <si>
+    <t>méh tokah irméh priméroh</t>
+  </si>
+  <si>
+    <t>Que se vayan conmigo todos en fila</t>
+  </si>
+  <si>
+    <t>Everyone, come with me in a line</t>
+  </si>
+  <si>
+    <t>kéh séh bayan konmigoh todohs én filah</t>
+  </si>
+  <si>
+    <t>Ya no creo de la calle el que más vacila</t>
+  </si>
+  <si>
+    <t>I no longer believe the one who hesitates the most on the street</t>
+  </si>
+  <si>
+    <t>yah noh kréoh dé lah kayéh éhl kéh mahs vasilah</t>
+  </si>
+  <si>
+    <t>Miles de problemas llevo en mi mochila</t>
+  </si>
+  <si>
+    <t>I carry thousands of problems in my backpack</t>
+  </si>
+  <si>
+    <t>milés dé problémahs yéboh én mi motchilah</t>
+  </si>
+  <si>
+    <t>Siempre he sido fiel</t>
+  </si>
+  <si>
+    <t>siémpréh éh sidoh fiél</t>
+  </si>
+  <si>
+    <t>I have always been faithful</t>
+  </si>
+  <si>
+    <t>Siempre soy de la L</t>
+  </si>
+  <si>
+    <t>I'm always from the L</t>
+  </si>
+  <si>
+    <t>siémpréh soy dé lah L</t>
+  </si>
+  <si>
+    <t>Que te mate la envidia o te mate cartón</t>
+  </si>
+  <si>
+    <t>kéh té maté la enbidia oh té maté karton</t>
+  </si>
+  <si>
+    <t>May envy kill you, or may cardboard kill you</t>
+  </si>
+  <si>
+    <t>Pero eso es cuando ya no quiera</t>
+  </si>
+  <si>
+    <t>péro ésoh és quandoh yah noh kiérah</t>
+  </si>
+  <si>
+    <t>But that's when I no longer want to</t>
+  </si>
+  <si>
+    <t>Estamos en pila de loquera</t>
+  </si>
+  <si>
+    <t>éstahmos én pilah dé lokérah</t>
+  </si>
+  <si>
+    <t>We're going crazy</t>
+  </si>
+  <si>
+    <t>Somos de la L, somos de la L</t>
+  </si>
+  <si>
+    <t>sohmos délah éleh, sohmos délah éleh</t>
+  </si>
+  <si>
+    <t>We're from L, we're from L</t>
+  </si>
+  <si>
+    <t>La guerra la hacemo' a cualquiera</t>
+  </si>
+  <si>
+    <t>We wage war against anyone</t>
+  </si>
+  <si>
+    <t>lah guérrah lah-asémoh à-qual-kéirah</t>
   </si>
 </sst>
 </file>
@@ -5388,207 +5823,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1689">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1669">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -22576,7 +22811,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:D603"/>
+  <dimension ref="B1:D652"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="1" customWidth="1"/>
@@ -29153,5013 +29388,5546 @@
         <v>1774</v>
       </c>
     </row>
+    <row r="604" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B604" s="1" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="605" spans="2:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="B605" s="1" t="s">
+        <v>1776</v>
+      </c>
+      <c r="C605" s="1" t="s">
+        <v>1778</v>
+      </c>
+      <c r="D605" s="2" t="s">
+        <v>1777</v>
+      </c>
+    </row>
+    <row r="606" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B606" s="1" t="s">
+        <v>1779</v>
+      </c>
+      <c r="C606" s="1" t="s">
+        <v>1781</v>
+      </c>
+      <c r="D606" s="1" t="s">
+        <v>1780</v>
+      </c>
+    </row>
+    <row r="607" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B607" s="1" t="s">
+        <v>1782</v>
+      </c>
+      <c r="C607" s="1" t="s">
+        <v>1784</v>
+      </c>
+      <c r="D607" s="1" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="608" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B608" s="1" t="s">
+        <v>1786</v>
+      </c>
+      <c r="C608" s="1" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D608" s="1" t="s">
+        <v>1785</v>
+      </c>
+    </row>
+    <row r="609" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B609" s="1" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C609" s="1" t="s">
+        <v>1790</v>
+      </c>
+      <c r="D609" s="1" t="s">
+        <v>1789</v>
+      </c>
+    </row>
+    <row r="610" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B610" s="1" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C610" s="1" t="s">
+        <v>1793</v>
+      </c>
+      <c r="D610" s="1" t="s">
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="611" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B611" s="1" t="s">
+        <v>1794</v>
+      </c>
+      <c r="C611" s="1" t="s">
+        <v>1796</v>
+      </c>
+      <c r="D611" s="1" t="s">
+        <v>1795</v>
+      </c>
+    </row>
+    <row r="612" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B612" s="1" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C612" s="1" t="s">
+        <v>1799</v>
+      </c>
+      <c r="D612" s="1" t="s">
+        <v>1798</v>
+      </c>
+    </row>
+    <row r="613" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B613" s="1" t="s">
+        <v>1800</v>
+      </c>
+      <c r="C613" s="1" t="s">
+        <v>1802</v>
+      </c>
+      <c r="D613" s="1" t="s">
+        <v>1801</v>
+      </c>
+    </row>
+    <row r="614" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B614" s="1" t="s">
+        <v>1803</v>
+      </c>
+      <c r="C614" s="1" t="s">
+        <v>1805</v>
+      </c>
+      <c r="D614" s="1" t="s">
+        <v>1804</v>
+      </c>
+    </row>
+    <row r="615" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B615" s="1" t="s">
+        <v>1806</v>
+      </c>
+      <c r="C615" s="1" t="s">
+        <v>1808</v>
+      </c>
+      <c r="D615" s="1" t="s">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="616" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B616" s="1" t="s">
+        <v>1809</v>
+      </c>
+      <c r="C616" s="1" t="s">
+        <v>1811</v>
+      </c>
+      <c r="D616" s="1" t="s">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="617" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B617" s="1" t="s">
+        <v>1818</v>
+      </c>
+      <c r="C617" s="1" t="s">
+        <v>1819</v>
+      </c>
+      <c r="D617" s="1" t="s">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="618" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B618" s="1" t="s">
+        <v>1814</v>
+      </c>
+      <c r="C618" s="1" t="s">
+        <v>1815</v>
+      </c>
+      <c r="D618" s="1" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="619" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B619" s="1" t="s">
+        <v>1816</v>
+      </c>
+      <c r="C619" s="1" t="s">
+        <v>1817</v>
+      </c>
+      <c r="D619" s="1" t="s">
+        <v>1812</v>
+      </c>
+    </row>
+    <row r="620" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B620" s="1" t="s">
+        <v>1821</v>
+      </c>
+      <c r="C620" s="1" t="s">
+        <v>1823</v>
+      </c>
+      <c r="D620" s="1" t="s">
+        <v>1822</v>
+      </c>
+    </row>
+    <row r="621" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B621" s="1" t="s">
+        <v>1824</v>
+      </c>
+      <c r="C621" s="1" t="s">
+        <v>1826</v>
+      </c>
+      <c r="D621" s="1" t="s">
+        <v>1825</v>
+      </c>
+    </row>
+    <row r="622" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B622" s="1" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C622" s="1" t="s">
+        <v>1828</v>
+      </c>
+      <c r="D622" s="1" t="s">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="623" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B623" s="1" t="s">
+        <v>1830</v>
+      </c>
+      <c r="C623" s="1" t="s">
+        <v>1832</v>
+      </c>
+      <c r="D623" s="1" t="s">
+        <v>1831</v>
+      </c>
+    </row>
+    <row r="624" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B624" s="1" t="s">
+        <v>1833</v>
+      </c>
+      <c r="C624" s="1" t="s">
+        <v>1835</v>
+      </c>
+      <c r="D624" s="1" t="s">
+        <v>1834</v>
+      </c>
+    </row>
+    <row r="625" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B625" s="1" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C625" s="1" t="s">
+        <v>1838</v>
+      </c>
+      <c r="D625" s="1" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="626" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B626" s="1" t="s">
+        <v>1839</v>
+      </c>
+      <c r="C626" s="1" t="s">
+        <v>1841</v>
+      </c>
+      <c r="D626" s="1" t="s">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="627" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B627" s="1" t="s">
+        <v>1842</v>
+      </c>
+      <c r="C627" s="1" t="s">
+        <v>1844</v>
+      </c>
+      <c r="D627" s="1" t="s">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="628" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B628" s="1" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C628" s="1" t="s">
+        <v>1847</v>
+      </c>
+      <c r="D628" s="1" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="629" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B629" s="1" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C629" s="1" t="s">
+        <v>1850</v>
+      </c>
+      <c r="D629" s="1" t="s">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="630" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B630" s="1" t="s">
+        <v>1851</v>
+      </c>
+      <c r="C630" s="1" t="s">
+        <v>1853</v>
+      </c>
+      <c r="D630" s="1" t="s">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="631" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B631" s="1" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C631" s="1" t="s">
+        <v>1856</v>
+      </c>
+      <c r="D631" s="1" t="s">
+        <v>1855</v>
+      </c>
+    </row>
+    <row r="632" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B632" s="1" t="s">
+        <v>1857</v>
+      </c>
+      <c r="C632" s="1" t="s">
+        <v>1859</v>
+      </c>
+      <c r="D632" s="1" t="s">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="633" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B633" s="1" t="s">
+        <v>1860</v>
+      </c>
+      <c r="C633" s="1" t="s">
+        <v>1862</v>
+      </c>
+      <c r="D633" s="1" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="634" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B634" s="1" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C634" s="1" t="s">
+        <v>1865</v>
+      </c>
+      <c r="D634" s="1" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="635" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B635" s="1" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C635" s="1" t="s">
+        <v>1868</v>
+      </c>
+      <c r="D635" s="1" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="636" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B636" s="1" t="s">
+        <v>1869</v>
+      </c>
+      <c r="C636" s="1" t="s">
+        <v>1871</v>
+      </c>
+      <c r="D636" s="1" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="637" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B637" s="1" t="s">
+        <v>1872</v>
+      </c>
+      <c r="C637" s="1" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D637" s="1" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="638" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B638" s="1" t="s">
+        <v>1875</v>
+      </c>
+      <c r="C638" s="1" t="s">
+        <v>1877</v>
+      </c>
+      <c r="D638" s="1" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="639" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B639" s="1" t="s">
+        <v>1878</v>
+      </c>
+      <c r="C639" s="1" t="s">
+        <v>1880</v>
+      </c>
+      <c r="D639" s="1" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="640" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B640" s="1" t="s">
+        <v>1881</v>
+      </c>
+      <c r="C640" s="1" t="s">
+        <v>1883</v>
+      </c>
+      <c r="D640" s="1" t="s">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="641" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B641" s="1" t="s">
+        <v>1884</v>
+      </c>
+      <c r="C641" s="1" t="s">
+        <v>1885</v>
+      </c>
+      <c r="D641" s="1" t="s">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="642" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B642" s="1" t="s">
+        <v>1887</v>
+      </c>
+      <c r="C642" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="D642" s="1" t="s">
+        <v>1888</v>
+      </c>
+    </row>
+    <row r="643" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B643" s="1" t="s">
+        <v>1890</v>
+      </c>
+      <c r="C643" s="1" t="s">
+        <v>1892</v>
+      </c>
+      <c r="D643" s="1" t="s">
+        <v>1891</v>
+      </c>
+    </row>
+    <row r="644" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B644" s="1" t="s">
+        <v>1893</v>
+      </c>
+      <c r="C644" s="1" t="s">
+        <v>1895</v>
+      </c>
+      <c r="D644" s="1" t="s">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="645" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B645" s="1" t="s">
+        <v>1896</v>
+      </c>
+      <c r="C645" s="1" t="s">
+        <v>1898</v>
+      </c>
+      <c r="D645" s="1" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="646" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B646" s="1" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C646" s="1" t="s">
+        <v>1900</v>
+      </c>
+      <c r="D646" s="1" t="s">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="647" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B647" s="1" t="s">
+        <v>1902</v>
+      </c>
+      <c r="C647" s="1" t="s">
+        <v>1904</v>
+      </c>
+      <c r="D647" s="1" t="s">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="648" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B648" s="1" t="s">
+        <v>1905</v>
+      </c>
+      <c r="C648" s="1" t="s">
+        <v>1906</v>
+      </c>
+      <c r="D648" s="1" t="s">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="649" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B649" s="1" t="s">
+        <v>1908</v>
+      </c>
+      <c r="C649" s="1" t="s">
+        <v>1909</v>
+      </c>
+      <c r="D649" s="1" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="650" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B650" s="1" t="s">
+        <v>1911</v>
+      </c>
+      <c r="C650" s="1" t="s">
+        <v>1912</v>
+      </c>
+      <c r="D650" s="1" t="s">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="651" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B651" s="1" t="s">
+        <v>1914</v>
+      </c>
+      <c r="C651" s="1" t="s">
+        <v>1915</v>
+      </c>
+      <c r="D651" s="1" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="652" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B652" s="1" t="s">
+        <v>1917</v>
+      </c>
+      <c r="C652" s="1" t="s">
+        <v>1919</v>
+      </c>
+      <c r="D652" s="1" t="s">
+        <v>1918</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B108">
-    <cfRule type="duplicateValues" dxfId="1688" priority="2489"/>
+    <cfRule type="duplicateValues" dxfId="1668" priority="2489"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B125">
-    <cfRule type="duplicateValues" dxfId="1687" priority="2488"/>
+    <cfRule type="duplicateValues" dxfId="1667" priority="2488"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B132">
-    <cfRule type="duplicateValues" dxfId="1686" priority="2487"/>
+    <cfRule type="duplicateValues" dxfId="1666" priority="2487"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B128">
-    <cfRule type="duplicateValues" dxfId="1685" priority="2486"/>
+    <cfRule type="duplicateValues" dxfId="1665" priority="2486"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B129">
-    <cfRule type="duplicateValues" dxfId="1684" priority="2485"/>
+    <cfRule type="duplicateValues" dxfId="1664" priority="2485"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B130">
-    <cfRule type="duplicateValues" dxfId="1683" priority="2484"/>
+    <cfRule type="duplicateValues" dxfId="1663" priority="2484"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B133">
-    <cfRule type="duplicateValues" dxfId="1682" priority="2483"/>
+    <cfRule type="duplicateValues" dxfId="1662" priority="2483"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B135">
-    <cfRule type="duplicateValues" dxfId="1681" priority="2482"/>
+    <cfRule type="duplicateValues" dxfId="1661" priority="2482"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B136">
-    <cfRule type="duplicateValues" dxfId="1680" priority="2481"/>
+    <cfRule type="duplicateValues" dxfId="1660" priority="2481"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B138">
-    <cfRule type="duplicateValues" dxfId="1679" priority="2480"/>
+    <cfRule type="duplicateValues" dxfId="1659" priority="2480"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B139">
-    <cfRule type="duplicateValues" dxfId="1678" priority="2479"/>
+    <cfRule type="duplicateValues" dxfId="1658" priority="2479"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B140">
-    <cfRule type="duplicateValues" dxfId="1677" priority="2478"/>
+    <cfRule type="duplicateValues" dxfId="1657" priority="2478"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B141">
-    <cfRule type="duplicateValues" dxfId="1676" priority="2477"/>
+    <cfRule type="duplicateValues" dxfId="1656" priority="2477"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B142">
-    <cfRule type="duplicateValues" dxfId="1675" priority="2476"/>
+    <cfRule type="duplicateValues" dxfId="1655" priority="2476"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B148">
-    <cfRule type="duplicateValues" dxfId="1674" priority="2475"/>
+    <cfRule type="duplicateValues" dxfId="1654" priority="2475"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B149">
-    <cfRule type="duplicateValues" dxfId="1673" priority="2474"/>
+    <cfRule type="duplicateValues" dxfId="1653" priority="2474"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B154">
-    <cfRule type="duplicateValues" dxfId="1672" priority="2472"/>
+    <cfRule type="duplicateValues" dxfId="1652" priority="2472"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B155">
-    <cfRule type="duplicateValues" dxfId="1671" priority="2471"/>
+    <cfRule type="duplicateValues" dxfId="1651" priority="2471"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B157">
-    <cfRule type="duplicateValues" dxfId="1670" priority="2469"/>
+    <cfRule type="duplicateValues" dxfId="1650" priority="2469"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B161">
-    <cfRule type="duplicateValues" dxfId="1669" priority="2468"/>
+    <cfRule type="duplicateValues" dxfId="1649" priority="2468"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B162">
-    <cfRule type="duplicateValues" dxfId="1668" priority="2467"/>
+    <cfRule type="duplicateValues" dxfId="1648" priority="2467"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B163">
-    <cfRule type="duplicateValues" dxfId="1667" priority="2466"/>
+    <cfRule type="duplicateValues" dxfId="1647" priority="2466"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B164">
-    <cfRule type="duplicateValues" dxfId="1666" priority="2465"/>
+    <cfRule type="duplicateValues" dxfId="1646" priority="2465"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B166">
-    <cfRule type="duplicateValues" dxfId="1665" priority="2463"/>
+    <cfRule type="duplicateValues" dxfId="1645" priority="2463"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B167">
-    <cfRule type="duplicateValues" dxfId="1664" priority="2462"/>
+    <cfRule type="duplicateValues" dxfId="1644" priority="2462"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B170">
-    <cfRule type="duplicateValues" dxfId="1663" priority="2461"/>
+    <cfRule type="duplicateValues" dxfId="1643" priority="2461"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B179">
-    <cfRule type="duplicateValues" dxfId="1662" priority="2455"/>
+    <cfRule type="duplicateValues" dxfId="1642" priority="2455"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B186">
-    <cfRule type="duplicateValues" dxfId="1661" priority="2454"/>
+    <cfRule type="duplicateValues" dxfId="1641" priority="2454"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B187">
-    <cfRule type="duplicateValues" dxfId="1660" priority="2453"/>
+    <cfRule type="duplicateValues" dxfId="1640" priority="2453"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B191">
-    <cfRule type="duplicateValues" dxfId="1659" priority="2451"/>
+    <cfRule type="duplicateValues" dxfId="1639" priority="2451"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B192">
-    <cfRule type="duplicateValues" dxfId="1658" priority="2450"/>
+    <cfRule type="duplicateValues" dxfId="1638" priority="2450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B193">
-    <cfRule type="duplicateValues" dxfId="1657" priority="2449"/>
+    <cfRule type="duplicateValues" dxfId="1637" priority="2449"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B194">
-    <cfRule type="duplicateValues" dxfId="1656" priority="2448"/>
+    <cfRule type="duplicateValues" dxfId="1636" priority="2448"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B196">
-    <cfRule type="duplicateValues" dxfId="1655" priority="2447"/>
+    <cfRule type="duplicateValues" dxfId="1635" priority="2447"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B197">
-    <cfRule type="duplicateValues" dxfId="1654" priority="2446"/>
+    <cfRule type="duplicateValues" dxfId="1634" priority="2446"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B198">
-    <cfRule type="duplicateValues" dxfId="1653" priority="2445"/>
+    <cfRule type="duplicateValues" dxfId="1633" priority="2445"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B200">
-    <cfRule type="duplicateValues" dxfId="1652" priority="2444"/>
+    <cfRule type="duplicateValues" dxfId="1632" priority="2444"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B201">
-    <cfRule type="duplicateValues" dxfId="1651" priority="2443"/>
+    <cfRule type="duplicateValues" dxfId="1631" priority="2443"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B202">
-    <cfRule type="duplicateValues" dxfId="1650" priority="2442"/>
+    <cfRule type="duplicateValues" dxfId="1630" priority="2442"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B204">
-    <cfRule type="duplicateValues" dxfId="1649" priority="2441"/>
+    <cfRule type="duplicateValues" dxfId="1629" priority="2441"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B205">
-    <cfRule type="duplicateValues" dxfId="1648" priority="2440"/>
+    <cfRule type="duplicateValues" dxfId="1628" priority="2440"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B209">
-    <cfRule type="duplicateValues" dxfId="1647" priority="2436"/>
+    <cfRule type="duplicateValues" dxfId="1627" priority="2436"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B210">
-    <cfRule type="duplicateValues" dxfId="1646" priority="2435"/>
+    <cfRule type="duplicateValues" dxfId="1626" priority="2435"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B211">
-    <cfRule type="duplicateValues" dxfId="1645" priority="2434"/>
+    <cfRule type="duplicateValues" dxfId="1625" priority="2434"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B214">
-    <cfRule type="duplicateValues" dxfId="1644" priority="2433"/>
+    <cfRule type="duplicateValues" dxfId="1624" priority="2433"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B216">
-    <cfRule type="duplicateValues" dxfId="1643" priority="2431"/>
+    <cfRule type="duplicateValues" dxfId="1623" priority="2431"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B217">
-    <cfRule type="duplicateValues" dxfId="1642" priority="2430"/>
+    <cfRule type="duplicateValues" dxfId="1622" priority="2430"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B219">
-    <cfRule type="duplicateValues" dxfId="1641" priority="2429"/>
+    <cfRule type="duplicateValues" dxfId="1621" priority="2429"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B220">
-    <cfRule type="duplicateValues" dxfId="1640" priority="2428"/>
+    <cfRule type="duplicateValues" dxfId="1620" priority="2428"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B225">
-    <cfRule type="duplicateValues" dxfId="1639" priority="2426"/>
+    <cfRule type="duplicateValues" dxfId="1619" priority="2426"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B226">
-    <cfRule type="duplicateValues" dxfId="1638" priority="2425"/>
+    <cfRule type="duplicateValues" dxfId="1618" priority="2425"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B227">
-    <cfRule type="duplicateValues" dxfId="1637" priority="2424"/>
+    <cfRule type="duplicateValues" dxfId="1617" priority="2424"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B228">
-    <cfRule type="duplicateValues" dxfId="1636" priority="2423"/>
+    <cfRule type="duplicateValues" dxfId="1616" priority="2423"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B237">
-    <cfRule type="duplicateValues" dxfId="1635" priority="2413"/>
+    <cfRule type="duplicateValues" dxfId="1615" priority="2413"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B237">
-    <cfRule type="duplicateValues" dxfId="1634" priority="2412"/>
+    <cfRule type="duplicateValues" dxfId="1614" priority="2412"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B238">
-    <cfRule type="duplicateValues" dxfId="1633" priority="2411"/>
+    <cfRule type="duplicateValues" dxfId="1613" priority="2411"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B238">
-    <cfRule type="duplicateValues" dxfId="1632" priority="2410"/>
+    <cfRule type="duplicateValues" dxfId="1612" priority="2410"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B241">
-    <cfRule type="duplicateValues" dxfId="1631" priority="2409"/>
+    <cfRule type="duplicateValues" dxfId="1611" priority="2409"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B241">
-    <cfRule type="duplicateValues" dxfId="1630" priority="2408"/>
+    <cfRule type="duplicateValues" dxfId="1610" priority="2408"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B245">
-    <cfRule type="duplicateValues" dxfId="1629" priority="2407"/>
+    <cfRule type="duplicateValues" dxfId="1609" priority="2407"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B245">
-    <cfRule type="duplicateValues" dxfId="1628" priority="2406"/>
+    <cfRule type="duplicateValues" dxfId="1608" priority="2406"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B246">
-    <cfRule type="duplicateValues" dxfId="1627" priority="2405"/>
+    <cfRule type="duplicateValues" dxfId="1607" priority="2405"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B246">
-    <cfRule type="duplicateValues" dxfId="1626" priority="2404"/>
+    <cfRule type="duplicateValues" dxfId="1606" priority="2404"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B247">
-    <cfRule type="duplicateValues" dxfId="1625" priority="2403"/>
+    <cfRule type="duplicateValues" dxfId="1605" priority="2403"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B247">
-    <cfRule type="duplicateValues" dxfId="1624" priority="2402"/>
+    <cfRule type="duplicateValues" dxfId="1604" priority="2402"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B248">
-    <cfRule type="duplicateValues" dxfId="1623" priority="2401"/>
+    <cfRule type="duplicateValues" dxfId="1603" priority="2401"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B248">
-    <cfRule type="duplicateValues" dxfId="1622" priority="2400"/>
+    <cfRule type="duplicateValues" dxfId="1602" priority="2400"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B249">
-    <cfRule type="duplicateValues" dxfId="1621" priority="2399"/>
+    <cfRule type="duplicateValues" dxfId="1601" priority="2399"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B249">
-    <cfRule type="duplicateValues" dxfId="1620" priority="2398"/>
+    <cfRule type="duplicateValues" dxfId="1600" priority="2398"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B252">
-    <cfRule type="duplicateValues" dxfId="1619" priority="2393"/>
+    <cfRule type="duplicateValues" dxfId="1599" priority="2393"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B252">
-    <cfRule type="duplicateValues" dxfId="1618" priority="2392"/>
+    <cfRule type="duplicateValues" dxfId="1598" priority="2392"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B255">
-    <cfRule type="duplicateValues" dxfId="1617" priority="2389"/>
+    <cfRule type="duplicateValues" dxfId="1597" priority="2389"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B255">
-    <cfRule type="duplicateValues" dxfId="1616" priority="2388"/>
+    <cfRule type="duplicateValues" dxfId="1596" priority="2388"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B263">
-    <cfRule type="duplicateValues" dxfId="1615" priority="2385"/>
+    <cfRule type="duplicateValues" dxfId="1595" priority="2385"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B263">
-    <cfRule type="duplicateValues" dxfId="1614" priority="2384"/>
+    <cfRule type="duplicateValues" dxfId="1594" priority="2384"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B271">
-    <cfRule type="duplicateValues" dxfId="1613" priority="2381"/>
+    <cfRule type="duplicateValues" dxfId="1593" priority="2381"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B271">
-    <cfRule type="duplicateValues" dxfId="1612" priority="2380"/>
+    <cfRule type="duplicateValues" dxfId="1592" priority="2380"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B274">
-    <cfRule type="duplicateValues" dxfId="1611" priority="2377"/>
+    <cfRule type="duplicateValues" dxfId="1591" priority="2377"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B274">
-    <cfRule type="duplicateValues" dxfId="1610" priority="2376"/>
+    <cfRule type="duplicateValues" dxfId="1590" priority="2376"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B275">
-    <cfRule type="duplicateValues" dxfId="1609" priority="2375"/>
+    <cfRule type="duplicateValues" dxfId="1589" priority="2375"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B275">
-    <cfRule type="duplicateValues" dxfId="1608" priority="2374"/>
+    <cfRule type="duplicateValues" dxfId="1588" priority="2374"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B276">
-    <cfRule type="duplicateValues" dxfId="1607" priority="2373"/>
+    <cfRule type="duplicateValues" dxfId="1587" priority="2373"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B276">
-    <cfRule type="duplicateValues" dxfId="1606" priority="2372"/>
+    <cfRule type="duplicateValues" dxfId="1586" priority="2372"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B277">
-    <cfRule type="duplicateValues" dxfId="1605" priority="2369"/>
+    <cfRule type="duplicateValues" dxfId="1585" priority="2369"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B277">
-    <cfRule type="duplicateValues" dxfId="1604" priority="2368"/>
+    <cfRule type="duplicateValues" dxfId="1584" priority="2368"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B279">
-    <cfRule type="duplicateValues" dxfId="1603" priority="2367"/>
+    <cfRule type="duplicateValues" dxfId="1583" priority="2367"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B279">
-    <cfRule type="duplicateValues" dxfId="1602" priority="2366"/>
+    <cfRule type="duplicateValues" dxfId="1582" priority="2366"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B281">
-    <cfRule type="duplicateValues" dxfId="1601" priority="2361"/>
+    <cfRule type="duplicateValues" dxfId="1581" priority="2361"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B281">
-    <cfRule type="duplicateValues" dxfId="1600" priority="2360"/>
+    <cfRule type="duplicateValues" dxfId="1580" priority="2360"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B282">
-    <cfRule type="duplicateValues" dxfId="1599" priority="2359"/>
+    <cfRule type="duplicateValues" dxfId="1579" priority="2359"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B282">
-    <cfRule type="duplicateValues" dxfId="1598" priority="2358"/>
+    <cfRule type="duplicateValues" dxfId="1578" priority="2358"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B283">
-    <cfRule type="duplicateValues" dxfId="1597" priority="2357"/>
+    <cfRule type="duplicateValues" dxfId="1577" priority="2357"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B283">
-    <cfRule type="duplicateValues" dxfId="1596" priority="2356"/>
+    <cfRule type="duplicateValues" dxfId="1576" priority="2356"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B286">
-    <cfRule type="duplicateValues" dxfId="1595" priority="2351"/>
+    <cfRule type="duplicateValues" dxfId="1575" priority="2351"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B287">
-    <cfRule type="duplicateValues" dxfId="1594" priority="2348"/>
+    <cfRule type="duplicateValues" dxfId="1574" priority="2348"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B287">
-    <cfRule type="duplicateValues" dxfId="1593" priority="2347"/>
+    <cfRule type="duplicateValues" dxfId="1573" priority="2347"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B290">
-    <cfRule type="duplicateValues" dxfId="1592" priority="2346"/>
+    <cfRule type="duplicateValues" dxfId="1572" priority="2346"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B290">
-    <cfRule type="duplicateValues" dxfId="1591" priority="2345"/>
+    <cfRule type="duplicateValues" dxfId="1571" priority="2345"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B292">
-    <cfRule type="duplicateValues" dxfId="1590" priority="2344"/>
+    <cfRule type="duplicateValues" dxfId="1570" priority="2344"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B292">
-    <cfRule type="duplicateValues" dxfId="1589" priority="2343"/>
+    <cfRule type="duplicateValues" dxfId="1569" priority="2343"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B293">
-    <cfRule type="duplicateValues" dxfId="1588" priority="2340"/>
+    <cfRule type="duplicateValues" dxfId="1568" priority="2340"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B293">
-    <cfRule type="duplicateValues" dxfId="1587" priority="2339"/>
+    <cfRule type="duplicateValues" dxfId="1567" priority="2339"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B294">
-    <cfRule type="duplicateValues" dxfId="1586" priority="2338"/>
+    <cfRule type="duplicateValues" dxfId="1566" priority="2338"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B294">
-    <cfRule type="duplicateValues" dxfId="1585" priority="2337"/>
+    <cfRule type="duplicateValues" dxfId="1565" priority="2337"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B300">
-    <cfRule type="duplicateValues" dxfId="1584" priority="2336"/>
+    <cfRule type="duplicateValues" dxfId="1564" priority="2336"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B300">
-    <cfRule type="duplicateValues" dxfId="1583" priority="2335"/>
+    <cfRule type="duplicateValues" dxfId="1563" priority="2335"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B301">
-    <cfRule type="duplicateValues" dxfId="1582" priority="2334"/>
+    <cfRule type="duplicateValues" dxfId="1562" priority="2334"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B301">
-    <cfRule type="duplicateValues" dxfId="1581" priority="2333"/>
+    <cfRule type="duplicateValues" dxfId="1561" priority="2333"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B302">
-    <cfRule type="duplicateValues" dxfId="1580" priority="2330"/>
+    <cfRule type="duplicateValues" dxfId="1560" priority="2330"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B302">
-    <cfRule type="duplicateValues" dxfId="1579" priority="2329"/>
+    <cfRule type="duplicateValues" dxfId="1559" priority="2329"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B303">
-    <cfRule type="duplicateValues" dxfId="1578" priority="2328"/>
+    <cfRule type="duplicateValues" dxfId="1558" priority="2328"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B303">
-    <cfRule type="duplicateValues" dxfId="1577" priority="2327"/>
+    <cfRule type="duplicateValues" dxfId="1557" priority="2327"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B304">
-    <cfRule type="duplicateValues" dxfId="1576" priority="2326"/>
+    <cfRule type="duplicateValues" dxfId="1556" priority="2326"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B304">
-    <cfRule type="duplicateValues" dxfId="1575" priority="2325"/>
+    <cfRule type="duplicateValues" dxfId="1555" priority="2325"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B305">
-    <cfRule type="duplicateValues" dxfId="1574" priority="2324"/>
+    <cfRule type="duplicateValues" dxfId="1554" priority="2324"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B305">
-    <cfRule type="duplicateValues" dxfId="1573" priority="2323"/>
+    <cfRule type="duplicateValues" dxfId="1553" priority="2323"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B308">
-    <cfRule type="duplicateValues" dxfId="1572" priority="2319"/>
+    <cfRule type="duplicateValues" dxfId="1552" priority="2319"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B308">
-    <cfRule type="duplicateValues" dxfId="1571" priority="2318"/>
+    <cfRule type="duplicateValues" dxfId="1551" priority="2318"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B309">
-    <cfRule type="duplicateValues" dxfId="1570" priority="2317"/>
+    <cfRule type="duplicateValues" dxfId="1550" priority="2317"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B309">
-    <cfRule type="duplicateValues" dxfId="1569" priority="2316"/>
+    <cfRule type="duplicateValues" dxfId="1549" priority="2316"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B310">
-    <cfRule type="duplicateValues" dxfId="1568" priority="2315"/>
+    <cfRule type="duplicateValues" dxfId="1548" priority="2315"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B310">
-    <cfRule type="duplicateValues" dxfId="1567" priority="2314"/>
+    <cfRule type="duplicateValues" dxfId="1547" priority="2314"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B312">
-    <cfRule type="duplicateValues" dxfId="1566" priority="2309"/>
+    <cfRule type="duplicateValues" dxfId="1546" priority="2309"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B312">
-    <cfRule type="duplicateValues" dxfId="1565" priority="2308"/>
+    <cfRule type="duplicateValues" dxfId="1545" priority="2308"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B315">
-    <cfRule type="duplicateValues" dxfId="1564" priority="2301"/>
+    <cfRule type="duplicateValues" dxfId="1544" priority="2301"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B315">
-    <cfRule type="duplicateValues" dxfId="1563" priority="2300"/>
+    <cfRule type="duplicateValues" dxfId="1543" priority="2300"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B317">
-    <cfRule type="duplicateValues" dxfId="1562" priority="2293"/>
+    <cfRule type="duplicateValues" dxfId="1542" priority="2293"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B317">
-    <cfRule type="duplicateValues" dxfId="1561" priority="2292"/>
+    <cfRule type="duplicateValues" dxfId="1541" priority="2292"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B318">
-    <cfRule type="duplicateValues" dxfId="1560" priority="2291"/>
+    <cfRule type="duplicateValues" dxfId="1540" priority="2291"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B318">
-    <cfRule type="duplicateValues" dxfId="1559" priority="2290"/>
+    <cfRule type="duplicateValues" dxfId="1539" priority="2290"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B320">
-    <cfRule type="duplicateValues" dxfId="1558" priority="2283"/>
+    <cfRule type="duplicateValues" dxfId="1538" priority="2283"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B320">
-    <cfRule type="duplicateValues" dxfId="1557" priority="2282"/>
+    <cfRule type="duplicateValues" dxfId="1537" priority="2282"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B321">
-    <cfRule type="duplicateValues" dxfId="1556" priority="2281"/>
+    <cfRule type="duplicateValues" dxfId="1536" priority="2281"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B321">
-    <cfRule type="duplicateValues" dxfId="1555" priority="2280"/>
+    <cfRule type="duplicateValues" dxfId="1535" priority="2280"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B329">
-    <cfRule type="duplicateValues" dxfId="1554" priority="2261"/>
+    <cfRule type="duplicateValues" dxfId="1534" priority="2261"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B329">
-    <cfRule type="duplicateValues" dxfId="1553" priority="2260"/>
+    <cfRule type="duplicateValues" dxfId="1533" priority="2260"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B330">
-    <cfRule type="duplicateValues" dxfId="1552" priority="2257"/>
+    <cfRule type="duplicateValues" dxfId="1532" priority="2257"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B330">
-    <cfRule type="duplicateValues" dxfId="1551" priority="2256"/>
+    <cfRule type="duplicateValues" dxfId="1531" priority="2256"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B332">
-    <cfRule type="duplicateValues" dxfId="1550" priority="2255"/>
+    <cfRule type="duplicateValues" dxfId="1530" priority="2255"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B332">
-    <cfRule type="duplicateValues" dxfId="1549" priority="2254"/>
+    <cfRule type="duplicateValues" dxfId="1529" priority="2254"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B334">
-    <cfRule type="duplicateValues" dxfId="1548" priority="2253"/>
+    <cfRule type="duplicateValues" dxfId="1528" priority="2253"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B334">
-    <cfRule type="duplicateValues" dxfId="1547" priority="2252"/>
+    <cfRule type="duplicateValues" dxfId="1527" priority="2252"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B335">
-    <cfRule type="duplicateValues" dxfId="1546" priority="2251"/>
+    <cfRule type="duplicateValues" dxfId="1526" priority="2251"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B335">
-    <cfRule type="duplicateValues" dxfId="1545" priority="2250"/>
+    <cfRule type="duplicateValues" dxfId="1525" priority="2250"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B336">
-    <cfRule type="duplicateValues" dxfId="1544" priority="2247"/>
+    <cfRule type="duplicateValues" dxfId="1524" priority="2247"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B336">
-    <cfRule type="duplicateValues" dxfId="1543" priority="2246"/>
+    <cfRule type="duplicateValues" dxfId="1523" priority="2246"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B339">
-    <cfRule type="duplicateValues" dxfId="1542" priority="2245"/>
+    <cfRule type="duplicateValues" dxfId="1522" priority="2245"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B339">
-    <cfRule type="duplicateValues" dxfId="1541" priority="2244"/>
+    <cfRule type="duplicateValues" dxfId="1521" priority="2244"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B342">
-    <cfRule type="duplicateValues" dxfId="1540" priority="2241"/>
+    <cfRule type="duplicateValues" dxfId="1520" priority="2241"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B342">
-    <cfRule type="duplicateValues" dxfId="1539" priority="2240"/>
+    <cfRule type="duplicateValues" dxfId="1519" priority="2240"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B344">
-    <cfRule type="duplicateValues" dxfId="1538" priority="2235"/>
+    <cfRule type="duplicateValues" dxfId="1518" priority="2235"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B344">
-    <cfRule type="duplicateValues" dxfId="1537" priority="2234"/>
+    <cfRule type="duplicateValues" dxfId="1517" priority="2234"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B347">
-    <cfRule type="duplicateValues" dxfId="1536" priority="2233"/>
+    <cfRule type="duplicateValues" dxfId="1516" priority="2233"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B347">
-    <cfRule type="duplicateValues" dxfId="1535" priority="2232"/>
+    <cfRule type="duplicateValues" dxfId="1515" priority="2232"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B349">
-    <cfRule type="duplicateValues" dxfId="1534" priority="2231"/>
+    <cfRule type="duplicateValues" dxfId="1514" priority="2231"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B349">
-    <cfRule type="duplicateValues" dxfId="1533" priority="2230"/>
+    <cfRule type="duplicateValues" dxfId="1513" priority="2230"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B350">
-    <cfRule type="duplicateValues" dxfId="1532" priority="2227"/>
+    <cfRule type="duplicateValues" dxfId="1512" priority="2227"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B350">
-    <cfRule type="duplicateValues" dxfId="1531" priority="2226"/>
+    <cfRule type="duplicateValues" dxfId="1511" priority="2226"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B352">
-    <cfRule type="duplicateValues" dxfId="1530" priority="2223"/>
+    <cfRule type="duplicateValues" dxfId="1510" priority="2223"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B352">
-    <cfRule type="duplicateValues" dxfId="1529" priority="2222"/>
+    <cfRule type="duplicateValues" dxfId="1509" priority="2222"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B353">
-    <cfRule type="duplicateValues" dxfId="1528" priority="2219"/>
+    <cfRule type="duplicateValues" dxfId="1508" priority="2219"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B353">
-    <cfRule type="duplicateValues" dxfId="1527" priority="2218"/>
+    <cfRule type="duplicateValues" dxfId="1507" priority="2218"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B355">
-    <cfRule type="duplicateValues" dxfId="1526" priority="2215"/>
+    <cfRule type="duplicateValues" dxfId="1506" priority="2215"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B355">
-    <cfRule type="duplicateValues" dxfId="1525" priority="2214"/>
+    <cfRule type="duplicateValues" dxfId="1505" priority="2214"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B356">
-    <cfRule type="duplicateValues" dxfId="1524" priority="2213"/>
+    <cfRule type="duplicateValues" dxfId="1504" priority="2213"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B356">
-    <cfRule type="duplicateValues" dxfId="1523" priority="2212"/>
+    <cfRule type="duplicateValues" dxfId="1503" priority="2212"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B357">
-    <cfRule type="duplicateValues" dxfId="1522" priority="2211"/>
+    <cfRule type="duplicateValues" dxfId="1502" priority="2211"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B357">
-    <cfRule type="duplicateValues" dxfId="1521" priority="2210"/>
+    <cfRule type="duplicateValues" dxfId="1501" priority="2210"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B358">
-    <cfRule type="duplicateValues" dxfId="1520" priority="2207"/>
+    <cfRule type="duplicateValues" dxfId="1500" priority="2207"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B358">
-    <cfRule type="duplicateValues" dxfId="1519" priority="2206"/>
+    <cfRule type="duplicateValues" dxfId="1499" priority="2206"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B359">
-    <cfRule type="duplicateValues" dxfId="1518" priority="2205"/>
+    <cfRule type="duplicateValues" dxfId="1498" priority="2205"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B359">
-    <cfRule type="duplicateValues" dxfId="1517" priority="2204"/>
+    <cfRule type="duplicateValues" dxfId="1497" priority="2204"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B360">
-    <cfRule type="duplicateValues" dxfId="1516" priority="2203"/>
+    <cfRule type="duplicateValues" dxfId="1496" priority="2203"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B360">
-    <cfRule type="duplicateValues" dxfId="1515" priority="2202"/>
+    <cfRule type="duplicateValues" dxfId="1495" priority="2202"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B361">
-    <cfRule type="duplicateValues" dxfId="1514" priority="2201"/>
+    <cfRule type="duplicateValues" dxfId="1494" priority="2201"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B361">
-    <cfRule type="duplicateValues" dxfId="1513" priority="2200"/>
+    <cfRule type="duplicateValues" dxfId="1493" priority="2200"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B363">
-    <cfRule type="duplicateValues" dxfId="1512" priority="2197"/>
+    <cfRule type="duplicateValues" dxfId="1492" priority="2197"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B363">
-    <cfRule type="duplicateValues" dxfId="1511" priority="2196"/>
+    <cfRule type="duplicateValues" dxfId="1491" priority="2196"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B365">
-    <cfRule type="duplicateValues" dxfId="1510" priority="2191"/>
+    <cfRule type="duplicateValues" dxfId="1490" priority="2191"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B365">
-    <cfRule type="duplicateValues" dxfId="1509" priority="2190"/>
+    <cfRule type="duplicateValues" dxfId="1489" priority="2190"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B366">
-    <cfRule type="duplicateValues" dxfId="1508" priority="2187"/>
+    <cfRule type="duplicateValues" dxfId="1488" priority="2187"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B366">
-    <cfRule type="duplicateValues" dxfId="1507" priority="2186"/>
+    <cfRule type="duplicateValues" dxfId="1487" priority="2186"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B367">
-    <cfRule type="duplicateValues" dxfId="1506" priority="2183"/>
+    <cfRule type="duplicateValues" dxfId="1486" priority="2183"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B367">
-    <cfRule type="duplicateValues" dxfId="1505" priority="2182"/>
+    <cfRule type="duplicateValues" dxfId="1485" priority="2182"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B368">
-    <cfRule type="duplicateValues" dxfId="1504" priority="2181"/>
+    <cfRule type="duplicateValues" dxfId="1484" priority="2181"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B368">
-    <cfRule type="duplicateValues" dxfId="1503" priority="2180"/>
+    <cfRule type="duplicateValues" dxfId="1483" priority="2180"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B370">
-    <cfRule type="duplicateValues" dxfId="1502" priority="2175"/>
+    <cfRule type="duplicateValues" dxfId="1482" priority="2175"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B370">
-    <cfRule type="duplicateValues" dxfId="1501" priority="2174"/>
+    <cfRule type="duplicateValues" dxfId="1481" priority="2174"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B371">
-    <cfRule type="duplicateValues" dxfId="1500" priority="2173"/>
+    <cfRule type="duplicateValues" dxfId="1480" priority="2173"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B371">
-    <cfRule type="duplicateValues" dxfId="1499" priority="2172"/>
+    <cfRule type="duplicateValues" dxfId="1479" priority="2172"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B374">
-    <cfRule type="duplicateValues" dxfId="1498" priority="2167"/>
+    <cfRule type="duplicateValues" dxfId="1478" priority="2167"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B374">
-    <cfRule type="duplicateValues" dxfId="1497" priority="2166"/>
+    <cfRule type="duplicateValues" dxfId="1477" priority="2166"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B375">
-    <cfRule type="duplicateValues" dxfId="1496" priority="2165"/>
+    <cfRule type="duplicateValues" dxfId="1476" priority="2165"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B375">
-    <cfRule type="duplicateValues" dxfId="1495" priority="2164"/>
+    <cfRule type="duplicateValues" dxfId="1475" priority="2164"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B376">
-    <cfRule type="duplicateValues" dxfId="1494" priority="2161"/>
+    <cfRule type="duplicateValues" dxfId="1474" priority="2161"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B376">
-    <cfRule type="duplicateValues" dxfId="1493" priority="2160"/>
+    <cfRule type="duplicateValues" dxfId="1473" priority="2160"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B377">
-    <cfRule type="duplicateValues" dxfId="1492" priority="2157"/>
+    <cfRule type="duplicateValues" dxfId="1472" priority="2157"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B377">
-    <cfRule type="duplicateValues" dxfId="1491" priority="2156"/>
+    <cfRule type="duplicateValues" dxfId="1471" priority="2156"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B381">
-    <cfRule type="duplicateValues" dxfId="1490" priority="2155"/>
+    <cfRule type="duplicateValues" dxfId="1470" priority="2155"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B381">
-    <cfRule type="duplicateValues" dxfId="1489" priority="2154"/>
+    <cfRule type="duplicateValues" dxfId="1469" priority="2154"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B382">
-    <cfRule type="duplicateValues" dxfId="1488" priority="2151"/>
+    <cfRule type="duplicateValues" dxfId="1468" priority="2151"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B382">
-    <cfRule type="duplicateValues" dxfId="1487" priority="2150"/>
+    <cfRule type="duplicateValues" dxfId="1467" priority="2150"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B383">
-    <cfRule type="duplicateValues" dxfId="1486" priority="2147"/>
+    <cfRule type="duplicateValues" dxfId="1466" priority="2147"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B383">
-    <cfRule type="duplicateValues" dxfId="1485" priority="2146"/>
+    <cfRule type="duplicateValues" dxfId="1465" priority="2146"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B385">
-    <cfRule type="duplicateValues" dxfId="1484" priority="2143"/>
+    <cfRule type="duplicateValues" dxfId="1464" priority="2143"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B385">
-    <cfRule type="duplicateValues" dxfId="1483" priority="2142"/>
+    <cfRule type="duplicateValues" dxfId="1463" priority="2142"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B386">
-    <cfRule type="duplicateValues" dxfId="1482" priority="2137"/>
+    <cfRule type="duplicateValues" dxfId="1462" priority="2137"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B386">
-    <cfRule type="duplicateValues" dxfId="1481" priority="2136"/>
+    <cfRule type="duplicateValues" dxfId="1461" priority="2136"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B387">
-    <cfRule type="duplicateValues" dxfId="1480" priority="2131"/>
+    <cfRule type="duplicateValues" dxfId="1460" priority="2131"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B387">
-    <cfRule type="duplicateValues" dxfId="1479" priority="2130"/>
+    <cfRule type="duplicateValues" dxfId="1459" priority="2130"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B388">
-    <cfRule type="duplicateValues" dxfId="1478" priority="2129"/>
+    <cfRule type="duplicateValues" dxfId="1458" priority="2129"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B388">
-    <cfRule type="duplicateValues" dxfId="1477" priority="2128"/>
+    <cfRule type="duplicateValues" dxfId="1457" priority="2128"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B392">
-    <cfRule type="duplicateValues" dxfId="1476" priority="2125"/>
+    <cfRule type="duplicateValues" dxfId="1456" priority="2125"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B392">
-    <cfRule type="duplicateValues" dxfId="1475" priority="2124"/>
+    <cfRule type="duplicateValues" dxfId="1455" priority="2124"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B393">
-    <cfRule type="duplicateValues" dxfId="1474" priority="2123"/>
+    <cfRule type="duplicateValues" dxfId="1454" priority="2123"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B393">
-    <cfRule type="duplicateValues" dxfId="1473" priority="2122"/>
+    <cfRule type="duplicateValues" dxfId="1453" priority="2122"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B394">
-    <cfRule type="duplicateValues" dxfId="1472" priority="2119"/>
+    <cfRule type="duplicateValues" dxfId="1452" priority="2119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B394">
-    <cfRule type="duplicateValues" dxfId="1471" priority="2118"/>
+    <cfRule type="duplicateValues" dxfId="1451" priority="2118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B395">
-    <cfRule type="duplicateValues" dxfId="1470" priority="2117"/>
+    <cfRule type="duplicateValues" dxfId="1450" priority="2117"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B395">
-    <cfRule type="duplicateValues" dxfId="1469" priority="2116"/>
+    <cfRule type="duplicateValues" dxfId="1449" priority="2116"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B398">
-    <cfRule type="duplicateValues" dxfId="1468" priority="2115"/>
+    <cfRule type="duplicateValues" dxfId="1448" priority="2115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B398">
-    <cfRule type="duplicateValues" dxfId="1467" priority="2114"/>
+    <cfRule type="duplicateValues" dxfId="1447" priority="2114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B399">
-    <cfRule type="duplicateValues" dxfId="1466" priority="2113"/>
+    <cfRule type="duplicateValues" dxfId="1446" priority="2113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B399">
-    <cfRule type="duplicateValues" dxfId="1465" priority="2112"/>
+    <cfRule type="duplicateValues" dxfId="1445" priority="2112"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B400">
-    <cfRule type="duplicateValues" dxfId="1464" priority="2109"/>
+    <cfRule type="duplicateValues" dxfId="1444" priority="2109"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B400">
-    <cfRule type="duplicateValues" dxfId="1463" priority="2108"/>
+    <cfRule type="duplicateValues" dxfId="1443" priority="2108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B402">
-    <cfRule type="duplicateValues" dxfId="1462" priority="2107"/>
+    <cfRule type="duplicateValues" dxfId="1442" priority="2107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B402">
-    <cfRule type="duplicateValues" dxfId="1461" priority="2106"/>
+    <cfRule type="duplicateValues" dxfId="1441" priority="2106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B403">
-    <cfRule type="duplicateValues" dxfId="1460" priority="2105"/>
+    <cfRule type="duplicateValues" dxfId="1440" priority="2105"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B403">
-    <cfRule type="duplicateValues" dxfId="1459" priority="2104"/>
+    <cfRule type="duplicateValues" dxfId="1439" priority="2104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B404">
-    <cfRule type="duplicateValues" dxfId="1458" priority="2103"/>
+    <cfRule type="duplicateValues" dxfId="1438" priority="2103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B404">
-    <cfRule type="duplicateValues" dxfId="1457" priority="2102"/>
+    <cfRule type="duplicateValues" dxfId="1437" priority="2102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B405">
-    <cfRule type="duplicateValues" dxfId="1456" priority="2101"/>
+    <cfRule type="duplicateValues" dxfId="1436" priority="2101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B405">
-    <cfRule type="duplicateValues" dxfId="1455" priority="2100"/>
+    <cfRule type="duplicateValues" dxfId="1435" priority="2100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B406">
-    <cfRule type="duplicateValues" dxfId="1454" priority="2099"/>
+    <cfRule type="duplicateValues" dxfId="1434" priority="2099"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B406">
-    <cfRule type="duplicateValues" dxfId="1453" priority="2098"/>
+    <cfRule type="duplicateValues" dxfId="1433" priority="2098"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B407">
-    <cfRule type="duplicateValues" dxfId="1452" priority="2097"/>
+    <cfRule type="duplicateValues" dxfId="1432" priority="2097"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B407">
-    <cfRule type="duplicateValues" dxfId="1451" priority="2096"/>
+    <cfRule type="duplicateValues" dxfId="1431" priority="2096"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B408">
-    <cfRule type="duplicateValues" dxfId="1450" priority="2095"/>
+    <cfRule type="duplicateValues" dxfId="1430" priority="2095"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B408">
-    <cfRule type="duplicateValues" dxfId="1449" priority="2094"/>
+    <cfRule type="duplicateValues" dxfId="1429" priority="2094"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B409">
-    <cfRule type="duplicateValues" dxfId="1448" priority="2093"/>
+    <cfRule type="duplicateValues" dxfId="1428" priority="2093"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B409">
-    <cfRule type="duplicateValues" dxfId="1447" priority="2092"/>
+    <cfRule type="duplicateValues" dxfId="1427" priority="2092"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B410">
-    <cfRule type="duplicateValues" dxfId="1446" priority="2091"/>
+    <cfRule type="duplicateValues" dxfId="1426" priority="2091"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B410">
-    <cfRule type="duplicateValues" dxfId="1445" priority="2090"/>
+    <cfRule type="duplicateValues" dxfId="1425" priority="2090"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B411">
-    <cfRule type="duplicateValues" dxfId="1444" priority="2089"/>
+    <cfRule type="duplicateValues" dxfId="1424" priority="2089"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B411">
-    <cfRule type="duplicateValues" dxfId="1443" priority="2088"/>
+    <cfRule type="duplicateValues" dxfId="1423" priority="2088"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B412">
-    <cfRule type="duplicateValues" dxfId="1442" priority="2085"/>
+    <cfRule type="duplicateValues" dxfId="1422" priority="2085"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B412">
-    <cfRule type="duplicateValues" dxfId="1441" priority="2084"/>
+    <cfRule type="duplicateValues" dxfId="1421" priority="2084"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B413">
-    <cfRule type="duplicateValues" dxfId="1440" priority="2081"/>
+    <cfRule type="duplicateValues" dxfId="1420" priority="2081"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B413">
-    <cfRule type="duplicateValues" dxfId="1439" priority="2080"/>
+    <cfRule type="duplicateValues" dxfId="1419" priority="2080"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B414">
-    <cfRule type="duplicateValues" dxfId="1438" priority="2079"/>
+    <cfRule type="duplicateValues" dxfId="1418" priority="2079"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B414">
-    <cfRule type="duplicateValues" dxfId="1437" priority="2078"/>
+    <cfRule type="duplicateValues" dxfId="1417" priority="2078"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B416">
-    <cfRule type="duplicateValues" dxfId="1436" priority="2069"/>
+    <cfRule type="duplicateValues" dxfId="1416" priority="2069"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B416">
-    <cfRule type="duplicateValues" dxfId="1435" priority="2068"/>
+    <cfRule type="duplicateValues" dxfId="1415" priority="2068"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B417">
-    <cfRule type="duplicateValues" dxfId="1434" priority="2067"/>
+    <cfRule type="duplicateValues" dxfId="1414" priority="2067"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B417">
-    <cfRule type="duplicateValues" dxfId="1433" priority="2066"/>
+    <cfRule type="duplicateValues" dxfId="1413" priority="2066"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B422">
-    <cfRule type="duplicateValues" dxfId="1432" priority="2063"/>
+    <cfRule type="duplicateValues" dxfId="1412" priority="2063"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B422">
-    <cfRule type="duplicateValues" dxfId="1431" priority="2062"/>
+    <cfRule type="duplicateValues" dxfId="1411" priority="2062"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B421">
-    <cfRule type="duplicateValues" dxfId="1430" priority="2061"/>
+    <cfRule type="duplicateValues" dxfId="1410" priority="2061"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B421">
-    <cfRule type="duplicateValues" dxfId="1429" priority="2060"/>
+    <cfRule type="duplicateValues" dxfId="1409" priority="2060"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B423">
-    <cfRule type="duplicateValues" dxfId="1428" priority="2057"/>
+    <cfRule type="duplicateValues" dxfId="1408" priority="2057"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B423">
-    <cfRule type="duplicateValues" dxfId="1427" priority="2056"/>
+    <cfRule type="duplicateValues" dxfId="1407" priority="2056"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B424">
-    <cfRule type="duplicateValues" dxfId="1426" priority="2055"/>
+    <cfRule type="duplicateValues" dxfId="1406" priority="2055"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B424">
-    <cfRule type="duplicateValues" dxfId="1425" priority="2054"/>
+    <cfRule type="duplicateValues" dxfId="1405" priority="2054"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B425">
-    <cfRule type="duplicateValues" dxfId="1424" priority="2053"/>
+    <cfRule type="duplicateValues" dxfId="1404" priority="2053"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B425">
-    <cfRule type="duplicateValues" dxfId="1423" priority="2052"/>
+    <cfRule type="duplicateValues" dxfId="1403" priority="2052"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B426">
-    <cfRule type="duplicateValues" dxfId="1422" priority="2051"/>
+    <cfRule type="duplicateValues" dxfId="1402" priority="2051"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B426">
-    <cfRule type="duplicateValues" dxfId="1421" priority="2050"/>
+    <cfRule type="duplicateValues" dxfId="1401" priority="2050"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B427">
-    <cfRule type="duplicateValues" dxfId="1420" priority="2049"/>
+    <cfRule type="duplicateValues" dxfId="1400" priority="2049"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B427">
-    <cfRule type="duplicateValues" dxfId="1419" priority="2048"/>
+    <cfRule type="duplicateValues" dxfId="1399" priority="2048"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B428">
-    <cfRule type="duplicateValues" dxfId="1418" priority="2047"/>
+    <cfRule type="duplicateValues" dxfId="1398" priority="2047"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B428">
-    <cfRule type="duplicateValues" dxfId="1417" priority="2046"/>
+    <cfRule type="duplicateValues" dxfId="1397" priority="2046"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B429">
-    <cfRule type="duplicateValues" dxfId="1416" priority="2045"/>
+    <cfRule type="duplicateValues" dxfId="1396" priority="2045"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B429">
-    <cfRule type="duplicateValues" dxfId="1415" priority="2044"/>
+    <cfRule type="duplicateValues" dxfId="1395" priority="2044"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B432">
-    <cfRule type="duplicateValues" dxfId="1414" priority="2041"/>
+    <cfRule type="duplicateValues" dxfId="1394" priority="2041"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B432">
-    <cfRule type="duplicateValues" dxfId="1413" priority="2040"/>
+    <cfRule type="duplicateValues" dxfId="1393" priority="2040"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B431">
-    <cfRule type="duplicateValues" dxfId="1412" priority="2039"/>
+    <cfRule type="duplicateValues" dxfId="1392" priority="2039"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B431">
-    <cfRule type="duplicateValues" dxfId="1411" priority="2038"/>
+    <cfRule type="duplicateValues" dxfId="1391" priority="2038"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B434">
-    <cfRule type="duplicateValues" dxfId="1410" priority="2037"/>
+    <cfRule type="duplicateValues" dxfId="1390" priority="2037"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B434">
-    <cfRule type="duplicateValues" dxfId="1409" priority="2036"/>
+    <cfRule type="duplicateValues" dxfId="1389" priority="2036"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B435">
-    <cfRule type="duplicateValues" dxfId="1408" priority="2033"/>
+    <cfRule type="duplicateValues" dxfId="1388" priority="2033"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B435">
-    <cfRule type="duplicateValues" dxfId="1407" priority="2032"/>
+    <cfRule type="duplicateValues" dxfId="1387" priority="2032"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B437">
-    <cfRule type="duplicateValues" dxfId="1406" priority="2029"/>
+    <cfRule type="duplicateValues" dxfId="1386" priority="2029"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B437">
-    <cfRule type="duplicateValues" dxfId="1405" priority="2028"/>
+    <cfRule type="duplicateValues" dxfId="1385" priority="2028"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B436">
-    <cfRule type="duplicateValues" dxfId="1404" priority="2027"/>
+    <cfRule type="duplicateValues" dxfId="1384" priority="2027"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B436">
-    <cfRule type="duplicateValues" dxfId="1403" priority="2026"/>
+    <cfRule type="duplicateValues" dxfId="1383" priority="2026"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B440">
-    <cfRule type="duplicateValues" dxfId="1402" priority="2025"/>
+    <cfRule type="duplicateValues" dxfId="1382" priority="2025"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B440">
-    <cfRule type="duplicateValues" dxfId="1401" priority="2024"/>
+    <cfRule type="duplicateValues" dxfId="1381" priority="2024"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B443">
-    <cfRule type="duplicateValues" dxfId="1400" priority="2021"/>
+    <cfRule type="duplicateValues" dxfId="1380" priority="2021"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B443">
-    <cfRule type="duplicateValues" dxfId="1399" priority="2020"/>
+    <cfRule type="duplicateValues" dxfId="1379" priority="2020"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B445">
-    <cfRule type="duplicateValues" dxfId="1398" priority="2019"/>
+    <cfRule type="duplicateValues" dxfId="1378" priority="2019"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B445">
-    <cfRule type="duplicateValues" dxfId="1397" priority="2018"/>
+    <cfRule type="duplicateValues" dxfId="1377" priority="2018"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B446">
-    <cfRule type="duplicateValues" dxfId="1396" priority="2015"/>
+    <cfRule type="duplicateValues" dxfId="1376" priority="2015"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B446">
-    <cfRule type="duplicateValues" dxfId="1395" priority="2014"/>
+    <cfRule type="duplicateValues" dxfId="1375" priority="2014"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B447">
-    <cfRule type="duplicateValues" dxfId="1394" priority="2013"/>
+    <cfRule type="duplicateValues" dxfId="1374" priority="2013"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B447">
-    <cfRule type="duplicateValues" dxfId="1393" priority="2012"/>
+    <cfRule type="duplicateValues" dxfId="1373" priority="2012"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B449">
-    <cfRule type="duplicateValues" dxfId="1392" priority="2011"/>
+    <cfRule type="duplicateValues" dxfId="1372" priority="2011"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B449">
-    <cfRule type="duplicateValues" dxfId="1391" priority="2010"/>
+    <cfRule type="duplicateValues" dxfId="1371" priority="2010"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B450">
-    <cfRule type="duplicateValues" dxfId="1390" priority="2009"/>
+    <cfRule type="duplicateValues" dxfId="1370" priority="2009"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B450">
-    <cfRule type="duplicateValues" dxfId="1389" priority="2008"/>
+    <cfRule type="duplicateValues" dxfId="1369" priority="2008"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B452">
-    <cfRule type="duplicateValues" dxfId="1388" priority="2007"/>
+    <cfRule type="duplicateValues" dxfId="1368" priority="2007"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B452">
-    <cfRule type="duplicateValues" dxfId="1387" priority="2006"/>
+    <cfRule type="duplicateValues" dxfId="1367" priority="2006"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B453">
-    <cfRule type="duplicateValues" dxfId="1386" priority="2003"/>
+    <cfRule type="duplicateValues" dxfId="1366" priority="2003"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B453">
-    <cfRule type="duplicateValues" dxfId="1385" priority="2002"/>
+    <cfRule type="duplicateValues" dxfId="1365" priority="2002"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B454">
-    <cfRule type="duplicateValues" dxfId="1384" priority="1997"/>
+    <cfRule type="duplicateValues" dxfId="1364" priority="1997"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B454">
-    <cfRule type="duplicateValues" dxfId="1383" priority="1996"/>
+    <cfRule type="duplicateValues" dxfId="1363" priority="1996"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B455">
-    <cfRule type="duplicateValues" dxfId="1382" priority="1995"/>
+    <cfRule type="duplicateValues" dxfId="1362" priority="1995"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B455">
-    <cfRule type="duplicateValues" dxfId="1381" priority="1994"/>
+    <cfRule type="duplicateValues" dxfId="1361" priority="1994"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B457">
-    <cfRule type="duplicateValues" dxfId="1380" priority="1991"/>
+    <cfRule type="duplicateValues" dxfId="1360" priority="1991"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B457">
-    <cfRule type="duplicateValues" dxfId="1379" priority="1990"/>
+    <cfRule type="duplicateValues" dxfId="1359" priority="1990"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B458">
-    <cfRule type="duplicateValues" dxfId="1378" priority="1989"/>
+    <cfRule type="duplicateValues" dxfId="1358" priority="1989"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B458">
-    <cfRule type="duplicateValues" dxfId="1377" priority="1988"/>
+    <cfRule type="duplicateValues" dxfId="1357" priority="1988"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B460">
-    <cfRule type="duplicateValues" dxfId="1376" priority="1987"/>
+    <cfRule type="duplicateValues" dxfId="1356" priority="1987"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B460">
-    <cfRule type="duplicateValues" dxfId="1375" priority="1986"/>
+    <cfRule type="duplicateValues" dxfId="1355" priority="1986"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B461">
-    <cfRule type="duplicateValues" dxfId="1374" priority="1985"/>
+    <cfRule type="duplicateValues" dxfId="1354" priority="1985"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B461">
-    <cfRule type="duplicateValues" dxfId="1373" priority="1984"/>
+    <cfRule type="duplicateValues" dxfId="1353" priority="1984"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B462">
-    <cfRule type="duplicateValues" dxfId="1372" priority="1981"/>
+    <cfRule type="duplicateValues" dxfId="1352" priority="1981"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B462">
-    <cfRule type="duplicateValues" dxfId="1371" priority="1980"/>
+    <cfRule type="duplicateValues" dxfId="1351" priority="1980"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B465">
-    <cfRule type="duplicateValues" dxfId="1370" priority="1977"/>
+    <cfRule type="duplicateValues" dxfId="1350" priority="1977"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B465">
-    <cfRule type="duplicateValues" dxfId="1369" priority="1976"/>
+    <cfRule type="duplicateValues" dxfId="1349" priority="1976"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B469">
-    <cfRule type="duplicateValues" dxfId="1368" priority="1975"/>
+    <cfRule type="duplicateValues" dxfId="1348" priority="1975"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B469">
-    <cfRule type="duplicateValues" dxfId="1367" priority="1974"/>
+    <cfRule type="duplicateValues" dxfId="1347" priority="1974"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B470">
-    <cfRule type="duplicateValues" dxfId="1366" priority="1973"/>
+    <cfRule type="duplicateValues" dxfId="1346" priority="1973"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B470">
-    <cfRule type="duplicateValues" dxfId="1365" priority="1972"/>
+    <cfRule type="duplicateValues" dxfId="1345" priority="1972"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B473">
-    <cfRule type="duplicateValues" dxfId="1364" priority="1969"/>
+    <cfRule type="duplicateValues" dxfId="1344" priority="1969"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B473">
-    <cfRule type="duplicateValues" dxfId="1363" priority="1968"/>
+    <cfRule type="duplicateValues" dxfId="1343" priority="1968"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B474">
-    <cfRule type="duplicateValues" dxfId="1362" priority="1967"/>
+    <cfRule type="duplicateValues" dxfId="1342" priority="1967"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B474">
-    <cfRule type="duplicateValues" dxfId="1361" priority="1966"/>
+    <cfRule type="duplicateValues" dxfId="1341" priority="1966"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B478">
-    <cfRule type="duplicateValues" dxfId="1360" priority="1961"/>
+    <cfRule type="duplicateValues" dxfId="1340" priority="1961"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B478">
-    <cfRule type="duplicateValues" dxfId="1359" priority="1960"/>
+    <cfRule type="duplicateValues" dxfId="1339" priority="1960"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B479">
-    <cfRule type="duplicateValues" dxfId="1358" priority="1957"/>
+    <cfRule type="duplicateValues" dxfId="1338" priority="1957"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B479">
-    <cfRule type="duplicateValues" dxfId="1357" priority="1956"/>
+    <cfRule type="duplicateValues" dxfId="1337" priority="1956"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B481">
-    <cfRule type="duplicateValues" dxfId="1356" priority="1949"/>
+    <cfRule type="duplicateValues" dxfId="1336" priority="1949"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B481">
-    <cfRule type="duplicateValues" dxfId="1355" priority="1948"/>
+    <cfRule type="duplicateValues" dxfId="1335" priority="1948"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B482">
-    <cfRule type="duplicateValues" dxfId="1354" priority="1947"/>
+    <cfRule type="duplicateValues" dxfId="1334" priority="1947"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B482">
-    <cfRule type="duplicateValues" dxfId="1353" priority="1946"/>
+    <cfRule type="duplicateValues" dxfId="1333" priority="1946"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B484">
-    <cfRule type="duplicateValues" dxfId="1352" priority="1945"/>
+    <cfRule type="duplicateValues" dxfId="1332" priority="1945"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B484">
-    <cfRule type="duplicateValues" dxfId="1351" priority="1944"/>
+    <cfRule type="duplicateValues" dxfId="1331" priority="1944"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B486">
-    <cfRule type="duplicateValues" dxfId="1350" priority="1935"/>
+    <cfRule type="duplicateValues" dxfId="1330" priority="1935"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B486">
-    <cfRule type="duplicateValues" dxfId="1349" priority="1934"/>
+    <cfRule type="duplicateValues" dxfId="1329" priority="1934"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B489">
-    <cfRule type="duplicateValues" dxfId="1348" priority="1931"/>
+    <cfRule type="duplicateValues" dxfId="1328" priority="1931"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B489">
-    <cfRule type="duplicateValues" dxfId="1347" priority="1930"/>
+    <cfRule type="duplicateValues" dxfId="1327" priority="1930"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B490">
-    <cfRule type="duplicateValues" dxfId="1346" priority="1929"/>
+    <cfRule type="duplicateValues" dxfId="1326" priority="1929"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B490">
-    <cfRule type="duplicateValues" dxfId="1345" priority="1928"/>
+    <cfRule type="duplicateValues" dxfId="1325" priority="1928"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B496">
-    <cfRule type="duplicateValues" dxfId="1344" priority="1913"/>
+    <cfRule type="duplicateValues" dxfId="1324" priority="1913"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B496">
-    <cfRule type="duplicateValues" dxfId="1343" priority="1912"/>
+    <cfRule type="duplicateValues" dxfId="1323" priority="1912"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B497">
-    <cfRule type="duplicateValues" dxfId="1342" priority="1911"/>
+    <cfRule type="duplicateValues" dxfId="1322" priority="1911"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B497">
-    <cfRule type="duplicateValues" dxfId="1341" priority="1910"/>
+    <cfRule type="duplicateValues" dxfId="1321" priority="1910"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B498">
-    <cfRule type="duplicateValues" dxfId="1340" priority="1907"/>
+    <cfRule type="duplicateValues" dxfId="1320" priority="1907"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B498">
-    <cfRule type="duplicateValues" dxfId="1339" priority="1906"/>
+    <cfRule type="duplicateValues" dxfId="1319" priority="1906"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B501">
-    <cfRule type="duplicateValues" dxfId="1338" priority="1901"/>
+    <cfRule type="duplicateValues" dxfId="1318" priority="1901"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B501">
-    <cfRule type="duplicateValues" dxfId="1337" priority="1900"/>
+    <cfRule type="duplicateValues" dxfId="1317" priority="1900"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B502">
-    <cfRule type="duplicateValues" dxfId="1336" priority="1899"/>
+    <cfRule type="duplicateValues" dxfId="1316" priority="1899"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B502:B503">
-    <cfRule type="duplicateValues" dxfId="1335" priority="1898"/>
+    <cfRule type="duplicateValues" dxfId="1315" priority="1898"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B503">
-    <cfRule type="duplicateValues" dxfId="1334" priority="1897"/>
+    <cfRule type="duplicateValues" dxfId="1314" priority="1897"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B503">
-    <cfRule type="duplicateValues" dxfId="1333" priority="1896"/>
+    <cfRule type="duplicateValues" dxfId="1313" priority="1896"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B504">
-    <cfRule type="duplicateValues" dxfId="1332" priority="1895"/>
+    <cfRule type="duplicateValues" dxfId="1312" priority="1895"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B504">
-    <cfRule type="duplicateValues" dxfId="1331" priority="1894"/>
+    <cfRule type="duplicateValues" dxfId="1311" priority="1894"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B508">
-    <cfRule type="duplicateValues" dxfId="1330" priority="1885"/>
+    <cfRule type="duplicateValues" dxfId="1310" priority="1885"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B508">
-    <cfRule type="duplicateValues" dxfId="1329" priority="1884"/>
+    <cfRule type="duplicateValues" dxfId="1309" priority="1884"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B509">
-    <cfRule type="duplicateValues" dxfId="1328" priority="1883"/>
+    <cfRule type="duplicateValues" dxfId="1308" priority="1883"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B509">
-    <cfRule type="duplicateValues" dxfId="1327" priority="1882"/>
+    <cfRule type="duplicateValues" dxfId="1307" priority="1882"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B510">
-    <cfRule type="duplicateValues" dxfId="1326" priority="1881"/>
+    <cfRule type="duplicateValues" dxfId="1306" priority="1881"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B510">
-    <cfRule type="duplicateValues" dxfId="1325" priority="1880"/>
+    <cfRule type="duplicateValues" dxfId="1305" priority="1880"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B512">
-    <cfRule type="duplicateValues" dxfId="1324" priority="1877"/>
+    <cfRule type="duplicateValues" dxfId="1304" priority="1877"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B512">
-    <cfRule type="duplicateValues" dxfId="1323" priority="1876"/>
+    <cfRule type="duplicateValues" dxfId="1303" priority="1876"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B513">
-    <cfRule type="duplicateValues" dxfId="1322" priority="1875"/>
+    <cfRule type="duplicateValues" dxfId="1302" priority="1875"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B513">
-    <cfRule type="duplicateValues" dxfId="1321" priority="1874"/>
+    <cfRule type="duplicateValues" dxfId="1301" priority="1874"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B515">
-    <cfRule type="duplicateValues" dxfId="1320" priority="1873"/>
+    <cfRule type="duplicateValues" dxfId="1300" priority="1873"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B515">
-    <cfRule type="duplicateValues" dxfId="1319" priority="1872"/>
+    <cfRule type="duplicateValues" dxfId="1299" priority="1872"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B516">
-    <cfRule type="duplicateValues" dxfId="1318" priority="1865"/>
+    <cfRule type="duplicateValues" dxfId="1298" priority="1865"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B516">
-    <cfRule type="duplicateValues" dxfId="1317" priority="1864"/>
+    <cfRule type="duplicateValues" dxfId="1297" priority="1864"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B517">
-    <cfRule type="duplicateValues" dxfId="1316" priority="1861"/>
+    <cfRule type="duplicateValues" dxfId="1296" priority="1861"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B517">
-    <cfRule type="duplicateValues" dxfId="1315" priority="1860"/>
+    <cfRule type="duplicateValues" dxfId="1295" priority="1860"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B518">
-    <cfRule type="duplicateValues" dxfId="1314" priority="1857"/>
+    <cfRule type="duplicateValues" dxfId="1294" priority="1857"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B518">
-    <cfRule type="duplicateValues" dxfId="1313" priority="1856"/>
+    <cfRule type="duplicateValues" dxfId="1293" priority="1856"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B522">
-    <cfRule type="duplicateValues" dxfId="1312" priority="1853"/>
+    <cfRule type="duplicateValues" dxfId="1292" priority="1853"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B522">
-    <cfRule type="duplicateValues" dxfId="1311" priority="1852"/>
+    <cfRule type="duplicateValues" dxfId="1291" priority="1852"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B520">
-    <cfRule type="duplicateValues" dxfId="1310" priority="1851"/>
+    <cfRule type="duplicateValues" dxfId="1290" priority="1851"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B520">
-    <cfRule type="duplicateValues" dxfId="1309" priority="1850"/>
+    <cfRule type="duplicateValues" dxfId="1289" priority="1850"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B521">
-    <cfRule type="duplicateValues" dxfId="1308" priority="1847"/>
+    <cfRule type="duplicateValues" dxfId="1288" priority="1847"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B521">
-    <cfRule type="duplicateValues" dxfId="1307" priority="1846"/>
+    <cfRule type="duplicateValues" dxfId="1287" priority="1846"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B523">
-    <cfRule type="duplicateValues" dxfId="1306" priority="1841"/>
+    <cfRule type="duplicateValues" dxfId="1286" priority="1841"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B523">
-    <cfRule type="duplicateValues" dxfId="1305" priority="1840"/>
+    <cfRule type="duplicateValues" dxfId="1285" priority="1840"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B527">
-    <cfRule type="duplicateValues" dxfId="1304" priority="1835"/>
+    <cfRule type="duplicateValues" dxfId="1284" priority="1835"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B527">
-    <cfRule type="duplicateValues" dxfId="1303" priority="1834"/>
+    <cfRule type="duplicateValues" dxfId="1283" priority="1834"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B526">
-    <cfRule type="duplicateValues" dxfId="1302" priority="1833"/>
+    <cfRule type="duplicateValues" dxfId="1282" priority="1833"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B526">
-    <cfRule type="duplicateValues" dxfId="1301" priority="1832"/>
+    <cfRule type="duplicateValues" dxfId="1281" priority="1832"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B525">
-    <cfRule type="duplicateValues" dxfId="1300" priority="1831"/>
+    <cfRule type="duplicateValues" dxfId="1280" priority="1831"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B525">
-    <cfRule type="duplicateValues" dxfId="1299" priority="1830"/>
+    <cfRule type="duplicateValues" dxfId="1279" priority="1830"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B530">
-    <cfRule type="duplicateValues" dxfId="1298" priority="1829"/>
+    <cfRule type="duplicateValues" dxfId="1278" priority="1829"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B530">
-    <cfRule type="duplicateValues" dxfId="1297" priority="1828"/>
+    <cfRule type="duplicateValues" dxfId="1277" priority="1828"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B536">
-    <cfRule type="duplicateValues" dxfId="1296" priority="1827"/>
+    <cfRule type="duplicateValues" dxfId="1276" priority="1827"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B536">
-    <cfRule type="duplicateValues" dxfId="1295" priority="1826"/>
+    <cfRule type="duplicateValues" dxfId="1275" priority="1826"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B538">
-    <cfRule type="duplicateValues" dxfId="1294" priority="1825"/>
+    <cfRule type="duplicateValues" dxfId="1274" priority="1825"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B538">
-    <cfRule type="duplicateValues" dxfId="1293" priority="1824"/>
+    <cfRule type="duplicateValues" dxfId="1273" priority="1824"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B540">
-    <cfRule type="duplicateValues" dxfId="1292" priority="1821"/>
+    <cfRule type="duplicateValues" dxfId="1272" priority="1821"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B540">
-    <cfRule type="duplicateValues" dxfId="1291" priority="1820"/>
+    <cfRule type="duplicateValues" dxfId="1271" priority="1820"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B543">
-    <cfRule type="duplicateValues" dxfId="1290" priority="1817"/>
+    <cfRule type="duplicateValues" dxfId="1270" priority="1817"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B543">
-    <cfRule type="duplicateValues" dxfId="1289" priority="1816"/>
+    <cfRule type="duplicateValues" dxfId="1269" priority="1816"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B541">
-    <cfRule type="duplicateValues" dxfId="1288" priority="1815"/>
+    <cfRule type="duplicateValues" dxfId="1268" priority="1815"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B541">
-    <cfRule type="duplicateValues" dxfId="1287" priority="1814"/>
+    <cfRule type="duplicateValues" dxfId="1267" priority="1814"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B542">
-    <cfRule type="duplicateValues" dxfId="1286" priority="1809"/>
+    <cfRule type="duplicateValues" dxfId="1266" priority="1809"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B542">
-    <cfRule type="duplicateValues" dxfId="1285" priority="1808"/>
+    <cfRule type="duplicateValues" dxfId="1265" priority="1808"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B544">
-    <cfRule type="duplicateValues" dxfId="1284" priority="1805"/>
+    <cfRule type="duplicateValues" dxfId="1264" priority="1805"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B544">
-    <cfRule type="duplicateValues" dxfId="1283" priority="1804"/>
+    <cfRule type="duplicateValues" dxfId="1263" priority="1804"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B545">
-    <cfRule type="duplicateValues" dxfId="1282" priority="1801"/>
+    <cfRule type="duplicateValues" dxfId="1262" priority="1801"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B545">
-    <cfRule type="duplicateValues" dxfId="1281" priority="1800"/>
+    <cfRule type="duplicateValues" dxfId="1261" priority="1800"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B546">
-    <cfRule type="duplicateValues" dxfId="1280" priority="1799"/>
+    <cfRule type="duplicateValues" dxfId="1260" priority="1799"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B546">
-    <cfRule type="duplicateValues" dxfId="1279" priority="1798"/>
+    <cfRule type="duplicateValues" dxfId="1259" priority="1798"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B547">
-    <cfRule type="duplicateValues" dxfId="1276" priority="1795"/>
+    <cfRule type="duplicateValues" dxfId="1258" priority="1795"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B547">
-    <cfRule type="duplicateValues" dxfId="1275" priority="1794"/>
+    <cfRule type="duplicateValues" dxfId="1257" priority="1794"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B549">
-    <cfRule type="duplicateValues" dxfId="1274" priority="1793"/>
+    <cfRule type="duplicateValues" dxfId="1256" priority="1793"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B549">
-    <cfRule type="duplicateValues" dxfId="1273" priority="1792"/>
+    <cfRule type="duplicateValues" dxfId="1255" priority="1792"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B551">
-    <cfRule type="duplicateValues" dxfId="1272" priority="1789"/>
+    <cfRule type="duplicateValues" dxfId="1254" priority="1789"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B551">
-    <cfRule type="duplicateValues" dxfId="1271" priority="1788"/>
+    <cfRule type="duplicateValues" dxfId="1253" priority="1788"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B552">
-    <cfRule type="duplicateValues" dxfId="1270" priority="1787"/>
+    <cfRule type="duplicateValues" dxfId="1252" priority="1787"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B552">
-    <cfRule type="duplicateValues" dxfId="1269" priority="1786"/>
+    <cfRule type="duplicateValues" dxfId="1251" priority="1786"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B553">
-    <cfRule type="duplicateValues" dxfId="1268" priority="1781"/>
+    <cfRule type="duplicateValues" dxfId="1250" priority="1781"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B553">
-    <cfRule type="duplicateValues" dxfId="1267" priority="1780"/>
+    <cfRule type="duplicateValues" dxfId="1249" priority="1780"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B554">
-    <cfRule type="duplicateValues" dxfId="1266" priority="1779"/>
+    <cfRule type="duplicateValues" dxfId="1248" priority="1779"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B554">
-    <cfRule type="duplicateValues" dxfId="1265" priority="1778"/>
+    <cfRule type="duplicateValues" dxfId="1247" priority="1778"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B555">
-    <cfRule type="duplicateValues" dxfId="1264" priority="1773"/>
+    <cfRule type="duplicateValues" dxfId="1246" priority="1773"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B555">
-    <cfRule type="duplicateValues" dxfId="1263" priority="1772"/>
+    <cfRule type="duplicateValues" dxfId="1245" priority="1772"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B556">
-    <cfRule type="duplicateValues" dxfId="1262" priority="1771"/>
+    <cfRule type="duplicateValues" dxfId="1244" priority="1771"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B556">
-    <cfRule type="duplicateValues" dxfId="1261" priority="1770"/>
+    <cfRule type="duplicateValues" dxfId="1243" priority="1770"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B557">
-    <cfRule type="duplicateValues" dxfId="1260" priority="1767"/>
+    <cfRule type="duplicateValues" dxfId="1242" priority="1767"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B557">
-    <cfRule type="duplicateValues" dxfId="1259" priority="1766"/>
+    <cfRule type="duplicateValues" dxfId="1241" priority="1766"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B558">
-    <cfRule type="duplicateValues" dxfId="1258" priority="1765"/>
+    <cfRule type="duplicateValues" dxfId="1240" priority="1765"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B558">
-    <cfRule type="duplicateValues" dxfId="1257" priority="1764"/>
+    <cfRule type="duplicateValues" dxfId="1239" priority="1764"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B562">
-    <cfRule type="duplicateValues" dxfId="1252" priority="1755"/>
+    <cfRule type="duplicateValues" dxfId="1238" priority="1755"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B562">
-    <cfRule type="duplicateValues" dxfId="1251" priority="1754"/>
+    <cfRule type="duplicateValues" dxfId="1237" priority="1754"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B564">
-    <cfRule type="duplicateValues" dxfId="1250" priority="1753"/>
+    <cfRule type="duplicateValues" dxfId="1236" priority="1753"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B564">
-    <cfRule type="duplicateValues" dxfId="1249" priority="1752"/>
+    <cfRule type="duplicateValues" dxfId="1235" priority="1752"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B563">
-    <cfRule type="duplicateValues" dxfId="1248" priority="1751"/>
+    <cfRule type="duplicateValues" dxfId="1234" priority="1751"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B563">
-    <cfRule type="duplicateValues" dxfId="1247" priority="1750"/>
+    <cfRule type="duplicateValues" dxfId="1233" priority="1750"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B565">
-    <cfRule type="duplicateValues" dxfId="1246" priority="1749"/>
+    <cfRule type="duplicateValues" dxfId="1232" priority="1749"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B565">
-    <cfRule type="duplicateValues" dxfId="1245" priority="1748"/>
+    <cfRule type="duplicateValues" dxfId="1231" priority="1748"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B566">
-    <cfRule type="duplicateValues" dxfId="1244" priority="1741"/>
+    <cfRule type="duplicateValues" dxfId="1230" priority="1741"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B566">
-    <cfRule type="duplicateValues" dxfId="1243" priority="1740"/>
+    <cfRule type="duplicateValues" dxfId="1229" priority="1740"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B569">
-    <cfRule type="duplicateValues" dxfId="1242" priority="1739"/>
+    <cfRule type="duplicateValues" dxfId="1228" priority="1739"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B569">
-    <cfRule type="duplicateValues" dxfId="1241" priority="1738"/>
+    <cfRule type="duplicateValues" dxfId="1227" priority="1738"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B567">
-    <cfRule type="duplicateValues" dxfId="1240" priority="1735"/>
+    <cfRule type="duplicateValues" dxfId="1226" priority="1735"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B567">
-    <cfRule type="duplicateValues" dxfId="1239" priority="1734"/>
+    <cfRule type="duplicateValues" dxfId="1225" priority="1734"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B568">
-    <cfRule type="duplicateValues" dxfId="1238" priority="1731"/>
+    <cfRule type="duplicateValues" dxfId="1224" priority="1731"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B568">
-    <cfRule type="duplicateValues" dxfId="1237" priority="1730"/>
+    <cfRule type="duplicateValues" dxfId="1223" priority="1730"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B571">
-    <cfRule type="duplicateValues" dxfId="1234" priority="1721"/>
+    <cfRule type="duplicateValues" dxfId="1222" priority="1721"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B572">
-    <cfRule type="duplicateValues" dxfId="1233" priority="1718"/>
+    <cfRule type="duplicateValues" dxfId="1221" priority="1718"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B572">
-    <cfRule type="duplicateValues" dxfId="1232" priority="1717"/>
+    <cfRule type="duplicateValues" dxfId="1220" priority="1717"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B575">
-    <cfRule type="duplicateValues" dxfId="1231" priority="1715"/>
+    <cfRule type="duplicateValues" dxfId="1219" priority="1715"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B575">
-    <cfRule type="duplicateValues" dxfId="1230" priority="1716"/>
+    <cfRule type="duplicateValues" dxfId="1218" priority="1716"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B577">
-    <cfRule type="duplicateValues" dxfId="1229" priority="1714"/>
+    <cfRule type="duplicateValues" dxfId="1217" priority="1714"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B577">
-    <cfRule type="duplicateValues" dxfId="1228" priority="1713"/>
+    <cfRule type="duplicateValues" dxfId="1216" priority="1713"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B578">
-    <cfRule type="duplicateValues" dxfId="1227" priority="1703"/>
+    <cfRule type="duplicateValues" dxfId="1215" priority="1703"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B578">
-    <cfRule type="duplicateValues" dxfId="1226" priority="1704"/>
+    <cfRule type="duplicateValues" dxfId="1214" priority="1704"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B579">
-    <cfRule type="duplicateValues" dxfId="1225" priority="1700"/>
+    <cfRule type="duplicateValues" dxfId="1213" priority="1700"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B580">
-    <cfRule type="duplicateValues" dxfId="1224" priority="1697"/>
+    <cfRule type="duplicateValues" dxfId="1212" priority="1697"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B581">
-    <cfRule type="duplicateValues" dxfId="1223" priority="1694"/>
+    <cfRule type="duplicateValues" dxfId="1211" priority="1694"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B581">
-    <cfRule type="duplicateValues" dxfId="1222" priority="1693"/>
+    <cfRule type="duplicateValues" dxfId="1210" priority="1693"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B582">
-    <cfRule type="duplicateValues" dxfId="1221" priority="1692"/>
+    <cfRule type="duplicateValues" dxfId="1209" priority="1692"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B582">
-    <cfRule type="duplicateValues" dxfId="1220" priority="1691"/>
+    <cfRule type="duplicateValues" dxfId="1208" priority="1691"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B583">
-    <cfRule type="duplicateValues" dxfId="1219" priority="1690"/>
+    <cfRule type="duplicateValues" dxfId="1207" priority="1690"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B583">
-    <cfRule type="duplicateValues" dxfId="1218" priority="1689"/>
+    <cfRule type="duplicateValues" dxfId="1206" priority="1689"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B584">
-    <cfRule type="duplicateValues" dxfId="1217" priority="1688"/>
+    <cfRule type="duplicateValues" dxfId="1205" priority="1688"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B584">
-    <cfRule type="duplicateValues" dxfId="1216" priority="1687"/>
+    <cfRule type="duplicateValues" dxfId="1204" priority="1687"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B587">
-    <cfRule type="duplicateValues" dxfId="1215" priority="1685"/>
+    <cfRule type="duplicateValues" dxfId="1203" priority="1685"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B587">
-    <cfRule type="duplicateValues" dxfId="1214" priority="1686"/>
+    <cfRule type="duplicateValues" dxfId="1202" priority="1686"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B586">
-    <cfRule type="duplicateValues" dxfId="1213" priority="1683"/>
+    <cfRule type="duplicateValues" dxfId="1201" priority="1683"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B586">
-    <cfRule type="duplicateValues" dxfId="1212" priority="1684"/>
+    <cfRule type="duplicateValues" dxfId="1200" priority="1684"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B589">
-    <cfRule type="duplicateValues" dxfId="1211" priority="1677"/>
+    <cfRule type="duplicateValues" dxfId="1199" priority="1677"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B589">
-    <cfRule type="duplicateValues" dxfId="1210" priority="1678"/>
+    <cfRule type="duplicateValues" dxfId="1198" priority="1678"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B591">
-    <cfRule type="duplicateValues" dxfId="1209" priority="1673"/>
+    <cfRule type="duplicateValues" dxfId="1197" priority="1673"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B591">
-    <cfRule type="duplicateValues" dxfId="1208" priority="1674"/>
+    <cfRule type="duplicateValues" dxfId="1196" priority="1674"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B592">
-    <cfRule type="duplicateValues" dxfId="1207" priority="1671"/>
+    <cfRule type="duplicateValues" dxfId="1195" priority="1671"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B592">
-    <cfRule type="duplicateValues" dxfId="1206" priority="1672"/>
+    <cfRule type="duplicateValues" dxfId="1194" priority="1672"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B593">
-    <cfRule type="duplicateValues" dxfId="1205" priority="1669"/>
+    <cfRule type="duplicateValues" dxfId="1193" priority="1669"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B593">
-    <cfRule type="duplicateValues" dxfId="1204" priority="1670"/>
+    <cfRule type="duplicateValues" dxfId="1192" priority="1670"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B594">
-    <cfRule type="duplicateValues" dxfId="1203" priority="1665"/>
+    <cfRule type="duplicateValues" dxfId="1191" priority="1665"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B594">
-    <cfRule type="duplicateValues" dxfId="1202" priority="1666"/>
+    <cfRule type="duplicateValues" dxfId="1190" priority="1666"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B595">
-    <cfRule type="duplicateValues" dxfId="1201" priority="1661"/>
+    <cfRule type="duplicateValues" dxfId="1189" priority="1661"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B595">
-    <cfRule type="duplicateValues" dxfId="1200" priority="1662"/>
+    <cfRule type="duplicateValues" dxfId="1188" priority="1662"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B596">
-    <cfRule type="duplicateValues" dxfId="1199" priority="1660"/>
+    <cfRule type="duplicateValues" dxfId="1187" priority="1660"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B601">
-    <cfRule type="duplicateValues" dxfId="1198" priority="1657"/>
+    <cfRule type="duplicateValues" dxfId="1186" priority="1657"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B602">
-    <cfRule type="duplicateValues" dxfId="1197" priority="1655"/>
+    <cfRule type="duplicateValues" dxfId="1185" priority="1655"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B602">
-    <cfRule type="duplicateValues" dxfId="1196" priority="1656"/>
+    <cfRule type="duplicateValues" dxfId="1184" priority="1656"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B604">
-    <cfRule type="duplicateValues" dxfId="1195" priority="1653"/>
+    <cfRule type="duplicateValues" dxfId="1183" priority="1653"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B604">
-    <cfRule type="duplicateValues" dxfId="1194" priority="1654"/>
+    <cfRule type="duplicateValues" dxfId="1182" priority="1654"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B603">
-    <cfRule type="duplicateValues" dxfId="1193" priority="1651"/>
+    <cfRule type="duplicateValues" dxfId="1181" priority="1651"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B603">
-    <cfRule type="duplicateValues" dxfId="1192" priority="1652"/>
+    <cfRule type="duplicateValues" dxfId="1180" priority="1652"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B605">
-    <cfRule type="duplicateValues" dxfId="1191" priority="1649"/>
+    <cfRule type="duplicateValues" dxfId="1179" priority="1649"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B605">
-    <cfRule type="duplicateValues" dxfId="1190" priority="1650"/>
+    <cfRule type="duplicateValues" dxfId="1178" priority="1650"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B606">
-    <cfRule type="duplicateValues" dxfId="1189" priority="1647"/>
+    <cfRule type="duplicateValues" dxfId="1177" priority="1647"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B606">
-    <cfRule type="duplicateValues" dxfId="1188" priority="1648"/>
+    <cfRule type="duplicateValues" dxfId="1176" priority="1648"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B607">
-    <cfRule type="duplicateValues" dxfId="1187" priority="1641"/>
+    <cfRule type="duplicateValues" dxfId="1175" priority="1641"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B607">
-    <cfRule type="duplicateValues" dxfId="1186" priority="1642"/>
+    <cfRule type="duplicateValues" dxfId="1174" priority="1642"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B608">
-    <cfRule type="duplicateValues" dxfId="1185" priority="1640"/>
+    <cfRule type="duplicateValues" dxfId="1173" priority="1640"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B608">
-    <cfRule type="duplicateValues" dxfId="1184" priority="1639"/>
+    <cfRule type="duplicateValues" dxfId="1172" priority="1639"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B609">
-    <cfRule type="duplicateValues" dxfId="1183" priority="1637"/>
+    <cfRule type="duplicateValues" dxfId="1171" priority="1637"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B609">
-    <cfRule type="duplicateValues" dxfId="1182" priority="1638"/>
+    <cfRule type="duplicateValues" dxfId="1170" priority="1638"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B610">
-    <cfRule type="duplicateValues" dxfId="1181" priority="1631"/>
+    <cfRule type="duplicateValues" dxfId="1169" priority="1631"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B610">
-    <cfRule type="duplicateValues" dxfId="1180" priority="1632"/>
+    <cfRule type="duplicateValues" dxfId="1168" priority="1632"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B611">
-    <cfRule type="duplicateValues" dxfId="1179" priority="1629"/>
+    <cfRule type="duplicateValues" dxfId="1167" priority="1629"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B611">
-    <cfRule type="duplicateValues" dxfId="1178" priority="1630"/>
+    <cfRule type="duplicateValues" dxfId="1166" priority="1630"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B613">
-    <cfRule type="duplicateValues" dxfId="1177" priority="1627"/>
+    <cfRule type="duplicateValues" dxfId="1165" priority="1627"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B613">
-    <cfRule type="duplicateValues" dxfId="1176" priority="1628"/>
+    <cfRule type="duplicateValues" dxfId="1164" priority="1628"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B614">
-    <cfRule type="duplicateValues" dxfId="1175" priority="1622"/>
+    <cfRule type="duplicateValues" dxfId="1163" priority="1622"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B614">
-    <cfRule type="duplicateValues" dxfId="1174" priority="1621"/>
+    <cfRule type="duplicateValues" dxfId="1162" priority="1621"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B615">
-    <cfRule type="duplicateValues" dxfId="1173" priority="1618"/>
+    <cfRule type="duplicateValues" dxfId="1161" priority="1618"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B615">
-    <cfRule type="duplicateValues" dxfId="1172" priority="1617"/>
+    <cfRule type="duplicateValues" dxfId="1160" priority="1617"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B616">
-    <cfRule type="duplicateValues" dxfId="1171" priority="1614"/>
+    <cfRule type="duplicateValues" dxfId="1159" priority="1614"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B616">
-    <cfRule type="duplicateValues" dxfId="1170" priority="1613"/>
+    <cfRule type="duplicateValues" dxfId="1158" priority="1613"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B617">
-    <cfRule type="duplicateValues" dxfId="1169" priority="1611"/>
+    <cfRule type="duplicateValues" dxfId="1157" priority="1611"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B617">
-    <cfRule type="duplicateValues" dxfId="1168" priority="1612"/>
+    <cfRule type="duplicateValues" dxfId="1156" priority="1612"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B618">
-    <cfRule type="duplicateValues" dxfId="1167" priority="1608"/>
+    <cfRule type="duplicateValues" dxfId="1155" priority="1608"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B619">
-    <cfRule type="duplicateValues" dxfId="1166" priority="1606"/>
+    <cfRule type="duplicateValues" dxfId="1154" priority="1606"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B619">
-    <cfRule type="duplicateValues" dxfId="1165" priority="1607"/>
+    <cfRule type="duplicateValues" dxfId="1153" priority="1607"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B620">
-    <cfRule type="duplicateValues" dxfId="1164" priority="1604"/>
+    <cfRule type="duplicateValues" dxfId="1152" priority="1604"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B620">
-    <cfRule type="duplicateValues" dxfId="1163" priority="1605"/>
+    <cfRule type="duplicateValues" dxfId="1151" priority="1605"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D621">
-    <cfRule type="duplicateValues" dxfId="1162" priority="1602"/>
+    <cfRule type="duplicateValues" dxfId="1150" priority="1602"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D621">
-    <cfRule type="duplicateValues" dxfId="1161" priority="1603"/>
+    <cfRule type="duplicateValues" dxfId="1149" priority="1603"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B621">
-    <cfRule type="duplicateValues" dxfId="1160" priority="1598"/>
+    <cfRule type="duplicateValues" dxfId="1148" priority="1598"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B621">
-    <cfRule type="duplicateValues" dxfId="1159" priority="1599"/>
+    <cfRule type="duplicateValues" dxfId="1147" priority="1599"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B625">
-    <cfRule type="duplicateValues" dxfId="1158" priority="1596"/>
+    <cfRule type="duplicateValues" dxfId="1146" priority="1596"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B625">
-    <cfRule type="duplicateValues" dxfId="1157" priority="1597"/>
+    <cfRule type="duplicateValues" dxfId="1145" priority="1597"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B627">
-    <cfRule type="duplicateValues" dxfId="1156" priority="1594"/>
+    <cfRule type="duplicateValues" dxfId="1144" priority="1594"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B627">
-    <cfRule type="duplicateValues" dxfId="1155" priority="1595"/>
+    <cfRule type="duplicateValues" dxfId="1143" priority="1595"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B626">
-    <cfRule type="duplicateValues" dxfId="1154" priority="1593"/>
+    <cfRule type="duplicateValues" dxfId="1142" priority="1593"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B626">
-    <cfRule type="duplicateValues" dxfId="1153" priority="1592"/>
+    <cfRule type="duplicateValues" dxfId="1141" priority="1592"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B628">
-    <cfRule type="duplicateValues" dxfId="1152" priority="1591"/>
+    <cfRule type="duplicateValues" dxfId="1140" priority="1591"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B628">
-    <cfRule type="duplicateValues" dxfId="1151" priority="1590"/>
+    <cfRule type="duplicateValues" dxfId="1139" priority="1590"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B629">
-    <cfRule type="duplicateValues" dxfId="1150" priority="1587"/>
+    <cfRule type="duplicateValues" dxfId="1138" priority="1587"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B629">
-    <cfRule type="duplicateValues" dxfId="1149" priority="1586"/>
+    <cfRule type="duplicateValues" dxfId="1137" priority="1586"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B630">
-    <cfRule type="duplicateValues" dxfId="1148" priority="1583"/>
+    <cfRule type="duplicateValues" dxfId="1136" priority="1583"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B630">
-    <cfRule type="duplicateValues" dxfId="1147" priority="1582"/>
+    <cfRule type="duplicateValues" dxfId="1135" priority="1582"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B631">
-    <cfRule type="duplicateValues" dxfId="1146" priority="1579"/>
+    <cfRule type="duplicateValues" dxfId="1134" priority="1579"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B631">
-    <cfRule type="duplicateValues" dxfId="1145" priority="1578"/>
+    <cfRule type="duplicateValues" dxfId="1133" priority="1578"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B632">
-    <cfRule type="duplicateValues" dxfId="1144" priority="1574"/>
+    <cfRule type="duplicateValues" dxfId="1132" priority="1574"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B632">
-    <cfRule type="duplicateValues" dxfId="1143" priority="1575"/>
+    <cfRule type="duplicateValues" dxfId="1131" priority="1575"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B633">
-    <cfRule type="duplicateValues" dxfId="1142" priority="1570"/>
+    <cfRule type="duplicateValues" dxfId="1130" priority="1570"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B633">
-    <cfRule type="duplicateValues" dxfId="1141" priority="1571"/>
+    <cfRule type="duplicateValues" dxfId="1129" priority="1571"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B634">
-    <cfRule type="duplicateValues" dxfId="1140" priority="1566"/>
+    <cfRule type="duplicateValues" dxfId="1128" priority="1566"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B634">
-    <cfRule type="duplicateValues" dxfId="1139" priority="1567"/>
+    <cfRule type="duplicateValues" dxfId="1127" priority="1567"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B635">
-    <cfRule type="duplicateValues" dxfId="1138" priority="1564"/>
+    <cfRule type="duplicateValues" dxfId="1126" priority="1564"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B635">
-    <cfRule type="duplicateValues" dxfId="1137" priority="1565"/>
+    <cfRule type="duplicateValues" dxfId="1125" priority="1565"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B637">
-    <cfRule type="duplicateValues" dxfId="1136" priority="1562"/>
+    <cfRule type="duplicateValues" dxfId="1124" priority="1562"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B637">
-    <cfRule type="duplicateValues" dxfId="1135" priority="1563"/>
+    <cfRule type="duplicateValues" dxfId="1123" priority="1563"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B636">
-    <cfRule type="duplicateValues" dxfId="1134" priority="1560"/>
+    <cfRule type="duplicateValues" dxfId="1122" priority="1560"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B636">
-    <cfRule type="duplicateValues" dxfId="1133" priority="1561"/>
+    <cfRule type="duplicateValues" dxfId="1121" priority="1561"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B638">
-    <cfRule type="duplicateValues" dxfId="1132" priority="1558"/>
+    <cfRule type="duplicateValues" dxfId="1120" priority="1558"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B638">
-    <cfRule type="duplicateValues" dxfId="1131" priority="1559"/>
+    <cfRule type="duplicateValues" dxfId="1119" priority="1559"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B640">
-    <cfRule type="duplicateValues" dxfId="1130" priority="1556"/>
+    <cfRule type="duplicateValues" dxfId="1118" priority="1556"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B640">
-    <cfRule type="duplicateValues" dxfId="1129" priority="1557"/>
+    <cfRule type="duplicateValues" dxfId="1117" priority="1557"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B641">
-    <cfRule type="duplicateValues" dxfId="1128" priority="1552"/>
+    <cfRule type="duplicateValues" dxfId="1116" priority="1552"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B641">
-    <cfRule type="duplicateValues" dxfId="1127" priority="1553"/>
+    <cfRule type="duplicateValues" dxfId="1115" priority="1553"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B642">
-    <cfRule type="duplicateValues" dxfId="1126" priority="1550"/>
+    <cfRule type="duplicateValues" dxfId="1114" priority="1550"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B642">
-    <cfRule type="duplicateValues" dxfId="1125" priority="1551"/>
+    <cfRule type="duplicateValues" dxfId="1113" priority="1551"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B644">
-    <cfRule type="duplicateValues" dxfId="1124" priority="1547"/>
+    <cfRule type="duplicateValues" dxfId="1112" priority="1547"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B644">
-    <cfRule type="duplicateValues" dxfId="1123" priority="1546"/>
+    <cfRule type="duplicateValues" dxfId="1111" priority="1546"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B643">
-    <cfRule type="duplicateValues" dxfId="1122" priority="1544"/>
+    <cfRule type="duplicateValues" dxfId="1110" priority="1544"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B643">
-    <cfRule type="duplicateValues" dxfId="1121" priority="1545"/>
+    <cfRule type="duplicateValues" dxfId="1109" priority="1545"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B645">
-    <cfRule type="duplicateValues" dxfId="1120" priority="1541"/>
+    <cfRule type="duplicateValues" dxfId="1108" priority="1541"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B645">
-    <cfRule type="duplicateValues" dxfId="1119" priority="1540"/>
+    <cfRule type="duplicateValues" dxfId="1107" priority="1540"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B646">
-    <cfRule type="duplicateValues" dxfId="1118" priority="1538"/>
+    <cfRule type="duplicateValues" dxfId="1106" priority="1538"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B646">
-    <cfRule type="duplicateValues" dxfId="1117" priority="1539"/>
+    <cfRule type="duplicateValues" dxfId="1105" priority="1539"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B647">
-    <cfRule type="duplicateValues" dxfId="1116" priority="1533"/>
+    <cfRule type="duplicateValues" dxfId="1104" priority="1533"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B647">
-    <cfRule type="duplicateValues" dxfId="1115" priority="1532"/>
+    <cfRule type="duplicateValues" dxfId="1103" priority="1532"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B648">
-    <cfRule type="duplicateValues" dxfId="1114" priority="1528"/>
+    <cfRule type="duplicateValues" dxfId="1102" priority="1528"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B648">
-    <cfRule type="duplicateValues" dxfId="1113" priority="1529"/>
+    <cfRule type="duplicateValues" dxfId="1101" priority="1529"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B649">
-    <cfRule type="duplicateValues" dxfId="1112" priority="1527"/>
+    <cfRule type="duplicateValues" dxfId="1100" priority="1527"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B649">
-    <cfRule type="duplicateValues" dxfId="1111" priority="1526"/>
+    <cfRule type="duplicateValues" dxfId="1099" priority="1526"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B650">
-    <cfRule type="duplicateValues" dxfId="1110" priority="1524"/>
+    <cfRule type="duplicateValues" dxfId="1098" priority="1524"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B650">
-    <cfRule type="duplicateValues" dxfId="1109" priority="1525"/>
+    <cfRule type="duplicateValues" dxfId="1097" priority="1525"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B651">
-    <cfRule type="duplicateValues" dxfId="1108" priority="1522"/>
+    <cfRule type="duplicateValues" dxfId="1096" priority="1522"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B651">
-    <cfRule type="duplicateValues" dxfId="1107" priority="1523"/>
+    <cfRule type="duplicateValues" dxfId="1095" priority="1523"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B652">
-    <cfRule type="duplicateValues" dxfId="1106" priority="1520"/>
+    <cfRule type="duplicateValues" dxfId="1094" priority="1520"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B652">
-    <cfRule type="duplicateValues" dxfId="1105" priority="1521"/>
+    <cfRule type="duplicateValues" dxfId="1093" priority="1521"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B653">
-    <cfRule type="duplicateValues" dxfId="1104" priority="1518"/>
+    <cfRule type="duplicateValues" dxfId="1092" priority="1518"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B653">
-    <cfRule type="duplicateValues" dxfId="1103" priority="1519"/>
+    <cfRule type="duplicateValues" dxfId="1091" priority="1519"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B654">
-    <cfRule type="duplicateValues" dxfId="1102" priority="1512"/>
+    <cfRule type="duplicateValues" dxfId="1090" priority="1512"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B654">
-    <cfRule type="duplicateValues" dxfId="1101" priority="1513"/>
+    <cfRule type="duplicateValues" dxfId="1089" priority="1513"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B656">
-    <cfRule type="duplicateValues" dxfId="1100" priority="1508"/>
+    <cfRule type="duplicateValues" dxfId="1088" priority="1508"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B656">
-    <cfRule type="duplicateValues" dxfId="1099" priority="1509"/>
+    <cfRule type="duplicateValues" dxfId="1087" priority="1509"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B657">
-    <cfRule type="duplicateValues" dxfId="1098" priority="1506"/>
+    <cfRule type="duplicateValues" dxfId="1086" priority="1506"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B657">
-    <cfRule type="duplicateValues" dxfId="1097" priority="1507"/>
+    <cfRule type="duplicateValues" dxfId="1085" priority="1507"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B658">
-    <cfRule type="duplicateValues" dxfId="1096" priority="1504"/>
+    <cfRule type="duplicateValues" dxfId="1084" priority="1504"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B658">
-    <cfRule type="duplicateValues" dxfId="1095" priority="1505"/>
+    <cfRule type="duplicateValues" dxfId="1083" priority="1505"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B659">
-    <cfRule type="duplicateValues" dxfId="1094" priority="1503"/>
+    <cfRule type="duplicateValues" dxfId="1082" priority="1503"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B659">
-    <cfRule type="duplicateValues" dxfId="1093" priority="1502"/>
+    <cfRule type="duplicateValues" dxfId="1081" priority="1502"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B660">
-    <cfRule type="duplicateValues" dxfId="1092" priority="1500"/>
+    <cfRule type="duplicateValues" dxfId="1080" priority="1500"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B660">
-    <cfRule type="duplicateValues" dxfId="1091" priority="1501"/>
+    <cfRule type="duplicateValues" dxfId="1079" priority="1501"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B661">
-    <cfRule type="duplicateValues" dxfId="1090" priority="1498"/>
+    <cfRule type="duplicateValues" dxfId="1078" priority="1498"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B661">
-    <cfRule type="duplicateValues" dxfId="1089" priority="1499"/>
+    <cfRule type="duplicateValues" dxfId="1077" priority="1499"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B662">
-    <cfRule type="duplicateValues" dxfId="1088" priority="1497"/>
+    <cfRule type="duplicateValues" dxfId="1076" priority="1497"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B662">
-    <cfRule type="duplicateValues" dxfId="1087" priority="1496"/>
+    <cfRule type="duplicateValues" dxfId="1075" priority="1496"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B666">
-    <cfRule type="duplicateValues" dxfId="1086" priority="1492"/>
+    <cfRule type="duplicateValues" dxfId="1074" priority="1492"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B666">
-    <cfRule type="duplicateValues" dxfId="1085" priority="1493"/>
+    <cfRule type="duplicateValues" dxfId="1073" priority="1493"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B667">
-    <cfRule type="duplicateValues" dxfId="1084" priority="1490"/>
+    <cfRule type="duplicateValues" dxfId="1072" priority="1490"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B667">
-    <cfRule type="duplicateValues" dxfId="1083" priority="1491"/>
+    <cfRule type="duplicateValues" dxfId="1071" priority="1491"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B668">
-    <cfRule type="duplicateValues" dxfId="1082" priority="1486"/>
+    <cfRule type="duplicateValues" dxfId="1070" priority="1486"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B668">
-    <cfRule type="duplicateValues" dxfId="1081" priority="1487"/>
+    <cfRule type="duplicateValues" dxfId="1069" priority="1487"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B669">
-    <cfRule type="duplicateValues" dxfId="1080" priority="1483"/>
+    <cfRule type="duplicateValues" dxfId="1068" priority="1483"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B669">
-    <cfRule type="duplicateValues" dxfId="1079" priority="1482"/>
+    <cfRule type="duplicateValues" dxfId="1067" priority="1482"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B670">
-    <cfRule type="duplicateValues" dxfId="1078" priority="1479"/>
+    <cfRule type="duplicateValues" dxfId="1066" priority="1479"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B670">
-    <cfRule type="duplicateValues" dxfId="1077" priority="1478"/>
+    <cfRule type="duplicateValues" dxfId="1065" priority="1478"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B672">
-    <cfRule type="duplicateValues" dxfId="1076" priority="1476"/>
+    <cfRule type="duplicateValues" dxfId="1064" priority="1476"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B672">
-    <cfRule type="duplicateValues" dxfId="1075" priority="1477"/>
+    <cfRule type="duplicateValues" dxfId="1063" priority="1477"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B673">
-    <cfRule type="duplicateValues" dxfId="1074" priority="1472"/>
+    <cfRule type="duplicateValues" dxfId="1062" priority="1472"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B673">
-    <cfRule type="duplicateValues" dxfId="1073" priority="1473"/>
+    <cfRule type="duplicateValues" dxfId="1061" priority="1473"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B674">
-    <cfRule type="duplicateValues" dxfId="1072" priority="1466"/>
+    <cfRule type="duplicateValues" dxfId="1060" priority="1466"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B674">
-    <cfRule type="duplicateValues" dxfId="1071" priority="1467"/>
+    <cfRule type="duplicateValues" dxfId="1059" priority="1467"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B675">
-    <cfRule type="duplicateValues" dxfId="1070" priority="1463"/>
+    <cfRule type="duplicateValues" dxfId="1058" priority="1463"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B675">
-    <cfRule type="duplicateValues" dxfId="1069" priority="1464"/>
+    <cfRule type="duplicateValues" dxfId="1057" priority="1464"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B675">
-    <cfRule type="duplicateValues" dxfId="1068" priority="1462"/>
+    <cfRule type="duplicateValues" dxfId="1056" priority="1462"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B676">
-    <cfRule type="duplicateValues" dxfId="1067" priority="1457"/>
+    <cfRule type="duplicateValues" dxfId="1055" priority="1457"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B676">
-    <cfRule type="duplicateValues" dxfId="1066" priority="1458"/>
+    <cfRule type="duplicateValues" dxfId="1054" priority="1458"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B676">
-    <cfRule type="duplicateValues" dxfId="1065" priority="1456"/>
+    <cfRule type="duplicateValues" dxfId="1053" priority="1456"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677">
-    <cfRule type="duplicateValues" dxfId="1064" priority="1454"/>
+    <cfRule type="duplicateValues" dxfId="1052" priority="1454"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677">
-    <cfRule type="duplicateValues" dxfId="1063" priority="1455"/>
+    <cfRule type="duplicateValues" dxfId="1051" priority="1455"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677">
-    <cfRule type="duplicateValues" dxfId="1062" priority="1453"/>
+    <cfRule type="duplicateValues" dxfId="1050" priority="1453"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B678">
-    <cfRule type="duplicateValues" dxfId="1061" priority="1451"/>
+    <cfRule type="duplicateValues" dxfId="1049" priority="1451"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B678">
-    <cfRule type="duplicateValues" dxfId="1060" priority="1452"/>
+    <cfRule type="duplicateValues" dxfId="1048" priority="1452"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B678">
-    <cfRule type="duplicateValues" dxfId="1059" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="1047" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B679">
-    <cfRule type="duplicateValues" dxfId="1058" priority="1448"/>
+    <cfRule type="duplicateValues" dxfId="1046" priority="1448"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B679">
-    <cfRule type="duplicateValues" dxfId="1057" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="1045" priority="1449"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B679">
-    <cfRule type="duplicateValues" dxfId="1056" priority="1447"/>
+    <cfRule type="duplicateValues" dxfId="1044" priority="1447"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B680">
-    <cfRule type="duplicateValues" dxfId="1055" priority="1442"/>
+    <cfRule type="duplicateValues" dxfId="1043" priority="1442"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B680">
-    <cfRule type="duplicateValues" dxfId="1054" priority="1443"/>
+    <cfRule type="duplicateValues" dxfId="1042" priority="1443"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B680">
-    <cfRule type="duplicateValues" dxfId="1053" priority="1441"/>
+    <cfRule type="duplicateValues" dxfId="1041" priority="1441"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B681">
-    <cfRule type="duplicateValues" dxfId="1052" priority="1437"/>
+    <cfRule type="duplicateValues" dxfId="1040" priority="1437"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B681">
-    <cfRule type="duplicateValues" dxfId="1051" priority="1436"/>
+    <cfRule type="duplicateValues" dxfId="1039" priority="1436"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B681">
-    <cfRule type="duplicateValues" dxfId="1050" priority="1435"/>
+    <cfRule type="duplicateValues" dxfId="1038" priority="1435"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B682">
-    <cfRule type="duplicateValues" dxfId="1049" priority="1431"/>
+    <cfRule type="duplicateValues" dxfId="1037" priority="1431"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B682">
-    <cfRule type="duplicateValues" dxfId="1048" priority="1430"/>
+    <cfRule type="duplicateValues" dxfId="1036" priority="1430"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B682">
-    <cfRule type="duplicateValues" dxfId="1047" priority="1429"/>
+    <cfRule type="duplicateValues" dxfId="1035" priority="1429"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B684">
-    <cfRule type="duplicateValues" dxfId="1046" priority="1418"/>
+    <cfRule type="duplicateValues" dxfId="1034" priority="1418"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B684">
-    <cfRule type="duplicateValues" dxfId="1045" priority="1419"/>
+    <cfRule type="duplicateValues" dxfId="1033" priority="1419"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B684">
-    <cfRule type="duplicateValues" dxfId="1044" priority="1417"/>
+    <cfRule type="duplicateValues" dxfId="1032" priority="1417"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B685">
-    <cfRule type="duplicateValues" dxfId="1043" priority="1415"/>
+    <cfRule type="duplicateValues" dxfId="1031" priority="1415"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B685">
-    <cfRule type="duplicateValues" dxfId="1042" priority="1416"/>
+    <cfRule type="duplicateValues" dxfId="1030" priority="1416"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B685">
-    <cfRule type="duplicateValues" dxfId="1041" priority="1414"/>
+    <cfRule type="duplicateValues" dxfId="1029" priority="1414"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B687">
-    <cfRule type="duplicateValues" dxfId="1040" priority="1412"/>
+    <cfRule type="duplicateValues" dxfId="1028" priority="1412"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B687">
-    <cfRule type="duplicateValues" dxfId="1039" priority="1413"/>
+    <cfRule type="duplicateValues" dxfId="1027" priority="1413"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B687">
-    <cfRule type="duplicateValues" dxfId="1038" priority="1411"/>
+    <cfRule type="duplicateValues" dxfId="1026" priority="1411"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B688">
-    <cfRule type="duplicateValues" dxfId="1037" priority="1409"/>
+    <cfRule type="duplicateValues" dxfId="1025" priority="1409"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B688">
-    <cfRule type="duplicateValues" dxfId="1036" priority="1410"/>
+    <cfRule type="duplicateValues" dxfId="1024" priority="1410"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B688">
-    <cfRule type="duplicateValues" dxfId="1035" priority="1408"/>
+    <cfRule type="duplicateValues" dxfId="1023" priority="1408"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B689">
-    <cfRule type="duplicateValues" dxfId="1034" priority="1400"/>
+    <cfRule type="duplicateValues" dxfId="1022" priority="1400"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B689">
-    <cfRule type="duplicateValues" dxfId="1033" priority="1401"/>
+    <cfRule type="duplicateValues" dxfId="1021" priority="1401"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B689">
-    <cfRule type="duplicateValues" dxfId="1032" priority="1399"/>
+    <cfRule type="duplicateValues" dxfId="1020" priority="1399"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B690">
-    <cfRule type="duplicateValues" dxfId="1031" priority="1397"/>
+    <cfRule type="duplicateValues" dxfId="1019" priority="1397"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B690">
-    <cfRule type="duplicateValues" dxfId="1030" priority="1398"/>
+    <cfRule type="duplicateValues" dxfId="1018" priority="1398"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B690">
-    <cfRule type="duplicateValues" dxfId="1029" priority="1396"/>
+    <cfRule type="duplicateValues" dxfId="1017" priority="1396"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B691">
-    <cfRule type="duplicateValues" dxfId="1028" priority="1392"/>
+    <cfRule type="duplicateValues" dxfId="1016" priority="1392"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B691">
-    <cfRule type="duplicateValues" dxfId="1027" priority="1391"/>
+    <cfRule type="duplicateValues" dxfId="1015" priority="1391"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B691">
-    <cfRule type="duplicateValues" dxfId="1026" priority="1390"/>
+    <cfRule type="duplicateValues" dxfId="1014" priority="1390"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B693">
-    <cfRule type="duplicateValues" dxfId="1025" priority="1389"/>
+    <cfRule type="duplicateValues" dxfId="1013" priority="1389"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B693">
-    <cfRule type="duplicateValues" dxfId="1024" priority="1388"/>
+    <cfRule type="duplicateValues" dxfId="1012" priority="1388"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B693">
-    <cfRule type="duplicateValues" dxfId="1023" priority="1387"/>
+    <cfRule type="duplicateValues" dxfId="1011" priority="1387"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B694">
-    <cfRule type="duplicateValues" dxfId="1022" priority="1383"/>
+    <cfRule type="duplicateValues" dxfId="1010" priority="1383"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B694">
-    <cfRule type="duplicateValues" dxfId="1021" priority="1382"/>
+    <cfRule type="duplicateValues" dxfId="1009" priority="1382"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B694">
-    <cfRule type="duplicateValues" dxfId="1020" priority="1381"/>
+    <cfRule type="duplicateValues" dxfId="1008" priority="1381"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B695">
-    <cfRule type="duplicateValues" dxfId="1019" priority="1374"/>
+    <cfRule type="duplicateValues" dxfId="1007" priority="1374"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B695">
-    <cfRule type="duplicateValues" dxfId="1018" priority="1373"/>
+    <cfRule type="duplicateValues" dxfId="1006" priority="1373"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B695">
-    <cfRule type="duplicateValues" dxfId="1017" priority="1372"/>
+    <cfRule type="duplicateValues" dxfId="1005" priority="1372"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B696">
-    <cfRule type="duplicateValues" dxfId="1016" priority="1370"/>
+    <cfRule type="duplicateValues" dxfId="1004" priority="1370"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B696">
-    <cfRule type="duplicateValues" dxfId="1015" priority="1371"/>
+    <cfRule type="duplicateValues" dxfId="1003" priority="1371"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B696">
-    <cfRule type="duplicateValues" dxfId="1014" priority="1369"/>
+    <cfRule type="duplicateValues" dxfId="1002" priority="1369"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B697">
-    <cfRule type="duplicateValues" dxfId="1013" priority="1367"/>
+    <cfRule type="duplicateValues" dxfId="1001" priority="1367"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B697">
-    <cfRule type="duplicateValues" dxfId="1012" priority="1368"/>
+    <cfRule type="duplicateValues" dxfId="1000" priority="1368"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B697">
-    <cfRule type="duplicateValues" dxfId="1011" priority="1366"/>
+    <cfRule type="duplicateValues" dxfId="999" priority="1366"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B698">
-    <cfRule type="duplicateValues" dxfId="1010" priority="1358"/>
+    <cfRule type="duplicateValues" dxfId="998" priority="1358"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B698">
-    <cfRule type="duplicateValues" dxfId="1009" priority="1359"/>
+    <cfRule type="duplicateValues" dxfId="997" priority="1359"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B698">
-    <cfRule type="duplicateValues" dxfId="1008" priority="1357"/>
+    <cfRule type="duplicateValues" dxfId="996" priority="1357"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B699">
-    <cfRule type="duplicateValues" dxfId="1007" priority="1355"/>
+    <cfRule type="duplicateValues" dxfId="995" priority="1355"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B699">
-    <cfRule type="duplicateValues" dxfId="1006" priority="1356"/>
+    <cfRule type="duplicateValues" dxfId="994" priority="1356"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B699">
-    <cfRule type="duplicateValues" dxfId="1005" priority="1354"/>
+    <cfRule type="duplicateValues" dxfId="993" priority="1354"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B701">
-    <cfRule type="duplicateValues" dxfId="1004" priority="1349"/>
+    <cfRule type="duplicateValues" dxfId="992" priority="1349"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B701">
-    <cfRule type="duplicateValues" dxfId="1003" priority="1350"/>
+    <cfRule type="duplicateValues" dxfId="991" priority="1350"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B701">
-    <cfRule type="duplicateValues" dxfId="1002" priority="1348"/>
+    <cfRule type="duplicateValues" dxfId="990" priority="1348"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B700">
-    <cfRule type="duplicateValues" dxfId="1001" priority="1347"/>
+    <cfRule type="duplicateValues" dxfId="989" priority="1347"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B700">
-    <cfRule type="duplicateValues" dxfId="1000" priority="1346"/>
+    <cfRule type="duplicateValues" dxfId="988" priority="1346"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B700">
-    <cfRule type="duplicateValues" dxfId="999" priority="1345"/>
+    <cfRule type="duplicateValues" dxfId="987" priority="1345"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B702">
-    <cfRule type="duplicateValues" dxfId="998" priority="1343"/>
+    <cfRule type="duplicateValues" dxfId="986" priority="1343"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B702">
-    <cfRule type="duplicateValues" dxfId="997" priority="1344"/>
+    <cfRule type="duplicateValues" dxfId="985" priority="1344"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B702">
-    <cfRule type="duplicateValues" dxfId="996" priority="1342"/>
+    <cfRule type="duplicateValues" dxfId="984" priority="1342"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B704">
-    <cfRule type="duplicateValues" dxfId="995" priority="1340"/>
+    <cfRule type="duplicateValues" dxfId="983" priority="1340"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B704">
-    <cfRule type="duplicateValues" dxfId="994" priority="1341"/>
+    <cfRule type="duplicateValues" dxfId="982" priority="1341"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B704">
-    <cfRule type="duplicateValues" dxfId="993" priority="1339"/>
+    <cfRule type="duplicateValues" dxfId="981" priority="1339"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B705">
-    <cfRule type="duplicateValues" dxfId="992" priority="1337"/>
+    <cfRule type="duplicateValues" dxfId="980" priority="1337"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B705">
-    <cfRule type="duplicateValues" dxfId="991" priority="1338"/>
+    <cfRule type="duplicateValues" dxfId="979" priority="1338"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B705">
-    <cfRule type="duplicateValues" dxfId="990" priority="1336"/>
+    <cfRule type="duplicateValues" dxfId="978" priority="1336"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B707">
-    <cfRule type="duplicateValues" dxfId="989" priority="1335"/>
+    <cfRule type="duplicateValues" dxfId="977" priority="1335"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B707">
-    <cfRule type="duplicateValues" dxfId="988" priority="1334"/>
+    <cfRule type="duplicateValues" dxfId="976" priority="1334"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B707">
-    <cfRule type="duplicateValues" dxfId="987" priority="1333"/>
+    <cfRule type="duplicateValues" dxfId="975" priority="1333"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B708">
-    <cfRule type="duplicateValues" dxfId="986" priority="1331"/>
+    <cfRule type="duplicateValues" dxfId="974" priority="1331"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B708">
-    <cfRule type="duplicateValues" dxfId="985" priority="1332"/>
+    <cfRule type="duplicateValues" dxfId="973" priority="1332"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B708">
-    <cfRule type="duplicateValues" dxfId="984" priority="1330"/>
+    <cfRule type="duplicateValues" dxfId="972" priority="1330"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B709">
-    <cfRule type="duplicateValues" dxfId="983" priority="1328"/>
+    <cfRule type="duplicateValues" dxfId="971" priority="1328"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B709">
-    <cfRule type="duplicateValues" dxfId="982" priority="1329"/>
+    <cfRule type="duplicateValues" dxfId="970" priority="1329"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B709">
-    <cfRule type="duplicateValues" dxfId="981" priority="1327"/>
+    <cfRule type="duplicateValues" dxfId="969" priority="1327"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B711">
-    <cfRule type="duplicateValues" dxfId="980" priority="1325"/>
+    <cfRule type="duplicateValues" dxfId="968" priority="1325"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B711">
-    <cfRule type="duplicateValues" dxfId="979" priority="1326"/>
+    <cfRule type="duplicateValues" dxfId="967" priority="1326"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B711">
-    <cfRule type="duplicateValues" dxfId="978" priority="1324"/>
+    <cfRule type="duplicateValues" dxfId="966" priority="1324"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B712">
-    <cfRule type="duplicateValues" dxfId="977" priority="1319"/>
+    <cfRule type="duplicateValues" dxfId="965" priority="1319"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B712">
-    <cfRule type="duplicateValues" dxfId="976" priority="1320"/>
+    <cfRule type="duplicateValues" dxfId="964" priority="1320"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B712">
-    <cfRule type="duplicateValues" dxfId="975" priority="1318"/>
+    <cfRule type="duplicateValues" dxfId="963" priority="1318"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B713">
-    <cfRule type="duplicateValues" dxfId="974" priority="1316"/>
+    <cfRule type="duplicateValues" dxfId="962" priority="1316"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B713">
-    <cfRule type="duplicateValues" dxfId="973" priority="1317"/>
+    <cfRule type="duplicateValues" dxfId="961" priority="1317"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B713">
-    <cfRule type="duplicateValues" dxfId="972" priority="1315"/>
+    <cfRule type="duplicateValues" dxfId="960" priority="1315"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B715">
-    <cfRule type="duplicateValues" dxfId="971" priority="1313"/>
+    <cfRule type="duplicateValues" dxfId="959" priority="1313"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B715">
-    <cfRule type="duplicateValues" dxfId="970" priority="1314"/>
+    <cfRule type="duplicateValues" dxfId="958" priority="1314"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B715">
-    <cfRule type="duplicateValues" dxfId="969" priority="1312"/>
+    <cfRule type="duplicateValues" dxfId="957" priority="1312"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B716">
-    <cfRule type="duplicateValues" dxfId="968" priority="1307"/>
+    <cfRule type="duplicateValues" dxfId="956" priority="1307"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B716">
-    <cfRule type="duplicateValues" dxfId="967" priority="1308"/>
+    <cfRule type="duplicateValues" dxfId="955" priority="1308"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B716">
-    <cfRule type="duplicateValues" dxfId="966" priority="1306"/>
+    <cfRule type="duplicateValues" dxfId="954" priority="1306"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B717">
-    <cfRule type="duplicateValues" dxfId="965" priority="1299"/>
+    <cfRule type="duplicateValues" dxfId="953" priority="1299"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B717">
-    <cfRule type="duplicateValues" dxfId="964" priority="1298"/>
+    <cfRule type="duplicateValues" dxfId="952" priority="1298"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B717">
-    <cfRule type="duplicateValues" dxfId="963" priority="1297"/>
+    <cfRule type="duplicateValues" dxfId="951" priority="1297"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B718">
-    <cfRule type="duplicateValues" dxfId="962" priority="1296"/>
+    <cfRule type="duplicateValues" dxfId="950" priority="1296"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B718">
-    <cfRule type="duplicateValues" dxfId="961" priority="1295"/>
+    <cfRule type="duplicateValues" dxfId="949" priority="1295"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B718">
-    <cfRule type="duplicateValues" dxfId="960" priority="1294"/>
+    <cfRule type="duplicateValues" dxfId="948" priority="1294"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B720">
-    <cfRule type="duplicateValues" dxfId="959" priority="1293"/>
+    <cfRule type="duplicateValues" dxfId="947" priority="1293"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B720">
-    <cfRule type="duplicateValues" dxfId="958" priority="1292"/>
+    <cfRule type="duplicateValues" dxfId="946" priority="1292"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B720">
-    <cfRule type="duplicateValues" dxfId="957" priority="1291"/>
+    <cfRule type="duplicateValues" dxfId="945" priority="1291"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B719">
-    <cfRule type="duplicateValues" dxfId="956" priority="1290"/>
+    <cfRule type="duplicateValues" dxfId="944" priority="1290"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B719">
-    <cfRule type="duplicateValues" dxfId="955" priority="1289"/>
+    <cfRule type="duplicateValues" dxfId="943" priority="1289"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B719">
-    <cfRule type="duplicateValues" dxfId="954" priority="1288"/>
+    <cfRule type="duplicateValues" dxfId="942" priority="1288"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B722">
-    <cfRule type="duplicateValues" dxfId="953" priority="1286"/>
+    <cfRule type="duplicateValues" dxfId="941" priority="1286"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B722">
-    <cfRule type="duplicateValues" dxfId="952" priority="1287"/>
+    <cfRule type="duplicateValues" dxfId="940" priority="1287"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B722">
-    <cfRule type="duplicateValues" dxfId="951" priority="1285"/>
+    <cfRule type="duplicateValues" dxfId="939" priority="1285"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B724">
-    <cfRule type="duplicateValues" dxfId="950" priority="1277"/>
+    <cfRule type="duplicateValues" dxfId="938" priority="1277"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B724">
-    <cfRule type="duplicateValues" dxfId="949" priority="1278"/>
+    <cfRule type="duplicateValues" dxfId="937" priority="1278"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B724">
-    <cfRule type="duplicateValues" dxfId="948" priority="1276"/>
+    <cfRule type="duplicateValues" dxfId="936" priority="1276"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B725">
-    <cfRule type="duplicateValues" dxfId="947" priority="1271"/>
+    <cfRule type="duplicateValues" dxfId="935" priority="1271"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B725">
-    <cfRule type="duplicateValues" dxfId="946" priority="1272"/>
+    <cfRule type="duplicateValues" dxfId="934" priority="1272"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B725">
-    <cfRule type="duplicateValues" dxfId="945" priority="1270"/>
+    <cfRule type="duplicateValues" dxfId="933" priority="1270"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B727">
-    <cfRule type="duplicateValues" dxfId="944" priority="1265"/>
+    <cfRule type="duplicateValues" dxfId="932" priority="1265"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B727">
-    <cfRule type="duplicateValues" dxfId="943" priority="1266"/>
+    <cfRule type="duplicateValues" dxfId="931" priority="1266"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B727">
-    <cfRule type="duplicateValues" dxfId="942" priority="1264"/>
+    <cfRule type="duplicateValues" dxfId="930" priority="1264"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B726">
-    <cfRule type="duplicateValues" dxfId="941" priority="1263"/>
+    <cfRule type="duplicateValues" dxfId="929" priority="1263"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B726">
-    <cfRule type="duplicateValues" dxfId="940" priority="1262"/>
+    <cfRule type="duplicateValues" dxfId="928" priority="1262"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B726">
-    <cfRule type="duplicateValues" dxfId="939" priority="1261"/>
+    <cfRule type="duplicateValues" dxfId="927" priority="1261"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B728">
-    <cfRule type="duplicateValues" dxfId="938" priority="1256"/>
+    <cfRule type="duplicateValues" dxfId="926" priority="1256"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B728">
-    <cfRule type="duplicateValues" dxfId="937" priority="1257"/>
+    <cfRule type="duplicateValues" dxfId="925" priority="1257"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B728">
-    <cfRule type="duplicateValues" dxfId="936" priority="1255"/>
+    <cfRule type="duplicateValues" dxfId="924" priority="1255"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B730">
-    <cfRule type="duplicateValues" dxfId="935" priority="1254"/>
+    <cfRule type="duplicateValues" dxfId="923" priority="1254"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B730">
-    <cfRule type="duplicateValues" dxfId="934" priority="1253"/>
+    <cfRule type="duplicateValues" dxfId="922" priority="1253"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B730">
-    <cfRule type="duplicateValues" dxfId="933" priority="1252"/>
+    <cfRule type="duplicateValues" dxfId="921" priority="1252"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B731">
-    <cfRule type="duplicateValues" dxfId="932" priority="1250"/>
+    <cfRule type="duplicateValues" dxfId="920" priority="1250"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B731">
-    <cfRule type="duplicateValues" dxfId="931" priority="1251"/>
+    <cfRule type="duplicateValues" dxfId="919" priority="1251"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B731">
-    <cfRule type="duplicateValues" dxfId="930" priority="1249"/>
+    <cfRule type="duplicateValues" dxfId="918" priority="1249"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B732">
-    <cfRule type="duplicateValues" dxfId="929" priority="1241"/>
+    <cfRule type="duplicateValues" dxfId="917" priority="1241"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B732">
-    <cfRule type="duplicateValues" dxfId="928" priority="1242"/>
+    <cfRule type="duplicateValues" dxfId="916" priority="1242"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B732">
-    <cfRule type="duplicateValues" dxfId="927" priority="1240"/>
+    <cfRule type="duplicateValues" dxfId="915" priority="1240"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B683 D46 B573:B574 B46 B104:B106 B109:B111 B126 B131 B134 B137 B143:B147 B150:B152 B159:B160 D154 B169 B181 B188 B190 B199 D195 B212 B222:B224 B229 B231:B232 B239:B240 B242:B244 B251 B258:B261 B264:B269 B273 B278 B288:B289 B291 B295:B299 B306:B307 B324 B331 B333 B337:B338 B340:B341 B343 B348 B345:B346 B351 B364 B372:B373 B378:B380 B389:B390 B396:B397 B401 B420 B430 B433 B438:B439 B442 B444 B448 B451 B459 B463 B466 B475:B476 B480 B488 B492:B495 B507 B514 B519 B524 B528:B529 B531:B535 B537 B539 B560 B576 B590 B599:B600 B612 B622:B624 B639 B655 B663:B665 B671 B686 B692 B703 B706 B710 B714 B721 B723 B729 B739 B755 B758 B766 B768:B769 B775:B776 B781:B783 B805 B808 B811 B824:B827 B838 B840 B842:B843 B847 B850 B855:B856 B860 B862 B864:B865 B876 B878 B897 B911 B927:B928 B930 B932:B933 B942 B950:B1048576 B1:B8 B11:B15 B18:B19 B22 B24 B30:B31 B34 B39:B41 B43 B48:B50 B53 B56:B58 B62:B64 B74:B94 B96:B102 B114:B119 B122 B124 B183:B184 B468">
-    <cfRule type="duplicateValues" dxfId="926" priority="2582"/>
+    <cfRule type="duplicateValues" dxfId="914" priority="2582"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B683 B573:B574 B231:B232 B239:B240 B242:B244 B251 B258:B261 B264:B269 B273 B278 B288:B289 B291 B295:B299 B306:B307 B324 B331 B333 B337:B338 B340:B341 B343 B348 B345:B346 B351 B364 B372:B373 B378:B380 B389:B390 B396:B397 B401 B420 B430 B433 B438:B439 B442 B444 B448 B451 B459 B463 B466 B475:B476 B480 B488 B492:B495 B507 B514 B519 B524 B528:B529 B531:B535 B537 B539 B560 B576 B590 B599:B600 B612 B622:B624 B639 B655 B663:B665 B671 B686 B692 B703 B706 B710 B714 B721 B723 B729 B739 B755 B758 B766 B768:B769 B775:B776 B781:B783 B805 B808 B811 B824:B827 B838 B840 B842:B843 B847 B850 B855:B856 B860 B862 B864:B865 B876 B878 B897 B911 B927:B928 B930 B932:B933 B942 B950:B1048576 B1:B8 B11:B15 B18:B19 B22 B24 B30:B31 B34 B39:B41 B43 B46 B48:B50 B53 B56:B58 B62:B64 B74:B94 B96:B106 B108:B111 B114:B119 B122 B124:B126 B128:B152 B154:B155 B157 B159:B164 B166:B167 B169:B170 B179 B181 B183:B184 B186:B188 B190:B202 B204:B205 B209:B212 B214 B216:B217 B219:B220 B222:B229 B468">
-    <cfRule type="duplicateValues" dxfId="925" priority="2694"/>
+    <cfRule type="duplicateValues" dxfId="913" priority="2694"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B683 B686 B692 B703 B706 B710 B714 B721 B723 B729 B739 B755 B758 B766 B768:B769 B775:B776 B781:B783 B805 B808 B811 B824:B827 B838 B840 B842:B843 B847 B850 B855:B856 B860 B862 B864:B865 B876 B878 B897 B911 B927:B928 B930 B932:B933 B942 B950:B1048576 B1:B8 B11:B15 B18:B19 B22 B24 B30:B31 B34 B39:B41 B43 B46 B48:B50 B53 B56:B58 B62:B64 B74:B94 B96:B106 B108:B111 B114:B119 B122 B124:B126 B128:B152 B154:B155 B157 B159:B164 B166:B167 B169:B170 B179 B181 B183:B184 B186:B188 B190:B202 B204:B205 B209:B212 B214 B216:B217 B219:B220 B222:B229 B231:B232 B237:B249 B251:B252 B255 B258:B261 B263:B269 B271 B273:B279 B281:B283 B286:B310 B312 B315 B317:B318 B320:B321 B324 B329:B353 B355:B361 B363:B368 B370:B383 B385:B390 B392:B414 B416:B417 B420:B440 B442:B455 B457:B463 B465:B466 B468:B470 B473:B476 B478:B482 B484 B486 B488:B490 B492:B498 B501:B504 B507:B510 B512:B547 B549 B551:B558 B560 B562:B569 B571:B584 B586:B587 B589:B596 B599:B674">
-    <cfRule type="duplicateValues" dxfId="924" priority="2780"/>
+    <cfRule type="duplicateValues" dxfId="912" priority="2780"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B733">
-    <cfRule type="duplicateValues" dxfId="923" priority="1234"/>
+    <cfRule type="duplicateValues" dxfId="911" priority="1234"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B733">
-    <cfRule type="duplicateValues" dxfId="922" priority="1235"/>
+    <cfRule type="duplicateValues" dxfId="910" priority="1235"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B733">
-    <cfRule type="duplicateValues" dxfId="921" priority="1236"/>
+    <cfRule type="duplicateValues" dxfId="909" priority="1236"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B734">
-    <cfRule type="duplicateValues" dxfId="920" priority="1229"/>
+    <cfRule type="duplicateValues" dxfId="908" priority="1229"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B734">
-    <cfRule type="duplicateValues" dxfId="919" priority="1228"/>
+    <cfRule type="duplicateValues" dxfId="907" priority="1228"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B734">
-    <cfRule type="duplicateValues" dxfId="918" priority="1230"/>
+    <cfRule type="duplicateValues" dxfId="906" priority="1230"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B735">
-    <cfRule type="duplicateValues" dxfId="917" priority="1225"/>
+    <cfRule type="duplicateValues" dxfId="905" priority="1225"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B735">
-    <cfRule type="duplicateValues" dxfId="916" priority="1226"/>
+    <cfRule type="duplicateValues" dxfId="904" priority="1226"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B735">
-    <cfRule type="duplicateValues" dxfId="915" priority="1227"/>
+    <cfRule type="duplicateValues" dxfId="903" priority="1227"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B736">
-    <cfRule type="duplicateValues" dxfId="914" priority="1220"/>
+    <cfRule type="duplicateValues" dxfId="902" priority="1220"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B736">
-    <cfRule type="duplicateValues" dxfId="913" priority="1221"/>
+    <cfRule type="duplicateValues" dxfId="901" priority="1221"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B736">
-    <cfRule type="duplicateValues" dxfId="912" priority="1219"/>
+    <cfRule type="duplicateValues" dxfId="900" priority="1219"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B737">
-    <cfRule type="duplicateValues" dxfId="911" priority="1213"/>
+    <cfRule type="duplicateValues" dxfId="899" priority="1213"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B737">
-    <cfRule type="duplicateValues" dxfId="910" priority="1214"/>
+    <cfRule type="duplicateValues" dxfId="898" priority="1214"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B737">
-    <cfRule type="duplicateValues" dxfId="909" priority="1215"/>
+    <cfRule type="duplicateValues" dxfId="897" priority="1215"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B738">
-    <cfRule type="duplicateValues" dxfId="908" priority="1211"/>
+    <cfRule type="duplicateValues" dxfId="896" priority="1211"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B738">
-    <cfRule type="duplicateValues" dxfId="907" priority="1212"/>
+    <cfRule type="duplicateValues" dxfId="895" priority="1212"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B738">
-    <cfRule type="duplicateValues" dxfId="906" priority="1210"/>
+    <cfRule type="duplicateValues" dxfId="894" priority="1210"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B740">
-    <cfRule type="duplicateValues" dxfId="905" priority="1205"/>
+    <cfRule type="duplicateValues" dxfId="893" priority="1205"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B740">
-    <cfRule type="duplicateValues" dxfId="904" priority="1206"/>
+    <cfRule type="duplicateValues" dxfId="892" priority="1206"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B741">
-    <cfRule type="duplicateValues" dxfId="903" priority="1203"/>
+    <cfRule type="duplicateValues" dxfId="891" priority="1203"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B741">
-    <cfRule type="duplicateValues" dxfId="902" priority="1202"/>
+    <cfRule type="duplicateValues" dxfId="890" priority="1202"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B741">
-    <cfRule type="duplicateValues" dxfId="901" priority="1204"/>
+    <cfRule type="duplicateValues" dxfId="889" priority="1204"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B742">
-    <cfRule type="duplicateValues" dxfId="900" priority="1196"/>
+    <cfRule type="duplicateValues" dxfId="888" priority="1196"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B742">
-    <cfRule type="duplicateValues" dxfId="899" priority="1197"/>
+    <cfRule type="duplicateValues" dxfId="887" priority="1197"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B742">
-    <cfRule type="duplicateValues" dxfId="898" priority="1198"/>
+    <cfRule type="duplicateValues" dxfId="886" priority="1198"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B743">
-    <cfRule type="duplicateValues" dxfId="897" priority="1193"/>
+    <cfRule type="duplicateValues" dxfId="885" priority="1193"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B743">
-    <cfRule type="duplicateValues" dxfId="896" priority="1194"/>
+    <cfRule type="duplicateValues" dxfId="884" priority="1194"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B743">
-    <cfRule type="duplicateValues" dxfId="895" priority="1195"/>
+    <cfRule type="duplicateValues" dxfId="883" priority="1195"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B744">
-    <cfRule type="duplicateValues" dxfId="894" priority="1187"/>
+    <cfRule type="duplicateValues" dxfId="882" priority="1187"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B744">
-    <cfRule type="duplicateValues" dxfId="893" priority="1188"/>
+    <cfRule type="duplicateValues" dxfId="881" priority="1188"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B744">
-    <cfRule type="duplicateValues" dxfId="892" priority="1189"/>
+    <cfRule type="duplicateValues" dxfId="880" priority="1189"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B745">
-    <cfRule type="duplicateValues" dxfId="891" priority="1172"/>
+    <cfRule type="duplicateValues" dxfId="879" priority="1172"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B745">
-    <cfRule type="duplicateValues" dxfId="890" priority="1173"/>
+    <cfRule type="duplicateValues" dxfId="878" priority="1173"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B745">
-    <cfRule type="duplicateValues" dxfId="889" priority="1174"/>
+    <cfRule type="duplicateValues" dxfId="877" priority="1174"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B746">
-    <cfRule type="duplicateValues" dxfId="888" priority="1166"/>
+    <cfRule type="duplicateValues" dxfId="876" priority="1166"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B746">
-    <cfRule type="duplicateValues" dxfId="887" priority="1167"/>
+    <cfRule type="duplicateValues" dxfId="875" priority="1167"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B746">
-    <cfRule type="duplicateValues" dxfId="886" priority="1168"/>
+    <cfRule type="duplicateValues" dxfId="874" priority="1168"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B747">
-    <cfRule type="duplicateValues" dxfId="885" priority="1160"/>
+    <cfRule type="duplicateValues" dxfId="873" priority="1160"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B747">
-    <cfRule type="duplicateValues" dxfId="884" priority="1161"/>
+    <cfRule type="duplicateValues" dxfId="872" priority="1161"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B747">
-    <cfRule type="duplicateValues" dxfId="883" priority="1162"/>
+    <cfRule type="duplicateValues" dxfId="871" priority="1162"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B748">
-    <cfRule type="duplicateValues" dxfId="882" priority="1158"/>
+    <cfRule type="duplicateValues" dxfId="870" priority="1158"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B748">
-    <cfRule type="duplicateValues" dxfId="881" priority="1159"/>
+    <cfRule type="duplicateValues" dxfId="869" priority="1159"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B748">
-    <cfRule type="duplicateValues" dxfId="880" priority="1157"/>
+    <cfRule type="duplicateValues" dxfId="868" priority="1157"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B749">
-    <cfRule type="duplicateValues" dxfId="879" priority="1148"/>
+    <cfRule type="duplicateValues" dxfId="867" priority="1148"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B749">
-    <cfRule type="duplicateValues" dxfId="878" priority="1149"/>
+    <cfRule type="duplicateValues" dxfId="866" priority="1149"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B749">
-    <cfRule type="duplicateValues" dxfId="877" priority="1150"/>
+    <cfRule type="duplicateValues" dxfId="865" priority="1150"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B750">
-    <cfRule type="duplicateValues" dxfId="876" priority="1140"/>
+    <cfRule type="duplicateValues" dxfId="864" priority="1140"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B750">
-    <cfRule type="duplicateValues" dxfId="875" priority="1139"/>
+    <cfRule type="duplicateValues" dxfId="863" priority="1139"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B750">
-    <cfRule type="duplicateValues" dxfId="874" priority="1141"/>
+    <cfRule type="duplicateValues" dxfId="862" priority="1141"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B751">
-    <cfRule type="duplicateValues" dxfId="873" priority="1137"/>
+    <cfRule type="duplicateValues" dxfId="861" priority="1137"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B751">
-    <cfRule type="duplicateValues" dxfId="872" priority="1136"/>
+    <cfRule type="duplicateValues" dxfId="860" priority="1136"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B751">
-    <cfRule type="duplicateValues" dxfId="871" priority="1138"/>
+    <cfRule type="duplicateValues" dxfId="859" priority="1138"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B752">
-    <cfRule type="duplicateValues" dxfId="870" priority="1131"/>
+    <cfRule type="duplicateValues" dxfId="858" priority="1131"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B752">
-    <cfRule type="duplicateValues" dxfId="869" priority="1132"/>
+    <cfRule type="duplicateValues" dxfId="857" priority="1132"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B752">
-    <cfRule type="duplicateValues" dxfId="868" priority="1130"/>
+    <cfRule type="duplicateValues" dxfId="856" priority="1130"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B753">
-    <cfRule type="duplicateValues" dxfId="867" priority="1124"/>
+    <cfRule type="duplicateValues" dxfId="855" priority="1124"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B753">
-    <cfRule type="duplicateValues" dxfId="866" priority="1125"/>
+    <cfRule type="duplicateValues" dxfId="854" priority="1125"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B753">
-    <cfRule type="duplicateValues" dxfId="865" priority="1126"/>
+    <cfRule type="duplicateValues" dxfId="853" priority="1126"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B754">
-    <cfRule type="duplicateValues" dxfId="864" priority="1121"/>
+    <cfRule type="duplicateValues" dxfId="852" priority="1121"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B754">
-    <cfRule type="duplicateValues" dxfId="863" priority="1122"/>
+    <cfRule type="duplicateValues" dxfId="851" priority="1122"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B754">
-    <cfRule type="duplicateValues" dxfId="862" priority="1123"/>
+    <cfRule type="duplicateValues" dxfId="850" priority="1123"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B756">
-    <cfRule type="duplicateValues" dxfId="861" priority="1118"/>
+    <cfRule type="duplicateValues" dxfId="849" priority="1118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B756">
-    <cfRule type="duplicateValues" dxfId="860" priority="1119"/>
+    <cfRule type="duplicateValues" dxfId="848" priority="1119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B756">
-    <cfRule type="duplicateValues" dxfId="859" priority="1120"/>
+    <cfRule type="duplicateValues" dxfId="847" priority="1120"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B757">
-    <cfRule type="duplicateValues" dxfId="858" priority="1115"/>
+    <cfRule type="duplicateValues" dxfId="846" priority="1115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B757">
-    <cfRule type="duplicateValues" dxfId="857" priority="1116"/>
+    <cfRule type="duplicateValues" dxfId="845" priority="1116"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B757">
-    <cfRule type="duplicateValues" dxfId="856" priority="1117"/>
+    <cfRule type="duplicateValues" dxfId="844" priority="1117"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B759">
-    <cfRule type="duplicateValues" dxfId="855" priority="1114"/>
+    <cfRule type="duplicateValues" dxfId="843" priority="1114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B759">
-    <cfRule type="duplicateValues" dxfId="854" priority="1113"/>
+    <cfRule type="duplicateValues" dxfId="842" priority="1113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B759">
-    <cfRule type="duplicateValues" dxfId="853" priority="1112"/>
+    <cfRule type="duplicateValues" dxfId="841" priority="1112"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B760">
-    <cfRule type="duplicateValues" dxfId="852" priority="1109"/>
+    <cfRule type="duplicateValues" dxfId="840" priority="1109"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B760">
-    <cfRule type="duplicateValues" dxfId="851" priority="1110"/>
+    <cfRule type="duplicateValues" dxfId="839" priority="1110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B760">
-    <cfRule type="duplicateValues" dxfId="850" priority="1111"/>
+    <cfRule type="duplicateValues" dxfId="838" priority="1111"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B761">
-    <cfRule type="duplicateValues" dxfId="849" priority="1106"/>
+    <cfRule type="duplicateValues" dxfId="837" priority="1106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B761">
-    <cfRule type="duplicateValues" dxfId="848" priority="1107"/>
+    <cfRule type="duplicateValues" dxfId="836" priority="1107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B761">
-    <cfRule type="duplicateValues" dxfId="847" priority="1108"/>
+    <cfRule type="duplicateValues" dxfId="835" priority="1108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B764">
-    <cfRule type="duplicateValues" dxfId="846" priority="1104"/>
+    <cfRule type="duplicateValues" dxfId="834" priority="1104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B764">
-    <cfRule type="duplicateValues" dxfId="845" priority="1105"/>
+    <cfRule type="duplicateValues" dxfId="833" priority="1105"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B764">
-    <cfRule type="duplicateValues" dxfId="844" priority="1103"/>
+    <cfRule type="duplicateValues" dxfId="832" priority="1103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B762">
-    <cfRule type="duplicateValues" dxfId="843" priority="1101"/>
+    <cfRule type="duplicateValues" dxfId="831" priority="1101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B762">
-    <cfRule type="duplicateValues" dxfId="842" priority="1102"/>
+    <cfRule type="duplicateValues" dxfId="830" priority="1102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B763">
-    <cfRule type="duplicateValues" dxfId="841" priority="1096"/>
+    <cfRule type="duplicateValues" dxfId="829" priority="1096"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B763">
-    <cfRule type="duplicateValues" dxfId="840" priority="1097"/>
+    <cfRule type="duplicateValues" dxfId="828" priority="1097"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B765">
-    <cfRule type="duplicateValues" dxfId="839" priority="1091"/>
+    <cfRule type="duplicateValues" dxfId="827" priority="1091"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B765">
-    <cfRule type="duplicateValues" dxfId="838" priority="1092"/>
+    <cfRule type="duplicateValues" dxfId="826" priority="1092"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B765">
-    <cfRule type="duplicateValues" dxfId="837" priority="1090"/>
+    <cfRule type="duplicateValues" dxfId="825" priority="1090"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B767">
-    <cfRule type="duplicateValues" dxfId="836" priority="1087"/>
+    <cfRule type="duplicateValues" dxfId="824" priority="1087"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B767">
-    <cfRule type="duplicateValues" dxfId="835" priority="1088"/>
+    <cfRule type="duplicateValues" dxfId="823" priority="1088"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B767">
-    <cfRule type="duplicateValues" dxfId="834" priority="1089"/>
+    <cfRule type="duplicateValues" dxfId="822" priority="1089"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B770">
-    <cfRule type="duplicateValues" dxfId="833" priority="1084"/>
+    <cfRule type="duplicateValues" dxfId="821" priority="1084"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B770">
-    <cfRule type="duplicateValues" dxfId="832" priority="1085"/>
+    <cfRule type="duplicateValues" dxfId="820" priority="1085"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B770">
-    <cfRule type="duplicateValues" dxfId="831" priority="1086"/>
+    <cfRule type="duplicateValues" dxfId="819" priority="1086"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B771">
-    <cfRule type="duplicateValues" dxfId="830" priority="1081"/>
+    <cfRule type="duplicateValues" dxfId="818" priority="1081"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B771">
-    <cfRule type="duplicateValues" dxfId="829" priority="1082"/>
+    <cfRule type="duplicateValues" dxfId="817" priority="1082"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B771">
-    <cfRule type="duplicateValues" dxfId="828" priority="1083"/>
+    <cfRule type="duplicateValues" dxfId="816" priority="1083"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B772">
-    <cfRule type="duplicateValues" dxfId="827" priority="1078"/>
+    <cfRule type="duplicateValues" dxfId="815" priority="1078"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B772">
-    <cfRule type="duplicateValues" dxfId="826" priority="1079"/>
+    <cfRule type="duplicateValues" dxfId="814" priority="1079"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B772">
-    <cfRule type="duplicateValues" dxfId="825" priority="1080"/>
+    <cfRule type="duplicateValues" dxfId="813" priority="1080"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B773">
-    <cfRule type="duplicateValues" dxfId="824" priority="1066"/>
+    <cfRule type="duplicateValues" dxfId="812" priority="1066"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B773">
-    <cfRule type="duplicateValues" dxfId="823" priority="1067"/>
+    <cfRule type="duplicateValues" dxfId="811" priority="1067"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B773">
-    <cfRule type="duplicateValues" dxfId="822" priority="1068"/>
+    <cfRule type="duplicateValues" dxfId="810" priority="1068"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B774">
-    <cfRule type="duplicateValues" dxfId="821" priority="1061"/>
+    <cfRule type="duplicateValues" dxfId="809" priority="1061"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B774">
-    <cfRule type="duplicateValues" dxfId="820" priority="1062"/>
+    <cfRule type="duplicateValues" dxfId="808" priority="1062"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B777">
-    <cfRule type="duplicateValues" dxfId="819" priority="1055"/>
+    <cfRule type="duplicateValues" dxfId="807" priority="1055"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B777">
-    <cfRule type="duplicateValues" dxfId="818" priority="1056"/>
+    <cfRule type="duplicateValues" dxfId="806" priority="1056"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B777">
-    <cfRule type="duplicateValues" dxfId="817" priority="1057"/>
+    <cfRule type="duplicateValues" dxfId="805" priority="1057"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B778">
-    <cfRule type="duplicateValues" dxfId="816" priority="1049"/>
+    <cfRule type="duplicateValues" dxfId="804" priority="1049"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B778">
-    <cfRule type="duplicateValues" dxfId="815" priority="1050"/>
+    <cfRule type="duplicateValues" dxfId="803" priority="1050"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B778">
-    <cfRule type="duplicateValues" dxfId="814" priority="1051"/>
+    <cfRule type="duplicateValues" dxfId="802" priority="1051"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B779">
-    <cfRule type="duplicateValues" dxfId="813" priority="1046"/>
+    <cfRule type="duplicateValues" dxfId="801" priority="1046"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B779">
-    <cfRule type="duplicateValues" dxfId="812" priority="1047"/>
+    <cfRule type="duplicateValues" dxfId="800" priority="1047"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B779">
-    <cfRule type="duplicateValues" dxfId="811" priority="1048"/>
+    <cfRule type="duplicateValues" dxfId="799" priority="1048"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B780">
-    <cfRule type="duplicateValues" dxfId="810" priority="1040"/>
+    <cfRule type="duplicateValues" dxfId="798" priority="1040"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B780">
-    <cfRule type="duplicateValues" dxfId="809" priority="1041"/>
+    <cfRule type="duplicateValues" dxfId="797" priority="1041"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B780">
-    <cfRule type="duplicateValues" dxfId="808" priority="1042"/>
+    <cfRule type="duplicateValues" dxfId="796" priority="1042"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B784">
-    <cfRule type="duplicateValues" dxfId="807" priority="1031"/>
+    <cfRule type="duplicateValues" dxfId="795" priority="1031"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B784">
-    <cfRule type="duplicateValues" dxfId="806" priority="1032"/>
+    <cfRule type="duplicateValues" dxfId="794" priority="1032"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B784">
-    <cfRule type="duplicateValues" dxfId="805" priority="1033"/>
+    <cfRule type="duplicateValues" dxfId="793" priority="1033"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B785">
-    <cfRule type="duplicateValues" dxfId="804" priority="1028"/>
+    <cfRule type="duplicateValues" dxfId="792" priority="1028"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B785">
-    <cfRule type="duplicateValues" dxfId="803" priority="1029"/>
+    <cfRule type="duplicateValues" dxfId="791" priority="1029"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B785">
-    <cfRule type="duplicateValues" dxfId="802" priority="1030"/>
+    <cfRule type="duplicateValues" dxfId="790" priority="1030"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B786">
-    <cfRule type="duplicateValues" dxfId="801" priority="1022"/>
+    <cfRule type="duplicateValues" dxfId="789" priority="1022"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B786">
-    <cfRule type="duplicateValues" dxfId="800" priority="1023"/>
+    <cfRule type="duplicateValues" dxfId="788" priority="1023"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B786">
-    <cfRule type="duplicateValues" dxfId="799" priority="1024"/>
+    <cfRule type="duplicateValues" dxfId="787" priority="1024"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B787">
-    <cfRule type="duplicateValues" dxfId="798" priority="1013"/>
+    <cfRule type="duplicateValues" dxfId="786" priority="1013"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B787">
-    <cfRule type="duplicateValues" dxfId="797" priority="1014"/>
+    <cfRule type="duplicateValues" dxfId="785" priority="1014"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B787">
-    <cfRule type="duplicateValues" dxfId="796" priority="1015"/>
+    <cfRule type="duplicateValues" dxfId="784" priority="1015"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B788">
-    <cfRule type="duplicateValues" dxfId="795" priority="1010"/>
+    <cfRule type="duplicateValues" dxfId="783" priority="1010"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B788">
-    <cfRule type="duplicateValues" dxfId="794" priority="1011"/>
+    <cfRule type="duplicateValues" dxfId="782" priority="1011"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B788">
-    <cfRule type="duplicateValues" dxfId="793" priority="1012"/>
+    <cfRule type="duplicateValues" dxfId="781" priority="1012"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B789">
-    <cfRule type="duplicateValues" dxfId="792" priority="1004"/>
+    <cfRule type="duplicateValues" dxfId="780" priority="1004"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B789">
-    <cfRule type="duplicateValues" dxfId="791" priority="1005"/>
+    <cfRule type="duplicateValues" dxfId="779" priority="1005"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B789">
-    <cfRule type="duplicateValues" dxfId="790" priority="1006"/>
+    <cfRule type="duplicateValues" dxfId="778" priority="1006"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B790">
-    <cfRule type="duplicateValues" dxfId="789" priority="1002"/>
+    <cfRule type="duplicateValues" dxfId="777" priority="1002"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B790">
-    <cfRule type="duplicateValues" dxfId="788" priority="1003"/>
+    <cfRule type="duplicateValues" dxfId="776" priority="1003"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B790">
-    <cfRule type="duplicateValues" dxfId="787" priority="1001"/>
+    <cfRule type="duplicateValues" dxfId="775" priority="1001"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B791">
-    <cfRule type="duplicateValues" dxfId="786" priority="998"/>
+    <cfRule type="duplicateValues" dxfId="774" priority="998"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B791">
-    <cfRule type="duplicateValues" dxfId="785" priority="999"/>
+    <cfRule type="duplicateValues" dxfId="773" priority="999"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B791">
-    <cfRule type="duplicateValues" dxfId="784" priority="1000"/>
+    <cfRule type="duplicateValues" dxfId="772" priority="1000"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B792">
-    <cfRule type="duplicateValues" dxfId="783" priority="996"/>
+    <cfRule type="duplicateValues" dxfId="771" priority="996"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B792">
-    <cfRule type="duplicateValues" dxfId="782" priority="995"/>
+    <cfRule type="duplicateValues" dxfId="770" priority="995"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B792">
-    <cfRule type="duplicateValues" dxfId="781" priority="997"/>
+    <cfRule type="duplicateValues" dxfId="769" priority="997"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B793">
-    <cfRule type="duplicateValues" dxfId="780" priority="986"/>
+    <cfRule type="duplicateValues" dxfId="768" priority="986"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B793">
-    <cfRule type="duplicateValues" dxfId="779" priority="987"/>
+    <cfRule type="duplicateValues" dxfId="767" priority="987"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B793">
-    <cfRule type="duplicateValues" dxfId="778" priority="988"/>
+    <cfRule type="duplicateValues" dxfId="766" priority="988"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B794">
-    <cfRule type="duplicateValues" dxfId="777" priority="983"/>
+    <cfRule type="duplicateValues" dxfId="765" priority="983"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B794">
-    <cfRule type="duplicateValues" dxfId="776" priority="984"/>
+    <cfRule type="duplicateValues" dxfId="764" priority="984"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B794">
-    <cfRule type="duplicateValues" dxfId="775" priority="985"/>
+    <cfRule type="duplicateValues" dxfId="763" priority="985"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B795">
-    <cfRule type="duplicateValues" dxfId="774" priority="980"/>
+    <cfRule type="duplicateValues" dxfId="762" priority="980"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B795">
-    <cfRule type="duplicateValues" dxfId="773" priority="981"/>
+    <cfRule type="duplicateValues" dxfId="761" priority="981"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B795">
-    <cfRule type="duplicateValues" dxfId="772" priority="982"/>
+    <cfRule type="duplicateValues" dxfId="760" priority="982"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B796">
-    <cfRule type="duplicateValues" dxfId="771" priority="977"/>
+    <cfRule type="duplicateValues" dxfId="759" priority="977"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B796">
-    <cfRule type="duplicateValues" dxfId="770" priority="978"/>
+    <cfRule type="duplicateValues" dxfId="758" priority="978"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B796">
-    <cfRule type="duplicateValues" dxfId="769" priority="979"/>
+    <cfRule type="duplicateValues" dxfId="757" priority="979"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B797">
-    <cfRule type="duplicateValues" dxfId="768" priority="974"/>
+    <cfRule type="duplicateValues" dxfId="756" priority="974"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B797">
-    <cfRule type="duplicateValues" dxfId="767" priority="975"/>
+    <cfRule type="duplicateValues" dxfId="755" priority="975"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B797">
-    <cfRule type="duplicateValues" dxfId="766" priority="976"/>
+    <cfRule type="duplicateValues" dxfId="754" priority="976"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B798">
-    <cfRule type="duplicateValues" dxfId="765" priority="971"/>
+    <cfRule type="duplicateValues" dxfId="753" priority="971"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B798">
-    <cfRule type="duplicateValues" dxfId="764" priority="972"/>
+    <cfRule type="duplicateValues" dxfId="752" priority="972"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B798">
-    <cfRule type="duplicateValues" dxfId="763" priority="973"/>
+    <cfRule type="duplicateValues" dxfId="751" priority="973"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B799">
-    <cfRule type="duplicateValues" dxfId="762" priority="965"/>
+    <cfRule type="duplicateValues" dxfId="750" priority="965"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B799">
-    <cfRule type="duplicateValues" dxfId="761" priority="966"/>
+    <cfRule type="duplicateValues" dxfId="749" priority="966"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B799">
-    <cfRule type="duplicateValues" dxfId="760" priority="967"/>
+    <cfRule type="duplicateValues" dxfId="748" priority="967"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B800">
-    <cfRule type="duplicateValues" dxfId="759" priority="962"/>
+    <cfRule type="duplicateValues" dxfId="747" priority="962"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B800">
-    <cfRule type="duplicateValues" dxfId="758" priority="963"/>
+    <cfRule type="duplicateValues" dxfId="746" priority="963"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B800">
-    <cfRule type="duplicateValues" dxfId="757" priority="964"/>
+    <cfRule type="duplicateValues" dxfId="745" priority="964"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B801">
-    <cfRule type="duplicateValues" dxfId="756" priority="954"/>
+    <cfRule type="duplicateValues" dxfId="744" priority="954"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B801">
-    <cfRule type="duplicateValues" dxfId="755" priority="955"/>
+    <cfRule type="duplicateValues" dxfId="743" priority="955"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B802">
-    <cfRule type="duplicateValues" dxfId="754" priority="949"/>
+    <cfRule type="duplicateValues" dxfId="742" priority="949"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B802">
-    <cfRule type="duplicateValues" dxfId="753" priority="950"/>
+    <cfRule type="duplicateValues" dxfId="741" priority="950"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B803">
-    <cfRule type="duplicateValues" dxfId="752" priority="947"/>
+    <cfRule type="duplicateValues" dxfId="740" priority="947"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B803">
-    <cfRule type="duplicateValues" dxfId="751" priority="946"/>
+    <cfRule type="duplicateValues" dxfId="739" priority="946"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B803">
-    <cfRule type="duplicateValues" dxfId="750" priority="948"/>
+    <cfRule type="duplicateValues" dxfId="738" priority="948"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B804">
-    <cfRule type="duplicateValues" dxfId="749" priority="937"/>
+    <cfRule type="duplicateValues" dxfId="737" priority="937"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B804">
-    <cfRule type="duplicateValues" dxfId="748" priority="938"/>
+    <cfRule type="duplicateValues" dxfId="736" priority="938"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B804">
-    <cfRule type="duplicateValues" dxfId="747" priority="939"/>
+    <cfRule type="duplicateValues" dxfId="735" priority="939"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B806">
-    <cfRule type="duplicateValues" dxfId="746" priority="934"/>
+    <cfRule type="duplicateValues" dxfId="734" priority="934"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B806">
-    <cfRule type="duplicateValues" dxfId="745" priority="935"/>
+    <cfRule type="duplicateValues" dxfId="733" priority="935"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B806">
-    <cfRule type="duplicateValues" dxfId="744" priority="936"/>
+    <cfRule type="duplicateValues" dxfId="732" priority="936"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B807">
-    <cfRule type="duplicateValues" dxfId="743" priority="931"/>
+    <cfRule type="duplicateValues" dxfId="731" priority="931"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B807">
-    <cfRule type="duplicateValues" dxfId="742" priority="932"/>
+    <cfRule type="duplicateValues" dxfId="730" priority="932"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B807">
-    <cfRule type="duplicateValues" dxfId="741" priority="933"/>
+    <cfRule type="duplicateValues" dxfId="729" priority="933"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B809">
-    <cfRule type="duplicateValues" dxfId="740" priority="928"/>
+    <cfRule type="duplicateValues" dxfId="728" priority="928"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B809">
-    <cfRule type="duplicateValues" dxfId="739" priority="929"/>
+    <cfRule type="duplicateValues" dxfId="727" priority="929"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B809">
-    <cfRule type="duplicateValues" dxfId="738" priority="930"/>
+    <cfRule type="duplicateValues" dxfId="726" priority="930"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B810">
-    <cfRule type="duplicateValues" dxfId="737" priority="926"/>
+    <cfRule type="duplicateValues" dxfId="725" priority="926"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B810">
-    <cfRule type="duplicateValues" dxfId="736" priority="927"/>
+    <cfRule type="duplicateValues" dxfId="724" priority="927"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B812">
-    <cfRule type="duplicateValues" dxfId="735" priority="918"/>
+    <cfRule type="duplicateValues" dxfId="723" priority="918"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B812">
-    <cfRule type="duplicateValues" dxfId="734" priority="917"/>
+    <cfRule type="duplicateValues" dxfId="722" priority="917"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B812">
-    <cfRule type="duplicateValues" dxfId="733" priority="919"/>
+    <cfRule type="duplicateValues" dxfId="721" priority="919"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B813">
-    <cfRule type="duplicateValues" dxfId="732" priority="911"/>
+    <cfRule type="duplicateValues" dxfId="720" priority="911"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B813">
-    <cfRule type="duplicateValues" dxfId="731" priority="912"/>
+    <cfRule type="duplicateValues" dxfId="719" priority="912"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B813">
-    <cfRule type="duplicateValues" dxfId="730" priority="913"/>
+    <cfRule type="duplicateValues" dxfId="718" priority="913"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B814">
-    <cfRule type="duplicateValues" dxfId="729" priority="908"/>
+    <cfRule type="duplicateValues" dxfId="717" priority="908"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B814">
-    <cfRule type="duplicateValues" dxfId="728" priority="909"/>
+    <cfRule type="duplicateValues" dxfId="716" priority="909"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B814">
-    <cfRule type="duplicateValues" dxfId="727" priority="910"/>
+    <cfRule type="duplicateValues" dxfId="715" priority="910"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B815">
-    <cfRule type="duplicateValues" dxfId="726" priority="905"/>
+    <cfRule type="duplicateValues" dxfId="714" priority="905"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B815">
-    <cfRule type="duplicateValues" dxfId="725" priority="906"/>
+    <cfRule type="duplicateValues" dxfId="713" priority="906"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B815">
-    <cfRule type="duplicateValues" dxfId="724" priority="907"/>
+    <cfRule type="duplicateValues" dxfId="712" priority="907"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B816">
-    <cfRule type="duplicateValues" dxfId="723" priority="902"/>
+    <cfRule type="duplicateValues" dxfId="711" priority="902"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B816">
-    <cfRule type="duplicateValues" dxfId="722" priority="903"/>
+    <cfRule type="duplicateValues" dxfId="710" priority="903"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B816">
-    <cfRule type="duplicateValues" dxfId="721" priority="904"/>
+    <cfRule type="duplicateValues" dxfId="709" priority="904"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B817">
-    <cfRule type="duplicateValues" dxfId="720" priority="899"/>
+    <cfRule type="duplicateValues" dxfId="708" priority="899"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B817">
-    <cfRule type="duplicateValues" dxfId="719" priority="900"/>
+    <cfRule type="duplicateValues" dxfId="707" priority="900"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B817">
-    <cfRule type="duplicateValues" dxfId="718" priority="901"/>
+    <cfRule type="duplicateValues" dxfId="706" priority="901"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B818">
-    <cfRule type="duplicateValues" dxfId="717" priority="896"/>
+    <cfRule type="duplicateValues" dxfId="705" priority="896"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B818">
-    <cfRule type="duplicateValues" dxfId="716" priority="897"/>
+    <cfRule type="duplicateValues" dxfId="704" priority="897"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B818">
-    <cfRule type="duplicateValues" dxfId="715" priority="898"/>
+    <cfRule type="duplicateValues" dxfId="703" priority="898"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B819">
-    <cfRule type="duplicateValues" dxfId="714" priority="890"/>
+    <cfRule type="duplicateValues" dxfId="702" priority="890"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B819">
-    <cfRule type="duplicateValues" dxfId="713" priority="891"/>
+    <cfRule type="duplicateValues" dxfId="701" priority="891"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B819">
-    <cfRule type="duplicateValues" dxfId="712" priority="892"/>
+    <cfRule type="duplicateValues" dxfId="700" priority="892"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B820">
-    <cfRule type="duplicateValues" dxfId="711" priority="887"/>
+    <cfRule type="duplicateValues" dxfId="699" priority="887"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B820">
-    <cfRule type="duplicateValues" dxfId="710" priority="888"/>
+    <cfRule type="duplicateValues" dxfId="698" priority="888"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B820">
-    <cfRule type="duplicateValues" dxfId="709" priority="889"/>
+    <cfRule type="duplicateValues" dxfId="697" priority="889"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B821">
-    <cfRule type="duplicateValues" dxfId="708" priority="884"/>
+    <cfRule type="duplicateValues" dxfId="696" priority="884"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B821">
-    <cfRule type="duplicateValues" dxfId="707" priority="885"/>
+    <cfRule type="duplicateValues" dxfId="695" priority="885"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B821">
-    <cfRule type="duplicateValues" dxfId="706" priority="886"/>
+    <cfRule type="duplicateValues" dxfId="694" priority="886"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B822">
-    <cfRule type="duplicateValues" dxfId="705" priority="882"/>
+    <cfRule type="duplicateValues" dxfId="693" priority="882"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B822">
-    <cfRule type="duplicateValues" dxfId="704" priority="883"/>
+    <cfRule type="duplicateValues" dxfId="692" priority="883"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B823">
-    <cfRule type="duplicateValues" dxfId="703" priority="879"/>
+    <cfRule type="duplicateValues" dxfId="691" priority="879"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B823">
-    <cfRule type="duplicateValues" dxfId="702" priority="880"/>
+    <cfRule type="duplicateValues" dxfId="690" priority="880"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B823">
-    <cfRule type="duplicateValues" dxfId="701" priority="881"/>
+    <cfRule type="duplicateValues" dxfId="689" priority="881"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B828">
-    <cfRule type="duplicateValues" dxfId="700" priority="876"/>
+    <cfRule type="duplicateValues" dxfId="688" priority="876"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B828">
-    <cfRule type="duplicateValues" dxfId="699" priority="877"/>
+    <cfRule type="duplicateValues" dxfId="687" priority="877"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B828">
-    <cfRule type="duplicateValues" dxfId="698" priority="878"/>
+    <cfRule type="duplicateValues" dxfId="686" priority="878"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B829">
-    <cfRule type="duplicateValues" dxfId="697" priority="867"/>
+    <cfRule type="duplicateValues" dxfId="685" priority="867"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B829">
-    <cfRule type="duplicateValues" dxfId="696" priority="868"/>
+    <cfRule type="duplicateValues" dxfId="684" priority="868"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B829">
-    <cfRule type="duplicateValues" dxfId="695" priority="869"/>
+    <cfRule type="duplicateValues" dxfId="683" priority="869"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B830">
-    <cfRule type="duplicateValues" dxfId="694" priority="864"/>
+    <cfRule type="duplicateValues" dxfId="682" priority="864"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B830">
-    <cfRule type="duplicateValues" dxfId="693" priority="865"/>
+    <cfRule type="duplicateValues" dxfId="681" priority="865"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B830">
-    <cfRule type="duplicateValues" dxfId="692" priority="866"/>
+    <cfRule type="duplicateValues" dxfId="680" priority="866"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B831">
-    <cfRule type="duplicateValues" dxfId="691" priority="861"/>
+    <cfRule type="duplicateValues" dxfId="679" priority="861"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B831">
-    <cfRule type="duplicateValues" dxfId="690" priority="862"/>
+    <cfRule type="duplicateValues" dxfId="678" priority="862"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B831">
-    <cfRule type="duplicateValues" dxfId="689" priority="863"/>
+    <cfRule type="duplicateValues" dxfId="677" priority="863"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B832">
-    <cfRule type="duplicateValues" dxfId="688" priority="858"/>
+    <cfRule type="duplicateValues" dxfId="676" priority="858"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B832">
-    <cfRule type="duplicateValues" dxfId="687" priority="859"/>
+    <cfRule type="duplicateValues" dxfId="675" priority="859"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B832">
-    <cfRule type="duplicateValues" dxfId="686" priority="860"/>
+    <cfRule type="duplicateValues" dxfId="674" priority="860"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B833">
-    <cfRule type="duplicateValues" dxfId="685" priority="855"/>
+    <cfRule type="duplicateValues" dxfId="673" priority="855"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B833">
-    <cfRule type="duplicateValues" dxfId="684" priority="856"/>
+    <cfRule type="duplicateValues" dxfId="672" priority="856"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B833">
-    <cfRule type="duplicateValues" dxfId="683" priority="857"/>
+    <cfRule type="duplicateValues" dxfId="671" priority="857"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B834">
-    <cfRule type="duplicateValues" dxfId="682" priority="853"/>
+    <cfRule type="duplicateValues" dxfId="670" priority="853"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B834">
-    <cfRule type="duplicateValues" dxfId="681" priority="852"/>
+    <cfRule type="duplicateValues" dxfId="669" priority="852"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B834">
-    <cfRule type="duplicateValues" dxfId="680" priority="854"/>
+    <cfRule type="duplicateValues" dxfId="668" priority="854"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B835">
-    <cfRule type="duplicateValues" dxfId="679" priority="849"/>
+    <cfRule type="duplicateValues" dxfId="667" priority="849"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B835">
-    <cfRule type="duplicateValues" dxfId="678" priority="850"/>
+    <cfRule type="duplicateValues" dxfId="666" priority="850"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B835">
-    <cfRule type="duplicateValues" dxfId="677" priority="851"/>
+    <cfRule type="duplicateValues" dxfId="665" priority="851"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B836">
-    <cfRule type="duplicateValues" dxfId="676" priority="846"/>
+    <cfRule type="duplicateValues" dxfId="664" priority="846"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B836">
-    <cfRule type="duplicateValues" dxfId="675" priority="847"/>
+    <cfRule type="duplicateValues" dxfId="663" priority="847"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B836">
-    <cfRule type="duplicateValues" dxfId="674" priority="848"/>
+    <cfRule type="duplicateValues" dxfId="662" priority="848"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B837">
-    <cfRule type="duplicateValues" dxfId="673" priority="840"/>
+    <cfRule type="duplicateValues" dxfId="661" priority="840"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B837">
-    <cfRule type="duplicateValues" dxfId="672" priority="841"/>
+    <cfRule type="duplicateValues" dxfId="660" priority="841"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B837">
-    <cfRule type="duplicateValues" dxfId="671" priority="842"/>
+    <cfRule type="duplicateValues" dxfId="659" priority="842"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B839">
-    <cfRule type="duplicateValues" dxfId="670" priority="837"/>
+    <cfRule type="duplicateValues" dxfId="658" priority="837"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B839">
-    <cfRule type="duplicateValues" dxfId="669" priority="838"/>
+    <cfRule type="duplicateValues" dxfId="657" priority="838"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B839">
-    <cfRule type="duplicateValues" dxfId="668" priority="839"/>
+    <cfRule type="duplicateValues" dxfId="656" priority="839"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B841">
-    <cfRule type="duplicateValues" dxfId="667" priority="834"/>
+    <cfRule type="duplicateValues" dxfId="655" priority="834"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B841">
-    <cfRule type="duplicateValues" dxfId="666" priority="835"/>
+    <cfRule type="duplicateValues" dxfId="654" priority="835"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B841">
-    <cfRule type="duplicateValues" dxfId="665" priority="836"/>
+    <cfRule type="duplicateValues" dxfId="653" priority="836"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B844">
-    <cfRule type="duplicateValues" dxfId="664" priority="831"/>
+    <cfRule type="duplicateValues" dxfId="652" priority="831"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B844">
-    <cfRule type="duplicateValues" dxfId="663" priority="832"/>
+    <cfRule type="duplicateValues" dxfId="651" priority="832"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B844">
-    <cfRule type="duplicateValues" dxfId="662" priority="833"/>
+    <cfRule type="duplicateValues" dxfId="650" priority="833"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B845">
-    <cfRule type="duplicateValues" dxfId="661" priority="828"/>
+    <cfRule type="duplicateValues" dxfId="649" priority="828"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B845">
-    <cfRule type="duplicateValues" dxfId="660" priority="829"/>
+    <cfRule type="duplicateValues" dxfId="648" priority="829"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B845">
-    <cfRule type="duplicateValues" dxfId="659" priority="830"/>
+    <cfRule type="duplicateValues" dxfId="647" priority="830"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B846">
-    <cfRule type="duplicateValues" dxfId="658" priority="825"/>
+    <cfRule type="duplicateValues" dxfId="646" priority="825"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B846">
-    <cfRule type="duplicateValues" dxfId="657" priority="826"/>
+    <cfRule type="duplicateValues" dxfId="645" priority="826"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B846">
-    <cfRule type="duplicateValues" dxfId="656" priority="827"/>
+    <cfRule type="duplicateValues" dxfId="644" priority="827"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B848">
-    <cfRule type="duplicateValues" dxfId="655" priority="819"/>
+    <cfRule type="duplicateValues" dxfId="643" priority="819"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B848">
-    <cfRule type="duplicateValues" dxfId="654" priority="820"/>
+    <cfRule type="duplicateValues" dxfId="642" priority="820"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B848">
-    <cfRule type="duplicateValues" dxfId="653" priority="821"/>
+    <cfRule type="duplicateValues" dxfId="641" priority="821"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B849">
-    <cfRule type="duplicateValues" dxfId="652" priority="813"/>
+    <cfRule type="duplicateValues" dxfId="640" priority="813"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B849">
-    <cfRule type="duplicateValues" dxfId="651" priority="814"/>
+    <cfRule type="duplicateValues" dxfId="639" priority="814"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B849">
-    <cfRule type="duplicateValues" dxfId="650" priority="815"/>
+    <cfRule type="duplicateValues" dxfId="638" priority="815"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B851">
-    <cfRule type="duplicateValues" dxfId="649" priority="810"/>
+    <cfRule type="duplicateValues" dxfId="637" priority="810"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B851">
-    <cfRule type="duplicateValues" dxfId="648" priority="811"/>
+    <cfRule type="duplicateValues" dxfId="636" priority="811"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B851">
-    <cfRule type="duplicateValues" dxfId="647" priority="812"/>
+    <cfRule type="duplicateValues" dxfId="635" priority="812"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B852">
-    <cfRule type="duplicateValues" dxfId="646" priority="801"/>
+    <cfRule type="duplicateValues" dxfId="634" priority="801"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B852">
-    <cfRule type="duplicateValues" dxfId="645" priority="802"/>
+    <cfRule type="duplicateValues" dxfId="633" priority="802"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B852">
-    <cfRule type="duplicateValues" dxfId="644" priority="803"/>
+    <cfRule type="duplicateValues" dxfId="632" priority="803"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B853">
-    <cfRule type="duplicateValues" dxfId="643" priority="795"/>
+    <cfRule type="duplicateValues" dxfId="631" priority="795"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B853">
-    <cfRule type="duplicateValues" dxfId="642" priority="796"/>
+    <cfRule type="duplicateValues" dxfId="630" priority="796"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B853">
-    <cfRule type="duplicateValues" dxfId="641" priority="797"/>
+    <cfRule type="duplicateValues" dxfId="629" priority="797"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B854">
-    <cfRule type="duplicateValues" dxfId="640" priority="792"/>
+    <cfRule type="duplicateValues" dxfId="628" priority="792"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B854">
-    <cfRule type="duplicateValues" dxfId="639" priority="793"/>
+    <cfRule type="duplicateValues" dxfId="627" priority="793"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B854">
-    <cfRule type="duplicateValues" dxfId="638" priority="794"/>
+    <cfRule type="duplicateValues" dxfId="626" priority="794"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B857">
-    <cfRule type="duplicateValues" dxfId="637" priority="789"/>
+    <cfRule type="duplicateValues" dxfId="625" priority="789"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B857">
-    <cfRule type="duplicateValues" dxfId="636" priority="790"/>
+    <cfRule type="duplicateValues" dxfId="624" priority="790"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B857">
-    <cfRule type="duplicateValues" dxfId="635" priority="791"/>
+    <cfRule type="duplicateValues" dxfId="623" priority="791"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B858">
-    <cfRule type="duplicateValues" dxfId="634" priority="786"/>
+    <cfRule type="duplicateValues" dxfId="622" priority="786"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B858">
-    <cfRule type="duplicateValues" dxfId="633" priority="787"/>
+    <cfRule type="duplicateValues" dxfId="621" priority="787"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B858">
-    <cfRule type="duplicateValues" dxfId="632" priority="788"/>
+    <cfRule type="duplicateValues" dxfId="620" priority="788"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B859">
-    <cfRule type="duplicateValues" dxfId="631" priority="783"/>
+    <cfRule type="duplicateValues" dxfId="619" priority="783"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B859">
-    <cfRule type="duplicateValues" dxfId="630" priority="784"/>
+    <cfRule type="duplicateValues" dxfId="618" priority="784"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B859">
-    <cfRule type="duplicateValues" dxfId="629" priority="785"/>
+    <cfRule type="duplicateValues" dxfId="617" priority="785"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B861">
-    <cfRule type="duplicateValues" dxfId="628" priority="780"/>
+    <cfRule type="duplicateValues" dxfId="616" priority="780"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B861">
-    <cfRule type="duplicateValues" dxfId="627" priority="779"/>
+    <cfRule type="duplicateValues" dxfId="615" priority="779"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B861">
-    <cfRule type="duplicateValues" dxfId="626" priority="778"/>
+    <cfRule type="duplicateValues" dxfId="614" priority="778"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B863">
-    <cfRule type="duplicateValues" dxfId="625" priority="769"/>
+    <cfRule type="duplicateValues" dxfId="613" priority="769"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B863">
-    <cfRule type="duplicateValues" dxfId="624" priority="770"/>
+    <cfRule type="duplicateValues" dxfId="612" priority="770"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B863">
-    <cfRule type="duplicateValues" dxfId="623" priority="771"/>
+    <cfRule type="duplicateValues" dxfId="611" priority="771"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B868">
-    <cfRule type="duplicateValues" dxfId="622" priority="758"/>
+    <cfRule type="duplicateValues" dxfId="610" priority="758"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B868">
-    <cfRule type="duplicateValues" dxfId="621" priority="759"/>
+    <cfRule type="duplicateValues" dxfId="609" priority="759"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B868">
-    <cfRule type="duplicateValues" dxfId="620" priority="760"/>
+    <cfRule type="duplicateValues" dxfId="608" priority="760"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B866">
-    <cfRule type="duplicateValues" dxfId="619" priority="755"/>
+    <cfRule type="duplicateValues" dxfId="607" priority="755"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B866">
-    <cfRule type="duplicateValues" dxfId="618" priority="756"/>
+    <cfRule type="duplicateValues" dxfId="606" priority="756"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B866">
-    <cfRule type="duplicateValues" dxfId="617" priority="757"/>
+    <cfRule type="duplicateValues" dxfId="605" priority="757"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B867">
-    <cfRule type="duplicateValues" dxfId="616" priority="752"/>
+    <cfRule type="duplicateValues" dxfId="604" priority="752"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B867">
-    <cfRule type="duplicateValues" dxfId="615" priority="753"/>
+    <cfRule type="duplicateValues" dxfId="603" priority="753"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B867">
-    <cfRule type="duplicateValues" dxfId="614" priority="754"/>
+    <cfRule type="duplicateValues" dxfId="602" priority="754"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B869">
-    <cfRule type="duplicateValues" dxfId="613" priority="750"/>
+    <cfRule type="duplicateValues" dxfId="601" priority="750"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B869">
-    <cfRule type="duplicateValues" dxfId="612" priority="749"/>
+    <cfRule type="duplicateValues" dxfId="600" priority="749"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B869">
-    <cfRule type="duplicateValues" dxfId="611" priority="751"/>
+    <cfRule type="duplicateValues" dxfId="599" priority="751"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B870">
-    <cfRule type="duplicateValues" dxfId="610" priority="743"/>
+    <cfRule type="duplicateValues" dxfId="598" priority="743"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B870">
-    <cfRule type="duplicateValues" dxfId="609" priority="744"/>
+    <cfRule type="duplicateValues" dxfId="597" priority="744"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B870">
-    <cfRule type="duplicateValues" dxfId="608" priority="745"/>
+    <cfRule type="duplicateValues" dxfId="596" priority="745"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B871">
-    <cfRule type="duplicateValues" dxfId="607" priority="737"/>
+    <cfRule type="duplicateValues" dxfId="595" priority="737"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B871">
-    <cfRule type="duplicateValues" dxfId="606" priority="738"/>
+    <cfRule type="duplicateValues" dxfId="594" priority="738"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B871">
-    <cfRule type="duplicateValues" dxfId="605" priority="739"/>
+    <cfRule type="duplicateValues" dxfId="593" priority="739"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B873">
-    <cfRule type="duplicateValues" dxfId="604" priority="734"/>
+    <cfRule type="duplicateValues" dxfId="592" priority="734"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B873">
-    <cfRule type="duplicateValues" dxfId="603" priority="735"/>
+    <cfRule type="duplicateValues" dxfId="591" priority="735"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B873">
-    <cfRule type="duplicateValues" dxfId="602" priority="736"/>
+    <cfRule type="duplicateValues" dxfId="590" priority="736"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B872">
-    <cfRule type="duplicateValues" dxfId="601" priority="728"/>
+    <cfRule type="duplicateValues" dxfId="589" priority="728"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B872">
-    <cfRule type="duplicateValues" dxfId="600" priority="729"/>
+    <cfRule type="duplicateValues" dxfId="588" priority="729"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B872">
-    <cfRule type="duplicateValues" dxfId="599" priority="730"/>
+    <cfRule type="duplicateValues" dxfId="587" priority="730"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B874">
-    <cfRule type="duplicateValues" dxfId="598" priority="722"/>
+    <cfRule type="duplicateValues" dxfId="586" priority="722"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B874">
-    <cfRule type="duplicateValues" dxfId="597" priority="723"/>
+    <cfRule type="duplicateValues" dxfId="585" priority="723"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B874">
-    <cfRule type="duplicateValues" dxfId="596" priority="724"/>
+    <cfRule type="duplicateValues" dxfId="584" priority="724"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B875">
-    <cfRule type="duplicateValues" dxfId="595" priority="719"/>
+    <cfRule type="duplicateValues" dxfId="583" priority="719"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B875">
-    <cfRule type="duplicateValues" dxfId="594" priority="720"/>
+    <cfRule type="duplicateValues" dxfId="582" priority="720"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B875">
-    <cfRule type="duplicateValues" dxfId="593" priority="721"/>
+    <cfRule type="duplicateValues" dxfId="581" priority="721"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B877">
-    <cfRule type="duplicateValues" dxfId="592" priority="716"/>
+    <cfRule type="duplicateValues" dxfId="580" priority="716"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B877">
-    <cfRule type="duplicateValues" dxfId="591" priority="717"/>
+    <cfRule type="duplicateValues" dxfId="579" priority="717"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B877">
-    <cfRule type="duplicateValues" dxfId="590" priority="718"/>
+    <cfRule type="duplicateValues" dxfId="578" priority="718"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B879">
-    <cfRule type="duplicateValues" dxfId="589" priority="713"/>
+    <cfRule type="duplicateValues" dxfId="577" priority="713"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B879">
-    <cfRule type="duplicateValues" dxfId="588" priority="714"/>
+    <cfRule type="duplicateValues" dxfId="576" priority="714"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B879">
-    <cfRule type="duplicateValues" dxfId="587" priority="715"/>
+    <cfRule type="duplicateValues" dxfId="575" priority="715"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B881">
-    <cfRule type="duplicateValues" dxfId="586" priority="710"/>
+    <cfRule type="duplicateValues" dxfId="574" priority="710"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B881">
-    <cfRule type="duplicateValues" dxfId="585" priority="711"/>
+    <cfRule type="duplicateValues" dxfId="573" priority="711"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B881">
-    <cfRule type="duplicateValues" dxfId="584" priority="712"/>
+    <cfRule type="duplicateValues" dxfId="572" priority="712"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B882">
-    <cfRule type="duplicateValues" dxfId="583" priority="708"/>
+    <cfRule type="duplicateValues" dxfId="571" priority="708"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B882">
-    <cfRule type="duplicateValues" dxfId="582" priority="707"/>
+    <cfRule type="duplicateValues" dxfId="570" priority="707"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B882">
-    <cfRule type="duplicateValues" dxfId="581" priority="709"/>
+    <cfRule type="duplicateValues" dxfId="569" priority="709"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B884">
-    <cfRule type="duplicateValues" dxfId="580" priority="704"/>
+    <cfRule type="duplicateValues" dxfId="568" priority="704"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B884">
-    <cfRule type="duplicateValues" dxfId="579" priority="705"/>
+    <cfRule type="duplicateValues" dxfId="567" priority="705"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B884">
-    <cfRule type="duplicateValues" dxfId="578" priority="706"/>
+    <cfRule type="duplicateValues" dxfId="566" priority="706"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B883">
-    <cfRule type="duplicateValues" dxfId="577" priority="701"/>
+    <cfRule type="duplicateValues" dxfId="565" priority="701"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B883">
-    <cfRule type="duplicateValues" dxfId="576" priority="702"/>
+    <cfRule type="duplicateValues" dxfId="564" priority="702"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B883">
-    <cfRule type="duplicateValues" dxfId="575" priority="703"/>
+    <cfRule type="duplicateValues" dxfId="563" priority="703"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B885">
-    <cfRule type="duplicateValues" dxfId="574" priority="698"/>
+    <cfRule type="duplicateValues" dxfId="562" priority="698"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B885">
-    <cfRule type="duplicateValues" dxfId="573" priority="699"/>
+    <cfRule type="duplicateValues" dxfId="561" priority="699"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B885">
-    <cfRule type="duplicateValues" dxfId="572" priority="700"/>
+    <cfRule type="duplicateValues" dxfId="560" priority="700"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B886">
-    <cfRule type="duplicateValues" dxfId="571" priority="695"/>
+    <cfRule type="duplicateValues" dxfId="559" priority="695"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B886">
-    <cfRule type="duplicateValues" dxfId="570" priority="696"/>
+    <cfRule type="duplicateValues" dxfId="558" priority="696"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B886">
-    <cfRule type="duplicateValues" dxfId="569" priority="697"/>
+    <cfRule type="duplicateValues" dxfId="557" priority="697"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B887">
-    <cfRule type="duplicateValues" dxfId="568" priority="689"/>
+    <cfRule type="duplicateValues" dxfId="556" priority="689"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B887">
-    <cfRule type="duplicateValues" dxfId="567" priority="690"/>
+    <cfRule type="duplicateValues" dxfId="555" priority="690"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B887">
-    <cfRule type="duplicateValues" dxfId="566" priority="691"/>
+    <cfRule type="duplicateValues" dxfId="554" priority="691"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B888">
-    <cfRule type="duplicateValues" dxfId="565" priority="683"/>
+    <cfRule type="duplicateValues" dxfId="553" priority="683"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B888">
-    <cfRule type="duplicateValues" dxfId="564" priority="684"/>
+    <cfRule type="duplicateValues" dxfId="552" priority="684"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B888">
-    <cfRule type="duplicateValues" dxfId="563" priority="685"/>
+    <cfRule type="duplicateValues" dxfId="551" priority="685"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B889">
-    <cfRule type="duplicateValues" dxfId="562" priority="680"/>
+    <cfRule type="duplicateValues" dxfId="550" priority="680"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B889">
-    <cfRule type="duplicateValues" dxfId="561" priority="681"/>
+    <cfRule type="duplicateValues" dxfId="549" priority="681"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B889">
-    <cfRule type="duplicateValues" dxfId="560" priority="682"/>
+    <cfRule type="duplicateValues" dxfId="548" priority="682"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B890">
-    <cfRule type="duplicateValues" dxfId="559" priority="671"/>
+    <cfRule type="duplicateValues" dxfId="547" priority="671"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B890">
-    <cfRule type="duplicateValues" dxfId="558" priority="672"/>
+    <cfRule type="duplicateValues" dxfId="546" priority="672"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B890">
-    <cfRule type="duplicateValues" dxfId="557" priority="673"/>
+    <cfRule type="duplicateValues" dxfId="545" priority="673"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B891">
-    <cfRule type="duplicateValues" dxfId="556" priority="668"/>
+    <cfRule type="duplicateValues" dxfId="544" priority="668"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B891">
-    <cfRule type="duplicateValues" dxfId="555" priority="669"/>
+    <cfRule type="duplicateValues" dxfId="543" priority="669"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B891">
-    <cfRule type="duplicateValues" dxfId="554" priority="670"/>
+    <cfRule type="duplicateValues" dxfId="542" priority="670"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B892">
-    <cfRule type="duplicateValues" dxfId="553" priority="667"/>
+    <cfRule type="duplicateValues" dxfId="541" priority="667"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B892">
-    <cfRule type="duplicateValues" dxfId="552" priority="666"/>
+    <cfRule type="duplicateValues" dxfId="540" priority="666"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B892">
-    <cfRule type="duplicateValues" dxfId="551" priority="665"/>
+    <cfRule type="duplicateValues" dxfId="539" priority="665"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B893">
-    <cfRule type="duplicateValues" dxfId="550" priority="656"/>
+    <cfRule type="duplicateValues" dxfId="538" priority="656"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B893">
-    <cfRule type="duplicateValues" dxfId="549" priority="657"/>
+    <cfRule type="duplicateValues" dxfId="537" priority="657"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B893">
-    <cfRule type="duplicateValues" dxfId="548" priority="658"/>
+    <cfRule type="duplicateValues" dxfId="536" priority="658"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B894">
-    <cfRule type="duplicateValues" dxfId="547" priority="647"/>
+    <cfRule type="duplicateValues" dxfId="535" priority="647"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B894">
-    <cfRule type="duplicateValues" dxfId="546" priority="648"/>
+    <cfRule type="duplicateValues" dxfId="534" priority="648"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B894">
-    <cfRule type="duplicateValues" dxfId="545" priority="649"/>
+    <cfRule type="duplicateValues" dxfId="533" priority="649"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B895">
-    <cfRule type="duplicateValues" dxfId="544" priority="644"/>
+    <cfRule type="duplicateValues" dxfId="532" priority="644"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B895">
-    <cfRule type="duplicateValues" dxfId="543" priority="645"/>
+    <cfRule type="duplicateValues" dxfId="531" priority="645"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B895">
-    <cfRule type="duplicateValues" dxfId="542" priority="646"/>
+    <cfRule type="duplicateValues" dxfId="530" priority="646"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B896">
-    <cfRule type="duplicateValues" dxfId="541" priority="642"/>
+    <cfRule type="duplicateValues" dxfId="529" priority="642"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B896">
-    <cfRule type="duplicateValues" dxfId="540" priority="641"/>
+    <cfRule type="duplicateValues" dxfId="528" priority="641"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B896">
-    <cfRule type="duplicateValues" dxfId="539" priority="643"/>
+    <cfRule type="duplicateValues" dxfId="527" priority="643"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B880">
-    <cfRule type="duplicateValues" dxfId="538" priority="638"/>
+    <cfRule type="duplicateValues" dxfId="526" priority="638"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B880">
-    <cfRule type="duplicateValues" dxfId="537" priority="639"/>
+    <cfRule type="duplicateValues" dxfId="525" priority="639"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B880">
-    <cfRule type="duplicateValues" dxfId="536" priority="640"/>
+    <cfRule type="duplicateValues" dxfId="524" priority="640"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B898">
-    <cfRule type="duplicateValues" dxfId="535" priority="633"/>
+    <cfRule type="duplicateValues" dxfId="523" priority="633"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B898">
-    <cfRule type="duplicateValues" dxfId="534" priority="632"/>
+    <cfRule type="duplicateValues" dxfId="522" priority="632"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B898">
-    <cfRule type="duplicateValues" dxfId="533" priority="634"/>
+    <cfRule type="duplicateValues" dxfId="521" priority="634"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B899">
-    <cfRule type="duplicateValues" dxfId="532" priority="629"/>
+    <cfRule type="duplicateValues" dxfId="520" priority="629"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B899">
-    <cfRule type="duplicateValues" dxfId="531" priority="630"/>
+    <cfRule type="duplicateValues" dxfId="519" priority="630"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B899">
-    <cfRule type="duplicateValues" dxfId="530" priority="631"/>
+    <cfRule type="duplicateValues" dxfId="518" priority="631"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B900">
-    <cfRule type="duplicateValues" dxfId="529" priority="620"/>
+    <cfRule type="duplicateValues" dxfId="517" priority="620"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B900">
-    <cfRule type="duplicateValues" dxfId="528" priority="621"/>
+    <cfRule type="duplicateValues" dxfId="516" priority="621"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B900">
-    <cfRule type="duplicateValues" dxfId="527" priority="622"/>
+    <cfRule type="duplicateValues" dxfId="515" priority="622"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B901">
-    <cfRule type="duplicateValues" dxfId="526" priority="617"/>
+    <cfRule type="duplicateValues" dxfId="514" priority="617"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B901">
-    <cfRule type="duplicateValues" dxfId="525" priority="618"/>
+    <cfRule type="duplicateValues" dxfId="513" priority="618"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B901">
-    <cfRule type="duplicateValues" dxfId="524" priority="619"/>
+    <cfRule type="duplicateValues" dxfId="512" priority="619"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B902">
-    <cfRule type="duplicateValues" dxfId="523" priority="612"/>
+    <cfRule type="duplicateValues" dxfId="511" priority="612"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B902">
-    <cfRule type="duplicateValues" dxfId="522" priority="613"/>
+    <cfRule type="duplicateValues" dxfId="510" priority="613"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B902">
-    <cfRule type="duplicateValues" dxfId="521" priority="614"/>
+    <cfRule type="duplicateValues" dxfId="509" priority="614"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B903">
-    <cfRule type="duplicateValues" dxfId="520" priority="609"/>
+    <cfRule type="duplicateValues" dxfId="508" priority="609"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B903">
-    <cfRule type="duplicateValues" dxfId="519" priority="610"/>
+    <cfRule type="duplicateValues" dxfId="507" priority="610"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B903">
-    <cfRule type="duplicateValues" dxfId="518" priority="611"/>
+    <cfRule type="duplicateValues" dxfId="506" priority="611"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B904">
-    <cfRule type="duplicateValues" dxfId="517" priority="603"/>
+    <cfRule type="duplicateValues" dxfId="505" priority="603"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B904">
-    <cfRule type="duplicateValues" dxfId="516" priority="604"/>
+    <cfRule type="duplicateValues" dxfId="504" priority="604"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B904">
-    <cfRule type="duplicateValues" dxfId="515" priority="605"/>
+    <cfRule type="duplicateValues" dxfId="503" priority="605"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B905">
-    <cfRule type="duplicateValues" dxfId="514" priority="597"/>
+    <cfRule type="duplicateValues" dxfId="502" priority="597"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B905">
-    <cfRule type="duplicateValues" dxfId="513" priority="598"/>
+    <cfRule type="duplicateValues" dxfId="501" priority="598"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B905">
-    <cfRule type="duplicateValues" dxfId="512" priority="599"/>
+    <cfRule type="duplicateValues" dxfId="500" priority="599"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B907">
-    <cfRule type="duplicateValues" dxfId="511" priority="594"/>
+    <cfRule type="duplicateValues" dxfId="499" priority="594"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B907">
-    <cfRule type="duplicateValues" dxfId="510" priority="595"/>
+    <cfRule type="duplicateValues" dxfId="498" priority="595"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B907">
-    <cfRule type="duplicateValues" dxfId="509" priority="596"/>
+    <cfRule type="duplicateValues" dxfId="497" priority="596"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B906">
-    <cfRule type="duplicateValues" dxfId="508" priority="591"/>
+    <cfRule type="duplicateValues" dxfId="496" priority="591"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B906">
-    <cfRule type="duplicateValues" dxfId="507" priority="592"/>
+    <cfRule type="duplicateValues" dxfId="495" priority="592"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B906">
-    <cfRule type="duplicateValues" dxfId="506" priority="593"/>
+    <cfRule type="duplicateValues" dxfId="494" priority="593"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B909">
-    <cfRule type="duplicateValues" dxfId="505" priority="588"/>
+    <cfRule type="duplicateValues" dxfId="493" priority="588"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B909">
-    <cfRule type="duplicateValues" dxfId="504" priority="589"/>
+    <cfRule type="duplicateValues" dxfId="492" priority="589"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B909">
-    <cfRule type="duplicateValues" dxfId="503" priority="590"/>
+    <cfRule type="duplicateValues" dxfId="491" priority="590"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B908">
-    <cfRule type="duplicateValues" dxfId="502" priority="585"/>
+    <cfRule type="duplicateValues" dxfId="490" priority="585"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B908">
-    <cfRule type="duplicateValues" dxfId="501" priority="586"/>
+    <cfRule type="duplicateValues" dxfId="489" priority="586"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B908">
-    <cfRule type="duplicateValues" dxfId="500" priority="587"/>
+    <cfRule type="duplicateValues" dxfId="488" priority="587"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B910">
-    <cfRule type="duplicateValues" dxfId="499" priority="576"/>
+    <cfRule type="duplicateValues" dxfId="487" priority="576"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B910">
-    <cfRule type="duplicateValues" dxfId="498" priority="577"/>
+    <cfRule type="duplicateValues" dxfId="486" priority="577"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B910">
-    <cfRule type="duplicateValues" dxfId="497" priority="578"/>
+    <cfRule type="duplicateValues" dxfId="485" priority="578"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B912">
-    <cfRule type="duplicateValues" dxfId="496" priority="573"/>
+    <cfRule type="duplicateValues" dxfId="484" priority="573"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B912">
-    <cfRule type="duplicateValues" dxfId="495" priority="574"/>
+    <cfRule type="duplicateValues" dxfId="483" priority="574"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B912">
-    <cfRule type="duplicateValues" dxfId="494" priority="575"/>
+    <cfRule type="duplicateValues" dxfId="482" priority="575"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B913">
-    <cfRule type="duplicateValues" dxfId="493" priority="570"/>
+    <cfRule type="duplicateValues" dxfId="481" priority="570"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B913">
-    <cfRule type="duplicateValues" dxfId="492" priority="571"/>
+    <cfRule type="duplicateValues" dxfId="480" priority="571"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B913">
-    <cfRule type="duplicateValues" dxfId="491" priority="572"/>
+    <cfRule type="duplicateValues" dxfId="479" priority="572"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B914">
-    <cfRule type="duplicateValues" dxfId="490" priority="567"/>
+    <cfRule type="duplicateValues" dxfId="478" priority="567"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B914">
-    <cfRule type="duplicateValues" dxfId="489" priority="568"/>
+    <cfRule type="duplicateValues" dxfId="477" priority="568"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B914">
-    <cfRule type="duplicateValues" dxfId="488" priority="569"/>
+    <cfRule type="duplicateValues" dxfId="476" priority="569"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B915">
-    <cfRule type="duplicateValues" dxfId="487" priority="561"/>
+    <cfRule type="duplicateValues" dxfId="475" priority="561"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B915">
-    <cfRule type="duplicateValues" dxfId="486" priority="562"/>
+    <cfRule type="duplicateValues" dxfId="474" priority="562"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B915">
-    <cfRule type="duplicateValues" dxfId="485" priority="563"/>
+    <cfRule type="duplicateValues" dxfId="473" priority="563"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B916">
-    <cfRule type="duplicateValues" dxfId="484" priority="558"/>
+    <cfRule type="duplicateValues" dxfId="472" priority="558"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B916">
-    <cfRule type="duplicateValues" dxfId="483" priority="559"/>
+    <cfRule type="duplicateValues" dxfId="471" priority="559"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B916">
-    <cfRule type="duplicateValues" dxfId="482" priority="560"/>
+    <cfRule type="duplicateValues" dxfId="470" priority="560"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B917">
-    <cfRule type="duplicateValues" dxfId="481" priority="556"/>
+    <cfRule type="duplicateValues" dxfId="469" priority="556"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B917">
-    <cfRule type="duplicateValues" dxfId="480" priority="557"/>
+    <cfRule type="duplicateValues" dxfId="468" priority="557"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B918">
-    <cfRule type="duplicateValues" dxfId="479" priority="553"/>
+    <cfRule type="duplicateValues" dxfId="467" priority="553"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B918">
-    <cfRule type="duplicateValues" dxfId="478" priority="554"/>
+    <cfRule type="duplicateValues" dxfId="466" priority="554"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B918">
-    <cfRule type="duplicateValues" dxfId="477" priority="555"/>
+    <cfRule type="duplicateValues" dxfId="465" priority="555"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B919">
-    <cfRule type="duplicateValues" dxfId="476" priority="550"/>
+    <cfRule type="duplicateValues" dxfId="464" priority="550"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B919">
-    <cfRule type="duplicateValues" dxfId="475" priority="551"/>
+    <cfRule type="duplicateValues" dxfId="463" priority="551"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B919">
-    <cfRule type="duplicateValues" dxfId="474" priority="552"/>
+    <cfRule type="duplicateValues" dxfId="462" priority="552"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B920">
-    <cfRule type="duplicateValues" dxfId="473" priority="541"/>
+    <cfRule type="duplicateValues" dxfId="461" priority="541"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B920">
-    <cfRule type="duplicateValues" dxfId="472" priority="542"/>
+    <cfRule type="duplicateValues" dxfId="460" priority="542"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B920">
-    <cfRule type="duplicateValues" dxfId="471" priority="543"/>
+    <cfRule type="duplicateValues" dxfId="459" priority="543"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B922">
-    <cfRule type="duplicateValues" dxfId="470" priority="540"/>
+    <cfRule type="duplicateValues" dxfId="458" priority="540"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B922">
-    <cfRule type="duplicateValues" dxfId="469" priority="539"/>
+    <cfRule type="duplicateValues" dxfId="457" priority="539"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B922">
-    <cfRule type="duplicateValues" dxfId="468" priority="538"/>
+    <cfRule type="duplicateValues" dxfId="456" priority="538"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B921">
-    <cfRule type="duplicateValues" dxfId="467" priority="529"/>
+    <cfRule type="duplicateValues" dxfId="455" priority="529"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B921">
-    <cfRule type="duplicateValues" dxfId="466" priority="530"/>
+    <cfRule type="duplicateValues" dxfId="454" priority="530"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B921">
-    <cfRule type="duplicateValues" dxfId="465" priority="531"/>
+    <cfRule type="duplicateValues" dxfId="453" priority="531"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B923">
-    <cfRule type="duplicateValues" dxfId="464" priority="526"/>
+    <cfRule type="duplicateValues" dxfId="452" priority="526"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B923">
-    <cfRule type="duplicateValues" dxfId="463" priority="527"/>
+    <cfRule type="duplicateValues" dxfId="451" priority="527"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B923">
-    <cfRule type="duplicateValues" dxfId="462" priority="528"/>
+    <cfRule type="duplicateValues" dxfId="450" priority="528"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B924">
-    <cfRule type="duplicateValues" dxfId="461" priority="520"/>
+    <cfRule type="duplicateValues" dxfId="449" priority="520"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B924">
-    <cfRule type="duplicateValues" dxfId="460" priority="521"/>
+    <cfRule type="duplicateValues" dxfId="448" priority="521"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B924">
-    <cfRule type="duplicateValues" dxfId="459" priority="522"/>
+    <cfRule type="duplicateValues" dxfId="447" priority="522"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B925">
-    <cfRule type="duplicateValues" dxfId="458" priority="511"/>
+    <cfRule type="duplicateValues" dxfId="446" priority="511"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B925">
-    <cfRule type="duplicateValues" dxfId="457" priority="512"/>
+    <cfRule type="duplicateValues" dxfId="445" priority="512"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B925">
-    <cfRule type="duplicateValues" dxfId="456" priority="513"/>
+    <cfRule type="duplicateValues" dxfId="444" priority="513"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B926">
-    <cfRule type="duplicateValues" dxfId="455" priority="508"/>
+    <cfRule type="duplicateValues" dxfId="443" priority="508"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B926">
-    <cfRule type="duplicateValues" dxfId="454" priority="509"/>
+    <cfRule type="duplicateValues" dxfId="442" priority="509"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B926">
-    <cfRule type="duplicateValues" dxfId="453" priority="510"/>
+    <cfRule type="duplicateValues" dxfId="441" priority="510"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B929">
-    <cfRule type="duplicateValues" dxfId="452" priority="505"/>
+    <cfRule type="duplicateValues" dxfId="440" priority="505"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B929">
-    <cfRule type="duplicateValues" dxfId="451" priority="506"/>
+    <cfRule type="duplicateValues" dxfId="439" priority="506"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B929">
-    <cfRule type="duplicateValues" dxfId="450" priority="507"/>
+    <cfRule type="duplicateValues" dxfId="438" priority="507"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B931">
-    <cfRule type="duplicateValues" dxfId="449" priority="502"/>
+    <cfRule type="duplicateValues" dxfId="437" priority="502"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B931">
-    <cfRule type="duplicateValues" dxfId="448" priority="503"/>
+    <cfRule type="duplicateValues" dxfId="436" priority="503"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B931">
-    <cfRule type="duplicateValues" dxfId="447" priority="504"/>
+    <cfRule type="duplicateValues" dxfId="435" priority="504"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B934">
-    <cfRule type="duplicateValues" dxfId="446" priority="499"/>
+    <cfRule type="duplicateValues" dxfId="434" priority="499"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B934">
-    <cfRule type="duplicateValues" dxfId="445" priority="500"/>
+    <cfRule type="duplicateValues" dxfId="433" priority="500"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B934">
-    <cfRule type="duplicateValues" dxfId="444" priority="501"/>
+    <cfRule type="duplicateValues" dxfId="432" priority="501"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B935">
-    <cfRule type="duplicateValues" dxfId="443" priority="493"/>
+    <cfRule type="duplicateValues" dxfId="431" priority="493"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B935">
-    <cfRule type="duplicateValues" dxfId="442" priority="494"/>
+    <cfRule type="duplicateValues" dxfId="430" priority="494"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B935">
-    <cfRule type="duplicateValues" dxfId="441" priority="495"/>
+    <cfRule type="duplicateValues" dxfId="429" priority="495"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B937">
-    <cfRule type="duplicateValues" dxfId="440" priority="490"/>
+    <cfRule type="duplicateValues" dxfId="428" priority="490"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B937">
-    <cfRule type="duplicateValues" dxfId="439" priority="491"/>
+    <cfRule type="duplicateValues" dxfId="427" priority="491"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B937">
-    <cfRule type="duplicateValues" dxfId="438" priority="492"/>
+    <cfRule type="duplicateValues" dxfId="426" priority="492"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B936">
-    <cfRule type="duplicateValues" dxfId="437" priority="484"/>
+    <cfRule type="duplicateValues" dxfId="425" priority="484"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B936">
-    <cfRule type="duplicateValues" dxfId="436" priority="485"/>
+    <cfRule type="duplicateValues" dxfId="424" priority="485"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B936">
-    <cfRule type="duplicateValues" dxfId="435" priority="486"/>
+    <cfRule type="duplicateValues" dxfId="423" priority="486"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B938">
-    <cfRule type="duplicateValues" dxfId="434" priority="478"/>
+    <cfRule type="duplicateValues" dxfId="422" priority="478"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B938">
-    <cfRule type="duplicateValues" dxfId="433" priority="479"/>
+    <cfRule type="duplicateValues" dxfId="421" priority="479"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B938">
-    <cfRule type="duplicateValues" dxfId="432" priority="480"/>
+    <cfRule type="duplicateValues" dxfId="420" priority="480"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B939">
-    <cfRule type="duplicateValues" dxfId="431" priority="472"/>
+    <cfRule type="duplicateValues" dxfId="419" priority="472"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B939">
-    <cfRule type="duplicateValues" dxfId="430" priority="473"/>
+    <cfRule type="duplicateValues" dxfId="418" priority="473"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B939">
-    <cfRule type="duplicateValues" dxfId="429" priority="474"/>
+    <cfRule type="duplicateValues" dxfId="417" priority="474"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B940">
-    <cfRule type="duplicateValues" dxfId="428" priority="463"/>
+    <cfRule type="duplicateValues" dxfId="416" priority="463"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B940">
-    <cfRule type="duplicateValues" dxfId="427" priority="464"/>
+    <cfRule type="duplicateValues" dxfId="415" priority="464"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B940">
-    <cfRule type="duplicateValues" dxfId="426" priority="465"/>
+    <cfRule type="duplicateValues" dxfId="414" priority="465"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B941">
-    <cfRule type="duplicateValues" dxfId="425" priority="458"/>
+    <cfRule type="duplicateValues" dxfId="413" priority="458"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B941">
-    <cfRule type="duplicateValues" dxfId="424" priority="457"/>
+    <cfRule type="duplicateValues" dxfId="412" priority="457"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B941">
-    <cfRule type="duplicateValues" dxfId="423" priority="459"/>
+    <cfRule type="duplicateValues" dxfId="411" priority="459"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B943">
-    <cfRule type="duplicateValues" dxfId="422" priority="448"/>
+    <cfRule type="duplicateValues" dxfId="410" priority="448"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B943">
-    <cfRule type="duplicateValues" dxfId="421" priority="449"/>
+    <cfRule type="duplicateValues" dxfId="409" priority="449"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B943">
-    <cfRule type="duplicateValues" dxfId="420" priority="450"/>
+    <cfRule type="duplicateValues" dxfId="408" priority="450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B944">
-    <cfRule type="duplicateValues" dxfId="419" priority="442"/>
+    <cfRule type="duplicateValues" dxfId="407" priority="442"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B944">
-    <cfRule type="duplicateValues" dxfId="418" priority="443"/>
+    <cfRule type="duplicateValues" dxfId="406" priority="443"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B944">
-    <cfRule type="duplicateValues" dxfId="417" priority="444"/>
+    <cfRule type="duplicateValues" dxfId="405" priority="444"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B945">
-    <cfRule type="duplicateValues" dxfId="416" priority="439"/>
+    <cfRule type="duplicateValues" dxfId="404" priority="439"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B945">
-    <cfRule type="duplicateValues" dxfId="415" priority="440"/>
+    <cfRule type="duplicateValues" dxfId="403" priority="440"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B945">
-    <cfRule type="duplicateValues" dxfId="414" priority="441"/>
+    <cfRule type="duplicateValues" dxfId="402" priority="441"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B946">
-    <cfRule type="duplicateValues" dxfId="413" priority="436"/>
+    <cfRule type="duplicateValues" dxfId="401" priority="436"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B946">
-    <cfRule type="duplicateValues" dxfId="412" priority="437"/>
+    <cfRule type="duplicateValues" dxfId="400" priority="437"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B946">
-    <cfRule type="duplicateValues" dxfId="411" priority="438"/>
+    <cfRule type="duplicateValues" dxfId="399" priority="438"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B947">
-    <cfRule type="duplicateValues" dxfId="410" priority="432"/>
+    <cfRule type="duplicateValues" dxfId="398" priority="432"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B947">
-    <cfRule type="duplicateValues" dxfId="409" priority="431"/>
+    <cfRule type="duplicateValues" dxfId="397" priority="431"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B947">
-    <cfRule type="duplicateValues" dxfId="408" priority="430"/>
+    <cfRule type="duplicateValues" dxfId="396" priority="430"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B948">
-    <cfRule type="duplicateValues" dxfId="407" priority="428"/>
+    <cfRule type="duplicateValues" dxfId="395" priority="428"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B948">
-    <cfRule type="duplicateValues" dxfId="406" priority="427"/>
+    <cfRule type="duplicateValues" dxfId="394" priority="427"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B948">
-    <cfRule type="duplicateValues" dxfId="405" priority="429"/>
+    <cfRule type="duplicateValues" dxfId="393" priority="429"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B949">
-    <cfRule type="duplicateValues" dxfId="404" priority="424"/>
+    <cfRule type="duplicateValues" dxfId="392" priority="424"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B949">
-    <cfRule type="duplicateValues" dxfId="403" priority="425"/>
+    <cfRule type="duplicateValues" dxfId="391" priority="425"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B949">
-    <cfRule type="duplicateValues" dxfId="402" priority="426"/>
+    <cfRule type="duplicateValues" dxfId="390" priority="426"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9">
-    <cfRule type="duplicateValues" dxfId="401" priority="421"/>
+    <cfRule type="duplicateValues" dxfId="389" priority="421"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9">
-    <cfRule type="duplicateValues" dxfId="400" priority="422"/>
+    <cfRule type="duplicateValues" dxfId="388" priority="422"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9">
-    <cfRule type="duplicateValues" dxfId="399" priority="423"/>
+    <cfRule type="duplicateValues" dxfId="387" priority="423"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10">
-    <cfRule type="duplicateValues" dxfId="398" priority="418"/>
+    <cfRule type="duplicateValues" dxfId="386" priority="418"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10">
-    <cfRule type="duplicateValues" dxfId="397" priority="419"/>
+    <cfRule type="duplicateValues" dxfId="385" priority="419"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10">
-    <cfRule type="duplicateValues" dxfId="396" priority="420"/>
+    <cfRule type="duplicateValues" dxfId="384" priority="420"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
-    <cfRule type="duplicateValues" dxfId="395" priority="415"/>
+    <cfRule type="duplicateValues" dxfId="383" priority="415"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
-    <cfRule type="duplicateValues" dxfId="394" priority="416"/>
+    <cfRule type="duplicateValues" dxfId="382" priority="416"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
-    <cfRule type="duplicateValues" dxfId="393" priority="417"/>
+    <cfRule type="duplicateValues" dxfId="381" priority="417"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="392" priority="412"/>
+    <cfRule type="duplicateValues" dxfId="380" priority="412"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="391" priority="413"/>
+    <cfRule type="duplicateValues" dxfId="379" priority="413"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="390" priority="414"/>
+    <cfRule type="duplicateValues" dxfId="378" priority="414"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20">
-    <cfRule type="duplicateValues" dxfId="389" priority="409"/>
+    <cfRule type="duplicateValues" dxfId="377" priority="409"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20">
-    <cfRule type="duplicateValues" dxfId="388" priority="410"/>
+    <cfRule type="duplicateValues" dxfId="376" priority="410"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20">
-    <cfRule type="duplicateValues" dxfId="387" priority="411"/>
+    <cfRule type="duplicateValues" dxfId="375" priority="411"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="duplicateValues" dxfId="386" priority="406"/>
+    <cfRule type="duplicateValues" dxfId="374" priority="406"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="duplicateValues" dxfId="385" priority="407"/>
+    <cfRule type="duplicateValues" dxfId="373" priority="407"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="duplicateValues" dxfId="384" priority="408"/>
+    <cfRule type="duplicateValues" dxfId="372" priority="408"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="duplicateValues" dxfId="383" priority="403"/>
+    <cfRule type="duplicateValues" dxfId="371" priority="403"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="duplicateValues" dxfId="382" priority="404"/>
+    <cfRule type="duplicateValues" dxfId="370" priority="404"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="duplicateValues" dxfId="381" priority="405"/>
+    <cfRule type="duplicateValues" dxfId="369" priority="405"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="duplicateValues" dxfId="380" priority="400"/>
+    <cfRule type="duplicateValues" dxfId="368" priority="400"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="duplicateValues" dxfId="379" priority="401"/>
+    <cfRule type="duplicateValues" dxfId="367" priority="401"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="duplicateValues" dxfId="378" priority="402"/>
+    <cfRule type="duplicateValues" dxfId="366" priority="402"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="377" priority="397"/>
+    <cfRule type="duplicateValues" dxfId="365" priority="397"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="376" priority="398"/>
+    <cfRule type="duplicateValues" dxfId="364" priority="398"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="375" priority="399"/>
+    <cfRule type="duplicateValues" dxfId="363" priority="399"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27">
-    <cfRule type="duplicateValues" dxfId="374" priority="394"/>
+    <cfRule type="duplicateValues" dxfId="362" priority="394"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27">
-    <cfRule type="duplicateValues" dxfId="373" priority="395"/>
+    <cfRule type="duplicateValues" dxfId="361" priority="395"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27">
-    <cfRule type="duplicateValues" dxfId="372" priority="396"/>
+    <cfRule type="duplicateValues" dxfId="360" priority="396"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28">
-    <cfRule type="duplicateValues" dxfId="371" priority="391"/>
+    <cfRule type="duplicateValues" dxfId="359" priority="391"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28">
-    <cfRule type="duplicateValues" dxfId="370" priority="392"/>
+    <cfRule type="duplicateValues" dxfId="358" priority="392"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28">
-    <cfRule type="duplicateValues" dxfId="369" priority="393"/>
+    <cfRule type="duplicateValues" dxfId="357" priority="393"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29">
-    <cfRule type="duplicateValues" dxfId="368" priority="388"/>
+    <cfRule type="duplicateValues" dxfId="356" priority="388"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29">
-    <cfRule type="duplicateValues" dxfId="367" priority="389"/>
+    <cfRule type="duplicateValues" dxfId="355" priority="389"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29">
-    <cfRule type="duplicateValues" dxfId="366" priority="390"/>
+    <cfRule type="duplicateValues" dxfId="354" priority="390"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="365" priority="385"/>
+    <cfRule type="duplicateValues" dxfId="353" priority="385"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="364" priority="386"/>
+    <cfRule type="duplicateValues" dxfId="352" priority="386"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="363" priority="387"/>
+    <cfRule type="duplicateValues" dxfId="351" priority="387"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="362" priority="382"/>
+    <cfRule type="duplicateValues" dxfId="350" priority="382"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="361" priority="383"/>
+    <cfRule type="duplicateValues" dxfId="349" priority="383"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="360" priority="384"/>
+    <cfRule type="duplicateValues" dxfId="348" priority="384"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="359" priority="379"/>
+    <cfRule type="duplicateValues" dxfId="347" priority="379"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="358" priority="380"/>
+    <cfRule type="duplicateValues" dxfId="346" priority="380"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="357" priority="381"/>
+    <cfRule type="duplicateValues" dxfId="345" priority="381"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="356" priority="376"/>
+    <cfRule type="duplicateValues" dxfId="344" priority="376"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="355" priority="377"/>
+    <cfRule type="duplicateValues" dxfId="343" priority="377"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="354" priority="378"/>
+    <cfRule type="duplicateValues" dxfId="342" priority="378"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="353" priority="373"/>
+    <cfRule type="duplicateValues" dxfId="341" priority="373"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="352" priority="374"/>
+    <cfRule type="duplicateValues" dxfId="340" priority="374"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="351" priority="375"/>
+    <cfRule type="duplicateValues" dxfId="339" priority="375"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="350" priority="370"/>
+    <cfRule type="duplicateValues" dxfId="338" priority="370"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="349" priority="371"/>
+    <cfRule type="duplicateValues" dxfId="337" priority="371"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="348" priority="372"/>
+    <cfRule type="duplicateValues" dxfId="336" priority="372"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="347" priority="367"/>
+    <cfRule type="duplicateValues" dxfId="335" priority="367"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="346" priority="368"/>
+    <cfRule type="duplicateValues" dxfId="334" priority="368"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="345" priority="369"/>
+    <cfRule type="duplicateValues" dxfId="333" priority="369"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="344" priority="364"/>
+    <cfRule type="duplicateValues" dxfId="332" priority="364"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="343" priority="365"/>
+    <cfRule type="duplicateValues" dxfId="331" priority="365"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="342" priority="366"/>
+    <cfRule type="duplicateValues" dxfId="330" priority="366"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="341" priority="361"/>
+    <cfRule type="duplicateValues" dxfId="329" priority="361"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="340" priority="362"/>
+    <cfRule type="duplicateValues" dxfId="328" priority="362"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="339" priority="363"/>
+    <cfRule type="duplicateValues" dxfId="327" priority="363"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47">
-    <cfRule type="duplicateValues" dxfId="338" priority="358"/>
+    <cfRule type="duplicateValues" dxfId="326" priority="358"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47">
-    <cfRule type="duplicateValues" dxfId="337" priority="359"/>
+    <cfRule type="duplicateValues" dxfId="325" priority="359"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47">
-    <cfRule type="duplicateValues" dxfId="336" priority="360"/>
+    <cfRule type="duplicateValues" dxfId="324" priority="360"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="335" priority="355"/>
+    <cfRule type="duplicateValues" dxfId="323" priority="355"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="334" priority="356"/>
+    <cfRule type="duplicateValues" dxfId="322" priority="356"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="333" priority="357"/>
+    <cfRule type="duplicateValues" dxfId="321" priority="357"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="332" priority="352"/>
+    <cfRule type="duplicateValues" dxfId="320" priority="352"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="331" priority="353"/>
+    <cfRule type="duplicateValues" dxfId="319" priority="353"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="330" priority="354"/>
+    <cfRule type="duplicateValues" dxfId="318" priority="354"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="329" priority="346"/>
+    <cfRule type="duplicateValues" dxfId="317" priority="346"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="328" priority="347"/>
+    <cfRule type="duplicateValues" dxfId="316" priority="347"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="327" priority="348"/>
+    <cfRule type="duplicateValues" dxfId="315" priority="348"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55">
-    <cfRule type="duplicateValues" dxfId="326" priority="343"/>
+    <cfRule type="duplicateValues" dxfId="314" priority="343"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55">
-    <cfRule type="duplicateValues" dxfId="325" priority="344"/>
+    <cfRule type="duplicateValues" dxfId="313" priority="344"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55">
-    <cfRule type="duplicateValues" dxfId="324" priority="345"/>
+    <cfRule type="duplicateValues" dxfId="312" priority="345"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="323" priority="340"/>
+    <cfRule type="duplicateValues" dxfId="311" priority="340"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="322" priority="341"/>
+    <cfRule type="duplicateValues" dxfId="310" priority="341"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="321" priority="342"/>
+    <cfRule type="duplicateValues" dxfId="309" priority="342"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B60">
-    <cfRule type="duplicateValues" dxfId="320" priority="337"/>
+    <cfRule type="duplicateValues" dxfId="308" priority="337"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B60">
-    <cfRule type="duplicateValues" dxfId="319" priority="338"/>
+    <cfRule type="duplicateValues" dxfId="307" priority="338"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B60">
-    <cfRule type="duplicateValues" dxfId="318" priority="339"/>
+    <cfRule type="duplicateValues" dxfId="306" priority="339"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B61">
-    <cfRule type="duplicateValues" dxfId="317" priority="334"/>
+    <cfRule type="duplicateValues" dxfId="305" priority="334"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B61">
-    <cfRule type="duplicateValues" dxfId="316" priority="335"/>
+    <cfRule type="duplicateValues" dxfId="304" priority="335"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B61">
-    <cfRule type="duplicateValues" dxfId="315" priority="336"/>
+    <cfRule type="duplicateValues" dxfId="303" priority="336"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B65">
-    <cfRule type="duplicateValues" dxfId="314" priority="331"/>
+    <cfRule type="duplicateValues" dxfId="302" priority="331"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B65">
-    <cfRule type="duplicateValues" dxfId="313" priority="332"/>
+    <cfRule type="duplicateValues" dxfId="301" priority="332"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B65">
-    <cfRule type="duplicateValues" dxfId="312" priority="333"/>
+    <cfRule type="duplicateValues" dxfId="300" priority="333"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B66">
-    <cfRule type="duplicateValues" dxfId="311" priority="328"/>
+    <cfRule type="duplicateValues" dxfId="299" priority="328"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B66">
-    <cfRule type="duplicateValues" dxfId="310" priority="329"/>
+    <cfRule type="duplicateValues" dxfId="298" priority="329"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B66">
-    <cfRule type="duplicateValues" dxfId="309" priority="330"/>
+    <cfRule type="duplicateValues" dxfId="297" priority="330"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="308" priority="325"/>
+    <cfRule type="duplicateValues" dxfId="296" priority="325"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="307" priority="326"/>
+    <cfRule type="duplicateValues" dxfId="295" priority="326"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="306" priority="327"/>
+    <cfRule type="duplicateValues" dxfId="294" priority="327"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68">
-    <cfRule type="duplicateValues" dxfId="305" priority="322"/>
+    <cfRule type="duplicateValues" dxfId="293" priority="322"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68">
-    <cfRule type="duplicateValues" dxfId="304" priority="323"/>
+    <cfRule type="duplicateValues" dxfId="292" priority="323"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68">
-    <cfRule type="duplicateValues" dxfId="303" priority="324"/>
+    <cfRule type="duplicateValues" dxfId="291" priority="324"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="302" priority="319"/>
+    <cfRule type="duplicateValues" dxfId="290" priority="319"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="301" priority="320"/>
+    <cfRule type="duplicateValues" dxfId="289" priority="320"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="300" priority="321"/>
+    <cfRule type="duplicateValues" dxfId="288" priority="321"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70">
-    <cfRule type="duplicateValues" dxfId="299" priority="313"/>
+    <cfRule type="duplicateValues" dxfId="287" priority="313"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70">
-    <cfRule type="duplicateValues" dxfId="298" priority="314"/>
+    <cfRule type="duplicateValues" dxfId="286" priority="314"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70">
-    <cfRule type="duplicateValues" dxfId="297" priority="315"/>
+    <cfRule type="duplicateValues" dxfId="285" priority="315"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="296" priority="310"/>
+    <cfRule type="duplicateValues" dxfId="284" priority="310"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="295" priority="311"/>
+    <cfRule type="duplicateValues" dxfId="283" priority="311"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="294" priority="312"/>
+    <cfRule type="duplicateValues" dxfId="282" priority="312"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72">
-    <cfRule type="duplicateValues" dxfId="293" priority="307"/>
+    <cfRule type="duplicateValues" dxfId="281" priority="307"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72">
-    <cfRule type="duplicateValues" dxfId="292" priority="308"/>
+    <cfRule type="duplicateValues" dxfId="280" priority="308"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72">
-    <cfRule type="duplicateValues" dxfId="291" priority="309"/>
+    <cfRule type="duplicateValues" dxfId="279" priority="309"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B73">
-    <cfRule type="duplicateValues" dxfId="290" priority="304"/>
+    <cfRule type="duplicateValues" dxfId="278" priority="304"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B73">
-    <cfRule type="duplicateValues" dxfId="289" priority="305"/>
+    <cfRule type="duplicateValues" dxfId="277" priority="305"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B73">
-    <cfRule type="duplicateValues" dxfId="288" priority="306"/>
+    <cfRule type="duplicateValues" dxfId="276" priority="306"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B95">
-    <cfRule type="duplicateValues" dxfId="287" priority="301"/>
+    <cfRule type="duplicateValues" dxfId="275" priority="301"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B95">
-    <cfRule type="duplicateValues" dxfId="286" priority="302"/>
+    <cfRule type="duplicateValues" dxfId="274" priority="302"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B95">
-    <cfRule type="duplicateValues" dxfId="285" priority="303"/>
+    <cfRule type="duplicateValues" dxfId="273" priority="303"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107">
-    <cfRule type="duplicateValues" dxfId="284" priority="298"/>
+    <cfRule type="duplicateValues" dxfId="272" priority="298"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107">
-    <cfRule type="duplicateValues" dxfId="283" priority="299"/>
+    <cfRule type="duplicateValues" dxfId="271" priority="299"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107">
-    <cfRule type="duplicateValues" dxfId="282" priority="300"/>
+    <cfRule type="duplicateValues" dxfId="270" priority="300"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112">
-    <cfRule type="duplicateValues" dxfId="281" priority="292"/>
+    <cfRule type="duplicateValues" dxfId="269" priority="292"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112">
-    <cfRule type="duplicateValues" dxfId="280" priority="293"/>
+    <cfRule type="duplicateValues" dxfId="268" priority="293"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112">
-    <cfRule type="duplicateValues" dxfId="279" priority="294"/>
+    <cfRule type="duplicateValues" dxfId="267" priority="294"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B113">
-    <cfRule type="duplicateValues" dxfId="278" priority="289"/>
+    <cfRule type="duplicateValues" dxfId="266" priority="289"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B113">
-    <cfRule type="duplicateValues" dxfId="277" priority="290"/>
+    <cfRule type="duplicateValues" dxfId="265" priority="290"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B113">
-    <cfRule type="duplicateValues" dxfId="276" priority="291"/>
+    <cfRule type="duplicateValues" dxfId="264" priority="291"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B120">
-    <cfRule type="duplicateValues" dxfId="275" priority="286"/>
+    <cfRule type="duplicateValues" dxfId="263" priority="286"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B120">
-    <cfRule type="duplicateValues" dxfId="274" priority="287"/>
+    <cfRule type="duplicateValues" dxfId="262" priority="287"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B120">
-    <cfRule type="duplicateValues" dxfId="273" priority="288"/>
+    <cfRule type="duplicateValues" dxfId="261" priority="288"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B121">
-    <cfRule type="duplicateValues" dxfId="272" priority="280"/>
+    <cfRule type="duplicateValues" dxfId="260" priority="280"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B121">
-    <cfRule type="duplicateValues" dxfId="271" priority="281"/>
+    <cfRule type="duplicateValues" dxfId="259" priority="281"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B121">
-    <cfRule type="duplicateValues" dxfId="270" priority="282"/>
+    <cfRule type="duplicateValues" dxfId="258" priority="282"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B123">
-    <cfRule type="duplicateValues" dxfId="269" priority="277"/>
+    <cfRule type="duplicateValues" dxfId="257" priority="277"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B123">
-    <cfRule type="duplicateValues" dxfId="268" priority="278"/>
+    <cfRule type="duplicateValues" dxfId="256" priority="278"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B123">
-    <cfRule type="duplicateValues" dxfId="267" priority="279"/>
+    <cfRule type="duplicateValues" dxfId="255" priority="279"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B127">
-    <cfRule type="duplicateValues" dxfId="266" priority="274"/>
+    <cfRule type="duplicateValues" dxfId="254" priority="274"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B127">
-    <cfRule type="duplicateValues" dxfId="265" priority="275"/>
+    <cfRule type="duplicateValues" dxfId="253" priority="275"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B127">
-    <cfRule type="duplicateValues" dxfId="264" priority="276"/>
+    <cfRule type="duplicateValues" dxfId="252" priority="276"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B153">
-    <cfRule type="duplicateValues" dxfId="263" priority="271"/>
+    <cfRule type="duplicateValues" dxfId="251" priority="271"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B153">
-    <cfRule type="duplicateValues" dxfId="262" priority="272"/>
+    <cfRule type="duplicateValues" dxfId="250" priority="272"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B153">
-    <cfRule type="duplicateValues" dxfId="261" priority="273"/>
+    <cfRule type="duplicateValues" dxfId="249" priority="273"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B155">
-    <cfRule type="duplicateValues" dxfId="260" priority="270"/>
+    <cfRule type="duplicateValues" dxfId="248" priority="270"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B156">
-    <cfRule type="duplicateValues" dxfId="259" priority="267"/>
+    <cfRule type="duplicateValues" dxfId="247" priority="267"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B156">
-    <cfRule type="duplicateValues" dxfId="258" priority="268"/>
+    <cfRule type="duplicateValues" dxfId="246" priority="268"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B156">
-    <cfRule type="duplicateValues" dxfId="257" priority="269"/>
+    <cfRule type="duplicateValues" dxfId="245" priority="269"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B158">
-    <cfRule type="duplicateValues" dxfId="256" priority="264"/>
+    <cfRule type="duplicateValues" dxfId="244" priority="264"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B158">
-    <cfRule type="duplicateValues" dxfId="255" priority="265"/>
+    <cfRule type="duplicateValues" dxfId="243" priority="265"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B158">
-    <cfRule type="duplicateValues" dxfId="254" priority="266"/>
+    <cfRule type="duplicateValues" dxfId="242" priority="266"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B165">
-    <cfRule type="duplicateValues" dxfId="253" priority="261"/>
+    <cfRule type="duplicateValues" dxfId="241" priority="261"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B165">
-    <cfRule type="duplicateValues" dxfId="252" priority="262"/>
+    <cfRule type="duplicateValues" dxfId="240" priority="262"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B165">
-    <cfRule type="duplicateValues" dxfId="251" priority="263"/>
+    <cfRule type="duplicateValues" dxfId="239" priority="263"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B168">
-    <cfRule type="duplicateValues" dxfId="250" priority="258"/>
+    <cfRule type="duplicateValues" dxfId="238" priority="258"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B168">
-    <cfRule type="duplicateValues" dxfId="249" priority="259"/>
+    <cfRule type="duplicateValues" dxfId="237" priority="259"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B168">
-    <cfRule type="duplicateValues" dxfId="248" priority="260"/>
+    <cfRule type="duplicateValues" dxfId="236" priority="260"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171">
-    <cfRule type="duplicateValues" dxfId="247" priority="255"/>
+    <cfRule type="duplicateValues" dxfId="235" priority="255"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171">
-    <cfRule type="duplicateValues" dxfId="246" priority="256"/>
+    <cfRule type="duplicateValues" dxfId="234" priority="256"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171">
-    <cfRule type="duplicateValues" dxfId="245" priority="257"/>
+    <cfRule type="duplicateValues" dxfId="233" priority="257"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B172">
-    <cfRule type="duplicateValues" dxfId="244" priority="249"/>
+    <cfRule type="duplicateValues" dxfId="232" priority="249"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B172">
-    <cfRule type="duplicateValues" dxfId="243" priority="250"/>
+    <cfRule type="duplicateValues" dxfId="231" priority="250"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B172">
-    <cfRule type="duplicateValues" dxfId="242" priority="251"/>
+    <cfRule type="duplicateValues" dxfId="230" priority="251"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B173">
-    <cfRule type="duplicateValues" dxfId="241" priority="246"/>
+    <cfRule type="duplicateValues" dxfId="229" priority="246"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B173">
-    <cfRule type="duplicateValues" dxfId="240" priority="247"/>
+    <cfRule type="duplicateValues" dxfId="228" priority="247"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B173">
-    <cfRule type="duplicateValues" dxfId="239" priority="248"/>
+    <cfRule type="duplicateValues" dxfId="227" priority="248"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B174">
-    <cfRule type="duplicateValues" dxfId="238" priority="243"/>
+    <cfRule type="duplicateValues" dxfId="226" priority="243"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B174">
-    <cfRule type="duplicateValues" dxfId="237" priority="244"/>
+    <cfRule type="duplicateValues" dxfId="225" priority="244"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B174">
-    <cfRule type="duplicateValues" dxfId="236" priority="245"/>
+    <cfRule type="duplicateValues" dxfId="224" priority="245"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B175">
-    <cfRule type="duplicateValues" dxfId="235" priority="240"/>
+    <cfRule type="duplicateValues" dxfId="223" priority="240"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B175">
-    <cfRule type="duplicateValues" dxfId="234" priority="241"/>
+    <cfRule type="duplicateValues" dxfId="222" priority="241"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B175">
-    <cfRule type="duplicateValues" dxfId="233" priority="242"/>
+    <cfRule type="duplicateValues" dxfId="221" priority="242"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B176">
-    <cfRule type="duplicateValues" dxfId="232" priority="237"/>
+    <cfRule type="duplicateValues" dxfId="220" priority="237"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B176">
-    <cfRule type="duplicateValues" dxfId="231" priority="238"/>
+    <cfRule type="duplicateValues" dxfId="219" priority="238"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B176">
-    <cfRule type="duplicateValues" dxfId="230" priority="239"/>
+    <cfRule type="duplicateValues" dxfId="218" priority="239"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B177">
-    <cfRule type="duplicateValues" dxfId="229" priority="234"/>
+    <cfRule type="duplicateValues" dxfId="217" priority="234"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B177">
-    <cfRule type="duplicateValues" dxfId="228" priority="235"/>
+    <cfRule type="duplicateValues" dxfId="216" priority="235"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B177">
-    <cfRule type="duplicateValues" dxfId="227" priority="236"/>
+    <cfRule type="duplicateValues" dxfId="215" priority="236"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B178">
-    <cfRule type="duplicateValues" dxfId="226" priority="231"/>
+    <cfRule type="duplicateValues" dxfId="214" priority="231"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B178">
-    <cfRule type="duplicateValues" dxfId="225" priority="232"/>
+    <cfRule type="duplicateValues" dxfId="213" priority="232"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B178">
-    <cfRule type="duplicateValues" dxfId="224" priority="233"/>
+    <cfRule type="duplicateValues" dxfId="212" priority="233"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B180">
-    <cfRule type="duplicateValues" dxfId="223" priority="228"/>
+    <cfRule type="duplicateValues" dxfId="211" priority="228"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B180">
-    <cfRule type="duplicateValues" dxfId="222" priority="229"/>
+    <cfRule type="duplicateValues" dxfId="210" priority="229"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B180">
-    <cfRule type="duplicateValues" dxfId="221" priority="230"/>
+    <cfRule type="duplicateValues" dxfId="209" priority="230"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B182">
-    <cfRule type="duplicateValues" dxfId="220" priority="225"/>
+    <cfRule type="duplicateValues" dxfId="208" priority="225"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B182">
-    <cfRule type="duplicateValues" dxfId="219" priority="226"/>
+    <cfRule type="duplicateValues" dxfId="207" priority="226"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B182">
-    <cfRule type="duplicateValues" dxfId="218" priority="227"/>
+    <cfRule type="duplicateValues" dxfId="206" priority="227"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B185">
-    <cfRule type="duplicateValues" dxfId="217" priority="222"/>
+    <cfRule type="duplicateValues" dxfId="205" priority="222"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B185">
-    <cfRule type="duplicateValues" dxfId="216" priority="223"/>
+    <cfRule type="duplicateValues" dxfId="204" priority="223"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B185">
-    <cfRule type="duplicateValues" dxfId="215" priority="224"/>
+    <cfRule type="duplicateValues" dxfId="203" priority="224"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B189">
-    <cfRule type="duplicateValues" dxfId="214" priority="219"/>
+    <cfRule type="duplicateValues" dxfId="202" priority="219"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B189">
-    <cfRule type="duplicateValues" dxfId="213" priority="220"/>
+    <cfRule type="duplicateValues" dxfId="201" priority="220"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B189">
-    <cfRule type="duplicateValues" dxfId="212" priority="221"/>
+    <cfRule type="duplicateValues" dxfId="200" priority="221"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B203">
-    <cfRule type="duplicateValues" dxfId="211" priority="216"/>
+    <cfRule type="duplicateValues" dxfId="199" priority="216"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B203">
-    <cfRule type="duplicateValues" dxfId="210" priority="217"/>
+    <cfRule type="duplicateValues" dxfId="198" priority="217"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B203">
-    <cfRule type="duplicateValues" dxfId="209" priority="218"/>
+    <cfRule type="duplicateValues" dxfId="197" priority="218"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B206">
-    <cfRule type="duplicateValues" dxfId="208" priority="213"/>
+    <cfRule type="duplicateValues" dxfId="196" priority="213"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B206">
-    <cfRule type="duplicateValues" dxfId="207" priority="214"/>
+    <cfRule type="duplicateValues" dxfId="195" priority="214"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B206">
-    <cfRule type="duplicateValues" dxfId="206" priority="215"/>
+    <cfRule type="duplicateValues" dxfId="194" priority="215"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B207">
-    <cfRule type="duplicateValues" dxfId="205" priority="210"/>
+    <cfRule type="duplicateValues" dxfId="193" priority="210"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B207">
-    <cfRule type="duplicateValues" dxfId="204" priority="211"/>
+    <cfRule type="duplicateValues" dxfId="192" priority="211"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B207">
-    <cfRule type="duplicateValues" dxfId="203" priority="212"/>
+    <cfRule type="duplicateValues" dxfId="191" priority="212"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B208">
-    <cfRule type="duplicateValues" dxfId="202" priority="204"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="204"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B208">
-    <cfRule type="duplicateValues" dxfId="201" priority="205"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="205"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B208">
-    <cfRule type="duplicateValues" dxfId="200" priority="206"/>
+    <cfRule type="duplicateValues" dxfId="188" priority="206"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B213">
-    <cfRule type="duplicateValues" dxfId="199" priority="201"/>
+    <cfRule type="duplicateValues" dxfId="187" priority="201"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B213">
-    <cfRule type="duplicateValues" dxfId="198" priority="202"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="202"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B213">
-    <cfRule type="duplicateValues" dxfId="197" priority="203"/>
+    <cfRule type="duplicateValues" dxfId="185" priority="203"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B215">
-    <cfRule type="duplicateValues" dxfId="196" priority="198"/>
+    <cfRule type="duplicateValues" dxfId="184" priority="198"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B215">
-    <cfRule type="duplicateValues" dxfId="195" priority="199"/>
+    <cfRule type="duplicateValues" dxfId="183" priority="199"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B215">
-    <cfRule type="duplicateValues" dxfId="194" priority="200"/>
+    <cfRule type="duplicateValues" dxfId="182" priority="200"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B218">
-    <cfRule type="duplicateValues" dxfId="193" priority="195"/>
+    <cfRule type="duplicateValues" dxfId="181" priority="195"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B218">
-    <cfRule type="duplicateValues" dxfId="192" priority="196"/>
+    <cfRule type="duplicateValues" dxfId="180" priority="196"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B218">
-    <cfRule type="duplicateValues" dxfId="191" priority="197"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="197"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B221">
-    <cfRule type="duplicateValues" dxfId="190" priority="192"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="192"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B221">
-    <cfRule type="duplicateValues" dxfId="189" priority="193"/>
+    <cfRule type="duplicateValues" dxfId="177" priority="193"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B221">
-    <cfRule type="duplicateValues" dxfId="188" priority="194"/>
+    <cfRule type="duplicateValues" dxfId="176" priority="194"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B230">
-    <cfRule type="duplicateValues" dxfId="187" priority="189"/>
+    <cfRule type="duplicateValues" dxfId="175" priority="189"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B230">
-    <cfRule type="duplicateValues" dxfId="186" priority="190"/>
+    <cfRule type="duplicateValues" dxfId="174" priority="190"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B230">
-    <cfRule type="duplicateValues" dxfId="185" priority="191"/>
+    <cfRule type="duplicateValues" dxfId="173" priority="191"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B234">
-    <cfRule type="duplicateValues" dxfId="184" priority="183"/>
+    <cfRule type="duplicateValues" dxfId="172" priority="183"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B234">
-    <cfRule type="duplicateValues" dxfId="183" priority="184"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="184"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B234">
-    <cfRule type="duplicateValues" dxfId="182" priority="185"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="185"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B233">
-    <cfRule type="duplicateValues" dxfId="181" priority="177"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="177"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B233">
-    <cfRule type="duplicateValues" dxfId="180" priority="178"/>
+    <cfRule type="duplicateValues" dxfId="168" priority="178"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B233">
-    <cfRule type="duplicateValues" dxfId="179" priority="179"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="179"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B236">
-    <cfRule type="duplicateValues" dxfId="178" priority="174"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="174"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B236">
-    <cfRule type="duplicateValues" dxfId="177" priority="175"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="175"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B236">
-    <cfRule type="duplicateValues" dxfId="176" priority="176"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="176"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B235">
-    <cfRule type="duplicateValues" dxfId="175" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="171"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B235">
-    <cfRule type="duplicateValues" dxfId="174" priority="172"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="172"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B235">
-    <cfRule type="duplicateValues" dxfId="173" priority="173"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="173"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B250">
-    <cfRule type="duplicateValues" dxfId="172" priority="168"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="168"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B250">
-    <cfRule type="duplicateValues" dxfId="171" priority="169"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="169"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B250">
-    <cfRule type="duplicateValues" dxfId="170" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="170"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B253">
-    <cfRule type="duplicateValues" dxfId="169" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="165"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B253">
-    <cfRule type="duplicateValues" dxfId="168" priority="166"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="166"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B253">
-    <cfRule type="duplicateValues" dxfId="167" priority="167"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="167"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B254">
-    <cfRule type="duplicateValues" dxfId="166" priority="162"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="162"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B254">
-    <cfRule type="duplicateValues" dxfId="165" priority="163"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="163"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B254">
-    <cfRule type="duplicateValues" dxfId="164" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="164"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B256">
-    <cfRule type="duplicateValues" dxfId="163" priority="159"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="159"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B256">
-    <cfRule type="duplicateValues" dxfId="162" priority="160"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="160"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B256">
-    <cfRule type="duplicateValues" dxfId="161" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="161"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B257">
-    <cfRule type="duplicateValues" dxfId="160" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="156"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B257">
-    <cfRule type="duplicateValues" dxfId="159" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="157"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B257">
-    <cfRule type="duplicateValues" dxfId="158" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="158"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B262">
-    <cfRule type="duplicateValues" dxfId="157" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="153"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B262">
-    <cfRule type="duplicateValues" dxfId="156" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="154"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B262">
-    <cfRule type="duplicateValues" dxfId="155" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="155"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B270">
-    <cfRule type="duplicateValues" dxfId="154" priority="150"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="150"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B270">
-    <cfRule type="duplicateValues" dxfId="153" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="151"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B270">
-    <cfRule type="duplicateValues" dxfId="152" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="152"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B272">
-    <cfRule type="duplicateValues" dxfId="151" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="148"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B272">
-    <cfRule type="duplicateValues" dxfId="150" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="147"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B272">
-    <cfRule type="duplicateValues" dxfId="149" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="149"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B280">
-    <cfRule type="duplicateValues" dxfId="148" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="144"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B280">
-    <cfRule type="duplicateValues" dxfId="147" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="145"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B280">
-    <cfRule type="duplicateValues" dxfId="146" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="146"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B284">
-    <cfRule type="duplicateValues" dxfId="145" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="139"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B284">
-    <cfRule type="duplicateValues" dxfId="144" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="138"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B284">
-    <cfRule type="duplicateValues" dxfId="143" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="140"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B285">
-    <cfRule type="duplicateValues" dxfId="142" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="135"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B285">
-    <cfRule type="duplicateValues" dxfId="141" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="136"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B285">
-    <cfRule type="duplicateValues" dxfId="140" priority="137"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="137"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B311">
-    <cfRule type="duplicateValues" dxfId="139" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="133"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B311">
-    <cfRule type="duplicateValues" dxfId="138" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="132"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B311">
-    <cfRule type="duplicateValues" dxfId="137" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="134"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B313">
-    <cfRule type="duplicateValues" dxfId="136" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="127"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B313">
-    <cfRule type="duplicateValues" dxfId="135" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="126"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B313">
-    <cfRule type="duplicateValues" dxfId="134" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="128"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B314">
-    <cfRule type="duplicateValues" dxfId="133" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="121"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B314">
-    <cfRule type="duplicateValues" dxfId="132" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="120"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B314">
-    <cfRule type="duplicateValues" dxfId="131" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="122"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B316">
-    <cfRule type="duplicateValues" dxfId="130" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="117"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B316">
-    <cfRule type="duplicateValues" dxfId="129" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B316">
-    <cfRule type="duplicateValues" dxfId="128" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B319">
-    <cfRule type="duplicateValues" dxfId="127" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B319">
-    <cfRule type="duplicateValues" dxfId="126" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B319">
-    <cfRule type="duplicateValues" dxfId="125" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="116"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B322">
-    <cfRule type="duplicateValues" dxfId="124" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="112"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B322">
-    <cfRule type="duplicateValues" dxfId="123" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="111"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B322">
-    <cfRule type="duplicateValues" dxfId="122" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B323">
-    <cfRule type="duplicateValues" dxfId="121" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="109"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B323">
-    <cfRule type="duplicateValues" dxfId="120" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B323">
-    <cfRule type="duplicateValues" dxfId="119" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B325">
-    <cfRule type="duplicateValues" dxfId="118" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="105"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B325">
-    <cfRule type="duplicateValues" dxfId="117" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B325">
-    <cfRule type="duplicateValues" dxfId="116" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B326">
-    <cfRule type="duplicateValues" dxfId="115" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B326">
-    <cfRule type="duplicateValues" dxfId="114" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B326">
-    <cfRule type="duplicateValues" dxfId="113" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B327">
-    <cfRule type="duplicateValues" dxfId="112" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="99"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B327">
-    <cfRule type="duplicateValues" dxfId="111" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B327">
-    <cfRule type="duplicateValues" dxfId="110" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B328">
-    <cfRule type="duplicateValues" dxfId="109" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B328">
-    <cfRule type="duplicateValues" dxfId="108" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="97"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B328">
-    <cfRule type="duplicateValues" dxfId="107" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="98"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B354">
-    <cfRule type="duplicateValues" dxfId="106" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="94"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B354">
-    <cfRule type="duplicateValues" dxfId="105" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="93"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B354">
-    <cfRule type="duplicateValues" dxfId="104" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="95"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B362">
-    <cfRule type="duplicateValues" dxfId="103" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B362">
-    <cfRule type="duplicateValues" dxfId="102" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="90"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B362">
-    <cfRule type="duplicateValues" dxfId="101" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="92"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B369">
-    <cfRule type="duplicateValues" dxfId="100" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B369">
-    <cfRule type="duplicateValues" dxfId="99" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B369">
-    <cfRule type="duplicateValues" dxfId="98" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="89"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B384">
-    <cfRule type="duplicateValues" dxfId="97" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B384">
-    <cfRule type="duplicateValues" dxfId="96" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B384">
-    <cfRule type="duplicateValues" dxfId="95" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B391">
-    <cfRule type="duplicateValues" dxfId="94" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B391">
-    <cfRule type="duplicateValues" dxfId="93" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B391">
-    <cfRule type="duplicateValues" dxfId="92" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B415">
-    <cfRule type="duplicateValues" dxfId="91" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B415">
-    <cfRule type="duplicateValues" dxfId="90" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B415">
-    <cfRule type="duplicateValues" dxfId="89" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B418">
-    <cfRule type="duplicateValues" dxfId="88" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B418">
-    <cfRule type="duplicateValues" dxfId="87" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B418">
-    <cfRule type="duplicateValues" dxfId="86" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B419">
-    <cfRule type="duplicateValues" dxfId="85" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B419">
-    <cfRule type="duplicateValues" dxfId="84" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B419">
-    <cfRule type="duplicateValues" dxfId="83" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B441">
-    <cfRule type="duplicateValues" dxfId="82" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B441">
-    <cfRule type="duplicateValues" dxfId="81" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B441">
-    <cfRule type="duplicateValues" dxfId="80" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B456">
-    <cfRule type="duplicateValues" dxfId="79" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B456">
-    <cfRule type="duplicateValues" dxfId="78" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B456">
-    <cfRule type="duplicateValues" dxfId="77" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B464">
-    <cfRule type="duplicateValues" dxfId="76" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B464">
-    <cfRule type="duplicateValues" dxfId="75" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B464">
-    <cfRule type="duplicateValues" dxfId="74" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B467">
-    <cfRule type="duplicateValues" dxfId="73" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B467">
-    <cfRule type="duplicateValues" dxfId="72" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B467">
-    <cfRule type="duplicateValues" dxfId="71" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B471">
-    <cfRule type="duplicateValues" dxfId="70" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B471">
-    <cfRule type="duplicateValues" dxfId="69" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B471">
-    <cfRule type="duplicateValues" dxfId="68" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B472">
-    <cfRule type="duplicateValues" dxfId="67" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B472">
-    <cfRule type="duplicateValues" dxfId="66" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B472">
-    <cfRule type="duplicateValues" dxfId="65" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B477">
-    <cfRule type="duplicateValues" dxfId="64" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B477">
-    <cfRule type="duplicateValues" dxfId="63" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B477">
-    <cfRule type="duplicateValues" dxfId="62" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B483">
-    <cfRule type="duplicateValues" dxfId="61" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B483">
-    <cfRule type="duplicateValues" dxfId="60" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B483">
-    <cfRule type="duplicateValues" dxfId="59" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B487">
-    <cfRule type="duplicateValues" dxfId="58" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B487">
-    <cfRule type="duplicateValues" dxfId="57" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B487">
-    <cfRule type="duplicateValues" dxfId="56" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B499">
-    <cfRule type="duplicateValues" dxfId="55" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B499">
-    <cfRule type="duplicateValues" dxfId="54" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B499">
-    <cfRule type="duplicateValues" dxfId="53" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B500">
-    <cfRule type="duplicateValues" dxfId="52" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B500">
-    <cfRule type="duplicateValues" dxfId="51" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B500">
-    <cfRule type="duplicateValues" dxfId="50" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B505">
-    <cfRule type="duplicateValues" dxfId="49" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B505">
-    <cfRule type="duplicateValues" dxfId="48" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B505">
-    <cfRule type="duplicateValues" dxfId="47" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B506">
-    <cfRule type="duplicateValues" dxfId="46" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B506">
-    <cfRule type="duplicateValues" dxfId="45" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B506">
-    <cfRule type="duplicateValues" dxfId="44" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B511">
-    <cfRule type="duplicateValues" dxfId="43" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B511">
-    <cfRule type="duplicateValues" dxfId="42" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B511">
-    <cfRule type="duplicateValues" dxfId="41" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B548">
-    <cfRule type="duplicateValues" dxfId="40" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B548">
-    <cfRule type="duplicateValues" dxfId="39" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B548">
-    <cfRule type="duplicateValues" dxfId="38" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B550">
-    <cfRule type="duplicateValues" dxfId="37" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B550">
-    <cfRule type="duplicateValues" dxfId="36" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B550">
-    <cfRule type="duplicateValues" dxfId="35" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B558">
-    <cfRule type="duplicateValues" dxfId="34" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B558">
-    <cfRule type="duplicateValues" dxfId="33" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B559">
-    <cfRule type="duplicateValues" dxfId="32" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B559">
-    <cfRule type="duplicateValues" dxfId="31" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B559">
-    <cfRule type="duplicateValues" dxfId="30" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B561">
-    <cfRule type="duplicateValues" dxfId="29" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B561">
-    <cfRule type="duplicateValues" dxfId="28" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B561">
-    <cfRule type="duplicateValues" dxfId="27" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B570">
-    <cfRule type="duplicateValues" dxfId="26" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B570">
-    <cfRule type="duplicateValues" dxfId="25" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B570">
-    <cfRule type="duplicateValues" dxfId="24" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B585">
-    <cfRule type="duplicateValues" dxfId="23" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B585">
-    <cfRule type="duplicateValues" dxfId="21" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B585">
-    <cfRule type="duplicateValues" dxfId="19" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B588">
-    <cfRule type="duplicateValues" dxfId="17" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B588">
-    <cfRule type="duplicateValues" dxfId="15" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B588">
-    <cfRule type="duplicateValues" dxfId="13" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B597">
-    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B597">
-    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B598">
-    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B598">
-    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B598">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B598">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Spanish Dictionary.xlsx
+++ b/Spanish Dictionary.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1929" uniqueCount="1920">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2019" uniqueCount="2010">
   <si>
     <t>Word / Expression</t>
   </si>
@@ -5388,9 +5388,6 @@
     <t>If you become a traitor</t>
   </si>
   <si>
-    <t>cee téh conbiérté-séh-nun-trais-yonéroh</t>
-  </si>
-  <si>
     <t>O le faltas a todo' tus valores</t>
   </si>
   <si>
@@ -5415,9 +5412,6 @@
     <t>There is no amount of money that will help you</t>
   </si>
   <si>
-    <t>noh ahyy dinéroh kéh ah te téh ayudéh</t>
-  </si>
-  <si>
     <t>Lo buscaban haciendo regates</t>
   </si>
   <si>
@@ -5442,9 +5436,6 @@
     <t>They never think about low-cut necklines</t>
   </si>
   <si>
-    <t>noh séh piénsah nuncah én los éscotés</t>
-  </si>
-  <si>
     <t>Solo money, nunca los pegotes</t>
   </si>
   <si>
@@ -5463,21 +5454,12 @@
     <t>Que botan los fajos pero de cincuenta</t>
   </si>
   <si>
-    <t>kéh botan los fakhos péroh dé cinquéntah</t>
-  </si>
-  <si>
     <t>Que botan los fajos de cien y de veinte</t>
   </si>
   <si>
-    <t xml:space="preserve">kéh botan los fakhos déh siéhn ee dé véintéh </t>
-  </si>
-  <si>
     <t>Que botan, que botan</t>
   </si>
   <si>
-    <t>kéh botan kéh botan</t>
-  </si>
-  <si>
     <t>Let them throw, let them throw</t>
   </si>
   <si>
@@ -5496,9 +5478,6 @@
     <t>She deserves everything she earns</t>
   </si>
   <si>
-    <t>éhyah sé méréséh todoh loh kéh ganéh</t>
-  </si>
-  <si>
     <t>No creo en gente que venga en tiempo y me lo mame</t>
   </si>
   <si>
@@ -5776,6 +5755,297 @@
   </si>
   <si>
     <t>lah guérrah lah-asémoh à-qual-kéirah</t>
+  </si>
+  <si>
+    <t>te enseño a hacerlo</t>
+  </si>
+  <si>
+    <t>té énsényoh ah asérlo</t>
+  </si>
+  <si>
+    <t>I teach you how to do it</t>
+  </si>
+  <si>
+    <t>le da pa'l pelo</t>
+  </si>
+  <si>
+    <t>lé dah pal péloh</t>
+  </si>
+  <si>
+    <t>gives him a hard time</t>
+  </si>
+  <si>
+    <t>El que habla</t>
+  </si>
+  <si>
+    <t>éhl kéh ablah</t>
+  </si>
+  <si>
+    <t>The one who speaks</t>
+  </si>
+  <si>
+    <t>le manda pa'l cielo</t>
+  </si>
+  <si>
+    <t>lé mandah pal ciélo</t>
+  </si>
+  <si>
+    <t>sends him to heaven</t>
+  </si>
+  <si>
+    <t>Obligado</t>
+  </si>
+  <si>
+    <t>obligadoh</t>
+  </si>
+  <si>
+    <t>Obligatory</t>
+  </si>
+  <si>
+    <t>es lo primero</t>
+  </si>
+  <si>
+    <t>és loh priméroh</t>
+  </si>
+  <si>
+    <t>it's the first thing</t>
+  </si>
+  <si>
+    <t>un traicionero</t>
+  </si>
+  <si>
+    <t>own-trais-yohnéroh</t>
+  </si>
+  <si>
+    <t>cee téh conbiérté-séh-nun-trais-yohnéroh</t>
+  </si>
+  <si>
+    <t>a traitor</t>
+  </si>
+  <si>
+    <t>O le faltas</t>
+  </si>
+  <si>
+    <t>oh léh faltas</t>
+  </si>
+  <si>
+    <t>Or you're missing it</t>
+  </si>
+  <si>
+    <t>tus valores</t>
+  </si>
+  <si>
+    <t>tus bahloréhs</t>
+  </si>
+  <si>
+    <t>your values</t>
+  </si>
+  <si>
+    <t>No hay dinero</t>
+  </si>
+  <si>
+    <t>noh ahyy dinéroh</t>
+  </si>
+  <si>
+    <t>there is no money</t>
+  </si>
+  <si>
+    <t>lo recupere</t>
+  </si>
+  <si>
+    <t>lo récupéréh</t>
+  </si>
+  <si>
+    <t>I got it back</t>
+  </si>
+  <si>
+    <t>a ti te ayude</t>
+  </si>
+  <si>
+    <t>noh ahyy dinéroh kéh ah tee téh ayudéh</t>
+  </si>
+  <si>
+    <t>ah tee téh ayudéh</t>
+  </si>
+  <si>
+    <t>I will help you</t>
+  </si>
+  <si>
+    <t>Lo buscaban</t>
+  </si>
+  <si>
+    <t>loh buscaban</t>
+  </si>
+  <si>
+    <t>They were looking for him</t>
+  </si>
+  <si>
+    <t>haciendo regates</t>
+  </si>
+  <si>
+    <t>ahsiéndoh régatés</t>
+  </si>
+  <si>
+    <t>doing dribbles</t>
+  </si>
+  <si>
+    <t>hasta que llegue al tope</t>
+  </si>
+  <si>
+    <t>astah kéh yégéh al topéh</t>
+  </si>
+  <si>
+    <t>until it reaches the top</t>
+  </si>
+  <si>
+    <t>nunca</t>
+  </si>
+  <si>
+    <t>never</t>
+  </si>
+  <si>
+    <t>noh séh piénsah nunkah én los éscotés</t>
+  </si>
+  <si>
+    <t>nunkah</t>
+  </si>
+  <si>
+    <t>los escotes</t>
+  </si>
+  <si>
+    <t>los éscotés</t>
+  </si>
+  <si>
+    <t>the necklines</t>
+  </si>
+  <si>
+    <t>se piensa</t>
+  </si>
+  <si>
+    <t>it is thought</t>
+  </si>
+  <si>
+    <t>séh piénsah</t>
+  </si>
+  <si>
+    <t>los pegotes</t>
+  </si>
+  <si>
+    <t>los pégotés</t>
+  </si>
+  <si>
+    <t>the sticky mess/substance</t>
+  </si>
+  <si>
+    <t>kéh bohtan kéh bohtan</t>
+  </si>
+  <si>
+    <t>kéh bohtan los fakhos péroh dé cinquéntah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kéh bohtan los fakhos déh siéhn ee dé véintéh </t>
+  </si>
+  <si>
+    <t>botan</t>
+  </si>
+  <si>
+    <t>bohtan</t>
+  </si>
+  <si>
+    <t>they throw away / toss</t>
+  </si>
+  <si>
+    <t>los fajos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">los fakhos </t>
+  </si>
+  <si>
+    <t>the bundles</t>
+  </si>
+  <si>
+    <t>cincuenta</t>
+  </si>
+  <si>
+    <t>cinquéntah</t>
+  </si>
+  <si>
+    <t>cien</t>
+  </si>
+  <si>
+    <t>siéhn</t>
+  </si>
+  <si>
+    <t>veinte</t>
+  </si>
+  <si>
+    <t>véintéh</t>
+  </si>
+  <si>
+    <t>Se busca</t>
+  </si>
+  <si>
+    <t>wanted / is being sought</t>
+  </si>
+  <si>
+    <t>séh buscah</t>
+  </si>
+  <si>
+    <t>Ella se merece</t>
+  </si>
+  <si>
+    <t>she deserves</t>
+  </si>
+  <si>
+    <t>todo lo que gane</t>
+  </si>
+  <si>
+    <t>todoh loh kéh ganéh</t>
+  </si>
+  <si>
+    <t>everything you win</t>
+  </si>
+  <si>
+    <t>éhyah sé méhréhséh</t>
+  </si>
+  <si>
+    <t>éhyah sé méhréhséh todoh loh kéh ganéh</t>
+  </si>
+  <si>
+    <t>No creo en gente</t>
+  </si>
+  <si>
+    <t>noh kréoh én khénté</t>
+  </si>
+  <si>
+    <t>I don't believe in people</t>
+  </si>
+  <si>
+    <t>que venga o no, no importa</t>
+  </si>
+  <si>
+    <t>kéh véngah oh noh noh importah</t>
+  </si>
+  <si>
+    <t>whether he/she comes or not, it doesn't matter</t>
+  </si>
+  <si>
+    <t>me lo mame</t>
+  </si>
+  <si>
+    <t>mé loh mamé</t>
+  </si>
+  <si>
+    <t>that I suck him off</t>
+  </si>
+  <si>
+    <t>No debo a ninguno</t>
+  </si>
+  <si>
+    <t>I don't owe anyone</t>
+  </si>
+  <si>
+    <t>noh déboh ah nengunoh</t>
   </si>
 </sst>
 </file>
@@ -5791,12 +6061,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -5811,13 +6087,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -22811,7 +23090,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:D652"/>
+  <dimension ref="B1:D683"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="1" customWidth="1"/>
@@ -29406,519 +29685,860 @@
     </row>
     <row r="606" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B606" s="1" t="s">
-        <v>1779</v>
+        <v>1913</v>
       </c>
       <c r="C606" s="1" t="s">
-        <v>1781</v>
-      </c>
-      <c r="D606" s="1" t="s">
-        <v>1780</v>
+        <v>1914</v>
+      </c>
+      <c r="D606" s="2" t="s">
+        <v>1915</v>
       </c>
     </row>
     <row r="607" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B607" s="1" t="s">
-        <v>1782</v>
+        <v>1779</v>
       </c>
       <c r="C607" s="1" t="s">
-        <v>1784</v>
+        <v>1781</v>
       </c>
       <c r="D607" s="1" t="s">
-        <v>1783</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="608" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B608" s="1" t="s">
-        <v>1786</v>
+        <v>1919</v>
       </c>
       <c r="C608" s="1" t="s">
-        <v>1787</v>
+        <v>1920</v>
       </c>
       <c r="D608" s="1" t="s">
-        <v>1785</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="609" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B609" s="1" t="s">
-        <v>1788</v>
+        <v>1916</v>
       </c>
       <c r="C609" s="1" t="s">
-        <v>1790</v>
+        <v>1917</v>
       </c>
       <c r="D609" s="1" t="s">
-        <v>1789</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="610" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B610" s="1" t="s">
-        <v>1791</v>
+        <v>1782</v>
       </c>
       <c r="C610" s="1" t="s">
-        <v>1793</v>
+        <v>1784</v>
       </c>
       <c r="D610" s="1" t="s">
-        <v>1792</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="611" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B611" s="1" t="s">
-        <v>1794</v>
+        <v>1922</v>
       </c>
       <c r="C611" s="1" t="s">
-        <v>1796</v>
+        <v>1923</v>
       </c>
       <c r="D611" s="1" t="s">
-        <v>1795</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="612" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B612" s="1" t="s">
-        <v>1797</v>
+        <v>1786</v>
       </c>
       <c r="C612" s="1" t="s">
-        <v>1799</v>
+        <v>1787</v>
       </c>
       <c r="D612" s="1" t="s">
-        <v>1798</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="613" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B613" s="1" t="s">
-        <v>1800</v>
+        <v>1925</v>
       </c>
       <c r="C613" s="1" t="s">
-        <v>1802</v>
+        <v>1926</v>
       </c>
       <c r="D613" s="1" t="s">
-        <v>1801</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="614" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B614" s="1" t="s">
-        <v>1803</v>
+        <v>1928</v>
       </c>
       <c r="C614" s="1" t="s">
-        <v>1805</v>
+        <v>1929</v>
       </c>
       <c r="D614" s="1" t="s">
-        <v>1804</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="615" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B615" s="1" t="s">
-        <v>1806</v>
+        <v>1788</v>
       </c>
       <c r="C615" s="1" t="s">
-        <v>1808</v>
+        <v>1933</v>
       </c>
       <c r="D615" s="1" t="s">
-        <v>1807</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="616" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B616" s="1" t="s">
-        <v>1809</v>
+        <v>1931</v>
       </c>
       <c r="C616" s="1" t="s">
-        <v>1811</v>
+        <v>1932</v>
       </c>
       <c r="D616" s="1" t="s">
-        <v>1810</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="617" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B617" s="1" t="s">
-        <v>1818</v>
+        <v>1790</v>
       </c>
       <c r="C617" s="1" t="s">
-        <v>1819</v>
+        <v>1792</v>
       </c>
       <c r="D617" s="1" t="s">
-        <v>1820</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="618" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B618" s="1" t="s">
-        <v>1814</v>
+        <v>1935</v>
       </c>
       <c r="C618" s="1" t="s">
-        <v>1815</v>
+        <v>1936</v>
       </c>
       <c r="D618" s="1" t="s">
-        <v>1813</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="619" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B619" s="1" t="s">
-        <v>1816</v>
+        <v>1938</v>
       </c>
       <c r="C619" s="1" t="s">
-        <v>1817</v>
+        <v>1939</v>
       </c>
       <c r="D619" s="1" t="s">
-        <v>1812</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="620" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B620" s="1" t="s">
-        <v>1821</v>
+        <v>1793</v>
       </c>
       <c r="C620" s="1" t="s">
-        <v>1823</v>
+        <v>1795</v>
       </c>
       <c r="D620" s="1" t="s">
-        <v>1822</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="621" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B621" s="1" t="s">
-        <v>1824</v>
+        <v>1941</v>
       </c>
       <c r="C621" s="1" t="s">
-        <v>1826</v>
+        <v>1942</v>
       </c>
       <c r="D621" s="1" t="s">
-        <v>1825</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="622" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B622" s="1" t="s">
-        <v>1827</v>
+        <v>1944</v>
       </c>
       <c r="C622" s="1" t="s">
-        <v>1828</v>
+        <v>1945</v>
       </c>
       <c r="D622" s="1" t="s">
-        <v>1829</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="623" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B623" s="1" t="s">
-        <v>1830</v>
+        <v>1796</v>
       </c>
       <c r="C623" s="1" t="s">
-        <v>1832</v>
+        <v>1948</v>
       </c>
       <c r="D623" s="1" t="s">
-        <v>1831</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="624" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B624" s="1" t="s">
-        <v>1833</v>
+        <v>1947</v>
       </c>
       <c r="C624" s="1" t="s">
-        <v>1835</v>
+        <v>1949</v>
       </c>
       <c r="D624" s="1" t="s">
-        <v>1834</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="625" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B625" s="1" t="s">
-        <v>1836</v>
+        <v>1798</v>
       </c>
       <c r="C625" s="1" t="s">
-        <v>1838</v>
+        <v>1800</v>
       </c>
       <c r="D625" s="1" t="s">
-        <v>1837</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="626" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B626" s="1" t="s">
-        <v>1839</v>
+        <v>1951</v>
       </c>
       <c r="C626" s="1" t="s">
-        <v>1841</v>
+        <v>1952</v>
       </c>
       <c r="D626" s="1" t="s">
-        <v>1840</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="627" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B627" s="1" t="s">
-        <v>1842</v>
+        <v>1954</v>
       </c>
       <c r="C627" s="1" t="s">
-        <v>1844</v>
+        <v>1955</v>
       </c>
       <c r="D627" s="1" t="s">
-        <v>1843</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="628" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B628" s="1" t="s">
-        <v>1845</v>
+        <v>1801</v>
       </c>
       <c r="C628" s="1" t="s">
-        <v>1847</v>
+        <v>1803</v>
       </c>
       <c r="D628" s="1" t="s">
-        <v>1846</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="629" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B629" s="1" t="s">
-        <v>1848</v>
+        <v>1957</v>
       </c>
       <c r="C629" s="1" t="s">
-        <v>1850</v>
+        <v>1958</v>
       </c>
       <c r="D629" s="1" t="s">
-        <v>1849</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="630" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B630" s="1" t="s">
-        <v>1851</v>
+        <v>1804</v>
       </c>
       <c r="C630" s="1" t="s">
-        <v>1853</v>
+        <v>1962</v>
       </c>
       <c r="D630" s="1" t="s">
-        <v>1852</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="631" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B631" s="1" t="s">
-        <v>1854</v>
+        <v>1967</v>
       </c>
       <c r="C631" s="1" t="s">
-        <v>1856</v>
+        <v>1969</v>
       </c>
       <c r="D631" s="1" t="s">
-        <v>1855</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="632" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B632" s="1" t="s">
-        <v>1857</v>
+        <v>1960</v>
       </c>
       <c r="C632" s="1" t="s">
-        <v>1859</v>
+        <v>1963</v>
       </c>
       <c r="D632" s="1" t="s">
-        <v>1858</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="633" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B633" s="1" t="s">
-        <v>1860</v>
+        <v>1964</v>
       </c>
       <c r="C633" s="1" t="s">
-        <v>1862</v>
+        <v>1965</v>
       </c>
       <c r="D633" s="1" t="s">
-        <v>1861</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="634" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B634" s="1" t="s">
-        <v>1863</v>
+        <v>1806</v>
       </c>
       <c r="C634" s="1" t="s">
-        <v>1865</v>
+        <v>1808</v>
       </c>
       <c r="D634" s="1" t="s">
-        <v>1864</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="635" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B635" s="1" t="s">
-        <v>1866</v>
+        <v>1970</v>
       </c>
       <c r="C635" s="1" t="s">
-        <v>1868</v>
+        <v>1971</v>
       </c>
       <c r="D635" s="1" t="s">
-        <v>1867</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="636" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B636" s="1" t="s">
-        <v>1869</v>
+        <v>1813</v>
       </c>
       <c r="C636" s="1" t="s">
-        <v>1871</v>
+        <v>1973</v>
       </c>
       <c r="D636" s="1" t="s">
-        <v>1870</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="637" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B637" s="1" t="s">
-        <v>1872</v>
+        <v>1976</v>
       </c>
       <c r="C637" s="1" t="s">
-        <v>1874</v>
+        <v>1977</v>
       </c>
       <c r="D637" s="1" t="s">
-        <v>1873</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="638" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B638" s="1" t="s">
-        <v>1875</v>
+        <v>1811</v>
       </c>
       <c r="C638" s="1" t="s">
-        <v>1877</v>
+        <v>1974</v>
       </c>
       <c r="D638" s="1" t="s">
-        <v>1876</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="639" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B639" s="1" t="s">
-        <v>1878</v>
+        <v>1979</v>
       </c>
       <c r="C639" s="1" t="s">
-        <v>1880</v>
+        <v>1980</v>
       </c>
       <c r="D639" s="1" t="s">
-        <v>1879</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="640" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B640" s="1" t="s">
-        <v>1881</v>
+        <v>1982</v>
       </c>
       <c r="C640" s="1" t="s">
-        <v>1883</v>
-      </c>
-      <c r="D640" s="1" t="s">
-        <v>1882</v>
+        <v>1983</v>
+      </c>
+      <c r="D640" s="1">
+        <v>50</v>
       </c>
     </row>
     <row r="641" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B641" s="1" t="s">
-        <v>1884</v>
+        <v>1812</v>
       </c>
       <c r="C641" s="1" t="s">
-        <v>1885</v>
+        <v>1975</v>
       </c>
       <c r="D641" s="1" t="s">
-        <v>1886</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="642" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B642" s="1" t="s">
-        <v>1887</v>
+        <v>1984</v>
       </c>
       <c r="C642" s="1" t="s">
-        <v>1889</v>
-      </c>
-      <c r="D642" s="1" t="s">
-        <v>1888</v>
+        <v>1985</v>
+      </c>
+      <c r="D642" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="643" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B643" s="1" t="s">
-        <v>1890</v>
+        <v>1986</v>
       </c>
       <c r="C643" s="1" t="s">
-        <v>1892</v>
-      </c>
-      <c r="D643" s="1" t="s">
-        <v>1891</v>
+        <v>1987</v>
+      </c>
+      <c r="D643" s="1">
+        <v>20</v>
       </c>
     </row>
     <row r="644" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B644" s="1" t="s">
-        <v>1893</v>
+        <v>1815</v>
       </c>
       <c r="C644" s="1" t="s">
-        <v>1895</v>
+        <v>1817</v>
       </c>
       <c r="D644" s="1" t="s">
-        <v>1894</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="645" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B645" s="1" t="s">
-        <v>1896</v>
+        <v>1988</v>
       </c>
       <c r="C645" s="1" t="s">
-        <v>1898</v>
+        <v>1990</v>
       </c>
       <c r="D645" s="1" t="s">
-        <v>1897</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="646" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B646" s="1" t="s">
-        <v>1899</v>
+        <v>1818</v>
       </c>
       <c r="C646" s="1" t="s">
-        <v>1900</v>
+        <v>1997</v>
       </c>
       <c r="D646" s="1" t="s">
-        <v>1901</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="647" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B647" s="1" t="s">
-        <v>1902</v>
+        <v>1991</v>
       </c>
       <c r="C647" s="1" t="s">
-        <v>1904</v>
+        <v>1996</v>
       </c>
       <c r="D647" s="1" t="s">
-        <v>1903</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="648" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B648" s="1" t="s">
-        <v>1905</v>
+        <v>1993</v>
       </c>
       <c r="C648" s="1" t="s">
-        <v>1906</v>
+        <v>1994</v>
       </c>
       <c r="D648" s="1" t="s">
-        <v>1907</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="649" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B649" s="1" t="s">
-        <v>1908</v>
+        <v>1820</v>
       </c>
       <c r="C649" s="1" t="s">
-        <v>1909</v>
+        <v>1821</v>
       </c>
       <c r="D649" s="1" t="s">
-        <v>1910</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="650" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B650" s="1" t="s">
-        <v>1911</v>
+        <v>2004</v>
       </c>
       <c r="C650" s="1" t="s">
-        <v>1912</v>
+        <v>2005</v>
       </c>
       <c r="D650" s="1" t="s">
-        <v>1913</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="651" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B651" s="1" t="s">
-        <v>1914</v>
+        <v>2001</v>
       </c>
       <c r="C651" s="1" t="s">
-        <v>1915</v>
+        <v>2002</v>
       </c>
       <c r="D651" s="1" t="s">
-        <v>1916</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="652" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B652" s="1" t="s">
-        <v>1917</v>
+        <v>1998</v>
       </c>
       <c r="C652" s="1" t="s">
-        <v>1919</v>
+        <v>1999</v>
       </c>
       <c r="D652" s="1" t="s">
-        <v>1918</v>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="653" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B653" s="1" t="s">
+        <v>1823</v>
+      </c>
+      <c r="C653" s="1" t="s">
+        <v>1825</v>
+      </c>
+      <c r="D653" s="1" t="s">
+        <v>1824</v>
+      </c>
+    </row>
+    <row r="654" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B654" s="1" t="s">
+        <v>2007</v>
+      </c>
+      <c r="C654" s="1" t="s">
+        <v>2009</v>
+      </c>
+      <c r="D654" s="1" t="s">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="655" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B655" s="3" t="s">
+        <v>1826</v>
+      </c>
+      <c r="C655" s="3" t="s">
+        <v>1828</v>
+      </c>
+      <c r="D655" s="3" t="s">
+        <v>1827</v>
+      </c>
+    </row>
+    <row r="656" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B656" s="1" t="s">
+        <v>1829</v>
+      </c>
+      <c r="C656" s="1" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D656" s="1" t="s">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="657" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B657" s="1" t="s">
+        <v>1832</v>
+      </c>
+      <c r="C657" s="1" t="s">
+        <v>1834</v>
+      </c>
+      <c r="D657" s="1" t="s">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="658" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B658" s="1" t="s">
+        <v>1835</v>
+      </c>
+      <c r="C658" s="1" t="s">
+        <v>1837</v>
+      </c>
+      <c r="D658" s="1" t="s">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="659" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B659" s="1" t="s">
+        <v>1838</v>
+      </c>
+      <c r="C659" s="1" t="s">
+        <v>1840</v>
+      </c>
+      <c r="D659" s="1" t="s">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="660" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B660" s="1" t="s">
+        <v>1841</v>
+      </c>
+      <c r="C660" s="1" t="s">
+        <v>1843</v>
+      </c>
+      <c r="D660" s="1" t="s">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="661" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B661" s="1" t="s">
+        <v>1844</v>
+      </c>
+      <c r="C661" s="1" t="s">
+        <v>1846</v>
+      </c>
+      <c r="D661" s="1" t="s">
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="662" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B662" s="1" t="s">
+        <v>1847</v>
+      </c>
+      <c r="C662" s="1" t="s">
+        <v>1849</v>
+      </c>
+      <c r="D662" s="1" t="s">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="663" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B663" s="1" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C663" s="1" t="s">
+        <v>1852</v>
+      </c>
+      <c r="D663" s="1" t="s">
+        <v>1851</v>
+      </c>
+    </row>
+    <row r="664" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B664" s="1" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C664" s="1" t="s">
+        <v>1855</v>
+      </c>
+      <c r="D664" s="1" t="s">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="665" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B665" s="1" t="s">
+        <v>1856</v>
+      </c>
+      <c r="C665" s="1" t="s">
+        <v>1858</v>
+      </c>
+      <c r="D665" s="1" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="666" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B666" s="1" t="s">
+        <v>1859</v>
+      </c>
+      <c r="C666" s="1" t="s">
+        <v>1861</v>
+      </c>
+      <c r="D666" s="1" t="s">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="667" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B667" s="1" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C667" s="1" t="s">
+        <v>1864</v>
+      </c>
+      <c r="D667" s="1" t="s">
+        <v>1863</v>
+      </c>
+    </row>
+    <row r="668" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B668" s="1" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C668" s="1" t="s">
+        <v>1867</v>
+      </c>
+      <c r="D668" s="1" t="s">
+        <v>1866</v>
+      </c>
+    </row>
+    <row r="669" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B669" s="1" t="s">
+        <v>1868</v>
+      </c>
+      <c r="C669" s="1" t="s">
+        <v>1870</v>
+      </c>
+      <c r="D669" s="1" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="670" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B670" s="1" t="s">
+        <v>1871</v>
+      </c>
+      <c r="C670" s="1" t="s">
+        <v>1873</v>
+      </c>
+      <c r="D670" s="1" t="s">
+        <v>1872</v>
+      </c>
+    </row>
+    <row r="671" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B671" s="1" t="s">
+        <v>1874</v>
+      </c>
+      <c r="C671" s="1" t="s">
+        <v>1876</v>
+      </c>
+      <c r="D671" s="1" t="s">
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="672" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B672" s="1" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C672" s="1" t="s">
+        <v>1878</v>
+      </c>
+      <c r="D672" s="1" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="673" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B673" s="1" t="s">
+        <v>1880</v>
+      </c>
+      <c r="C673" s="1" t="s">
+        <v>1882</v>
+      </c>
+      <c r="D673" s="1" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="674" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B674" s="1" t="s">
+        <v>1883</v>
+      </c>
+      <c r="C674" s="1" t="s">
+        <v>1885</v>
+      </c>
+      <c r="D674" s="1" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="675" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B675" s="1" t="s">
+        <v>1886</v>
+      </c>
+      <c r="C675" s="1" t="s">
+        <v>1888</v>
+      </c>
+      <c r="D675" s="1" t="s">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="676" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B676" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="C676" s="1" t="s">
+        <v>1891</v>
+      </c>
+      <c r="D676" s="1" t="s">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="677" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B677" s="1" t="s">
+        <v>1892</v>
+      </c>
+      <c r="C677" s="1" t="s">
+        <v>1893</v>
+      </c>
+      <c r="D677" s="1" t="s">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="678" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B678" s="1" t="s">
+        <v>1895</v>
+      </c>
+      <c r="C678" s="1" t="s">
+        <v>1897</v>
+      </c>
+      <c r="D678" s="1" t="s">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="679" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B679" s="1" t="s">
+        <v>1898</v>
+      </c>
+      <c r="C679" s="1" t="s">
+        <v>1899</v>
+      </c>
+      <c r="D679" s="1" t="s">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="680" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B680" s="1" t="s">
+        <v>1901</v>
+      </c>
+      <c r="C680" s="1" t="s">
+        <v>1902</v>
+      </c>
+      <c r="D680" s="1" t="s">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="681" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B681" s="1" t="s">
+        <v>1904</v>
+      </c>
+      <c r="C681" s="1" t="s">
+        <v>1905</v>
+      </c>
+      <c r="D681" s="1" t="s">
+        <v>1906</v>
+      </c>
+    </row>
+    <row r="682" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B682" s="1" t="s">
+        <v>1907</v>
+      </c>
+      <c r="C682" s="1" t="s">
+        <v>1908</v>
+      </c>
+      <c r="D682" s="1" t="s">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="683" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B683" s="1" t="s">
+        <v>1910</v>
+      </c>
+      <c r="C683" s="1" t="s">
+        <v>1912</v>
+      </c>
+      <c r="D683" s="1" t="s">
+        <v>1911</v>
       </c>
     </row>
   </sheetData>
@@ -31389,2374 +32009,2374 @@
   <conditionalFormatting sqref="B603">
     <cfRule type="duplicateValues" dxfId="1180" priority="1652"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B605">
+  <conditionalFormatting sqref="B605:B606">
     <cfRule type="duplicateValues" dxfId="1179" priority="1649"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B605">
+  <conditionalFormatting sqref="B605:B606">
     <cfRule type="duplicateValues" dxfId="1178" priority="1650"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B606">
+  <conditionalFormatting sqref="B607:B609">
     <cfRule type="duplicateValues" dxfId="1177" priority="1647"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B606">
+  <conditionalFormatting sqref="B607:B609">
     <cfRule type="duplicateValues" dxfId="1176" priority="1648"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B607">
+  <conditionalFormatting sqref="B610:B611">
     <cfRule type="duplicateValues" dxfId="1175" priority="1641"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B607">
+  <conditionalFormatting sqref="B610:B611">
     <cfRule type="duplicateValues" dxfId="1174" priority="1642"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B608">
+  <conditionalFormatting sqref="B612:B614">
     <cfRule type="duplicateValues" dxfId="1173" priority="1640"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B608">
+  <conditionalFormatting sqref="B612:B614">
     <cfRule type="duplicateValues" dxfId="1172" priority="1639"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B609">
+  <conditionalFormatting sqref="B615:B616">
     <cfRule type="duplicateValues" dxfId="1171" priority="1637"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B609">
+  <conditionalFormatting sqref="B615:B616">
     <cfRule type="duplicateValues" dxfId="1170" priority="1638"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B610">
+  <conditionalFormatting sqref="B617:B619">
     <cfRule type="duplicateValues" dxfId="1169" priority="1631"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B610">
+  <conditionalFormatting sqref="B617:B619">
     <cfRule type="duplicateValues" dxfId="1168" priority="1632"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B611">
+  <conditionalFormatting sqref="B620:B622">
     <cfRule type="duplicateValues" dxfId="1167" priority="1629"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B611">
+  <conditionalFormatting sqref="B620:B622">
     <cfRule type="duplicateValues" dxfId="1166" priority="1630"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B613">
+  <conditionalFormatting sqref="B625:B627">
     <cfRule type="duplicateValues" dxfId="1165" priority="1627"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B613">
+  <conditionalFormatting sqref="B625:B627">
     <cfRule type="duplicateValues" dxfId="1164" priority="1628"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B614">
+  <conditionalFormatting sqref="B628:B629">
     <cfRule type="duplicateValues" dxfId="1163" priority="1622"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B614">
+  <conditionalFormatting sqref="B628:B629">
     <cfRule type="duplicateValues" dxfId="1162" priority="1621"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B615">
+  <conditionalFormatting sqref="B630:B633">
     <cfRule type="duplicateValues" dxfId="1161" priority="1618"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B615">
+  <conditionalFormatting sqref="B630:B633">
     <cfRule type="duplicateValues" dxfId="1160" priority="1617"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B616">
+  <conditionalFormatting sqref="B634:B635">
     <cfRule type="duplicateValues" dxfId="1159" priority="1614"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B616">
+  <conditionalFormatting sqref="B634:B635">
     <cfRule type="duplicateValues" dxfId="1158" priority="1613"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B617">
+  <conditionalFormatting sqref="B636:B637">
     <cfRule type="duplicateValues" dxfId="1157" priority="1611"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B617">
+  <conditionalFormatting sqref="B636:B637">
     <cfRule type="duplicateValues" dxfId="1156" priority="1612"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B618">
+  <conditionalFormatting sqref="B638:B640">
     <cfRule type="duplicateValues" dxfId="1155" priority="1608"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B619">
+  <conditionalFormatting sqref="B641:B643">
     <cfRule type="duplicateValues" dxfId="1154" priority="1606"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B619">
+  <conditionalFormatting sqref="B641:B643">
     <cfRule type="duplicateValues" dxfId="1153" priority="1607"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B620">
+  <conditionalFormatting sqref="B644:B645">
     <cfRule type="duplicateValues" dxfId="1152" priority="1604"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B620">
+  <conditionalFormatting sqref="B644:B645">
     <cfRule type="duplicateValues" dxfId="1151" priority="1605"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D621">
+  <conditionalFormatting sqref="D646:D648">
     <cfRule type="duplicateValues" dxfId="1150" priority="1602"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D621">
+  <conditionalFormatting sqref="D646:D648">
     <cfRule type="duplicateValues" dxfId="1149" priority="1603"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B621">
+  <conditionalFormatting sqref="B646:B648">
     <cfRule type="duplicateValues" dxfId="1148" priority="1598"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B621">
+  <conditionalFormatting sqref="B646:B648">
     <cfRule type="duplicateValues" dxfId="1147" priority="1599"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B625">
+  <conditionalFormatting sqref="B656">
     <cfRule type="duplicateValues" dxfId="1146" priority="1596"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B625">
+  <conditionalFormatting sqref="B656">
     <cfRule type="duplicateValues" dxfId="1145" priority="1597"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B627">
+  <conditionalFormatting sqref="B658">
     <cfRule type="duplicateValues" dxfId="1144" priority="1594"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B627">
+  <conditionalFormatting sqref="B658">
     <cfRule type="duplicateValues" dxfId="1143" priority="1595"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B626">
+  <conditionalFormatting sqref="B657">
     <cfRule type="duplicateValues" dxfId="1142" priority="1593"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B626">
+  <conditionalFormatting sqref="B657">
     <cfRule type="duplicateValues" dxfId="1141" priority="1592"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B628">
+  <conditionalFormatting sqref="B659">
     <cfRule type="duplicateValues" dxfId="1140" priority="1591"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B628">
+  <conditionalFormatting sqref="B659">
     <cfRule type="duplicateValues" dxfId="1139" priority="1590"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B629">
+  <conditionalFormatting sqref="B660">
     <cfRule type="duplicateValues" dxfId="1138" priority="1587"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B629">
+  <conditionalFormatting sqref="B660">
     <cfRule type="duplicateValues" dxfId="1137" priority="1586"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B630">
+  <conditionalFormatting sqref="B661">
     <cfRule type="duplicateValues" dxfId="1136" priority="1583"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B630">
+  <conditionalFormatting sqref="B661">
     <cfRule type="duplicateValues" dxfId="1135" priority="1582"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B631">
+  <conditionalFormatting sqref="B662">
     <cfRule type="duplicateValues" dxfId="1134" priority="1579"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B631">
+  <conditionalFormatting sqref="B662">
     <cfRule type="duplicateValues" dxfId="1133" priority="1578"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B632">
+  <conditionalFormatting sqref="B663">
     <cfRule type="duplicateValues" dxfId="1132" priority="1574"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B632">
+  <conditionalFormatting sqref="B663">
     <cfRule type="duplicateValues" dxfId="1131" priority="1575"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B633">
+  <conditionalFormatting sqref="B664">
     <cfRule type="duplicateValues" dxfId="1130" priority="1570"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B633">
+  <conditionalFormatting sqref="B664">
     <cfRule type="duplicateValues" dxfId="1129" priority="1571"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B634">
+  <conditionalFormatting sqref="B665">
     <cfRule type="duplicateValues" dxfId="1128" priority="1566"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B634">
+  <conditionalFormatting sqref="B665">
     <cfRule type="duplicateValues" dxfId="1127" priority="1567"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B635">
+  <conditionalFormatting sqref="B666">
     <cfRule type="duplicateValues" dxfId="1126" priority="1564"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B635">
+  <conditionalFormatting sqref="B666">
     <cfRule type="duplicateValues" dxfId="1125" priority="1565"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B637">
+  <conditionalFormatting sqref="B668">
     <cfRule type="duplicateValues" dxfId="1124" priority="1562"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B637">
+  <conditionalFormatting sqref="B668">
     <cfRule type="duplicateValues" dxfId="1123" priority="1563"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B636">
+  <conditionalFormatting sqref="B667">
     <cfRule type="duplicateValues" dxfId="1122" priority="1560"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B636">
+  <conditionalFormatting sqref="B667">
     <cfRule type="duplicateValues" dxfId="1121" priority="1561"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B638">
+  <conditionalFormatting sqref="B669">
     <cfRule type="duplicateValues" dxfId="1120" priority="1558"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B638">
+  <conditionalFormatting sqref="B669">
     <cfRule type="duplicateValues" dxfId="1119" priority="1559"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B640">
+  <conditionalFormatting sqref="B671">
     <cfRule type="duplicateValues" dxfId="1118" priority="1556"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B640">
+  <conditionalFormatting sqref="B671">
     <cfRule type="duplicateValues" dxfId="1117" priority="1557"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B641">
+  <conditionalFormatting sqref="B672">
     <cfRule type="duplicateValues" dxfId="1116" priority="1552"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B641">
+  <conditionalFormatting sqref="B672">
     <cfRule type="duplicateValues" dxfId="1115" priority="1553"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B642">
+  <conditionalFormatting sqref="B673">
     <cfRule type="duplicateValues" dxfId="1114" priority="1550"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B642">
+  <conditionalFormatting sqref="B673">
     <cfRule type="duplicateValues" dxfId="1113" priority="1551"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B644">
+  <conditionalFormatting sqref="B675">
     <cfRule type="duplicateValues" dxfId="1112" priority="1547"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B644">
+  <conditionalFormatting sqref="B675">
     <cfRule type="duplicateValues" dxfId="1111" priority="1546"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B643">
+  <conditionalFormatting sqref="B674">
     <cfRule type="duplicateValues" dxfId="1110" priority="1544"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B643">
+  <conditionalFormatting sqref="B674">
     <cfRule type="duplicateValues" dxfId="1109" priority="1545"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B645">
+  <conditionalFormatting sqref="B676">
     <cfRule type="duplicateValues" dxfId="1108" priority="1541"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B645">
+  <conditionalFormatting sqref="B676">
     <cfRule type="duplicateValues" dxfId="1107" priority="1540"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B646">
+  <conditionalFormatting sqref="B677">
     <cfRule type="duplicateValues" dxfId="1106" priority="1538"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B646">
+  <conditionalFormatting sqref="B677">
     <cfRule type="duplicateValues" dxfId="1105" priority="1539"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B647">
+  <conditionalFormatting sqref="B678">
     <cfRule type="duplicateValues" dxfId="1104" priority="1533"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B647">
+  <conditionalFormatting sqref="B678">
     <cfRule type="duplicateValues" dxfId="1103" priority="1532"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B648">
+  <conditionalFormatting sqref="B679">
     <cfRule type="duplicateValues" dxfId="1102" priority="1528"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B648">
+  <conditionalFormatting sqref="B679">
     <cfRule type="duplicateValues" dxfId="1101" priority="1529"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B649">
+  <conditionalFormatting sqref="B680">
     <cfRule type="duplicateValues" dxfId="1100" priority="1527"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B649">
+  <conditionalFormatting sqref="B680">
     <cfRule type="duplicateValues" dxfId="1099" priority="1526"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B650">
+  <conditionalFormatting sqref="B681">
     <cfRule type="duplicateValues" dxfId="1098" priority="1524"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B650">
+  <conditionalFormatting sqref="B681">
     <cfRule type="duplicateValues" dxfId="1097" priority="1525"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B651">
+  <conditionalFormatting sqref="B682">
     <cfRule type="duplicateValues" dxfId="1096" priority="1522"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B651">
+  <conditionalFormatting sqref="B682">
     <cfRule type="duplicateValues" dxfId="1095" priority="1523"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B652">
+  <conditionalFormatting sqref="B683">
     <cfRule type="duplicateValues" dxfId="1094" priority="1520"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B652">
+  <conditionalFormatting sqref="B683">
     <cfRule type="duplicateValues" dxfId="1093" priority="1521"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B653">
+  <conditionalFormatting sqref="B684">
     <cfRule type="duplicateValues" dxfId="1092" priority="1518"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B653">
+  <conditionalFormatting sqref="B684">
     <cfRule type="duplicateValues" dxfId="1091" priority="1519"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B654">
+  <conditionalFormatting sqref="B685">
     <cfRule type="duplicateValues" dxfId="1090" priority="1512"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B654">
+  <conditionalFormatting sqref="B685">
     <cfRule type="duplicateValues" dxfId="1089" priority="1513"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B656">
+  <conditionalFormatting sqref="B687">
     <cfRule type="duplicateValues" dxfId="1088" priority="1508"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B656">
+  <conditionalFormatting sqref="B687">
     <cfRule type="duplicateValues" dxfId="1087" priority="1509"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B657">
+  <conditionalFormatting sqref="B688">
     <cfRule type="duplicateValues" dxfId="1086" priority="1506"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B657">
+  <conditionalFormatting sqref="B688">
     <cfRule type="duplicateValues" dxfId="1085" priority="1507"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B658">
+  <conditionalFormatting sqref="B689">
     <cfRule type="duplicateValues" dxfId="1084" priority="1504"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B658">
+  <conditionalFormatting sqref="B689">
     <cfRule type="duplicateValues" dxfId="1083" priority="1505"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B659">
+  <conditionalFormatting sqref="B690">
     <cfRule type="duplicateValues" dxfId="1082" priority="1503"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B659">
+  <conditionalFormatting sqref="B690">
     <cfRule type="duplicateValues" dxfId="1081" priority="1502"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B660">
+  <conditionalFormatting sqref="B691">
     <cfRule type="duplicateValues" dxfId="1080" priority="1500"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B660">
+  <conditionalFormatting sqref="B691">
     <cfRule type="duplicateValues" dxfId="1079" priority="1501"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B661">
+  <conditionalFormatting sqref="B692">
     <cfRule type="duplicateValues" dxfId="1078" priority="1498"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B661">
+  <conditionalFormatting sqref="B692">
     <cfRule type="duplicateValues" dxfId="1077" priority="1499"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B662">
+  <conditionalFormatting sqref="B693">
     <cfRule type="duplicateValues" dxfId="1076" priority="1497"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B662">
+  <conditionalFormatting sqref="B693">
     <cfRule type="duplicateValues" dxfId="1075" priority="1496"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B666">
+  <conditionalFormatting sqref="B697">
     <cfRule type="duplicateValues" dxfId="1074" priority="1492"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B666">
+  <conditionalFormatting sqref="B697">
     <cfRule type="duplicateValues" dxfId="1073" priority="1493"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B667">
+  <conditionalFormatting sqref="B698">
     <cfRule type="duplicateValues" dxfId="1072" priority="1490"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B667">
+  <conditionalFormatting sqref="B698">
     <cfRule type="duplicateValues" dxfId="1071" priority="1491"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B668">
+  <conditionalFormatting sqref="B699">
     <cfRule type="duplicateValues" dxfId="1070" priority="1486"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B668">
+  <conditionalFormatting sqref="B699">
     <cfRule type="duplicateValues" dxfId="1069" priority="1487"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B669">
+  <conditionalFormatting sqref="B700">
     <cfRule type="duplicateValues" dxfId="1068" priority="1483"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B669">
+  <conditionalFormatting sqref="B700">
     <cfRule type="duplicateValues" dxfId="1067" priority="1482"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B670">
+  <conditionalFormatting sqref="B701">
     <cfRule type="duplicateValues" dxfId="1066" priority="1479"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B670">
+  <conditionalFormatting sqref="B701">
     <cfRule type="duplicateValues" dxfId="1065" priority="1478"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B672">
+  <conditionalFormatting sqref="B703">
     <cfRule type="duplicateValues" dxfId="1064" priority="1476"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B672">
+  <conditionalFormatting sqref="B703">
     <cfRule type="duplicateValues" dxfId="1063" priority="1477"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B673">
+  <conditionalFormatting sqref="B704">
     <cfRule type="duplicateValues" dxfId="1062" priority="1472"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B673">
+  <conditionalFormatting sqref="B704">
     <cfRule type="duplicateValues" dxfId="1061" priority="1473"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B674">
+  <conditionalFormatting sqref="B705">
     <cfRule type="duplicateValues" dxfId="1060" priority="1466"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B674">
+  <conditionalFormatting sqref="B705">
     <cfRule type="duplicateValues" dxfId="1059" priority="1467"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B675">
+  <conditionalFormatting sqref="B706">
     <cfRule type="duplicateValues" dxfId="1058" priority="1463"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B675">
+  <conditionalFormatting sqref="B706">
     <cfRule type="duplicateValues" dxfId="1057" priority="1464"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B675">
+  <conditionalFormatting sqref="B706">
     <cfRule type="duplicateValues" dxfId="1056" priority="1462"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B676">
+  <conditionalFormatting sqref="B707">
     <cfRule type="duplicateValues" dxfId="1055" priority="1457"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B676">
+  <conditionalFormatting sqref="B707">
     <cfRule type="duplicateValues" dxfId="1054" priority="1458"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B676">
+  <conditionalFormatting sqref="B707">
     <cfRule type="duplicateValues" dxfId="1053" priority="1456"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B677">
+  <conditionalFormatting sqref="B708">
     <cfRule type="duplicateValues" dxfId="1052" priority="1454"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B677">
+  <conditionalFormatting sqref="B708">
     <cfRule type="duplicateValues" dxfId="1051" priority="1455"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B677">
+  <conditionalFormatting sqref="B708">
     <cfRule type="duplicateValues" dxfId="1050" priority="1453"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B678">
+  <conditionalFormatting sqref="B709">
     <cfRule type="duplicateValues" dxfId="1049" priority="1451"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B678">
+  <conditionalFormatting sqref="B709">
     <cfRule type="duplicateValues" dxfId="1048" priority="1452"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B678">
+  <conditionalFormatting sqref="B709">
     <cfRule type="duplicateValues" dxfId="1047" priority="1450"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B679">
+  <conditionalFormatting sqref="B710">
     <cfRule type="duplicateValues" dxfId="1046" priority="1448"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B679">
+  <conditionalFormatting sqref="B710">
     <cfRule type="duplicateValues" dxfId="1045" priority="1449"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B679">
+  <conditionalFormatting sqref="B710">
     <cfRule type="duplicateValues" dxfId="1044" priority="1447"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B680">
+  <conditionalFormatting sqref="B711">
     <cfRule type="duplicateValues" dxfId="1043" priority="1442"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B680">
+  <conditionalFormatting sqref="B711">
     <cfRule type="duplicateValues" dxfId="1042" priority="1443"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B680">
+  <conditionalFormatting sqref="B711">
     <cfRule type="duplicateValues" dxfId="1041" priority="1441"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B681">
+  <conditionalFormatting sqref="B712">
     <cfRule type="duplicateValues" dxfId="1040" priority="1437"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B681">
+  <conditionalFormatting sqref="B712">
     <cfRule type="duplicateValues" dxfId="1039" priority="1436"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B681">
+  <conditionalFormatting sqref="B712">
     <cfRule type="duplicateValues" dxfId="1038" priority="1435"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B682">
+  <conditionalFormatting sqref="B713">
     <cfRule type="duplicateValues" dxfId="1037" priority="1431"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B682">
+  <conditionalFormatting sqref="B713">
     <cfRule type="duplicateValues" dxfId="1036" priority="1430"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B682">
+  <conditionalFormatting sqref="B713">
     <cfRule type="duplicateValues" dxfId="1035" priority="1429"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B684">
+  <conditionalFormatting sqref="B715">
     <cfRule type="duplicateValues" dxfId="1034" priority="1418"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B684">
+  <conditionalFormatting sqref="B715">
     <cfRule type="duplicateValues" dxfId="1033" priority="1419"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B684">
+  <conditionalFormatting sqref="B715">
     <cfRule type="duplicateValues" dxfId="1032" priority="1417"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B685">
+  <conditionalFormatting sqref="B716">
     <cfRule type="duplicateValues" dxfId="1031" priority="1415"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B685">
+  <conditionalFormatting sqref="B716">
     <cfRule type="duplicateValues" dxfId="1030" priority="1416"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B685">
+  <conditionalFormatting sqref="B716">
     <cfRule type="duplicateValues" dxfId="1029" priority="1414"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B687">
+  <conditionalFormatting sqref="B718">
     <cfRule type="duplicateValues" dxfId="1028" priority="1412"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B687">
+  <conditionalFormatting sqref="B718">
     <cfRule type="duplicateValues" dxfId="1027" priority="1413"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B687">
+  <conditionalFormatting sqref="B718">
     <cfRule type="duplicateValues" dxfId="1026" priority="1411"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B688">
+  <conditionalFormatting sqref="B719">
     <cfRule type="duplicateValues" dxfId="1025" priority="1409"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B688">
+  <conditionalFormatting sqref="B719">
     <cfRule type="duplicateValues" dxfId="1024" priority="1410"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B688">
+  <conditionalFormatting sqref="B719">
     <cfRule type="duplicateValues" dxfId="1023" priority="1408"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B689">
+  <conditionalFormatting sqref="B720">
     <cfRule type="duplicateValues" dxfId="1022" priority="1400"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B689">
+  <conditionalFormatting sqref="B720">
     <cfRule type="duplicateValues" dxfId="1021" priority="1401"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B689">
+  <conditionalFormatting sqref="B720">
     <cfRule type="duplicateValues" dxfId="1020" priority="1399"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B690">
+  <conditionalFormatting sqref="B721">
     <cfRule type="duplicateValues" dxfId="1019" priority="1397"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B690">
+  <conditionalFormatting sqref="B721">
     <cfRule type="duplicateValues" dxfId="1018" priority="1398"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B690">
+  <conditionalFormatting sqref="B721">
     <cfRule type="duplicateValues" dxfId="1017" priority="1396"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B691">
+  <conditionalFormatting sqref="B722">
     <cfRule type="duplicateValues" dxfId="1016" priority="1392"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B691">
+  <conditionalFormatting sqref="B722">
     <cfRule type="duplicateValues" dxfId="1015" priority="1391"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B691">
+  <conditionalFormatting sqref="B722">
     <cfRule type="duplicateValues" dxfId="1014" priority="1390"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B693">
+  <conditionalFormatting sqref="B724">
     <cfRule type="duplicateValues" dxfId="1013" priority="1389"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B693">
+  <conditionalFormatting sqref="B724">
     <cfRule type="duplicateValues" dxfId="1012" priority="1388"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B693">
+  <conditionalFormatting sqref="B724">
     <cfRule type="duplicateValues" dxfId="1011" priority="1387"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B694">
+  <conditionalFormatting sqref="B725">
     <cfRule type="duplicateValues" dxfId="1010" priority="1383"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B694">
+  <conditionalFormatting sqref="B725">
     <cfRule type="duplicateValues" dxfId="1009" priority="1382"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B694">
+  <conditionalFormatting sqref="B725">
     <cfRule type="duplicateValues" dxfId="1008" priority="1381"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B695">
+  <conditionalFormatting sqref="B726">
     <cfRule type="duplicateValues" dxfId="1007" priority="1374"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B695">
+  <conditionalFormatting sqref="B726">
     <cfRule type="duplicateValues" dxfId="1006" priority="1373"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B695">
+  <conditionalFormatting sqref="B726">
     <cfRule type="duplicateValues" dxfId="1005" priority="1372"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B696">
+  <conditionalFormatting sqref="B727">
     <cfRule type="duplicateValues" dxfId="1004" priority="1370"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B696">
+  <conditionalFormatting sqref="B727">
     <cfRule type="duplicateValues" dxfId="1003" priority="1371"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B696">
+  <conditionalFormatting sqref="B727">
     <cfRule type="duplicateValues" dxfId="1002" priority="1369"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B697">
+  <conditionalFormatting sqref="B728">
     <cfRule type="duplicateValues" dxfId="1001" priority="1367"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B697">
+  <conditionalFormatting sqref="B728">
     <cfRule type="duplicateValues" dxfId="1000" priority="1368"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B697">
+  <conditionalFormatting sqref="B728">
     <cfRule type="duplicateValues" dxfId="999" priority="1366"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B698">
+  <conditionalFormatting sqref="B729">
     <cfRule type="duplicateValues" dxfId="998" priority="1358"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B698">
+  <conditionalFormatting sqref="B729">
     <cfRule type="duplicateValues" dxfId="997" priority="1359"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B698">
+  <conditionalFormatting sqref="B729">
     <cfRule type="duplicateValues" dxfId="996" priority="1357"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B699">
+  <conditionalFormatting sqref="B730">
     <cfRule type="duplicateValues" dxfId="995" priority="1355"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B699">
+  <conditionalFormatting sqref="B730">
     <cfRule type="duplicateValues" dxfId="994" priority="1356"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B699">
+  <conditionalFormatting sqref="B730">
     <cfRule type="duplicateValues" dxfId="993" priority="1354"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B701">
+  <conditionalFormatting sqref="B732">
     <cfRule type="duplicateValues" dxfId="992" priority="1349"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B701">
+  <conditionalFormatting sqref="B732">
     <cfRule type="duplicateValues" dxfId="991" priority="1350"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B701">
+  <conditionalFormatting sqref="B732">
     <cfRule type="duplicateValues" dxfId="990" priority="1348"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B700">
+  <conditionalFormatting sqref="B731">
     <cfRule type="duplicateValues" dxfId="989" priority="1347"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B700">
+  <conditionalFormatting sqref="B731">
     <cfRule type="duplicateValues" dxfId="988" priority="1346"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B700">
+  <conditionalFormatting sqref="B731">
     <cfRule type="duplicateValues" dxfId="987" priority="1345"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B702">
+  <conditionalFormatting sqref="B733">
     <cfRule type="duplicateValues" dxfId="986" priority="1343"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B702">
+  <conditionalFormatting sqref="B733">
     <cfRule type="duplicateValues" dxfId="985" priority="1344"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B702">
+  <conditionalFormatting sqref="B733">
     <cfRule type="duplicateValues" dxfId="984" priority="1342"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B704">
+  <conditionalFormatting sqref="B735">
     <cfRule type="duplicateValues" dxfId="983" priority="1340"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B704">
+  <conditionalFormatting sqref="B735">
     <cfRule type="duplicateValues" dxfId="982" priority="1341"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B704">
+  <conditionalFormatting sqref="B735">
     <cfRule type="duplicateValues" dxfId="981" priority="1339"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B705">
+  <conditionalFormatting sqref="B736">
     <cfRule type="duplicateValues" dxfId="980" priority="1337"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B705">
+  <conditionalFormatting sqref="B736">
     <cfRule type="duplicateValues" dxfId="979" priority="1338"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B705">
+  <conditionalFormatting sqref="B736">
     <cfRule type="duplicateValues" dxfId="978" priority="1336"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B707">
+  <conditionalFormatting sqref="B738">
     <cfRule type="duplicateValues" dxfId="977" priority="1335"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B707">
+  <conditionalFormatting sqref="B738">
     <cfRule type="duplicateValues" dxfId="976" priority="1334"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B707">
+  <conditionalFormatting sqref="B738">
     <cfRule type="duplicateValues" dxfId="975" priority="1333"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B708">
+  <conditionalFormatting sqref="B739">
     <cfRule type="duplicateValues" dxfId="974" priority="1331"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B708">
+  <conditionalFormatting sqref="B739">
     <cfRule type="duplicateValues" dxfId="973" priority="1332"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B708">
+  <conditionalFormatting sqref="B739">
     <cfRule type="duplicateValues" dxfId="972" priority="1330"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B709">
+  <conditionalFormatting sqref="B740">
     <cfRule type="duplicateValues" dxfId="971" priority="1328"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B709">
+  <conditionalFormatting sqref="B740">
     <cfRule type="duplicateValues" dxfId="970" priority="1329"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B709">
+  <conditionalFormatting sqref="B740">
     <cfRule type="duplicateValues" dxfId="969" priority="1327"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B711">
+  <conditionalFormatting sqref="B742">
     <cfRule type="duplicateValues" dxfId="968" priority="1325"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B711">
+  <conditionalFormatting sqref="B742">
     <cfRule type="duplicateValues" dxfId="967" priority="1326"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B711">
+  <conditionalFormatting sqref="B742">
     <cfRule type="duplicateValues" dxfId="966" priority="1324"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B712">
+  <conditionalFormatting sqref="B743">
     <cfRule type="duplicateValues" dxfId="965" priority="1319"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B712">
+  <conditionalFormatting sqref="B743">
     <cfRule type="duplicateValues" dxfId="964" priority="1320"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B712">
+  <conditionalFormatting sqref="B743">
     <cfRule type="duplicateValues" dxfId="963" priority="1318"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B713">
+  <conditionalFormatting sqref="B744">
     <cfRule type="duplicateValues" dxfId="962" priority="1316"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B713">
+  <conditionalFormatting sqref="B744">
     <cfRule type="duplicateValues" dxfId="961" priority="1317"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B713">
+  <conditionalFormatting sqref="B744">
     <cfRule type="duplicateValues" dxfId="960" priority="1315"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B715">
+  <conditionalFormatting sqref="B746">
     <cfRule type="duplicateValues" dxfId="959" priority="1313"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B715">
+  <conditionalFormatting sqref="B746">
     <cfRule type="duplicateValues" dxfId="958" priority="1314"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B715">
+  <conditionalFormatting sqref="B746">
     <cfRule type="duplicateValues" dxfId="957" priority="1312"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B716">
+  <conditionalFormatting sqref="B747">
     <cfRule type="duplicateValues" dxfId="956" priority="1307"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B716">
+  <conditionalFormatting sqref="B747">
     <cfRule type="duplicateValues" dxfId="955" priority="1308"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B716">
+  <conditionalFormatting sqref="B747">
     <cfRule type="duplicateValues" dxfId="954" priority="1306"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B717">
+  <conditionalFormatting sqref="B748">
     <cfRule type="duplicateValues" dxfId="953" priority="1299"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B717">
+  <conditionalFormatting sqref="B748">
     <cfRule type="duplicateValues" dxfId="952" priority="1298"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B717">
+  <conditionalFormatting sqref="B748">
     <cfRule type="duplicateValues" dxfId="951" priority="1297"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B718">
+  <conditionalFormatting sqref="B749">
     <cfRule type="duplicateValues" dxfId="950" priority="1296"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B718">
+  <conditionalFormatting sqref="B749">
     <cfRule type="duplicateValues" dxfId="949" priority="1295"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B718">
+  <conditionalFormatting sqref="B749">
     <cfRule type="duplicateValues" dxfId="948" priority="1294"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B720">
+  <conditionalFormatting sqref="B751">
     <cfRule type="duplicateValues" dxfId="947" priority="1293"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B720">
+  <conditionalFormatting sqref="B751">
     <cfRule type="duplicateValues" dxfId="946" priority="1292"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B720">
+  <conditionalFormatting sqref="B751">
     <cfRule type="duplicateValues" dxfId="945" priority="1291"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B719">
+  <conditionalFormatting sqref="B750">
     <cfRule type="duplicateValues" dxfId="944" priority="1290"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B719">
+  <conditionalFormatting sqref="B750">
     <cfRule type="duplicateValues" dxfId="943" priority="1289"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B719">
+  <conditionalFormatting sqref="B750">
     <cfRule type="duplicateValues" dxfId="942" priority="1288"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B722">
+  <conditionalFormatting sqref="B753">
     <cfRule type="duplicateValues" dxfId="941" priority="1286"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B722">
+  <conditionalFormatting sqref="B753">
     <cfRule type="duplicateValues" dxfId="940" priority="1287"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B722">
+  <conditionalFormatting sqref="B753">
     <cfRule type="duplicateValues" dxfId="939" priority="1285"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B724">
+  <conditionalFormatting sqref="B755">
     <cfRule type="duplicateValues" dxfId="938" priority="1277"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B724">
+  <conditionalFormatting sqref="B755">
     <cfRule type="duplicateValues" dxfId="937" priority="1278"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B724">
+  <conditionalFormatting sqref="B755">
     <cfRule type="duplicateValues" dxfId="936" priority="1276"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B725">
+  <conditionalFormatting sqref="B756">
     <cfRule type="duplicateValues" dxfId="935" priority="1271"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B725">
+  <conditionalFormatting sqref="B756">
     <cfRule type="duplicateValues" dxfId="934" priority="1272"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B725">
+  <conditionalFormatting sqref="B756">
     <cfRule type="duplicateValues" dxfId="933" priority="1270"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B727">
+  <conditionalFormatting sqref="B758">
     <cfRule type="duplicateValues" dxfId="932" priority="1265"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B727">
+  <conditionalFormatting sqref="B758">
     <cfRule type="duplicateValues" dxfId="931" priority="1266"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B727">
+  <conditionalFormatting sqref="B758">
     <cfRule type="duplicateValues" dxfId="930" priority="1264"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B726">
+  <conditionalFormatting sqref="B757">
     <cfRule type="duplicateValues" dxfId="929" priority="1263"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B726">
+  <conditionalFormatting sqref="B757">
     <cfRule type="duplicateValues" dxfId="928" priority="1262"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B726">
+  <conditionalFormatting sqref="B757">
     <cfRule type="duplicateValues" dxfId="927" priority="1261"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B728">
+  <conditionalFormatting sqref="B759">
     <cfRule type="duplicateValues" dxfId="926" priority="1256"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B728">
+  <conditionalFormatting sqref="B759">
     <cfRule type="duplicateValues" dxfId="925" priority="1257"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B728">
+  <conditionalFormatting sqref="B759">
     <cfRule type="duplicateValues" dxfId="924" priority="1255"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B730">
+  <conditionalFormatting sqref="B761">
     <cfRule type="duplicateValues" dxfId="923" priority="1254"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B730">
+  <conditionalFormatting sqref="B761">
     <cfRule type="duplicateValues" dxfId="922" priority="1253"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B730">
+  <conditionalFormatting sqref="B761">
     <cfRule type="duplicateValues" dxfId="921" priority="1252"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B731">
+  <conditionalFormatting sqref="B762">
     <cfRule type="duplicateValues" dxfId="920" priority="1250"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B731">
+  <conditionalFormatting sqref="B762">
     <cfRule type="duplicateValues" dxfId="919" priority="1251"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B731">
+  <conditionalFormatting sqref="B762">
     <cfRule type="duplicateValues" dxfId="918" priority="1249"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B732">
+  <conditionalFormatting sqref="B763">
     <cfRule type="duplicateValues" dxfId="917" priority="1241"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B732">
+  <conditionalFormatting sqref="B763">
     <cfRule type="duplicateValues" dxfId="916" priority="1242"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B732">
+  <conditionalFormatting sqref="B763">
     <cfRule type="duplicateValues" dxfId="915" priority="1240"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B683 D46 B573:B574 B46 B104:B106 B109:B111 B126 B131 B134 B137 B143:B147 B150:B152 B159:B160 D154 B169 B181 B188 B190 B199 D195 B212 B222:B224 B229 B231:B232 B239:B240 B242:B244 B251 B258:B261 B264:B269 B273 B278 B288:B289 B291 B295:B299 B306:B307 B324 B331 B333 B337:B338 B340:B341 B343 B348 B345:B346 B351 B364 B372:B373 B378:B380 B389:B390 B396:B397 B401 B420 B430 B433 B438:B439 B442 B444 B448 B451 B459 B463 B466 B475:B476 B480 B488 B492:B495 B507 B514 B519 B524 B528:B529 B531:B535 B537 B539 B560 B576 B590 B599:B600 B612 B622:B624 B639 B655 B663:B665 B671 B686 B692 B703 B706 B710 B714 B721 B723 B729 B739 B755 B758 B766 B768:B769 B775:B776 B781:B783 B805 B808 B811 B824:B827 B838 B840 B842:B843 B847 B850 B855:B856 B860 B862 B864:B865 B876 B878 B897 B911 B927:B928 B930 B932:B933 B942 B950:B1048576 B1:B8 B11:B15 B18:B19 B22 B24 B30:B31 B34 B39:B41 B43 B48:B50 B53 B56:B58 B62:B64 B74:B94 B96:B102 B114:B119 B122 B124 B183:B184 B468">
+  <conditionalFormatting sqref="B714 D46 B573:B574 B46 B104:B106 B109:B111 B126 B131 B134 B137 B143:B147 B150:B152 B159:B160 D154 B169 B181 B188 B190 B199 D195 B212 B222:B224 B229 B231:B232 B239:B240 B242:B244 B251 B258:B261 B264:B269 B273 B278 B288:B289 B291 B295:B299 B306:B307 B324 B331 B333 B337:B338 B340:B341 B343 B348 B345:B346 B351 B364 B372:B373 B378:B380 B389:B390 B396:B397 B401 B420 B430 B433 B438:B439 B442 B444 B448 B451 B459 B463 B466 B475:B476 B480 B488 B492:B495 B507 B514 B519 B524 B528:B529 B531:B535 B537 B539 B560 B576 B590 B599:B600 B623:B624 B649:B655 B670 B686 B694:B696 B702 B717 B723 B734 B737 B741 B745 B752 B754 B760 B770 B786 B789 B797 B799:B800 B806:B807 B812:B814 B836 B839 B842 B855:B858 B869 B871 B873:B874 B878 B881 B886:B887 B891 B893 B895:B896 B907 B909 B928 B942 B958:B959 B961 B963:B964 B973 B981:B1048576 B1:B8 B11:B15 B18:B19 B22 B24 B30:B31 B34 B39:B41 B43 B48:B50 B53 B56:B58 B62:B64 B74:B94 B96:B102 B114:B119 B122 B124 B183:B184 B468">
     <cfRule type="duplicateValues" dxfId="914" priority="2582"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B683 B573:B574 B231:B232 B239:B240 B242:B244 B251 B258:B261 B264:B269 B273 B278 B288:B289 B291 B295:B299 B306:B307 B324 B331 B333 B337:B338 B340:B341 B343 B348 B345:B346 B351 B364 B372:B373 B378:B380 B389:B390 B396:B397 B401 B420 B430 B433 B438:B439 B442 B444 B448 B451 B459 B463 B466 B475:B476 B480 B488 B492:B495 B507 B514 B519 B524 B528:B529 B531:B535 B537 B539 B560 B576 B590 B599:B600 B612 B622:B624 B639 B655 B663:B665 B671 B686 B692 B703 B706 B710 B714 B721 B723 B729 B739 B755 B758 B766 B768:B769 B775:B776 B781:B783 B805 B808 B811 B824:B827 B838 B840 B842:B843 B847 B850 B855:B856 B860 B862 B864:B865 B876 B878 B897 B911 B927:B928 B930 B932:B933 B942 B950:B1048576 B1:B8 B11:B15 B18:B19 B22 B24 B30:B31 B34 B39:B41 B43 B46 B48:B50 B53 B56:B58 B62:B64 B74:B94 B96:B106 B108:B111 B114:B119 B122 B124:B126 B128:B152 B154:B155 B157 B159:B164 B166:B167 B169:B170 B179 B181 B183:B184 B186:B188 B190:B202 B204:B205 B209:B212 B214 B216:B217 B219:B220 B222:B229 B468">
+  <conditionalFormatting sqref="B714 B573:B574 B231:B232 B239:B240 B242:B244 B251 B258:B261 B264:B269 B273 B278 B288:B289 B291 B295:B299 B306:B307 B324 B331 B333 B337:B338 B340:B341 B343 B348 B345:B346 B351 B364 B372:B373 B378:B380 B389:B390 B396:B397 B401 B420 B430 B433 B438:B439 B442 B444 B448 B451 B459 B463 B466 B475:B476 B480 B488 B492:B495 B507 B514 B519 B524 B528:B529 B531:B535 B537 B539 B560 B576 B590 B599:B600 B623:B624 B649:B655 B670 B686 B694:B696 B702 B717 B723 B734 B737 B741 B745 B752 B754 B760 B770 B786 B789 B797 B799:B800 B806:B807 B812:B814 B836 B839 B842 B855:B858 B869 B871 B873:B874 B878 B881 B886:B887 B891 B893 B895:B896 B907 B909 B928 B942 B958:B959 B961 B963:B964 B973 B981:B1048576 B1:B8 B11:B15 B18:B19 B22 B24 B30:B31 B34 B39:B41 B43 B46 B48:B50 B53 B56:B58 B62:B64 B74:B94 B96:B106 B108:B111 B114:B119 B122 B124:B126 B128:B152 B154:B155 B157 B159:B164 B166:B167 B169:B170 B179 B181 B183:B184 B186:B188 B190:B202 B204:B205 B209:B212 B214 B216:B217 B219:B220 B222:B229 B468">
     <cfRule type="duplicateValues" dxfId="913" priority="2694"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B683 B686 B692 B703 B706 B710 B714 B721 B723 B729 B739 B755 B758 B766 B768:B769 B775:B776 B781:B783 B805 B808 B811 B824:B827 B838 B840 B842:B843 B847 B850 B855:B856 B860 B862 B864:B865 B876 B878 B897 B911 B927:B928 B930 B932:B933 B942 B950:B1048576 B1:B8 B11:B15 B18:B19 B22 B24 B30:B31 B34 B39:B41 B43 B46 B48:B50 B53 B56:B58 B62:B64 B74:B94 B96:B106 B108:B111 B114:B119 B122 B124:B126 B128:B152 B154:B155 B157 B159:B164 B166:B167 B169:B170 B179 B181 B183:B184 B186:B188 B190:B202 B204:B205 B209:B212 B214 B216:B217 B219:B220 B222:B229 B231:B232 B237:B249 B251:B252 B255 B258:B261 B263:B269 B271 B273:B279 B281:B283 B286:B310 B312 B315 B317:B318 B320:B321 B324 B329:B353 B355:B361 B363:B368 B370:B383 B385:B390 B392:B414 B416:B417 B420:B440 B442:B455 B457:B463 B465:B466 B468:B470 B473:B476 B478:B482 B484 B486 B488:B490 B492:B498 B501:B504 B507:B510 B512:B547 B549 B551:B558 B560 B562:B569 B571:B584 B586:B587 B589:B596 B599:B674">
+  <conditionalFormatting sqref="B714 B717 B723 B734 B737 B741 B745 B752 B754 B760 B770 B786 B789 B797 B799:B800 B806:B807 B812:B814 B836 B839 B842 B855:B858 B869 B871 B873:B874 B878 B881 B886:B887 B891 B893 B895:B896 B907 B909 B928 B942 B958:B959 B961 B963:B964 B973 B981:B1048576 B1:B8 B11:B15 B18:B19 B22 B24 B30:B31 B34 B39:B41 B43 B46 B48:B50 B53 B56:B58 B62:B64 B74:B94 B96:B106 B108:B111 B114:B119 B122 B124:B126 B128:B152 B154:B155 B157 B159:B164 B166:B167 B169:B170 B179 B181 B183:B184 B186:B188 B190:B202 B204:B205 B209:B212 B214 B216:B217 B219:B220 B222:B229 B231:B232 B237:B249 B251:B252 B255 B258:B261 B263:B269 B271 B273:B279 B281:B283 B286:B310 B312 B315 B317:B318 B320:B321 B324 B329:B353 B355:B361 B363:B368 B370:B383 B385:B390 B392:B414 B416:B417 B420:B440 B442:B455 B457:B463 B465:B466 B468:B470 B473:B476 B478:B482 B484 B486 B488:B490 B492:B498 B501:B504 B507:B510 B512:B547 B549 B551:B558 B560 B562:B569 B571:B584 B586:B587 B589:B596 B599:B705">
     <cfRule type="duplicateValues" dxfId="912" priority="2780"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B733">
+  <conditionalFormatting sqref="B764">
     <cfRule type="duplicateValues" dxfId="911" priority="1234"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B733">
+  <conditionalFormatting sqref="B764">
     <cfRule type="duplicateValues" dxfId="910" priority="1235"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B733">
+  <conditionalFormatting sqref="B764">
     <cfRule type="duplicateValues" dxfId="909" priority="1236"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B734">
+  <conditionalFormatting sqref="B765">
     <cfRule type="duplicateValues" dxfId="908" priority="1229"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B734">
+  <conditionalFormatting sqref="B765">
     <cfRule type="duplicateValues" dxfId="907" priority="1228"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B734">
+  <conditionalFormatting sqref="B765">
     <cfRule type="duplicateValues" dxfId="906" priority="1230"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B735">
+  <conditionalFormatting sqref="B766">
     <cfRule type="duplicateValues" dxfId="905" priority="1225"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B735">
+  <conditionalFormatting sqref="B766">
     <cfRule type="duplicateValues" dxfId="904" priority="1226"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B735">
+  <conditionalFormatting sqref="B766">
     <cfRule type="duplicateValues" dxfId="903" priority="1227"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B736">
+  <conditionalFormatting sqref="B767">
     <cfRule type="duplicateValues" dxfId="902" priority="1220"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B736">
+  <conditionalFormatting sqref="B767">
     <cfRule type="duplicateValues" dxfId="901" priority="1221"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B736">
+  <conditionalFormatting sqref="B767">
     <cfRule type="duplicateValues" dxfId="900" priority="1219"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B737">
+  <conditionalFormatting sqref="B768">
     <cfRule type="duplicateValues" dxfId="899" priority="1213"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B737">
+  <conditionalFormatting sqref="B768">
     <cfRule type="duplicateValues" dxfId="898" priority="1214"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B737">
+  <conditionalFormatting sqref="B768">
     <cfRule type="duplicateValues" dxfId="897" priority="1215"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B738">
+  <conditionalFormatting sqref="B769">
     <cfRule type="duplicateValues" dxfId="896" priority="1211"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B738">
+  <conditionalFormatting sqref="B769">
     <cfRule type="duplicateValues" dxfId="895" priority="1212"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B738">
+  <conditionalFormatting sqref="B769">
     <cfRule type="duplicateValues" dxfId="894" priority="1210"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B740">
+  <conditionalFormatting sqref="B771">
     <cfRule type="duplicateValues" dxfId="893" priority="1205"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B740">
+  <conditionalFormatting sqref="B771">
     <cfRule type="duplicateValues" dxfId="892" priority="1206"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B741">
+  <conditionalFormatting sqref="B772">
     <cfRule type="duplicateValues" dxfId="891" priority="1203"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B741">
+  <conditionalFormatting sqref="B772">
     <cfRule type="duplicateValues" dxfId="890" priority="1202"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B741">
+  <conditionalFormatting sqref="B772">
     <cfRule type="duplicateValues" dxfId="889" priority="1204"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B742">
+  <conditionalFormatting sqref="B773">
     <cfRule type="duplicateValues" dxfId="888" priority="1196"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B742">
+  <conditionalFormatting sqref="B773">
     <cfRule type="duplicateValues" dxfId="887" priority="1197"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B742">
+  <conditionalFormatting sqref="B773">
     <cfRule type="duplicateValues" dxfId="886" priority="1198"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B743">
+  <conditionalFormatting sqref="B774">
     <cfRule type="duplicateValues" dxfId="885" priority="1193"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B743">
+  <conditionalFormatting sqref="B774">
     <cfRule type="duplicateValues" dxfId="884" priority="1194"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B743">
+  <conditionalFormatting sqref="B774">
     <cfRule type="duplicateValues" dxfId="883" priority="1195"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B744">
+  <conditionalFormatting sqref="B775">
     <cfRule type="duplicateValues" dxfId="882" priority="1187"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B744">
+  <conditionalFormatting sqref="B775">
     <cfRule type="duplicateValues" dxfId="881" priority="1188"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B744">
+  <conditionalFormatting sqref="B775">
     <cfRule type="duplicateValues" dxfId="880" priority="1189"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B745">
+  <conditionalFormatting sqref="B776">
     <cfRule type="duplicateValues" dxfId="879" priority="1172"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B745">
+  <conditionalFormatting sqref="B776">
     <cfRule type="duplicateValues" dxfId="878" priority="1173"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B745">
+  <conditionalFormatting sqref="B776">
     <cfRule type="duplicateValues" dxfId="877" priority="1174"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B746">
+  <conditionalFormatting sqref="B777">
     <cfRule type="duplicateValues" dxfId="876" priority="1166"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B746">
+  <conditionalFormatting sqref="B777">
     <cfRule type="duplicateValues" dxfId="875" priority="1167"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B746">
+  <conditionalFormatting sqref="B777">
     <cfRule type="duplicateValues" dxfId="874" priority="1168"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B747">
+  <conditionalFormatting sqref="B778">
     <cfRule type="duplicateValues" dxfId="873" priority="1160"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B747">
+  <conditionalFormatting sqref="B778">
     <cfRule type="duplicateValues" dxfId="872" priority="1161"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B747">
+  <conditionalFormatting sqref="B778">
     <cfRule type="duplicateValues" dxfId="871" priority="1162"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B748">
+  <conditionalFormatting sqref="B779">
     <cfRule type="duplicateValues" dxfId="870" priority="1158"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B748">
+  <conditionalFormatting sqref="B779">
     <cfRule type="duplicateValues" dxfId="869" priority="1159"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B748">
+  <conditionalFormatting sqref="B779">
     <cfRule type="duplicateValues" dxfId="868" priority="1157"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B749">
+  <conditionalFormatting sqref="B780">
     <cfRule type="duplicateValues" dxfId="867" priority="1148"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B749">
+  <conditionalFormatting sqref="B780">
     <cfRule type="duplicateValues" dxfId="866" priority="1149"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B749">
+  <conditionalFormatting sqref="B780">
     <cfRule type="duplicateValues" dxfId="865" priority="1150"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B750">
+  <conditionalFormatting sqref="B781">
     <cfRule type="duplicateValues" dxfId="864" priority="1140"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B750">
+  <conditionalFormatting sqref="B781">
     <cfRule type="duplicateValues" dxfId="863" priority="1139"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B750">
+  <conditionalFormatting sqref="B781">
     <cfRule type="duplicateValues" dxfId="862" priority="1141"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B751">
+  <conditionalFormatting sqref="B782">
     <cfRule type="duplicateValues" dxfId="861" priority="1137"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B751">
+  <conditionalFormatting sqref="B782">
     <cfRule type="duplicateValues" dxfId="860" priority="1136"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B751">
+  <conditionalFormatting sqref="B782">
     <cfRule type="duplicateValues" dxfId="859" priority="1138"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B752">
+  <conditionalFormatting sqref="B783">
     <cfRule type="duplicateValues" dxfId="858" priority="1131"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B752">
+  <conditionalFormatting sqref="B783">
     <cfRule type="duplicateValues" dxfId="857" priority="1132"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B752">
+  <conditionalFormatting sqref="B783">
     <cfRule type="duplicateValues" dxfId="856" priority="1130"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B753">
+  <conditionalFormatting sqref="B784">
     <cfRule type="duplicateValues" dxfId="855" priority="1124"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B753">
+  <conditionalFormatting sqref="B784">
     <cfRule type="duplicateValues" dxfId="854" priority="1125"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B753">
+  <conditionalFormatting sqref="B784">
     <cfRule type="duplicateValues" dxfId="853" priority="1126"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B754">
+  <conditionalFormatting sqref="B785">
     <cfRule type="duplicateValues" dxfId="852" priority="1121"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B754">
+  <conditionalFormatting sqref="B785">
     <cfRule type="duplicateValues" dxfId="851" priority="1122"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B754">
+  <conditionalFormatting sqref="B785">
     <cfRule type="duplicateValues" dxfId="850" priority="1123"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B756">
+  <conditionalFormatting sqref="B787">
     <cfRule type="duplicateValues" dxfId="849" priority="1118"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B756">
+  <conditionalFormatting sqref="B787">
     <cfRule type="duplicateValues" dxfId="848" priority="1119"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B756">
+  <conditionalFormatting sqref="B787">
     <cfRule type="duplicateValues" dxfId="847" priority="1120"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B757">
+  <conditionalFormatting sqref="B788">
     <cfRule type="duplicateValues" dxfId="846" priority="1115"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B757">
+  <conditionalFormatting sqref="B788">
     <cfRule type="duplicateValues" dxfId="845" priority="1116"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B757">
+  <conditionalFormatting sqref="B788">
     <cfRule type="duplicateValues" dxfId="844" priority="1117"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B759">
+  <conditionalFormatting sqref="B790">
     <cfRule type="duplicateValues" dxfId="843" priority="1114"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B759">
+  <conditionalFormatting sqref="B790">
     <cfRule type="duplicateValues" dxfId="842" priority="1113"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B759">
+  <conditionalFormatting sqref="B790">
     <cfRule type="duplicateValues" dxfId="841" priority="1112"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B760">
+  <conditionalFormatting sqref="B791">
     <cfRule type="duplicateValues" dxfId="840" priority="1109"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B760">
+  <conditionalFormatting sqref="B791">
     <cfRule type="duplicateValues" dxfId="839" priority="1110"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B760">
+  <conditionalFormatting sqref="B791">
     <cfRule type="duplicateValues" dxfId="838" priority="1111"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B761">
+  <conditionalFormatting sqref="B792">
     <cfRule type="duplicateValues" dxfId="837" priority="1106"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B761">
+  <conditionalFormatting sqref="B792">
     <cfRule type="duplicateValues" dxfId="836" priority="1107"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B761">
+  <conditionalFormatting sqref="B792">
     <cfRule type="duplicateValues" dxfId="835" priority="1108"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B764">
+  <conditionalFormatting sqref="B795">
     <cfRule type="duplicateValues" dxfId="834" priority="1104"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B764">
+  <conditionalFormatting sqref="B795">
     <cfRule type="duplicateValues" dxfId="833" priority="1105"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B764">
+  <conditionalFormatting sqref="B795">
     <cfRule type="duplicateValues" dxfId="832" priority="1103"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B762">
+  <conditionalFormatting sqref="B793">
     <cfRule type="duplicateValues" dxfId="831" priority="1101"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B762">
+  <conditionalFormatting sqref="B793">
     <cfRule type="duplicateValues" dxfId="830" priority="1102"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B763">
+  <conditionalFormatting sqref="B794">
     <cfRule type="duplicateValues" dxfId="829" priority="1096"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B763">
+  <conditionalFormatting sqref="B794">
     <cfRule type="duplicateValues" dxfId="828" priority="1097"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B765">
+  <conditionalFormatting sqref="B796">
     <cfRule type="duplicateValues" dxfId="827" priority="1091"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B765">
+  <conditionalFormatting sqref="B796">
     <cfRule type="duplicateValues" dxfId="826" priority="1092"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B765">
+  <conditionalFormatting sqref="B796">
     <cfRule type="duplicateValues" dxfId="825" priority="1090"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B767">
+  <conditionalFormatting sqref="B798">
     <cfRule type="duplicateValues" dxfId="824" priority="1087"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B767">
+  <conditionalFormatting sqref="B798">
     <cfRule type="duplicateValues" dxfId="823" priority="1088"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B767">
+  <conditionalFormatting sqref="B798">
     <cfRule type="duplicateValues" dxfId="822" priority="1089"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B770">
+  <conditionalFormatting sqref="B801">
     <cfRule type="duplicateValues" dxfId="821" priority="1084"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B770">
+  <conditionalFormatting sqref="B801">
     <cfRule type="duplicateValues" dxfId="820" priority="1085"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B770">
+  <conditionalFormatting sqref="B801">
     <cfRule type="duplicateValues" dxfId="819" priority="1086"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B771">
+  <conditionalFormatting sqref="B802">
     <cfRule type="duplicateValues" dxfId="818" priority="1081"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B771">
+  <conditionalFormatting sqref="B802">
     <cfRule type="duplicateValues" dxfId="817" priority="1082"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B771">
+  <conditionalFormatting sqref="B802">
     <cfRule type="duplicateValues" dxfId="816" priority="1083"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B772">
+  <conditionalFormatting sqref="B803">
     <cfRule type="duplicateValues" dxfId="815" priority="1078"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B772">
+  <conditionalFormatting sqref="B803">
     <cfRule type="duplicateValues" dxfId="814" priority="1079"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B772">
+  <conditionalFormatting sqref="B803">
     <cfRule type="duplicateValues" dxfId="813" priority="1080"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B773">
+  <conditionalFormatting sqref="B804">
     <cfRule type="duplicateValues" dxfId="812" priority="1066"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B773">
+  <conditionalFormatting sqref="B804">
     <cfRule type="duplicateValues" dxfId="811" priority="1067"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B773">
+  <conditionalFormatting sqref="B804">
     <cfRule type="duplicateValues" dxfId="810" priority="1068"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B774">
+  <conditionalFormatting sqref="B805">
     <cfRule type="duplicateValues" dxfId="809" priority="1061"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B774">
+  <conditionalFormatting sqref="B805">
     <cfRule type="duplicateValues" dxfId="808" priority="1062"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B777">
+  <conditionalFormatting sqref="B808">
     <cfRule type="duplicateValues" dxfId="807" priority="1055"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B777">
+  <conditionalFormatting sqref="B808">
     <cfRule type="duplicateValues" dxfId="806" priority="1056"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B777">
+  <conditionalFormatting sqref="B808">
     <cfRule type="duplicateValues" dxfId="805" priority="1057"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B778">
+  <conditionalFormatting sqref="B809">
     <cfRule type="duplicateValues" dxfId="804" priority="1049"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B778">
+  <conditionalFormatting sqref="B809">
     <cfRule type="duplicateValues" dxfId="803" priority="1050"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B778">
+  <conditionalFormatting sqref="B809">
     <cfRule type="duplicateValues" dxfId="802" priority="1051"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B779">
+  <conditionalFormatting sqref="B810">
     <cfRule type="duplicateValues" dxfId="801" priority="1046"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B779">
+  <conditionalFormatting sqref="B810">
     <cfRule type="duplicateValues" dxfId="800" priority="1047"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B779">
+  <conditionalFormatting sqref="B810">
     <cfRule type="duplicateValues" dxfId="799" priority="1048"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B780">
+  <conditionalFormatting sqref="B811">
     <cfRule type="duplicateValues" dxfId="798" priority="1040"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B780">
+  <conditionalFormatting sqref="B811">
     <cfRule type="duplicateValues" dxfId="797" priority="1041"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B780">
+  <conditionalFormatting sqref="B811">
     <cfRule type="duplicateValues" dxfId="796" priority="1042"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B784">
+  <conditionalFormatting sqref="B815">
     <cfRule type="duplicateValues" dxfId="795" priority="1031"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B784">
+  <conditionalFormatting sqref="B815">
     <cfRule type="duplicateValues" dxfId="794" priority="1032"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B784">
+  <conditionalFormatting sqref="B815">
     <cfRule type="duplicateValues" dxfId="793" priority="1033"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B785">
+  <conditionalFormatting sqref="B816">
     <cfRule type="duplicateValues" dxfId="792" priority="1028"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B785">
+  <conditionalFormatting sqref="B816">
     <cfRule type="duplicateValues" dxfId="791" priority="1029"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B785">
+  <conditionalFormatting sqref="B816">
     <cfRule type="duplicateValues" dxfId="790" priority="1030"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B786">
+  <conditionalFormatting sqref="B817">
     <cfRule type="duplicateValues" dxfId="789" priority="1022"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B786">
+  <conditionalFormatting sqref="B817">
     <cfRule type="duplicateValues" dxfId="788" priority="1023"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B786">
+  <conditionalFormatting sqref="B817">
     <cfRule type="duplicateValues" dxfId="787" priority="1024"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B787">
+  <conditionalFormatting sqref="B818">
     <cfRule type="duplicateValues" dxfId="786" priority="1013"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B787">
+  <conditionalFormatting sqref="B818">
     <cfRule type="duplicateValues" dxfId="785" priority="1014"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B787">
+  <conditionalFormatting sqref="B818">
     <cfRule type="duplicateValues" dxfId="784" priority="1015"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B788">
+  <conditionalFormatting sqref="B819">
     <cfRule type="duplicateValues" dxfId="783" priority="1010"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B788">
+  <conditionalFormatting sqref="B819">
     <cfRule type="duplicateValues" dxfId="782" priority="1011"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B788">
+  <conditionalFormatting sqref="B819">
     <cfRule type="duplicateValues" dxfId="781" priority="1012"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B789">
+  <conditionalFormatting sqref="B820">
     <cfRule type="duplicateValues" dxfId="780" priority="1004"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B789">
+  <conditionalFormatting sqref="B820">
     <cfRule type="duplicateValues" dxfId="779" priority="1005"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B789">
+  <conditionalFormatting sqref="B820">
     <cfRule type="duplicateValues" dxfId="778" priority="1006"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B790">
+  <conditionalFormatting sqref="B821">
     <cfRule type="duplicateValues" dxfId="777" priority="1002"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B790">
+  <conditionalFormatting sqref="B821">
     <cfRule type="duplicateValues" dxfId="776" priority="1003"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B790">
+  <conditionalFormatting sqref="B821">
     <cfRule type="duplicateValues" dxfId="775" priority="1001"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B791">
+  <conditionalFormatting sqref="B822">
     <cfRule type="duplicateValues" dxfId="774" priority="998"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B791">
+  <conditionalFormatting sqref="B822">
     <cfRule type="duplicateValues" dxfId="773" priority="999"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B791">
+  <conditionalFormatting sqref="B822">
     <cfRule type="duplicateValues" dxfId="772" priority="1000"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B792">
+  <conditionalFormatting sqref="B823">
     <cfRule type="duplicateValues" dxfId="771" priority="996"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B792">
+  <conditionalFormatting sqref="B823">
     <cfRule type="duplicateValues" dxfId="770" priority="995"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B792">
+  <conditionalFormatting sqref="B823">
     <cfRule type="duplicateValues" dxfId="769" priority="997"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B793">
+  <conditionalFormatting sqref="B824">
     <cfRule type="duplicateValues" dxfId="768" priority="986"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B793">
+  <conditionalFormatting sqref="B824">
     <cfRule type="duplicateValues" dxfId="767" priority="987"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B793">
+  <conditionalFormatting sqref="B824">
     <cfRule type="duplicateValues" dxfId="766" priority="988"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B794">
+  <conditionalFormatting sqref="B825">
     <cfRule type="duplicateValues" dxfId="765" priority="983"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B794">
+  <conditionalFormatting sqref="B825">
     <cfRule type="duplicateValues" dxfId="764" priority="984"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B794">
+  <conditionalFormatting sqref="B825">
     <cfRule type="duplicateValues" dxfId="763" priority="985"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B795">
+  <conditionalFormatting sqref="B826">
     <cfRule type="duplicateValues" dxfId="762" priority="980"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B795">
+  <conditionalFormatting sqref="B826">
     <cfRule type="duplicateValues" dxfId="761" priority="981"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B795">
+  <conditionalFormatting sqref="B826">
     <cfRule type="duplicateValues" dxfId="760" priority="982"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B796">
+  <conditionalFormatting sqref="B827">
     <cfRule type="duplicateValues" dxfId="759" priority="977"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B796">
+  <conditionalFormatting sqref="B827">
     <cfRule type="duplicateValues" dxfId="758" priority="978"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B796">
+  <conditionalFormatting sqref="B827">
     <cfRule type="duplicateValues" dxfId="757" priority="979"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B797">
+  <conditionalFormatting sqref="B828">
     <cfRule type="duplicateValues" dxfId="756" priority="974"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B797">
+  <conditionalFormatting sqref="B828">
     <cfRule type="duplicateValues" dxfId="755" priority="975"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B797">
+  <conditionalFormatting sqref="B828">
     <cfRule type="duplicateValues" dxfId="754" priority="976"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B798">
+  <conditionalFormatting sqref="B829">
     <cfRule type="duplicateValues" dxfId="753" priority="971"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B798">
+  <conditionalFormatting sqref="B829">
     <cfRule type="duplicateValues" dxfId="752" priority="972"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B798">
+  <conditionalFormatting sqref="B829">
     <cfRule type="duplicateValues" dxfId="751" priority="973"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B799">
+  <conditionalFormatting sqref="B830">
     <cfRule type="duplicateValues" dxfId="750" priority="965"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B799">
+  <conditionalFormatting sqref="B830">
     <cfRule type="duplicateValues" dxfId="749" priority="966"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B799">
+  <conditionalFormatting sqref="B830">
     <cfRule type="duplicateValues" dxfId="748" priority="967"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B800">
+  <conditionalFormatting sqref="B831">
     <cfRule type="duplicateValues" dxfId="747" priority="962"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B800">
+  <conditionalFormatting sqref="B831">
     <cfRule type="duplicateValues" dxfId="746" priority="963"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B800">
+  <conditionalFormatting sqref="B831">
     <cfRule type="duplicateValues" dxfId="745" priority="964"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B801">
+  <conditionalFormatting sqref="B832">
     <cfRule type="duplicateValues" dxfId="744" priority="954"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B801">
+  <conditionalFormatting sqref="B832">
     <cfRule type="duplicateValues" dxfId="743" priority="955"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B802">
+  <conditionalFormatting sqref="B833">
     <cfRule type="duplicateValues" dxfId="742" priority="949"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B802">
+  <conditionalFormatting sqref="B833">
     <cfRule type="duplicateValues" dxfId="741" priority="950"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B803">
+  <conditionalFormatting sqref="B834">
     <cfRule type="duplicateValues" dxfId="740" priority="947"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B803">
+  <conditionalFormatting sqref="B834">
     <cfRule type="duplicateValues" dxfId="739" priority="946"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B803">
+  <conditionalFormatting sqref="B834">
     <cfRule type="duplicateValues" dxfId="738" priority="948"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B804">
+  <conditionalFormatting sqref="B835">
     <cfRule type="duplicateValues" dxfId="737" priority="937"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B804">
+  <conditionalFormatting sqref="B835">
     <cfRule type="duplicateValues" dxfId="736" priority="938"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B804">
+  <conditionalFormatting sqref="B835">
     <cfRule type="duplicateValues" dxfId="735" priority="939"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B806">
+  <conditionalFormatting sqref="B837">
     <cfRule type="duplicateValues" dxfId="734" priority="934"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B806">
+  <conditionalFormatting sqref="B837">
     <cfRule type="duplicateValues" dxfId="733" priority="935"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B806">
+  <conditionalFormatting sqref="B837">
     <cfRule type="duplicateValues" dxfId="732" priority="936"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B807">
+  <conditionalFormatting sqref="B838">
     <cfRule type="duplicateValues" dxfId="731" priority="931"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B807">
+  <conditionalFormatting sqref="B838">
     <cfRule type="duplicateValues" dxfId="730" priority="932"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B807">
+  <conditionalFormatting sqref="B838">
     <cfRule type="duplicateValues" dxfId="729" priority="933"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B809">
+  <conditionalFormatting sqref="B840">
     <cfRule type="duplicateValues" dxfId="728" priority="928"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B809">
+  <conditionalFormatting sqref="B840">
     <cfRule type="duplicateValues" dxfId="727" priority="929"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B809">
+  <conditionalFormatting sqref="B840">
     <cfRule type="duplicateValues" dxfId="726" priority="930"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B810">
+  <conditionalFormatting sqref="B841">
     <cfRule type="duplicateValues" dxfId="725" priority="926"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B810">
+  <conditionalFormatting sqref="B841">
     <cfRule type="duplicateValues" dxfId="724" priority="927"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B812">
+  <conditionalFormatting sqref="B843">
     <cfRule type="duplicateValues" dxfId="723" priority="918"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B812">
+  <conditionalFormatting sqref="B843">
     <cfRule type="duplicateValues" dxfId="722" priority="917"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B812">
+  <conditionalFormatting sqref="B843">
     <cfRule type="duplicateValues" dxfId="721" priority="919"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B813">
+  <conditionalFormatting sqref="B844">
     <cfRule type="duplicateValues" dxfId="720" priority="911"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B813">
+  <conditionalFormatting sqref="B844">
     <cfRule type="duplicateValues" dxfId="719" priority="912"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B813">
+  <conditionalFormatting sqref="B844">
     <cfRule type="duplicateValues" dxfId="718" priority="913"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B814">
+  <conditionalFormatting sqref="B845">
     <cfRule type="duplicateValues" dxfId="717" priority="908"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B814">
+  <conditionalFormatting sqref="B845">
     <cfRule type="duplicateValues" dxfId="716" priority="909"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B814">
+  <conditionalFormatting sqref="B845">
     <cfRule type="duplicateValues" dxfId="715" priority="910"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B815">
+  <conditionalFormatting sqref="B846">
     <cfRule type="duplicateValues" dxfId="714" priority="905"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B815">
+  <conditionalFormatting sqref="B846">
     <cfRule type="duplicateValues" dxfId="713" priority="906"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B815">
+  <conditionalFormatting sqref="B846">
     <cfRule type="duplicateValues" dxfId="712" priority="907"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B816">
+  <conditionalFormatting sqref="B847">
     <cfRule type="duplicateValues" dxfId="711" priority="902"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B816">
+  <conditionalFormatting sqref="B847">
     <cfRule type="duplicateValues" dxfId="710" priority="903"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B816">
+  <conditionalFormatting sqref="B847">
     <cfRule type="duplicateValues" dxfId="709" priority="904"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B817">
+  <conditionalFormatting sqref="B848">
     <cfRule type="duplicateValues" dxfId="708" priority="899"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B817">
+  <conditionalFormatting sqref="B848">
     <cfRule type="duplicateValues" dxfId="707" priority="900"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B817">
+  <conditionalFormatting sqref="B848">
     <cfRule type="duplicateValues" dxfId="706" priority="901"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B818">
+  <conditionalFormatting sqref="B849">
     <cfRule type="duplicateValues" dxfId="705" priority="896"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B818">
+  <conditionalFormatting sqref="B849">
     <cfRule type="duplicateValues" dxfId="704" priority="897"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B818">
+  <conditionalFormatting sqref="B849">
     <cfRule type="duplicateValues" dxfId="703" priority="898"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B819">
+  <conditionalFormatting sqref="B850">
     <cfRule type="duplicateValues" dxfId="702" priority="890"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B819">
+  <conditionalFormatting sqref="B850">
     <cfRule type="duplicateValues" dxfId="701" priority="891"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B819">
+  <conditionalFormatting sqref="B850">
     <cfRule type="duplicateValues" dxfId="700" priority="892"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B820">
+  <conditionalFormatting sqref="B851">
     <cfRule type="duplicateValues" dxfId="699" priority="887"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B820">
+  <conditionalFormatting sqref="B851">
     <cfRule type="duplicateValues" dxfId="698" priority="888"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B820">
+  <conditionalFormatting sqref="B851">
     <cfRule type="duplicateValues" dxfId="697" priority="889"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B821">
+  <conditionalFormatting sqref="B852">
     <cfRule type="duplicateValues" dxfId="696" priority="884"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B821">
+  <conditionalFormatting sqref="B852">
     <cfRule type="duplicateValues" dxfId="695" priority="885"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B821">
+  <conditionalFormatting sqref="B852">
     <cfRule type="duplicateValues" dxfId="694" priority="886"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B822">
+  <conditionalFormatting sqref="B853">
     <cfRule type="duplicateValues" dxfId="693" priority="882"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B822">
+  <conditionalFormatting sqref="B853">
     <cfRule type="duplicateValues" dxfId="692" priority="883"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B823">
+  <conditionalFormatting sqref="B854">
     <cfRule type="duplicateValues" dxfId="691" priority="879"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B823">
+  <conditionalFormatting sqref="B854">
     <cfRule type="duplicateValues" dxfId="690" priority="880"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B823">
+  <conditionalFormatting sqref="B854">
     <cfRule type="duplicateValues" dxfId="689" priority="881"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B828">
+  <conditionalFormatting sqref="B859">
     <cfRule type="duplicateValues" dxfId="688" priority="876"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B828">
+  <conditionalFormatting sqref="B859">
     <cfRule type="duplicateValues" dxfId="687" priority="877"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B828">
+  <conditionalFormatting sqref="B859">
     <cfRule type="duplicateValues" dxfId="686" priority="878"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B829">
+  <conditionalFormatting sqref="B860">
     <cfRule type="duplicateValues" dxfId="685" priority="867"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B829">
+  <conditionalFormatting sqref="B860">
     <cfRule type="duplicateValues" dxfId="684" priority="868"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B829">
+  <conditionalFormatting sqref="B860">
     <cfRule type="duplicateValues" dxfId="683" priority="869"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B830">
+  <conditionalFormatting sqref="B861">
     <cfRule type="duplicateValues" dxfId="682" priority="864"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B830">
+  <conditionalFormatting sqref="B861">
     <cfRule type="duplicateValues" dxfId="681" priority="865"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B830">
+  <conditionalFormatting sqref="B861">
     <cfRule type="duplicateValues" dxfId="680" priority="866"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B831">
+  <conditionalFormatting sqref="B862">
     <cfRule type="duplicateValues" dxfId="679" priority="861"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B831">
+  <conditionalFormatting sqref="B862">
     <cfRule type="duplicateValues" dxfId="678" priority="862"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B831">
+  <conditionalFormatting sqref="B862">
     <cfRule type="duplicateValues" dxfId="677" priority="863"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B832">
+  <conditionalFormatting sqref="B863">
     <cfRule type="duplicateValues" dxfId="676" priority="858"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B832">
+  <conditionalFormatting sqref="B863">
     <cfRule type="duplicateValues" dxfId="675" priority="859"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B832">
+  <conditionalFormatting sqref="B863">
     <cfRule type="duplicateValues" dxfId="674" priority="860"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B833">
+  <conditionalFormatting sqref="B864">
     <cfRule type="duplicateValues" dxfId="673" priority="855"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B833">
+  <conditionalFormatting sqref="B864">
     <cfRule type="duplicateValues" dxfId="672" priority="856"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B833">
+  <conditionalFormatting sqref="B864">
     <cfRule type="duplicateValues" dxfId="671" priority="857"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B834">
+  <conditionalFormatting sqref="B865">
     <cfRule type="duplicateValues" dxfId="670" priority="853"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B834">
+  <conditionalFormatting sqref="B865">
     <cfRule type="duplicateValues" dxfId="669" priority="852"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B834">
+  <conditionalFormatting sqref="B865">
     <cfRule type="duplicateValues" dxfId="668" priority="854"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B835">
+  <conditionalFormatting sqref="B866">
     <cfRule type="duplicateValues" dxfId="667" priority="849"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B835">
+  <conditionalFormatting sqref="B866">
     <cfRule type="duplicateValues" dxfId="666" priority="850"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B835">
+  <conditionalFormatting sqref="B866">
     <cfRule type="duplicateValues" dxfId="665" priority="851"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B836">
+  <conditionalFormatting sqref="B867">
     <cfRule type="duplicateValues" dxfId="664" priority="846"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B836">
+  <conditionalFormatting sqref="B867">
     <cfRule type="duplicateValues" dxfId="663" priority="847"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B836">
+  <conditionalFormatting sqref="B867">
     <cfRule type="duplicateValues" dxfId="662" priority="848"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B837">
+  <conditionalFormatting sqref="B868">
     <cfRule type="duplicateValues" dxfId="661" priority="840"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B837">
+  <conditionalFormatting sqref="B868">
     <cfRule type="duplicateValues" dxfId="660" priority="841"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B837">
+  <conditionalFormatting sqref="B868">
     <cfRule type="duplicateValues" dxfId="659" priority="842"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B839">
+  <conditionalFormatting sqref="B870">
     <cfRule type="duplicateValues" dxfId="658" priority="837"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B839">
+  <conditionalFormatting sqref="B870">
     <cfRule type="duplicateValues" dxfId="657" priority="838"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B839">
+  <conditionalFormatting sqref="B870">
     <cfRule type="duplicateValues" dxfId="656" priority="839"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B841">
+  <conditionalFormatting sqref="B872">
     <cfRule type="duplicateValues" dxfId="655" priority="834"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B841">
+  <conditionalFormatting sqref="B872">
     <cfRule type="duplicateValues" dxfId="654" priority="835"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B841">
+  <conditionalFormatting sqref="B872">
     <cfRule type="duplicateValues" dxfId="653" priority="836"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B844">
+  <conditionalFormatting sqref="B875">
     <cfRule type="duplicateValues" dxfId="652" priority="831"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B844">
+  <conditionalFormatting sqref="B875">
     <cfRule type="duplicateValues" dxfId="651" priority="832"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B844">
+  <conditionalFormatting sqref="B875">
     <cfRule type="duplicateValues" dxfId="650" priority="833"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B845">
+  <conditionalFormatting sqref="B876">
     <cfRule type="duplicateValues" dxfId="649" priority="828"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B845">
+  <conditionalFormatting sqref="B876">
     <cfRule type="duplicateValues" dxfId="648" priority="829"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B845">
+  <conditionalFormatting sqref="B876">
     <cfRule type="duplicateValues" dxfId="647" priority="830"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B846">
+  <conditionalFormatting sqref="B877">
     <cfRule type="duplicateValues" dxfId="646" priority="825"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B846">
+  <conditionalFormatting sqref="B877">
     <cfRule type="duplicateValues" dxfId="645" priority="826"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B846">
+  <conditionalFormatting sqref="B877">
     <cfRule type="duplicateValues" dxfId="644" priority="827"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B848">
+  <conditionalFormatting sqref="B879">
     <cfRule type="duplicateValues" dxfId="643" priority="819"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B848">
+  <conditionalFormatting sqref="B879">
     <cfRule type="duplicateValues" dxfId="642" priority="820"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B848">
+  <conditionalFormatting sqref="B879">
     <cfRule type="duplicateValues" dxfId="641" priority="821"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B849">
+  <conditionalFormatting sqref="B880">
     <cfRule type="duplicateValues" dxfId="640" priority="813"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B849">
+  <conditionalFormatting sqref="B880">
     <cfRule type="duplicateValues" dxfId="639" priority="814"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B849">
+  <conditionalFormatting sqref="B880">
     <cfRule type="duplicateValues" dxfId="638" priority="815"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B851">
+  <conditionalFormatting sqref="B882">
     <cfRule type="duplicateValues" dxfId="637" priority="810"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B851">
+  <conditionalFormatting sqref="B882">
     <cfRule type="duplicateValues" dxfId="636" priority="811"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B851">
+  <conditionalFormatting sqref="B882">
     <cfRule type="duplicateValues" dxfId="635" priority="812"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B852">
+  <conditionalFormatting sqref="B883">
     <cfRule type="duplicateValues" dxfId="634" priority="801"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B852">
+  <conditionalFormatting sqref="B883">
     <cfRule type="duplicateValues" dxfId="633" priority="802"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B852">
+  <conditionalFormatting sqref="B883">
     <cfRule type="duplicateValues" dxfId="632" priority="803"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B853">
+  <conditionalFormatting sqref="B884">
     <cfRule type="duplicateValues" dxfId="631" priority="795"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B853">
+  <conditionalFormatting sqref="B884">
     <cfRule type="duplicateValues" dxfId="630" priority="796"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B853">
+  <conditionalFormatting sqref="B884">
     <cfRule type="duplicateValues" dxfId="629" priority="797"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B854">
+  <conditionalFormatting sqref="B885">
     <cfRule type="duplicateValues" dxfId="628" priority="792"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B854">
+  <conditionalFormatting sqref="B885">
     <cfRule type="duplicateValues" dxfId="627" priority="793"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B854">
+  <conditionalFormatting sqref="B885">
     <cfRule type="duplicateValues" dxfId="626" priority="794"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B857">
+  <conditionalFormatting sqref="B888">
     <cfRule type="duplicateValues" dxfId="625" priority="789"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B857">
+  <conditionalFormatting sqref="B888">
     <cfRule type="duplicateValues" dxfId="624" priority="790"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B857">
+  <conditionalFormatting sqref="B888">
     <cfRule type="duplicateValues" dxfId="623" priority="791"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B858">
+  <conditionalFormatting sqref="B889">
     <cfRule type="duplicateValues" dxfId="622" priority="786"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B858">
+  <conditionalFormatting sqref="B889">
     <cfRule type="duplicateValues" dxfId="621" priority="787"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B858">
+  <conditionalFormatting sqref="B889">
     <cfRule type="duplicateValues" dxfId="620" priority="788"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B859">
+  <conditionalFormatting sqref="B890">
     <cfRule type="duplicateValues" dxfId="619" priority="783"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B859">
+  <conditionalFormatting sqref="B890">
     <cfRule type="duplicateValues" dxfId="618" priority="784"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B859">
+  <conditionalFormatting sqref="B890">
     <cfRule type="duplicateValues" dxfId="617" priority="785"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B861">
+  <conditionalFormatting sqref="B892">
     <cfRule type="duplicateValues" dxfId="616" priority="780"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B861">
+  <conditionalFormatting sqref="B892">
     <cfRule type="duplicateValues" dxfId="615" priority="779"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B861">
+  <conditionalFormatting sqref="B892">
     <cfRule type="duplicateValues" dxfId="614" priority="778"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B863">
+  <conditionalFormatting sqref="B894">
     <cfRule type="duplicateValues" dxfId="613" priority="769"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B863">
+  <conditionalFormatting sqref="B894">
     <cfRule type="duplicateValues" dxfId="612" priority="770"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B863">
+  <conditionalFormatting sqref="B894">
     <cfRule type="duplicateValues" dxfId="611" priority="771"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B868">
+  <conditionalFormatting sqref="B899">
     <cfRule type="duplicateValues" dxfId="610" priority="758"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B868">
+  <conditionalFormatting sqref="B899">
     <cfRule type="duplicateValues" dxfId="609" priority="759"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B868">
+  <conditionalFormatting sqref="B899">
     <cfRule type="duplicateValues" dxfId="608" priority="760"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B866">
+  <conditionalFormatting sqref="B897">
     <cfRule type="duplicateValues" dxfId="607" priority="755"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B866">
+  <conditionalFormatting sqref="B897">
     <cfRule type="duplicateValues" dxfId="606" priority="756"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B866">
+  <conditionalFormatting sqref="B897">
     <cfRule type="duplicateValues" dxfId="605" priority="757"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B867">
+  <conditionalFormatting sqref="B898">
     <cfRule type="duplicateValues" dxfId="604" priority="752"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B867">
+  <conditionalFormatting sqref="B898">
     <cfRule type="duplicateValues" dxfId="603" priority="753"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B867">
+  <conditionalFormatting sqref="B898">
     <cfRule type="duplicateValues" dxfId="602" priority="754"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B869">
+  <conditionalFormatting sqref="B900">
     <cfRule type="duplicateValues" dxfId="601" priority="750"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B869">
+  <conditionalFormatting sqref="B900">
     <cfRule type="duplicateValues" dxfId="600" priority="749"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B869">
+  <conditionalFormatting sqref="B900">
     <cfRule type="duplicateValues" dxfId="599" priority="751"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B870">
+  <conditionalFormatting sqref="B901">
     <cfRule type="duplicateValues" dxfId="598" priority="743"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B870">
+  <conditionalFormatting sqref="B901">
     <cfRule type="duplicateValues" dxfId="597" priority="744"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B870">
+  <conditionalFormatting sqref="B901">
     <cfRule type="duplicateValues" dxfId="596" priority="745"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B871">
+  <conditionalFormatting sqref="B902">
     <cfRule type="duplicateValues" dxfId="595" priority="737"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B871">
+  <conditionalFormatting sqref="B902">
     <cfRule type="duplicateValues" dxfId="594" priority="738"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B871">
+  <conditionalFormatting sqref="B902">
     <cfRule type="duplicateValues" dxfId="593" priority="739"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B873">
+  <conditionalFormatting sqref="B904">
     <cfRule type="duplicateValues" dxfId="592" priority="734"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B873">
+  <conditionalFormatting sqref="B904">
     <cfRule type="duplicateValues" dxfId="591" priority="735"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B873">
+  <conditionalFormatting sqref="B904">
     <cfRule type="duplicateValues" dxfId="590" priority="736"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B872">
+  <conditionalFormatting sqref="B903">
     <cfRule type="duplicateValues" dxfId="589" priority="728"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B872">
+  <conditionalFormatting sqref="B903">
     <cfRule type="duplicateValues" dxfId="588" priority="729"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B872">
+  <conditionalFormatting sqref="B903">
     <cfRule type="duplicateValues" dxfId="587" priority="730"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B874">
+  <conditionalFormatting sqref="B905">
     <cfRule type="duplicateValues" dxfId="586" priority="722"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B874">
+  <conditionalFormatting sqref="B905">
     <cfRule type="duplicateValues" dxfId="585" priority="723"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B874">
+  <conditionalFormatting sqref="B905">
     <cfRule type="duplicateValues" dxfId="584" priority="724"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B875">
+  <conditionalFormatting sqref="B906">
     <cfRule type="duplicateValues" dxfId="583" priority="719"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B875">
+  <conditionalFormatting sqref="B906">
     <cfRule type="duplicateValues" dxfId="582" priority="720"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B875">
+  <conditionalFormatting sqref="B906">
     <cfRule type="duplicateValues" dxfId="581" priority="721"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B877">
+  <conditionalFormatting sqref="B908">
     <cfRule type="duplicateValues" dxfId="580" priority="716"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B877">
+  <conditionalFormatting sqref="B908">
     <cfRule type="duplicateValues" dxfId="579" priority="717"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B877">
+  <conditionalFormatting sqref="B908">
     <cfRule type="duplicateValues" dxfId="578" priority="718"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B879">
+  <conditionalFormatting sqref="B910">
     <cfRule type="duplicateValues" dxfId="577" priority="713"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B879">
+  <conditionalFormatting sqref="B910">
     <cfRule type="duplicateValues" dxfId="576" priority="714"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B879">
+  <conditionalFormatting sqref="B910">
     <cfRule type="duplicateValues" dxfId="575" priority="715"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B881">
+  <conditionalFormatting sqref="B912">
     <cfRule type="duplicateValues" dxfId="574" priority="710"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B881">
+  <conditionalFormatting sqref="B912">
     <cfRule type="duplicateValues" dxfId="573" priority="711"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B881">
+  <conditionalFormatting sqref="B912">
     <cfRule type="duplicateValues" dxfId="572" priority="712"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B882">
+  <conditionalFormatting sqref="B913">
     <cfRule type="duplicateValues" dxfId="571" priority="708"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B882">
+  <conditionalFormatting sqref="B913">
     <cfRule type="duplicateValues" dxfId="570" priority="707"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B882">
+  <conditionalFormatting sqref="B913">
     <cfRule type="duplicateValues" dxfId="569" priority="709"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B884">
+  <conditionalFormatting sqref="B915">
     <cfRule type="duplicateValues" dxfId="568" priority="704"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B884">
+  <conditionalFormatting sqref="B915">
     <cfRule type="duplicateValues" dxfId="567" priority="705"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B884">
+  <conditionalFormatting sqref="B915">
     <cfRule type="duplicateValues" dxfId="566" priority="706"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B883">
+  <conditionalFormatting sqref="B914">
     <cfRule type="duplicateValues" dxfId="565" priority="701"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B883">
+  <conditionalFormatting sqref="B914">
     <cfRule type="duplicateValues" dxfId="564" priority="702"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B883">
+  <conditionalFormatting sqref="B914">
     <cfRule type="duplicateValues" dxfId="563" priority="703"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B885">
+  <conditionalFormatting sqref="B916">
     <cfRule type="duplicateValues" dxfId="562" priority="698"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B885">
+  <conditionalFormatting sqref="B916">
     <cfRule type="duplicateValues" dxfId="561" priority="699"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B885">
+  <conditionalFormatting sqref="B916">
     <cfRule type="duplicateValues" dxfId="560" priority="700"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B886">
+  <conditionalFormatting sqref="B917">
     <cfRule type="duplicateValues" dxfId="559" priority="695"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B886">
+  <conditionalFormatting sqref="B917">
     <cfRule type="duplicateValues" dxfId="558" priority="696"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B886">
+  <conditionalFormatting sqref="B917">
     <cfRule type="duplicateValues" dxfId="557" priority="697"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B887">
+  <conditionalFormatting sqref="B918">
     <cfRule type="duplicateValues" dxfId="556" priority="689"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B887">
+  <conditionalFormatting sqref="B918">
     <cfRule type="duplicateValues" dxfId="555" priority="690"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B887">
+  <conditionalFormatting sqref="B918">
     <cfRule type="duplicateValues" dxfId="554" priority="691"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B888">
+  <conditionalFormatting sqref="B919">
     <cfRule type="duplicateValues" dxfId="553" priority="683"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B888">
+  <conditionalFormatting sqref="B919">
     <cfRule type="duplicateValues" dxfId="552" priority="684"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B888">
+  <conditionalFormatting sqref="B919">
     <cfRule type="duplicateValues" dxfId="551" priority="685"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B889">
+  <conditionalFormatting sqref="B920">
     <cfRule type="duplicateValues" dxfId="550" priority="680"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B889">
+  <conditionalFormatting sqref="B920">
     <cfRule type="duplicateValues" dxfId="549" priority="681"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B889">
+  <conditionalFormatting sqref="B920">
     <cfRule type="duplicateValues" dxfId="548" priority="682"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B890">
+  <conditionalFormatting sqref="B921">
     <cfRule type="duplicateValues" dxfId="547" priority="671"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B890">
+  <conditionalFormatting sqref="B921">
     <cfRule type="duplicateValues" dxfId="546" priority="672"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B890">
+  <conditionalFormatting sqref="B921">
     <cfRule type="duplicateValues" dxfId="545" priority="673"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B891">
+  <conditionalFormatting sqref="B922">
     <cfRule type="duplicateValues" dxfId="544" priority="668"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B891">
+  <conditionalFormatting sqref="B922">
     <cfRule type="duplicateValues" dxfId="543" priority="669"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B891">
+  <conditionalFormatting sqref="B922">
     <cfRule type="duplicateValues" dxfId="542" priority="670"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B892">
+  <conditionalFormatting sqref="B923">
     <cfRule type="duplicateValues" dxfId="541" priority="667"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B892">
+  <conditionalFormatting sqref="B923">
     <cfRule type="duplicateValues" dxfId="540" priority="666"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B892">
+  <conditionalFormatting sqref="B923">
     <cfRule type="duplicateValues" dxfId="539" priority="665"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B893">
+  <conditionalFormatting sqref="B924">
     <cfRule type="duplicateValues" dxfId="538" priority="656"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B893">
+  <conditionalFormatting sqref="B924">
     <cfRule type="duplicateValues" dxfId="537" priority="657"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B893">
+  <conditionalFormatting sqref="B924">
     <cfRule type="duplicateValues" dxfId="536" priority="658"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B894">
+  <conditionalFormatting sqref="B925">
     <cfRule type="duplicateValues" dxfId="535" priority="647"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B894">
+  <conditionalFormatting sqref="B925">
     <cfRule type="duplicateValues" dxfId="534" priority="648"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B894">
+  <conditionalFormatting sqref="B925">
     <cfRule type="duplicateValues" dxfId="533" priority="649"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B895">
+  <conditionalFormatting sqref="B926">
     <cfRule type="duplicateValues" dxfId="532" priority="644"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B895">
+  <conditionalFormatting sqref="B926">
     <cfRule type="duplicateValues" dxfId="531" priority="645"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B895">
+  <conditionalFormatting sqref="B926">
     <cfRule type="duplicateValues" dxfId="530" priority="646"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B896">
+  <conditionalFormatting sqref="B927">
     <cfRule type="duplicateValues" dxfId="529" priority="642"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B896">
+  <conditionalFormatting sqref="B927">
     <cfRule type="duplicateValues" dxfId="528" priority="641"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B896">
+  <conditionalFormatting sqref="B927">
     <cfRule type="duplicateValues" dxfId="527" priority="643"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B880">
+  <conditionalFormatting sqref="B911">
     <cfRule type="duplicateValues" dxfId="526" priority="638"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B880">
+  <conditionalFormatting sqref="B911">
     <cfRule type="duplicateValues" dxfId="525" priority="639"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B880">
+  <conditionalFormatting sqref="B911">
     <cfRule type="duplicateValues" dxfId="524" priority="640"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B898">
+  <conditionalFormatting sqref="B929">
     <cfRule type="duplicateValues" dxfId="523" priority="633"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B898">
+  <conditionalFormatting sqref="B929">
     <cfRule type="duplicateValues" dxfId="522" priority="632"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B898">
+  <conditionalFormatting sqref="B929">
     <cfRule type="duplicateValues" dxfId="521" priority="634"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B899">
+  <conditionalFormatting sqref="B930">
     <cfRule type="duplicateValues" dxfId="520" priority="629"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B899">
+  <conditionalFormatting sqref="B930">
     <cfRule type="duplicateValues" dxfId="519" priority="630"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B899">
+  <conditionalFormatting sqref="B930">
     <cfRule type="duplicateValues" dxfId="518" priority="631"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B900">
+  <conditionalFormatting sqref="B931">
     <cfRule type="duplicateValues" dxfId="517" priority="620"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B900">
+  <conditionalFormatting sqref="B931">
     <cfRule type="duplicateValues" dxfId="516" priority="621"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B900">
+  <conditionalFormatting sqref="B931">
     <cfRule type="duplicateValues" dxfId="515" priority="622"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B901">
+  <conditionalFormatting sqref="B932">
     <cfRule type="duplicateValues" dxfId="514" priority="617"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B901">
+  <conditionalFormatting sqref="B932">
     <cfRule type="duplicateValues" dxfId="513" priority="618"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B901">
+  <conditionalFormatting sqref="B932">
     <cfRule type="duplicateValues" dxfId="512" priority="619"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B902">
+  <conditionalFormatting sqref="B933">
     <cfRule type="duplicateValues" dxfId="511" priority="612"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B902">
+  <conditionalFormatting sqref="B933">
     <cfRule type="duplicateValues" dxfId="510" priority="613"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B902">
+  <conditionalFormatting sqref="B933">
     <cfRule type="duplicateValues" dxfId="509" priority="614"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B903">
+  <conditionalFormatting sqref="B934">
     <cfRule type="duplicateValues" dxfId="508" priority="609"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B903">
+  <conditionalFormatting sqref="B934">
     <cfRule type="duplicateValues" dxfId="507" priority="610"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B903">
+  <conditionalFormatting sqref="B934">
     <cfRule type="duplicateValues" dxfId="506" priority="611"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B904">
+  <conditionalFormatting sqref="B935">
     <cfRule type="duplicateValues" dxfId="505" priority="603"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B904">
+  <conditionalFormatting sqref="B935">
     <cfRule type="duplicateValues" dxfId="504" priority="604"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B904">
+  <conditionalFormatting sqref="B935">
     <cfRule type="duplicateValues" dxfId="503" priority="605"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B905">
+  <conditionalFormatting sqref="B936">
     <cfRule type="duplicateValues" dxfId="502" priority="597"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B905">
+  <conditionalFormatting sqref="B936">
     <cfRule type="duplicateValues" dxfId="501" priority="598"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B905">
+  <conditionalFormatting sqref="B936">
     <cfRule type="duplicateValues" dxfId="500" priority="599"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B907">
+  <conditionalFormatting sqref="B938">
     <cfRule type="duplicateValues" dxfId="499" priority="594"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B907">
+  <conditionalFormatting sqref="B938">
     <cfRule type="duplicateValues" dxfId="498" priority="595"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B907">
+  <conditionalFormatting sqref="B938">
     <cfRule type="duplicateValues" dxfId="497" priority="596"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B906">
+  <conditionalFormatting sqref="B937">
     <cfRule type="duplicateValues" dxfId="496" priority="591"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B906">
+  <conditionalFormatting sqref="B937">
     <cfRule type="duplicateValues" dxfId="495" priority="592"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B906">
+  <conditionalFormatting sqref="B937">
     <cfRule type="duplicateValues" dxfId="494" priority="593"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B909">
+  <conditionalFormatting sqref="B940">
     <cfRule type="duplicateValues" dxfId="493" priority="588"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B909">
+  <conditionalFormatting sqref="B940">
     <cfRule type="duplicateValues" dxfId="492" priority="589"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B909">
+  <conditionalFormatting sqref="B940">
     <cfRule type="duplicateValues" dxfId="491" priority="590"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B908">
+  <conditionalFormatting sqref="B939">
     <cfRule type="duplicateValues" dxfId="490" priority="585"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B908">
+  <conditionalFormatting sqref="B939">
     <cfRule type="duplicateValues" dxfId="489" priority="586"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B908">
+  <conditionalFormatting sqref="B939">
     <cfRule type="duplicateValues" dxfId="488" priority="587"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B910">
+  <conditionalFormatting sqref="B941">
     <cfRule type="duplicateValues" dxfId="487" priority="576"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B910">
+  <conditionalFormatting sqref="B941">
     <cfRule type="duplicateValues" dxfId="486" priority="577"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B910">
+  <conditionalFormatting sqref="B941">
     <cfRule type="duplicateValues" dxfId="485" priority="578"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B912">
+  <conditionalFormatting sqref="B943">
     <cfRule type="duplicateValues" dxfId="484" priority="573"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B912">
+  <conditionalFormatting sqref="B943">
     <cfRule type="duplicateValues" dxfId="483" priority="574"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B912">
+  <conditionalFormatting sqref="B943">
     <cfRule type="duplicateValues" dxfId="482" priority="575"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B913">
+  <conditionalFormatting sqref="B944">
     <cfRule type="duplicateValues" dxfId="481" priority="570"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B913">
+  <conditionalFormatting sqref="B944">
     <cfRule type="duplicateValues" dxfId="480" priority="571"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B913">
+  <conditionalFormatting sqref="B944">
     <cfRule type="duplicateValues" dxfId="479" priority="572"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B914">
+  <conditionalFormatting sqref="B945">
     <cfRule type="duplicateValues" dxfId="478" priority="567"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B914">
+  <conditionalFormatting sqref="B945">
     <cfRule type="duplicateValues" dxfId="477" priority="568"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B914">
+  <conditionalFormatting sqref="B945">
     <cfRule type="duplicateValues" dxfId="476" priority="569"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B915">
+  <conditionalFormatting sqref="B946">
     <cfRule type="duplicateValues" dxfId="475" priority="561"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B915">
+  <conditionalFormatting sqref="B946">
     <cfRule type="duplicateValues" dxfId="474" priority="562"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B915">
+  <conditionalFormatting sqref="B946">
     <cfRule type="duplicateValues" dxfId="473" priority="563"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B916">
+  <conditionalFormatting sqref="B947">
     <cfRule type="duplicateValues" dxfId="472" priority="558"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B916">
+  <conditionalFormatting sqref="B947">
     <cfRule type="duplicateValues" dxfId="471" priority="559"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B916">
+  <conditionalFormatting sqref="B947">
     <cfRule type="duplicateValues" dxfId="470" priority="560"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B917">
+  <conditionalFormatting sqref="B948">
     <cfRule type="duplicateValues" dxfId="469" priority="556"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B917">
+  <conditionalFormatting sqref="B948">
     <cfRule type="duplicateValues" dxfId="468" priority="557"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B918">
+  <conditionalFormatting sqref="B949">
     <cfRule type="duplicateValues" dxfId="467" priority="553"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B918">
+  <conditionalFormatting sqref="B949">
     <cfRule type="duplicateValues" dxfId="466" priority="554"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B918">
+  <conditionalFormatting sqref="B949">
     <cfRule type="duplicateValues" dxfId="465" priority="555"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B919">
+  <conditionalFormatting sqref="B950">
     <cfRule type="duplicateValues" dxfId="464" priority="550"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B919">
+  <conditionalFormatting sqref="B950">
     <cfRule type="duplicateValues" dxfId="463" priority="551"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B919">
+  <conditionalFormatting sqref="B950">
     <cfRule type="duplicateValues" dxfId="462" priority="552"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B920">
+  <conditionalFormatting sqref="B951">
     <cfRule type="duplicateValues" dxfId="461" priority="541"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B920">
+  <conditionalFormatting sqref="B951">
     <cfRule type="duplicateValues" dxfId="460" priority="542"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B920">
+  <conditionalFormatting sqref="B951">
     <cfRule type="duplicateValues" dxfId="459" priority="543"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B922">
+  <conditionalFormatting sqref="B953">
     <cfRule type="duplicateValues" dxfId="458" priority="540"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B922">
+  <conditionalFormatting sqref="B953">
     <cfRule type="duplicateValues" dxfId="457" priority="539"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B922">
+  <conditionalFormatting sqref="B953">
     <cfRule type="duplicateValues" dxfId="456" priority="538"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B921">
+  <conditionalFormatting sqref="B952">
     <cfRule type="duplicateValues" dxfId="455" priority="529"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B921">
+  <conditionalFormatting sqref="B952">
     <cfRule type="duplicateValues" dxfId="454" priority="530"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B921">
+  <conditionalFormatting sqref="B952">
     <cfRule type="duplicateValues" dxfId="453" priority="531"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B923">
+  <conditionalFormatting sqref="B954">
     <cfRule type="duplicateValues" dxfId="452" priority="526"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B923">
+  <conditionalFormatting sqref="B954">
     <cfRule type="duplicateValues" dxfId="451" priority="527"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B923">
+  <conditionalFormatting sqref="B954">
     <cfRule type="duplicateValues" dxfId="450" priority="528"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B924">
+  <conditionalFormatting sqref="B955">
     <cfRule type="duplicateValues" dxfId="449" priority="520"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B924">
+  <conditionalFormatting sqref="B955">
     <cfRule type="duplicateValues" dxfId="448" priority="521"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B924">
+  <conditionalFormatting sqref="B955">
     <cfRule type="duplicateValues" dxfId="447" priority="522"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B925">
+  <conditionalFormatting sqref="B956">
     <cfRule type="duplicateValues" dxfId="446" priority="511"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B925">
+  <conditionalFormatting sqref="B956">
     <cfRule type="duplicateValues" dxfId="445" priority="512"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B925">
+  <conditionalFormatting sqref="B956">
     <cfRule type="duplicateValues" dxfId="444" priority="513"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B926">
+  <conditionalFormatting sqref="B957">
     <cfRule type="duplicateValues" dxfId="443" priority="508"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B926">
+  <conditionalFormatting sqref="B957">
     <cfRule type="duplicateValues" dxfId="442" priority="509"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B926">
+  <conditionalFormatting sqref="B957">
     <cfRule type="duplicateValues" dxfId="441" priority="510"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B929">
+  <conditionalFormatting sqref="B960">
     <cfRule type="duplicateValues" dxfId="440" priority="505"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B929">
+  <conditionalFormatting sqref="B960">
     <cfRule type="duplicateValues" dxfId="439" priority="506"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B929">
+  <conditionalFormatting sqref="B960">
     <cfRule type="duplicateValues" dxfId="438" priority="507"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B931">
+  <conditionalFormatting sqref="B962">
     <cfRule type="duplicateValues" dxfId="437" priority="502"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B931">
+  <conditionalFormatting sqref="B962">
     <cfRule type="duplicateValues" dxfId="436" priority="503"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B931">
+  <conditionalFormatting sqref="B962">
     <cfRule type="duplicateValues" dxfId="435" priority="504"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B934">
+  <conditionalFormatting sqref="B965">
     <cfRule type="duplicateValues" dxfId="434" priority="499"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B934">
+  <conditionalFormatting sqref="B965">
     <cfRule type="duplicateValues" dxfId="433" priority="500"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B934">
+  <conditionalFormatting sqref="B965">
     <cfRule type="duplicateValues" dxfId="432" priority="501"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B935">
+  <conditionalFormatting sqref="B966">
     <cfRule type="duplicateValues" dxfId="431" priority="493"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B935">
+  <conditionalFormatting sqref="B966">
     <cfRule type="duplicateValues" dxfId="430" priority="494"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B935">
+  <conditionalFormatting sqref="B966">
     <cfRule type="duplicateValues" dxfId="429" priority="495"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B937">
+  <conditionalFormatting sqref="B968">
     <cfRule type="duplicateValues" dxfId="428" priority="490"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B937">
+  <conditionalFormatting sqref="B968">
     <cfRule type="duplicateValues" dxfId="427" priority="491"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B937">
+  <conditionalFormatting sqref="B968">
     <cfRule type="duplicateValues" dxfId="426" priority="492"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B936">
+  <conditionalFormatting sqref="B967">
     <cfRule type="duplicateValues" dxfId="425" priority="484"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B936">
+  <conditionalFormatting sqref="B967">
     <cfRule type="duplicateValues" dxfId="424" priority="485"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B936">
+  <conditionalFormatting sqref="B967">
     <cfRule type="duplicateValues" dxfId="423" priority="486"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B938">
+  <conditionalFormatting sqref="B969">
     <cfRule type="duplicateValues" dxfId="422" priority="478"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B938">
+  <conditionalFormatting sqref="B969">
     <cfRule type="duplicateValues" dxfId="421" priority="479"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B938">
+  <conditionalFormatting sqref="B969">
     <cfRule type="duplicateValues" dxfId="420" priority="480"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B939">
+  <conditionalFormatting sqref="B970">
     <cfRule type="duplicateValues" dxfId="419" priority="472"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B939">
+  <conditionalFormatting sqref="B970">
     <cfRule type="duplicateValues" dxfId="418" priority="473"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B939">
+  <conditionalFormatting sqref="B970">
     <cfRule type="duplicateValues" dxfId="417" priority="474"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B940">
+  <conditionalFormatting sqref="B971">
     <cfRule type="duplicateValues" dxfId="416" priority="463"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B940">
+  <conditionalFormatting sqref="B971">
     <cfRule type="duplicateValues" dxfId="415" priority="464"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B940">
+  <conditionalFormatting sqref="B971">
     <cfRule type="duplicateValues" dxfId="414" priority="465"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B941">
+  <conditionalFormatting sqref="B972">
     <cfRule type="duplicateValues" dxfId="413" priority="458"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B941">
+  <conditionalFormatting sqref="B972">
     <cfRule type="duplicateValues" dxfId="412" priority="457"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B941">
+  <conditionalFormatting sqref="B972">
     <cfRule type="duplicateValues" dxfId="411" priority="459"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B943">
+  <conditionalFormatting sqref="B974">
     <cfRule type="duplicateValues" dxfId="410" priority="448"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B943">
+  <conditionalFormatting sqref="B974">
     <cfRule type="duplicateValues" dxfId="409" priority="449"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B943">
+  <conditionalFormatting sqref="B974">
     <cfRule type="duplicateValues" dxfId="408" priority="450"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B944">
+  <conditionalFormatting sqref="B975">
     <cfRule type="duplicateValues" dxfId="407" priority="442"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B944">
+  <conditionalFormatting sqref="B975">
     <cfRule type="duplicateValues" dxfId="406" priority="443"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B944">
+  <conditionalFormatting sqref="B975">
     <cfRule type="duplicateValues" dxfId="405" priority="444"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B945">
+  <conditionalFormatting sqref="B976">
     <cfRule type="duplicateValues" dxfId="404" priority="439"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B945">
+  <conditionalFormatting sqref="B976">
     <cfRule type="duplicateValues" dxfId="403" priority="440"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B945">
+  <conditionalFormatting sqref="B976">
     <cfRule type="duplicateValues" dxfId="402" priority="441"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B946">
+  <conditionalFormatting sqref="B977">
     <cfRule type="duplicateValues" dxfId="401" priority="436"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B946">
+  <conditionalFormatting sqref="B977">
     <cfRule type="duplicateValues" dxfId="400" priority="437"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B946">
+  <conditionalFormatting sqref="B977">
     <cfRule type="duplicateValues" dxfId="399" priority="438"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B947">
+  <conditionalFormatting sqref="B978">
     <cfRule type="duplicateValues" dxfId="398" priority="432"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B947">
+  <conditionalFormatting sqref="B978">
     <cfRule type="duplicateValues" dxfId="397" priority="431"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B947">
+  <conditionalFormatting sqref="B978">
     <cfRule type="duplicateValues" dxfId="396" priority="430"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B948">
+  <conditionalFormatting sqref="B979">
     <cfRule type="duplicateValues" dxfId="395" priority="428"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B948">
+  <conditionalFormatting sqref="B979">
     <cfRule type="duplicateValues" dxfId="394" priority="427"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B948">
+  <conditionalFormatting sqref="B979">
     <cfRule type="duplicateValues" dxfId="393" priority="429"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B949">
+  <conditionalFormatting sqref="B980">
     <cfRule type="duplicateValues" dxfId="392" priority="424"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B949">
+  <conditionalFormatting sqref="B980">
     <cfRule type="duplicateValues" dxfId="391" priority="425"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B949">
+  <conditionalFormatting sqref="B980">
     <cfRule type="duplicateValues" dxfId="390" priority="426"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9">

--- a/Spanish Dictionary.xlsx
+++ b/Spanish Dictionary.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2019" uniqueCount="2010">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2142" uniqueCount="2133">
   <si>
     <t>Word / Expression</t>
   </si>
@@ -5520,9 +5520,6 @@
     <t>I started all by myself from nothing</t>
   </si>
   <si>
-    <t>émpécéh yoh soloh déh lah nadah</t>
-  </si>
-  <si>
     <t>El que envidia a mí me deseaba</t>
   </si>
   <si>
@@ -5538,30 +5535,12 @@
     <t>I watched myself rise</t>
   </si>
   <si>
-    <t>véiah komoh mé élébabah</t>
-  </si>
-  <si>
     <t>Veía como yo subia</t>
   </si>
   <si>
-    <t>He watched me go up</t>
-  </si>
-  <si>
-    <t>véiah komoh yoh subiah</t>
-  </si>
-  <si>
     <t>Veía que nunca cambiaba</t>
   </si>
   <si>
-    <t>I saw that he never changed</t>
-  </si>
-  <si>
-    <t>véiah kéh nunkah kambiabah</t>
-  </si>
-  <si>
-    <t>Y que siempre tengo yo la calle metia'</t>
-  </si>
-  <si>
     <t>And that I always have the street involved</t>
   </si>
   <si>
@@ -5574,9 +5553,6 @@
     <t>They could see I didn't give a damn</t>
   </si>
   <si>
-    <t>véian kéh méh lah sudabah</t>
-  </si>
-  <si>
     <t>Que ganase lo que fuera al día</t>
   </si>
   <si>
@@ -5592,9 +5568,6 @@
     <t>They saw that he never called</t>
   </si>
   <si>
-    <t>véian kéh nunkah yahmabah</t>
-  </si>
-  <si>
     <t>Pase lo que pasaria</t>
   </si>
   <si>
@@ -5619,9 +5592,6 @@
     <t>As well as at the police station</t>
   </si>
   <si>
-    <t>komoh también én komisariah</t>
-  </si>
-  <si>
     <t>Nunca me escondo</t>
   </si>
   <si>
@@ -5637,18 +5607,12 @@
     <t>Although I sometimes hear that some of these would kill</t>
   </si>
   <si>
-    <t>ah-ownkéh  ah véséhs éskoutchoh kéh algunoh déh éstos matarian</t>
-  </si>
-  <si>
     <t>La vida es una</t>
   </si>
   <si>
     <t>life is one</t>
   </si>
   <si>
-    <t>la vidah éhs ownah</t>
-  </si>
-  <si>
     <t>Tengo la lista por si algún día</t>
   </si>
   <si>
@@ -5664,9 +5628,6 @@
     <t>It's my turn to go first</t>
   </si>
   <si>
-    <t>méh tokah irméh priméroh</t>
-  </si>
-  <si>
     <t>Que se vayan conmigo todos en fila</t>
   </si>
   <si>
@@ -5679,12 +5640,6 @@
     <t>Ya no creo de la calle el que más vacila</t>
   </si>
   <si>
-    <t>I no longer believe the one who hesitates the most on the street</t>
-  </si>
-  <si>
-    <t>yah noh kréoh dé lah kayéh éhl kéh mahs vasilah</t>
-  </si>
-  <si>
     <t>Miles de problemas llevo en mi mochila</t>
   </si>
   <si>
@@ -5715,9 +5670,6 @@
     <t>Que te mate la envidia o te mate cartón</t>
   </si>
   <si>
-    <t>kéh té maté la enbidia oh té maté karton</t>
-  </si>
-  <si>
     <t>May envy kill you, or may cardboard kill you</t>
   </si>
   <si>
@@ -5748,15 +5700,9 @@
     <t>We're from L, we're from L</t>
   </si>
   <si>
-    <t>La guerra la hacemo' a cualquiera</t>
-  </si>
-  <si>
     <t>We wage war against anyone</t>
   </si>
   <si>
-    <t>lah guérrah lah-asémoh à-qual-kéirah</t>
-  </si>
-  <si>
     <t>te enseño a hacerlo</t>
   </si>
   <si>
@@ -6046,6 +5992,429 @@
   </si>
   <si>
     <t>noh déboh ah nengunoh</t>
+  </si>
+  <si>
+    <t>solo por la fama</t>
+  </si>
+  <si>
+    <t>soloh por lah famah</t>
+  </si>
+  <si>
+    <t>just for fame</t>
+  </si>
+  <si>
+    <t>ninguno</t>
+  </si>
+  <si>
+    <t>nengunoh</t>
+  </si>
+  <si>
+    <t>no one/no body</t>
+  </si>
+  <si>
+    <t>Empecé</t>
+  </si>
+  <si>
+    <t>I started</t>
+  </si>
+  <si>
+    <t>émpéséh yoh soloh déh lah nadah</t>
+  </si>
+  <si>
+    <t>émpéséh</t>
+  </si>
+  <si>
+    <t>El que envidia a mí</t>
+  </si>
+  <si>
+    <t>éhl kéh-énbidiah ah me</t>
+  </si>
+  <si>
+    <t>The one who envies me</t>
+  </si>
+  <si>
+    <t>me deseaba</t>
+  </si>
+  <si>
+    <t>mé déséabah</t>
+  </si>
+  <si>
+    <t>he/she desired/wanted me</t>
+  </si>
+  <si>
+    <t>Veía</t>
+  </si>
+  <si>
+    <t>béiah komoh mé élébabah</t>
+  </si>
+  <si>
+    <t>béiah komoh yoh subiah</t>
+  </si>
+  <si>
+    <t>béiah kéh nunkah kambiabah</t>
+  </si>
+  <si>
+    <t>béian kéh méh lah sudabah</t>
+  </si>
+  <si>
+    <t>béian kéh nunkah yahmabah</t>
+  </si>
+  <si>
+    <t>I saw</t>
+  </si>
+  <si>
+    <t>béiah</t>
+  </si>
+  <si>
+    <t>me elevaba</t>
+  </si>
+  <si>
+    <t>mé élébabah</t>
+  </si>
+  <si>
+    <t>I was rising</t>
+  </si>
+  <si>
+    <t>I watched myself go up</t>
+  </si>
+  <si>
+    <t>yo subia</t>
+  </si>
+  <si>
+    <t>yoh subiah</t>
+  </si>
+  <si>
+    <t>I was going up</t>
+  </si>
+  <si>
+    <t>cambiaba</t>
+  </si>
+  <si>
+    <t>I saw that I never changed</t>
+  </si>
+  <si>
+    <t>I was changing</t>
+  </si>
+  <si>
+    <t>kambiabah</t>
+  </si>
+  <si>
+    <t>siempre</t>
+  </si>
+  <si>
+    <t>siémpréh</t>
+  </si>
+  <si>
+    <t>always</t>
+  </si>
+  <si>
+    <t>Y que siempre tengo yo la calle metia</t>
+  </si>
+  <si>
+    <t>metia</t>
+  </si>
+  <si>
+    <t>I was putting</t>
+  </si>
+  <si>
+    <t>métiah</t>
+  </si>
+  <si>
+    <t>Veian</t>
+  </si>
+  <si>
+    <t>béian</t>
+  </si>
+  <si>
+    <t>they saw / were seeing</t>
+  </si>
+  <si>
+    <t>ganase</t>
+  </si>
+  <si>
+    <t>ganaséh</t>
+  </si>
+  <si>
+    <t>he/she earned</t>
+  </si>
+  <si>
+    <t>he sido</t>
+  </si>
+  <si>
+    <t>éh sidoh</t>
+  </si>
+  <si>
+    <t>I have been</t>
+  </si>
+  <si>
+    <t>un hombre</t>
+  </si>
+  <si>
+    <t>own-ombré</t>
+  </si>
+  <si>
+    <t>a man</t>
+  </si>
+  <si>
+    <t>Como también</t>
+  </si>
+  <si>
+    <t>as well as</t>
+  </si>
+  <si>
+    <t>komoh tambiénn</t>
+  </si>
+  <si>
+    <t>komoh tambiénn én komisariah</t>
+  </si>
+  <si>
+    <t>comisaria</t>
+  </si>
+  <si>
+    <t>police station</t>
+  </si>
+  <si>
+    <t>komisariah</t>
+  </si>
+  <si>
+    <t>escondo</t>
+  </si>
+  <si>
+    <t>I hide / I am hiding</t>
+  </si>
+  <si>
+    <t>éskondoh</t>
+  </si>
+  <si>
+    <t>Aunque</t>
+  </si>
+  <si>
+    <t>although / even though</t>
+  </si>
+  <si>
+    <t>ah-ownkéh</t>
+  </si>
+  <si>
+    <t>a veces</t>
+  </si>
+  <si>
+    <t>sometimes</t>
+  </si>
+  <si>
+    <t>ah véséhs</t>
+  </si>
+  <si>
+    <t>alguno</t>
+  </si>
+  <si>
+    <t>algunoh</t>
+  </si>
+  <si>
+    <t>some</t>
+  </si>
+  <si>
+    <t>matarían</t>
+  </si>
+  <si>
+    <t>they would kill</t>
+  </si>
+  <si>
+    <t>matah-reyan</t>
+  </si>
+  <si>
+    <t>ah-ownkéh ah véséhs éskoutchoh kéh algunoh déh éstos matah-reyan</t>
+  </si>
+  <si>
+    <t>La vida</t>
+  </si>
+  <si>
+    <t>the life</t>
+  </si>
+  <si>
+    <t>la beedah éhs ownah</t>
+  </si>
+  <si>
+    <t>la beedah</t>
+  </si>
+  <si>
+    <t>irme</t>
+  </si>
+  <si>
+    <t>to leave / to go away / to depart</t>
+  </si>
+  <si>
+    <t>méh tokah eer-méh priméroh</t>
+  </si>
+  <si>
+    <t>eer-méh</t>
+  </si>
+  <si>
+    <t>Me toca</t>
+  </si>
+  <si>
+    <t>méh tokah</t>
+  </si>
+  <si>
+    <t>it's my turn</t>
+  </si>
+  <si>
+    <t>Que se vayan</t>
+  </si>
+  <si>
+    <t>kéh séh bayan</t>
+  </si>
+  <si>
+    <t>let them go / they should leave</t>
+  </si>
+  <si>
+    <t>conmigo</t>
+  </si>
+  <si>
+    <t>konmigoh</t>
+  </si>
+  <si>
+    <t>with me</t>
+  </si>
+  <si>
+    <t>fila</t>
+  </si>
+  <si>
+    <t>line / row</t>
+  </si>
+  <si>
+    <t>filah</t>
+  </si>
+  <si>
+    <t>yah noh kréoh dé lah kayéh éhl kéh mahs basilah</t>
+  </si>
+  <si>
+    <t>vacila</t>
+  </si>
+  <si>
+    <t>basilah</t>
+  </si>
+  <si>
+    <t>I no longer believe the one who shows off the most on the street</t>
+  </si>
+  <si>
+    <t>he/she shows off</t>
+  </si>
+  <si>
+    <t>Ya no creo</t>
+  </si>
+  <si>
+    <t>yah noh kréoh</t>
+  </si>
+  <si>
+    <t>I no longer believe</t>
+  </si>
+  <si>
+    <t>más</t>
+  </si>
+  <si>
+    <t>more / most</t>
+  </si>
+  <si>
+    <t>mahs</t>
+  </si>
+  <si>
+    <t>mochila</t>
+  </si>
+  <si>
+    <t>backpack</t>
+  </si>
+  <si>
+    <t>motchilah</t>
+  </si>
+  <si>
+    <t>llevo</t>
+  </si>
+  <si>
+    <t>I carry</t>
+  </si>
+  <si>
+    <t>yéboh</t>
+  </si>
+  <si>
+    <t>fiel</t>
+  </si>
+  <si>
+    <t>faithful</t>
+  </si>
+  <si>
+    <t>fiél</t>
+  </si>
+  <si>
+    <t>la envidia</t>
+  </si>
+  <si>
+    <t>the envy</t>
+  </si>
+  <si>
+    <t>la énbidiah</t>
+  </si>
+  <si>
+    <t>kéh té maté la énbidiah oh té maté karton</t>
+  </si>
+  <si>
+    <t>cuando</t>
+  </si>
+  <si>
+    <t>quandoh</t>
+  </si>
+  <si>
+    <t>when</t>
+  </si>
+  <si>
+    <t>loquera</t>
+  </si>
+  <si>
+    <t>madness / insanity</t>
+  </si>
+  <si>
+    <t>lokérah</t>
+  </si>
+  <si>
+    <t>somos</t>
+  </si>
+  <si>
+    <t>sohmos</t>
+  </si>
+  <si>
+    <t>cualquiera</t>
+  </si>
+  <si>
+    <t>anyone / anybody</t>
+  </si>
+  <si>
+    <t>qual-kéirah</t>
+  </si>
+  <si>
+    <t>La guerra la hacemos a cualquiera</t>
+  </si>
+  <si>
+    <t>hacemos</t>
+  </si>
+  <si>
+    <t>ahsémohs</t>
+  </si>
+  <si>
+    <t>lah guérrah lah-ahsémohs à-qual-kéirah</t>
+  </si>
+  <si>
+    <t>we do / we make</t>
+  </si>
+  <si>
+    <t>Estamos</t>
+  </si>
+  <si>
+    <t>éstahmos</t>
+  </si>
+  <si>
+    <t>we are (temporary state)</t>
+  </si>
+  <si>
+    <t>we are (permanent traits)</t>
   </si>
 </sst>
 </file>
@@ -6061,18 +6430,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -6095,54 +6458,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1669">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1665">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -23090,7 +23413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:D683"/>
+  <dimension ref="B1:D724"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="1" customWidth="1"/>
@@ -29685,13 +30008,13 @@
     </row>
     <row r="606" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B606" s="1" t="s">
-        <v>1913</v>
+        <v>1895</v>
       </c>
       <c r="C606" s="1" t="s">
-        <v>1914</v>
+        <v>1896</v>
       </c>
       <c r="D606" s="2" t="s">
-        <v>1915</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="607" spans="2:4" x14ac:dyDescent="0.25">
@@ -29707,24 +30030,24 @@
     </row>
     <row r="608" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B608" s="1" t="s">
-        <v>1919</v>
+        <v>1901</v>
       </c>
       <c r="C608" s="1" t="s">
-        <v>1920</v>
+        <v>1902</v>
       </c>
       <c r="D608" s="1" t="s">
-        <v>1921</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="609" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B609" s="1" t="s">
-        <v>1916</v>
+        <v>1898</v>
       </c>
       <c r="C609" s="1" t="s">
-        <v>1917</v>
+        <v>1899</v>
       </c>
       <c r="D609" s="1" t="s">
-        <v>1918</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="610" spans="2:4" x14ac:dyDescent="0.25">
@@ -29740,13 +30063,13 @@
     </row>
     <row r="611" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B611" s="1" t="s">
-        <v>1922</v>
+        <v>1904</v>
       </c>
       <c r="C611" s="1" t="s">
-        <v>1923</v>
+        <v>1905</v>
       </c>
       <c r="D611" s="1" t="s">
-        <v>1924</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="612" spans="2:4" x14ac:dyDescent="0.25">
@@ -29762,24 +30085,24 @@
     </row>
     <row r="613" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B613" s="1" t="s">
-        <v>1925</v>
+        <v>1907</v>
       </c>
       <c r="C613" s="1" t="s">
-        <v>1926</v>
+        <v>1908</v>
       </c>
       <c r="D613" s="1" t="s">
-        <v>1927</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="614" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B614" s="1" t="s">
-        <v>1928</v>
+        <v>1910</v>
       </c>
       <c r="C614" s="1" t="s">
-        <v>1929</v>
+        <v>1911</v>
       </c>
       <c r="D614" s="1" t="s">
-        <v>1930</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="615" spans="2:4" x14ac:dyDescent="0.25">
@@ -29787,7 +30110,7 @@
         <v>1788</v>
       </c>
       <c r="C615" s="1" t="s">
-        <v>1933</v>
+        <v>1915</v>
       </c>
       <c r="D615" s="1" t="s">
         <v>1789</v>
@@ -29795,13 +30118,13 @@
     </row>
     <row r="616" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B616" s="1" t="s">
-        <v>1931</v>
+        <v>1913</v>
       </c>
       <c r="C616" s="1" t="s">
-        <v>1932</v>
+        <v>1914</v>
       </c>
       <c r="D616" s="1" t="s">
-        <v>1934</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="617" spans="2:4" x14ac:dyDescent="0.25">
@@ -29817,24 +30140,24 @@
     </row>
     <row r="618" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B618" s="1" t="s">
-        <v>1935</v>
+        <v>1917</v>
       </c>
       <c r="C618" s="1" t="s">
-        <v>1936</v>
+        <v>1918</v>
       </c>
       <c r="D618" s="1" t="s">
-        <v>1937</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="619" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B619" s="1" t="s">
-        <v>1938</v>
+        <v>1920</v>
       </c>
       <c r="C619" s="1" t="s">
-        <v>1939</v>
+        <v>1921</v>
       </c>
       <c r="D619" s="1" t="s">
-        <v>1940</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="620" spans="2:4" x14ac:dyDescent="0.25">
@@ -29850,24 +30173,24 @@
     </row>
     <row r="621" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B621" s="1" t="s">
-        <v>1941</v>
+        <v>1923</v>
       </c>
       <c r="C621" s="1" t="s">
-        <v>1942</v>
+        <v>1924</v>
       </c>
       <c r="D621" s="1" t="s">
-        <v>1943</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="622" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B622" s="1" t="s">
-        <v>1944</v>
+        <v>1926</v>
       </c>
       <c r="C622" s="1" t="s">
-        <v>1945</v>
+        <v>1927</v>
       </c>
       <c r="D622" s="1" t="s">
-        <v>1946</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="623" spans="2:4" x14ac:dyDescent="0.25">
@@ -29875,7 +30198,7 @@
         <v>1796</v>
       </c>
       <c r="C623" s="1" t="s">
-        <v>1948</v>
+        <v>1930</v>
       </c>
       <c r="D623" s="1" t="s">
         <v>1797</v>
@@ -29883,13 +30206,13 @@
     </row>
     <row r="624" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B624" s="1" t="s">
-        <v>1947</v>
+        <v>1929</v>
       </c>
       <c r="C624" s="1" t="s">
-        <v>1949</v>
+        <v>1931</v>
       </c>
       <c r="D624" s="1" t="s">
-        <v>1950</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="625" spans="2:4" x14ac:dyDescent="0.25">
@@ -29905,24 +30228,24 @@
     </row>
     <row r="626" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B626" s="1" t="s">
-        <v>1951</v>
+        <v>1933</v>
       </c>
       <c r="C626" s="1" t="s">
-        <v>1952</v>
+        <v>1934</v>
       </c>
       <c r="D626" s="1" t="s">
-        <v>1953</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="627" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B627" s="1" t="s">
-        <v>1954</v>
+        <v>1936</v>
       </c>
       <c r="C627" s="1" t="s">
-        <v>1955</v>
+        <v>1937</v>
       </c>
       <c r="D627" s="1" t="s">
-        <v>1956</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="628" spans="2:4" x14ac:dyDescent="0.25">
@@ -29938,13 +30261,13 @@
     </row>
     <row r="629" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B629" s="1" t="s">
-        <v>1957</v>
+        <v>1939</v>
       </c>
       <c r="C629" s="1" t="s">
-        <v>1958</v>
+        <v>1940</v>
       </c>
       <c r="D629" s="1" t="s">
-        <v>1959</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="630" spans="2:4" x14ac:dyDescent="0.25">
@@ -29952,7 +30275,7 @@
         <v>1804</v>
       </c>
       <c r="C630" s="1" t="s">
-        <v>1962</v>
+        <v>1944</v>
       </c>
       <c r="D630" s="1" t="s">
         <v>1805</v>
@@ -29960,35 +30283,35 @@
     </row>
     <row r="631" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B631" s="1" t="s">
-        <v>1967</v>
+        <v>1949</v>
       </c>
       <c r="C631" s="1" t="s">
-        <v>1969</v>
+        <v>1951</v>
       </c>
       <c r="D631" s="1" t="s">
-        <v>1968</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="632" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B632" s="1" t="s">
-        <v>1960</v>
+        <v>1942</v>
       </c>
       <c r="C632" s="1" t="s">
-        <v>1963</v>
+        <v>1945</v>
       </c>
       <c r="D632" s="1" t="s">
-        <v>1961</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="633" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B633" s="1" t="s">
-        <v>1964</v>
+        <v>1946</v>
       </c>
       <c r="C633" s="1" t="s">
-        <v>1965</v>
+        <v>1947</v>
       </c>
       <c r="D633" s="1" t="s">
-        <v>1966</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="634" spans="2:4" x14ac:dyDescent="0.25">
@@ -30004,13 +30327,13 @@
     </row>
     <row r="635" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B635" s="1" t="s">
-        <v>1970</v>
+        <v>1952</v>
       </c>
       <c r="C635" s="1" t="s">
-        <v>1971</v>
+        <v>1953</v>
       </c>
       <c r="D635" s="1" t="s">
-        <v>1972</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="636" spans="2:4" x14ac:dyDescent="0.25">
@@ -30018,7 +30341,7 @@
         <v>1813</v>
       </c>
       <c r="C636" s="1" t="s">
-        <v>1973</v>
+        <v>1955</v>
       </c>
       <c r="D636" s="1" t="s">
         <v>1814</v>
@@ -30026,13 +30349,13 @@
     </row>
     <row r="637" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B637" s="1" t="s">
-        <v>1976</v>
+        <v>1958</v>
       </c>
       <c r="C637" s="1" t="s">
-        <v>1977</v>
+        <v>1959</v>
       </c>
       <c r="D637" s="1" t="s">
-        <v>1978</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="638" spans="2:4" x14ac:dyDescent="0.25">
@@ -30040,7 +30363,7 @@
         <v>1811</v>
       </c>
       <c r="C638" s="1" t="s">
-        <v>1974</v>
+        <v>1956</v>
       </c>
       <c r="D638" s="1" t="s">
         <v>1810</v>
@@ -30048,21 +30371,21 @@
     </row>
     <row r="639" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B639" s="1" t="s">
-        <v>1979</v>
+        <v>1961</v>
       </c>
       <c r="C639" s="1" t="s">
-        <v>1980</v>
+        <v>1962</v>
       </c>
       <c r="D639" s="1" t="s">
-        <v>1981</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="640" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B640" s="1" t="s">
-        <v>1982</v>
+        <v>1964</v>
       </c>
       <c r="C640" s="1" t="s">
-        <v>1983</v>
+        <v>1965</v>
       </c>
       <c r="D640" s="1">
         <v>50</v>
@@ -30073,7 +30396,7 @@
         <v>1812</v>
       </c>
       <c r="C641" s="1" t="s">
-        <v>1975</v>
+        <v>1957</v>
       </c>
       <c r="D641" s="1" t="s">
         <v>1809</v>
@@ -30081,10 +30404,10 @@
     </row>
     <row r="642" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B642" s="1" t="s">
-        <v>1984</v>
+        <v>1966</v>
       </c>
       <c r="C642" s="1" t="s">
-        <v>1985</v>
+        <v>1967</v>
       </c>
       <c r="D642" s="1">
         <v>100</v>
@@ -30092,10 +30415,10 @@
     </row>
     <row r="643" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B643" s="1" t="s">
-        <v>1986</v>
+        <v>1968</v>
       </c>
       <c r="C643" s="1" t="s">
-        <v>1987</v>
+        <v>1969</v>
       </c>
       <c r="D643" s="1">
         <v>20</v>
@@ -30114,13 +30437,13 @@
     </row>
     <row r="645" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B645" s="1" t="s">
-        <v>1988</v>
+        <v>1970</v>
       </c>
       <c r="C645" s="1" t="s">
-        <v>1990</v>
+        <v>1972</v>
       </c>
       <c r="D645" s="1" t="s">
-        <v>1989</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="646" spans="2:4" x14ac:dyDescent="0.25">
@@ -30128,7 +30451,7 @@
         <v>1818</v>
       </c>
       <c r="C646" s="1" t="s">
-        <v>1997</v>
+        <v>1979</v>
       </c>
       <c r="D646" s="1" t="s">
         <v>1819</v>
@@ -30136,24 +30459,24 @@
     </row>
     <row r="647" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B647" s="1" t="s">
-        <v>1991</v>
+        <v>1973</v>
       </c>
       <c r="C647" s="1" t="s">
-        <v>1996</v>
+        <v>1978</v>
       </c>
       <c r="D647" s="1" t="s">
-        <v>1992</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="648" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B648" s="1" t="s">
-        <v>1993</v>
+        <v>1975</v>
       </c>
       <c r="C648" s="1" t="s">
-        <v>1994</v>
+        <v>1976</v>
       </c>
       <c r="D648" s="1" t="s">
-        <v>1995</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="649" spans="2:4" x14ac:dyDescent="0.25">
@@ -30169,35 +30492,35 @@
     </row>
     <row r="650" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B650" s="1" t="s">
-        <v>2004</v>
+        <v>1986</v>
       </c>
       <c r="C650" s="1" t="s">
-        <v>2005</v>
+        <v>1987</v>
       </c>
       <c r="D650" s="1" t="s">
-        <v>2006</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="651" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B651" s="1" t="s">
-        <v>2001</v>
+        <v>1983</v>
       </c>
       <c r="C651" s="1" t="s">
-        <v>2002</v>
+        <v>1984</v>
       </c>
       <c r="D651" s="1" t="s">
-        <v>2003</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="652" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B652" s="1" t="s">
-        <v>1998</v>
+        <v>1980</v>
       </c>
       <c r="C652" s="1" t="s">
-        <v>1999</v>
+        <v>1981</v>
       </c>
       <c r="D652" s="1" t="s">
-        <v>2000</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="653" spans="2:4" x14ac:dyDescent="0.25">
@@ -30213,13 +30536,13 @@
     </row>
     <row r="654" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B654" s="1" t="s">
-        <v>2007</v>
+        <v>1989</v>
       </c>
       <c r="C654" s="1" t="s">
-        <v>2009</v>
+        <v>1991</v>
       </c>
       <c r="D654" s="1" t="s">
-        <v>2008</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="655" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -30233,5321 +30556,5760 @@
         <v>1827</v>
       </c>
     </row>
-    <row r="656" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B656" s="1" t="s">
-        <v>1829</v>
-      </c>
-      <c r="C656" s="1" t="s">
-        <v>1831</v>
-      </c>
-      <c r="D656" s="1" t="s">
-        <v>1830</v>
+    <row r="656" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B656" s="3" t="s">
+        <v>1992</v>
+      </c>
+      <c r="C656" s="3" t="s">
+        <v>1993</v>
+      </c>
+      <c r="D656" s="3" t="s">
+        <v>1994</v>
       </c>
     </row>
     <row r="657" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B657" s="1" t="s">
-        <v>1832</v>
+        <v>1829</v>
       </c>
       <c r="C657" s="1" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="D657" s="1" t="s">
-        <v>1833</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="658" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B658" s="1" t="s">
-        <v>1835</v>
+        <v>1995</v>
       </c>
       <c r="C658" s="1" t="s">
-        <v>1837</v>
+        <v>1996</v>
       </c>
       <c r="D658" s="1" t="s">
-        <v>1836</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="659" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B659" s="1" t="s">
-        <v>1838</v>
+        <v>1832</v>
       </c>
       <c r="C659" s="1" t="s">
-        <v>1840</v>
+        <v>2000</v>
       </c>
       <c r="D659" s="1" t="s">
-        <v>1839</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="660" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B660" s="1" t="s">
-        <v>1841</v>
+        <v>1998</v>
       </c>
       <c r="C660" s="1" t="s">
-        <v>1843</v>
+        <v>2001</v>
       </c>
       <c r="D660" s="1" t="s">
-        <v>1842</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="661" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B661" s="1" t="s">
-        <v>1844</v>
+        <v>1834</v>
       </c>
       <c r="C661" s="1" t="s">
-        <v>1846</v>
+        <v>1836</v>
       </c>
       <c r="D661" s="1" t="s">
-        <v>1845</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="662" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B662" s="1" t="s">
-        <v>1847</v>
+        <v>2002</v>
       </c>
       <c r="C662" s="1" t="s">
-        <v>1849</v>
+        <v>2003</v>
       </c>
       <c r="D662" s="1" t="s">
-        <v>1848</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="663" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B663" s="1" t="s">
-        <v>1850</v>
+        <v>2005</v>
       </c>
       <c r="C663" s="1" t="s">
-        <v>1852</v>
+        <v>2006</v>
       </c>
       <c r="D663" s="1" t="s">
-        <v>1851</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="664" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B664" s="1" t="s">
-        <v>1853</v>
+        <v>1837</v>
       </c>
       <c r="C664" s="1" t="s">
-        <v>1855</v>
+        <v>2009</v>
       </c>
       <c r="D664" s="1" t="s">
-        <v>1854</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="665" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B665" s="1" t="s">
-        <v>1856</v>
+        <v>2008</v>
       </c>
       <c r="C665" s="1" t="s">
-        <v>1858</v>
+        <v>2015</v>
       </c>
       <c r="D665" s="1" t="s">
-        <v>1857</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="666" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B666" s="1" t="s">
-        <v>1859</v>
+        <v>2016</v>
       </c>
       <c r="C666" s="1" t="s">
-        <v>1861</v>
+        <v>2017</v>
       </c>
       <c r="D666" s="1" t="s">
-        <v>1860</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="667" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B667" s="1" t="s">
-        <v>1862</v>
+        <v>1839</v>
       </c>
       <c r="C667" s="1" t="s">
-        <v>1864</v>
+        <v>2010</v>
       </c>
       <c r="D667" s="1" t="s">
-        <v>1863</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="668" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B668" s="1" t="s">
-        <v>1865</v>
+        <v>2020</v>
       </c>
       <c r="C668" s="1" t="s">
-        <v>1867</v>
+        <v>2021</v>
       </c>
       <c r="D668" s="1" t="s">
-        <v>1866</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="669" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B669" s="1" t="s">
-        <v>1868</v>
+        <v>1840</v>
       </c>
       <c r="C669" s="1" t="s">
-        <v>1870</v>
+        <v>2011</v>
       </c>
       <c r="D669" s="1" t="s">
-        <v>1869</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="670" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B670" s="1" t="s">
-        <v>1871</v>
+        <v>2023</v>
       </c>
       <c r="C670" s="1" t="s">
-        <v>1873</v>
+        <v>2026</v>
       </c>
       <c r="D670" s="1" t="s">
-        <v>1872</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="671" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B671" s="1" t="s">
-        <v>1874</v>
+        <v>2030</v>
       </c>
       <c r="C671" s="1" t="s">
-        <v>1876</v>
+        <v>1842</v>
       </c>
       <c r="D671" s="1" t="s">
-        <v>1875</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="672" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B672" s="1" t="s">
-        <v>1877</v>
+        <v>2027</v>
       </c>
       <c r="C672" s="1" t="s">
-        <v>1878</v>
+        <v>2028</v>
       </c>
       <c r="D672" s="1" t="s">
-        <v>1879</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="673" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B673" s="1" t="s">
-        <v>1880</v>
+        <v>2031</v>
       </c>
       <c r="C673" s="1" t="s">
-        <v>1882</v>
+        <v>2033</v>
       </c>
       <c r="D673" s="1" t="s">
-        <v>1881</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="674" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B674" s="1" t="s">
-        <v>1883</v>
+        <v>1843</v>
       </c>
       <c r="C674" s="1" t="s">
-        <v>1885</v>
+        <v>2012</v>
       </c>
       <c r="D674" s="1" t="s">
-        <v>1884</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="675" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B675" s="1" t="s">
-        <v>1886</v>
+        <v>2034</v>
       </c>
       <c r="C675" s="1" t="s">
-        <v>1888</v>
+        <v>2035</v>
       </c>
       <c r="D675" s="1" t="s">
-        <v>1887</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="676" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B676" s="1" t="s">
-        <v>1889</v>
+        <v>1845</v>
       </c>
       <c r="C676" s="1" t="s">
-        <v>1891</v>
+        <v>1847</v>
       </c>
       <c r="D676" s="1" t="s">
-        <v>1890</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="677" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B677" s="1" t="s">
-        <v>1892</v>
+        <v>2037</v>
       </c>
       <c r="C677" s="1" t="s">
-        <v>1893</v>
+        <v>2038</v>
       </c>
       <c r="D677" s="1" t="s">
-        <v>1894</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="678" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B678" s="1" t="s">
-        <v>1895</v>
+        <v>1848</v>
       </c>
       <c r="C678" s="1" t="s">
-        <v>1897</v>
+        <v>2013</v>
       </c>
       <c r="D678" s="1" t="s">
-        <v>1896</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="679" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B679" s="1" t="s">
-        <v>1898</v>
+        <v>1850</v>
       </c>
       <c r="C679" s="1" t="s">
-        <v>1899</v>
+        <v>1852</v>
       </c>
       <c r="D679" s="1" t="s">
-        <v>1900</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="680" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B680" s="1" t="s">
-        <v>1901</v>
+        <v>1853</v>
       </c>
       <c r="C680" s="1" t="s">
-        <v>1902</v>
+        <v>1855</v>
       </c>
       <c r="D680" s="1" t="s">
-        <v>1903</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="681" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B681" s="1" t="s">
-        <v>1904</v>
+        <v>2040</v>
       </c>
       <c r="C681" s="1" t="s">
-        <v>1905</v>
+        <v>2041</v>
       </c>
       <c r="D681" s="1" t="s">
-        <v>1906</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="682" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B682" s="1" t="s">
-        <v>1907</v>
+        <v>2043</v>
       </c>
       <c r="C682" s="1" t="s">
-        <v>1908</v>
+        <v>2044</v>
       </c>
       <c r="D682" s="1" t="s">
-        <v>1909</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="683" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B683" s="1" t="s">
-        <v>1910</v>
+        <v>1856</v>
       </c>
       <c r="C683" s="1" t="s">
-        <v>1912</v>
+        <v>2049</v>
       </c>
       <c r="D683" s="1" t="s">
-        <v>1911</v>
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="684" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B684" s="1" t="s">
+        <v>2046</v>
+      </c>
+      <c r="C684" s="1" t="s">
+        <v>2048</v>
+      </c>
+      <c r="D684" s="1" t="s">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="685" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B685" s="1" t="s">
+        <v>2050</v>
+      </c>
+      <c r="C685" s="1" t="s">
+        <v>2052</v>
+      </c>
+      <c r="D685" s="1" t="s">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="686" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B686" s="1" t="s">
+        <v>1858</v>
+      </c>
+      <c r="C686" s="1" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D686" s="1" t="s">
+        <v>1859</v>
+      </c>
+    </row>
+    <row r="687" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B687" s="1" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C687" s="1" t="s">
+        <v>2055</v>
+      </c>
+      <c r="D687" s="1" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="688" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B688" s="1" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C688" s="1" t="s">
+        <v>2068</v>
+      </c>
+      <c r="D688" s="1" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="689" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B689" s="1" t="s">
+        <v>2056</v>
+      </c>
+      <c r="C689" s="1" t="s">
+        <v>2058</v>
+      </c>
+      <c r="D689" s="1" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="690" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B690" s="1" t="s">
+        <v>2059</v>
+      </c>
+      <c r="C690" s="1" t="s">
+        <v>2061</v>
+      </c>
+      <c r="D690" s="1" t="s">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="691" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B691" s="1" t="s">
+        <v>2062</v>
+      </c>
+      <c r="C691" s="1" t="s">
+        <v>2063</v>
+      </c>
+      <c r="D691" s="1" t="s">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="692" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B692" s="1" t="s">
+        <v>2065</v>
+      </c>
+      <c r="C692" s="1" t="s">
+        <v>2067</v>
+      </c>
+      <c r="D692" s="1" t="s">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="693" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B693" s="1" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C693" s="1" t="s">
+        <v>2071</v>
+      </c>
+      <c r="D693" s="1" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="694" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B694" s="1" t="s">
+        <v>2069</v>
+      </c>
+      <c r="C694" s="1" t="s">
+        <v>2072</v>
+      </c>
+      <c r="D694" s="1" t="s">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="695" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B695" s="1" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C695" s="1" t="s">
+        <v>1866</v>
+      </c>
+      <c r="D695" s="1" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="696" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B696" s="1" t="s">
+        <v>1868</v>
+      </c>
+      <c r="C696" s="1" t="s">
+        <v>2075</v>
+      </c>
+      <c r="D696" s="1" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="697" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B697" s="1" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C697" s="1" t="s">
+        <v>2076</v>
+      </c>
+      <c r="D697" s="1" t="s">
+        <v>2074</v>
+      </c>
+    </row>
+    <row r="698" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B698" s="1" t="s">
+        <v>2077</v>
+      </c>
+      <c r="C698" s="1" t="s">
+        <v>2078</v>
+      </c>
+      <c r="D698" s="1" t="s">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="699" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B699" s="1" t="s">
+        <v>1870</v>
+      </c>
+      <c r="C699" s="1" t="s">
+        <v>1872</v>
+      </c>
+      <c r="D699" s="1" t="s">
+        <v>1871</v>
+      </c>
+    </row>
+    <row r="700" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B700" s="1" t="s">
+        <v>2080</v>
+      </c>
+      <c r="C700" s="1" t="s">
+        <v>2081</v>
+      </c>
+      <c r="D700" s="1" t="s">
+        <v>2082</v>
+      </c>
+    </row>
+    <row r="701" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B701" s="1" t="s">
+        <v>2083</v>
+      </c>
+      <c r="C701" s="1" t="s">
+        <v>2084</v>
+      </c>
+      <c r="D701" s="1" t="s">
+        <v>2085</v>
+      </c>
+    </row>
+    <row r="702" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B702" s="1" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C702" s="1" t="s">
+        <v>2088</v>
+      </c>
+      <c r="D702" s="1" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="703" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B703" s="1" t="s">
+        <v>1873</v>
+      </c>
+      <c r="C703" s="1" t="s">
+        <v>2089</v>
+      </c>
+      <c r="D703" s="1" t="s">
+        <v>2092</v>
+      </c>
+    </row>
+    <row r="704" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B704" s="1" t="s">
+        <v>2090</v>
+      </c>
+      <c r="C704" s="1" t="s">
+        <v>2091</v>
+      </c>
+      <c r="D704" s="1" t="s">
+        <v>2093</v>
+      </c>
+    </row>
+    <row r="705" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B705" s="1" t="s">
+        <v>2094</v>
+      </c>
+      <c r="C705" s="1" t="s">
+        <v>2095</v>
+      </c>
+      <c r="D705" s="1" t="s">
+        <v>2096</v>
+      </c>
+    </row>
+    <row r="706" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B706" s="1" t="s">
+        <v>2097</v>
+      </c>
+      <c r="C706" s="1" t="s">
+        <v>2099</v>
+      </c>
+      <c r="D706" s="1" t="s">
+        <v>2098</v>
+      </c>
+    </row>
+    <row r="707" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B707" s="1" t="s">
+        <v>1874</v>
+      </c>
+      <c r="C707" s="1" t="s">
+        <v>1876</v>
+      </c>
+      <c r="D707" s="1" t="s">
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="708" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B708" s="1" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C708" s="1" t="s">
+        <v>2102</v>
+      </c>
+      <c r="D708" s="1" t="s">
+        <v>2101</v>
+      </c>
+    </row>
+    <row r="709" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B709" s="1" t="s">
+        <v>2103</v>
+      </c>
+      <c r="C709" s="1" t="s">
+        <v>2105</v>
+      </c>
+      <c r="D709" s="1" t="s">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="710" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B710" s="1" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C710" s="1" t="s">
+        <v>1878</v>
+      </c>
+      <c r="D710" s="1" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="711" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B711" s="1" t="s">
+        <v>2106</v>
+      </c>
+      <c r="C711" s="1" t="s">
+        <v>2108</v>
+      </c>
+      <c r="D711" s="1" t="s">
+        <v>2107</v>
+      </c>
+    </row>
+    <row r="712" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B712" s="1" t="s">
+        <v>1880</v>
+      </c>
+      <c r="C712" s="1" t="s">
+        <v>1882</v>
+      </c>
+      <c r="D712" s="1" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="713" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B713" s="1" t="s">
+        <v>1883</v>
+      </c>
+      <c r="C713" s="1" t="s">
+        <v>2112</v>
+      </c>
+      <c r="D713" s="1" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="714" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B714" s="1" t="s">
+        <v>2109</v>
+      </c>
+      <c r="C714" s="1" t="s">
+        <v>2111</v>
+      </c>
+      <c r="D714" s="1" t="s">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="715" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B715" s="1" t="s">
+        <v>1885</v>
+      </c>
+      <c r="C715" s="1" t="s">
+        <v>1886</v>
+      </c>
+      <c r="D715" s="1" t="s">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="716" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B716" s="1" t="s">
+        <v>2113</v>
+      </c>
+      <c r="C716" s="1" t="s">
+        <v>2114</v>
+      </c>
+      <c r="D716" s="1" t="s">
+        <v>2115</v>
+      </c>
+    </row>
+    <row r="717" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B717" s="1" t="s">
+        <v>1888</v>
+      </c>
+      <c r="C717" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="D717" s="1" t="s">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="718" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B718" s="1" t="s">
+        <v>2129</v>
+      </c>
+      <c r="C718" s="1" t="s">
+        <v>2130</v>
+      </c>
+      <c r="D718" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="719" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B719" s="1" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C719" s="1" t="s">
+        <v>2118</v>
+      </c>
+      <c r="D719" s="1" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="720" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B720" s="1" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C720" s="1" t="s">
+        <v>1892</v>
+      </c>
+      <c r="D720" s="1" t="s">
+        <v>1893</v>
+      </c>
+    </row>
+    <row r="721" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B721" s="1" t="s">
+        <v>2119</v>
+      </c>
+      <c r="C721" s="1" t="s">
+        <v>2120</v>
+      </c>
+      <c r="D721" s="1" t="s">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="722" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B722" s="1" t="s">
+        <v>2124</v>
+      </c>
+      <c r="C722" s="1" t="s">
+        <v>2127</v>
+      </c>
+      <c r="D722" s="1" t="s">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="723" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B723" s="1" t="s">
+        <v>2121</v>
+      </c>
+      <c r="C723" s="1" t="s">
+        <v>2123</v>
+      </c>
+      <c r="D723" s="1" t="s">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="724" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B724" s="1" t="s">
+        <v>2125</v>
+      </c>
+      <c r="C724" s="1" t="s">
+        <v>2126</v>
+      </c>
+      <c r="D724" s="1" t="s">
+        <v>2128</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B108">
-    <cfRule type="duplicateValues" dxfId="1668" priority="2489"/>
+    <cfRule type="duplicateValues" dxfId="1664" priority="2489"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B125">
-    <cfRule type="duplicateValues" dxfId="1667" priority="2488"/>
+    <cfRule type="duplicateValues" dxfId="1663" priority="2488"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B132">
-    <cfRule type="duplicateValues" dxfId="1666" priority="2487"/>
+    <cfRule type="duplicateValues" dxfId="1662" priority="2487"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B128">
-    <cfRule type="duplicateValues" dxfId="1665" priority="2486"/>
+    <cfRule type="duplicateValues" dxfId="1661" priority="2486"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B129">
-    <cfRule type="duplicateValues" dxfId="1664" priority="2485"/>
+    <cfRule type="duplicateValues" dxfId="1660" priority="2485"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B130">
-    <cfRule type="duplicateValues" dxfId="1663" priority="2484"/>
+    <cfRule type="duplicateValues" dxfId="1659" priority="2484"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B133">
-    <cfRule type="duplicateValues" dxfId="1662" priority="2483"/>
+    <cfRule type="duplicateValues" dxfId="1658" priority="2483"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B135">
-    <cfRule type="duplicateValues" dxfId="1661" priority="2482"/>
+    <cfRule type="duplicateValues" dxfId="1657" priority="2482"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B136">
-    <cfRule type="duplicateValues" dxfId="1660" priority="2481"/>
+    <cfRule type="duplicateValues" dxfId="1656" priority="2481"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B138">
-    <cfRule type="duplicateValues" dxfId="1659" priority="2480"/>
+    <cfRule type="duplicateValues" dxfId="1655" priority="2480"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B139">
-    <cfRule type="duplicateValues" dxfId="1658" priority="2479"/>
+    <cfRule type="duplicateValues" dxfId="1654" priority="2479"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B140">
-    <cfRule type="duplicateValues" dxfId="1657" priority="2478"/>
+    <cfRule type="duplicateValues" dxfId="1653" priority="2478"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B141">
-    <cfRule type="duplicateValues" dxfId="1656" priority="2477"/>
+    <cfRule type="duplicateValues" dxfId="1652" priority="2477"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B142">
-    <cfRule type="duplicateValues" dxfId="1655" priority="2476"/>
+    <cfRule type="duplicateValues" dxfId="1651" priority="2476"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B148">
-    <cfRule type="duplicateValues" dxfId="1654" priority="2475"/>
+    <cfRule type="duplicateValues" dxfId="1650" priority="2475"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B149">
-    <cfRule type="duplicateValues" dxfId="1653" priority="2474"/>
+    <cfRule type="duplicateValues" dxfId="1649" priority="2474"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B154">
-    <cfRule type="duplicateValues" dxfId="1652" priority="2472"/>
+    <cfRule type="duplicateValues" dxfId="1648" priority="2472"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B155">
-    <cfRule type="duplicateValues" dxfId="1651" priority="2471"/>
+    <cfRule type="duplicateValues" dxfId="1647" priority="2471"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B157">
-    <cfRule type="duplicateValues" dxfId="1650" priority="2469"/>
+    <cfRule type="duplicateValues" dxfId="1646" priority="2469"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B161">
-    <cfRule type="duplicateValues" dxfId="1649" priority="2468"/>
+    <cfRule type="duplicateValues" dxfId="1645" priority="2468"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B162">
-    <cfRule type="duplicateValues" dxfId="1648" priority="2467"/>
+    <cfRule type="duplicateValues" dxfId="1644" priority="2467"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B163">
-    <cfRule type="duplicateValues" dxfId="1647" priority="2466"/>
+    <cfRule type="duplicateValues" dxfId="1643" priority="2466"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B164">
-    <cfRule type="duplicateValues" dxfId="1646" priority="2465"/>
+    <cfRule type="duplicateValues" dxfId="1642" priority="2465"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B166">
-    <cfRule type="duplicateValues" dxfId="1645" priority="2463"/>
+    <cfRule type="duplicateValues" dxfId="1641" priority="2463"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B167">
-    <cfRule type="duplicateValues" dxfId="1644" priority="2462"/>
+    <cfRule type="duplicateValues" dxfId="1640" priority="2462"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B170">
-    <cfRule type="duplicateValues" dxfId="1643" priority="2461"/>
+    <cfRule type="duplicateValues" dxfId="1639" priority="2461"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B179">
-    <cfRule type="duplicateValues" dxfId="1642" priority="2455"/>
+    <cfRule type="duplicateValues" dxfId="1638" priority="2455"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B186">
-    <cfRule type="duplicateValues" dxfId="1641" priority="2454"/>
+    <cfRule type="duplicateValues" dxfId="1637" priority="2454"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B187">
-    <cfRule type="duplicateValues" dxfId="1640" priority="2453"/>
+    <cfRule type="duplicateValues" dxfId="1636" priority="2453"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B191">
-    <cfRule type="duplicateValues" dxfId="1639" priority="2451"/>
+    <cfRule type="duplicateValues" dxfId="1635" priority="2451"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B192">
-    <cfRule type="duplicateValues" dxfId="1638" priority="2450"/>
+    <cfRule type="duplicateValues" dxfId="1634" priority="2450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B193">
-    <cfRule type="duplicateValues" dxfId="1637" priority="2449"/>
+    <cfRule type="duplicateValues" dxfId="1633" priority="2449"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B194">
-    <cfRule type="duplicateValues" dxfId="1636" priority="2448"/>
+    <cfRule type="duplicateValues" dxfId="1632" priority="2448"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B196">
-    <cfRule type="duplicateValues" dxfId="1635" priority="2447"/>
+    <cfRule type="duplicateValues" dxfId="1631" priority="2447"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B197">
-    <cfRule type="duplicateValues" dxfId="1634" priority="2446"/>
+    <cfRule type="duplicateValues" dxfId="1630" priority="2446"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B198">
-    <cfRule type="duplicateValues" dxfId="1633" priority="2445"/>
+    <cfRule type="duplicateValues" dxfId="1629" priority="2445"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B200">
-    <cfRule type="duplicateValues" dxfId="1632" priority="2444"/>
+    <cfRule type="duplicateValues" dxfId="1628" priority="2444"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B201">
-    <cfRule type="duplicateValues" dxfId="1631" priority="2443"/>
+    <cfRule type="duplicateValues" dxfId="1627" priority="2443"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B202">
-    <cfRule type="duplicateValues" dxfId="1630" priority="2442"/>
+    <cfRule type="duplicateValues" dxfId="1626" priority="2442"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B204">
-    <cfRule type="duplicateValues" dxfId="1629" priority="2441"/>
+    <cfRule type="duplicateValues" dxfId="1625" priority="2441"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B205">
-    <cfRule type="duplicateValues" dxfId="1628" priority="2440"/>
+    <cfRule type="duplicateValues" dxfId="1624" priority="2440"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B209">
-    <cfRule type="duplicateValues" dxfId="1627" priority="2436"/>
+    <cfRule type="duplicateValues" dxfId="1623" priority="2436"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B210">
-    <cfRule type="duplicateValues" dxfId="1626" priority="2435"/>
+    <cfRule type="duplicateValues" dxfId="1622" priority="2435"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B211">
-    <cfRule type="duplicateValues" dxfId="1625" priority="2434"/>
+    <cfRule type="duplicateValues" dxfId="1621" priority="2434"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B214">
-    <cfRule type="duplicateValues" dxfId="1624" priority="2433"/>
+    <cfRule type="duplicateValues" dxfId="1620" priority="2433"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B216">
-    <cfRule type="duplicateValues" dxfId="1623" priority="2431"/>
+    <cfRule type="duplicateValues" dxfId="1619" priority="2431"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B217">
-    <cfRule type="duplicateValues" dxfId="1622" priority="2430"/>
+    <cfRule type="duplicateValues" dxfId="1618" priority="2430"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B219">
-    <cfRule type="duplicateValues" dxfId="1621" priority="2429"/>
+    <cfRule type="duplicateValues" dxfId="1617" priority="2429"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B220">
-    <cfRule type="duplicateValues" dxfId="1620" priority="2428"/>
+    <cfRule type="duplicateValues" dxfId="1616" priority="2428"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B225">
-    <cfRule type="duplicateValues" dxfId="1619" priority="2426"/>
+    <cfRule type="duplicateValues" dxfId="1615" priority="2426"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B226">
-    <cfRule type="duplicateValues" dxfId="1618" priority="2425"/>
+    <cfRule type="duplicateValues" dxfId="1614" priority="2425"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B227">
-    <cfRule type="duplicateValues" dxfId="1617" priority="2424"/>
+    <cfRule type="duplicateValues" dxfId="1613" priority="2424"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B228">
-    <cfRule type="duplicateValues" dxfId="1616" priority="2423"/>
+    <cfRule type="duplicateValues" dxfId="1612" priority="2423"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B237">
-    <cfRule type="duplicateValues" dxfId="1615" priority="2413"/>
+    <cfRule type="duplicateValues" dxfId="1611" priority="2413"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B237">
-    <cfRule type="duplicateValues" dxfId="1614" priority="2412"/>
+    <cfRule type="duplicateValues" dxfId="1610" priority="2412"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B238">
-    <cfRule type="duplicateValues" dxfId="1613" priority="2411"/>
+    <cfRule type="duplicateValues" dxfId="1609" priority="2411"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B238">
-    <cfRule type="duplicateValues" dxfId="1612" priority="2410"/>
+    <cfRule type="duplicateValues" dxfId="1608" priority="2410"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B241">
-    <cfRule type="duplicateValues" dxfId="1611" priority="2409"/>
+    <cfRule type="duplicateValues" dxfId="1607" priority="2409"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B241">
-    <cfRule type="duplicateValues" dxfId="1610" priority="2408"/>
+    <cfRule type="duplicateValues" dxfId="1606" priority="2408"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B245">
-    <cfRule type="duplicateValues" dxfId="1609" priority="2407"/>
+    <cfRule type="duplicateValues" dxfId="1605" priority="2407"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B245">
-    <cfRule type="duplicateValues" dxfId="1608" priority="2406"/>
+    <cfRule type="duplicateValues" dxfId="1604" priority="2406"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B246">
-    <cfRule type="duplicateValues" dxfId="1607" priority="2405"/>
+    <cfRule type="duplicateValues" dxfId="1603" priority="2405"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B246">
-    <cfRule type="duplicateValues" dxfId="1606" priority="2404"/>
+    <cfRule type="duplicateValues" dxfId="1602" priority="2404"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B247">
-    <cfRule type="duplicateValues" dxfId="1605" priority="2403"/>
+    <cfRule type="duplicateValues" dxfId="1601" priority="2403"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B247">
-    <cfRule type="duplicateValues" dxfId="1604" priority="2402"/>
+    <cfRule type="duplicateValues" dxfId="1600" priority="2402"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B248">
-    <cfRule type="duplicateValues" dxfId="1603" priority="2401"/>
+    <cfRule type="duplicateValues" dxfId="1599" priority="2401"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B248">
-    <cfRule type="duplicateValues" dxfId="1602" priority="2400"/>
+    <cfRule type="duplicateValues" dxfId="1598" priority="2400"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B249">
-    <cfRule type="duplicateValues" dxfId="1601" priority="2399"/>
+    <cfRule type="duplicateValues" dxfId="1597" priority="2399"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B249">
-    <cfRule type="duplicateValues" dxfId="1600" priority="2398"/>
+    <cfRule type="duplicateValues" dxfId="1596" priority="2398"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B252">
-    <cfRule type="duplicateValues" dxfId="1599" priority="2393"/>
+    <cfRule type="duplicateValues" dxfId="1595" priority="2393"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B252">
-    <cfRule type="duplicateValues" dxfId="1598" priority="2392"/>
+    <cfRule type="duplicateValues" dxfId="1594" priority="2392"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B255">
-    <cfRule type="duplicateValues" dxfId="1597" priority="2389"/>
+    <cfRule type="duplicateValues" dxfId="1593" priority="2389"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B255">
-    <cfRule type="duplicateValues" dxfId="1596" priority="2388"/>
+    <cfRule type="duplicateValues" dxfId="1592" priority="2388"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B263">
-    <cfRule type="duplicateValues" dxfId="1595" priority="2385"/>
+    <cfRule type="duplicateValues" dxfId="1591" priority="2385"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B263">
-    <cfRule type="duplicateValues" dxfId="1594" priority="2384"/>
+    <cfRule type="duplicateValues" dxfId="1590" priority="2384"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B271">
-    <cfRule type="duplicateValues" dxfId="1593" priority="2381"/>
+    <cfRule type="duplicateValues" dxfId="1589" priority="2381"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B271">
-    <cfRule type="duplicateValues" dxfId="1592" priority="2380"/>
+    <cfRule type="duplicateValues" dxfId="1588" priority="2380"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B274">
-    <cfRule type="duplicateValues" dxfId="1591" priority="2377"/>
+    <cfRule type="duplicateValues" dxfId="1587" priority="2377"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B274">
-    <cfRule type="duplicateValues" dxfId="1590" priority="2376"/>
+    <cfRule type="duplicateValues" dxfId="1586" priority="2376"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B275">
-    <cfRule type="duplicateValues" dxfId="1589" priority="2375"/>
+    <cfRule type="duplicateValues" dxfId="1585" priority="2375"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B275">
-    <cfRule type="duplicateValues" dxfId="1588" priority="2374"/>
+    <cfRule type="duplicateValues" dxfId="1584" priority="2374"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B276">
-    <cfRule type="duplicateValues" dxfId="1587" priority="2373"/>
+    <cfRule type="duplicateValues" dxfId="1583" priority="2373"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B276">
-    <cfRule type="duplicateValues" dxfId="1586" priority="2372"/>
+    <cfRule type="duplicateValues" dxfId="1582" priority="2372"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B277">
-    <cfRule type="duplicateValues" dxfId="1585" priority="2369"/>
+    <cfRule type="duplicateValues" dxfId="1581" priority="2369"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B277">
-    <cfRule type="duplicateValues" dxfId="1584" priority="2368"/>
+    <cfRule type="duplicateValues" dxfId="1580" priority="2368"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B279">
-    <cfRule type="duplicateValues" dxfId="1583" priority="2367"/>
+    <cfRule type="duplicateValues" dxfId="1579" priority="2367"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B279">
-    <cfRule type="duplicateValues" dxfId="1582" priority="2366"/>
+    <cfRule type="duplicateValues" dxfId="1578" priority="2366"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B281">
-    <cfRule type="duplicateValues" dxfId="1581" priority="2361"/>
+    <cfRule type="duplicateValues" dxfId="1577" priority="2361"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B281">
-    <cfRule type="duplicateValues" dxfId="1580" priority="2360"/>
+    <cfRule type="duplicateValues" dxfId="1576" priority="2360"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B282">
-    <cfRule type="duplicateValues" dxfId="1579" priority="2359"/>
+    <cfRule type="duplicateValues" dxfId="1575" priority="2359"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B282">
-    <cfRule type="duplicateValues" dxfId="1578" priority="2358"/>
+    <cfRule type="duplicateValues" dxfId="1574" priority="2358"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B283">
-    <cfRule type="duplicateValues" dxfId="1577" priority="2357"/>
+    <cfRule type="duplicateValues" dxfId="1573" priority="2357"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B283">
-    <cfRule type="duplicateValues" dxfId="1576" priority="2356"/>
+    <cfRule type="duplicateValues" dxfId="1572" priority="2356"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B286">
-    <cfRule type="duplicateValues" dxfId="1575" priority="2351"/>
+    <cfRule type="duplicateValues" dxfId="1571" priority="2351"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B287">
-    <cfRule type="duplicateValues" dxfId="1574" priority="2348"/>
+    <cfRule type="duplicateValues" dxfId="1570" priority="2348"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B287">
-    <cfRule type="duplicateValues" dxfId="1573" priority="2347"/>
+    <cfRule type="duplicateValues" dxfId="1569" priority="2347"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B290">
-    <cfRule type="duplicateValues" dxfId="1572" priority="2346"/>
+    <cfRule type="duplicateValues" dxfId="1568" priority="2346"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B290">
-    <cfRule type="duplicateValues" dxfId="1571" priority="2345"/>
+    <cfRule type="duplicateValues" dxfId="1567" priority="2345"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B292">
-    <cfRule type="duplicateValues" dxfId="1570" priority="2344"/>
+    <cfRule type="duplicateValues" dxfId="1566" priority="2344"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B292">
-    <cfRule type="duplicateValues" dxfId="1569" priority="2343"/>
+    <cfRule type="duplicateValues" dxfId="1565" priority="2343"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B293">
-    <cfRule type="duplicateValues" dxfId="1568" priority="2340"/>
+    <cfRule type="duplicateValues" dxfId="1564" priority="2340"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B293">
-    <cfRule type="duplicateValues" dxfId="1567" priority="2339"/>
+    <cfRule type="duplicateValues" dxfId="1563" priority="2339"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B294">
-    <cfRule type="duplicateValues" dxfId="1566" priority="2338"/>
+    <cfRule type="duplicateValues" dxfId="1562" priority="2338"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B294">
-    <cfRule type="duplicateValues" dxfId="1565" priority="2337"/>
+    <cfRule type="duplicateValues" dxfId="1561" priority="2337"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B300">
-    <cfRule type="duplicateValues" dxfId="1564" priority="2336"/>
+    <cfRule type="duplicateValues" dxfId="1560" priority="2336"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B300">
-    <cfRule type="duplicateValues" dxfId="1563" priority="2335"/>
+    <cfRule type="duplicateValues" dxfId="1559" priority="2335"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B301">
-    <cfRule type="duplicateValues" dxfId="1562" priority="2334"/>
+    <cfRule type="duplicateValues" dxfId="1558" priority="2334"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B301">
-    <cfRule type="duplicateValues" dxfId="1561" priority="2333"/>
+    <cfRule type="duplicateValues" dxfId="1557" priority="2333"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B302">
-    <cfRule type="duplicateValues" dxfId="1560" priority="2330"/>
+    <cfRule type="duplicateValues" dxfId="1556" priority="2330"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B302">
-    <cfRule type="duplicateValues" dxfId="1559" priority="2329"/>
+    <cfRule type="duplicateValues" dxfId="1555" priority="2329"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B303">
-    <cfRule type="duplicateValues" dxfId="1558" priority="2328"/>
+    <cfRule type="duplicateValues" dxfId="1554" priority="2328"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B303">
-    <cfRule type="duplicateValues" dxfId="1557" priority="2327"/>
+    <cfRule type="duplicateValues" dxfId="1553" priority="2327"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B304">
-    <cfRule type="duplicateValues" dxfId="1556" priority="2326"/>
+    <cfRule type="duplicateValues" dxfId="1552" priority="2326"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B304">
-    <cfRule type="duplicateValues" dxfId="1555" priority="2325"/>
+    <cfRule type="duplicateValues" dxfId="1551" priority="2325"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B305">
-    <cfRule type="duplicateValues" dxfId="1554" priority="2324"/>
+    <cfRule type="duplicateValues" dxfId="1550" priority="2324"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B305">
-    <cfRule type="duplicateValues" dxfId="1553" priority="2323"/>
+    <cfRule type="duplicateValues" dxfId="1549" priority="2323"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B308">
-    <cfRule type="duplicateValues" dxfId="1552" priority="2319"/>
+    <cfRule type="duplicateValues" dxfId="1548" priority="2319"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B308">
-    <cfRule type="duplicateValues" dxfId="1551" priority="2318"/>
+    <cfRule type="duplicateValues" dxfId="1547" priority="2318"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B309">
-    <cfRule type="duplicateValues" dxfId="1550" priority="2317"/>
+    <cfRule type="duplicateValues" dxfId="1546" priority="2317"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B309">
-    <cfRule type="duplicateValues" dxfId="1549" priority="2316"/>
+    <cfRule type="duplicateValues" dxfId="1545" priority="2316"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B310">
-    <cfRule type="duplicateValues" dxfId="1548" priority="2315"/>
+    <cfRule type="duplicateValues" dxfId="1544" priority="2315"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B310">
-    <cfRule type="duplicateValues" dxfId="1547" priority="2314"/>
+    <cfRule type="duplicateValues" dxfId="1543" priority="2314"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B312">
-    <cfRule type="duplicateValues" dxfId="1546" priority="2309"/>
+    <cfRule type="duplicateValues" dxfId="1542" priority="2309"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B312">
-    <cfRule type="duplicateValues" dxfId="1545" priority="2308"/>
+    <cfRule type="duplicateValues" dxfId="1541" priority="2308"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B315">
-    <cfRule type="duplicateValues" dxfId="1544" priority="2301"/>
+    <cfRule type="duplicateValues" dxfId="1540" priority="2301"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B315">
-    <cfRule type="duplicateValues" dxfId="1543" priority="2300"/>
+    <cfRule type="duplicateValues" dxfId="1539" priority="2300"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B317">
-    <cfRule type="duplicateValues" dxfId="1542" priority="2293"/>
+    <cfRule type="duplicateValues" dxfId="1538" priority="2293"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B317">
-    <cfRule type="duplicateValues" dxfId="1541" priority="2292"/>
+    <cfRule type="duplicateValues" dxfId="1537" priority="2292"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B318">
-    <cfRule type="duplicateValues" dxfId="1540" priority="2291"/>
+    <cfRule type="duplicateValues" dxfId="1536" priority="2291"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B318">
-    <cfRule type="duplicateValues" dxfId="1539" priority="2290"/>
+    <cfRule type="duplicateValues" dxfId="1535" priority="2290"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B320">
-    <cfRule type="duplicateValues" dxfId="1538" priority="2283"/>
+    <cfRule type="duplicateValues" dxfId="1534" priority="2283"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B320">
-    <cfRule type="duplicateValues" dxfId="1537" priority="2282"/>
+    <cfRule type="duplicateValues" dxfId="1533" priority="2282"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B321">
-    <cfRule type="duplicateValues" dxfId="1536" priority="2281"/>
+    <cfRule type="duplicateValues" dxfId="1532" priority="2281"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B321">
-    <cfRule type="duplicateValues" dxfId="1535" priority="2280"/>
+    <cfRule type="duplicateValues" dxfId="1531" priority="2280"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B329">
-    <cfRule type="duplicateValues" dxfId="1534" priority="2261"/>
+    <cfRule type="duplicateValues" dxfId="1530" priority="2261"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B329">
-    <cfRule type="duplicateValues" dxfId="1533" priority="2260"/>
+    <cfRule type="duplicateValues" dxfId="1529" priority="2260"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B330">
-    <cfRule type="duplicateValues" dxfId="1532" priority="2257"/>
+    <cfRule type="duplicateValues" dxfId="1528" priority="2257"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B330">
-    <cfRule type="duplicateValues" dxfId="1531" priority="2256"/>
+    <cfRule type="duplicateValues" dxfId="1527" priority="2256"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B332">
-    <cfRule type="duplicateValues" dxfId="1530" priority="2255"/>
+    <cfRule type="duplicateValues" dxfId="1526" priority="2255"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B332">
-    <cfRule type="duplicateValues" dxfId="1529" priority="2254"/>
+    <cfRule type="duplicateValues" dxfId="1525" priority="2254"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B334">
-    <cfRule type="duplicateValues" dxfId="1528" priority="2253"/>
+    <cfRule type="duplicateValues" dxfId="1524" priority="2253"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B334">
-    <cfRule type="duplicateValues" dxfId="1527" priority="2252"/>
+    <cfRule type="duplicateValues" dxfId="1523" priority="2252"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B335">
-    <cfRule type="duplicateValues" dxfId="1526" priority="2251"/>
+    <cfRule type="duplicateValues" dxfId="1522" priority="2251"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B335">
-    <cfRule type="duplicateValues" dxfId="1525" priority="2250"/>
+    <cfRule type="duplicateValues" dxfId="1521" priority="2250"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B336">
-    <cfRule type="duplicateValues" dxfId="1524" priority="2247"/>
+    <cfRule type="duplicateValues" dxfId="1520" priority="2247"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B336">
-    <cfRule type="duplicateValues" dxfId="1523" priority="2246"/>
+    <cfRule type="duplicateValues" dxfId="1519" priority="2246"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B339">
-    <cfRule type="duplicateValues" dxfId="1522" priority="2245"/>
+    <cfRule type="duplicateValues" dxfId="1518" priority="2245"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B339">
-    <cfRule type="duplicateValues" dxfId="1521" priority="2244"/>
+    <cfRule type="duplicateValues" dxfId="1517" priority="2244"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B342">
-    <cfRule type="duplicateValues" dxfId="1520" priority="2241"/>
+    <cfRule type="duplicateValues" dxfId="1516" priority="2241"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B342">
-    <cfRule type="duplicateValues" dxfId="1519" priority="2240"/>
+    <cfRule type="duplicateValues" dxfId="1515" priority="2240"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B344">
-    <cfRule type="duplicateValues" dxfId="1518" priority="2235"/>
+    <cfRule type="duplicateValues" dxfId="1514" priority="2235"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B344">
-    <cfRule type="duplicateValues" dxfId="1517" priority="2234"/>
+    <cfRule type="duplicateValues" dxfId="1513" priority="2234"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B347">
-    <cfRule type="duplicateValues" dxfId="1516" priority="2233"/>
+    <cfRule type="duplicateValues" dxfId="1512" priority="2233"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B347">
-    <cfRule type="duplicateValues" dxfId="1515" priority="2232"/>
+    <cfRule type="duplicateValues" dxfId="1511" priority="2232"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B349">
-    <cfRule type="duplicateValues" dxfId="1514" priority="2231"/>
+    <cfRule type="duplicateValues" dxfId="1510" priority="2231"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B349">
-    <cfRule type="duplicateValues" dxfId="1513" priority="2230"/>
+    <cfRule type="duplicateValues" dxfId="1509" priority="2230"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B350">
-    <cfRule type="duplicateValues" dxfId="1512" priority="2227"/>
+    <cfRule type="duplicateValues" dxfId="1508" priority="2227"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B350">
-    <cfRule type="duplicateValues" dxfId="1511" priority="2226"/>
+    <cfRule type="duplicateValues" dxfId="1507" priority="2226"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B352">
-    <cfRule type="duplicateValues" dxfId="1510" priority="2223"/>
+    <cfRule type="duplicateValues" dxfId="1506" priority="2223"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B352">
-    <cfRule type="duplicateValues" dxfId="1509" priority="2222"/>
+    <cfRule type="duplicateValues" dxfId="1505" priority="2222"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B353">
-    <cfRule type="duplicateValues" dxfId="1508" priority="2219"/>
+    <cfRule type="duplicateValues" dxfId="1504" priority="2219"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B353">
-    <cfRule type="duplicateValues" dxfId="1507" priority="2218"/>
+    <cfRule type="duplicateValues" dxfId="1503" priority="2218"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B355">
-    <cfRule type="duplicateValues" dxfId="1506" priority="2215"/>
+    <cfRule type="duplicateValues" dxfId="1502" priority="2215"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B355">
-    <cfRule type="duplicateValues" dxfId="1505" priority="2214"/>
+    <cfRule type="duplicateValues" dxfId="1501" priority="2214"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B356">
-    <cfRule type="duplicateValues" dxfId="1504" priority="2213"/>
+    <cfRule type="duplicateValues" dxfId="1500" priority="2213"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B356">
-    <cfRule type="duplicateValues" dxfId="1503" priority="2212"/>
+    <cfRule type="duplicateValues" dxfId="1499" priority="2212"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B357">
-    <cfRule type="duplicateValues" dxfId="1502" priority="2211"/>
+    <cfRule type="duplicateValues" dxfId="1498" priority="2211"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B357">
-    <cfRule type="duplicateValues" dxfId="1501" priority="2210"/>
+    <cfRule type="duplicateValues" dxfId="1497" priority="2210"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B358">
-    <cfRule type="duplicateValues" dxfId="1500" priority="2207"/>
+    <cfRule type="duplicateValues" dxfId="1496" priority="2207"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B358">
-    <cfRule type="duplicateValues" dxfId="1499" priority="2206"/>
+    <cfRule type="duplicateValues" dxfId="1495" priority="2206"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B359">
-    <cfRule type="duplicateValues" dxfId="1498" priority="2205"/>
+    <cfRule type="duplicateValues" dxfId="1494" priority="2205"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B359">
-    <cfRule type="duplicateValues" dxfId="1497" priority="2204"/>
+    <cfRule type="duplicateValues" dxfId="1493" priority="2204"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B360">
-    <cfRule type="duplicateValues" dxfId="1496" priority="2203"/>
+    <cfRule type="duplicateValues" dxfId="1492" priority="2203"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B360">
-    <cfRule type="duplicateValues" dxfId="1495" priority="2202"/>
+    <cfRule type="duplicateValues" dxfId="1491" priority="2202"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B361">
-    <cfRule type="duplicateValues" dxfId="1494" priority="2201"/>
+    <cfRule type="duplicateValues" dxfId="1490" priority="2201"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B361">
-    <cfRule type="duplicateValues" dxfId="1493" priority="2200"/>
+    <cfRule type="duplicateValues" dxfId="1489" priority="2200"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B363">
-    <cfRule type="duplicateValues" dxfId="1492" priority="2197"/>
+    <cfRule type="duplicateValues" dxfId="1488" priority="2197"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B363">
-    <cfRule type="duplicateValues" dxfId="1491" priority="2196"/>
+    <cfRule type="duplicateValues" dxfId="1487" priority="2196"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B365">
-    <cfRule type="duplicateValues" dxfId="1490" priority="2191"/>
+    <cfRule type="duplicateValues" dxfId="1486" priority="2191"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B365">
-    <cfRule type="duplicateValues" dxfId="1489" priority="2190"/>
+    <cfRule type="duplicateValues" dxfId="1485" priority="2190"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B366">
-    <cfRule type="duplicateValues" dxfId="1488" priority="2187"/>
+    <cfRule type="duplicateValues" dxfId="1484" priority="2187"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B366">
-    <cfRule type="duplicateValues" dxfId="1487" priority="2186"/>
+    <cfRule type="duplicateValues" dxfId="1483" priority="2186"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B367">
-    <cfRule type="duplicateValues" dxfId="1486" priority="2183"/>
+    <cfRule type="duplicateValues" dxfId="1482" priority="2183"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B367">
-    <cfRule type="duplicateValues" dxfId="1485" priority="2182"/>
+    <cfRule type="duplicateValues" dxfId="1481" priority="2182"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B368">
-    <cfRule type="duplicateValues" dxfId="1484" priority="2181"/>
+    <cfRule type="duplicateValues" dxfId="1480" priority="2181"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B368">
-    <cfRule type="duplicateValues" dxfId="1483" priority="2180"/>
+    <cfRule type="duplicateValues" dxfId="1479" priority="2180"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B370">
-    <cfRule type="duplicateValues" dxfId="1482" priority="2175"/>
+    <cfRule type="duplicateValues" dxfId="1478" priority="2175"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B370">
-    <cfRule type="duplicateValues" dxfId="1481" priority="2174"/>
+    <cfRule type="duplicateValues" dxfId="1477" priority="2174"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B371">
-    <cfRule type="duplicateValues" dxfId="1480" priority="2173"/>
+    <cfRule type="duplicateValues" dxfId="1476" priority="2173"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B371">
-    <cfRule type="duplicateValues" dxfId="1479" priority="2172"/>
+    <cfRule type="duplicateValues" dxfId="1475" priority="2172"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B374">
-    <cfRule type="duplicateValues" dxfId="1478" priority="2167"/>
+    <cfRule type="duplicateValues" dxfId="1474" priority="2167"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B374">
-    <cfRule type="duplicateValues" dxfId="1477" priority="2166"/>
+    <cfRule type="duplicateValues" dxfId="1473" priority="2166"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B375">
-    <cfRule type="duplicateValues" dxfId="1476" priority="2165"/>
+    <cfRule type="duplicateValues" dxfId="1472" priority="2165"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B375">
-    <cfRule type="duplicateValues" dxfId="1475" priority="2164"/>
+    <cfRule type="duplicateValues" dxfId="1471" priority="2164"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B376">
-    <cfRule type="duplicateValues" dxfId="1474" priority="2161"/>
+    <cfRule type="duplicateValues" dxfId="1470" priority="2161"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B376">
-    <cfRule type="duplicateValues" dxfId="1473" priority="2160"/>
+    <cfRule type="duplicateValues" dxfId="1469" priority="2160"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B377">
-    <cfRule type="duplicateValues" dxfId="1472" priority="2157"/>
+    <cfRule type="duplicateValues" dxfId="1468" priority="2157"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B377">
-    <cfRule type="duplicateValues" dxfId="1471" priority="2156"/>
+    <cfRule type="duplicateValues" dxfId="1467" priority="2156"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B381">
-    <cfRule type="duplicateValues" dxfId="1470" priority="2155"/>
+    <cfRule type="duplicateValues" dxfId="1466" priority="2155"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B381">
-    <cfRule type="duplicateValues" dxfId="1469" priority="2154"/>
+    <cfRule type="duplicateValues" dxfId="1465" priority="2154"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B382">
-    <cfRule type="duplicateValues" dxfId="1468" priority="2151"/>
+    <cfRule type="duplicateValues" dxfId="1464" priority="2151"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B382">
-    <cfRule type="duplicateValues" dxfId="1467" priority="2150"/>
+    <cfRule type="duplicateValues" dxfId="1463" priority="2150"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B383">
-    <cfRule type="duplicateValues" dxfId="1466" priority="2147"/>
+    <cfRule type="duplicateValues" dxfId="1462" priority="2147"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B383">
-    <cfRule type="duplicateValues" dxfId="1465" priority="2146"/>
+    <cfRule type="duplicateValues" dxfId="1461" priority="2146"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B385">
-    <cfRule type="duplicateValues" dxfId="1464" priority="2143"/>
+    <cfRule type="duplicateValues" dxfId="1460" priority="2143"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B385">
-    <cfRule type="duplicateValues" dxfId="1463" priority="2142"/>
+    <cfRule type="duplicateValues" dxfId="1459" priority="2142"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B386">
-    <cfRule type="duplicateValues" dxfId="1462" priority="2137"/>
+    <cfRule type="duplicateValues" dxfId="1458" priority="2137"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B386">
-    <cfRule type="duplicateValues" dxfId="1461" priority="2136"/>
+    <cfRule type="duplicateValues" dxfId="1457" priority="2136"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B387">
-    <cfRule type="duplicateValues" dxfId="1460" priority="2131"/>
+    <cfRule type="duplicateValues" dxfId="1456" priority="2131"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B387">
-    <cfRule type="duplicateValues" dxfId="1459" priority="2130"/>
+    <cfRule type="duplicateValues" dxfId="1455" priority="2130"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B388">
-    <cfRule type="duplicateValues" dxfId="1458" priority="2129"/>
+    <cfRule type="duplicateValues" dxfId="1454" priority="2129"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B388">
-    <cfRule type="duplicateValues" dxfId="1457" priority="2128"/>
+    <cfRule type="duplicateValues" dxfId="1453" priority="2128"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B392">
-    <cfRule type="duplicateValues" dxfId="1456" priority="2125"/>
+    <cfRule type="duplicateValues" dxfId="1452" priority="2125"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B392">
-    <cfRule type="duplicateValues" dxfId="1455" priority="2124"/>
+    <cfRule type="duplicateValues" dxfId="1451" priority="2124"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B393">
-    <cfRule type="duplicateValues" dxfId="1454" priority="2123"/>
+    <cfRule type="duplicateValues" dxfId="1450" priority="2123"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B393">
-    <cfRule type="duplicateValues" dxfId="1453" priority="2122"/>
+    <cfRule type="duplicateValues" dxfId="1449" priority="2122"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B394">
-    <cfRule type="duplicateValues" dxfId="1452" priority="2119"/>
+    <cfRule type="duplicateValues" dxfId="1448" priority="2119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B394">
-    <cfRule type="duplicateValues" dxfId="1451" priority="2118"/>
+    <cfRule type="duplicateValues" dxfId="1447" priority="2118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B395">
-    <cfRule type="duplicateValues" dxfId="1450" priority="2117"/>
+    <cfRule type="duplicateValues" dxfId="1446" priority="2117"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B395">
-    <cfRule type="duplicateValues" dxfId="1449" priority="2116"/>
+    <cfRule type="duplicateValues" dxfId="1445" priority="2116"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B398">
-    <cfRule type="duplicateValues" dxfId="1448" priority="2115"/>
+    <cfRule type="duplicateValues" dxfId="1444" priority="2115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B398">
-    <cfRule type="duplicateValues" dxfId="1447" priority="2114"/>
+    <cfRule type="duplicateValues" dxfId="1443" priority="2114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B399">
-    <cfRule type="duplicateValues" dxfId="1446" priority="2113"/>
+    <cfRule type="duplicateValues" dxfId="1442" priority="2113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B399">
-    <cfRule type="duplicateValues" dxfId="1445" priority="2112"/>
+    <cfRule type="duplicateValues" dxfId="1441" priority="2112"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B400">
-    <cfRule type="duplicateValues" dxfId="1444" priority="2109"/>
+    <cfRule type="duplicateValues" dxfId="1440" priority="2109"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B400">
-    <cfRule type="duplicateValues" dxfId="1443" priority="2108"/>
+    <cfRule type="duplicateValues" dxfId="1439" priority="2108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B402">
-    <cfRule type="duplicateValues" dxfId="1442" priority="2107"/>
+    <cfRule type="duplicateValues" dxfId="1438" priority="2107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B402">
-    <cfRule type="duplicateValues" dxfId="1441" priority="2106"/>
+    <cfRule type="duplicateValues" dxfId="1437" priority="2106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B403">
-    <cfRule type="duplicateValues" dxfId="1440" priority="2105"/>
+    <cfRule type="duplicateValues" dxfId="1436" priority="2105"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B403">
-    <cfRule type="duplicateValues" dxfId="1439" priority="2104"/>
+    <cfRule type="duplicateValues" dxfId="1435" priority="2104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B404">
-    <cfRule type="duplicateValues" dxfId="1438" priority="2103"/>
+    <cfRule type="duplicateValues" dxfId="1434" priority="2103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B404">
-    <cfRule type="duplicateValues" dxfId="1437" priority="2102"/>
+    <cfRule type="duplicateValues" dxfId="1433" priority="2102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B405">
-    <cfRule type="duplicateValues" dxfId="1436" priority="2101"/>
+    <cfRule type="duplicateValues" dxfId="1432" priority="2101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B405">
-    <cfRule type="duplicateValues" dxfId="1435" priority="2100"/>
+    <cfRule type="duplicateValues" dxfId="1431" priority="2100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B406">
-    <cfRule type="duplicateValues" dxfId="1434" priority="2099"/>
+    <cfRule type="duplicateValues" dxfId="1430" priority="2099"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B406">
-    <cfRule type="duplicateValues" dxfId="1433" priority="2098"/>
+    <cfRule type="duplicateValues" dxfId="1429" priority="2098"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B407">
-    <cfRule type="duplicateValues" dxfId="1432" priority="2097"/>
+    <cfRule type="duplicateValues" dxfId="1428" priority="2097"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B407">
-    <cfRule type="duplicateValues" dxfId="1431" priority="2096"/>
+    <cfRule type="duplicateValues" dxfId="1427" priority="2096"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B408">
-    <cfRule type="duplicateValues" dxfId="1430" priority="2095"/>
+    <cfRule type="duplicateValues" dxfId="1426" priority="2095"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B408">
-    <cfRule type="duplicateValues" dxfId="1429" priority="2094"/>
+    <cfRule type="duplicateValues" dxfId="1425" priority="2094"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B409">
-    <cfRule type="duplicateValues" dxfId="1428" priority="2093"/>
+    <cfRule type="duplicateValues" dxfId="1424" priority="2093"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B409">
-    <cfRule type="duplicateValues" dxfId="1427" priority="2092"/>
+    <cfRule type="duplicateValues" dxfId="1423" priority="2092"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B410">
-    <cfRule type="duplicateValues" dxfId="1426" priority="2091"/>
+    <cfRule type="duplicateValues" dxfId="1422" priority="2091"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B410">
-    <cfRule type="duplicateValues" dxfId="1425" priority="2090"/>
+    <cfRule type="duplicateValues" dxfId="1421" priority="2090"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B411">
-    <cfRule type="duplicateValues" dxfId="1424" priority="2089"/>
+    <cfRule type="duplicateValues" dxfId="1420" priority="2089"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B411">
-    <cfRule type="duplicateValues" dxfId="1423" priority="2088"/>
+    <cfRule type="duplicateValues" dxfId="1419" priority="2088"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B412">
-    <cfRule type="duplicateValues" dxfId="1422" priority="2085"/>
+    <cfRule type="duplicateValues" dxfId="1418" priority="2085"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B412">
-    <cfRule type="duplicateValues" dxfId="1421" priority="2084"/>
+    <cfRule type="duplicateValues" dxfId="1417" priority="2084"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B413">
-    <cfRule type="duplicateValues" dxfId="1420" priority="2081"/>
+    <cfRule type="duplicateValues" dxfId="1416" priority="2081"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B413">
-    <cfRule type="duplicateValues" dxfId="1419" priority="2080"/>
+    <cfRule type="duplicateValues" dxfId="1415" priority="2080"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B414">
-    <cfRule type="duplicateValues" dxfId="1418" priority="2079"/>
+    <cfRule type="duplicateValues" dxfId="1414" priority="2079"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B414">
-    <cfRule type="duplicateValues" dxfId="1417" priority="2078"/>
+    <cfRule type="duplicateValues" dxfId="1413" priority="2078"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B416">
-    <cfRule type="duplicateValues" dxfId="1416" priority="2069"/>
+    <cfRule type="duplicateValues" dxfId="1412" priority="2069"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B416">
-    <cfRule type="duplicateValues" dxfId="1415" priority="2068"/>
+    <cfRule type="duplicateValues" dxfId="1411" priority="2068"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B417">
-    <cfRule type="duplicateValues" dxfId="1414" priority="2067"/>
+    <cfRule type="duplicateValues" dxfId="1410" priority="2067"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B417">
-    <cfRule type="duplicateValues" dxfId="1413" priority="2066"/>
+    <cfRule type="duplicateValues" dxfId="1409" priority="2066"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B422">
-    <cfRule type="duplicateValues" dxfId="1412" priority="2063"/>
+    <cfRule type="duplicateValues" dxfId="1408" priority="2063"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B422">
-    <cfRule type="duplicateValues" dxfId="1411" priority="2062"/>
+    <cfRule type="duplicateValues" dxfId="1407" priority="2062"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B421">
-    <cfRule type="duplicateValues" dxfId="1410" priority="2061"/>
+    <cfRule type="duplicateValues" dxfId="1406" priority="2061"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B421">
-    <cfRule type="duplicateValues" dxfId="1409" priority="2060"/>
+    <cfRule type="duplicateValues" dxfId="1405" priority="2060"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B423">
-    <cfRule type="duplicateValues" dxfId="1408" priority="2057"/>
+    <cfRule type="duplicateValues" dxfId="1404" priority="2057"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B423">
-    <cfRule type="duplicateValues" dxfId="1407" priority="2056"/>
+    <cfRule type="duplicateValues" dxfId="1403" priority="2056"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B424">
-    <cfRule type="duplicateValues" dxfId="1406" priority="2055"/>
+    <cfRule type="duplicateValues" dxfId="1402" priority="2055"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B424">
-    <cfRule type="duplicateValues" dxfId="1405" priority="2054"/>
+    <cfRule type="duplicateValues" dxfId="1401" priority="2054"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B425">
-    <cfRule type="duplicateValues" dxfId="1404" priority="2053"/>
+    <cfRule type="duplicateValues" dxfId="1400" priority="2053"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B425">
-    <cfRule type="duplicateValues" dxfId="1403" priority="2052"/>
+    <cfRule type="duplicateValues" dxfId="1399" priority="2052"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B426">
-    <cfRule type="duplicateValues" dxfId="1402" priority="2051"/>
+    <cfRule type="duplicateValues" dxfId="1398" priority="2051"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B426">
-    <cfRule type="duplicateValues" dxfId="1401" priority="2050"/>
+    <cfRule type="duplicateValues" dxfId="1397" priority="2050"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B427">
-    <cfRule type="duplicateValues" dxfId="1400" priority="2049"/>
+    <cfRule type="duplicateValues" dxfId="1396" priority="2049"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B427">
-    <cfRule type="duplicateValues" dxfId="1399" priority="2048"/>
+    <cfRule type="duplicateValues" dxfId="1395" priority="2048"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B428">
-    <cfRule type="duplicateValues" dxfId="1398" priority="2047"/>
+    <cfRule type="duplicateValues" dxfId="1394" priority="2047"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B428">
-    <cfRule type="duplicateValues" dxfId="1397" priority="2046"/>
+    <cfRule type="duplicateValues" dxfId="1393" priority="2046"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B429">
-    <cfRule type="duplicateValues" dxfId="1396" priority="2045"/>
+    <cfRule type="duplicateValues" dxfId="1392" priority="2045"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B429">
-    <cfRule type="duplicateValues" dxfId="1395" priority="2044"/>
+    <cfRule type="duplicateValues" dxfId="1391" priority="2044"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B432">
-    <cfRule type="duplicateValues" dxfId="1394" priority="2041"/>
+    <cfRule type="duplicateValues" dxfId="1390" priority="2041"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B432">
-    <cfRule type="duplicateValues" dxfId="1393" priority="2040"/>
+    <cfRule type="duplicateValues" dxfId="1389" priority="2040"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B431">
-    <cfRule type="duplicateValues" dxfId="1392" priority="2039"/>
+    <cfRule type="duplicateValues" dxfId="1388" priority="2039"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B431">
-    <cfRule type="duplicateValues" dxfId="1391" priority="2038"/>
+    <cfRule type="duplicateValues" dxfId="1387" priority="2038"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B434">
-    <cfRule type="duplicateValues" dxfId="1390" priority="2037"/>
+    <cfRule type="duplicateValues" dxfId="1386" priority="2037"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B434">
-    <cfRule type="duplicateValues" dxfId="1389" priority="2036"/>
+    <cfRule type="duplicateValues" dxfId="1385" priority="2036"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B435">
-    <cfRule type="duplicateValues" dxfId="1388" priority="2033"/>
+    <cfRule type="duplicateValues" dxfId="1384" priority="2033"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B435">
-    <cfRule type="duplicateValues" dxfId="1387" priority="2032"/>
+    <cfRule type="duplicateValues" dxfId="1383" priority="2032"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B437">
-    <cfRule type="duplicateValues" dxfId="1386" priority="2029"/>
+    <cfRule type="duplicateValues" dxfId="1382" priority="2029"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B437">
-    <cfRule type="duplicateValues" dxfId="1385" priority="2028"/>
+    <cfRule type="duplicateValues" dxfId="1381" priority="2028"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B436">
-    <cfRule type="duplicateValues" dxfId="1384" priority="2027"/>
+    <cfRule type="duplicateValues" dxfId="1380" priority="2027"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B436">
-    <cfRule type="duplicateValues" dxfId="1383" priority="2026"/>
+    <cfRule type="duplicateValues" dxfId="1379" priority="2026"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B440">
-    <cfRule type="duplicateValues" dxfId="1382" priority="2025"/>
+    <cfRule type="duplicateValues" dxfId="1378" priority="2025"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B440">
-    <cfRule type="duplicateValues" dxfId="1381" priority="2024"/>
+    <cfRule type="duplicateValues" dxfId="1377" priority="2024"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B443">
-    <cfRule type="duplicateValues" dxfId="1380" priority="2021"/>
+    <cfRule type="duplicateValues" dxfId="1376" priority="2021"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B443">
-    <cfRule type="duplicateValues" dxfId="1379" priority="2020"/>
+    <cfRule type="duplicateValues" dxfId="1375" priority="2020"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B445">
-    <cfRule type="duplicateValues" dxfId="1378" priority="2019"/>
+    <cfRule type="duplicateValues" dxfId="1374" priority="2019"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B445">
-    <cfRule type="duplicateValues" dxfId="1377" priority="2018"/>
+    <cfRule type="duplicateValues" dxfId="1373" priority="2018"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B446">
-    <cfRule type="duplicateValues" dxfId="1376" priority="2015"/>
+    <cfRule type="duplicateValues" dxfId="1372" priority="2015"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B446">
-    <cfRule type="duplicateValues" dxfId="1375" priority="2014"/>
+    <cfRule type="duplicateValues" dxfId="1371" priority="2014"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B447">
-    <cfRule type="duplicateValues" dxfId="1374" priority="2013"/>
+    <cfRule type="duplicateValues" dxfId="1370" priority="2013"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B447">
-    <cfRule type="duplicateValues" dxfId="1373" priority="2012"/>
+    <cfRule type="duplicateValues" dxfId="1369" priority="2012"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B449">
-    <cfRule type="duplicateValues" dxfId="1372" priority="2011"/>
+    <cfRule type="duplicateValues" dxfId="1368" priority="2011"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B449">
-    <cfRule type="duplicateValues" dxfId="1371" priority="2010"/>
+    <cfRule type="duplicateValues" dxfId="1367" priority="2010"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B450">
-    <cfRule type="duplicateValues" dxfId="1370" priority="2009"/>
+    <cfRule type="duplicateValues" dxfId="1366" priority="2009"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B450">
-    <cfRule type="duplicateValues" dxfId="1369" priority="2008"/>
+    <cfRule type="duplicateValues" dxfId="1365" priority="2008"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B452">
-    <cfRule type="duplicateValues" dxfId="1368" priority="2007"/>
+    <cfRule type="duplicateValues" dxfId="1364" priority="2007"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B452">
-    <cfRule type="duplicateValues" dxfId="1367" priority="2006"/>
+    <cfRule type="duplicateValues" dxfId="1363" priority="2006"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B453">
-    <cfRule type="duplicateValues" dxfId="1366" priority="2003"/>
+    <cfRule type="duplicateValues" dxfId="1362" priority="2003"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B453">
-    <cfRule type="duplicateValues" dxfId="1365" priority="2002"/>
+    <cfRule type="duplicateValues" dxfId="1361" priority="2002"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B454">
-    <cfRule type="duplicateValues" dxfId="1364" priority="1997"/>
+    <cfRule type="duplicateValues" dxfId="1360" priority="1997"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B454">
-    <cfRule type="duplicateValues" dxfId="1363" priority="1996"/>
+    <cfRule type="duplicateValues" dxfId="1359" priority="1996"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B455">
-    <cfRule type="duplicateValues" dxfId="1362" priority="1995"/>
+    <cfRule type="duplicateValues" dxfId="1358" priority="1995"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B455">
-    <cfRule type="duplicateValues" dxfId="1361" priority="1994"/>
+    <cfRule type="duplicateValues" dxfId="1357" priority="1994"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B457">
-    <cfRule type="duplicateValues" dxfId="1360" priority="1991"/>
+    <cfRule type="duplicateValues" dxfId="1356" priority="1991"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B457">
-    <cfRule type="duplicateValues" dxfId="1359" priority="1990"/>
+    <cfRule type="duplicateValues" dxfId="1355" priority="1990"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B458">
-    <cfRule type="duplicateValues" dxfId="1358" priority="1989"/>
+    <cfRule type="duplicateValues" dxfId="1354" priority="1989"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B458">
-    <cfRule type="duplicateValues" dxfId="1357" priority="1988"/>
+    <cfRule type="duplicateValues" dxfId="1353" priority="1988"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B460">
-    <cfRule type="duplicateValues" dxfId="1356" priority="1987"/>
+    <cfRule type="duplicateValues" dxfId="1352" priority="1987"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B460">
-    <cfRule type="duplicateValues" dxfId="1355" priority="1986"/>
+    <cfRule type="duplicateValues" dxfId="1351" priority="1986"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B461">
-    <cfRule type="duplicateValues" dxfId="1354" priority="1985"/>
+    <cfRule type="duplicateValues" dxfId="1350" priority="1985"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B461">
-    <cfRule type="duplicateValues" dxfId="1353" priority="1984"/>
+    <cfRule type="duplicateValues" dxfId="1349" priority="1984"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B462">
-    <cfRule type="duplicateValues" dxfId="1352" priority="1981"/>
+    <cfRule type="duplicateValues" dxfId="1348" priority="1981"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B462">
-    <cfRule type="duplicateValues" dxfId="1351" priority="1980"/>
+    <cfRule type="duplicateValues" dxfId="1347" priority="1980"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B465">
-    <cfRule type="duplicateValues" dxfId="1350" priority="1977"/>
+    <cfRule type="duplicateValues" dxfId="1346" priority="1977"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B465">
-    <cfRule type="duplicateValues" dxfId="1349" priority="1976"/>
+    <cfRule type="duplicateValues" dxfId="1345" priority="1976"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B469">
-    <cfRule type="duplicateValues" dxfId="1348" priority="1975"/>
+    <cfRule type="duplicateValues" dxfId="1344" priority="1975"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B469">
-    <cfRule type="duplicateValues" dxfId="1347" priority="1974"/>
+    <cfRule type="duplicateValues" dxfId="1343" priority="1974"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B470">
-    <cfRule type="duplicateValues" dxfId="1346" priority="1973"/>
+    <cfRule type="duplicateValues" dxfId="1342" priority="1973"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B470">
-    <cfRule type="duplicateValues" dxfId="1345" priority="1972"/>
+    <cfRule type="duplicateValues" dxfId="1341" priority="1972"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B473">
-    <cfRule type="duplicateValues" dxfId="1344" priority="1969"/>
+    <cfRule type="duplicateValues" dxfId="1340" priority="1969"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B473">
-    <cfRule type="duplicateValues" dxfId="1343" priority="1968"/>
+    <cfRule type="duplicateValues" dxfId="1339" priority="1968"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B474">
-    <cfRule type="duplicateValues" dxfId="1342" priority="1967"/>
+    <cfRule type="duplicateValues" dxfId="1338" priority="1967"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B474">
-    <cfRule type="duplicateValues" dxfId="1341" priority="1966"/>
+    <cfRule type="duplicateValues" dxfId="1337" priority="1966"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B478">
-    <cfRule type="duplicateValues" dxfId="1340" priority="1961"/>
+    <cfRule type="duplicateValues" dxfId="1336" priority="1961"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B478">
-    <cfRule type="duplicateValues" dxfId="1339" priority="1960"/>
+    <cfRule type="duplicateValues" dxfId="1335" priority="1960"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B479">
-    <cfRule type="duplicateValues" dxfId="1338" priority="1957"/>
+    <cfRule type="duplicateValues" dxfId="1334" priority="1957"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B479">
-    <cfRule type="duplicateValues" dxfId="1337" priority="1956"/>
+    <cfRule type="duplicateValues" dxfId="1333" priority="1956"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B481">
-    <cfRule type="duplicateValues" dxfId="1336" priority="1949"/>
+    <cfRule type="duplicateValues" dxfId="1332" priority="1949"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B481">
-    <cfRule type="duplicateValues" dxfId="1335" priority="1948"/>
+    <cfRule type="duplicateValues" dxfId="1331" priority="1948"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B482">
-    <cfRule type="duplicateValues" dxfId="1334" priority="1947"/>
+    <cfRule type="duplicateValues" dxfId="1330" priority="1947"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B482">
-    <cfRule type="duplicateValues" dxfId="1333" priority="1946"/>
+    <cfRule type="duplicateValues" dxfId="1329" priority="1946"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B484">
-    <cfRule type="duplicateValues" dxfId="1332" priority="1945"/>
+    <cfRule type="duplicateValues" dxfId="1328" priority="1945"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B484">
-    <cfRule type="duplicateValues" dxfId="1331" priority="1944"/>
+    <cfRule type="duplicateValues" dxfId="1327" priority="1944"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B486">
-    <cfRule type="duplicateValues" dxfId="1330" priority="1935"/>
+    <cfRule type="duplicateValues" dxfId="1326" priority="1935"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B486">
-    <cfRule type="duplicateValues" dxfId="1329" priority="1934"/>
+    <cfRule type="duplicateValues" dxfId="1325" priority="1934"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B489">
-    <cfRule type="duplicateValues" dxfId="1328" priority="1931"/>
+    <cfRule type="duplicateValues" dxfId="1324" priority="1931"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B489">
-    <cfRule type="duplicateValues" dxfId="1327" priority="1930"/>
+    <cfRule type="duplicateValues" dxfId="1323" priority="1930"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B490">
-    <cfRule type="duplicateValues" dxfId="1326" priority="1929"/>
+    <cfRule type="duplicateValues" dxfId="1322" priority="1929"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B490">
-    <cfRule type="duplicateValues" dxfId="1325" priority="1928"/>
+    <cfRule type="duplicateValues" dxfId="1321" priority="1928"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B496">
-    <cfRule type="duplicateValues" dxfId="1324" priority="1913"/>
+    <cfRule type="duplicateValues" dxfId="1320" priority="1913"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B496">
-    <cfRule type="duplicateValues" dxfId="1323" priority="1912"/>
+    <cfRule type="duplicateValues" dxfId="1319" priority="1912"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B497">
-    <cfRule type="duplicateValues" dxfId="1322" priority="1911"/>
+    <cfRule type="duplicateValues" dxfId="1318" priority="1911"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B497">
-    <cfRule type="duplicateValues" dxfId="1321" priority="1910"/>
+    <cfRule type="duplicateValues" dxfId="1317" priority="1910"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B498">
-    <cfRule type="duplicateValues" dxfId="1320" priority="1907"/>
+    <cfRule type="duplicateValues" dxfId="1316" priority="1907"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B498">
-    <cfRule type="duplicateValues" dxfId="1319" priority="1906"/>
+    <cfRule type="duplicateValues" dxfId="1315" priority="1906"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B501">
-    <cfRule type="duplicateValues" dxfId="1318" priority="1901"/>
+    <cfRule type="duplicateValues" dxfId="1314" priority="1901"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B501">
-    <cfRule type="duplicateValues" dxfId="1317" priority="1900"/>
+    <cfRule type="duplicateValues" dxfId="1313" priority="1900"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B502">
-    <cfRule type="duplicateValues" dxfId="1316" priority="1899"/>
+    <cfRule type="duplicateValues" dxfId="1312" priority="1899"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B502:B503">
-    <cfRule type="duplicateValues" dxfId="1315" priority="1898"/>
+    <cfRule type="duplicateValues" dxfId="1311" priority="1898"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B503">
-    <cfRule type="duplicateValues" dxfId="1314" priority="1897"/>
+    <cfRule type="duplicateValues" dxfId="1310" priority="1897"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B503">
-    <cfRule type="duplicateValues" dxfId="1313" priority="1896"/>
+    <cfRule type="duplicateValues" dxfId="1309" priority="1896"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B504">
-    <cfRule type="duplicateValues" dxfId="1312" priority="1895"/>
+    <cfRule type="duplicateValues" dxfId="1308" priority="1895"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B504">
-    <cfRule type="duplicateValues" dxfId="1311" priority="1894"/>
+    <cfRule type="duplicateValues" dxfId="1307" priority="1894"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B508">
-    <cfRule type="duplicateValues" dxfId="1310" priority="1885"/>
+    <cfRule type="duplicateValues" dxfId="1306" priority="1885"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B508">
-    <cfRule type="duplicateValues" dxfId="1309" priority="1884"/>
+    <cfRule type="duplicateValues" dxfId="1305" priority="1884"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B509">
-    <cfRule type="duplicateValues" dxfId="1308" priority="1883"/>
+    <cfRule type="duplicateValues" dxfId="1304" priority="1883"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B509">
-    <cfRule type="duplicateValues" dxfId="1307" priority="1882"/>
+    <cfRule type="duplicateValues" dxfId="1303" priority="1882"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B510">
-    <cfRule type="duplicateValues" dxfId="1306" priority="1881"/>
+    <cfRule type="duplicateValues" dxfId="1302" priority="1881"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B510">
-    <cfRule type="duplicateValues" dxfId="1305" priority="1880"/>
+    <cfRule type="duplicateValues" dxfId="1301" priority="1880"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B512">
-    <cfRule type="duplicateValues" dxfId="1304" priority="1877"/>
+    <cfRule type="duplicateValues" dxfId="1300" priority="1877"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B512">
-    <cfRule type="duplicateValues" dxfId="1303" priority="1876"/>
+    <cfRule type="duplicateValues" dxfId="1299" priority="1876"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B513">
-    <cfRule type="duplicateValues" dxfId="1302" priority="1875"/>
+    <cfRule type="duplicateValues" dxfId="1298" priority="1875"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B513">
-    <cfRule type="duplicateValues" dxfId="1301" priority="1874"/>
+    <cfRule type="duplicateValues" dxfId="1297" priority="1874"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B515">
-    <cfRule type="duplicateValues" dxfId="1300" priority="1873"/>
+    <cfRule type="duplicateValues" dxfId="1296" priority="1873"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B515">
-    <cfRule type="duplicateValues" dxfId="1299" priority="1872"/>
+    <cfRule type="duplicateValues" dxfId="1295" priority="1872"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B516">
-    <cfRule type="duplicateValues" dxfId="1298" priority="1865"/>
+    <cfRule type="duplicateValues" dxfId="1294" priority="1865"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B516">
-    <cfRule type="duplicateValues" dxfId="1297" priority="1864"/>
+    <cfRule type="duplicateValues" dxfId="1293" priority="1864"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B517">
-    <cfRule type="duplicateValues" dxfId="1296" priority="1861"/>
+    <cfRule type="duplicateValues" dxfId="1292" priority="1861"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B517">
-    <cfRule type="duplicateValues" dxfId="1295" priority="1860"/>
+    <cfRule type="duplicateValues" dxfId="1291" priority="1860"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B518">
-    <cfRule type="duplicateValues" dxfId="1294" priority="1857"/>
+    <cfRule type="duplicateValues" dxfId="1290" priority="1857"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B518">
-    <cfRule type="duplicateValues" dxfId="1293" priority="1856"/>
+    <cfRule type="duplicateValues" dxfId="1289" priority="1856"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B522">
-    <cfRule type="duplicateValues" dxfId="1292" priority="1853"/>
+    <cfRule type="duplicateValues" dxfId="1288" priority="1853"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B522">
-    <cfRule type="duplicateValues" dxfId="1291" priority="1852"/>
+    <cfRule type="duplicateValues" dxfId="1287" priority="1852"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B520">
-    <cfRule type="duplicateValues" dxfId="1290" priority="1851"/>
+    <cfRule type="duplicateValues" dxfId="1286" priority="1851"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B520">
-    <cfRule type="duplicateValues" dxfId="1289" priority="1850"/>
+    <cfRule type="duplicateValues" dxfId="1285" priority="1850"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B521">
-    <cfRule type="duplicateValues" dxfId="1288" priority="1847"/>
+    <cfRule type="duplicateValues" dxfId="1284" priority="1847"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B521">
-    <cfRule type="duplicateValues" dxfId="1287" priority="1846"/>
+    <cfRule type="duplicateValues" dxfId="1283" priority="1846"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B523">
-    <cfRule type="duplicateValues" dxfId="1286" priority="1841"/>
+    <cfRule type="duplicateValues" dxfId="1282" priority="1841"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B523">
-    <cfRule type="duplicateValues" dxfId="1285" priority="1840"/>
+    <cfRule type="duplicateValues" dxfId="1281" priority="1840"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B527">
-    <cfRule type="duplicateValues" dxfId="1284" priority="1835"/>
+    <cfRule type="duplicateValues" dxfId="1280" priority="1835"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B527">
-    <cfRule type="duplicateValues" dxfId="1283" priority="1834"/>
+    <cfRule type="duplicateValues" dxfId="1279" priority="1834"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B526">
-    <cfRule type="duplicateValues" dxfId="1282" priority="1833"/>
+    <cfRule type="duplicateValues" dxfId="1278" priority="1833"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B526">
-    <cfRule type="duplicateValues" dxfId="1281" priority="1832"/>
+    <cfRule type="duplicateValues" dxfId="1277" priority="1832"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B525">
-    <cfRule type="duplicateValues" dxfId="1280" priority="1831"/>
+    <cfRule type="duplicateValues" dxfId="1276" priority="1831"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B525">
-    <cfRule type="duplicateValues" dxfId="1279" priority="1830"/>
+    <cfRule type="duplicateValues" dxfId="1275" priority="1830"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B530">
-    <cfRule type="duplicateValues" dxfId="1278" priority="1829"/>
+    <cfRule type="duplicateValues" dxfId="1274" priority="1829"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B530">
-    <cfRule type="duplicateValues" dxfId="1277" priority="1828"/>
+    <cfRule type="duplicateValues" dxfId="1273" priority="1828"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B536">
-    <cfRule type="duplicateValues" dxfId="1276" priority="1827"/>
+    <cfRule type="duplicateValues" dxfId="1272" priority="1827"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B536">
-    <cfRule type="duplicateValues" dxfId="1275" priority="1826"/>
+    <cfRule type="duplicateValues" dxfId="1271" priority="1826"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B538">
-    <cfRule type="duplicateValues" dxfId="1274" priority="1825"/>
+    <cfRule type="duplicateValues" dxfId="1270" priority="1825"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B538">
-    <cfRule type="duplicateValues" dxfId="1273" priority="1824"/>
+    <cfRule type="duplicateValues" dxfId="1269" priority="1824"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B540">
-    <cfRule type="duplicateValues" dxfId="1272" priority="1821"/>
+    <cfRule type="duplicateValues" dxfId="1268" priority="1821"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B540">
-    <cfRule type="duplicateValues" dxfId="1271" priority="1820"/>
+    <cfRule type="duplicateValues" dxfId="1267" priority="1820"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B543">
-    <cfRule type="duplicateValues" dxfId="1270" priority="1817"/>
+    <cfRule type="duplicateValues" dxfId="1266" priority="1817"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B543">
-    <cfRule type="duplicateValues" dxfId="1269" priority="1816"/>
+    <cfRule type="duplicateValues" dxfId="1265" priority="1816"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B541">
-    <cfRule type="duplicateValues" dxfId="1268" priority="1815"/>
+    <cfRule type="duplicateValues" dxfId="1264" priority="1815"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B541">
-    <cfRule type="duplicateValues" dxfId="1267" priority="1814"/>
+    <cfRule type="duplicateValues" dxfId="1263" priority="1814"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B542">
-    <cfRule type="duplicateValues" dxfId="1266" priority="1809"/>
+    <cfRule type="duplicateValues" dxfId="1262" priority="1809"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B542">
-    <cfRule type="duplicateValues" dxfId="1265" priority="1808"/>
+    <cfRule type="duplicateValues" dxfId="1261" priority="1808"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B544">
-    <cfRule type="duplicateValues" dxfId="1264" priority="1805"/>
+    <cfRule type="duplicateValues" dxfId="1260" priority="1805"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B544">
-    <cfRule type="duplicateValues" dxfId="1263" priority="1804"/>
+    <cfRule type="duplicateValues" dxfId="1259" priority="1804"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B545">
-    <cfRule type="duplicateValues" dxfId="1262" priority="1801"/>
+    <cfRule type="duplicateValues" dxfId="1258" priority="1801"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B545">
-    <cfRule type="duplicateValues" dxfId="1261" priority="1800"/>
+    <cfRule type="duplicateValues" dxfId="1257" priority="1800"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B546">
-    <cfRule type="duplicateValues" dxfId="1260" priority="1799"/>
+    <cfRule type="duplicateValues" dxfId="1256" priority="1799"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B546">
-    <cfRule type="duplicateValues" dxfId="1259" priority="1798"/>
+    <cfRule type="duplicateValues" dxfId="1255" priority="1798"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B547">
-    <cfRule type="duplicateValues" dxfId="1258" priority="1795"/>
+    <cfRule type="duplicateValues" dxfId="1254" priority="1795"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B547">
-    <cfRule type="duplicateValues" dxfId="1257" priority="1794"/>
+    <cfRule type="duplicateValues" dxfId="1253" priority="1794"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B549">
-    <cfRule type="duplicateValues" dxfId="1256" priority="1793"/>
+    <cfRule type="duplicateValues" dxfId="1252" priority="1793"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B549">
-    <cfRule type="duplicateValues" dxfId="1255" priority="1792"/>
+    <cfRule type="duplicateValues" dxfId="1251" priority="1792"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B551">
-    <cfRule type="duplicateValues" dxfId="1254" priority="1789"/>
+    <cfRule type="duplicateValues" dxfId="1250" priority="1789"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B551">
-    <cfRule type="duplicateValues" dxfId="1253" priority="1788"/>
+    <cfRule type="duplicateValues" dxfId="1249" priority="1788"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B552">
-    <cfRule type="duplicateValues" dxfId="1252" priority="1787"/>
+    <cfRule type="duplicateValues" dxfId="1248" priority="1787"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B552">
-    <cfRule type="duplicateValues" dxfId="1251" priority="1786"/>
+    <cfRule type="duplicateValues" dxfId="1247" priority="1786"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B553">
-    <cfRule type="duplicateValues" dxfId="1250" priority="1781"/>
+    <cfRule type="duplicateValues" dxfId="1246" priority="1781"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B553">
-    <cfRule type="duplicateValues" dxfId="1249" priority="1780"/>
+    <cfRule type="duplicateValues" dxfId="1245" priority="1780"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B554">
-    <cfRule type="duplicateValues" dxfId="1248" priority="1779"/>
+    <cfRule type="duplicateValues" dxfId="1244" priority="1779"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B554">
-    <cfRule type="duplicateValues" dxfId="1247" priority="1778"/>
+    <cfRule type="duplicateValues" dxfId="1243" priority="1778"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B555">
-    <cfRule type="duplicateValues" dxfId="1246" priority="1773"/>
+    <cfRule type="duplicateValues" dxfId="1242" priority="1773"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B555">
-    <cfRule type="duplicateValues" dxfId="1245" priority="1772"/>
+    <cfRule type="duplicateValues" dxfId="1241" priority="1772"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B556">
-    <cfRule type="duplicateValues" dxfId="1244" priority="1771"/>
+    <cfRule type="duplicateValues" dxfId="1240" priority="1771"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B556">
-    <cfRule type="duplicateValues" dxfId="1243" priority="1770"/>
+    <cfRule type="duplicateValues" dxfId="1239" priority="1770"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B557">
-    <cfRule type="duplicateValues" dxfId="1242" priority="1767"/>
+    <cfRule type="duplicateValues" dxfId="1238" priority="1767"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B557">
-    <cfRule type="duplicateValues" dxfId="1241" priority="1766"/>
+    <cfRule type="duplicateValues" dxfId="1237" priority="1766"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B558">
-    <cfRule type="duplicateValues" dxfId="1240" priority="1765"/>
+    <cfRule type="duplicateValues" dxfId="1236" priority="1765"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B558">
-    <cfRule type="duplicateValues" dxfId="1239" priority="1764"/>
+    <cfRule type="duplicateValues" dxfId="1235" priority="1764"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B562">
-    <cfRule type="duplicateValues" dxfId="1238" priority="1755"/>
+    <cfRule type="duplicateValues" dxfId="1234" priority="1755"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B562">
-    <cfRule type="duplicateValues" dxfId="1237" priority="1754"/>
+    <cfRule type="duplicateValues" dxfId="1233" priority="1754"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B564">
-    <cfRule type="duplicateValues" dxfId="1236" priority="1753"/>
+    <cfRule type="duplicateValues" dxfId="1232" priority="1753"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B564">
-    <cfRule type="duplicateValues" dxfId="1235" priority="1752"/>
+    <cfRule type="duplicateValues" dxfId="1231" priority="1752"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B563">
-    <cfRule type="duplicateValues" dxfId="1234" priority="1751"/>
+    <cfRule type="duplicateValues" dxfId="1230" priority="1751"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B563">
-    <cfRule type="duplicateValues" dxfId="1233" priority="1750"/>
+    <cfRule type="duplicateValues" dxfId="1229" priority="1750"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B565">
-    <cfRule type="duplicateValues" dxfId="1232" priority="1749"/>
+    <cfRule type="duplicateValues" dxfId="1228" priority="1749"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B565">
-    <cfRule type="duplicateValues" dxfId="1231" priority="1748"/>
+    <cfRule type="duplicateValues" dxfId="1227" priority="1748"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B566">
-    <cfRule type="duplicateValues" dxfId="1230" priority="1741"/>
+    <cfRule type="duplicateValues" dxfId="1226" priority="1741"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B566">
-    <cfRule type="duplicateValues" dxfId="1229" priority="1740"/>
+    <cfRule type="duplicateValues" dxfId="1225" priority="1740"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B569">
-    <cfRule type="duplicateValues" dxfId="1228" priority="1739"/>
+    <cfRule type="duplicateValues" dxfId="1224" priority="1739"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B569">
-    <cfRule type="duplicateValues" dxfId="1227" priority="1738"/>
+    <cfRule type="duplicateValues" dxfId="1223" priority="1738"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B567">
-    <cfRule type="duplicateValues" dxfId="1226" priority="1735"/>
+    <cfRule type="duplicateValues" dxfId="1222" priority="1735"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B567">
-    <cfRule type="duplicateValues" dxfId="1225" priority="1734"/>
+    <cfRule type="duplicateValues" dxfId="1221" priority="1734"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B568">
-    <cfRule type="duplicateValues" dxfId="1224" priority="1731"/>
+    <cfRule type="duplicateValues" dxfId="1220" priority="1731"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B568">
-    <cfRule type="duplicateValues" dxfId="1223" priority="1730"/>
+    <cfRule type="duplicateValues" dxfId="1219" priority="1730"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B571">
-    <cfRule type="duplicateValues" dxfId="1222" priority="1721"/>
+    <cfRule type="duplicateValues" dxfId="1218" priority="1721"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B572">
-    <cfRule type="duplicateValues" dxfId="1221" priority="1718"/>
+    <cfRule type="duplicateValues" dxfId="1217" priority="1718"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B572">
-    <cfRule type="duplicateValues" dxfId="1220" priority="1717"/>
+    <cfRule type="duplicateValues" dxfId="1216" priority="1717"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B575">
-    <cfRule type="duplicateValues" dxfId="1219" priority="1715"/>
+    <cfRule type="duplicateValues" dxfId="1215" priority="1715"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B575">
-    <cfRule type="duplicateValues" dxfId="1218" priority="1716"/>
+    <cfRule type="duplicateValues" dxfId="1214" priority="1716"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B577">
-    <cfRule type="duplicateValues" dxfId="1217" priority="1714"/>
+    <cfRule type="duplicateValues" dxfId="1213" priority="1714"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B577">
-    <cfRule type="duplicateValues" dxfId="1216" priority="1713"/>
+    <cfRule type="duplicateValues" dxfId="1212" priority="1713"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B578">
-    <cfRule type="duplicateValues" dxfId="1215" priority="1703"/>
+    <cfRule type="duplicateValues" dxfId="1211" priority="1703"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B578">
-    <cfRule type="duplicateValues" dxfId="1214" priority="1704"/>
+    <cfRule type="duplicateValues" dxfId="1210" priority="1704"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B579">
-    <cfRule type="duplicateValues" dxfId="1213" priority="1700"/>
+    <cfRule type="duplicateValues" dxfId="1209" priority="1700"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B580">
-    <cfRule type="duplicateValues" dxfId="1212" priority="1697"/>
+    <cfRule type="duplicateValues" dxfId="1208" priority="1697"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B581">
-    <cfRule type="duplicateValues" dxfId="1211" priority="1694"/>
+    <cfRule type="duplicateValues" dxfId="1207" priority="1694"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B581">
-    <cfRule type="duplicateValues" dxfId="1210" priority="1693"/>
+    <cfRule type="duplicateValues" dxfId="1206" priority="1693"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B582">
-    <cfRule type="duplicateValues" dxfId="1209" priority="1692"/>
+    <cfRule type="duplicateValues" dxfId="1205" priority="1692"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B582">
-    <cfRule type="duplicateValues" dxfId="1208" priority="1691"/>
+    <cfRule type="duplicateValues" dxfId="1204" priority="1691"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B583">
-    <cfRule type="duplicateValues" dxfId="1207" priority="1690"/>
+    <cfRule type="duplicateValues" dxfId="1203" priority="1690"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B583">
-    <cfRule type="duplicateValues" dxfId="1206" priority="1689"/>
+    <cfRule type="duplicateValues" dxfId="1202" priority="1689"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B584">
-    <cfRule type="duplicateValues" dxfId="1205" priority="1688"/>
+    <cfRule type="duplicateValues" dxfId="1201" priority="1688"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B584">
-    <cfRule type="duplicateValues" dxfId="1204" priority="1687"/>
+    <cfRule type="duplicateValues" dxfId="1200" priority="1687"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B587">
-    <cfRule type="duplicateValues" dxfId="1203" priority="1685"/>
+    <cfRule type="duplicateValues" dxfId="1199" priority="1685"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B587">
-    <cfRule type="duplicateValues" dxfId="1202" priority="1686"/>
+    <cfRule type="duplicateValues" dxfId="1198" priority="1686"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B586">
-    <cfRule type="duplicateValues" dxfId="1201" priority="1683"/>
+    <cfRule type="duplicateValues" dxfId="1197" priority="1683"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B586">
-    <cfRule type="duplicateValues" dxfId="1200" priority="1684"/>
+    <cfRule type="duplicateValues" dxfId="1196" priority="1684"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B589">
-    <cfRule type="duplicateValues" dxfId="1199" priority="1677"/>
+    <cfRule type="duplicateValues" dxfId="1195" priority="1677"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B589">
-    <cfRule type="duplicateValues" dxfId="1198" priority="1678"/>
+    <cfRule type="duplicateValues" dxfId="1194" priority="1678"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B591">
-    <cfRule type="duplicateValues" dxfId="1197" priority="1673"/>
+    <cfRule type="duplicateValues" dxfId="1193" priority="1673"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B591">
-    <cfRule type="duplicateValues" dxfId="1196" priority="1674"/>
+    <cfRule type="duplicateValues" dxfId="1192" priority="1674"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B592">
-    <cfRule type="duplicateValues" dxfId="1195" priority="1671"/>
+    <cfRule type="duplicateValues" dxfId="1191" priority="1671"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B592">
-    <cfRule type="duplicateValues" dxfId="1194" priority="1672"/>
+    <cfRule type="duplicateValues" dxfId="1190" priority="1672"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B593">
-    <cfRule type="duplicateValues" dxfId="1193" priority="1669"/>
+    <cfRule type="duplicateValues" dxfId="1189" priority="1669"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B593">
-    <cfRule type="duplicateValues" dxfId="1192" priority="1670"/>
+    <cfRule type="duplicateValues" dxfId="1188" priority="1670"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B594">
-    <cfRule type="duplicateValues" dxfId="1191" priority="1665"/>
+    <cfRule type="duplicateValues" dxfId="1187" priority="1665"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B594">
-    <cfRule type="duplicateValues" dxfId="1190" priority="1666"/>
+    <cfRule type="duplicateValues" dxfId="1186" priority="1666"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B595">
-    <cfRule type="duplicateValues" dxfId="1189" priority="1661"/>
+    <cfRule type="duplicateValues" dxfId="1185" priority="1661"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B595">
-    <cfRule type="duplicateValues" dxfId="1188" priority="1662"/>
+    <cfRule type="duplicateValues" dxfId="1184" priority="1662"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B596">
-    <cfRule type="duplicateValues" dxfId="1187" priority="1660"/>
+    <cfRule type="duplicateValues" dxfId="1183" priority="1660"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B601">
-    <cfRule type="duplicateValues" dxfId="1186" priority="1657"/>
+    <cfRule type="duplicateValues" dxfId="1182" priority="1657"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B602">
-    <cfRule type="duplicateValues" dxfId="1185" priority="1655"/>
+    <cfRule type="duplicateValues" dxfId="1181" priority="1655"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B602">
-    <cfRule type="duplicateValues" dxfId="1184" priority="1656"/>
+    <cfRule type="duplicateValues" dxfId="1180" priority="1656"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B604">
-    <cfRule type="duplicateValues" dxfId="1183" priority="1653"/>
+    <cfRule type="duplicateValues" dxfId="1179" priority="1653"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B604">
-    <cfRule type="duplicateValues" dxfId="1182" priority="1654"/>
+    <cfRule type="duplicateValues" dxfId="1178" priority="1654"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B603">
-    <cfRule type="duplicateValues" dxfId="1181" priority="1651"/>
+    <cfRule type="duplicateValues" dxfId="1177" priority="1651"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B603">
-    <cfRule type="duplicateValues" dxfId="1180" priority="1652"/>
+    <cfRule type="duplicateValues" dxfId="1176" priority="1652"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B605:B606">
-    <cfRule type="duplicateValues" dxfId="1179" priority="1649"/>
+    <cfRule type="duplicateValues" dxfId="1175" priority="1649"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B605:B606">
-    <cfRule type="duplicateValues" dxfId="1178" priority="1650"/>
+    <cfRule type="duplicateValues" dxfId="1174" priority="1650"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B607:B609">
-    <cfRule type="duplicateValues" dxfId="1177" priority="1647"/>
+    <cfRule type="duplicateValues" dxfId="1173" priority="1647"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B607:B609">
-    <cfRule type="duplicateValues" dxfId="1176" priority="1648"/>
+    <cfRule type="duplicateValues" dxfId="1172" priority="1648"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B610:B611">
-    <cfRule type="duplicateValues" dxfId="1175" priority="1641"/>
+    <cfRule type="duplicateValues" dxfId="1171" priority="1641"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B610:B611">
-    <cfRule type="duplicateValues" dxfId="1174" priority="1642"/>
+    <cfRule type="duplicateValues" dxfId="1170" priority="1642"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B612:B614">
-    <cfRule type="duplicateValues" dxfId="1173" priority="1640"/>
+    <cfRule type="duplicateValues" dxfId="1169" priority="1640"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B612:B614">
-    <cfRule type="duplicateValues" dxfId="1172" priority="1639"/>
+    <cfRule type="duplicateValues" dxfId="1168" priority="1639"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B615:B616">
-    <cfRule type="duplicateValues" dxfId="1171" priority="1637"/>
+    <cfRule type="duplicateValues" dxfId="1167" priority="1637"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B615:B616">
-    <cfRule type="duplicateValues" dxfId="1170" priority="1638"/>
+    <cfRule type="duplicateValues" dxfId="1166" priority="1638"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B617:B619">
-    <cfRule type="duplicateValues" dxfId="1169" priority="1631"/>
+    <cfRule type="duplicateValues" dxfId="1165" priority="1631"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B617:B619">
-    <cfRule type="duplicateValues" dxfId="1168" priority="1632"/>
+    <cfRule type="duplicateValues" dxfId="1164" priority="1632"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B620:B622">
-    <cfRule type="duplicateValues" dxfId="1167" priority="1629"/>
+    <cfRule type="duplicateValues" dxfId="1163" priority="1629"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B620:B622">
-    <cfRule type="duplicateValues" dxfId="1166" priority="1630"/>
+    <cfRule type="duplicateValues" dxfId="1162" priority="1630"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B625:B627">
-    <cfRule type="duplicateValues" dxfId="1165" priority="1627"/>
+    <cfRule type="duplicateValues" dxfId="1161" priority="1627"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B625:B627">
-    <cfRule type="duplicateValues" dxfId="1164" priority="1628"/>
+    <cfRule type="duplicateValues" dxfId="1160" priority="1628"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B628:B629">
-    <cfRule type="duplicateValues" dxfId="1163" priority="1622"/>
+    <cfRule type="duplicateValues" dxfId="1159" priority="1622"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B628:B629">
-    <cfRule type="duplicateValues" dxfId="1162" priority="1621"/>
+    <cfRule type="duplicateValues" dxfId="1158" priority="1621"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B630:B633">
-    <cfRule type="duplicateValues" dxfId="1161" priority="1618"/>
+    <cfRule type="duplicateValues" dxfId="1157" priority="1618"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B630:B633">
-    <cfRule type="duplicateValues" dxfId="1160" priority="1617"/>
+    <cfRule type="duplicateValues" dxfId="1156" priority="1617"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B634:B635">
-    <cfRule type="duplicateValues" dxfId="1159" priority="1614"/>
+    <cfRule type="duplicateValues" dxfId="1155" priority="1614"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B634:B635">
-    <cfRule type="duplicateValues" dxfId="1158" priority="1613"/>
+    <cfRule type="duplicateValues" dxfId="1154" priority="1613"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B636:B637">
-    <cfRule type="duplicateValues" dxfId="1157" priority="1611"/>
+    <cfRule type="duplicateValues" dxfId="1153" priority="1611"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B636:B637">
-    <cfRule type="duplicateValues" dxfId="1156" priority="1612"/>
+    <cfRule type="duplicateValues" dxfId="1152" priority="1612"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B638:B640">
-    <cfRule type="duplicateValues" dxfId="1155" priority="1608"/>
+    <cfRule type="duplicateValues" dxfId="1151" priority="1608"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B641:B643">
-    <cfRule type="duplicateValues" dxfId="1154" priority="1606"/>
+    <cfRule type="duplicateValues" dxfId="1150" priority="1606"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B641:B643">
-    <cfRule type="duplicateValues" dxfId="1153" priority="1607"/>
+    <cfRule type="duplicateValues" dxfId="1149" priority="1607"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B644:B645">
-    <cfRule type="duplicateValues" dxfId="1152" priority="1604"/>
+    <cfRule type="duplicateValues" dxfId="1148" priority="1604"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B644:B645">
-    <cfRule type="duplicateValues" dxfId="1151" priority="1605"/>
+    <cfRule type="duplicateValues" dxfId="1147" priority="1605"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D646:D648">
-    <cfRule type="duplicateValues" dxfId="1150" priority="1602"/>
+    <cfRule type="duplicateValues" dxfId="1146" priority="1602"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D646:D648">
-    <cfRule type="duplicateValues" dxfId="1149" priority="1603"/>
+    <cfRule type="duplicateValues" dxfId="1145" priority="1603"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B646:B648">
-    <cfRule type="duplicateValues" dxfId="1148" priority="1598"/>
+    <cfRule type="duplicateValues" dxfId="1144" priority="1598"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B646:B648">
-    <cfRule type="duplicateValues" dxfId="1147" priority="1599"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B656">
-    <cfRule type="duplicateValues" dxfId="1146" priority="1596"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B656">
-    <cfRule type="duplicateValues" dxfId="1145" priority="1597"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B658">
-    <cfRule type="duplicateValues" dxfId="1144" priority="1594"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B658">
-    <cfRule type="duplicateValues" dxfId="1143" priority="1595"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B657">
-    <cfRule type="duplicateValues" dxfId="1142" priority="1593"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B657">
-    <cfRule type="duplicateValues" dxfId="1141" priority="1592"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B659">
-    <cfRule type="duplicateValues" dxfId="1140" priority="1591"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B659">
-    <cfRule type="duplicateValues" dxfId="1139" priority="1590"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B660">
-    <cfRule type="duplicateValues" dxfId="1138" priority="1587"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B660">
-    <cfRule type="duplicateValues" dxfId="1137" priority="1586"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B661">
-    <cfRule type="duplicateValues" dxfId="1136" priority="1583"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B661">
-    <cfRule type="duplicateValues" dxfId="1135" priority="1582"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B662">
-    <cfRule type="duplicateValues" dxfId="1134" priority="1579"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B662">
-    <cfRule type="duplicateValues" dxfId="1133" priority="1578"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B663">
-    <cfRule type="duplicateValues" dxfId="1132" priority="1574"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B663">
-    <cfRule type="duplicateValues" dxfId="1131" priority="1575"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B664">
-    <cfRule type="duplicateValues" dxfId="1130" priority="1570"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B664">
-    <cfRule type="duplicateValues" dxfId="1129" priority="1571"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B665">
-    <cfRule type="duplicateValues" dxfId="1128" priority="1566"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B665">
-    <cfRule type="duplicateValues" dxfId="1127" priority="1567"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B666">
-    <cfRule type="duplicateValues" dxfId="1126" priority="1564"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B666">
-    <cfRule type="duplicateValues" dxfId="1125" priority="1565"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B668">
-    <cfRule type="duplicateValues" dxfId="1124" priority="1562"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B668">
-    <cfRule type="duplicateValues" dxfId="1123" priority="1563"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B667">
-    <cfRule type="duplicateValues" dxfId="1122" priority="1560"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B667">
-    <cfRule type="duplicateValues" dxfId="1121" priority="1561"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B669">
-    <cfRule type="duplicateValues" dxfId="1120" priority="1558"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B669">
-    <cfRule type="duplicateValues" dxfId="1119" priority="1559"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B671">
-    <cfRule type="duplicateValues" dxfId="1118" priority="1556"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B671">
-    <cfRule type="duplicateValues" dxfId="1117" priority="1557"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B672">
-    <cfRule type="duplicateValues" dxfId="1116" priority="1552"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B672">
-    <cfRule type="duplicateValues" dxfId="1115" priority="1553"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B673">
-    <cfRule type="duplicateValues" dxfId="1114" priority="1550"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B673">
-    <cfRule type="duplicateValues" dxfId="1113" priority="1551"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B675">
-    <cfRule type="duplicateValues" dxfId="1112" priority="1547"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B675">
-    <cfRule type="duplicateValues" dxfId="1111" priority="1546"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B674">
-    <cfRule type="duplicateValues" dxfId="1110" priority="1544"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B674">
-    <cfRule type="duplicateValues" dxfId="1109" priority="1545"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B676">
-    <cfRule type="duplicateValues" dxfId="1108" priority="1541"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B676">
-    <cfRule type="duplicateValues" dxfId="1107" priority="1540"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B677">
-    <cfRule type="duplicateValues" dxfId="1106" priority="1538"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B677">
-    <cfRule type="duplicateValues" dxfId="1105" priority="1539"/>
+    <cfRule type="duplicateValues" dxfId="1143" priority="1599"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B657:B658">
+    <cfRule type="duplicateValues" dxfId="1142" priority="1596"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B657:B658">
+    <cfRule type="duplicateValues" dxfId="1141" priority="1597"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B661:B663">
+    <cfRule type="duplicateValues" dxfId="1140" priority="1594"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B661:B663">
+    <cfRule type="duplicateValues" dxfId="1139" priority="1595"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B659:B660">
+    <cfRule type="duplicateValues" dxfId="1138" priority="1593"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B659:B660">
+    <cfRule type="duplicateValues" dxfId="1137" priority="1592"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B664:B666">
+    <cfRule type="duplicateValues" dxfId="1136" priority="1591"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B664:B666">
+    <cfRule type="duplicateValues" dxfId="1135" priority="1590"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B667:B668">
+    <cfRule type="duplicateValues" dxfId="1134" priority="1587"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B667:B668">
+    <cfRule type="duplicateValues" dxfId="1133" priority="1586"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B671:B673">
+    <cfRule type="duplicateValues" dxfId="1132" priority="1579"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B671:B673">
+    <cfRule type="duplicateValues" dxfId="1131" priority="1578"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B678">
-    <cfRule type="duplicateValues" dxfId="1104" priority="1533"/>
+    <cfRule type="duplicateValues" dxfId="1130" priority="1566"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B678">
-    <cfRule type="duplicateValues" dxfId="1103" priority="1532"/>
+    <cfRule type="duplicateValues" dxfId="1129" priority="1567"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B679">
-    <cfRule type="duplicateValues" dxfId="1102" priority="1528"/>
+    <cfRule type="duplicateValues" dxfId="1128" priority="1564"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B679">
-    <cfRule type="duplicateValues" dxfId="1101" priority="1529"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B680">
-    <cfRule type="duplicateValues" dxfId="1100" priority="1527"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B680">
-    <cfRule type="duplicateValues" dxfId="1099" priority="1526"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B681">
-    <cfRule type="duplicateValues" dxfId="1098" priority="1524"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B681">
-    <cfRule type="duplicateValues" dxfId="1097" priority="1525"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B682">
-    <cfRule type="duplicateValues" dxfId="1096" priority="1522"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B682">
-    <cfRule type="duplicateValues" dxfId="1095" priority="1523"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B683">
-    <cfRule type="duplicateValues" dxfId="1094" priority="1520"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B683">
-    <cfRule type="duplicateValues" dxfId="1093" priority="1521"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B684">
-    <cfRule type="duplicateValues" dxfId="1092" priority="1518"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B684">
-    <cfRule type="duplicateValues" dxfId="1091" priority="1519"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B685">
-    <cfRule type="duplicateValues" dxfId="1090" priority="1512"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B685">
-    <cfRule type="duplicateValues" dxfId="1089" priority="1513"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B687">
-    <cfRule type="duplicateValues" dxfId="1088" priority="1508"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B687">
-    <cfRule type="duplicateValues" dxfId="1087" priority="1509"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B688">
-    <cfRule type="duplicateValues" dxfId="1086" priority="1506"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B688">
-    <cfRule type="duplicateValues" dxfId="1085" priority="1507"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B689">
-    <cfRule type="duplicateValues" dxfId="1084" priority="1504"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B689">
-    <cfRule type="duplicateValues" dxfId="1083" priority="1505"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B690">
-    <cfRule type="duplicateValues" dxfId="1082" priority="1503"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B690">
-    <cfRule type="duplicateValues" dxfId="1081" priority="1502"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B691">
-    <cfRule type="duplicateValues" dxfId="1080" priority="1500"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B691">
-    <cfRule type="duplicateValues" dxfId="1079" priority="1501"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B692">
-    <cfRule type="duplicateValues" dxfId="1078" priority="1498"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B692">
-    <cfRule type="duplicateValues" dxfId="1077" priority="1499"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B693">
-    <cfRule type="duplicateValues" dxfId="1076" priority="1497"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B693">
-    <cfRule type="duplicateValues" dxfId="1075" priority="1496"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B697">
-    <cfRule type="duplicateValues" dxfId="1074" priority="1492"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B697">
-    <cfRule type="duplicateValues" dxfId="1073" priority="1493"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B698">
-    <cfRule type="duplicateValues" dxfId="1072" priority="1490"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B698">
-    <cfRule type="duplicateValues" dxfId="1071" priority="1491"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B699">
-    <cfRule type="duplicateValues" dxfId="1070" priority="1486"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B699">
-    <cfRule type="duplicateValues" dxfId="1069" priority="1487"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B700">
-    <cfRule type="duplicateValues" dxfId="1068" priority="1483"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B700">
-    <cfRule type="duplicateValues" dxfId="1067" priority="1482"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B701">
-    <cfRule type="duplicateValues" dxfId="1066" priority="1479"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B701">
-    <cfRule type="duplicateValues" dxfId="1065" priority="1478"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B703">
-    <cfRule type="duplicateValues" dxfId="1064" priority="1476"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B703">
-    <cfRule type="duplicateValues" dxfId="1063" priority="1477"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B704">
-    <cfRule type="duplicateValues" dxfId="1062" priority="1472"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B704">
-    <cfRule type="duplicateValues" dxfId="1061" priority="1473"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B705">
-    <cfRule type="duplicateValues" dxfId="1060" priority="1466"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B705">
-    <cfRule type="duplicateValues" dxfId="1059" priority="1467"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B706">
-    <cfRule type="duplicateValues" dxfId="1058" priority="1463"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B706">
-    <cfRule type="duplicateValues" dxfId="1057" priority="1464"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B706">
-    <cfRule type="duplicateValues" dxfId="1056" priority="1462"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B707">
-    <cfRule type="duplicateValues" dxfId="1055" priority="1457"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B707">
-    <cfRule type="duplicateValues" dxfId="1054" priority="1458"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B707">
-    <cfRule type="duplicateValues" dxfId="1053" priority="1456"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B708">
-    <cfRule type="duplicateValues" dxfId="1052" priority="1454"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B708">
-    <cfRule type="duplicateValues" dxfId="1051" priority="1455"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B708">
-    <cfRule type="duplicateValues" dxfId="1050" priority="1453"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B709">
-    <cfRule type="duplicateValues" dxfId="1049" priority="1451"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B709">
-    <cfRule type="duplicateValues" dxfId="1048" priority="1452"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B709">
-    <cfRule type="duplicateValues" dxfId="1047" priority="1450"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B710">
-    <cfRule type="duplicateValues" dxfId="1046" priority="1448"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B710">
-    <cfRule type="duplicateValues" dxfId="1045" priority="1449"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B710">
-    <cfRule type="duplicateValues" dxfId="1044" priority="1447"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B711">
-    <cfRule type="duplicateValues" dxfId="1043" priority="1442"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B711">
-    <cfRule type="duplicateValues" dxfId="1042" priority="1443"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B711">
-    <cfRule type="duplicateValues" dxfId="1041" priority="1441"/>
+    <cfRule type="duplicateValues" dxfId="1127" priority="1565"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B683:B685">
+    <cfRule type="duplicateValues" dxfId="1126" priority="1562"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B683:B685">
+    <cfRule type="duplicateValues" dxfId="1125" priority="1563"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B680:B682">
+    <cfRule type="duplicateValues" dxfId="1124" priority="1560"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B680:B682">
+    <cfRule type="duplicateValues" dxfId="1123" priority="1561"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B686:B687">
+    <cfRule type="duplicateValues" dxfId="1122" priority="1558"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B686:B687">
+    <cfRule type="duplicateValues" dxfId="1121" priority="1559"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B693:B694">
+    <cfRule type="duplicateValues" dxfId="1120" priority="1556"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B693:B694">
+    <cfRule type="duplicateValues" dxfId="1119" priority="1557"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B695">
+    <cfRule type="duplicateValues" dxfId="1118" priority="1552"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B695">
+    <cfRule type="duplicateValues" dxfId="1117" priority="1553"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B696:B698">
+    <cfRule type="duplicateValues" dxfId="1116" priority="1550"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B696:B698">
+    <cfRule type="duplicateValues" dxfId="1115" priority="1551"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B703:B706">
+    <cfRule type="duplicateValues" dxfId="1114" priority="1547"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B703:B706">
+    <cfRule type="duplicateValues" dxfId="1113" priority="1546"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B699:B702">
+    <cfRule type="duplicateValues" dxfId="1112" priority="1544"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B699:B702">
+    <cfRule type="duplicateValues" dxfId="1111" priority="1545"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B710:B711">
+    <cfRule type="duplicateValues" dxfId="1110" priority="1538"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B710:B711">
+    <cfRule type="duplicateValues" dxfId="1109" priority="1539"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B712">
-    <cfRule type="duplicateValues" dxfId="1040" priority="1437"/>
+    <cfRule type="duplicateValues" dxfId="1108" priority="1533"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B712">
-    <cfRule type="duplicateValues" dxfId="1039" priority="1436"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B712">
-    <cfRule type="duplicateValues" dxfId="1038" priority="1435"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B713">
-    <cfRule type="duplicateValues" dxfId="1037" priority="1431"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B713">
-    <cfRule type="duplicateValues" dxfId="1036" priority="1430"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B713">
-    <cfRule type="duplicateValues" dxfId="1035" priority="1429"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B715">
-    <cfRule type="duplicateValues" dxfId="1034" priority="1418"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B715">
-    <cfRule type="duplicateValues" dxfId="1033" priority="1419"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B715">
-    <cfRule type="duplicateValues" dxfId="1032" priority="1417"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B716">
-    <cfRule type="duplicateValues" dxfId="1031" priority="1415"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B716">
-    <cfRule type="duplicateValues" dxfId="1030" priority="1416"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B716">
-    <cfRule type="duplicateValues" dxfId="1029" priority="1414"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B718">
-    <cfRule type="duplicateValues" dxfId="1028" priority="1412"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B718">
-    <cfRule type="duplicateValues" dxfId="1027" priority="1413"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B718">
-    <cfRule type="duplicateValues" dxfId="1026" priority="1411"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B719">
-    <cfRule type="duplicateValues" dxfId="1025" priority="1409"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B719">
-    <cfRule type="duplicateValues" dxfId="1024" priority="1410"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B719">
-    <cfRule type="duplicateValues" dxfId="1023" priority="1408"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B720">
-    <cfRule type="duplicateValues" dxfId="1022" priority="1400"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B720">
-    <cfRule type="duplicateValues" dxfId="1021" priority="1401"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B720">
-    <cfRule type="duplicateValues" dxfId="1020" priority="1399"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B721">
-    <cfRule type="duplicateValues" dxfId="1019" priority="1397"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B721">
-    <cfRule type="duplicateValues" dxfId="1018" priority="1398"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B721">
-    <cfRule type="duplicateValues" dxfId="1017" priority="1396"/>
+    <cfRule type="duplicateValues" dxfId="1107" priority="1532"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B713:B714">
+    <cfRule type="duplicateValues" dxfId="1106" priority="1528"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B713:B714">
+    <cfRule type="duplicateValues" dxfId="1105" priority="1529"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B715:B716">
+    <cfRule type="duplicateValues" dxfId="1104" priority="1527"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B715:B716">
+    <cfRule type="duplicateValues" dxfId="1103" priority="1526"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B717:B719">
+    <cfRule type="duplicateValues" dxfId="1102" priority="1524"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B717:B719">
+    <cfRule type="duplicateValues" dxfId="1101" priority="1525"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B720:B721">
+    <cfRule type="duplicateValues" dxfId="1100" priority="1522"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B720:B721">
+    <cfRule type="duplicateValues" dxfId="1099" priority="1523"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B722">
-    <cfRule type="duplicateValues" dxfId="1016" priority="1392"/>
+    <cfRule type="duplicateValues" dxfId="1098" priority="1520"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B722">
-    <cfRule type="duplicateValues" dxfId="1015" priority="1391"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B722">
-    <cfRule type="duplicateValues" dxfId="1014" priority="1390"/>
+    <cfRule type="duplicateValues" dxfId="1097" priority="1521"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B723">
+    <cfRule type="duplicateValues" dxfId="1096" priority="1518"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B723">
+    <cfRule type="duplicateValues" dxfId="1095" priority="1519"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B724">
-    <cfRule type="duplicateValues" dxfId="1013" priority="1389"/>
+    <cfRule type="duplicateValues" dxfId="1094" priority="1512"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B724">
-    <cfRule type="duplicateValues" dxfId="1012" priority="1388"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B724">
-    <cfRule type="duplicateValues" dxfId="1011" priority="1387"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B725">
-    <cfRule type="duplicateValues" dxfId="1010" priority="1383"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B725">
-    <cfRule type="duplicateValues" dxfId="1009" priority="1382"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B725">
-    <cfRule type="duplicateValues" dxfId="1008" priority="1381"/>
+    <cfRule type="duplicateValues" dxfId="1093" priority="1513"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B726">
-    <cfRule type="duplicateValues" dxfId="1007" priority="1374"/>
+    <cfRule type="duplicateValues" dxfId="1092" priority="1508"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B726">
-    <cfRule type="duplicateValues" dxfId="1006" priority="1373"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B726">
-    <cfRule type="duplicateValues" dxfId="1005" priority="1372"/>
+    <cfRule type="duplicateValues" dxfId="1091" priority="1509"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B727">
-    <cfRule type="duplicateValues" dxfId="1004" priority="1370"/>
+    <cfRule type="duplicateValues" dxfId="1090" priority="1506"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B727">
-    <cfRule type="duplicateValues" dxfId="1003" priority="1371"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B727">
-    <cfRule type="duplicateValues" dxfId="1002" priority="1369"/>
+    <cfRule type="duplicateValues" dxfId="1089" priority="1507"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B728">
-    <cfRule type="duplicateValues" dxfId="1001" priority="1367"/>
+    <cfRule type="duplicateValues" dxfId="1088" priority="1504"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B728">
-    <cfRule type="duplicateValues" dxfId="1000" priority="1368"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B728">
-    <cfRule type="duplicateValues" dxfId="999" priority="1366"/>
+    <cfRule type="duplicateValues" dxfId="1087" priority="1505"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B729">
-    <cfRule type="duplicateValues" dxfId="998" priority="1358"/>
+    <cfRule type="duplicateValues" dxfId="1086" priority="1503"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B729">
-    <cfRule type="duplicateValues" dxfId="997" priority="1359"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B729">
-    <cfRule type="duplicateValues" dxfId="996" priority="1357"/>
+    <cfRule type="duplicateValues" dxfId="1085" priority="1502"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B730">
-    <cfRule type="duplicateValues" dxfId="995" priority="1355"/>
+    <cfRule type="duplicateValues" dxfId="1084" priority="1500"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B730">
-    <cfRule type="duplicateValues" dxfId="994" priority="1356"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B730">
-    <cfRule type="duplicateValues" dxfId="993" priority="1354"/>
+    <cfRule type="duplicateValues" dxfId="1083" priority="1501"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B731">
+    <cfRule type="duplicateValues" dxfId="1082" priority="1498"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B731">
+    <cfRule type="duplicateValues" dxfId="1081" priority="1499"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B732">
-    <cfRule type="duplicateValues" dxfId="992" priority="1349"/>
+    <cfRule type="duplicateValues" dxfId="1080" priority="1497"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B732">
-    <cfRule type="duplicateValues" dxfId="991" priority="1350"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B732">
-    <cfRule type="duplicateValues" dxfId="990" priority="1348"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B731">
-    <cfRule type="duplicateValues" dxfId="989" priority="1347"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B731">
-    <cfRule type="duplicateValues" dxfId="988" priority="1346"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B731">
-    <cfRule type="duplicateValues" dxfId="987" priority="1345"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B733">
-    <cfRule type="duplicateValues" dxfId="986" priority="1343"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B733">
-    <cfRule type="duplicateValues" dxfId="985" priority="1344"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B733">
-    <cfRule type="duplicateValues" dxfId="984" priority="1342"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B735">
-    <cfRule type="duplicateValues" dxfId="983" priority="1340"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B735">
-    <cfRule type="duplicateValues" dxfId="982" priority="1341"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B735">
-    <cfRule type="duplicateValues" dxfId="981" priority="1339"/>
+    <cfRule type="duplicateValues" dxfId="1079" priority="1496"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B736">
-    <cfRule type="duplicateValues" dxfId="980" priority="1337"/>
+    <cfRule type="duplicateValues" dxfId="1078" priority="1492"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B736">
-    <cfRule type="duplicateValues" dxfId="979" priority="1338"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B736">
-    <cfRule type="duplicateValues" dxfId="978" priority="1336"/>
+    <cfRule type="duplicateValues" dxfId="1077" priority="1493"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B737">
+    <cfRule type="duplicateValues" dxfId="1076" priority="1490"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B737">
+    <cfRule type="duplicateValues" dxfId="1075" priority="1491"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B738">
-    <cfRule type="duplicateValues" dxfId="977" priority="1335"/>
+    <cfRule type="duplicateValues" dxfId="1074" priority="1486"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B738">
-    <cfRule type="duplicateValues" dxfId="976" priority="1334"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B738">
-    <cfRule type="duplicateValues" dxfId="975" priority="1333"/>
+    <cfRule type="duplicateValues" dxfId="1073" priority="1487"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B739">
-    <cfRule type="duplicateValues" dxfId="974" priority="1331"/>
+    <cfRule type="duplicateValues" dxfId="1072" priority="1483"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B739">
-    <cfRule type="duplicateValues" dxfId="973" priority="1332"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B739">
-    <cfRule type="duplicateValues" dxfId="972" priority="1330"/>
+    <cfRule type="duplicateValues" dxfId="1071" priority="1482"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B740">
-    <cfRule type="duplicateValues" dxfId="971" priority="1328"/>
+    <cfRule type="duplicateValues" dxfId="1070" priority="1479"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B740">
-    <cfRule type="duplicateValues" dxfId="970" priority="1329"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B740">
-    <cfRule type="duplicateValues" dxfId="969" priority="1327"/>
+    <cfRule type="duplicateValues" dxfId="1069" priority="1478"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B742">
-    <cfRule type="duplicateValues" dxfId="968" priority="1325"/>
+    <cfRule type="duplicateValues" dxfId="1068" priority="1476"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B742">
-    <cfRule type="duplicateValues" dxfId="967" priority="1326"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B742">
-    <cfRule type="duplicateValues" dxfId="966" priority="1324"/>
+    <cfRule type="duplicateValues" dxfId="1067" priority="1477"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B743">
-    <cfRule type="duplicateValues" dxfId="965" priority="1319"/>
+    <cfRule type="duplicateValues" dxfId="1066" priority="1472"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B743">
-    <cfRule type="duplicateValues" dxfId="964" priority="1320"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B743">
-    <cfRule type="duplicateValues" dxfId="963" priority="1318"/>
+    <cfRule type="duplicateValues" dxfId="1065" priority="1473"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B744">
-    <cfRule type="duplicateValues" dxfId="962" priority="1316"/>
+    <cfRule type="duplicateValues" dxfId="1064" priority="1466"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B744">
-    <cfRule type="duplicateValues" dxfId="961" priority="1317"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B744">
-    <cfRule type="duplicateValues" dxfId="960" priority="1315"/>
+    <cfRule type="duplicateValues" dxfId="1063" priority="1467"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B745">
+    <cfRule type="duplicateValues" dxfId="1062" priority="1463"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B745">
+    <cfRule type="duplicateValues" dxfId="1061" priority="1464"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B745">
+    <cfRule type="duplicateValues" dxfId="1060" priority="1462"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B746">
-    <cfRule type="duplicateValues" dxfId="959" priority="1313"/>
+    <cfRule type="duplicateValues" dxfId="1059" priority="1457"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B746">
-    <cfRule type="duplicateValues" dxfId="958" priority="1314"/>
+    <cfRule type="duplicateValues" dxfId="1058" priority="1458"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B746">
-    <cfRule type="duplicateValues" dxfId="957" priority="1312"/>
+    <cfRule type="duplicateValues" dxfId="1057" priority="1456"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B747">
-    <cfRule type="duplicateValues" dxfId="956" priority="1307"/>
+    <cfRule type="duplicateValues" dxfId="1056" priority="1454"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B747">
-    <cfRule type="duplicateValues" dxfId="955" priority="1308"/>
+    <cfRule type="duplicateValues" dxfId="1055" priority="1455"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B747">
-    <cfRule type="duplicateValues" dxfId="954" priority="1306"/>
+    <cfRule type="duplicateValues" dxfId="1054" priority="1453"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B748">
-    <cfRule type="duplicateValues" dxfId="953" priority="1299"/>
+    <cfRule type="duplicateValues" dxfId="1053" priority="1451"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B748">
-    <cfRule type="duplicateValues" dxfId="952" priority="1298"/>
+    <cfRule type="duplicateValues" dxfId="1052" priority="1452"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B748">
-    <cfRule type="duplicateValues" dxfId="951" priority="1297"/>
+    <cfRule type="duplicateValues" dxfId="1051" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B749">
-    <cfRule type="duplicateValues" dxfId="950" priority="1296"/>
+    <cfRule type="duplicateValues" dxfId="1050" priority="1448"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B749">
-    <cfRule type="duplicateValues" dxfId="949" priority="1295"/>
+    <cfRule type="duplicateValues" dxfId="1049" priority="1449"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B749">
-    <cfRule type="duplicateValues" dxfId="948" priority="1294"/>
+    <cfRule type="duplicateValues" dxfId="1048" priority="1447"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B750">
+    <cfRule type="duplicateValues" dxfId="1047" priority="1442"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B750">
+    <cfRule type="duplicateValues" dxfId="1046" priority="1443"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B750">
+    <cfRule type="duplicateValues" dxfId="1045" priority="1441"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B751">
-    <cfRule type="duplicateValues" dxfId="947" priority="1293"/>
+    <cfRule type="duplicateValues" dxfId="1044" priority="1437"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B751">
-    <cfRule type="duplicateValues" dxfId="946" priority="1292"/>
+    <cfRule type="duplicateValues" dxfId="1043" priority="1436"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B751">
-    <cfRule type="duplicateValues" dxfId="945" priority="1291"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B750">
-    <cfRule type="duplicateValues" dxfId="944" priority="1290"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B750">
-    <cfRule type="duplicateValues" dxfId="943" priority="1289"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B750">
-    <cfRule type="duplicateValues" dxfId="942" priority="1288"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B753">
-    <cfRule type="duplicateValues" dxfId="941" priority="1286"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B753">
-    <cfRule type="duplicateValues" dxfId="940" priority="1287"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B753">
-    <cfRule type="duplicateValues" dxfId="939" priority="1285"/>
+    <cfRule type="duplicateValues" dxfId="1042" priority="1435"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B752">
+    <cfRule type="duplicateValues" dxfId="1041" priority="1431"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B752">
+    <cfRule type="duplicateValues" dxfId="1040" priority="1430"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B752">
+    <cfRule type="duplicateValues" dxfId="1039" priority="1429"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B754">
+    <cfRule type="duplicateValues" dxfId="1038" priority="1418"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B754">
+    <cfRule type="duplicateValues" dxfId="1037" priority="1419"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B754">
+    <cfRule type="duplicateValues" dxfId="1036" priority="1417"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B755">
-    <cfRule type="duplicateValues" dxfId="938" priority="1277"/>
+    <cfRule type="duplicateValues" dxfId="1035" priority="1415"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B755">
-    <cfRule type="duplicateValues" dxfId="937" priority="1278"/>
+    <cfRule type="duplicateValues" dxfId="1034" priority="1416"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B755">
-    <cfRule type="duplicateValues" dxfId="936" priority="1276"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B756">
-    <cfRule type="duplicateValues" dxfId="935" priority="1271"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B756">
-    <cfRule type="duplicateValues" dxfId="934" priority="1272"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B756">
-    <cfRule type="duplicateValues" dxfId="933" priority="1270"/>
+    <cfRule type="duplicateValues" dxfId="1033" priority="1414"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B757">
+    <cfRule type="duplicateValues" dxfId="1032" priority="1412"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B757">
+    <cfRule type="duplicateValues" dxfId="1031" priority="1413"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B757">
+    <cfRule type="duplicateValues" dxfId="1030" priority="1411"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B758">
-    <cfRule type="duplicateValues" dxfId="932" priority="1265"/>
+    <cfRule type="duplicateValues" dxfId="1029" priority="1409"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B758">
-    <cfRule type="duplicateValues" dxfId="931" priority="1266"/>
+    <cfRule type="duplicateValues" dxfId="1028" priority="1410"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B758">
-    <cfRule type="duplicateValues" dxfId="930" priority="1264"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B757">
-    <cfRule type="duplicateValues" dxfId="929" priority="1263"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B757">
-    <cfRule type="duplicateValues" dxfId="928" priority="1262"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B757">
-    <cfRule type="duplicateValues" dxfId="927" priority="1261"/>
+    <cfRule type="duplicateValues" dxfId="1027" priority="1408"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B759">
-    <cfRule type="duplicateValues" dxfId="926" priority="1256"/>
+    <cfRule type="duplicateValues" dxfId="1026" priority="1400"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B759">
-    <cfRule type="duplicateValues" dxfId="925" priority="1257"/>
+    <cfRule type="duplicateValues" dxfId="1025" priority="1401"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B759">
-    <cfRule type="duplicateValues" dxfId="924" priority="1255"/>
+    <cfRule type="duplicateValues" dxfId="1024" priority="1399"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B760">
+    <cfRule type="duplicateValues" dxfId="1023" priority="1397"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B760">
+    <cfRule type="duplicateValues" dxfId="1022" priority="1398"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B760">
+    <cfRule type="duplicateValues" dxfId="1021" priority="1396"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B761">
-    <cfRule type="duplicateValues" dxfId="923" priority="1254"/>
+    <cfRule type="duplicateValues" dxfId="1020" priority="1392"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B761">
-    <cfRule type="duplicateValues" dxfId="922" priority="1253"/>
+    <cfRule type="duplicateValues" dxfId="1019" priority="1391"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B761">
-    <cfRule type="duplicateValues" dxfId="921" priority="1252"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B762">
-    <cfRule type="duplicateValues" dxfId="920" priority="1250"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B762">
-    <cfRule type="duplicateValues" dxfId="919" priority="1251"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B762">
-    <cfRule type="duplicateValues" dxfId="918" priority="1249"/>
+    <cfRule type="duplicateValues" dxfId="1018" priority="1390"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B763">
-    <cfRule type="duplicateValues" dxfId="917" priority="1241"/>
+    <cfRule type="duplicateValues" dxfId="1017" priority="1389"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B763">
-    <cfRule type="duplicateValues" dxfId="916" priority="1242"/>
+    <cfRule type="duplicateValues" dxfId="1016" priority="1388"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B763">
-    <cfRule type="duplicateValues" dxfId="915" priority="1240"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B714 D46 B573:B574 B46 B104:B106 B109:B111 B126 B131 B134 B137 B143:B147 B150:B152 B159:B160 D154 B169 B181 B188 B190 B199 D195 B212 B222:B224 B229 B231:B232 B239:B240 B242:B244 B251 B258:B261 B264:B269 B273 B278 B288:B289 B291 B295:B299 B306:B307 B324 B331 B333 B337:B338 B340:B341 B343 B348 B345:B346 B351 B364 B372:B373 B378:B380 B389:B390 B396:B397 B401 B420 B430 B433 B438:B439 B442 B444 B448 B451 B459 B463 B466 B475:B476 B480 B488 B492:B495 B507 B514 B519 B524 B528:B529 B531:B535 B537 B539 B560 B576 B590 B599:B600 B623:B624 B649:B655 B670 B686 B694:B696 B702 B717 B723 B734 B737 B741 B745 B752 B754 B760 B770 B786 B789 B797 B799:B800 B806:B807 B812:B814 B836 B839 B842 B855:B858 B869 B871 B873:B874 B878 B881 B886:B887 B891 B893 B895:B896 B907 B909 B928 B942 B958:B959 B961 B963:B964 B973 B981:B1048576 B1:B8 B11:B15 B18:B19 B22 B24 B30:B31 B34 B39:B41 B43 B48:B50 B53 B56:B58 B62:B64 B74:B94 B96:B102 B114:B119 B122 B124 B183:B184 B468">
-    <cfRule type="duplicateValues" dxfId="914" priority="2582"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B714 B573:B574 B231:B232 B239:B240 B242:B244 B251 B258:B261 B264:B269 B273 B278 B288:B289 B291 B295:B299 B306:B307 B324 B331 B333 B337:B338 B340:B341 B343 B348 B345:B346 B351 B364 B372:B373 B378:B380 B389:B390 B396:B397 B401 B420 B430 B433 B438:B439 B442 B444 B448 B451 B459 B463 B466 B475:B476 B480 B488 B492:B495 B507 B514 B519 B524 B528:B529 B531:B535 B537 B539 B560 B576 B590 B599:B600 B623:B624 B649:B655 B670 B686 B694:B696 B702 B717 B723 B734 B737 B741 B745 B752 B754 B760 B770 B786 B789 B797 B799:B800 B806:B807 B812:B814 B836 B839 B842 B855:B858 B869 B871 B873:B874 B878 B881 B886:B887 B891 B893 B895:B896 B907 B909 B928 B942 B958:B959 B961 B963:B964 B973 B981:B1048576 B1:B8 B11:B15 B18:B19 B22 B24 B30:B31 B34 B39:B41 B43 B46 B48:B50 B53 B56:B58 B62:B64 B74:B94 B96:B106 B108:B111 B114:B119 B122 B124:B126 B128:B152 B154:B155 B157 B159:B164 B166:B167 B169:B170 B179 B181 B183:B184 B186:B188 B190:B202 B204:B205 B209:B212 B214 B216:B217 B219:B220 B222:B229 B468">
-    <cfRule type="duplicateValues" dxfId="913" priority="2694"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B714 B717 B723 B734 B737 B741 B745 B752 B754 B760 B770 B786 B789 B797 B799:B800 B806:B807 B812:B814 B836 B839 B842 B855:B858 B869 B871 B873:B874 B878 B881 B886:B887 B891 B893 B895:B896 B907 B909 B928 B942 B958:B959 B961 B963:B964 B973 B981:B1048576 B1:B8 B11:B15 B18:B19 B22 B24 B30:B31 B34 B39:B41 B43 B46 B48:B50 B53 B56:B58 B62:B64 B74:B94 B96:B106 B108:B111 B114:B119 B122 B124:B126 B128:B152 B154:B155 B157 B159:B164 B166:B167 B169:B170 B179 B181 B183:B184 B186:B188 B190:B202 B204:B205 B209:B212 B214 B216:B217 B219:B220 B222:B229 B231:B232 B237:B249 B251:B252 B255 B258:B261 B263:B269 B271 B273:B279 B281:B283 B286:B310 B312 B315 B317:B318 B320:B321 B324 B329:B353 B355:B361 B363:B368 B370:B383 B385:B390 B392:B414 B416:B417 B420:B440 B442:B455 B457:B463 B465:B466 B468:B470 B473:B476 B478:B482 B484 B486 B488:B490 B492:B498 B501:B504 B507:B510 B512:B547 B549 B551:B558 B560 B562:B569 B571:B584 B586:B587 B589:B596 B599:B705">
-    <cfRule type="duplicateValues" dxfId="912" priority="2780"/>
+    <cfRule type="duplicateValues" dxfId="1015" priority="1387"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B764">
-    <cfRule type="duplicateValues" dxfId="911" priority="1234"/>
+    <cfRule type="duplicateValues" dxfId="1014" priority="1383"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B764">
-    <cfRule type="duplicateValues" dxfId="910" priority="1235"/>
+    <cfRule type="duplicateValues" dxfId="1013" priority="1382"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B764">
-    <cfRule type="duplicateValues" dxfId="909" priority="1236"/>
+    <cfRule type="duplicateValues" dxfId="1012" priority="1381"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B765">
-    <cfRule type="duplicateValues" dxfId="908" priority="1229"/>
+    <cfRule type="duplicateValues" dxfId="1011" priority="1374"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B765">
-    <cfRule type="duplicateValues" dxfId="907" priority="1228"/>
+    <cfRule type="duplicateValues" dxfId="1010" priority="1373"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B765">
-    <cfRule type="duplicateValues" dxfId="906" priority="1230"/>
+    <cfRule type="duplicateValues" dxfId="1009" priority="1372"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B766">
-    <cfRule type="duplicateValues" dxfId="905" priority="1225"/>
+    <cfRule type="duplicateValues" dxfId="1008" priority="1370"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B766">
-    <cfRule type="duplicateValues" dxfId="904" priority="1226"/>
+    <cfRule type="duplicateValues" dxfId="1007" priority="1371"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B766">
-    <cfRule type="duplicateValues" dxfId="903" priority="1227"/>
+    <cfRule type="duplicateValues" dxfId="1006" priority="1369"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B767">
-    <cfRule type="duplicateValues" dxfId="902" priority="1220"/>
+    <cfRule type="duplicateValues" dxfId="1005" priority="1367"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B767">
-    <cfRule type="duplicateValues" dxfId="901" priority="1221"/>
+    <cfRule type="duplicateValues" dxfId="1004" priority="1368"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B767">
-    <cfRule type="duplicateValues" dxfId="900" priority="1219"/>
+    <cfRule type="duplicateValues" dxfId="1003" priority="1366"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B768">
-    <cfRule type="duplicateValues" dxfId="899" priority="1213"/>
+    <cfRule type="duplicateValues" dxfId="1002" priority="1358"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B768">
-    <cfRule type="duplicateValues" dxfId="898" priority="1214"/>
+    <cfRule type="duplicateValues" dxfId="1001" priority="1359"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B768">
-    <cfRule type="duplicateValues" dxfId="897" priority="1215"/>
+    <cfRule type="duplicateValues" dxfId="1000" priority="1357"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B769">
-    <cfRule type="duplicateValues" dxfId="896" priority="1211"/>
+    <cfRule type="duplicateValues" dxfId="999" priority="1355"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B769">
-    <cfRule type="duplicateValues" dxfId="895" priority="1212"/>
+    <cfRule type="duplicateValues" dxfId="998" priority="1356"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B769">
-    <cfRule type="duplicateValues" dxfId="894" priority="1210"/>
+    <cfRule type="duplicateValues" dxfId="997" priority="1354"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B771">
-    <cfRule type="duplicateValues" dxfId="893" priority="1205"/>
+    <cfRule type="duplicateValues" dxfId="996" priority="1349"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B771">
-    <cfRule type="duplicateValues" dxfId="892" priority="1206"/>
+    <cfRule type="duplicateValues" dxfId="995" priority="1350"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B771">
+    <cfRule type="duplicateValues" dxfId="994" priority="1348"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B770">
+    <cfRule type="duplicateValues" dxfId="993" priority="1347"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B770">
+    <cfRule type="duplicateValues" dxfId="992" priority="1346"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B770">
+    <cfRule type="duplicateValues" dxfId="991" priority="1345"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B772">
-    <cfRule type="duplicateValues" dxfId="891" priority="1203"/>
+    <cfRule type="duplicateValues" dxfId="990" priority="1343"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B772">
-    <cfRule type="duplicateValues" dxfId="890" priority="1202"/>
+    <cfRule type="duplicateValues" dxfId="989" priority="1344"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B772">
-    <cfRule type="duplicateValues" dxfId="889" priority="1204"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B773">
-    <cfRule type="duplicateValues" dxfId="888" priority="1196"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B773">
-    <cfRule type="duplicateValues" dxfId="887" priority="1197"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B773">
-    <cfRule type="duplicateValues" dxfId="886" priority="1198"/>
+    <cfRule type="duplicateValues" dxfId="988" priority="1342"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B774">
-    <cfRule type="duplicateValues" dxfId="885" priority="1193"/>
+    <cfRule type="duplicateValues" dxfId="987" priority="1340"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B774">
-    <cfRule type="duplicateValues" dxfId="884" priority="1194"/>
+    <cfRule type="duplicateValues" dxfId="986" priority="1341"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B774">
-    <cfRule type="duplicateValues" dxfId="883" priority="1195"/>
+    <cfRule type="duplicateValues" dxfId="985" priority="1339"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B775">
-    <cfRule type="duplicateValues" dxfId="882" priority="1187"/>
+    <cfRule type="duplicateValues" dxfId="984" priority="1337"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B775">
-    <cfRule type="duplicateValues" dxfId="881" priority="1188"/>
+    <cfRule type="duplicateValues" dxfId="983" priority="1338"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B775">
-    <cfRule type="duplicateValues" dxfId="880" priority="1189"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B776">
-    <cfRule type="duplicateValues" dxfId="879" priority="1172"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B776">
-    <cfRule type="duplicateValues" dxfId="878" priority="1173"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B776">
-    <cfRule type="duplicateValues" dxfId="877" priority="1174"/>
+    <cfRule type="duplicateValues" dxfId="982" priority="1336"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B777">
-    <cfRule type="duplicateValues" dxfId="876" priority="1166"/>
+    <cfRule type="duplicateValues" dxfId="981" priority="1335"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B777">
-    <cfRule type="duplicateValues" dxfId="875" priority="1167"/>
+    <cfRule type="duplicateValues" dxfId="980" priority="1334"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B777">
-    <cfRule type="duplicateValues" dxfId="874" priority="1168"/>
+    <cfRule type="duplicateValues" dxfId="979" priority="1333"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B778">
-    <cfRule type="duplicateValues" dxfId="873" priority="1160"/>
+    <cfRule type="duplicateValues" dxfId="978" priority="1331"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B778">
-    <cfRule type="duplicateValues" dxfId="872" priority="1161"/>
+    <cfRule type="duplicateValues" dxfId="977" priority="1332"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B778">
-    <cfRule type="duplicateValues" dxfId="871" priority="1162"/>
+    <cfRule type="duplicateValues" dxfId="976" priority="1330"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B779">
-    <cfRule type="duplicateValues" dxfId="870" priority="1158"/>
+    <cfRule type="duplicateValues" dxfId="975" priority="1328"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B779">
-    <cfRule type="duplicateValues" dxfId="869" priority="1159"/>
+    <cfRule type="duplicateValues" dxfId="974" priority="1329"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B779">
-    <cfRule type="duplicateValues" dxfId="868" priority="1157"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B780">
-    <cfRule type="duplicateValues" dxfId="867" priority="1148"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B780">
-    <cfRule type="duplicateValues" dxfId="866" priority="1149"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B780">
-    <cfRule type="duplicateValues" dxfId="865" priority="1150"/>
+    <cfRule type="duplicateValues" dxfId="973" priority="1327"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B781">
-    <cfRule type="duplicateValues" dxfId="864" priority="1140"/>
+    <cfRule type="duplicateValues" dxfId="972" priority="1325"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B781">
-    <cfRule type="duplicateValues" dxfId="863" priority="1139"/>
+    <cfRule type="duplicateValues" dxfId="971" priority="1326"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B781">
-    <cfRule type="duplicateValues" dxfId="862" priority="1141"/>
+    <cfRule type="duplicateValues" dxfId="970" priority="1324"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B782">
-    <cfRule type="duplicateValues" dxfId="861" priority="1137"/>
+    <cfRule type="duplicateValues" dxfId="969" priority="1319"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B782">
-    <cfRule type="duplicateValues" dxfId="860" priority="1136"/>
+    <cfRule type="duplicateValues" dxfId="968" priority="1320"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B782">
-    <cfRule type="duplicateValues" dxfId="859" priority="1138"/>
+    <cfRule type="duplicateValues" dxfId="967" priority="1318"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B783">
-    <cfRule type="duplicateValues" dxfId="858" priority="1131"/>
+    <cfRule type="duplicateValues" dxfId="966" priority="1316"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B783">
-    <cfRule type="duplicateValues" dxfId="857" priority="1132"/>
+    <cfRule type="duplicateValues" dxfId="965" priority="1317"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B783">
-    <cfRule type="duplicateValues" dxfId="856" priority="1130"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B784">
-    <cfRule type="duplicateValues" dxfId="855" priority="1124"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B784">
-    <cfRule type="duplicateValues" dxfId="854" priority="1125"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B784">
-    <cfRule type="duplicateValues" dxfId="853" priority="1126"/>
+    <cfRule type="duplicateValues" dxfId="964" priority="1315"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B785">
-    <cfRule type="duplicateValues" dxfId="852" priority="1121"/>
+    <cfRule type="duplicateValues" dxfId="963" priority="1313"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B785">
-    <cfRule type="duplicateValues" dxfId="851" priority="1122"/>
+    <cfRule type="duplicateValues" dxfId="962" priority="1314"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B785">
-    <cfRule type="duplicateValues" dxfId="850" priority="1123"/>
+    <cfRule type="duplicateValues" dxfId="961" priority="1312"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B786">
+    <cfRule type="duplicateValues" dxfId="960" priority="1307"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B786">
+    <cfRule type="duplicateValues" dxfId="959" priority="1308"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B786">
+    <cfRule type="duplicateValues" dxfId="958" priority="1306"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B787">
-    <cfRule type="duplicateValues" dxfId="849" priority="1118"/>
+    <cfRule type="duplicateValues" dxfId="957" priority="1299"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B787">
-    <cfRule type="duplicateValues" dxfId="848" priority="1119"/>
+    <cfRule type="duplicateValues" dxfId="956" priority="1298"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B787">
-    <cfRule type="duplicateValues" dxfId="847" priority="1120"/>
+    <cfRule type="duplicateValues" dxfId="955" priority="1297"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B788">
-    <cfRule type="duplicateValues" dxfId="846" priority="1115"/>
+    <cfRule type="duplicateValues" dxfId="954" priority="1296"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B788">
-    <cfRule type="duplicateValues" dxfId="845" priority="1116"/>
+    <cfRule type="duplicateValues" dxfId="953" priority="1295"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B788">
-    <cfRule type="duplicateValues" dxfId="844" priority="1117"/>
+    <cfRule type="duplicateValues" dxfId="952" priority="1294"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B790">
-    <cfRule type="duplicateValues" dxfId="843" priority="1114"/>
+    <cfRule type="duplicateValues" dxfId="951" priority="1293"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B790">
-    <cfRule type="duplicateValues" dxfId="842" priority="1113"/>
+    <cfRule type="duplicateValues" dxfId="950" priority="1292"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B790">
-    <cfRule type="duplicateValues" dxfId="841" priority="1112"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B791">
-    <cfRule type="duplicateValues" dxfId="840" priority="1109"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B791">
-    <cfRule type="duplicateValues" dxfId="839" priority="1110"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B791">
-    <cfRule type="duplicateValues" dxfId="838" priority="1111"/>
+    <cfRule type="duplicateValues" dxfId="949" priority="1291"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B789">
+    <cfRule type="duplicateValues" dxfId="948" priority="1290"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B789">
+    <cfRule type="duplicateValues" dxfId="947" priority="1289"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B789">
+    <cfRule type="duplicateValues" dxfId="946" priority="1288"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B792">
-    <cfRule type="duplicateValues" dxfId="837" priority="1106"/>
+    <cfRule type="duplicateValues" dxfId="945" priority="1286"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B792">
-    <cfRule type="duplicateValues" dxfId="836" priority="1107"/>
+    <cfRule type="duplicateValues" dxfId="944" priority="1287"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B792">
-    <cfRule type="duplicateValues" dxfId="835" priority="1108"/>
+    <cfRule type="duplicateValues" dxfId="943" priority="1285"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B794">
+    <cfRule type="duplicateValues" dxfId="942" priority="1277"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B794">
+    <cfRule type="duplicateValues" dxfId="941" priority="1278"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B794">
+    <cfRule type="duplicateValues" dxfId="940" priority="1276"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B795">
-    <cfRule type="duplicateValues" dxfId="834" priority="1104"/>
+    <cfRule type="duplicateValues" dxfId="939" priority="1271"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B795">
-    <cfRule type="duplicateValues" dxfId="833" priority="1105"/>
+    <cfRule type="duplicateValues" dxfId="938" priority="1272"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B795">
-    <cfRule type="duplicateValues" dxfId="832" priority="1103"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B793">
-    <cfRule type="duplicateValues" dxfId="831" priority="1101"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B793">
-    <cfRule type="duplicateValues" dxfId="830" priority="1102"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B794">
-    <cfRule type="duplicateValues" dxfId="829" priority="1096"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B794">
-    <cfRule type="duplicateValues" dxfId="828" priority="1097"/>
+    <cfRule type="duplicateValues" dxfId="937" priority="1270"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B797">
+    <cfRule type="duplicateValues" dxfId="936" priority="1265"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B797">
+    <cfRule type="duplicateValues" dxfId="935" priority="1266"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B797">
+    <cfRule type="duplicateValues" dxfId="934" priority="1264"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B796">
-    <cfRule type="duplicateValues" dxfId="827" priority="1091"/>
+    <cfRule type="duplicateValues" dxfId="933" priority="1263"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B796">
-    <cfRule type="duplicateValues" dxfId="826" priority="1092"/>
+    <cfRule type="duplicateValues" dxfId="932" priority="1262"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B796">
-    <cfRule type="duplicateValues" dxfId="825" priority="1090"/>
+    <cfRule type="duplicateValues" dxfId="931" priority="1261"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B798">
-    <cfRule type="duplicateValues" dxfId="824" priority="1087"/>
+    <cfRule type="duplicateValues" dxfId="930" priority="1256"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B798">
-    <cfRule type="duplicateValues" dxfId="823" priority="1088"/>
+    <cfRule type="duplicateValues" dxfId="929" priority="1257"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B798">
-    <cfRule type="duplicateValues" dxfId="822" priority="1089"/>
+    <cfRule type="duplicateValues" dxfId="928" priority="1255"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B800">
+    <cfRule type="duplicateValues" dxfId="927" priority="1254"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B800">
+    <cfRule type="duplicateValues" dxfId="926" priority="1253"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B800">
+    <cfRule type="duplicateValues" dxfId="925" priority="1252"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B801">
-    <cfRule type="duplicateValues" dxfId="821" priority="1084"/>
+    <cfRule type="duplicateValues" dxfId="924" priority="1250"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B801">
-    <cfRule type="duplicateValues" dxfId="820" priority="1085"/>
+    <cfRule type="duplicateValues" dxfId="923" priority="1251"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B801">
-    <cfRule type="duplicateValues" dxfId="819" priority="1086"/>
+    <cfRule type="duplicateValues" dxfId="922" priority="1249"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B802">
-    <cfRule type="duplicateValues" dxfId="818" priority="1081"/>
+    <cfRule type="duplicateValues" dxfId="921" priority="1241"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B802">
-    <cfRule type="duplicateValues" dxfId="817" priority="1082"/>
+    <cfRule type="duplicateValues" dxfId="920" priority="1242"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B802">
-    <cfRule type="duplicateValues" dxfId="816" priority="1083"/>
+    <cfRule type="duplicateValues" dxfId="919" priority="1240"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B753 D46 B573:B574 B46 B104:B106 B109:B111 B126 B131 B134 B137 B143:B147 B150:B152 B159:B160 D154 B169 B181 B188 B190 B199 D195 B212 B222:B224 B229 B231:B232 B239:B240 B242:B244 B251 B258:B261 B264:B269 B273 B278 B288:B289 B291 B295:B299 B306:B307 B324 B331 B333 B337:B338 B340:B341 B343 B348 B345:B346 B351 B364 B372:B373 B378:B380 B389:B390 B396:B397 B401 B420 B430 B433 B438:B439 B442 B444 B448 B451 B459 B463 B466 B475:B476 B480 B488 B492:B495 B507 B514 B519 B524 B528:B529 B531:B535 B537 B539 B560 B576 B590 B599:B600 B623:B624 B649:B656 B688:B692 B725 B733:B735 B741 B756 B762 B773 B776 B780 B784 B791 B793 B799 B809 B825 B828 B836 B838:B839 B845:B846 B851:B853 B875 B878 B881 B894:B897 B908 B910 B912:B913 B917 B920 B925:B926 B930 B932 B934:B935 B946 B948 B967 B981 B997:B998 B1000 B1002:B1003 B1012 B1020:B1048576 B1:B8 B11:B15 B18:B19 B22 B24 B30:B31 B34 B39:B41 B43 B48:B50 B53 B56:B58 B62:B64 B74:B94 B96:B102 B114:B119 B122 B124 B183:B184 B468">
+    <cfRule type="duplicateValues" dxfId="918" priority="2582"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B753 B573:B574 B231:B232 B239:B240 B242:B244 B251 B258:B261 B264:B269 B273 B278 B288:B289 B291 B295:B299 B306:B307 B324 B331 B333 B337:B338 B340:B341 B343 B348 B345:B346 B351 B364 B372:B373 B378:B380 B389:B390 B396:B397 B401 B420 B430 B433 B438:B439 B442 B444 B448 B451 B459 B463 B466 B475:B476 B480 B488 B492:B495 B507 B514 B519 B524 B528:B529 B531:B535 B537 B539 B560 B576 B590 B599:B600 B623:B624 B649:B656 B688:B692 B725 B733:B735 B741 B756 B762 B773 B776 B780 B784 B791 B793 B799 B809 B825 B828 B836 B838:B839 B845:B846 B851:B853 B875 B878 B881 B894:B897 B908 B910 B912:B913 B917 B920 B925:B926 B930 B932 B934:B935 B946 B948 B967 B981 B997:B998 B1000 B1002:B1003 B1012 B1020:B1048576 B1:B8 B11:B15 B18:B19 B22 B24 B30:B31 B34 B39:B41 B43 B46 B48:B50 B53 B56:B58 B62:B64 B74:B94 B96:B106 B108:B111 B114:B119 B122 B124:B126 B128:B152 B154:B155 B157 B159:B164 B166:B167 B169:B170 B179 B181 B183:B184 B186:B188 B190:B202 B204:B205 B209:B212 B214 B216:B217 B219:B220 B222:B229 B468">
+    <cfRule type="duplicateValues" dxfId="917" priority="2694"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B753 B756 B762 B773 B776 B780 B784 B791 B793 B799 B809 B825 B828 B836 B838:B839 B845:B846 B851:B853 B875 B878 B881 B894:B897 B908 B910 B912:B913 B917 B920 B925:B926 B930 B932 B934:B935 B946 B948 B967 B981 B997:B998 B1000 B1002:B1003 B1012 B1020:B1048576 B1:B8 B11:B15 B18:B19 B22 B24 B30:B31 B34 B39:B41 B43 B46 B48:B50 B53 B56:B58 B62:B64 B74:B94 B96:B106 B108:B111 B114:B119 B122 B124:B126 B128:B152 B154:B155 B157 B159:B164 B166:B167 B169:B170 B179 B181 B183:B184 B186:B188 B190:B202 B204:B205 B209:B212 B214 B216:B217 B219:B220 B222:B229 B231:B232 B237:B249 B251:B252 B255 B258:B261 B263:B269 B271 B273:B279 B281:B283 B286:B310 B312 B315 B317:B318 B320:B321 B324 B329:B353 B355:B361 B363:B368 B370:B383 B385:B390 B392:B414 B416:B417 B420:B440 B442:B455 B457:B463 B465:B466 B468:B470 B473:B476 B478:B482 B484 B486 B488:B490 B492:B498 B501:B504 B507:B510 B512:B547 B549 B551:B558 B560 B562:B569 B571:B584 B586:B587 B589:B596 B599:B744">
+    <cfRule type="duplicateValues" dxfId="916" priority="2780"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B803">
-    <cfRule type="duplicateValues" dxfId="815" priority="1078"/>
+    <cfRule type="duplicateValues" dxfId="915" priority="1234"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B803">
-    <cfRule type="duplicateValues" dxfId="814" priority="1079"/>
+    <cfRule type="duplicateValues" dxfId="914" priority="1235"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B803">
-    <cfRule type="duplicateValues" dxfId="813" priority="1080"/>
+    <cfRule type="duplicateValues" dxfId="913" priority="1236"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B804">
-    <cfRule type="duplicateValues" dxfId="812" priority="1066"/>
+    <cfRule type="duplicateValues" dxfId="912" priority="1229"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B804">
-    <cfRule type="duplicateValues" dxfId="811" priority="1067"/>
+    <cfRule type="duplicateValues" dxfId="911" priority="1228"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B804">
-    <cfRule type="duplicateValues" dxfId="810" priority="1068"/>
+    <cfRule type="duplicateValues" dxfId="910" priority="1230"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B805">
-    <cfRule type="duplicateValues" dxfId="809" priority="1061"/>
+    <cfRule type="duplicateValues" dxfId="909" priority="1225"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B805">
-    <cfRule type="duplicateValues" dxfId="808" priority="1062"/>
+    <cfRule type="duplicateValues" dxfId="908" priority="1226"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B805">
+    <cfRule type="duplicateValues" dxfId="907" priority="1227"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B806">
+    <cfRule type="duplicateValues" dxfId="906" priority="1220"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B806">
+    <cfRule type="duplicateValues" dxfId="905" priority="1221"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B806">
+    <cfRule type="duplicateValues" dxfId="904" priority="1219"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B807">
+    <cfRule type="duplicateValues" dxfId="903" priority="1213"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B807">
+    <cfRule type="duplicateValues" dxfId="902" priority="1214"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B807">
+    <cfRule type="duplicateValues" dxfId="901" priority="1215"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B808">
-    <cfRule type="duplicateValues" dxfId="807" priority="1055"/>
+    <cfRule type="duplicateValues" dxfId="900" priority="1211"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B808">
-    <cfRule type="duplicateValues" dxfId="806" priority="1056"/>
+    <cfRule type="duplicateValues" dxfId="899" priority="1212"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B808">
-    <cfRule type="duplicateValues" dxfId="805" priority="1057"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B809">
-    <cfRule type="duplicateValues" dxfId="804" priority="1049"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B809">
-    <cfRule type="duplicateValues" dxfId="803" priority="1050"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B809">
-    <cfRule type="duplicateValues" dxfId="802" priority="1051"/>
+    <cfRule type="duplicateValues" dxfId="898" priority="1210"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B810">
-    <cfRule type="duplicateValues" dxfId="801" priority="1046"/>
+    <cfRule type="duplicateValues" dxfId="897" priority="1205"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B810">
-    <cfRule type="duplicateValues" dxfId="800" priority="1047"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B810">
-    <cfRule type="duplicateValues" dxfId="799" priority="1048"/>
+    <cfRule type="duplicateValues" dxfId="896" priority="1206"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B811">
-    <cfRule type="duplicateValues" dxfId="798" priority="1040"/>
+    <cfRule type="duplicateValues" dxfId="895" priority="1203"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B811">
-    <cfRule type="duplicateValues" dxfId="797" priority="1041"/>
+    <cfRule type="duplicateValues" dxfId="894" priority="1202"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B811">
-    <cfRule type="duplicateValues" dxfId="796" priority="1042"/>
+    <cfRule type="duplicateValues" dxfId="893" priority="1204"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B812">
+    <cfRule type="duplicateValues" dxfId="892" priority="1196"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B812">
+    <cfRule type="duplicateValues" dxfId="891" priority="1197"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B812">
+    <cfRule type="duplicateValues" dxfId="890" priority="1198"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B813">
+    <cfRule type="duplicateValues" dxfId="889" priority="1193"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B813">
+    <cfRule type="duplicateValues" dxfId="888" priority="1194"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B813">
+    <cfRule type="duplicateValues" dxfId="887" priority="1195"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B814">
+    <cfRule type="duplicateValues" dxfId="886" priority="1187"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B814">
+    <cfRule type="duplicateValues" dxfId="885" priority="1188"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B814">
+    <cfRule type="duplicateValues" dxfId="884" priority="1189"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B815">
-    <cfRule type="duplicateValues" dxfId="795" priority="1031"/>
+    <cfRule type="duplicateValues" dxfId="883" priority="1172"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B815">
-    <cfRule type="duplicateValues" dxfId="794" priority="1032"/>
+    <cfRule type="duplicateValues" dxfId="882" priority="1173"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B815">
-    <cfRule type="duplicateValues" dxfId="793" priority="1033"/>
+    <cfRule type="duplicateValues" dxfId="881" priority="1174"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B816">
-    <cfRule type="duplicateValues" dxfId="792" priority="1028"/>
+    <cfRule type="duplicateValues" dxfId="880" priority="1166"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B816">
-    <cfRule type="duplicateValues" dxfId="791" priority="1029"/>
+    <cfRule type="duplicateValues" dxfId="879" priority="1167"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B816">
-    <cfRule type="duplicateValues" dxfId="790" priority="1030"/>
+    <cfRule type="duplicateValues" dxfId="878" priority="1168"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B817">
-    <cfRule type="duplicateValues" dxfId="789" priority="1022"/>
+    <cfRule type="duplicateValues" dxfId="877" priority="1160"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B817">
-    <cfRule type="duplicateValues" dxfId="788" priority="1023"/>
+    <cfRule type="duplicateValues" dxfId="876" priority="1161"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B817">
-    <cfRule type="duplicateValues" dxfId="787" priority="1024"/>
+    <cfRule type="duplicateValues" dxfId="875" priority="1162"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B818">
-    <cfRule type="duplicateValues" dxfId="786" priority="1013"/>
+    <cfRule type="duplicateValues" dxfId="874" priority="1158"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B818">
-    <cfRule type="duplicateValues" dxfId="785" priority="1014"/>
+    <cfRule type="duplicateValues" dxfId="873" priority="1159"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B818">
-    <cfRule type="duplicateValues" dxfId="784" priority="1015"/>
+    <cfRule type="duplicateValues" dxfId="872" priority="1157"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B819">
-    <cfRule type="duplicateValues" dxfId="783" priority="1010"/>
+    <cfRule type="duplicateValues" dxfId="871" priority="1148"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B819">
-    <cfRule type="duplicateValues" dxfId="782" priority="1011"/>
+    <cfRule type="duplicateValues" dxfId="870" priority="1149"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B819">
-    <cfRule type="duplicateValues" dxfId="781" priority="1012"/>
+    <cfRule type="duplicateValues" dxfId="869" priority="1150"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B820">
-    <cfRule type="duplicateValues" dxfId="780" priority="1004"/>
+    <cfRule type="duplicateValues" dxfId="868" priority="1140"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B820">
-    <cfRule type="duplicateValues" dxfId="779" priority="1005"/>
+    <cfRule type="duplicateValues" dxfId="867" priority="1139"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B820">
-    <cfRule type="duplicateValues" dxfId="778" priority="1006"/>
+    <cfRule type="duplicateValues" dxfId="866" priority="1141"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B821">
-    <cfRule type="duplicateValues" dxfId="777" priority="1002"/>
+    <cfRule type="duplicateValues" dxfId="865" priority="1137"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B821">
-    <cfRule type="duplicateValues" dxfId="776" priority="1003"/>
+    <cfRule type="duplicateValues" dxfId="864" priority="1136"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B821">
-    <cfRule type="duplicateValues" dxfId="775" priority="1001"/>
+    <cfRule type="duplicateValues" dxfId="863" priority="1138"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B822">
-    <cfRule type="duplicateValues" dxfId="774" priority="998"/>
+    <cfRule type="duplicateValues" dxfId="862" priority="1131"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B822">
-    <cfRule type="duplicateValues" dxfId="773" priority="999"/>
+    <cfRule type="duplicateValues" dxfId="861" priority="1132"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B822">
-    <cfRule type="duplicateValues" dxfId="772" priority="1000"/>
+    <cfRule type="duplicateValues" dxfId="860" priority="1130"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B823">
-    <cfRule type="duplicateValues" dxfId="771" priority="996"/>
+    <cfRule type="duplicateValues" dxfId="859" priority="1124"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B823">
-    <cfRule type="duplicateValues" dxfId="770" priority="995"/>
+    <cfRule type="duplicateValues" dxfId="858" priority="1125"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B823">
-    <cfRule type="duplicateValues" dxfId="769" priority="997"/>
+    <cfRule type="duplicateValues" dxfId="857" priority="1126"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B824">
-    <cfRule type="duplicateValues" dxfId="768" priority="986"/>
+    <cfRule type="duplicateValues" dxfId="856" priority="1121"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B824">
-    <cfRule type="duplicateValues" dxfId="767" priority="987"/>
+    <cfRule type="duplicateValues" dxfId="855" priority="1122"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B824">
-    <cfRule type="duplicateValues" dxfId="766" priority="988"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B825">
-    <cfRule type="duplicateValues" dxfId="765" priority="983"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B825">
-    <cfRule type="duplicateValues" dxfId="764" priority="984"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B825">
-    <cfRule type="duplicateValues" dxfId="763" priority="985"/>
+    <cfRule type="duplicateValues" dxfId="854" priority="1123"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B826">
-    <cfRule type="duplicateValues" dxfId="762" priority="980"/>
+    <cfRule type="duplicateValues" dxfId="853" priority="1118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B826">
-    <cfRule type="duplicateValues" dxfId="761" priority="981"/>
+    <cfRule type="duplicateValues" dxfId="852" priority="1119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B826">
-    <cfRule type="duplicateValues" dxfId="760" priority="982"/>
+    <cfRule type="duplicateValues" dxfId="851" priority="1120"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B827">
-    <cfRule type="duplicateValues" dxfId="759" priority="977"/>
+    <cfRule type="duplicateValues" dxfId="850" priority="1115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B827">
-    <cfRule type="duplicateValues" dxfId="758" priority="978"/>
+    <cfRule type="duplicateValues" dxfId="849" priority="1116"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B827">
-    <cfRule type="duplicateValues" dxfId="757" priority="979"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B828">
-    <cfRule type="duplicateValues" dxfId="756" priority="974"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B828">
-    <cfRule type="duplicateValues" dxfId="755" priority="975"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B828">
-    <cfRule type="duplicateValues" dxfId="754" priority="976"/>
+    <cfRule type="duplicateValues" dxfId="848" priority="1117"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B829">
-    <cfRule type="duplicateValues" dxfId="753" priority="971"/>
+    <cfRule type="duplicateValues" dxfId="847" priority="1114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B829">
-    <cfRule type="duplicateValues" dxfId="752" priority="972"/>
+    <cfRule type="duplicateValues" dxfId="846" priority="1113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B829">
-    <cfRule type="duplicateValues" dxfId="751" priority="973"/>
+    <cfRule type="duplicateValues" dxfId="845" priority="1112"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B830">
-    <cfRule type="duplicateValues" dxfId="750" priority="965"/>
+    <cfRule type="duplicateValues" dxfId="844" priority="1109"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B830">
-    <cfRule type="duplicateValues" dxfId="749" priority="966"/>
+    <cfRule type="duplicateValues" dxfId="843" priority="1110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B830">
-    <cfRule type="duplicateValues" dxfId="748" priority="967"/>
+    <cfRule type="duplicateValues" dxfId="842" priority="1111"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B831">
-    <cfRule type="duplicateValues" dxfId="747" priority="962"/>
+    <cfRule type="duplicateValues" dxfId="841" priority="1106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B831">
-    <cfRule type="duplicateValues" dxfId="746" priority="963"/>
+    <cfRule type="duplicateValues" dxfId="840" priority="1107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B831">
-    <cfRule type="duplicateValues" dxfId="745" priority="964"/>
+    <cfRule type="duplicateValues" dxfId="839" priority="1108"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B834">
+    <cfRule type="duplicateValues" dxfId="838" priority="1104"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B834">
+    <cfRule type="duplicateValues" dxfId="837" priority="1105"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B834">
+    <cfRule type="duplicateValues" dxfId="836" priority="1103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B832">
-    <cfRule type="duplicateValues" dxfId="744" priority="954"/>
+    <cfRule type="duplicateValues" dxfId="835" priority="1101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B832">
-    <cfRule type="duplicateValues" dxfId="743" priority="955"/>
+    <cfRule type="duplicateValues" dxfId="834" priority="1102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B833">
-    <cfRule type="duplicateValues" dxfId="742" priority="949"/>
+    <cfRule type="duplicateValues" dxfId="833" priority="1096"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B833">
-    <cfRule type="duplicateValues" dxfId="741" priority="950"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B834">
-    <cfRule type="duplicateValues" dxfId="740" priority="947"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B834">
-    <cfRule type="duplicateValues" dxfId="739" priority="946"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B834">
-    <cfRule type="duplicateValues" dxfId="738" priority="948"/>
+    <cfRule type="duplicateValues" dxfId="832" priority="1097"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B835">
-    <cfRule type="duplicateValues" dxfId="737" priority="937"/>
+    <cfRule type="duplicateValues" dxfId="831" priority="1091"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B835">
-    <cfRule type="duplicateValues" dxfId="736" priority="938"/>
+    <cfRule type="duplicateValues" dxfId="830" priority="1092"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B835">
-    <cfRule type="duplicateValues" dxfId="735" priority="939"/>
+    <cfRule type="duplicateValues" dxfId="829" priority="1090"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B837">
-    <cfRule type="duplicateValues" dxfId="734" priority="934"/>
+    <cfRule type="duplicateValues" dxfId="828" priority="1087"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B837">
-    <cfRule type="duplicateValues" dxfId="733" priority="935"/>
+    <cfRule type="duplicateValues" dxfId="827" priority="1088"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B837">
-    <cfRule type="duplicateValues" dxfId="732" priority="936"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B838">
-    <cfRule type="duplicateValues" dxfId="731" priority="931"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B838">
-    <cfRule type="duplicateValues" dxfId="730" priority="932"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B838">
-    <cfRule type="duplicateValues" dxfId="729" priority="933"/>
+    <cfRule type="duplicateValues" dxfId="826" priority="1089"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B840">
-    <cfRule type="duplicateValues" dxfId="728" priority="928"/>
+    <cfRule type="duplicateValues" dxfId="825" priority="1084"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B840">
-    <cfRule type="duplicateValues" dxfId="727" priority="929"/>
+    <cfRule type="duplicateValues" dxfId="824" priority="1085"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B840">
-    <cfRule type="duplicateValues" dxfId="726" priority="930"/>
+    <cfRule type="duplicateValues" dxfId="823" priority="1086"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B841">
-    <cfRule type="duplicateValues" dxfId="725" priority="926"/>
+    <cfRule type="duplicateValues" dxfId="822" priority="1081"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B841">
-    <cfRule type="duplicateValues" dxfId="724" priority="927"/>
+    <cfRule type="duplicateValues" dxfId="821" priority="1082"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B841">
+    <cfRule type="duplicateValues" dxfId="820" priority="1083"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B842">
+    <cfRule type="duplicateValues" dxfId="819" priority="1078"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B842">
+    <cfRule type="duplicateValues" dxfId="818" priority="1079"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B842">
+    <cfRule type="duplicateValues" dxfId="817" priority="1080"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B843">
-    <cfRule type="duplicateValues" dxfId="723" priority="918"/>
+    <cfRule type="duplicateValues" dxfId="816" priority="1066"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B843">
-    <cfRule type="duplicateValues" dxfId="722" priority="917"/>
+    <cfRule type="duplicateValues" dxfId="815" priority="1067"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B843">
-    <cfRule type="duplicateValues" dxfId="721" priority="919"/>
+    <cfRule type="duplicateValues" dxfId="814" priority="1068"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B844">
-    <cfRule type="duplicateValues" dxfId="720" priority="911"/>
+    <cfRule type="duplicateValues" dxfId="813" priority="1061"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B844">
-    <cfRule type="duplicateValues" dxfId="719" priority="912"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B844">
-    <cfRule type="duplicateValues" dxfId="718" priority="913"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B845">
-    <cfRule type="duplicateValues" dxfId="717" priority="908"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B845">
-    <cfRule type="duplicateValues" dxfId="716" priority="909"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B845">
-    <cfRule type="duplicateValues" dxfId="715" priority="910"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B846">
-    <cfRule type="duplicateValues" dxfId="714" priority="905"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B846">
-    <cfRule type="duplicateValues" dxfId="713" priority="906"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B846">
-    <cfRule type="duplicateValues" dxfId="712" priority="907"/>
+    <cfRule type="duplicateValues" dxfId="812" priority="1062"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B847">
-    <cfRule type="duplicateValues" dxfId="711" priority="902"/>
+    <cfRule type="duplicateValues" dxfId="811" priority="1055"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B847">
-    <cfRule type="duplicateValues" dxfId="710" priority="903"/>
+    <cfRule type="duplicateValues" dxfId="810" priority="1056"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B847">
-    <cfRule type="duplicateValues" dxfId="709" priority="904"/>
+    <cfRule type="duplicateValues" dxfId="809" priority="1057"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B848">
-    <cfRule type="duplicateValues" dxfId="708" priority="899"/>
+    <cfRule type="duplicateValues" dxfId="808" priority="1049"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B848">
-    <cfRule type="duplicateValues" dxfId="707" priority="900"/>
+    <cfRule type="duplicateValues" dxfId="807" priority="1050"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B848">
-    <cfRule type="duplicateValues" dxfId="706" priority="901"/>
+    <cfRule type="duplicateValues" dxfId="806" priority="1051"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B849">
-    <cfRule type="duplicateValues" dxfId="705" priority="896"/>
+    <cfRule type="duplicateValues" dxfId="805" priority="1046"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B849">
-    <cfRule type="duplicateValues" dxfId="704" priority="897"/>
+    <cfRule type="duplicateValues" dxfId="804" priority="1047"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B849">
-    <cfRule type="duplicateValues" dxfId="703" priority="898"/>
+    <cfRule type="duplicateValues" dxfId="803" priority="1048"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B850">
-    <cfRule type="duplicateValues" dxfId="702" priority="890"/>
+    <cfRule type="duplicateValues" dxfId="802" priority="1040"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B850">
-    <cfRule type="duplicateValues" dxfId="701" priority="891"/>
+    <cfRule type="duplicateValues" dxfId="801" priority="1041"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B850">
-    <cfRule type="duplicateValues" dxfId="700" priority="892"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B851">
-    <cfRule type="duplicateValues" dxfId="699" priority="887"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B851">
-    <cfRule type="duplicateValues" dxfId="698" priority="888"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B851">
-    <cfRule type="duplicateValues" dxfId="697" priority="889"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B852">
-    <cfRule type="duplicateValues" dxfId="696" priority="884"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B852">
-    <cfRule type="duplicateValues" dxfId="695" priority="885"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B852">
-    <cfRule type="duplicateValues" dxfId="694" priority="886"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B853">
-    <cfRule type="duplicateValues" dxfId="693" priority="882"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B853">
-    <cfRule type="duplicateValues" dxfId="692" priority="883"/>
+    <cfRule type="duplicateValues" dxfId="800" priority="1042"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B854">
-    <cfRule type="duplicateValues" dxfId="691" priority="879"/>
+    <cfRule type="duplicateValues" dxfId="799" priority="1031"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B854">
-    <cfRule type="duplicateValues" dxfId="690" priority="880"/>
+    <cfRule type="duplicateValues" dxfId="798" priority="1032"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B854">
-    <cfRule type="duplicateValues" dxfId="689" priority="881"/>
+    <cfRule type="duplicateValues" dxfId="797" priority="1033"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B855">
+    <cfRule type="duplicateValues" dxfId="796" priority="1028"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B855">
+    <cfRule type="duplicateValues" dxfId="795" priority="1029"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B855">
+    <cfRule type="duplicateValues" dxfId="794" priority="1030"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B856">
+    <cfRule type="duplicateValues" dxfId="793" priority="1022"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B856">
+    <cfRule type="duplicateValues" dxfId="792" priority="1023"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B856">
+    <cfRule type="duplicateValues" dxfId="791" priority="1024"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B857">
+    <cfRule type="duplicateValues" dxfId="790" priority="1013"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B857">
+    <cfRule type="duplicateValues" dxfId="789" priority="1014"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B857">
+    <cfRule type="duplicateValues" dxfId="788" priority="1015"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B858">
+    <cfRule type="duplicateValues" dxfId="787" priority="1010"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B858">
+    <cfRule type="duplicateValues" dxfId="786" priority="1011"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B858">
+    <cfRule type="duplicateValues" dxfId="785" priority="1012"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B859">
-    <cfRule type="duplicateValues" dxfId="688" priority="876"/>
+    <cfRule type="duplicateValues" dxfId="784" priority="1004"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B859">
-    <cfRule type="duplicateValues" dxfId="687" priority="877"/>
+    <cfRule type="duplicateValues" dxfId="783" priority="1005"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B859">
-    <cfRule type="duplicateValues" dxfId="686" priority="878"/>
+    <cfRule type="duplicateValues" dxfId="782" priority="1006"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B860">
-    <cfRule type="duplicateValues" dxfId="685" priority="867"/>
+    <cfRule type="duplicateValues" dxfId="781" priority="1002"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B860">
-    <cfRule type="duplicateValues" dxfId="684" priority="868"/>
+    <cfRule type="duplicateValues" dxfId="780" priority="1003"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B860">
-    <cfRule type="duplicateValues" dxfId="683" priority="869"/>
+    <cfRule type="duplicateValues" dxfId="779" priority="1001"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B861">
-    <cfRule type="duplicateValues" dxfId="682" priority="864"/>
+    <cfRule type="duplicateValues" dxfId="778" priority="998"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B861">
-    <cfRule type="duplicateValues" dxfId="681" priority="865"/>
+    <cfRule type="duplicateValues" dxfId="777" priority="999"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B861">
-    <cfRule type="duplicateValues" dxfId="680" priority="866"/>
+    <cfRule type="duplicateValues" dxfId="776" priority="1000"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B862">
-    <cfRule type="duplicateValues" dxfId="679" priority="861"/>
+    <cfRule type="duplicateValues" dxfId="775" priority="996"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B862">
-    <cfRule type="duplicateValues" dxfId="678" priority="862"/>
+    <cfRule type="duplicateValues" dxfId="774" priority="995"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B862">
-    <cfRule type="duplicateValues" dxfId="677" priority="863"/>
+    <cfRule type="duplicateValues" dxfId="773" priority="997"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B863">
-    <cfRule type="duplicateValues" dxfId="676" priority="858"/>
+    <cfRule type="duplicateValues" dxfId="772" priority="986"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B863">
-    <cfRule type="duplicateValues" dxfId="675" priority="859"/>
+    <cfRule type="duplicateValues" dxfId="771" priority="987"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B863">
-    <cfRule type="duplicateValues" dxfId="674" priority="860"/>
+    <cfRule type="duplicateValues" dxfId="770" priority="988"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B864">
-    <cfRule type="duplicateValues" dxfId="673" priority="855"/>
+    <cfRule type="duplicateValues" dxfId="769" priority="983"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B864">
-    <cfRule type="duplicateValues" dxfId="672" priority="856"/>
+    <cfRule type="duplicateValues" dxfId="768" priority="984"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B864">
-    <cfRule type="duplicateValues" dxfId="671" priority="857"/>
+    <cfRule type="duplicateValues" dxfId="767" priority="985"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B865">
-    <cfRule type="duplicateValues" dxfId="670" priority="853"/>
+    <cfRule type="duplicateValues" dxfId="766" priority="980"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B865">
-    <cfRule type="duplicateValues" dxfId="669" priority="852"/>
+    <cfRule type="duplicateValues" dxfId="765" priority="981"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B865">
-    <cfRule type="duplicateValues" dxfId="668" priority="854"/>
+    <cfRule type="duplicateValues" dxfId="764" priority="982"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B866">
-    <cfRule type="duplicateValues" dxfId="667" priority="849"/>
+    <cfRule type="duplicateValues" dxfId="763" priority="977"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B866">
-    <cfRule type="duplicateValues" dxfId="666" priority="850"/>
+    <cfRule type="duplicateValues" dxfId="762" priority="978"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B866">
-    <cfRule type="duplicateValues" dxfId="665" priority="851"/>
+    <cfRule type="duplicateValues" dxfId="761" priority="979"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B867">
-    <cfRule type="duplicateValues" dxfId="664" priority="846"/>
+    <cfRule type="duplicateValues" dxfId="760" priority="974"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B867">
-    <cfRule type="duplicateValues" dxfId="663" priority="847"/>
+    <cfRule type="duplicateValues" dxfId="759" priority="975"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B867">
-    <cfRule type="duplicateValues" dxfId="662" priority="848"/>
+    <cfRule type="duplicateValues" dxfId="758" priority="976"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B868">
-    <cfRule type="duplicateValues" dxfId="661" priority="840"/>
+    <cfRule type="duplicateValues" dxfId="757" priority="971"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B868">
-    <cfRule type="duplicateValues" dxfId="660" priority="841"/>
+    <cfRule type="duplicateValues" dxfId="756" priority="972"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B868">
-    <cfRule type="duplicateValues" dxfId="659" priority="842"/>
+    <cfRule type="duplicateValues" dxfId="755" priority="973"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B869">
+    <cfRule type="duplicateValues" dxfId="754" priority="965"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B869">
+    <cfRule type="duplicateValues" dxfId="753" priority="966"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B869">
+    <cfRule type="duplicateValues" dxfId="752" priority="967"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B870">
-    <cfRule type="duplicateValues" dxfId="658" priority="837"/>
+    <cfRule type="duplicateValues" dxfId="751" priority="962"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B870">
-    <cfRule type="duplicateValues" dxfId="657" priority="838"/>
+    <cfRule type="duplicateValues" dxfId="750" priority="963"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B870">
-    <cfRule type="duplicateValues" dxfId="656" priority="839"/>
+    <cfRule type="duplicateValues" dxfId="749" priority="964"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B871">
+    <cfRule type="duplicateValues" dxfId="748" priority="954"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B871">
+    <cfRule type="duplicateValues" dxfId="747" priority="955"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B872">
-    <cfRule type="duplicateValues" dxfId="655" priority="834"/>
+    <cfRule type="duplicateValues" dxfId="746" priority="949"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B872">
-    <cfRule type="duplicateValues" dxfId="654" priority="835"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B872">
-    <cfRule type="duplicateValues" dxfId="653" priority="836"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B875">
-    <cfRule type="duplicateValues" dxfId="652" priority="831"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B875">
-    <cfRule type="duplicateValues" dxfId="651" priority="832"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B875">
-    <cfRule type="duplicateValues" dxfId="650" priority="833"/>
+    <cfRule type="duplicateValues" dxfId="745" priority="950"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B873">
+    <cfRule type="duplicateValues" dxfId="744" priority="947"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B873">
+    <cfRule type="duplicateValues" dxfId="743" priority="946"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B873">
+    <cfRule type="duplicateValues" dxfId="742" priority="948"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B874">
+    <cfRule type="duplicateValues" dxfId="741" priority="937"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B874">
+    <cfRule type="duplicateValues" dxfId="740" priority="938"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B874">
+    <cfRule type="duplicateValues" dxfId="739" priority="939"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B876">
-    <cfRule type="duplicateValues" dxfId="649" priority="828"/>
+    <cfRule type="duplicateValues" dxfId="738" priority="934"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B876">
-    <cfRule type="duplicateValues" dxfId="648" priority="829"/>
+    <cfRule type="duplicateValues" dxfId="737" priority="935"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B876">
-    <cfRule type="duplicateValues" dxfId="647" priority="830"/>
+    <cfRule type="duplicateValues" dxfId="736" priority="936"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B877">
-    <cfRule type="duplicateValues" dxfId="646" priority="825"/>
+    <cfRule type="duplicateValues" dxfId="735" priority="931"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B877">
-    <cfRule type="duplicateValues" dxfId="645" priority="826"/>
+    <cfRule type="duplicateValues" dxfId="734" priority="932"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B877">
-    <cfRule type="duplicateValues" dxfId="644" priority="827"/>
+    <cfRule type="duplicateValues" dxfId="733" priority="933"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B879">
-    <cfRule type="duplicateValues" dxfId="643" priority="819"/>
+    <cfRule type="duplicateValues" dxfId="732" priority="928"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B879">
-    <cfRule type="duplicateValues" dxfId="642" priority="820"/>
+    <cfRule type="duplicateValues" dxfId="731" priority="929"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B879">
-    <cfRule type="duplicateValues" dxfId="641" priority="821"/>
+    <cfRule type="duplicateValues" dxfId="730" priority="930"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B880">
-    <cfRule type="duplicateValues" dxfId="640" priority="813"/>
+    <cfRule type="duplicateValues" dxfId="729" priority="926"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B880">
-    <cfRule type="duplicateValues" dxfId="639" priority="814"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B880">
-    <cfRule type="duplicateValues" dxfId="638" priority="815"/>
+    <cfRule type="duplicateValues" dxfId="728" priority="927"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B882">
-    <cfRule type="duplicateValues" dxfId="637" priority="810"/>
+    <cfRule type="duplicateValues" dxfId="727" priority="918"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B882">
-    <cfRule type="duplicateValues" dxfId="636" priority="811"/>
+    <cfRule type="duplicateValues" dxfId="726" priority="917"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B882">
-    <cfRule type="duplicateValues" dxfId="635" priority="812"/>
+    <cfRule type="duplicateValues" dxfId="725" priority="919"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B883">
-    <cfRule type="duplicateValues" dxfId="634" priority="801"/>
+    <cfRule type="duplicateValues" dxfId="724" priority="911"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B883">
-    <cfRule type="duplicateValues" dxfId="633" priority="802"/>
+    <cfRule type="duplicateValues" dxfId="723" priority="912"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B883">
-    <cfRule type="duplicateValues" dxfId="632" priority="803"/>
+    <cfRule type="duplicateValues" dxfId="722" priority="913"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B884">
-    <cfRule type="duplicateValues" dxfId="631" priority="795"/>
+    <cfRule type="duplicateValues" dxfId="721" priority="908"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B884">
-    <cfRule type="duplicateValues" dxfId="630" priority="796"/>
+    <cfRule type="duplicateValues" dxfId="720" priority="909"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B884">
-    <cfRule type="duplicateValues" dxfId="629" priority="797"/>
+    <cfRule type="duplicateValues" dxfId="719" priority="910"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B885">
-    <cfRule type="duplicateValues" dxfId="628" priority="792"/>
+    <cfRule type="duplicateValues" dxfId="718" priority="905"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B885">
-    <cfRule type="duplicateValues" dxfId="627" priority="793"/>
+    <cfRule type="duplicateValues" dxfId="717" priority="906"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B885">
-    <cfRule type="duplicateValues" dxfId="626" priority="794"/>
+    <cfRule type="duplicateValues" dxfId="716" priority="907"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B886">
+    <cfRule type="duplicateValues" dxfId="715" priority="902"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B886">
+    <cfRule type="duplicateValues" dxfId="714" priority="903"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B886">
+    <cfRule type="duplicateValues" dxfId="713" priority="904"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B887">
+    <cfRule type="duplicateValues" dxfId="712" priority="899"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B887">
+    <cfRule type="duplicateValues" dxfId="711" priority="900"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B887">
+    <cfRule type="duplicateValues" dxfId="710" priority="901"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B888">
-    <cfRule type="duplicateValues" dxfId="625" priority="789"/>
+    <cfRule type="duplicateValues" dxfId="709" priority="896"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B888">
-    <cfRule type="duplicateValues" dxfId="624" priority="790"/>
+    <cfRule type="duplicateValues" dxfId="708" priority="897"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B888">
-    <cfRule type="duplicateValues" dxfId="623" priority="791"/>
+    <cfRule type="duplicateValues" dxfId="707" priority="898"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B889">
-    <cfRule type="duplicateValues" dxfId="622" priority="786"/>
+    <cfRule type="duplicateValues" dxfId="706" priority="890"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B889">
-    <cfRule type="duplicateValues" dxfId="621" priority="787"/>
+    <cfRule type="duplicateValues" dxfId="705" priority="891"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B889">
-    <cfRule type="duplicateValues" dxfId="620" priority="788"/>
+    <cfRule type="duplicateValues" dxfId="704" priority="892"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B890">
-    <cfRule type="duplicateValues" dxfId="619" priority="783"/>
+    <cfRule type="duplicateValues" dxfId="703" priority="887"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B890">
-    <cfRule type="duplicateValues" dxfId="618" priority="784"/>
+    <cfRule type="duplicateValues" dxfId="702" priority="888"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B890">
-    <cfRule type="duplicateValues" dxfId="617" priority="785"/>
+    <cfRule type="duplicateValues" dxfId="701" priority="889"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B891">
+    <cfRule type="duplicateValues" dxfId="700" priority="884"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B891">
+    <cfRule type="duplicateValues" dxfId="699" priority="885"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B891">
+    <cfRule type="duplicateValues" dxfId="698" priority="886"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B892">
-    <cfRule type="duplicateValues" dxfId="616" priority="780"/>
+    <cfRule type="duplicateValues" dxfId="697" priority="882"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B892">
-    <cfRule type="duplicateValues" dxfId="615" priority="779"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B892">
-    <cfRule type="duplicateValues" dxfId="614" priority="778"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B894">
-    <cfRule type="duplicateValues" dxfId="613" priority="769"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B894">
-    <cfRule type="duplicateValues" dxfId="612" priority="770"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B894">
-    <cfRule type="duplicateValues" dxfId="611" priority="771"/>
+    <cfRule type="duplicateValues" dxfId="696" priority="883"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B893">
+    <cfRule type="duplicateValues" dxfId="695" priority="879"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B893">
+    <cfRule type="duplicateValues" dxfId="694" priority="880"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B893">
+    <cfRule type="duplicateValues" dxfId="693" priority="881"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B898">
+    <cfRule type="duplicateValues" dxfId="692" priority="876"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B898">
+    <cfRule type="duplicateValues" dxfId="691" priority="877"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B898">
+    <cfRule type="duplicateValues" dxfId="690" priority="878"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B899">
-    <cfRule type="duplicateValues" dxfId="610" priority="758"/>
+    <cfRule type="duplicateValues" dxfId="689" priority="867"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B899">
-    <cfRule type="duplicateValues" dxfId="609" priority="759"/>
+    <cfRule type="duplicateValues" dxfId="688" priority="868"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B899">
-    <cfRule type="duplicateValues" dxfId="608" priority="760"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B897">
-    <cfRule type="duplicateValues" dxfId="607" priority="755"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B897">
-    <cfRule type="duplicateValues" dxfId="606" priority="756"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B897">
-    <cfRule type="duplicateValues" dxfId="605" priority="757"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B898">
-    <cfRule type="duplicateValues" dxfId="604" priority="752"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B898">
-    <cfRule type="duplicateValues" dxfId="603" priority="753"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B898">
-    <cfRule type="duplicateValues" dxfId="602" priority="754"/>
+    <cfRule type="duplicateValues" dxfId="687" priority="869"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B900">
-    <cfRule type="duplicateValues" dxfId="601" priority="750"/>
+    <cfRule type="duplicateValues" dxfId="686" priority="864"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B900">
-    <cfRule type="duplicateValues" dxfId="600" priority="749"/>
+    <cfRule type="duplicateValues" dxfId="685" priority="865"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B900">
-    <cfRule type="duplicateValues" dxfId="599" priority="751"/>
+    <cfRule type="duplicateValues" dxfId="684" priority="866"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B901">
-    <cfRule type="duplicateValues" dxfId="598" priority="743"/>
+    <cfRule type="duplicateValues" dxfId="683" priority="861"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B901">
-    <cfRule type="duplicateValues" dxfId="597" priority="744"/>
+    <cfRule type="duplicateValues" dxfId="682" priority="862"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B901">
-    <cfRule type="duplicateValues" dxfId="596" priority="745"/>
+    <cfRule type="duplicateValues" dxfId="681" priority="863"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B902">
-    <cfRule type="duplicateValues" dxfId="595" priority="737"/>
+    <cfRule type="duplicateValues" dxfId="680" priority="858"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B902">
-    <cfRule type="duplicateValues" dxfId="594" priority="738"/>
+    <cfRule type="duplicateValues" dxfId="679" priority="859"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B902">
-    <cfRule type="duplicateValues" dxfId="593" priority="739"/>
+    <cfRule type="duplicateValues" dxfId="678" priority="860"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B903">
+    <cfRule type="duplicateValues" dxfId="677" priority="855"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B903">
+    <cfRule type="duplicateValues" dxfId="676" priority="856"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B903">
+    <cfRule type="duplicateValues" dxfId="675" priority="857"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B904">
-    <cfRule type="duplicateValues" dxfId="592" priority="734"/>
+    <cfRule type="duplicateValues" dxfId="674" priority="853"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B904">
-    <cfRule type="duplicateValues" dxfId="591" priority="735"/>
+    <cfRule type="duplicateValues" dxfId="673" priority="852"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B904">
-    <cfRule type="duplicateValues" dxfId="590" priority="736"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B903">
-    <cfRule type="duplicateValues" dxfId="589" priority="728"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B903">
-    <cfRule type="duplicateValues" dxfId="588" priority="729"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B903">
-    <cfRule type="duplicateValues" dxfId="587" priority="730"/>
+    <cfRule type="duplicateValues" dxfId="672" priority="854"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B905">
-    <cfRule type="duplicateValues" dxfId="586" priority="722"/>
+    <cfRule type="duplicateValues" dxfId="671" priority="849"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B905">
-    <cfRule type="duplicateValues" dxfId="585" priority="723"/>
+    <cfRule type="duplicateValues" dxfId="670" priority="850"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B905">
-    <cfRule type="duplicateValues" dxfId="584" priority="724"/>
+    <cfRule type="duplicateValues" dxfId="669" priority="851"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B906">
-    <cfRule type="duplicateValues" dxfId="583" priority="719"/>
+    <cfRule type="duplicateValues" dxfId="668" priority="846"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B906">
-    <cfRule type="duplicateValues" dxfId="582" priority="720"/>
+    <cfRule type="duplicateValues" dxfId="667" priority="847"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B906">
-    <cfRule type="duplicateValues" dxfId="581" priority="721"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B908">
-    <cfRule type="duplicateValues" dxfId="580" priority="716"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B908">
-    <cfRule type="duplicateValues" dxfId="579" priority="717"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B908">
-    <cfRule type="duplicateValues" dxfId="578" priority="718"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B910">
-    <cfRule type="duplicateValues" dxfId="577" priority="713"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B910">
-    <cfRule type="duplicateValues" dxfId="576" priority="714"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B910">
-    <cfRule type="duplicateValues" dxfId="575" priority="715"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B912">
-    <cfRule type="duplicateValues" dxfId="574" priority="710"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B912">
-    <cfRule type="duplicateValues" dxfId="573" priority="711"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B912">
-    <cfRule type="duplicateValues" dxfId="572" priority="712"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B913">
-    <cfRule type="duplicateValues" dxfId="571" priority="708"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B913">
-    <cfRule type="duplicateValues" dxfId="570" priority="707"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B913">
-    <cfRule type="duplicateValues" dxfId="569" priority="709"/>
+    <cfRule type="duplicateValues" dxfId="666" priority="848"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B907">
+    <cfRule type="duplicateValues" dxfId="665" priority="840"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B907">
+    <cfRule type="duplicateValues" dxfId="664" priority="841"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B907">
+    <cfRule type="duplicateValues" dxfId="663" priority="842"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B909">
+    <cfRule type="duplicateValues" dxfId="662" priority="837"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B909">
+    <cfRule type="duplicateValues" dxfId="661" priority="838"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B909">
+    <cfRule type="duplicateValues" dxfId="660" priority="839"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B911">
+    <cfRule type="duplicateValues" dxfId="659" priority="834"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B911">
+    <cfRule type="duplicateValues" dxfId="658" priority="835"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B911">
+    <cfRule type="duplicateValues" dxfId="657" priority="836"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B914">
+    <cfRule type="duplicateValues" dxfId="656" priority="831"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B914">
+    <cfRule type="duplicateValues" dxfId="655" priority="832"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B914">
+    <cfRule type="duplicateValues" dxfId="654" priority="833"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B915">
-    <cfRule type="duplicateValues" dxfId="568" priority="704"/>
+    <cfRule type="duplicateValues" dxfId="653" priority="828"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B915">
-    <cfRule type="duplicateValues" dxfId="567" priority="705"/>
+    <cfRule type="duplicateValues" dxfId="652" priority="829"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B915">
-    <cfRule type="duplicateValues" dxfId="566" priority="706"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B914">
-    <cfRule type="duplicateValues" dxfId="565" priority="701"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B914">
-    <cfRule type="duplicateValues" dxfId="564" priority="702"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B914">
-    <cfRule type="duplicateValues" dxfId="563" priority="703"/>
+    <cfRule type="duplicateValues" dxfId="651" priority="830"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B916">
-    <cfRule type="duplicateValues" dxfId="562" priority="698"/>
+    <cfRule type="duplicateValues" dxfId="650" priority="825"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B916">
-    <cfRule type="duplicateValues" dxfId="561" priority="699"/>
+    <cfRule type="duplicateValues" dxfId="649" priority="826"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B916">
-    <cfRule type="duplicateValues" dxfId="560" priority="700"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B917">
-    <cfRule type="duplicateValues" dxfId="559" priority="695"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B917">
-    <cfRule type="duplicateValues" dxfId="558" priority="696"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B917">
-    <cfRule type="duplicateValues" dxfId="557" priority="697"/>
+    <cfRule type="duplicateValues" dxfId="648" priority="827"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B918">
-    <cfRule type="duplicateValues" dxfId="556" priority="689"/>
+    <cfRule type="duplicateValues" dxfId="647" priority="819"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B918">
-    <cfRule type="duplicateValues" dxfId="555" priority="690"/>
+    <cfRule type="duplicateValues" dxfId="646" priority="820"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B918">
-    <cfRule type="duplicateValues" dxfId="554" priority="691"/>
+    <cfRule type="duplicateValues" dxfId="645" priority="821"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B919">
-    <cfRule type="duplicateValues" dxfId="553" priority="683"/>
+    <cfRule type="duplicateValues" dxfId="644" priority="813"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B919">
-    <cfRule type="duplicateValues" dxfId="552" priority="684"/>
+    <cfRule type="duplicateValues" dxfId="643" priority="814"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B919">
-    <cfRule type="duplicateValues" dxfId="551" priority="685"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B920">
-    <cfRule type="duplicateValues" dxfId="550" priority="680"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B920">
-    <cfRule type="duplicateValues" dxfId="549" priority="681"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B920">
-    <cfRule type="duplicateValues" dxfId="548" priority="682"/>
+    <cfRule type="duplicateValues" dxfId="642" priority="815"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B921">
-    <cfRule type="duplicateValues" dxfId="547" priority="671"/>
+    <cfRule type="duplicateValues" dxfId="641" priority="810"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B921">
-    <cfRule type="duplicateValues" dxfId="546" priority="672"/>
+    <cfRule type="duplicateValues" dxfId="640" priority="811"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B921">
-    <cfRule type="duplicateValues" dxfId="545" priority="673"/>
+    <cfRule type="duplicateValues" dxfId="639" priority="812"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B922">
-    <cfRule type="duplicateValues" dxfId="544" priority="668"/>
+    <cfRule type="duplicateValues" dxfId="638" priority="801"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B922">
-    <cfRule type="duplicateValues" dxfId="543" priority="669"/>
+    <cfRule type="duplicateValues" dxfId="637" priority="802"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B922">
-    <cfRule type="duplicateValues" dxfId="542" priority="670"/>
+    <cfRule type="duplicateValues" dxfId="636" priority="803"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B923">
-    <cfRule type="duplicateValues" dxfId="541" priority="667"/>
+    <cfRule type="duplicateValues" dxfId="635" priority="795"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B923">
-    <cfRule type="duplicateValues" dxfId="540" priority="666"/>
+    <cfRule type="duplicateValues" dxfId="634" priority="796"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B923">
-    <cfRule type="duplicateValues" dxfId="539" priority="665"/>
+    <cfRule type="duplicateValues" dxfId="633" priority="797"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B924">
-    <cfRule type="duplicateValues" dxfId="538" priority="656"/>
+    <cfRule type="duplicateValues" dxfId="632" priority="792"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B924">
-    <cfRule type="duplicateValues" dxfId="537" priority="657"/>
+    <cfRule type="duplicateValues" dxfId="631" priority="793"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B924">
-    <cfRule type="duplicateValues" dxfId="536" priority="658"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B925">
-    <cfRule type="duplicateValues" dxfId="535" priority="647"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B925">
-    <cfRule type="duplicateValues" dxfId="534" priority="648"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B925">
-    <cfRule type="duplicateValues" dxfId="533" priority="649"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B926">
-    <cfRule type="duplicateValues" dxfId="532" priority="644"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B926">
-    <cfRule type="duplicateValues" dxfId="531" priority="645"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B926">
-    <cfRule type="duplicateValues" dxfId="530" priority="646"/>
+    <cfRule type="duplicateValues" dxfId="630" priority="794"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B927">
-    <cfRule type="duplicateValues" dxfId="529" priority="642"/>
+    <cfRule type="duplicateValues" dxfId="629" priority="789"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B927">
-    <cfRule type="duplicateValues" dxfId="528" priority="641"/>
+    <cfRule type="duplicateValues" dxfId="628" priority="790"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B927">
-    <cfRule type="duplicateValues" dxfId="527" priority="643"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B911">
-    <cfRule type="duplicateValues" dxfId="526" priority="638"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B911">
-    <cfRule type="duplicateValues" dxfId="525" priority="639"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B911">
-    <cfRule type="duplicateValues" dxfId="524" priority="640"/>
+    <cfRule type="duplicateValues" dxfId="627" priority="791"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B928">
+    <cfRule type="duplicateValues" dxfId="626" priority="786"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B928">
+    <cfRule type="duplicateValues" dxfId="625" priority="787"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B928">
+    <cfRule type="duplicateValues" dxfId="624" priority="788"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B929">
-    <cfRule type="duplicateValues" dxfId="523" priority="633"/>
+    <cfRule type="duplicateValues" dxfId="623" priority="783"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B929">
-    <cfRule type="duplicateValues" dxfId="522" priority="632"/>
+    <cfRule type="duplicateValues" dxfId="622" priority="784"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B929">
-    <cfRule type="duplicateValues" dxfId="521" priority="634"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B930">
-    <cfRule type="duplicateValues" dxfId="520" priority="629"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B930">
-    <cfRule type="duplicateValues" dxfId="519" priority="630"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B930">
-    <cfRule type="duplicateValues" dxfId="518" priority="631"/>
+    <cfRule type="duplicateValues" dxfId="621" priority="785"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B931">
-    <cfRule type="duplicateValues" dxfId="517" priority="620"/>
+    <cfRule type="duplicateValues" dxfId="620" priority="780"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B931">
-    <cfRule type="duplicateValues" dxfId="516" priority="621"/>
+    <cfRule type="duplicateValues" dxfId="619" priority="779"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B931">
-    <cfRule type="duplicateValues" dxfId="515" priority="622"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B932">
-    <cfRule type="duplicateValues" dxfId="514" priority="617"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B932">
-    <cfRule type="duplicateValues" dxfId="513" priority="618"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B932">
-    <cfRule type="duplicateValues" dxfId="512" priority="619"/>
+    <cfRule type="duplicateValues" dxfId="618" priority="778"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B933">
-    <cfRule type="duplicateValues" dxfId="511" priority="612"/>
+    <cfRule type="duplicateValues" dxfId="617" priority="769"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B933">
-    <cfRule type="duplicateValues" dxfId="510" priority="613"/>
+    <cfRule type="duplicateValues" dxfId="616" priority="770"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B933">
-    <cfRule type="duplicateValues" dxfId="509" priority="614"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B934">
-    <cfRule type="duplicateValues" dxfId="508" priority="609"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B934">
-    <cfRule type="duplicateValues" dxfId="507" priority="610"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B934">
-    <cfRule type="duplicateValues" dxfId="506" priority="611"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B935">
-    <cfRule type="duplicateValues" dxfId="505" priority="603"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B935">
-    <cfRule type="duplicateValues" dxfId="504" priority="604"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B935">
-    <cfRule type="duplicateValues" dxfId="503" priority="605"/>
+    <cfRule type="duplicateValues" dxfId="615" priority="771"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B938">
+    <cfRule type="duplicateValues" dxfId="614" priority="758"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B938">
+    <cfRule type="duplicateValues" dxfId="613" priority="759"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B938">
+    <cfRule type="duplicateValues" dxfId="612" priority="760"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B936">
-    <cfRule type="duplicateValues" dxfId="502" priority="597"/>
+    <cfRule type="duplicateValues" dxfId="611" priority="755"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B936">
-    <cfRule type="duplicateValues" dxfId="501" priority="598"/>
+    <cfRule type="duplicateValues" dxfId="610" priority="756"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B936">
-    <cfRule type="duplicateValues" dxfId="500" priority="599"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B938">
-    <cfRule type="duplicateValues" dxfId="499" priority="594"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B938">
-    <cfRule type="duplicateValues" dxfId="498" priority="595"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B938">
-    <cfRule type="duplicateValues" dxfId="497" priority="596"/>
+    <cfRule type="duplicateValues" dxfId="609" priority="757"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B937">
-    <cfRule type="duplicateValues" dxfId="496" priority="591"/>
+    <cfRule type="duplicateValues" dxfId="608" priority="752"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B937">
-    <cfRule type="duplicateValues" dxfId="495" priority="592"/>
+    <cfRule type="duplicateValues" dxfId="607" priority="753"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B937">
-    <cfRule type="duplicateValues" dxfId="494" priority="593"/>
+    <cfRule type="duplicateValues" dxfId="606" priority="754"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B939">
+    <cfRule type="duplicateValues" dxfId="605" priority="750"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B939">
+    <cfRule type="duplicateValues" dxfId="604" priority="749"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B939">
+    <cfRule type="duplicateValues" dxfId="603" priority="751"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B940">
-    <cfRule type="duplicateValues" dxfId="493" priority="588"/>
+    <cfRule type="duplicateValues" dxfId="602" priority="743"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B940">
-    <cfRule type="duplicateValues" dxfId="492" priority="589"/>
+    <cfRule type="duplicateValues" dxfId="601" priority="744"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B940">
-    <cfRule type="duplicateValues" dxfId="491" priority="590"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B939">
-    <cfRule type="duplicateValues" dxfId="490" priority="585"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B939">
-    <cfRule type="duplicateValues" dxfId="489" priority="586"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B939">
-    <cfRule type="duplicateValues" dxfId="488" priority="587"/>
+    <cfRule type="duplicateValues" dxfId="600" priority="745"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B941">
-    <cfRule type="duplicateValues" dxfId="487" priority="576"/>
+    <cfRule type="duplicateValues" dxfId="599" priority="737"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B941">
-    <cfRule type="duplicateValues" dxfId="486" priority="577"/>
+    <cfRule type="duplicateValues" dxfId="598" priority="738"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B941">
-    <cfRule type="duplicateValues" dxfId="485" priority="578"/>
+    <cfRule type="duplicateValues" dxfId="597" priority="739"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B943">
-    <cfRule type="duplicateValues" dxfId="484" priority="573"/>
+    <cfRule type="duplicateValues" dxfId="596" priority="734"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B943">
-    <cfRule type="duplicateValues" dxfId="483" priority="574"/>
+    <cfRule type="duplicateValues" dxfId="595" priority="735"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B943">
-    <cfRule type="duplicateValues" dxfId="482" priority="575"/>
+    <cfRule type="duplicateValues" dxfId="594" priority="736"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B942">
+    <cfRule type="duplicateValues" dxfId="593" priority="728"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B942">
+    <cfRule type="duplicateValues" dxfId="592" priority="729"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B942">
+    <cfRule type="duplicateValues" dxfId="591" priority="730"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B944">
-    <cfRule type="duplicateValues" dxfId="481" priority="570"/>
+    <cfRule type="duplicateValues" dxfId="590" priority="722"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B944">
-    <cfRule type="duplicateValues" dxfId="480" priority="571"/>
+    <cfRule type="duplicateValues" dxfId="589" priority="723"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B944">
-    <cfRule type="duplicateValues" dxfId="479" priority="572"/>
+    <cfRule type="duplicateValues" dxfId="588" priority="724"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B945">
-    <cfRule type="duplicateValues" dxfId="478" priority="567"/>
+    <cfRule type="duplicateValues" dxfId="587" priority="719"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B945">
-    <cfRule type="duplicateValues" dxfId="477" priority="568"/>
+    <cfRule type="duplicateValues" dxfId="586" priority="720"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B945">
-    <cfRule type="duplicateValues" dxfId="476" priority="569"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B946">
-    <cfRule type="duplicateValues" dxfId="475" priority="561"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B946">
-    <cfRule type="duplicateValues" dxfId="474" priority="562"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B946">
-    <cfRule type="duplicateValues" dxfId="473" priority="563"/>
+    <cfRule type="duplicateValues" dxfId="585" priority="721"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B947">
-    <cfRule type="duplicateValues" dxfId="472" priority="558"/>
+    <cfRule type="duplicateValues" dxfId="584" priority="716"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B947">
-    <cfRule type="duplicateValues" dxfId="471" priority="559"/>
+    <cfRule type="duplicateValues" dxfId="583" priority="717"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B947">
-    <cfRule type="duplicateValues" dxfId="470" priority="560"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B948">
-    <cfRule type="duplicateValues" dxfId="469" priority="556"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B948">
-    <cfRule type="duplicateValues" dxfId="468" priority="557"/>
+    <cfRule type="duplicateValues" dxfId="582" priority="718"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B949">
-    <cfRule type="duplicateValues" dxfId="467" priority="553"/>
+    <cfRule type="duplicateValues" dxfId="581" priority="713"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B949">
-    <cfRule type="duplicateValues" dxfId="466" priority="554"/>
+    <cfRule type="duplicateValues" dxfId="580" priority="714"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B949">
-    <cfRule type="duplicateValues" dxfId="465" priority="555"/>
+    <cfRule type="duplicateValues" dxfId="579" priority="715"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B951">
+    <cfRule type="duplicateValues" dxfId="578" priority="710"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B951">
+    <cfRule type="duplicateValues" dxfId="577" priority="711"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B951">
+    <cfRule type="duplicateValues" dxfId="576" priority="712"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B952">
+    <cfRule type="duplicateValues" dxfId="575" priority="708"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B952">
+    <cfRule type="duplicateValues" dxfId="574" priority="707"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B952">
+    <cfRule type="duplicateValues" dxfId="573" priority="709"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B954">
+    <cfRule type="duplicateValues" dxfId="572" priority="704"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B954">
+    <cfRule type="duplicateValues" dxfId="571" priority="705"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B954">
+    <cfRule type="duplicateValues" dxfId="570" priority="706"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B953">
+    <cfRule type="duplicateValues" dxfId="569" priority="701"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B953">
+    <cfRule type="duplicateValues" dxfId="568" priority="702"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B953">
+    <cfRule type="duplicateValues" dxfId="567" priority="703"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B955">
+    <cfRule type="duplicateValues" dxfId="566" priority="698"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B955">
+    <cfRule type="duplicateValues" dxfId="565" priority="699"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B955">
+    <cfRule type="duplicateValues" dxfId="564" priority="700"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B956">
+    <cfRule type="duplicateValues" dxfId="563" priority="695"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B956">
+    <cfRule type="duplicateValues" dxfId="562" priority="696"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B956">
+    <cfRule type="duplicateValues" dxfId="561" priority="697"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B957">
+    <cfRule type="duplicateValues" dxfId="560" priority="689"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B957">
+    <cfRule type="duplicateValues" dxfId="559" priority="690"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B957">
+    <cfRule type="duplicateValues" dxfId="558" priority="691"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B958">
+    <cfRule type="duplicateValues" dxfId="557" priority="683"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B958">
+    <cfRule type="duplicateValues" dxfId="556" priority="684"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B958">
+    <cfRule type="duplicateValues" dxfId="555" priority="685"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B959">
+    <cfRule type="duplicateValues" dxfId="554" priority="680"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B959">
+    <cfRule type="duplicateValues" dxfId="553" priority="681"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B959">
+    <cfRule type="duplicateValues" dxfId="552" priority="682"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B960">
+    <cfRule type="duplicateValues" dxfId="551" priority="671"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B960">
+    <cfRule type="duplicateValues" dxfId="550" priority="672"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B960">
+    <cfRule type="duplicateValues" dxfId="549" priority="673"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B961">
+    <cfRule type="duplicateValues" dxfId="548" priority="668"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B961">
+    <cfRule type="duplicateValues" dxfId="547" priority="669"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B961">
+    <cfRule type="duplicateValues" dxfId="546" priority="670"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B962">
+    <cfRule type="duplicateValues" dxfId="545" priority="667"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B962">
+    <cfRule type="duplicateValues" dxfId="544" priority="666"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B962">
+    <cfRule type="duplicateValues" dxfId="543" priority="665"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B963">
+    <cfRule type="duplicateValues" dxfId="542" priority="656"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B963">
+    <cfRule type="duplicateValues" dxfId="541" priority="657"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B963">
+    <cfRule type="duplicateValues" dxfId="540" priority="658"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B964">
+    <cfRule type="duplicateValues" dxfId="539" priority="647"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B964">
+    <cfRule type="duplicateValues" dxfId="538" priority="648"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B964">
+    <cfRule type="duplicateValues" dxfId="537" priority="649"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B965">
+    <cfRule type="duplicateValues" dxfId="536" priority="644"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B965">
+    <cfRule type="duplicateValues" dxfId="535" priority="645"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B965">
+    <cfRule type="duplicateValues" dxfId="534" priority="646"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B966">
+    <cfRule type="duplicateValues" dxfId="533" priority="642"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B966">
+    <cfRule type="duplicateValues" dxfId="532" priority="641"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B966">
+    <cfRule type="duplicateValues" dxfId="531" priority="643"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B950">
-    <cfRule type="duplicateValues" dxfId="464" priority="550"/>
+    <cfRule type="duplicateValues" dxfId="530" priority="638"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B950">
-    <cfRule type="duplicateValues" dxfId="463" priority="551"/>
+    <cfRule type="duplicateValues" dxfId="529" priority="639"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B950">
-    <cfRule type="duplicateValues" dxfId="462" priority="552"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B951">
-    <cfRule type="duplicateValues" dxfId="461" priority="541"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B951">
-    <cfRule type="duplicateValues" dxfId="460" priority="542"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B951">
-    <cfRule type="duplicateValues" dxfId="459" priority="543"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B953">
-    <cfRule type="duplicateValues" dxfId="458" priority="540"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B953">
-    <cfRule type="duplicateValues" dxfId="457" priority="539"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B953">
-    <cfRule type="duplicateValues" dxfId="456" priority="538"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B952">
-    <cfRule type="duplicateValues" dxfId="455" priority="529"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B952">
-    <cfRule type="duplicateValues" dxfId="454" priority="530"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B952">
-    <cfRule type="duplicateValues" dxfId="453" priority="531"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B954">
-    <cfRule type="duplicateValues" dxfId="452" priority="526"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B954">
-    <cfRule type="duplicateValues" dxfId="451" priority="527"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B954">
-    <cfRule type="duplicateValues" dxfId="450" priority="528"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B955">
-    <cfRule type="duplicateValues" dxfId="449" priority="520"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B955">
-    <cfRule type="duplicateValues" dxfId="448" priority="521"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B955">
-    <cfRule type="duplicateValues" dxfId="447" priority="522"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B956">
-    <cfRule type="duplicateValues" dxfId="446" priority="511"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B956">
-    <cfRule type="duplicateValues" dxfId="445" priority="512"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B956">
-    <cfRule type="duplicateValues" dxfId="444" priority="513"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B957">
-    <cfRule type="duplicateValues" dxfId="443" priority="508"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B957">
-    <cfRule type="duplicateValues" dxfId="442" priority="509"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B957">
-    <cfRule type="duplicateValues" dxfId="441" priority="510"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B960">
-    <cfRule type="duplicateValues" dxfId="440" priority="505"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B960">
-    <cfRule type="duplicateValues" dxfId="439" priority="506"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B960">
-    <cfRule type="duplicateValues" dxfId="438" priority="507"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B962">
-    <cfRule type="duplicateValues" dxfId="437" priority="502"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B962">
-    <cfRule type="duplicateValues" dxfId="436" priority="503"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B962">
-    <cfRule type="duplicateValues" dxfId="435" priority="504"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B965">
-    <cfRule type="duplicateValues" dxfId="434" priority="499"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B965">
-    <cfRule type="duplicateValues" dxfId="433" priority="500"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B965">
-    <cfRule type="duplicateValues" dxfId="432" priority="501"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B966">
-    <cfRule type="duplicateValues" dxfId="431" priority="493"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B966">
-    <cfRule type="duplicateValues" dxfId="430" priority="494"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B966">
-    <cfRule type="duplicateValues" dxfId="429" priority="495"/>
+    <cfRule type="duplicateValues" dxfId="528" priority="640"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B968">
-    <cfRule type="duplicateValues" dxfId="428" priority="490"/>
+    <cfRule type="duplicateValues" dxfId="527" priority="633"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B968">
-    <cfRule type="duplicateValues" dxfId="427" priority="491"/>
+    <cfRule type="duplicateValues" dxfId="526" priority="632"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B968">
-    <cfRule type="duplicateValues" dxfId="426" priority="492"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B967">
-    <cfRule type="duplicateValues" dxfId="425" priority="484"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B967">
-    <cfRule type="duplicateValues" dxfId="424" priority="485"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B967">
-    <cfRule type="duplicateValues" dxfId="423" priority="486"/>
+    <cfRule type="duplicateValues" dxfId="525" priority="634"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B969">
-    <cfRule type="duplicateValues" dxfId="422" priority="478"/>
+    <cfRule type="duplicateValues" dxfId="524" priority="629"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B969">
-    <cfRule type="duplicateValues" dxfId="421" priority="479"/>
+    <cfRule type="duplicateValues" dxfId="523" priority="630"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B969">
-    <cfRule type="duplicateValues" dxfId="420" priority="480"/>
+    <cfRule type="duplicateValues" dxfId="522" priority="631"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B970">
-    <cfRule type="duplicateValues" dxfId="419" priority="472"/>
+    <cfRule type="duplicateValues" dxfId="521" priority="620"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B970">
-    <cfRule type="duplicateValues" dxfId="418" priority="473"/>
+    <cfRule type="duplicateValues" dxfId="520" priority="621"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B970">
-    <cfRule type="duplicateValues" dxfId="417" priority="474"/>
+    <cfRule type="duplicateValues" dxfId="519" priority="622"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B971">
-    <cfRule type="duplicateValues" dxfId="416" priority="463"/>
+    <cfRule type="duplicateValues" dxfId="518" priority="617"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B971">
-    <cfRule type="duplicateValues" dxfId="415" priority="464"/>
+    <cfRule type="duplicateValues" dxfId="517" priority="618"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B971">
-    <cfRule type="duplicateValues" dxfId="414" priority="465"/>
+    <cfRule type="duplicateValues" dxfId="516" priority="619"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B972">
-    <cfRule type="duplicateValues" dxfId="413" priority="458"/>
+    <cfRule type="duplicateValues" dxfId="515" priority="612"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B972">
-    <cfRule type="duplicateValues" dxfId="412" priority="457"/>
+    <cfRule type="duplicateValues" dxfId="514" priority="613"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B972">
-    <cfRule type="duplicateValues" dxfId="411" priority="459"/>
+    <cfRule type="duplicateValues" dxfId="513" priority="614"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B973">
+    <cfRule type="duplicateValues" dxfId="512" priority="609"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B973">
+    <cfRule type="duplicateValues" dxfId="511" priority="610"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B973">
+    <cfRule type="duplicateValues" dxfId="510" priority="611"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B974">
-    <cfRule type="duplicateValues" dxfId="410" priority="448"/>
+    <cfRule type="duplicateValues" dxfId="509" priority="603"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B974">
-    <cfRule type="duplicateValues" dxfId="409" priority="449"/>
+    <cfRule type="duplicateValues" dxfId="508" priority="604"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B974">
-    <cfRule type="duplicateValues" dxfId="408" priority="450"/>
+    <cfRule type="duplicateValues" dxfId="507" priority="605"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B975">
-    <cfRule type="duplicateValues" dxfId="407" priority="442"/>
+    <cfRule type="duplicateValues" dxfId="506" priority="597"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B975">
-    <cfRule type="duplicateValues" dxfId="406" priority="443"/>
+    <cfRule type="duplicateValues" dxfId="505" priority="598"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B975">
-    <cfRule type="duplicateValues" dxfId="405" priority="444"/>
+    <cfRule type="duplicateValues" dxfId="504" priority="599"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B977">
+    <cfRule type="duplicateValues" dxfId="503" priority="594"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B977">
+    <cfRule type="duplicateValues" dxfId="502" priority="595"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B977">
+    <cfRule type="duplicateValues" dxfId="501" priority="596"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B976">
-    <cfRule type="duplicateValues" dxfId="404" priority="439"/>
+    <cfRule type="duplicateValues" dxfId="500" priority="591"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B976">
-    <cfRule type="duplicateValues" dxfId="403" priority="440"/>
+    <cfRule type="duplicateValues" dxfId="499" priority="592"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B976">
-    <cfRule type="duplicateValues" dxfId="402" priority="441"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B977">
-    <cfRule type="duplicateValues" dxfId="401" priority="436"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B977">
-    <cfRule type="duplicateValues" dxfId="400" priority="437"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B977">
-    <cfRule type="duplicateValues" dxfId="399" priority="438"/>
+    <cfRule type="duplicateValues" dxfId="498" priority="593"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B979">
+    <cfRule type="duplicateValues" dxfId="497" priority="588"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B979">
+    <cfRule type="duplicateValues" dxfId="496" priority="589"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B979">
+    <cfRule type="duplicateValues" dxfId="495" priority="590"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B978">
-    <cfRule type="duplicateValues" dxfId="398" priority="432"/>
+    <cfRule type="duplicateValues" dxfId="494" priority="585"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B978">
-    <cfRule type="duplicateValues" dxfId="397" priority="431"/>
+    <cfRule type="duplicateValues" dxfId="493" priority="586"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B978">
-    <cfRule type="duplicateValues" dxfId="396" priority="430"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B979">
-    <cfRule type="duplicateValues" dxfId="395" priority="428"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B979">
-    <cfRule type="duplicateValues" dxfId="394" priority="427"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B979">
-    <cfRule type="duplicateValues" dxfId="393" priority="429"/>
+    <cfRule type="duplicateValues" dxfId="492" priority="587"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B980">
-    <cfRule type="duplicateValues" dxfId="392" priority="424"/>
+    <cfRule type="duplicateValues" dxfId="491" priority="576"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B980">
-    <cfRule type="duplicateValues" dxfId="391" priority="425"/>
+    <cfRule type="duplicateValues" dxfId="490" priority="577"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B980">
-    <cfRule type="duplicateValues" dxfId="390" priority="426"/>
+    <cfRule type="duplicateValues" dxfId="489" priority="578"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B982">
+    <cfRule type="duplicateValues" dxfId="488" priority="573"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B982">
+    <cfRule type="duplicateValues" dxfId="487" priority="574"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B982">
+    <cfRule type="duplicateValues" dxfId="486" priority="575"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B983">
+    <cfRule type="duplicateValues" dxfId="485" priority="570"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B983">
+    <cfRule type="duplicateValues" dxfId="484" priority="571"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B983">
+    <cfRule type="duplicateValues" dxfId="483" priority="572"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B984">
+    <cfRule type="duplicateValues" dxfId="482" priority="567"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B984">
+    <cfRule type="duplicateValues" dxfId="481" priority="568"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B984">
+    <cfRule type="duplicateValues" dxfId="480" priority="569"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B985">
+    <cfRule type="duplicateValues" dxfId="479" priority="561"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B985">
+    <cfRule type="duplicateValues" dxfId="478" priority="562"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B985">
+    <cfRule type="duplicateValues" dxfId="477" priority="563"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B986">
+    <cfRule type="duplicateValues" dxfId="476" priority="558"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B986">
+    <cfRule type="duplicateValues" dxfId="475" priority="559"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B986">
+    <cfRule type="duplicateValues" dxfId="474" priority="560"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B987">
+    <cfRule type="duplicateValues" dxfId="473" priority="556"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B987">
+    <cfRule type="duplicateValues" dxfId="472" priority="557"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B988">
+    <cfRule type="duplicateValues" dxfId="471" priority="553"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B988">
+    <cfRule type="duplicateValues" dxfId="470" priority="554"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B988">
+    <cfRule type="duplicateValues" dxfId="469" priority="555"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B989">
+    <cfRule type="duplicateValues" dxfId="468" priority="550"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B989">
+    <cfRule type="duplicateValues" dxfId="467" priority="551"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B989">
+    <cfRule type="duplicateValues" dxfId="466" priority="552"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B990">
+    <cfRule type="duplicateValues" dxfId="465" priority="541"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B990">
+    <cfRule type="duplicateValues" dxfId="464" priority="542"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B990">
+    <cfRule type="duplicateValues" dxfId="463" priority="543"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B992">
+    <cfRule type="duplicateValues" dxfId="462" priority="540"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B992">
+    <cfRule type="duplicateValues" dxfId="461" priority="539"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B992">
+    <cfRule type="duplicateValues" dxfId="460" priority="538"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B991">
+    <cfRule type="duplicateValues" dxfId="459" priority="529"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B991">
+    <cfRule type="duplicateValues" dxfId="458" priority="530"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B991">
+    <cfRule type="duplicateValues" dxfId="457" priority="531"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B993">
+    <cfRule type="duplicateValues" dxfId="456" priority="526"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B993">
+    <cfRule type="duplicateValues" dxfId="455" priority="527"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B993">
+    <cfRule type="duplicateValues" dxfId="454" priority="528"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B994">
+    <cfRule type="duplicateValues" dxfId="453" priority="520"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B994">
+    <cfRule type="duplicateValues" dxfId="452" priority="521"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B994">
+    <cfRule type="duplicateValues" dxfId="451" priority="522"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B995">
+    <cfRule type="duplicateValues" dxfId="450" priority="511"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B995">
+    <cfRule type="duplicateValues" dxfId="449" priority="512"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B995">
+    <cfRule type="duplicateValues" dxfId="448" priority="513"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B996">
+    <cfRule type="duplicateValues" dxfId="447" priority="508"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B996">
+    <cfRule type="duplicateValues" dxfId="446" priority="509"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B996">
+    <cfRule type="duplicateValues" dxfId="445" priority="510"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B999">
+    <cfRule type="duplicateValues" dxfId="444" priority="505"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B999">
+    <cfRule type="duplicateValues" dxfId="443" priority="506"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B999">
+    <cfRule type="duplicateValues" dxfId="442" priority="507"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1001">
+    <cfRule type="duplicateValues" dxfId="441" priority="502"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1001">
+    <cfRule type="duplicateValues" dxfId="440" priority="503"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1001">
+    <cfRule type="duplicateValues" dxfId="439" priority="504"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1004">
+    <cfRule type="duplicateValues" dxfId="438" priority="499"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1004">
+    <cfRule type="duplicateValues" dxfId="437" priority="500"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1004">
+    <cfRule type="duplicateValues" dxfId="436" priority="501"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1005">
+    <cfRule type="duplicateValues" dxfId="435" priority="493"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1005">
+    <cfRule type="duplicateValues" dxfId="434" priority="494"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1005">
+    <cfRule type="duplicateValues" dxfId="433" priority="495"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1007">
+    <cfRule type="duplicateValues" dxfId="432" priority="490"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1007">
+    <cfRule type="duplicateValues" dxfId="431" priority="491"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1007">
+    <cfRule type="duplicateValues" dxfId="430" priority="492"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1006">
+    <cfRule type="duplicateValues" dxfId="429" priority="484"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1006">
+    <cfRule type="duplicateValues" dxfId="428" priority="485"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1006">
+    <cfRule type="duplicateValues" dxfId="427" priority="486"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1008">
+    <cfRule type="duplicateValues" dxfId="426" priority="478"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1008">
+    <cfRule type="duplicateValues" dxfId="425" priority="479"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1008">
+    <cfRule type="duplicateValues" dxfId="424" priority="480"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1009">
+    <cfRule type="duplicateValues" dxfId="423" priority="472"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1009">
+    <cfRule type="duplicateValues" dxfId="422" priority="473"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1009">
+    <cfRule type="duplicateValues" dxfId="421" priority="474"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1010">
+    <cfRule type="duplicateValues" dxfId="420" priority="463"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1010">
+    <cfRule type="duplicateValues" dxfId="419" priority="464"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1010">
+    <cfRule type="duplicateValues" dxfId="418" priority="465"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1011">
+    <cfRule type="duplicateValues" dxfId="417" priority="458"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1011">
+    <cfRule type="duplicateValues" dxfId="416" priority="457"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1011">
+    <cfRule type="duplicateValues" dxfId="415" priority="459"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1013">
+    <cfRule type="duplicateValues" dxfId="414" priority="448"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1013">
+    <cfRule type="duplicateValues" dxfId="413" priority="449"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1013">
+    <cfRule type="duplicateValues" dxfId="412" priority="450"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1014">
+    <cfRule type="duplicateValues" dxfId="411" priority="442"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1014">
+    <cfRule type="duplicateValues" dxfId="410" priority="443"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1014">
+    <cfRule type="duplicateValues" dxfId="409" priority="444"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1015">
+    <cfRule type="duplicateValues" dxfId="408" priority="439"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1015">
+    <cfRule type="duplicateValues" dxfId="407" priority="440"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1015">
+    <cfRule type="duplicateValues" dxfId="406" priority="441"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1016">
+    <cfRule type="duplicateValues" dxfId="405" priority="436"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1016">
+    <cfRule type="duplicateValues" dxfId="404" priority="437"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1016">
+    <cfRule type="duplicateValues" dxfId="403" priority="438"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1017">
+    <cfRule type="duplicateValues" dxfId="402" priority="432"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1017">
+    <cfRule type="duplicateValues" dxfId="401" priority="431"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1017">
+    <cfRule type="duplicateValues" dxfId="400" priority="430"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1018">
+    <cfRule type="duplicateValues" dxfId="399" priority="428"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1018">
+    <cfRule type="duplicateValues" dxfId="398" priority="427"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1018">
+    <cfRule type="duplicateValues" dxfId="397" priority="429"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1019">
+    <cfRule type="duplicateValues" dxfId="396" priority="424"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1019">
+    <cfRule type="duplicateValues" dxfId="395" priority="425"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1019">
+    <cfRule type="duplicateValues" dxfId="394" priority="426"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9">
-    <cfRule type="duplicateValues" dxfId="389" priority="421"/>
+    <cfRule type="duplicateValues" dxfId="393" priority="421"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9">
-    <cfRule type="duplicateValues" dxfId="388" priority="422"/>
+    <cfRule type="duplicateValues" dxfId="392" priority="422"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9">
-    <cfRule type="duplicateValues" dxfId="387" priority="423"/>
+    <cfRule type="duplicateValues" dxfId="391" priority="423"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10">
-    <cfRule type="duplicateValues" dxfId="386" priority="418"/>
+    <cfRule type="duplicateValues" dxfId="390" priority="418"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10">
-    <cfRule type="duplicateValues" dxfId="385" priority="419"/>
+    <cfRule type="duplicateValues" dxfId="389" priority="419"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10">
-    <cfRule type="duplicateValues" dxfId="384" priority="420"/>
+    <cfRule type="duplicateValues" dxfId="388" priority="420"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
-    <cfRule type="duplicateValues" dxfId="383" priority="415"/>
+    <cfRule type="duplicateValues" dxfId="387" priority="415"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
-    <cfRule type="duplicateValues" dxfId="382" priority="416"/>
+    <cfRule type="duplicateValues" dxfId="386" priority="416"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
-    <cfRule type="duplicateValues" dxfId="381" priority="417"/>
+    <cfRule type="duplicateValues" dxfId="385" priority="417"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="380" priority="412"/>
+    <cfRule type="duplicateValues" dxfId="384" priority="412"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="379" priority="413"/>
+    <cfRule type="duplicateValues" dxfId="383" priority="413"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="378" priority="414"/>
+    <cfRule type="duplicateValues" dxfId="382" priority="414"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20">
-    <cfRule type="duplicateValues" dxfId="377" priority="409"/>
+    <cfRule type="duplicateValues" dxfId="381" priority="409"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20">
-    <cfRule type="duplicateValues" dxfId="376" priority="410"/>
+    <cfRule type="duplicateValues" dxfId="380" priority="410"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20">
-    <cfRule type="duplicateValues" dxfId="375" priority="411"/>
+    <cfRule type="duplicateValues" dxfId="379" priority="411"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="duplicateValues" dxfId="374" priority="406"/>
+    <cfRule type="duplicateValues" dxfId="378" priority="406"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="duplicateValues" dxfId="373" priority="407"/>
+    <cfRule type="duplicateValues" dxfId="377" priority="407"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="duplicateValues" dxfId="372" priority="408"/>
+    <cfRule type="duplicateValues" dxfId="376" priority="408"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="duplicateValues" dxfId="371" priority="403"/>
+    <cfRule type="duplicateValues" dxfId="375" priority="403"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="duplicateValues" dxfId="370" priority="404"/>
+    <cfRule type="duplicateValues" dxfId="374" priority="404"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="duplicateValues" dxfId="369" priority="405"/>
+    <cfRule type="duplicateValues" dxfId="373" priority="405"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="duplicateValues" dxfId="368" priority="400"/>
+    <cfRule type="duplicateValues" dxfId="372" priority="400"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="duplicateValues" dxfId="367" priority="401"/>
+    <cfRule type="duplicateValues" dxfId="371" priority="401"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="duplicateValues" dxfId="366" priority="402"/>
+    <cfRule type="duplicateValues" dxfId="370" priority="402"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="365" priority="397"/>
+    <cfRule type="duplicateValues" dxfId="369" priority="397"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="364" priority="398"/>
+    <cfRule type="duplicateValues" dxfId="368" priority="398"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="363" priority="399"/>
+    <cfRule type="duplicateValues" dxfId="367" priority="399"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27">
-    <cfRule type="duplicateValues" dxfId="362" priority="394"/>
+    <cfRule type="duplicateValues" dxfId="366" priority="394"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27">
-    <cfRule type="duplicateValues" dxfId="361" priority="395"/>
+    <cfRule type="duplicateValues" dxfId="365" priority="395"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27">
-    <cfRule type="duplicateValues" dxfId="360" priority="396"/>
+    <cfRule type="duplicateValues" dxfId="364" priority="396"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28">
-    <cfRule type="duplicateValues" dxfId="359" priority="391"/>
+    <cfRule type="duplicateValues" dxfId="363" priority="391"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28">
-    <cfRule type="duplicateValues" dxfId="358" priority="392"/>
+    <cfRule type="duplicateValues" dxfId="362" priority="392"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28">
-    <cfRule type="duplicateValues" dxfId="357" priority="393"/>
+    <cfRule type="duplicateValues" dxfId="361" priority="393"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29">
-    <cfRule type="duplicateValues" dxfId="356" priority="388"/>
+    <cfRule type="duplicateValues" dxfId="360" priority="388"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29">
-    <cfRule type="duplicateValues" dxfId="355" priority="389"/>
+    <cfRule type="duplicateValues" dxfId="359" priority="389"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29">
-    <cfRule type="duplicateValues" dxfId="354" priority="390"/>
+    <cfRule type="duplicateValues" dxfId="358" priority="390"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="353" priority="385"/>
+    <cfRule type="duplicateValues" dxfId="357" priority="385"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="352" priority="386"/>
+    <cfRule type="duplicateValues" dxfId="356" priority="386"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="351" priority="387"/>
+    <cfRule type="duplicateValues" dxfId="355" priority="387"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="350" priority="382"/>
+    <cfRule type="duplicateValues" dxfId="354" priority="382"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="349" priority="383"/>
+    <cfRule type="duplicateValues" dxfId="353" priority="383"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="348" priority="384"/>
+    <cfRule type="duplicateValues" dxfId="352" priority="384"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="347" priority="379"/>
+    <cfRule type="duplicateValues" dxfId="351" priority="379"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="346" priority="380"/>
+    <cfRule type="duplicateValues" dxfId="350" priority="380"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="345" priority="381"/>
+    <cfRule type="duplicateValues" dxfId="349" priority="381"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="344" priority="376"/>
+    <cfRule type="duplicateValues" dxfId="348" priority="376"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="343" priority="377"/>
+    <cfRule type="duplicateValues" dxfId="347" priority="377"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="342" priority="378"/>
+    <cfRule type="duplicateValues" dxfId="346" priority="378"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="341" priority="373"/>
+    <cfRule type="duplicateValues" dxfId="345" priority="373"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="340" priority="374"/>
+    <cfRule type="duplicateValues" dxfId="344" priority="374"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="339" priority="375"/>
+    <cfRule type="duplicateValues" dxfId="343" priority="375"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="338" priority="370"/>
+    <cfRule type="duplicateValues" dxfId="342" priority="370"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="337" priority="371"/>
+    <cfRule type="duplicateValues" dxfId="341" priority="371"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="336" priority="372"/>
+    <cfRule type="duplicateValues" dxfId="340" priority="372"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="335" priority="367"/>
+    <cfRule type="duplicateValues" dxfId="339" priority="367"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="334" priority="368"/>
+    <cfRule type="duplicateValues" dxfId="338" priority="368"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="333" priority="369"/>
+    <cfRule type="duplicateValues" dxfId="337" priority="369"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="332" priority="364"/>
+    <cfRule type="duplicateValues" dxfId="336" priority="364"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="331" priority="365"/>
+    <cfRule type="duplicateValues" dxfId="335" priority="365"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="330" priority="366"/>
+    <cfRule type="duplicateValues" dxfId="334" priority="366"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="329" priority="361"/>
+    <cfRule type="duplicateValues" dxfId="333" priority="361"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="328" priority="362"/>
+    <cfRule type="duplicateValues" dxfId="332" priority="362"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="327" priority="363"/>
+    <cfRule type="duplicateValues" dxfId="331" priority="363"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47">
-    <cfRule type="duplicateValues" dxfId="326" priority="358"/>
+    <cfRule type="duplicateValues" dxfId="330" priority="358"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47">
-    <cfRule type="duplicateValues" dxfId="325" priority="359"/>
+    <cfRule type="duplicateValues" dxfId="329" priority="359"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47">
-    <cfRule type="duplicateValues" dxfId="324" priority="360"/>
+    <cfRule type="duplicateValues" dxfId="328" priority="360"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="323" priority="355"/>
+    <cfRule type="duplicateValues" dxfId="327" priority="355"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="322" priority="356"/>
+    <cfRule type="duplicateValues" dxfId="326" priority="356"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="321" priority="357"/>
+    <cfRule type="duplicateValues" dxfId="325" priority="357"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="320" priority="352"/>
+    <cfRule type="duplicateValues" dxfId="324" priority="352"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="319" priority="353"/>
+    <cfRule type="duplicateValues" dxfId="323" priority="353"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="318" priority="354"/>
+    <cfRule type="duplicateValues" dxfId="322" priority="354"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="317" priority="346"/>
+    <cfRule type="duplicateValues" dxfId="321" priority="346"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="316" priority="347"/>
+    <cfRule type="duplicateValues" dxfId="320" priority="347"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="315" priority="348"/>
+    <cfRule type="duplicateValues" dxfId="319" priority="348"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55">
-    <cfRule type="duplicateValues" dxfId="314" priority="343"/>
+    <cfRule type="duplicateValues" dxfId="318" priority="343"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55">
-    <cfRule type="duplicateValues" dxfId="313" priority="344"/>
+    <cfRule type="duplicateValues" dxfId="317" priority="344"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55">
-    <cfRule type="duplicateValues" dxfId="312" priority="345"/>
+    <cfRule type="duplicateValues" dxfId="316" priority="345"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="311" priority="340"/>
+    <cfRule type="duplicateValues" dxfId="315" priority="340"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="310" priority="341"/>
+    <cfRule type="duplicateValues" dxfId="314" priority="341"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="309" priority="342"/>
+    <cfRule type="duplicateValues" dxfId="313" priority="342"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B60">
-    <cfRule type="duplicateValues" dxfId="308" priority="337"/>
+    <cfRule type="duplicateValues" dxfId="312" priority="337"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B60">
-    <cfRule type="duplicateValues" dxfId="307" priority="338"/>
+    <cfRule type="duplicateValues" dxfId="311" priority="338"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B60">
-    <cfRule type="duplicateValues" dxfId="306" priority="339"/>
+    <cfRule type="duplicateValues" dxfId="310" priority="339"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B61">
-    <cfRule type="duplicateValues" dxfId="305" priority="334"/>
+    <cfRule type="duplicateValues" dxfId="309" priority="334"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B61">
-    <cfRule type="duplicateValues" dxfId="304" priority="335"/>
+    <cfRule type="duplicateValues" dxfId="308" priority="335"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B61">
-    <cfRule type="duplicateValues" dxfId="303" priority="336"/>
+    <cfRule type="duplicateValues" dxfId="307" priority="336"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B65">
-    <cfRule type="duplicateValues" dxfId="302" priority="331"/>
+    <cfRule type="duplicateValues" dxfId="306" priority="331"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B65">
-    <cfRule type="duplicateValues" dxfId="301" priority="332"/>
+    <cfRule type="duplicateValues" dxfId="305" priority="332"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B65">
-    <cfRule type="duplicateValues" dxfId="300" priority="333"/>
+    <cfRule type="duplicateValues" dxfId="304" priority="333"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B66">
-    <cfRule type="duplicateValues" dxfId="299" priority="328"/>
+    <cfRule type="duplicateValues" dxfId="303" priority="328"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B66">
-    <cfRule type="duplicateValues" dxfId="298" priority="329"/>
+    <cfRule type="duplicateValues" dxfId="302" priority="329"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B66">
-    <cfRule type="duplicateValues" dxfId="297" priority="330"/>
+    <cfRule type="duplicateValues" dxfId="301" priority="330"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="296" priority="325"/>
+    <cfRule type="duplicateValues" dxfId="300" priority="325"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="295" priority="326"/>
+    <cfRule type="duplicateValues" dxfId="299" priority="326"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="294" priority="327"/>
+    <cfRule type="duplicateValues" dxfId="298" priority="327"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68">
-    <cfRule type="duplicateValues" dxfId="293" priority="322"/>
+    <cfRule type="duplicateValues" dxfId="297" priority="322"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68">
-    <cfRule type="duplicateValues" dxfId="292" priority="323"/>
+    <cfRule type="duplicateValues" dxfId="296" priority="323"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68">
-    <cfRule type="duplicateValues" dxfId="291" priority="324"/>
+    <cfRule type="duplicateValues" dxfId="295" priority="324"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="290" priority="319"/>
+    <cfRule type="duplicateValues" dxfId="294" priority="319"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="289" priority="320"/>
+    <cfRule type="duplicateValues" dxfId="293" priority="320"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="288" priority="321"/>
+    <cfRule type="duplicateValues" dxfId="292" priority="321"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70">
-    <cfRule type="duplicateValues" dxfId="287" priority="313"/>
+    <cfRule type="duplicateValues" dxfId="291" priority="313"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70">
-    <cfRule type="duplicateValues" dxfId="286" priority="314"/>
+    <cfRule type="duplicateValues" dxfId="290" priority="314"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70">
-    <cfRule type="duplicateValues" dxfId="285" priority="315"/>
+    <cfRule type="duplicateValues" dxfId="289" priority="315"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="284" priority="310"/>
+    <cfRule type="duplicateValues" dxfId="288" priority="310"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="283" priority="311"/>
+    <cfRule type="duplicateValues" dxfId="287" priority="311"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="282" priority="312"/>
+    <cfRule type="duplicateValues" dxfId="286" priority="312"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72">
-    <cfRule type="duplicateValues" dxfId="281" priority="307"/>
+    <cfRule type="duplicateValues" dxfId="285" priority="307"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72">
-    <cfRule type="duplicateValues" dxfId="280" priority="308"/>
+    <cfRule type="duplicateValues" dxfId="284" priority="308"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72">
-    <cfRule type="duplicateValues" dxfId="279" priority="309"/>
+    <cfRule type="duplicateValues" dxfId="283" priority="309"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B73">
-    <cfRule type="duplicateValues" dxfId="278" priority="304"/>
+    <cfRule type="duplicateValues" dxfId="282" priority="304"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B73">
-    <cfRule type="duplicateValues" dxfId="277" priority="305"/>
+    <cfRule type="duplicateValues" dxfId="281" priority="305"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B73">
-    <cfRule type="duplicateValues" dxfId="276" priority="306"/>
+    <cfRule type="duplicateValues" dxfId="280" priority="306"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B95">
-    <cfRule type="duplicateValues" dxfId="275" priority="301"/>
+    <cfRule type="duplicateValues" dxfId="279" priority="301"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B95">
-    <cfRule type="duplicateValues" dxfId="274" priority="302"/>
+    <cfRule type="duplicateValues" dxfId="278" priority="302"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B95">
-    <cfRule type="duplicateValues" dxfId="273" priority="303"/>
+    <cfRule type="duplicateValues" dxfId="277" priority="303"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107">
-    <cfRule type="duplicateValues" dxfId="272" priority="298"/>
+    <cfRule type="duplicateValues" dxfId="276" priority="298"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107">
-    <cfRule type="duplicateValues" dxfId="271" priority="299"/>
+    <cfRule type="duplicateValues" dxfId="275" priority="299"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107">
-    <cfRule type="duplicateValues" dxfId="270" priority="300"/>
+    <cfRule type="duplicateValues" dxfId="274" priority="300"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112">
-    <cfRule type="duplicateValues" dxfId="269" priority="292"/>
+    <cfRule type="duplicateValues" dxfId="273" priority="292"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112">
-    <cfRule type="duplicateValues" dxfId="268" priority="293"/>
+    <cfRule type="duplicateValues" dxfId="272" priority="293"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112">
-    <cfRule type="duplicateValues" dxfId="267" priority="294"/>
+    <cfRule type="duplicateValues" dxfId="271" priority="294"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B113">
-    <cfRule type="duplicateValues" dxfId="266" priority="289"/>
+    <cfRule type="duplicateValues" dxfId="270" priority="289"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B113">
-    <cfRule type="duplicateValues" dxfId="265" priority="290"/>
+    <cfRule type="duplicateValues" dxfId="269" priority="290"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B113">
-    <cfRule type="duplicateValues" dxfId="264" priority="291"/>
+    <cfRule type="duplicateValues" dxfId="268" priority="291"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B120">
-    <cfRule type="duplicateValues" dxfId="263" priority="286"/>
+    <cfRule type="duplicateValues" dxfId="267" priority="286"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B120">
-    <cfRule type="duplicateValues" dxfId="262" priority="287"/>
+    <cfRule type="duplicateValues" dxfId="266" priority="287"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B120">
-    <cfRule type="duplicateValues" dxfId="261" priority="288"/>
+    <cfRule type="duplicateValues" dxfId="265" priority="288"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B121">
-    <cfRule type="duplicateValues" dxfId="260" priority="280"/>
+    <cfRule type="duplicateValues" dxfId="264" priority="280"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B121">
-    <cfRule type="duplicateValues" dxfId="259" priority="281"/>
+    <cfRule type="duplicateValues" dxfId="263" priority="281"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B121">
-    <cfRule type="duplicateValues" dxfId="258" priority="282"/>
+    <cfRule type="duplicateValues" dxfId="262" priority="282"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B123">
-    <cfRule type="duplicateValues" dxfId="257" priority="277"/>
+    <cfRule type="duplicateValues" dxfId="261" priority="277"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B123">
-    <cfRule type="duplicateValues" dxfId="256" priority="278"/>
+    <cfRule type="duplicateValues" dxfId="260" priority="278"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B123">
-    <cfRule type="duplicateValues" dxfId="255" priority="279"/>
+    <cfRule type="duplicateValues" dxfId="259" priority="279"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B127">
-    <cfRule type="duplicateValues" dxfId="254" priority="274"/>
+    <cfRule type="duplicateValues" dxfId="258" priority="274"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B127">
-    <cfRule type="duplicateValues" dxfId="253" priority="275"/>
+    <cfRule type="duplicateValues" dxfId="257" priority="275"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B127">
-    <cfRule type="duplicateValues" dxfId="252" priority="276"/>
+    <cfRule type="duplicateValues" dxfId="256" priority="276"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B153">
-    <cfRule type="duplicateValues" dxfId="251" priority="271"/>
+    <cfRule type="duplicateValues" dxfId="255" priority="271"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B153">
-    <cfRule type="duplicateValues" dxfId="250" priority="272"/>
+    <cfRule type="duplicateValues" dxfId="254" priority="272"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B153">
-    <cfRule type="duplicateValues" dxfId="249" priority="273"/>
+    <cfRule type="duplicateValues" dxfId="253" priority="273"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B155">
-    <cfRule type="duplicateValues" dxfId="248" priority="270"/>
+    <cfRule type="duplicateValues" dxfId="252" priority="270"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B156">
-    <cfRule type="duplicateValues" dxfId="247" priority="267"/>
+    <cfRule type="duplicateValues" dxfId="251" priority="267"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B156">
-    <cfRule type="duplicateValues" dxfId="246" priority="268"/>
+    <cfRule type="duplicateValues" dxfId="250" priority="268"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B156">
-    <cfRule type="duplicateValues" dxfId="245" priority="269"/>
+    <cfRule type="duplicateValues" dxfId="249" priority="269"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B158">
-    <cfRule type="duplicateValues" dxfId="244" priority="264"/>
+    <cfRule type="duplicateValues" dxfId="248" priority="264"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B158">
-    <cfRule type="duplicateValues" dxfId="243" priority="265"/>
+    <cfRule type="duplicateValues" dxfId="247" priority="265"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B158">
-    <cfRule type="duplicateValues" dxfId="242" priority="266"/>
+    <cfRule type="duplicateValues" dxfId="246" priority="266"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B165">
-    <cfRule type="duplicateValues" dxfId="241" priority="261"/>
+    <cfRule type="duplicateValues" dxfId="245" priority="261"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B165">
-    <cfRule type="duplicateValues" dxfId="240" priority="262"/>
+    <cfRule type="duplicateValues" dxfId="244" priority="262"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B165">
-    <cfRule type="duplicateValues" dxfId="239" priority="263"/>
+    <cfRule type="duplicateValues" dxfId="243" priority="263"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B168">
-    <cfRule type="duplicateValues" dxfId="238" priority="258"/>
+    <cfRule type="duplicateValues" dxfId="242" priority="258"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B168">
-    <cfRule type="duplicateValues" dxfId="237" priority="259"/>
+    <cfRule type="duplicateValues" dxfId="241" priority="259"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B168">
-    <cfRule type="duplicateValues" dxfId="236" priority="260"/>
+    <cfRule type="duplicateValues" dxfId="240" priority="260"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171">
-    <cfRule type="duplicateValues" dxfId="235" priority="255"/>
+    <cfRule type="duplicateValues" dxfId="239" priority="255"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171">
-    <cfRule type="duplicateValues" dxfId="234" priority="256"/>
+    <cfRule type="duplicateValues" dxfId="238" priority="256"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171">
-    <cfRule type="duplicateValues" dxfId="233" priority="257"/>
+    <cfRule type="duplicateValues" dxfId="237" priority="257"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B172">
-    <cfRule type="duplicateValues" dxfId="232" priority="249"/>
+    <cfRule type="duplicateValues" dxfId="236" priority="249"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B172">
-    <cfRule type="duplicateValues" dxfId="231" priority="250"/>
+    <cfRule type="duplicateValues" dxfId="235" priority="250"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B172">
-    <cfRule type="duplicateValues" dxfId="230" priority="251"/>
+    <cfRule type="duplicateValues" dxfId="234" priority="251"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B173">
-    <cfRule type="duplicateValues" dxfId="229" priority="246"/>
+    <cfRule type="duplicateValues" dxfId="233" priority="246"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B173">
-    <cfRule type="duplicateValues" dxfId="228" priority="247"/>
+    <cfRule type="duplicateValues" dxfId="232" priority="247"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B173">
-    <cfRule type="duplicateValues" dxfId="227" priority="248"/>
+    <cfRule type="duplicateValues" dxfId="231" priority="248"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B174">
-    <cfRule type="duplicateValues" dxfId="226" priority="243"/>
+    <cfRule type="duplicateValues" dxfId="230" priority="243"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B174">
-    <cfRule type="duplicateValues" dxfId="225" priority="244"/>
+    <cfRule type="duplicateValues" dxfId="229" priority="244"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B174">
-    <cfRule type="duplicateValues" dxfId="224" priority="245"/>
+    <cfRule type="duplicateValues" dxfId="228" priority="245"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B175">
-    <cfRule type="duplicateValues" dxfId="223" priority="240"/>
+    <cfRule type="duplicateValues" dxfId="227" priority="240"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B175">
-    <cfRule type="duplicateValues" dxfId="222" priority="241"/>
+    <cfRule type="duplicateValues" dxfId="226" priority="241"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B175">
-    <cfRule type="duplicateValues" dxfId="221" priority="242"/>
+    <cfRule type="duplicateValues" dxfId="225" priority="242"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B176">
-    <cfRule type="duplicateValues" dxfId="220" priority="237"/>
+    <cfRule type="duplicateValues" dxfId="224" priority="237"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B176">
-    <cfRule type="duplicateValues" dxfId="219" priority="238"/>
+    <cfRule type="duplicateValues" dxfId="223" priority="238"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B176">
-    <cfRule type="duplicateValues" dxfId="218" priority="239"/>
+    <cfRule type="duplicateValues" dxfId="222" priority="239"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B177">
-    <cfRule type="duplicateValues" dxfId="217" priority="234"/>
+    <cfRule type="duplicateValues" dxfId="221" priority="234"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B177">
-    <cfRule type="duplicateValues" dxfId="216" priority="235"/>
+    <cfRule type="duplicateValues" dxfId="220" priority="235"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B177">
-    <cfRule type="duplicateValues" dxfId="215" priority="236"/>
+    <cfRule type="duplicateValues" dxfId="219" priority="236"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B178">
-    <cfRule type="duplicateValues" dxfId="214" priority="231"/>
+    <cfRule type="duplicateValues" dxfId="218" priority="231"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B178">
-    <cfRule type="duplicateValues" dxfId="213" priority="232"/>
+    <cfRule type="duplicateValues" dxfId="217" priority="232"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B178">
-    <cfRule type="duplicateValues" dxfId="212" priority="233"/>
+    <cfRule type="duplicateValues" dxfId="216" priority="233"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B180">
-    <cfRule type="duplicateValues" dxfId="211" priority="228"/>
+    <cfRule type="duplicateValues" dxfId="215" priority="228"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B180">
-    <cfRule type="duplicateValues" dxfId="210" priority="229"/>
+    <cfRule type="duplicateValues" dxfId="214" priority="229"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B180">
-    <cfRule type="duplicateValues" dxfId="209" priority="230"/>
+    <cfRule type="duplicateValues" dxfId="213" priority="230"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B182">
-    <cfRule type="duplicateValues" dxfId="208" priority="225"/>
+    <cfRule type="duplicateValues" dxfId="212" priority="225"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B182">
-    <cfRule type="duplicateValues" dxfId="207" priority="226"/>
+    <cfRule type="duplicateValues" dxfId="211" priority="226"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B182">
-    <cfRule type="duplicateValues" dxfId="206" priority="227"/>
+    <cfRule type="duplicateValues" dxfId="210" priority="227"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B185">
-    <cfRule type="duplicateValues" dxfId="205" priority="222"/>
+    <cfRule type="duplicateValues" dxfId="209" priority="222"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B185">
-    <cfRule type="duplicateValues" dxfId="204" priority="223"/>
+    <cfRule type="duplicateValues" dxfId="208" priority="223"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B185">
-    <cfRule type="duplicateValues" dxfId="203" priority="224"/>
+    <cfRule type="duplicateValues" dxfId="207" priority="224"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B189">
-    <cfRule type="duplicateValues" dxfId="202" priority="219"/>
+    <cfRule type="duplicateValues" dxfId="206" priority="219"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B189">
-    <cfRule type="duplicateValues" dxfId="201" priority="220"/>
+    <cfRule type="duplicateValues" dxfId="205" priority="220"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B189">
-    <cfRule type="duplicateValues" dxfId="200" priority="221"/>
+    <cfRule type="duplicateValues" dxfId="204" priority="221"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B203">
-    <cfRule type="duplicateValues" dxfId="199" priority="216"/>
+    <cfRule type="duplicateValues" dxfId="203" priority="216"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B203">
-    <cfRule type="duplicateValues" dxfId="198" priority="217"/>
+    <cfRule type="duplicateValues" dxfId="202" priority="217"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B203">
-    <cfRule type="duplicateValues" dxfId="197" priority="218"/>
+    <cfRule type="duplicateValues" dxfId="201" priority="218"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B206">
-    <cfRule type="duplicateValues" dxfId="196" priority="213"/>
+    <cfRule type="duplicateValues" dxfId="200" priority="213"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B206">
-    <cfRule type="duplicateValues" dxfId="195" priority="214"/>
+    <cfRule type="duplicateValues" dxfId="199" priority="214"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B206">
-    <cfRule type="duplicateValues" dxfId="194" priority="215"/>
+    <cfRule type="duplicateValues" dxfId="198" priority="215"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B207">
-    <cfRule type="duplicateValues" dxfId="193" priority="210"/>
+    <cfRule type="duplicateValues" dxfId="197" priority="210"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B207">
-    <cfRule type="duplicateValues" dxfId="192" priority="211"/>
+    <cfRule type="duplicateValues" dxfId="196" priority="211"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B207">
-    <cfRule type="duplicateValues" dxfId="191" priority="212"/>
+    <cfRule type="duplicateValues" dxfId="195" priority="212"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B208">
-    <cfRule type="duplicateValues" dxfId="190" priority="204"/>
+    <cfRule type="duplicateValues" dxfId="194" priority="204"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B208">
-    <cfRule type="duplicateValues" dxfId="189" priority="205"/>
+    <cfRule type="duplicateValues" dxfId="193" priority="205"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B208">
-    <cfRule type="duplicateValues" dxfId="188" priority="206"/>
+    <cfRule type="duplicateValues" dxfId="192" priority="206"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B213">
-    <cfRule type="duplicateValues" dxfId="187" priority="201"/>
+    <cfRule type="duplicateValues" dxfId="191" priority="201"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B213">
-    <cfRule type="duplicateValues" dxfId="186" priority="202"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="202"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B213">
-    <cfRule type="duplicateValues" dxfId="185" priority="203"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="203"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B215">
-    <cfRule type="duplicateValues" dxfId="184" priority="198"/>
+    <cfRule type="duplicateValues" dxfId="188" priority="198"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B215">
-    <cfRule type="duplicateValues" dxfId="183" priority="199"/>
+    <cfRule type="duplicateValues" dxfId="187" priority="199"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B215">
-    <cfRule type="duplicateValues" dxfId="182" priority="200"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="200"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B218">
-    <cfRule type="duplicateValues" dxfId="181" priority="195"/>
+    <cfRule type="duplicateValues" dxfId="185" priority="195"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B218">
-    <cfRule type="duplicateValues" dxfId="180" priority="196"/>
+    <cfRule type="duplicateValues" dxfId="184" priority="196"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B218">
-    <cfRule type="duplicateValues" dxfId="179" priority="197"/>
+    <cfRule type="duplicateValues" dxfId="183" priority="197"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B221">
-    <cfRule type="duplicateValues" dxfId="178" priority="192"/>
+    <cfRule type="duplicateValues" dxfId="182" priority="192"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B221">
-    <cfRule type="duplicateValues" dxfId="177" priority="193"/>
+    <cfRule type="duplicateValues" dxfId="181" priority="193"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B221">
-    <cfRule type="duplicateValues" dxfId="176" priority="194"/>
+    <cfRule type="duplicateValues" dxfId="180" priority="194"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B230">
-    <cfRule type="duplicateValues" dxfId="175" priority="189"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="189"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B230">
-    <cfRule type="duplicateValues" dxfId="174" priority="190"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="190"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B230">
-    <cfRule type="duplicateValues" dxfId="173" priority="191"/>
+    <cfRule type="duplicateValues" dxfId="177" priority="191"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B234">
-    <cfRule type="duplicateValues" dxfId="172" priority="183"/>
+    <cfRule type="duplicateValues" dxfId="176" priority="183"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B234">
-    <cfRule type="duplicateValues" dxfId="171" priority="184"/>
+    <cfRule type="duplicateValues" dxfId="175" priority="184"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B234">
-    <cfRule type="duplicateValues" dxfId="170" priority="185"/>
+    <cfRule type="duplicateValues" dxfId="174" priority="185"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B233">
-    <cfRule type="duplicateValues" dxfId="169" priority="177"/>
+    <cfRule type="duplicateValues" dxfId="173" priority="177"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B233">
-    <cfRule type="duplicateValues" dxfId="168" priority="178"/>
+    <cfRule type="duplicateValues" dxfId="172" priority="178"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B233">
-    <cfRule type="duplicateValues" dxfId="167" priority="179"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="179"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B236">
-    <cfRule type="duplicateValues" dxfId="166" priority="174"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="174"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B236">
-    <cfRule type="duplicateValues" dxfId="165" priority="175"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="175"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B236">
-    <cfRule type="duplicateValues" dxfId="164" priority="176"/>
+    <cfRule type="duplicateValues" dxfId="168" priority="176"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B235">
-    <cfRule type="duplicateValues" dxfId="163" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="171"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B235">
-    <cfRule type="duplicateValues" dxfId="162" priority="172"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="172"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B235">
-    <cfRule type="duplicateValues" dxfId="161" priority="173"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="173"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B250">
-    <cfRule type="duplicateValues" dxfId="160" priority="168"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="168"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B250">
-    <cfRule type="duplicateValues" dxfId="159" priority="169"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="169"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B250">
-    <cfRule type="duplicateValues" dxfId="158" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="170"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B253">
-    <cfRule type="duplicateValues" dxfId="157" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="165"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B253">
-    <cfRule type="duplicateValues" dxfId="156" priority="166"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="166"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B253">
-    <cfRule type="duplicateValues" dxfId="155" priority="167"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="167"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B254">
-    <cfRule type="duplicateValues" dxfId="154" priority="162"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="162"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B254">
-    <cfRule type="duplicateValues" dxfId="153" priority="163"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="163"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B254">
-    <cfRule type="duplicateValues" dxfId="152" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="164"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B256">
-    <cfRule type="duplicateValues" dxfId="151" priority="159"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="159"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B256">
-    <cfRule type="duplicateValues" dxfId="150" priority="160"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="160"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B256">
-    <cfRule type="duplicateValues" dxfId="149" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="161"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B257">
-    <cfRule type="duplicateValues" dxfId="148" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="156"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B257">
-    <cfRule type="duplicateValues" dxfId="147" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="157"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B257">
-    <cfRule type="duplicateValues" dxfId="146" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="158"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B262">
-    <cfRule type="duplicateValues" dxfId="145" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="153"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B262">
-    <cfRule type="duplicateValues" dxfId="144" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="154"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B262">
-    <cfRule type="duplicateValues" dxfId="143" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="155"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B270">
-    <cfRule type="duplicateValues" dxfId="142" priority="150"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="150"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B270">
-    <cfRule type="duplicateValues" dxfId="141" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="151"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B270">
-    <cfRule type="duplicateValues" dxfId="140" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="152"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B272">
-    <cfRule type="duplicateValues" dxfId="139" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="148"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B272">
-    <cfRule type="duplicateValues" dxfId="138" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="147"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B272">
-    <cfRule type="duplicateValues" dxfId="137" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="149"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B280">
-    <cfRule type="duplicateValues" dxfId="136" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="144"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B280">
-    <cfRule type="duplicateValues" dxfId="135" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="145"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B280">
-    <cfRule type="duplicateValues" dxfId="134" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="146"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B284">
-    <cfRule type="duplicateValues" dxfId="133" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="139"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B284">
-    <cfRule type="duplicateValues" dxfId="132" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="138"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B284">
-    <cfRule type="duplicateValues" dxfId="131" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="140"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B285">
-    <cfRule type="duplicateValues" dxfId="130" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="135"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B285">
-    <cfRule type="duplicateValues" dxfId="129" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="136"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B285">
-    <cfRule type="duplicateValues" dxfId="128" priority="137"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="137"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B311">
-    <cfRule type="duplicateValues" dxfId="127" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="133"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B311">
-    <cfRule type="duplicateValues" dxfId="126" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="132"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B311">
-    <cfRule type="duplicateValues" dxfId="125" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="134"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B313">
-    <cfRule type="duplicateValues" dxfId="124" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="127"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B313">
-    <cfRule type="duplicateValues" dxfId="123" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="126"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B313">
-    <cfRule type="duplicateValues" dxfId="122" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="128"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B314">
-    <cfRule type="duplicateValues" dxfId="121" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="121"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B314">
-    <cfRule type="duplicateValues" dxfId="120" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="120"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B314">
-    <cfRule type="duplicateValues" dxfId="119" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="122"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B316">
-    <cfRule type="duplicateValues" dxfId="118" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="117"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B316">
-    <cfRule type="duplicateValues" dxfId="117" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B316">
-    <cfRule type="duplicateValues" dxfId="116" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B319">
-    <cfRule type="duplicateValues" dxfId="115" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B319">
-    <cfRule type="duplicateValues" dxfId="114" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B319">
-    <cfRule type="duplicateValues" dxfId="113" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="116"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B322">
-    <cfRule type="duplicateValues" dxfId="112" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="112"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B322">
-    <cfRule type="duplicateValues" dxfId="111" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="111"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B322">
-    <cfRule type="duplicateValues" dxfId="110" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B323">
-    <cfRule type="duplicateValues" dxfId="109" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="109"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B323">
-    <cfRule type="duplicateValues" dxfId="108" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B323">
-    <cfRule type="duplicateValues" dxfId="107" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B325">
-    <cfRule type="duplicateValues" dxfId="106" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="105"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B325">
-    <cfRule type="duplicateValues" dxfId="105" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B325">
-    <cfRule type="duplicateValues" dxfId="104" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B326">
-    <cfRule type="duplicateValues" dxfId="103" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B326">
-    <cfRule type="duplicateValues" dxfId="102" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B326">
-    <cfRule type="duplicateValues" dxfId="101" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B327">
-    <cfRule type="duplicateValues" dxfId="100" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="99"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B327">
-    <cfRule type="duplicateValues" dxfId="99" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B327">
-    <cfRule type="duplicateValues" dxfId="98" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B328">
-    <cfRule type="duplicateValues" dxfId="97" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B328">
-    <cfRule type="duplicateValues" dxfId="96" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="97"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B328">
-    <cfRule type="duplicateValues" dxfId="95" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="98"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B354">
-    <cfRule type="duplicateValues" dxfId="94" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="94"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B354">
-    <cfRule type="duplicateValues" dxfId="93" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="93"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B354">
-    <cfRule type="duplicateValues" dxfId="92" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="95"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B362">
-    <cfRule type="duplicateValues" dxfId="91" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B362">
-    <cfRule type="duplicateValues" dxfId="90" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="90"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B362">
-    <cfRule type="duplicateValues" dxfId="89" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="92"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B369">
-    <cfRule type="duplicateValues" dxfId="88" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B369">
-    <cfRule type="duplicateValues" dxfId="87" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B369">
-    <cfRule type="duplicateValues" dxfId="86" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="89"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B384">
-    <cfRule type="duplicateValues" dxfId="85" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B384">
-    <cfRule type="duplicateValues" dxfId="84" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B384">
-    <cfRule type="duplicateValues" dxfId="83" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B391">
-    <cfRule type="duplicateValues" dxfId="82" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B391">
-    <cfRule type="duplicateValues" dxfId="81" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B391">
-    <cfRule type="duplicateValues" dxfId="80" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B415">
-    <cfRule type="duplicateValues" dxfId="79" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B415">
-    <cfRule type="duplicateValues" dxfId="78" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B415">
-    <cfRule type="duplicateValues" dxfId="77" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B418">
-    <cfRule type="duplicateValues" dxfId="76" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B418">
-    <cfRule type="duplicateValues" dxfId="75" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B418">
-    <cfRule type="duplicateValues" dxfId="74" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B419">
-    <cfRule type="duplicateValues" dxfId="73" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B419">
-    <cfRule type="duplicateValues" dxfId="72" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B419">
-    <cfRule type="duplicateValues" dxfId="71" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B441">
-    <cfRule type="duplicateValues" dxfId="70" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B441">
-    <cfRule type="duplicateValues" dxfId="69" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B441">
-    <cfRule type="duplicateValues" dxfId="68" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B456">
-    <cfRule type="duplicateValues" dxfId="67" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B456">
-    <cfRule type="duplicateValues" dxfId="66" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B456">
-    <cfRule type="duplicateValues" dxfId="65" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B464">
-    <cfRule type="duplicateValues" dxfId="64" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B464">
-    <cfRule type="duplicateValues" dxfId="63" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B464">
-    <cfRule type="duplicateValues" dxfId="62" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B467">
-    <cfRule type="duplicateValues" dxfId="61" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B467">
-    <cfRule type="duplicateValues" dxfId="60" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B467">
-    <cfRule type="duplicateValues" dxfId="59" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B471">
-    <cfRule type="duplicateValues" dxfId="58" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B471">
-    <cfRule type="duplicateValues" dxfId="57" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B471">
-    <cfRule type="duplicateValues" dxfId="56" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B472">
-    <cfRule type="duplicateValues" dxfId="55" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B472">
-    <cfRule type="duplicateValues" dxfId="54" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B472">
-    <cfRule type="duplicateValues" dxfId="53" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B477">
-    <cfRule type="duplicateValues" dxfId="52" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B477">
-    <cfRule type="duplicateValues" dxfId="51" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B477">
-    <cfRule type="duplicateValues" dxfId="50" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B483">
-    <cfRule type="duplicateValues" dxfId="49" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B483">
-    <cfRule type="duplicateValues" dxfId="48" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B483">
-    <cfRule type="duplicateValues" dxfId="47" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B487">
-    <cfRule type="duplicateValues" dxfId="46" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B487">
-    <cfRule type="duplicateValues" dxfId="45" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B487">
-    <cfRule type="duplicateValues" dxfId="44" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B499">
-    <cfRule type="duplicateValues" dxfId="43" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B499">
-    <cfRule type="duplicateValues" dxfId="42" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B499">
-    <cfRule type="duplicateValues" dxfId="41" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B500">
-    <cfRule type="duplicateValues" dxfId="40" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B500">
-    <cfRule type="duplicateValues" dxfId="39" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B500">
-    <cfRule type="duplicateValues" dxfId="38" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B505">
-    <cfRule type="duplicateValues" dxfId="37" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B505">
-    <cfRule type="duplicateValues" dxfId="36" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B505">
-    <cfRule type="duplicateValues" dxfId="35" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B506">
-    <cfRule type="duplicateValues" dxfId="34" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B506">
-    <cfRule type="duplicateValues" dxfId="33" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B506">
-    <cfRule type="duplicateValues" dxfId="32" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B511">
-    <cfRule type="duplicateValues" dxfId="31" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B511">
-    <cfRule type="duplicateValues" dxfId="30" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B511">
-    <cfRule type="duplicateValues" dxfId="29" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B548">
-    <cfRule type="duplicateValues" dxfId="28" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B548">
-    <cfRule type="duplicateValues" dxfId="27" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B548">
-    <cfRule type="duplicateValues" dxfId="26" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B550">
-    <cfRule type="duplicateValues" dxfId="25" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B550">
-    <cfRule type="duplicateValues" dxfId="24" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B550">
-    <cfRule type="duplicateValues" dxfId="23" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B558">
-    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B558">
-    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B559">
-    <cfRule type="duplicateValues" dxfId="20" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B559">
-    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B559">
-    <cfRule type="duplicateValues" dxfId="18" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B561">
-    <cfRule type="duplicateValues" dxfId="17" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B561">
-    <cfRule type="duplicateValues" dxfId="16" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B561">
-    <cfRule type="duplicateValues" dxfId="15" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B570">
-    <cfRule type="duplicateValues" dxfId="14" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B570">
-    <cfRule type="duplicateValues" dxfId="13" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B570">
-    <cfRule type="duplicateValues" dxfId="12" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B585">
-    <cfRule type="duplicateValues" dxfId="11" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B585">
-    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B585">
-    <cfRule type="duplicateValues" dxfId="9" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B588">
-    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B588">
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B588">
-    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B597">
-    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B597">
-    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B598">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B598">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B598">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B598">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B669:B670">
+    <cfRule type="duplicateValues" dxfId="3" priority="2781"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B674:B675">
+    <cfRule type="duplicateValues" dxfId="2" priority="2782"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B676:B677">
+    <cfRule type="duplicateValues" dxfId="1" priority="2783"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B707:B709">
+    <cfRule type="duplicateValues" dxfId="0" priority="2784"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Spanish Dictionary.xlsx
+++ b/Spanish Dictionary.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2288" uniqueCount="2279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2421" uniqueCount="2412">
   <si>
     <t>Word / Expression</t>
   </si>
@@ -6201,9 +6201,6 @@
     <t>sometimes</t>
   </si>
   <si>
-    <t>ah véséhs</t>
-  </si>
-  <si>
     <t>alguno</t>
   </si>
   <si>
@@ -6222,9 +6219,6 @@
     <t>matah-reyan</t>
   </si>
   <si>
-    <t>ah-ownkéh ah véséhs éskoutchoh kéh algunoh déh éstos matah-reyan</t>
-  </si>
-  <si>
     <t>La vida</t>
   </si>
   <si>
@@ -6843,9 +6837,6 @@
     <t>porkéh téngoh él deenéroh ohyy</t>
   </si>
   <si>
-    <t>unit 13</t>
-  </si>
-  <si>
     <t>y mañana no tengo nada</t>
   </si>
   <si>
@@ -6853,6 +6844,414 @@
   </si>
   <si>
     <t>ee manianah noh téngoh nadah</t>
+  </si>
+  <si>
+    <t>ah béséhs</t>
+  </si>
+  <si>
+    <t>ah-ownkéh ah béséhs éskoutchoh kéh algunoh déh éstos matah-reyan</t>
+  </si>
+  <si>
+    <t>Morad - PELELE</t>
+  </si>
+  <si>
+    <t>Pelele</t>
+  </si>
+  <si>
+    <t>péléléh</t>
+  </si>
+  <si>
+    <t>dummy, weak easily manipulated person</t>
+  </si>
+  <si>
+    <t>Hombre, no te sale</t>
+  </si>
+  <si>
+    <t>Man, you can't do it</t>
+  </si>
+  <si>
+    <t>ombréh noh téh salé</t>
+  </si>
+  <si>
+    <t>Morad cómo te sales, si entras aquí no sales</t>
+  </si>
+  <si>
+    <t>Morad komoh téh salé, cee éntras aqui noh salés</t>
+  </si>
+  <si>
+    <t>Morad, how do you get out? If you come in here, you won't get out.</t>
+  </si>
+  <si>
+    <t>Sabes que tú no vales</t>
+  </si>
+  <si>
+    <t>You know you're worthless</t>
+  </si>
+  <si>
+    <t>como sueno yo en instrumentales</t>
+  </si>
+  <si>
+    <t>how I sound in instrumentals</t>
+  </si>
+  <si>
+    <t>komoh suénoh yoh én eenstruméntalés</t>
+  </si>
+  <si>
+    <t>Hablando de los mundo' de ilegale</t>
+  </si>
+  <si>
+    <t>Speaking of the world of illegals</t>
+  </si>
+  <si>
+    <t>ablandoh déh lohs mundoh déh eelégaléh</t>
+  </si>
+  <si>
+    <t>Pegadizo como "Dale Don Dale"</t>
+  </si>
+  <si>
+    <t>Catchy like "Dale Don Dale"</t>
+  </si>
+  <si>
+    <t>pégadisoh komoh daléh don dalé</t>
+  </si>
+  <si>
+    <t>Dale Don Dale</t>
+  </si>
+  <si>
+    <t>go ahead, Don, go ahead</t>
+  </si>
+  <si>
+    <t>daléh don dalé</t>
+  </si>
+  <si>
+    <t>I'm always playing in the street, you're on the Top 40</t>
+  </si>
+  <si>
+    <t>Yo sonando siеmpre en la calle, tú cuarenta Principalеs</t>
+  </si>
+  <si>
+    <t>cuarenta</t>
+  </si>
+  <si>
+    <t>quarentah</t>
+  </si>
+  <si>
+    <t>sabés kéh toh noh balés</t>
+  </si>
+  <si>
+    <t>yoh sonandoh siémpréh én lah cahyéh, toh quarentah preenceepalés</t>
+  </si>
+  <si>
+    <t>Four guitarists, 17 who have an orchestra</t>
+  </si>
+  <si>
+    <t>diecisiete</t>
+  </si>
+  <si>
+    <t>diéhsee-siétéh</t>
+  </si>
+  <si>
+    <t>quatroh geetarristah diéhsee-siétéh kéh tiénén orkéstah</t>
+  </si>
+  <si>
+    <t>Cuatro guitarrista', diecisiete que tienen orquesta</t>
+  </si>
+  <si>
+    <t>Para hacer un tema que no suena ni en la fiesta</t>
+  </si>
+  <si>
+    <t>To make a song that doesn't even get played at the party</t>
+  </si>
+  <si>
+    <t>parah asér own témah kéh noh suénah ni én lah fiéstah</t>
+  </si>
+  <si>
+    <t>Yo hago mi escritura fumando uno de verdura</t>
+  </si>
+  <si>
+    <t>I do my writing while smoking a marijuana joint</t>
+  </si>
+  <si>
+    <t>yoh agoh mee éscreeturah fumandoh ownoh dé vérdurah</t>
+  </si>
+  <si>
+    <t>Tú dos meses duras, tú está fuera de cobertura</t>
+  </si>
+  <si>
+    <t>You last two months, you're out of coverage</t>
+  </si>
+  <si>
+    <t>toh dohs mésés durahs, toh estah fuerah déh cobérturah</t>
+  </si>
+  <si>
+    <t>La calle está loca (Loca), eso e' lo que pica</t>
+  </si>
+  <si>
+    <t>The street is crazy (Crazy), that's what's stinging</t>
+  </si>
+  <si>
+    <t>lah cahyéh estah lokah ésoh éh loh kéh peekah</t>
+  </si>
+  <si>
+    <t>Pagamos a toca y tú pidiéndole a tu chica</t>
+  </si>
+  <si>
+    <t>We pay in full and you're asking your girl</t>
+  </si>
+  <si>
+    <t>pahgahmos ah tokah ee toh peediéndoléh ah toh tchikah</t>
+  </si>
+  <si>
+    <t>El capo González puede que te cale</t>
+  </si>
+  <si>
+    <t>The boss González might get to you</t>
+  </si>
+  <si>
+    <t>éhl kapoh gonzaléh puédéh kéh téh kaléh</t>
+  </si>
+  <si>
+    <t>Tu coche se cala, y acaba' luego en la tele (Cuidado)</t>
+  </si>
+  <si>
+    <t>Your car stalls, and then it ends up on TV (Watch out)</t>
+  </si>
+  <si>
+    <t>toh kotchéh séh kalah ee akabah luégoh én lah téléh quidadoh</t>
+  </si>
+  <si>
+    <t>Mira que ya e' fácil (Cuidado), en cinco minuto' (Cuidado)</t>
+  </si>
+  <si>
+    <t>Look how easy it is now (Careful), in five minutes (Careful)</t>
+  </si>
+  <si>
+    <t>meerah kéh yah éh faseel quidadoh éhn sinkoh meenutoh quidadoh</t>
+  </si>
+  <si>
+    <t>Lo hago ya duro, rápido y también impoluto</t>
+  </si>
+  <si>
+    <t>I do it hard, fast, and also spotless</t>
+  </si>
+  <si>
+    <t>loh agoh yah duroh rapidoh ee tambiénn empolutoh</t>
+  </si>
+  <si>
+    <t>Más duro que yeso, más de uno lo discuto</t>
+  </si>
+  <si>
+    <t>Harder than plaster, more than one person would argue.</t>
+  </si>
+  <si>
+    <t>mahs duroh kéh yésoh mahs déh ownoh loh deskutoh</t>
+  </si>
+  <si>
+    <t>Para, para, para</t>
+  </si>
+  <si>
+    <t>Stop, stop, stop</t>
+  </si>
+  <si>
+    <t>parah parah parah</t>
+  </si>
+  <si>
+    <t>Espera, espera, espera, espera que lo cambie</t>
+  </si>
+  <si>
+    <t>Wait, wait, wait, wait, let me change it</t>
+  </si>
+  <si>
+    <t>éspérah, éspérah, éspérah, éspérah kéh loh kambiéh</t>
+  </si>
+  <si>
+    <t>Dime dónde para', para ir a buscarte, y cogerte aparte</t>
+  </si>
+  <si>
+    <t>Tell me where you're staying, so I can come find you and we can go off on our own.</t>
+  </si>
+  <si>
+    <t>deeméh dondéh parah parah eer ah buscartéh ee kokhértéh aparté</t>
+  </si>
+  <si>
+    <t>¿Dónde está' escondí'o? A mí no interesa</t>
+  </si>
+  <si>
+    <t>Where is he hiding? I don't care.</t>
+  </si>
+  <si>
+    <t>dondéh estah éskondioh ah mee noh eentérésah</t>
+  </si>
+  <si>
+    <t>Tener que grabarte, si eres un desastre</t>
+  </si>
+  <si>
+    <t>Having to record yourself, if you're a disaster</t>
+  </si>
+  <si>
+    <t>ténér kéh grabartéh cee-érés own désastréh</t>
+  </si>
+  <si>
+    <t>¿Dónde está' escondí'o? ¿Y quién es tu colega?</t>
+  </si>
+  <si>
+    <t>Where is he hiding? And who is your colleague?</t>
+  </si>
+  <si>
+    <t>El que te lo brega o el que por ti se pega</t>
+  </si>
+  <si>
+    <t>The one who works hard for you or the one who sticks for you</t>
+  </si>
+  <si>
+    <t>éhl kéh téh loh brégah oh éhl kéh por ti séh pégah</t>
+  </si>
+  <si>
+    <t>¿Dónde está' escondí'o? ¿Dónde e' tu grupo?</t>
+  </si>
+  <si>
+    <t>Where are you hiding? Where are you from your group?</t>
+  </si>
+  <si>
+    <t>dondéh estah éskondioh ee kién-és toh kolégah?</t>
+  </si>
+  <si>
+    <t>dondéh estah éskondioh dondéh éh toh grupoh?</t>
+  </si>
+  <si>
+    <t>To see how I spit it out, and then I don't worry</t>
+  </si>
+  <si>
+    <t>parah vér komoh loh éskupoh ee luégoh noh méh préokupoh</t>
+  </si>
+  <si>
+    <t>Para ver cómo lo escupo, y luego no me preocupo</t>
+  </si>
+  <si>
+    <t>Tú tiene' una pistola pero no dispara</t>
+  </si>
+  <si>
+    <t>You have a gun but it doesn't shoot</t>
+  </si>
+  <si>
+    <t>toh tiéné ownah peestolah péroh noh deesparah</t>
+  </si>
+  <si>
+    <t>Eladio dijo "no hay chaleco para la cara"</t>
+  </si>
+  <si>
+    <t>Eladio said, "There's no vest for the face."</t>
+  </si>
+  <si>
+    <t>Eladio dikhoh noh ahyy tchalekoh parah la karah</t>
+  </si>
+  <si>
+    <t>Entonces te haremos la de los 9amara, la de los 9amara (Te raja)</t>
+  </si>
+  <si>
+    <t>Then we'll do the 9amara one to you, the 9amara one (It'll cut you open)</t>
+  </si>
+  <si>
+    <t>éntonséhs téh arémos lah dé lohs amarah, lah déh lohs amarah téh rakhah</t>
+  </si>
+  <si>
+    <t>Wait, now I see that I'm doing what I want</t>
+  </si>
+  <si>
+    <t>éspérah ahorah véoh kéh estoy asiéndoh loh kéh kiérah</t>
+  </si>
+  <si>
+    <t>Espera, ahora veo que estoy haciendo lo que quiera</t>
+  </si>
+  <si>
+    <t>ee toh aprétadoh kon entéréhs déh deskérah</t>
+  </si>
+  <si>
+    <t>Y tú apretado con interés de disquera</t>
+  </si>
+  <si>
+    <t>And you're squeezed with record label interest</t>
+  </si>
+  <si>
+    <t>Y yo tranquilo hasta el día que me muera, hasta que me oye</t>
+  </si>
+  <si>
+    <t>And I'll be at peace until the day I die, until he hears me</t>
+  </si>
+  <si>
+    <t>ee yoh tranquiloh astah él diah kéh mé muérah astah kéh méh ohyéh</t>
+  </si>
+  <si>
+    <t>pelele, te crees que es muy fácil nombrar a la L</t>
+  </si>
+  <si>
+    <t>You fool, you think it's so easy to name the letter L</t>
+  </si>
+  <si>
+    <t>péléléh téh krées kéh éhs muyy fasel nombrar á lah élé</t>
+  </si>
+  <si>
+    <t>Si sabemos que tú no llega' a los nivele'</t>
+  </si>
+  <si>
+    <t>If we know that you don't reach the levels</t>
+  </si>
+  <si>
+    <t>cee sabémos kéh toh noh yégah á lohs nebéléh</t>
+  </si>
+  <si>
+    <t>Y nosotros os pusimos a vosotro' los chele', los primero' chele'</t>
+  </si>
+  <si>
+    <t>And we called you 'the whites', the first 'whites'</t>
+  </si>
+  <si>
+    <t>ee nosotrohs ohs pusimohs ah vosotroh lohs tchéléh lohs preeméroh tchéléh</t>
+  </si>
+  <si>
+    <t>Cuando me ven de frente ya me dicen "para"</t>
+  </si>
+  <si>
+    <t>quandoh méh bén déh fréntéh yah méh desén parah</t>
+  </si>
+  <si>
+    <t>When they see me from the front they already tell me "stop"</t>
+  </si>
+  <si>
+    <t>Veo a tu grupo</t>
+  </si>
+  <si>
+    <t>I see your group</t>
+  </si>
+  <si>
+    <t>béyoh ah toh grupoh</t>
+  </si>
+  <si>
+    <t>Si yo los veo</t>
+  </si>
+  <si>
+    <t>cee yoh lohs béyoh</t>
+  </si>
+  <si>
+    <t>If I see them</t>
+  </si>
+  <si>
+    <t>Veo a tu grupo y solo me sale</t>
+  </si>
+  <si>
+    <t>béyoh ah toh grupoh ee soloh méh saléh</t>
+  </si>
+  <si>
+    <t>I see your group and all I see is</t>
+  </si>
+  <si>
+    <t>Tú mamá de teta</t>
+  </si>
+  <si>
+    <t>Your breastfeeding mom</t>
+  </si>
+  <si>
+    <t>toh mamah déh tétah</t>
   </si>
 </sst>
 </file>
@@ -6903,237 +7302,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1690">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1667">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -24101,7 +24270,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:D774"/>
+  <dimension ref="B1:D819"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="1" customWidth="1"/>
@@ -31596,7 +31765,7 @@
         <v>1861</v>
       </c>
       <c r="C687" s="1" t="s">
-        <v>2068</v>
+        <v>2277</v>
       </c>
       <c r="D687" s="1" t="s">
         <v>1862</v>
@@ -31618,7 +31787,7 @@
         <v>2059</v>
       </c>
       <c r="C689" s="1" t="s">
-        <v>2061</v>
+        <v>2276</v>
       </c>
       <c r="D689" s="1" t="s">
         <v>2060</v>
@@ -31626,24 +31795,24 @@
     </row>
     <row r="690" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B690" s="1" t="s">
+        <v>2061</v>
+      </c>
+      <c r="C690" s="1" t="s">
         <v>2062</v>
       </c>
-      <c r="C690" s="1" t="s">
+      <c r="D690" s="1" t="s">
         <v>2063</v>
-      </c>
-      <c r="D690" s="1" t="s">
-        <v>2064</v>
       </c>
     </row>
     <row r="691" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B691" s="1" t="s">
+        <v>2064</v>
+      </c>
+      <c r="C691" s="1" t="s">
+        <v>2066</v>
+      </c>
+      <c r="D691" s="1" t="s">
         <v>2065</v>
-      </c>
-      <c r="C691" s="1" t="s">
-        <v>2067</v>
-      </c>
-      <c r="D691" s="1" t="s">
-        <v>2066</v>
       </c>
     </row>
     <row r="692" spans="2:4" x14ac:dyDescent="0.25">
@@ -31651,7 +31820,7 @@
         <v>1863</v>
       </c>
       <c r="C692" s="1" t="s">
-        <v>2071</v>
+        <v>2069</v>
       </c>
       <c r="D692" s="1" t="s">
         <v>1864</v>
@@ -31659,13 +31828,13 @@
     </row>
     <row r="693" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B693" s="1" t="s">
-        <v>2069</v>
+        <v>2067</v>
       </c>
       <c r="C693" s="1" t="s">
-        <v>2072</v>
+        <v>2070</v>
       </c>
       <c r="D693" s="1" t="s">
-        <v>2070</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="694" spans="2:4" x14ac:dyDescent="0.25">
@@ -31684,7 +31853,7 @@
         <v>1868</v>
       </c>
       <c r="C695" s="1" t="s">
-        <v>2075</v>
+        <v>2073</v>
       </c>
       <c r="D695" s="1" t="s">
         <v>1869</v>
@@ -31692,24 +31861,24 @@
     </row>
     <row r="696" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B696" s="1" t="s">
-        <v>2073</v>
+        <v>2071</v>
       </c>
       <c r="C696" s="1" t="s">
-        <v>2076</v>
+        <v>2074</v>
       </c>
       <c r="D696" s="1" t="s">
-        <v>2074</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="697" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B697" s="1" t="s">
+        <v>2075</v>
+      </c>
+      <c r="C697" s="1" t="s">
+        <v>2076</v>
+      </c>
+      <c r="D697" s="1" t="s">
         <v>2077</v>
-      </c>
-      <c r="C697" s="1" t="s">
-        <v>2078</v>
-      </c>
-      <c r="D697" s="1" t="s">
-        <v>2079</v>
       </c>
     </row>
     <row r="698" spans="2:4" x14ac:dyDescent="0.25">
@@ -31725,35 +31894,35 @@
     </row>
     <row r="699" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B699" s="1" t="s">
+        <v>2078</v>
+      </c>
+      <c r="C699" s="1" t="s">
+        <v>2079</v>
+      </c>
+      <c r="D699" s="1" t="s">
         <v>2080</v>
-      </c>
-      <c r="C699" s="1" t="s">
-        <v>2081</v>
-      </c>
-      <c r="D699" s="1" t="s">
-        <v>2082</v>
       </c>
     </row>
     <row r="700" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B700" s="1" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C700" s="1" t="s">
+        <v>2082</v>
+      </c>
+      <c r="D700" s="1" t="s">
         <v>2083</v>
-      </c>
-      <c r="C700" s="1" t="s">
-        <v>2084</v>
-      </c>
-      <c r="D700" s="1" t="s">
-        <v>2085</v>
       </c>
     </row>
     <row r="701" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B701" s="1" t="s">
+        <v>2084</v>
+      </c>
+      <c r="C701" s="1" t="s">
         <v>2086</v>
       </c>
-      <c r="C701" s="1" t="s">
-        <v>2088</v>
-      </c>
       <c r="D701" s="1" t="s">
-        <v>2087</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="702" spans="2:4" x14ac:dyDescent="0.25">
@@ -31761,43 +31930,43 @@
         <v>1873</v>
       </c>
       <c r="C702" s="1" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="D702" s="1" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="703" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B703" s="1" t="s">
-        <v>2090</v>
+        <v>2088</v>
       </c>
       <c r="C703" s="1" t="s">
+        <v>2089</v>
+      </c>
+      <c r="D703" s="1" t="s">
         <v>2091</v>
-      </c>
-      <c r="D703" s="1" t="s">
-        <v>2093</v>
       </c>
     </row>
     <row r="704" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B704" s="1" t="s">
+        <v>2092</v>
+      </c>
+      <c r="C704" s="1" t="s">
+        <v>2093</v>
+      </c>
+      <c r="D704" s="1" t="s">
         <v>2094</v>
-      </c>
-      <c r="C704" s="1" t="s">
-        <v>2095</v>
-      </c>
-      <c r="D704" s="1" t="s">
-        <v>2096</v>
       </c>
     </row>
     <row r="705" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B705" s="1" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C705" s="1" t="s">
         <v>2097</v>
       </c>
-      <c r="C705" s="1" t="s">
-        <v>2099</v>
-      </c>
       <c r="D705" s="1" t="s">
-        <v>2098</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="706" spans="2:4" x14ac:dyDescent="0.25">
@@ -31813,24 +31982,24 @@
     </row>
     <row r="707" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B707" s="1" t="s">
+        <v>2098</v>
+      </c>
+      <c r="C707" s="1" t="s">
         <v>2100</v>
       </c>
-      <c r="C707" s="1" t="s">
-        <v>2102</v>
-      </c>
       <c r="D707" s="1" t="s">
-        <v>2101</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="708" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B708" s="1" t="s">
+        <v>2101</v>
+      </c>
+      <c r="C708" s="1" t="s">
         <v>2103</v>
       </c>
-      <c r="C708" s="1" t="s">
-        <v>2105</v>
-      </c>
       <c r="D708" s="1" t="s">
-        <v>2104</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="709" spans="2:4" x14ac:dyDescent="0.25">
@@ -31846,13 +32015,13 @@
     </row>
     <row r="710" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B710" s="1" t="s">
+        <v>2104</v>
+      </c>
+      <c r="C710" s="1" t="s">
         <v>2106</v>
       </c>
-      <c r="C710" s="1" t="s">
-        <v>2108</v>
-      </c>
       <c r="D710" s="1" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="711" spans="2:4" x14ac:dyDescent="0.25">
@@ -31871,7 +32040,7 @@
         <v>1883</v>
       </c>
       <c r="C712" s="1" t="s">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="D712" s="1" t="s">
         <v>1884</v>
@@ -31879,13 +32048,13 @@
     </row>
     <row r="713" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B713" s="1" t="s">
+        <v>2107</v>
+      </c>
+      <c r="C713" s="1" t="s">
         <v>2109</v>
       </c>
-      <c r="C713" s="1" t="s">
-        <v>2111</v>
-      </c>
       <c r="D713" s="1" t="s">
-        <v>2110</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="714" spans="2:4" x14ac:dyDescent="0.25">
@@ -31901,13 +32070,13 @@
     </row>
     <row r="715" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B715" s="1" t="s">
+        <v>2111</v>
+      </c>
+      <c r="C715" s="1" t="s">
+        <v>2112</v>
+      </c>
+      <c r="D715" s="1" t="s">
         <v>2113</v>
-      </c>
-      <c r="C715" s="1" t="s">
-        <v>2114</v>
-      </c>
-      <c r="D715" s="1" t="s">
-        <v>2115</v>
       </c>
     </row>
     <row r="716" spans="2:4" x14ac:dyDescent="0.25">
@@ -31923,24 +32092,24 @@
     </row>
     <row r="717" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B717" s="1" t="s">
+        <v>2127</v>
+      </c>
+      <c r="C717" s="1" t="s">
+        <v>2128</v>
+      </c>
+      <c r="D717" s="1" t="s">
         <v>2129</v>
-      </c>
-      <c r="C717" s="1" t="s">
-        <v>2130</v>
-      </c>
-      <c r="D717" s="1" t="s">
-        <v>2131</v>
       </c>
     </row>
     <row r="718" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B718" s="1" t="s">
+        <v>2114</v>
+      </c>
+      <c r="C718" s="1" t="s">
         <v>2116</v>
       </c>
-      <c r="C718" s="1" t="s">
-        <v>2118</v>
-      </c>
       <c r="D718" s="1" t="s">
-        <v>2117</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="719" spans="2:4" x14ac:dyDescent="0.25">
@@ -31956,21 +32125,21 @@
     </row>
     <row r="720" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B720" s="1" t="s">
-        <v>2119</v>
+        <v>2117</v>
       </c>
       <c r="C720" s="1" t="s">
-        <v>2120</v>
+        <v>2118</v>
       </c>
       <c r="D720" s="1" t="s">
-        <v>2132</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="721" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B721" s="1" t="s">
-        <v>2124</v>
+        <v>2122</v>
       </c>
       <c r="C721" s="1" t="s">
-        <v>2127</v>
+        <v>2125</v>
       </c>
       <c r="D721" s="1" t="s">
         <v>1894</v>
@@ -31978,24 +32147,24 @@
     </row>
     <row r="722" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B722" s="1" t="s">
+        <v>2119</v>
+      </c>
+      <c r="C722" s="1" t="s">
         <v>2121</v>
       </c>
-      <c r="C722" s="1" t="s">
-        <v>2123</v>
-      </c>
       <c r="D722" s="1" t="s">
-        <v>2122</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="723" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B723" s="1" t="s">
-        <v>2125</v>
+        <v>2123</v>
       </c>
       <c r="C723" s="1" t="s">
+        <v>2124</v>
+      </c>
+      <c r="D723" s="1" t="s">
         <v>2126</v>
-      </c>
-      <c r="D723" s="1" t="s">
-        <v>2128</v>
       </c>
     </row>
     <row r="724" spans="2:4" x14ac:dyDescent="0.25">
@@ -32005,384 +32174,384 @@
     </row>
     <row r="725" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B725" s="1" t="s">
+        <v>2131</v>
+      </c>
+      <c r="C725" s="1" t="s">
         <v>2133</v>
       </c>
-      <c r="C725" s="1" t="s">
-        <v>2135</v>
-      </c>
       <c r="D725" s="1" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="726" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B726" s="1" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C726" s="1" t="s">
+        <v>2135</v>
+      </c>
+      <c r="D726" s="1" t="s">
         <v>2136</v>
-      </c>
-      <c r="C726" s="1" t="s">
-        <v>2137</v>
-      </c>
-      <c r="D726" s="1" t="s">
-        <v>2138</v>
       </c>
     </row>
     <row r="727" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B727" s="1" t="s">
+        <v>2137</v>
+      </c>
+      <c r="C727" s="1" t="s">
         <v>2139</v>
       </c>
-      <c r="C727" s="1" t="s">
-        <v>2141</v>
-      </c>
       <c r="D727" s="1" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="728" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B728" s="1" t="s">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="C728" s="1" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="D728" s="1" t="s">
-        <v>2142</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="729" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B729" s="1" t="s">
-        <v>2146</v>
+        <v>2144</v>
       </c>
       <c r="C729" s="1" t="s">
-        <v>2147</v>
+        <v>2145</v>
       </c>
       <c r="D729" s="1" t="s">
-        <v>2145</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="730" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B730" s="1" t="s">
-        <v>2149</v>
+        <v>2147</v>
       </c>
       <c r="C730" s="1" t="s">
-        <v>2150</v>
+        <v>2148</v>
       </c>
       <c r="D730" s="1" t="s">
-        <v>2148</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="731" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B731" s="1" t="s">
-        <v>2152</v>
+        <v>2150</v>
       </c>
       <c r="C731" s="1" t="s">
-        <v>2153</v>
+        <v>2151</v>
       </c>
       <c r="D731" s="1" t="s">
-        <v>2151</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="732" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B732" s="1" t="s">
-        <v>2155</v>
+        <v>2153</v>
       </c>
       <c r="C732" s="1" t="s">
-        <v>2156</v>
+        <v>2154</v>
       </c>
       <c r="D732" s="1" t="s">
-        <v>2154</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="733" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B733" s="1" t="s">
-        <v>2158</v>
+        <v>2156</v>
       </c>
       <c r="C733" s="1" t="s">
-        <v>2159</v>
+        <v>2157</v>
       </c>
       <c r="D733" s="1" t="s">
-        <v>2157</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="734" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B734" s="1" t="s">
-        <v>2161</v>
+        <v>2159</v>
       </c>
       <c r="C734" s="1" t="s">
-        <v>2162</v>
+        <v>2160</v>
       </c>
       <c r="D734" s="1" t="s">
-        <v>2160</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="735" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B735" s="1" t="s">
-        <v>2164</v>
+        <v>2162</v>
       </c>
       <c r="C735" s="1" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
       <c r="D735" s="1" t="s">
-        <v>2163</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="736" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B736" s="1" t="s">
-        <v>2167</v>
+        <v>2165</v>
       </c>
       <c r="C736" s="1" t="s">
-        <v>2168</v>
+        <v>2166</v>
       </c>
       <c r="D736" s="1" t="s">
-        <v>2166</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="737" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B737" s="1" t="s">
-        <v>2170</v>
+        <v>2168</v>
       </c>
       <c r="C737" s="1" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
       <c r="D737" s="1" t="s">
-        <v>2169</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="738" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B738" s="1" t="s">
-        <v>2173</v>
+        <v>2171</v>
       </c>
       <c r="C738" s="1" t="s">
-        <v>2174</v>
+        <v>2172</v>
       </c>
       <c r="D738" s="1" t="s">
-        <v>2172</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="739" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B739" s="1" t="s">
+        <v>2173</v>
+      </c>
+      <c r="C739" s="1" t="s">
         <v>2175</v>
       </c>
-      <c r="C739" s="1" t="s">
-        <v>2177</v>
-      </c>
       <c r="D739" s="1" t="s">
-        <v>2176</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="740" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B740" s="1" t="s">
-        <v>2179</v>
+        <v>2177</v>
       </c>
       <c r="C740" s="1" t="s">
-        <v>2180</v>
+        <v>2178</v>
       </c>
       <c r="D740" s="1" t="s">
-        <v>2178</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="741" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B741" s="1" t="s">
-        <v>2182</v>
+        <v>2180</v>
       </c>
       <c r="C741" s="1" t="s">
-        <v>2183</v>
+        <v>2181</v>
       </c>
       <c r="D741" s="1" t="s">
-        <v>2181</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="742" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B742" s="1" t="s">
-        <v>2185</v>
+        <v>2183</v>
       </c>
       <c r="C742" s="1" t="s">
-        <v>2186</v>
+        <v>2184</v>
       </c>
       <c r="D742" s="1" t="s">
-        <v>2184</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="743" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B743" s="1" t="s">
-        <v>2188</v>
+        <v>2186</v>
       </c>
       <c r="C743" s="1" t="s">
-        <v>2189</v>
+        <v>2187</v>
       </c>
       <c r="D743" s="1" t="s">
-        <v>2187</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="744" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B744" s="1" t="s">
-        <v>2191</v>
+        <v>2189</v>
       </c>
       <c r="C744" s="1" t="s">
-        <v>2194</v>
+        <v>2192</v>
       </c>
       <c r="D744" s="1" t="s">
-        <v>2190</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="745" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B745" s="1" t="s">
+        <v>2191</v>
+      </c>
+      <c r="C745" s="1" t="s">
         <v>2193</v>
       </c>
-      <c r="C745" s="1" t="s">
-        <v>2195</v>
-      </c>
       <c r="D745" s="1" t="s">
-        <v>2192</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="746" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B746" s="1" t="s">
-        <v>2197</v>
+        <v>2195</v>
       </c>
       <c r="C746" s="1" t="s">
-        <v>2198</v>
+        <v>2196</v>
       </c>
       <c r="D746" s="1" t="s">
-        <v>2196</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="747" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B747" s="1" t="s">
-        <v>2200</v>
+        <v>2198</v>
       </c>
       <c r="C747" s="1" t="s">
-        <v>2201</v>
+        <v>2199</v>
       </c>
       <c r="D747" s="1" t="s">
-        <v>2199</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="748" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B748" s="1" t="s">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="C748" s="1" t="s">
-        <v>2204</v>
+        <v>2202</v>
       </c>
       <c r="D748" s="1" t="s">
-        <v>2202</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="749" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B749" s="1" t="s">
-        <v>2206</v>
+        <v>2204</v>
       </c>
       <c r="C749" s="1" t="s">
-        <v>2207</v>
+        <v>2205</v>
       </c>
       <c r="D749" s="1" t="s">
-        <v>2205</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="750" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B750" s="1" t="s">
-        <v>2209</v>
+        <v>2207</v>
       </c>
       <c r="C750" s="1" t="s">
-        <v>2210</v>
+        <v>2208</v>
       </c>
       <c r="D750" s="1" t="s">
-        <v>2208</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="751" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B751" s="1" t="s">
-        <v>2212</v>
+        <v>2210</v>
       </c>
       <c r="C751" s="1" t="s">
-        <v>2213</v>
+        <v>2211</v>
       </c>
       <c r="D751" s="1" t="s">
-        <v>2211</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="752" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B752" s="1" t="s">
-        <v>2215</v>
+        <v>2213</v>
       </c>
       <c r="C752" s="1" t="s">
-        <v>2216</v>
+        <v>2214</v>
       </c>
       <c r="D752" s="1" t="s">
-        <v>2214</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="753" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B753" s="1" t="s">
-        <v>2218</v>
+        <v>2216</v>
       </c>
       <c r="C753" s="1" t="s">
-        <v>2219</v>
+        <v>2217</v>
       </c>
       <c r="D753" s="1" t="s">
-        <v>2217</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="754" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B754" s="1" t="s">
-        <v>2221</v>
+        <v>2219</v>
       </c>
       <c r="C754" s="1" t="s">
-        <v>2222</v>
+        <v>2220</v>
       </c>
       <c r="D754" s="1" t="s">
-        <v>2220</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="755" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B755" s="1" t="s">
-        <v>2224</v>
+        <v>2222</v>
       </c>
       <c r="C755" s="1" t="s">
-        <v>2225</v>
+        <v>2223</v>
       </c>
       <c r="D755" s="1" t="s">
-        <v>2223</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="756" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B756" s="1" t="s">
-        <v>2227</v>
+        <v>2225</v>
       </c>
       <c r="C756" s="1" t="s">
-        <v>2228</v>
+        <v>2226</v>
       </c>
       <c r="D756" s="1" t="s">
-        <v>2226</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="757" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B757" s="1" t="s">
-        <v>2230</v>
+        <v>2228</v>
       </c>
       <c r="C757" s="1" t="s">
-        <v>2231</v>
+        <v>2229</v>
       </c>
       <c r="D757" s="1" t="s">
-        <v>2229</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="758" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B758" s="1" t="s">
-        <v>2233</v>
+        <v>2231</v>
       </c>
       <c r="C758" s="1" t="s">
-        <v>2234</v>
+        <v>2232</v>
       </c>
       <c r="D758" s="1" t="s">
-        <v>2232</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="759" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B759" s="1" t="s">
-        <v>2235</v>
+        <v>2233</v>
       </c>
       <c r="C759" s="1" t="s">
-        <v>2236</v>
+        <v>2234</v>
       </c>
       <c r="D759" s="1">
         <v>14</v>
@@ -32390,10 +32559,10 @@
     </row>
     <row r="760" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B760" s="1" t="s">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="C760" s="1" t="s">
-        <v>2238</v>
+        <v>2236</v>
       </c>
       <c r="D760" s="1">
         <v>15</v>
@@ -32401,5153 +32570,5648 @@
     </row>
     <row r="761" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B761" s="1" t="s">
+        <v>2237</v>
+      </c>
+      <c r="C761" s="1" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D761" s="1" t="s">
         <v>2239</v>
-      </c>
-      <c r="C761" s="1" t="s">
-        <v>2240</v>
-      </c>
-      <c r="D761" s="1" t="s">
-        <v>2241</v>
       </c>
     </row>
     <row r="762" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B762" s="1" t="s">
-        <v>2243</v>
+        <v>2241</v>
       </c>
       <c r="C762" s="1" t="s">
-        <v>2244</v>
+        <v>2242</v>
       </c>
       <c r="D762" s="1" t="s">
-        <v>2242</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="763" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B763" s="1" t="s">
-        <v>2246</v>
+        <v>2244</v>
       </c>
       <c r="C763" s="1" t="s">
-        <v>2247</v>
+        <v>2245</v>
       </c>
       <c r="D763" s="1" t="s">
-        <v>2245</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="764" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B764" s="1" t="s">
-        <v>2249</v>
+        <v>2247</v>
       </c>
       <c r="C764" s="1" t="s">
-        <v>2250</v>
+        <v>2248</v>
       </c>
       <c r="D764" s="1" t="s">
-        <v>2248</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="765" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B765" s="1" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
       <c r="C765" s="1" t="s">
-        <v>2253</v>
+        <v>2251</v>
       </c>
       <c r="D765" s="1" t="s">
-        <v>2251</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="766" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B766" s="1" t="s">
-        <v>2255</v>
+        <v>2253</v>
       </c>
       <c r="C766" s="1" t="s">
-        <v>2256</v>
+        <v>2254</v>
       </c>
       <c r="D766" s="1" t="s">
-        <v>2254</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="767" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B767" s="1" t="s">
-        <v>2258</v>
+        <v>2256</v>
       </c>
       <c r="C767" s="1" t="s">
-        <v>2259</v>
+        <v>2257</v>
       </c>
       <c r="D767" s="1" t="s">
-        <v>2257</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="768" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B768" s="1" t="s">
-        <v>2261</v>
+        <v>2259</v>
       </c>
       <c r="C768" s="1" t="s">
-        <v>2262</v>
+        <v>2260</v>
       </c>
       <c r="D768" s="1" t="s">
-        <v>2260</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="769" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B769" s="1" t="s">
-        <v>2264</v>
+        <v>2262</v>
       </c>
       <c r="C769" s="1" t="s">
-        <v>2265</v>
+        <v>2263</v>
       </c>
       <c r="D769" s="1" t="s">
-        <v>2263</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="770" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B770" s="1" t="s">
-        <v>2267</v>
+        <v>2265</v>
       </c>
       <c r="C770" s="1" t="s">
-        <v>2268</v>
+        <v>2266</v>
       </c>
       <c r="D770" s="1" t="s">
-        <v>2266</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="771" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B771" s="1" t="s">
-        <v>2270</v>
+        <v>2268</v>
       </c>
       <c r="C771" s="1" t="s">
-        <v>2271</v>
+        <v>2269</v>
       </c>
       <c r="D771" s="1" t="s">
-        <v>2269</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="772" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B772" s="1" t="s">
+        <v>2270</v>
+      </c>
+      <c r="C772" s="1" t="s">
         <v>2272</v>
       </c>
-      <c r="C772" s="1" t="s">
-        <v>2274</v>
-      </c>
       <c r="D772" s="1" t="s">
-        <v>2273</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="773" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B773" s="1" t="s">
-        <v>2276</v>
+        <v>2273</v>
       </c>
       <c r="C773" s="1" t="s">
-        <v>2278</v>
+        <v>2275</v>
       </c>
       <c r="D773" s="1" t="s">
-        <v>2277</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="774" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B774" s="1" t="s">
-        <v>2275</v>
+        <v>2278</v>
+      </c>
+    </row>
+    <row r="775" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B775" s="1" t="s">
+        <v>2279</v>
+      </c>
+      <c r="C775" s="1" t="s">
+        <v>2280</v>
+      </c>
+      <c r="D775" s="1" t="s">
+        <v>2281</v>
+      </c>
+    </row>
+    <row r="776" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B776" s="1" t="s">
+        <v>2282</v>
+      </c>
+      <c r="C776" s="1" t="s">
+        <v>2284</v>
+      </c>
+      <c r="D776" s="1" t="s">
+        <v>2283</v>
+      </c>
+    </row>
+    <row r="777" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B777" s="1" t="s">
+        <v>2285</v>
+      </c>
+      <c r="C777" s="1" t="s">
+        <v>2286</v>
+      </c>
+      <c r="D777" s="1" t="s">
+        <v>2287</v>
+      </c>
+    </row>
+    <row r="778" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B778" s="1" t="s">
+        <v>2288</v>
+      </c>
+      <c r="C778" s="1" t="s">
+        <v>2306</v>
+      </c>
+      <c r="D778" s="1" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="779" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B779" s="1" t="s">
+        <v>2290</v>
+      </c>
+      <c r="C779" s="1" t="s">
+        <v>2292</v>
+      </c>
+      <c r="D779" s="1" t="s">
+        <v>2291</v>
+      </c>
+    </row>
+    <row r="780" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B780" s="1" t="s">
+        <v>2293</v>
+      </c>
+      <c r="C780" s="1" t="s">
+        <v>2295</v>
+      </c>
+      <c r="D780" s="1" t="s">
+        <v>2294</v>
+      </c>
+    </row>
+    <row r="781" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B781" s="1" t="s">
+        <v>2296</v>
+      </c>
+      <c r="C781" s="1" t="s">
+        <v>2298</v>
+      </c>
+      <c r="D781" s="1" t="s">
+        <v>2297</v>
+      </c>
+    </row>
+    <row r="782" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B782" s="1" t="s">
+        <v>2299</v>
+      </c>
+      <c r="C782" s="1" t="s">
+        <v>2301</v>
+      </c>
+      <c r="D782" s="1" t="s">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="783" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B783" s="1" t="s">
+        <v>2303</v>
+      </c>
+      <c r="C783" s="1" t="s">
+        <v>2307</v>
+      </c>
+      <c r="D783" s="1" t="s">
+        <v>2302</v>
+      </c>
+    </row>
+    <row r="784" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B784" s="1" t="s">
+        <v>2304</v>
+      </c>
+      <c r="C784" s="1" t="s">
+        <v>2305</v>
+      </c>
+      <c r="D784" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="785" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B785" s="1" t="s">
+        <v>2312</v>
+      </c>
+      <c r="C785" s="1" t="s">
+        <v>2311</v>
+      </c>
+      <c r="D785" s="1" t="s">
+        <v>2308</v>
+      </c>
+    </row>
+    <row r="786" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B786" s="1" t="s">
+        <v>2309</v>
+      </c>
+      <c r="C786" s="1" t="s">
+        <v>2310</v>
+      </c>
+      <c r="D786" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="787" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B787" s="1" t="s">
+        <v>2313</v>
+      </c>
+      <c r="C787" s="1" t="s">
+        <v>2315</v>
+      </c>
+      <c r="D787" s="1" t="s">
+        <v>2314</v>
+      </c>
+    </row>
+    <row r="788" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B788" s="1" t="s">
+        <v>2316</v>
+      </c>
+      <c r="C788" s="1" t="s">
+        <v>2318</v>
+      </c>
+      <c r="D788" s="1" t="s">
+        <v>2317</v>
+      </c>
+    </row>
+    <row r="789" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B789" s="1" t="s">
+        <v>2319</v>
+      </c>
+      <c r="C789" s="1" t="s">
+        <v>2321</v>
+      </c>
+      <c r="D789" s="1" t="s">
+        <v>2320</v>
+      </c>
+    </row>
+    <row r="790" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B790" s="1" t="s">
+        <v>2322</v>
+      </c>
+      <c r="C790" s="1" t="s">
+        <v>2324</v>
+      </c>
+      <c r="D790" s="1" t="s">
+        <v>2323</v>
+      </c>
+    </row>
+    <row r="791" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B791" s="1" t="s">
+        <v>2325</v>
+      </c>
+      <c r="C791" s="1" t="s">
+        <v>2327</v>
+      </c>
+      <c r="D791" s="1" t="s">
+        <v>2326</v>
+      </c>
+    </row>
+    <row r="792" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B792" s="1" t="s">
+        <v>2328</v>
+      </c>
+      <c r="C792" s="1" t="s">
+        <v>2330</v>
+      </c>
+      <c r="D792" s="1" t="s">
+        <v>2329</v>
+      </c>
+    </row>
+    <row r="793" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B793" s="1" t="s">
+        <v>2331</v>
+      </c>
+      <c r="C793" s="1" t="s">
+        <v>2333</v>
+      </c>
+      <c r="D793" s="1" t="s">
+        <v>2332</v>
+      </c>
+    </row>
+    <row r="794" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B794" s="1" t="s">
+        <v>2334</v>
+      </c>
+      <c r="C794" s="1" t="s">
+        <v>2336</v>
+      </c>
+      <c r="D794" s="1" t="s">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="795" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B795" s="1" t="s">
+        <v>2337</v>
+      </c>
+      <c r="C795" s="1" t="s">
+        <v>2339</v>
+      </c>
+      <c r="D795" s="1" t="s">
+        <v>2338</v>
+      </c>
+    </row>
+    <row r="796" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B796" s="1" t="s">
+        <v>2340</v>
+      </c>
+      <c r="C796" s="1" t="s">
+        <v>2342</v>
+      </c>
+      <c r="D796" s="1" t="s">
+        <v>2341</v>
+      </c>
+    </row>
+    <row r="797" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B797" s="1" t="s">
+        <v>2343</v>
+      </c>
+      <c r="C797" s="1" t="s">
+        <v>2345</v>
+      </c>
+      <c r="D797" s="1" t="s">
+        <v>2344</v>
+      </c>
+    </row>
+    <row r="798" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B798" s="1" t="s">
+        <v>2346</v>
+      </c>
+      <c r="C798" s="1" t="s">
+        <v>2348</v>
+      </c>
+      <c r="D798" s="1" t="s">
+        <v>2347</v>
+      </c>
+    </row>
+    <row r="799" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B799" s="1" t="s">
+        <v>2349</v>
+      </c>
+      <c r="C799" s="1" t="s">
+        <v>2351</v>
+      </c>
+      <c r="D799" s="1" t="s">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="800" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B800" s="2" t="s">
+        <v>2352</v>
+      </c>
+      <c r="C800" s="1" t="s">
+        <v>2354</v>
+      </c>
+      <c r="D800" s="1" t="s">
+        <v>2353</v>
+      </c>
+    </row>
+    <row r="801" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B801" s="1" t="s">
+        <v>2355</v>
+      </c>
+      <c r="C801" s="1" t="s">
+        <v>2357</v>
+      </c>
+      <c r="D801" s="1" t="s">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="802" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B802" s="1" t="s">
+        <v>2358</v>
+      </c>
+      <c r="C802" s="1" t="s">
+        <v>2365</v>
+      </c>
+      <c r="D802" s="1" t="s">
+        <v>2359</v>
+      </c>
+    </row>
+    <row r="803" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B803" s="1" t="s">
+        <v>2360</v>
+      </c>
+      <c r="C803" s="1" t="s">
+        <v>2362</v>
+      </c>
+      <c r="D803" s="1" t="s">
+        <v>2361</v>
+      </c>
+    </row>
+    <row r="804" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B804" s="1" t="s">
+        <v>2363</v>
+      </c>
+      <c r="C804" s="1" t="s">
+        <v>2366</v>
+      </c>
+      <c r="D804" s="1" t="s">
+        <v>2364</v>
+      </c>
+    </row>
+    <row r="805" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B805" s="1" t="s">
+        <v>2369</v>
+      </c>
+      <c r="C805" s="1" t="s">
+        <v>2368</v>
+      </c>
+      <c r="D805" s="1" t="s">
+        <v>2367</v>
+      </c>
+    </row>
+    <row r="806" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B806" s="1" t="s">
+        <v>2370</v>
+      </c>
+      <c r="C806" s="1" t="s">
+        <v>2372</v>
+      </c>
+      <c r="D806" s="1" t="s">
+        <v>2371</v>
+      </c>
+    </row>
+    <row r="807" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B807" s="1" t="s">
+        <v>2373</v>
+      </c>
+      <c r="C807" s="1" t="s">
+        <v>2375</v>
+      </c>
+      <c r="D807" s="1" t="s">
+        <v>2374</v>
+      </c>
+    </row>
+    <row r="808" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B808" s="1" t="s">
+        <v>2376</v>
+      </c>
+      <c r="C808" s="1" t="s">
+        <v>2378</v>
+      </c>
+      <c r="D808" s="1" t="s">
+        <v>2377</v>
+      </c>
+    </row>
+    <row r="809" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B809" s="1" t="s">
+        <v>2381</v>
+      </c>
+      <c r="C809" s="1" t="s">
+        <v>2380</v>
+      </c>
+      <c r="D809" s="1" t="s">
+        <v>2379</v>
+      </c>
+    </row>
+    <row r="810" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B810" s="1" t="s">
+        <v>2383</v>
+      </c>
+      <c r="C810" s="1" t="s">
+        <v>2382</v>
+      </c>
+      <c r="D810" s="1" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="811" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B811" s="1" t="s">
+        <v>2385</v>
+      </c>
+      <c r="C811" s="1" t="s">
+        <v>2387</v>
+      </c>
+      <c r="D811" s="1" t="s">
+        <v>2386</v>
+      </c>
+    </row>
+    <row r="812" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B812" s="1" t="s">
+        <v>2388</v>
+      </c>
+      <c r="C812" s="1" t="s">
+        <v>2390</v>
+      </c>
+      <c r="D812" s="1" t="s">
+        <v>2389</v>
+      </c>
+    </row>
+    <row r="813" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B813" s="1" t="s">
+        <v>2391</v>
+      </c>
+      <c r="C813" s="1" t="s">
+        <v>2393</v>
+      </c>
+      <c r="D813" s="1" t="s">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="814" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B814" s="1" t="s">
+        <v>2394</v>
+      </c>
+      <c r="C814" s="1" t="s">
+        <v>2396</v>
+      </c>
+      <c r="D814" s="1" t="s">
+        <v>2395</v>
+      </c>
+    </row>
+    <row r="815" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B815" s="1" t="s">
+        <v>2397</v>
+      </c>
+      <c r="C815" s="1" t="s">
+        <v>2398</v>
+      </c>
+      <c r="D815" s="1" t="s">
+        <v>2399</v>
+      </c>
+    </row>
+    <row r="816" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B816" s="1" t="s">
+        <v>2400</v>
+      </c>
+      <c r="C816" s="1" t="s">
+        <v>2402</v>
+      </c>
+      <c r="D816" s="1" t="s">
+        <v>2401</v>
+      </c>
+    </row>
+    <row r="817" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B817" s="1" t="s">
+        <v>2403</v>
+      </c>
+      <c r="C817" s="1" t="s">
+        <v>2404</v>
+      </c>
+      <c r="D817" s="1" t="s">
+        <v>2405</v>
+      </c>
+    </row>
+    <row r="818" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B818" s="1" t="s">
+        <v>2406</v>
+      </c>
+      <c r="C818" s="1" t="s">
+        <v>2407</v>
+      </c>
+      <c r="D818" s="1" t="s">
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="819" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B819" s="1" t="s">
+        <v>2409</v>
+      </c>
+      <c r="C819" s="1" t="s">
+        <v>2411</v>
+      </c>
+      <c r="D819" s="1" t="s">
+        <v>2410</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B108">
-    <cfRule type="duplicateValues" dxfId="1689" priority="2507"/>
+    <cfRule type="duplicateValues" dxfId="1666" priority="2507"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B125">
-    <cfRule type="duplicateValues" dxfId="1688" priority="2506"/>
+    <cfRule type="duplicateValues" dxfId="1665" priority="2506"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B132">
-    <cfRule type="duplicateValues" dxfId="1687" priority="2505"/>
+    <cfRule type="duplicateValues" dxfId="1664" priority="2505"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B128">
-    <cfRule type="duplicateValues" dxfId="1686" priority="2504"/>
+    <cfRule type="duplicateValues" dxfId="1663" priority="2504"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B129">
-    <cfRule type="duplicateValues" dxfId="1685" priority="2503"/>
+    <cfRule type="duplicateValues" dxfId="1662" priority="2503"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B130">
-    <cfRule type="duplicateValues" dxfId="1684" priority="2502"/>
+    <cfRule type="duplicateValues" dxfId="1661" priority="2502"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B133">
-    <cfRule type="duplicateValues" dxfId="1683" priority="2501"/>
+    <cfRule type="duplicateValues" dxfId="1660" priority="2501"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B135">
-    <cfRule type="duplicateValues" dxfId="1682" priority="2500"/>
+    <cfRule type="duplicateValues" dxfId="1659" priority="2500"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B136">
-    <cfRule type="duplicateValues" dxfId="1681" priority="2499"/>
+    <cfRule type="duplicateValues" dxfId="1658" priority="2499"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B138">
-    <cfRule type="duplicateValues" dxfId="1680" priority="2498"/>
+    <cfRule type="duplicateValues" dxfId="1657" priority="2498"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B139">
-    <cfRule type="duplicateValues" dxfId="1679" priority="2497"/>
+    <cfRule type="duplicateValues" dxfId="1656" priority="2497"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B140">
-    <cfRule type="duplicateValues" dxfId="1678" priority="2496"/>
+    <cfRule type="duplicateValues" dxfId="1655" priority="2496"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B141">
-    <cfRule type="duplicateValues" dxfId="1677" priority="2495"/>
+    <cfRule type="duplicateValues" dxfId="1654" priority="2495"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B142">
-    <cfRule type="duplicateValues" dxfId="1676" priority="2494"/>
+    <cfRule type="duplicateValues" dxfId="1653" priority="2494"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B148">
-    <cfRule type="duplicateValues" dxfId="1675" priority="2493"/>
+    <cfRule type="duplicateValues" dxfId="1652" priority="2493"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B149">
-    <cfRule type="duplicateValues" dxfId="1674" priority="2492"/>
+    <cfRule type="duplicateValues" dxfId="1651" priority="2492"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B154">
-    <cfRule type="duplicateValues" dxfId="1673" priority="2490"/>
+    <cfRule type="duplicateValues" dxfId="1650" priority="2490"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B155">
-    <cfRule type="duplicateValues" dxfId="1672" priority="2489"/>
+    <cfRule type="duplicateValues" dxfId="1649" priority="2489"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B157">
-    <cfRule type="duplicateValues" dxfId="1671" priority="2487"/>
+    <cfRule type="duplicateValues" dxfId="1648" priority="2487"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B161">
-    <cfRule type="duplicateValues" dxfId="1670" priority="2486"/>
+    <cfRule type="duplicateValues" dxfId="1647" priority="2486"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B162">
-    <cfRule type="duplicateValues" dxfId="1669" priority="2485"/>
+    <cfRule type="duplicateValues" dxfId="1646" priority="2485"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B163">
-    <cfRule type="duplicateValues" dxfId="1668" priority="2484"/>
+    <cfRule type="duplicateValues" dxfId="1645" priority="2484"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B164">
-    <cfRule type="duplicateValues" dxfId="1667" priority="2483"/>
+    <cfRule type="duplicateValues" dxfId="1644" priority="2483"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B166">
-    <cfRule type="duplicateValues" dxfId="1666" priority="2481"/>
+    <cfRule type="duplicateValues" dxfId="1643" priority="2481"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B167">
-    <cfRule type="duplicateValues" dxfId="1665" priority="2480"/>
+    <cfRule type="duplicateValues" dxfId="1642" priority="2480"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B170">
-    <cfRule type="duplicateValues" dxfId="1664" priority="2479"/>
+    <cfRule type="duplicateValues" dxfId="1641" priority="2479"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B179">
-    <cfRule type="duplicateValues" dxfId="1663" priority="2473"/>
+    <cfRule type="duplicateValues" dxfId="1640" priority="2473"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B186">
-    <cfRule type="duplicateValues" dxfId="1662" priority="2472"/>
+    <cfRule type="duplicateValues" dxfId="1639" priority="2472"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B187">
-    <cfRule type="duplicateValues" dxfId="1661" priority="2471"/>
+    <cfRule type="duplicateValues" dxfId="1638" priority="2471"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B191">
-    <cfRule type="duplicateValues" dxfId="1660" priority="2469"/>
+    <cfRule type="duplicateValues" dxfId="1637" priority="2469"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B192">
-    <cfRule type="duplicateValues" dxfId="1659" priority="2468"/>
+    <cfRule type="duplicateValues" dxfId="1636" priority="2468"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B193">
-    <cfRule type="duplicateValues" dxfId="1658" priority="2467"/>
+    <cfRule type="duplicateValues" dxfId="1635" priority="2467"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B194">
-    <cfRule type="duplicateValues" dxfId="1657" priority="2466"/>
+    <cfRule type="duplicateValues" dxfId="1634" priority="2466"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B196">
-    <cfRule type="duplicateValues" dxfId="1656" priority="2465"/>
+    <cfRule type="duplicateValues" dxfId="1633" priority="2465"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B197">
-    <cfRule type="duplicateValues" dxfId="1655" priority="2464"/>
+    <cfRule type="duplicateValues" dxfId="1632" priority="2464"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B198">
-    <cfRule type="duplicateValues" dxfId="1654" priority="2463"/>
+    <cfRule type="duplicateValues" dxfId="1631" priority="2463"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B200">
-    <cfRule type="duplicateValues" dxfId="1653" priority="2462"/>
+    <cfRule type="duplicateValues" dxfId="1630" priority="2462"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B201">
-    <cfRule type="duplicateValues" dxfId="1652" priority="2461"/>
+    <cfRule type="duplicateValues" dxfId="1629" priority="2461"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B202">
-    <cfRule type="duplicateValues" dxfId="1651" priority="2460"/>
+    <cfRule type="duplicateValues" dxfId="1628" priority="2460"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B204">
-    <cfRule type="duplicateValues" dxfId="1650" priority="2459"/>
+    <cfRule type="duplicateValues" dxfId="1627" priority="2459"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B205">
-    <cfRule type="duplicateValues" dxfId="1649" priority="2458"/>
+    <cfRule type="duplicateValues" dxfId="1626" priority="2458"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B209">
-    <cfRule type="duplicateValues" dxfId="1648" priority="2454"/>
+    <cfRule type="duplicateValues" dxfId="1625" priority="2454"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B210">
-    <cfRule type="duplicateValues" dxfId="1647" priority="2453"/>
+    <cfRule type="duplicateValues" dxfId="1624" priority="2453"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B211">
-    <cfRule type="duplicateValues" dxfId="1646" priority="2452"/>
+    <cfRule type="duplicateValues" dxfId="1623" priority="2452"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B214">
-    <cfRule type="duplicateValues" dxfId="1645" priority="2451"/>
+    <cfRule type="duplicateValues" dxfId="1622" priority="2451"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B216">
-    <cfRule type="duplicateValues" dxfId="1644" priority="2449"/>
+    <cfRule type="duplicateValues" dxfId="1621" priority="2449"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B217">
-    <cfRule type="duplicateValues" dxfId="1643" priority="2448"/>
+    <cfRule type="duplicateValues" dxfId="1620" priority="2448"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B219">
-    <cfRule type="duplicateValues" dxfId="1642" priority="2447"/>
+    <cfRule type="duplicateValues" dxfId="1619" priority="2447"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B220">
-    <cfRule type="duplicateValues" dxfId="1641" priority="2446"/>
+    <cfRule type="duplicateValues" dxfId="1618" priority="2446"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B225">
-    <cfRule type="duplicateValues" dxfId="1640" priority="2444"/>
+    <cfRule type="duplicateValues" dxfId="1617" priority="2444"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B226">
-    <cfRule type="duplicateValues" dxfId="1639" priority="2443"/>
+    <cfRule type="duplicateValues" dxfId="1616" priority="2443"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B227">
-    <cfRule type="duplicateValues" dxfId="1638" priority="2442"/>
+    <cfRule type="duplicateValues" dxfId="1615" priority="2442"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B228">
-    <cfRule type="duplicateValues" dxfId="1637" priority="2441"/>
+    <cfRule type="duplicateValues" dxfId="1614" priority="2441"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B237">
-    <cfRule type="duplicateValues" dxfId="1636" priority="2431"/>
+    <cfRule type="duplicateValues" dxfId="1613" priority="2431"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B237">
-    <cfRule type="duplicateValues" dxfId="1635" priority="2430"/>
+    <cfRule type="duplicateValues" dxfId="1612" priority="2430"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B238">
-    <cfRule type="duplicateValues" dxfId="1634" priority="2429"/>
+    <cfRule type="duplicateValues" dxfId="1611" priority="2429"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B238">
-    <cfRule type="duplicateValues" dxfId="1633" priority="2428"/>
+    <cfRule type="duplicateValues" dxfId="1610" priority="2428"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B241">
-    <cfRule type="duplicateValues" dxfId="1632" priority="2427"/>
+    <cfRule type="duplicateValues" dxfId="1609" priority="2427"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B241">
-    <cfRule type="duplicateValues" dxfId="1631" priority="2426"/>
+    <cfRule type="duplicateValues" dxfId="1608" priority="2426"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B245">
-    <cfRule type="duplicateValues" dxfId="1630" priority="2425"/>
+    <cfRule type="duplicateValues" dxfId="1607" priority="2425"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B245">
-    <cfRule type="duplicateValues" dxfId="1629" priority="2424"/>
+    <cfRule type="duplicateValues" dxfId="1606" priority="2424"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B246">
-    <cfRule type="duplicateValues" dxfId="1628" priority="2423"/>
+    <cfRule type="duplicateValues" dxfId="1605" priority="2423"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B246">
-    <cfRule type="duplicateValues" dxfId="1627" priority="2422"/>
+    <cfRule type="duplicateValues" dxfId="1604" priority="2422"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B247">
-    <cfRule type="duplicateValues" dxfId="1626" priority="2421"/>
+    <cfRule type="duplicateValues" dxfId="1603" priority="2421"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B247">
-    <cfRule type="duplicateValues" dxfId="1625" priority="2420"/>
+    <cfRule type="duplicateValues" dxfId="1602" priority="2420"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B248">
-    <cfRule type="duplicateValues" dxfId="1624" priority="2419"/>
+    <cfRule type="duplicateValues" dxfId="1601" priority="2419"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B248">
-    <cfRule type="duplicateValues" dxfId="1623" priority="2418"/>
+    <cfRule type="duplicateValues" dxfId="1600" priority="2418"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B249">
-    <cfRule type="duplicateValues" dxfId="1622" priority="2417"/>
+    <cfRule type="duplicateValues" dxfId="1599" priority="2417"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B249">
-    <cfRule type="duplicateValues" dxfId="1621" priority="2416"/>
+    <cfRule type="duplicateValues" dxfId="1598" priority="2416"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B252">
-    <cfRule type="duplicateValues" dxfId="1620" priority="2411"/>
+    <cfRule type="duplicateValues" dxfId="1597" priority="2411"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B252">
-    <cfRule type="duplicateValues" dxfId="1619" priority="2410"/>
+    <cfRule type="duplicateValues" dxfId="1596" priority="2410"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B255">
-    <cfRule type="duplicateValues" dxfId="1618" priority="2407"/>
+    <cfRule type="duplicateValues" dxfId="1595" priority="2407"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B255">
-    <cfRule type="duplicateValues" dxfId="1617" priority="2406"/>
+    <cfRule type="duplicateValues" dxfId="1594" priority="2406"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B263">
-    <cfRule type="duplicateValues" dxfId="1616" priority="2403"/>
+    <cfRule type="duplicateValues" dxfId="1593" priority="2403"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B263">
-    <cfRule type="duplicateValues" dxfId="1615" priority="2402"/>
+    <cfRule type="duplicateValues" dxfId="1592" priority="2402"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B271">
-    <cfRule type="duplicateValues" dxfId="1614" priority="2399"/>
+    <cfRule type="duplicateValues" dxfId="1591" priority="2399"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B271">
-    <cfRule type="duplicateValues" dxfId="1613" priority="2398"/>
+    <cfRule type="duplicateValues" dxfId="1590" priority="2398"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B274">
-    <cfRule type="duplicateValues" dxfId="1612" priority="2395"/>
+    <cfRule type="duplicateValues" dxfId="1589" priority="2395"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B274">
-    <cfRule type="duplicateValues" dxfId="1611" priority="2394"/>
+    <cfRule type="duplicateValues" dxfId="1588" priority="2394"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B275">
-    <cfRule type="duplicateValues" dxfId="1610" priority="2393"/>
+    <cfRule type="duplicateValues" dxfId="1587" priority="2393"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B275">
-    <cfRule type="duplicateValues" dxfId="1609" priority="2392"/>
+    <cfRule type="duplicateValues" dxfId="1586" priority="2392"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B276">
-    <cfRule type="duplicateValues" dxfId="1608" priority="2391"/>
+    <cfRule type="duplicateValues" dxfId="1585" priority="2391"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B276">
-    <cfRule type="duplicateValues" dxfId="1607" priority="2390"/>
+    <cfRule type="duplicateValues" dxfId="1584" priority="2390"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B277">
-    <cfRule type="duplicateValues" dxfId="1606" priority="2387"/>
+    <cfRule type="duplicateValues" dxfId="1583" priority="2387"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B277">
-    <cfRule type="duplicateValues" dxfId="1605" priority="2386"/>
+    <cfRule type="duplicateValues" dxfId="1582" priority="2386"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B279">
-    <cfRule type="duplicateValues" dxfId="1604" priority="2385"/>
+    <cfRule type="duplicateValues" dxfId="1581" priority="2385"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B279">
-    <cfRule type="duplicateValues" dxfId="1603" priority="2384"/>
+    <cfRule type="duplicateValues" dxfId="1580" priority="2384"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B281">
-    <cfRule type="duplicateValues" dxfId="1602" priority="2379"/>
+    <cfRule type="duplicateValues" dxfId="1579" priority="2379"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B281">
-    <cfRule type="duplicateValues" dxfId="1601" priority="2378"/>
+    <cfRule type="duplicateValues" dxfId="1578" priority="2378"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B282">
-    <cfRule type="duplicateValues" dxfId="1600" priority="2377"/>
+    <cfRule type="duplicateValues" dxfId="1577" priority="2377"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B282">
-    <cfRule type="duplicateValues" dxfId="1599" priority="2376"/>
+    <cfRule type="duplicateValues" dxfId="1576" priority="2376"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B283">
-    <cfRule type="duplicateValues" dxfId="1598" priority="2375"/>
+    <cfRule type="duplicateValues" dxfId="1575" priority="2375"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B283">
-    <cfRule type="duplicateValues" dxfId="1597" priority="2374"/>
+    <cfRule type="duplicateValues" dxfId="1574" priority="2374"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B286">
-    <cfRule type="duplicateValues" dxfId="1596" priority="2369"/>
+    <cfRule type="duplicateValues" dxfId="1573" priority="2369"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B287">
-    <cfRule type="duplicateValues" dxfId="1595" priority="2366"/>
+    <cfRule type="duplicateValues" dxfId="1572" priority="2366"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B287">
-    <cfRule type="duplicateValues" dxfId="1594" priority="2365"/>
+    <cfRule type="duplicateValues" dxfId="1571" priority="2365"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B290">
-    <cfRule type="duplicateValues" dxfId="1593" priority="2364"/>
+    <cfRule type="duplicateValues" dxfId="1570" priority="2364"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B290">
-    <cfRule type="duplicateValues" dxfId="1592" priority="2363"/>
+    <cfRule type="duplicateValues" dxfId="1569" priority="2363"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B292">
-    <cfRule type="duplicateValues" dxfId="1591" priority="2362"/>
+    <cfRule type="duplicateValues" dxfId="1568" priority="2362"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B292">
-    <cfRule type="duplicateValues" dxfId="1590" priority="2361"/>
+    <cfRule type="duplicateValues" dxfId="1567" priority="2361"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B293">
-    <cfRule type="duplicateValues" dxfId="1589" priority="2358"/>
+    <cfRule type="duplicateValues" dxfId="1566" priority="2358"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B293">
-    <cfRule type="duplicateValues" dxfId="1588" priority="2357"/>
+    <cfRule type="duplicateValues" dxfId="1565" priority="2357"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B294">
-    <cfRule type="duplicateValues" dxfId="1587" priority="2356"/>
+    <cfRule type="duplicateValues" dxfId="1564" priority="2356"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B294">
-    <cfRule type="duplicateValues" dxfId="1586" priority="2355"/>
+    <cfRule type="duplicateValues" dxfId="1563" priority="2355"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B300">
-    <cfRule type="duplicateValues" dxfId="1585" priority="2354"/>
+    <cfRule type="duplicateValues" dxfId="1562" priority="2354"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B300">
-    <cfRule type="duplicateValues" dxfId="1584" priority="2353"/>
+    <cfRule type="duplicateValues" dxfId="1561" priority="2353"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B301">
-    <cfRule type="duplicateValues" dxfId="1583" priority="2352"/>
+    <cfRule type="duplicateValues" dxfId="1560" priority="2352"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B301">
-    <cfRule type="duplicateValues" dxfId="1582" priority="2351"/>
+    <cfRule type="duplicateValues" dxfId="1559" priority="2351"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B302">
-    <cfRule type="duplicateValues" dxfId="1581" priority="2348"/>
+    <cfRule type="duplicateValues" dxfId="1558" priority="2348"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B302">
-    <cfRule type="duplicateValues" dxfId="1580" priority="2347"/>
+    <cfRule type="duplicateValues" dxfId="1557" priority="2347"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B303">
-    <cfRule type="duplicateValues" dxfId="1579" priority="2346"/>
+    <cfRule type="duplicateValues" dxfId="1556" priority="2346"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B303">
-    <cfRule type="duplicateValues" dxfId="1578" priority="2345"/>
+    <cfRule type="duplicateValues" dxfId="1555" priority="2345"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B304">
-    <cfRule type="duplicateValues" dxfId="1577" priority="2344"/>
+    <cfRule type="duplicateValues" dxfId="1554" priority="2344"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B304">
-    <cfRule type="duplicateValues" dxfId="1576" priority="2343"/>
+    <cfRule type="duplicateValues" dxfId="1553" priority="2343"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B305">
-    <cfRule type="duplicateValues" dxfId="1575" priority="2342"/>
+    <cfRule type="duplicateValues" dxfId="1552" priority="2342"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B305">
-    <cfRule type="duplicateValues" dxfId="1574" priority="2341"/>
+    <cfRule type="duplicateValues" dxfId="1551" priority="2341"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B308">
-    <cfRule type="duplicateValues" dxfId="1573" priority="2337"/>
+    <cfRule type="duplicateValues" dxfId="1550" priority="2337"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B308">
-    <cfRule type="duplicateValues" dxfId="1572" priority="2336"/>
+    <cfRule type="duplicateValues" dxfId="1549" priority="2336"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B309">
-    <cfRule type="duplicateValues" dxfId="1571" priority="2335"/>
+    <cfRule type="duplicateValues" dxfId="1548" priority="2335"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B309">
-    <cfRule type="duplicateValues" dxfId="1570" priority="2334"/>
+    <cfRule type="duplicateValues" dxfId="1547" priority="2334"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B310">
-    <cfRule type="duplicateValues" dxfId="1569" priority="2333"/>
+    <cfRule type="duplicateValues" dxfId="1546" priority="2333"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B310">
-    <cfRule type="duplicateValues" dxfId="1568" priority="2332"/>
+    <cfRule type="duplicateValues" dxfId="1545" priority="2332"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B312">
-    <cfRule type="duplicateValues" dxfId="1567" priority="2327"/>
+    <cfRule type="duplicateValues" dxfId="1544" priority="2327"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B312">
-    <cfRule type="duplicateValues" dxfId="1566" priority="2326"/>
+    <cfRule type="duplicateValues" dxfId="1543" priority="2326"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B315">
-    <cfRule type="duplicateValues" dxfId="1565" priority="2319"/>
+    <cfRule type="duplicateValues" dxfId="1542" priority="2319"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B315">
-    <cfRule type="duplicateValues" dxfId="1564" priority="2318"/>
+    <cfRule type="duplicateValues" dxfId="1541" priority="2318"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B317">
-    <cfRule type="duplicateValues" dxfId="1563" priority="2311"/>
+    <cfRule type="duplicateValues" dxfId="1540" priority="2311"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B317">
-    <cfRule type="duplicateValues" dxfId="1562" priority="2310"/>
+    <cfRule type="duplicateValues" dxfId="1539" priority="2310"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B318">
-    <cfRule type="duplicateValues" dxfId="1561" priority="2309"/>
+    <cfRule type="duplicateValues" dxfId="1538" priority="2309"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B318">
-    <cfRule type="duplicateValues" dxfId="1560" priority="2308"/>
+    <cfRule type="duplicateValues" dxfId="1537" priority="2308"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B320">
-    <cfRule type="duplicateValues" dxfId="1559" priority="2301"/>
+    <cfRule type="duplicateValues" dxfId="1536" priority="2301"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B320">
-    <cfRule type="duplicateValues" dxfId="1558" priority="2300"/>
+    <cfRule type="duplicateValues" dxfId="1535" priority="2300"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B321">
-    <cfRule type="duplicateValues" dxfId="1557" priority="2299"/>
+    <cfRule type="duplicateValues" dxfId="1534" priority="2299"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B321">
-    <cfRule type="duplicateValues" dxfId="1556" priority="2298"/>
+    <cfRule type="duplicateValues" dxfId="1533" priority="2298"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B329">
-    <cfRule type="duplicateValues" dxfId="1555" priority="2279"/>
+    <cfRule type="duplicateValues" dxfId="1532" priority="2279"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B329">
-    <cfRule type="duplicateValues" dxfId="1554" priority="2278"/>
+    <cfRule type="duplicateValues" dxfId="1531" priority="2278"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B330">
-    <cfRule type="duplicateValues" dxfId="1553" priority="2275"/>
+    <cfRule type="duplicateValues" dxfId="1530" priority="2275"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B330">
-    <cfRule type="duplicateValues" dxfId="1552" priority="2274"/>
+    <cfRule type="duplicateValues" dxfId="1529" priority="2274"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B332">
-    <cfRule type="duplicateValues" dxfId="1551" priority="2273"/>
+    <cfRule type="duplicateValues" dxfId="1528" priority="2273"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B332">
-    <cfRule type="duplicateValues" dxfId="1550" priority="2272"/>
+    <cfRule type="duplicateValues" dxfId="1527" priority="2272"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B334">
-    <cfRule type="duplicateValues" dxfId="1549" priority="2271"/>
+    <cfRule type="duplicateValues" dxfId="1526" priority="2271"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B334">
-    <cfRule type="duplicateValues" dxfId="1548" priority="2270"/>
+    <cfRule type="duplicateValues" dxfId="1525" priority="2270"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B335">
-    <cfRule type="duplicateValues" dxfId="1547" priority="2269"/>
+    <cfRule type="duplicateValues" dxfId="1524" priority="2269"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B335">
-    <cfRule type="duplicateValues" dxfId="1546" priority="2268"/>
+    <cfRule type="duplicateValues" dxfId="1523" priority="2268"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B336">
-    <cfRule type="duplicateValues" dxfId="1545" priority="2265"/>
+    <cfRule type="duplicateValues" dxfId="1522" priority="2265"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B336">
-    <cfRule type="duplicateValues" dxfId="1544" priority="2264"/>
+    <cfRule type="duplicateValues" dxfId="1521" priority="2264"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B339">
-    <cfRule type="duplicateValues" dxfId="1543" priority="2263"/>
+    <cfRule type="duplicateValues" dxfId="1520" priority="2263"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B339">
-    <cfRule type="duplicateValues" dxfId="1542" priority="2262"/>
+    <cfRule type="duplicateValues" dxfId="1519" priority="2262"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B342">
-    <cfRule type="duplicateValues" dxfId="1541" priority="2259"/>
+    <cfRule type="duplicateValues" dxfId="1518" priority="2259"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B342">
-    <cfRule type="duplicateValues" dxfId="1540" priority="2258"/>
+    <cfRule type="duplicateValues" dxfId="1517" priority="2258"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B344">
-    <cfRule type="duplicateValues" dxfId="1539" priority="2253"/>
+    <cfRule type="duplicateValues" dxfId="1516" priority="2253"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B344">
-    <cfRule type="duplicateValues" dxfId="1538" priority="2252"/>
+    <cfRule type="duplicateValues" dxfId="1515" priority="2252"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B347">
-    <cfRule type="duplicateValues" dxfId="1537" priority="2251"/>
+    <cfRule type="duplicateValues" dxfId="1514" priority="2251"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B347">
-    <cfRule type="duplicateValues" dxfId="1536" priority="2250"/>
+    <cfRule type="duplicateValues" dxfId="1513" priority="2250"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B349">
-    <cfRule type="duplicateValues" dxfId="1535" priority="2249"/>
+    <cfRule type="duplicateValues" dxfId="1512" priority="2249"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B349">
-    <cfRule type="duplicateValues" dxfId="1534" priority="2248"/>
+    <cfRule type="duplicateValues" dxfId="1511" priority="2248"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B350">
-    <cfRule type="duplicateValues" dxfId="1533" priority="2245"/>
+    <cfRule type="duplicateValues" dxfId="1510" priority="2245"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B350">
-    <cfRule type="duplicateValues" dxfId="1532" priority="2244"/>
+    <cfRule type="duplicateValues" dxfId="1509" priority="2244"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B352">
-    <cfRule type="duplicateValues" dxfId="1531" priority="2241"/>
+    <cfRule type="duplicateValues" dxfId="1508" priority="2241"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B352">
-    <cfRule type="duplicateValues" dxfId="1530" priority="2240"/>
+    <cfRule type="duplicateValues" dxfId="1507" priority="2240"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B353">
-    <cfRule type="duplicateValues" dxfId="1529" priority="2237"/>
+    <cfRule type="duplicateValues" dxfId="1506" priority="2237"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B353">
-    <cfRule type="duplicateValues" dxfId="1528" priority="2236"/>
+    <cfRule type="duplicateValues" dxfId="1505" priority="2236"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B355">
-    <cfRule type="duplicateValues" dxfId="1527" priority="2233"/>
+    <cfRule type="duplicateValues" dxfId="1504" priority="2233"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B355">
-    <cfRule type="duplicateValues" dxfId="1526" priority="2232"/>
+    <cfRule type="duplicateValues" dxfId="1503" priority="2232"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B356">
-    <cfRule type="duplicateValues" dxfId="1525" priority="2231"/>
+    <cfRule type="duplicateValues" dxfId="1502" priority="2231"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B356">
-    <cfRule type="duplicateValues" dxfId="1524" priority="2230"/>
+    <cfRule type="duplicateValues" dxfId="1501" priority="2230"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B357">
-    <cfRule type="duplicateValues" dxfId="1523" priority="2229"/>
+    <cfRule type="duplicateValues" dxfId="1500" priority="2229"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B357">
-    <cfRule type="duplicateValues" dxfId="1522" priority="2228"/>
+    <cfRule type="duplicateValues" dxfId="1499" priority="2228"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B358">
-    <cfRule type="duplicateValues" dxfId="1521" priority="2225"/>
+    <cfRule type="duplicateValues" dxfId="1498" priority="2225"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B358">
-    <cfRule type="duplicateValues" dxfId="1520" priority="2224"/>
+    <cfRule type="duplicateValues" dxfId="1497" priority="2224"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B359">
-    <cfRule type="duplicateValues" dxfId="1519" priority="2223"/>
+    <cfRule type="duplicateValues" dxfId="1496" priority="2223"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B359">
-    <cfRule type="duplicateValues" dxfId="1518" priority="2222"/>
+    <cfRule type="duplicateValues" dxfId="1495" priority="2222"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B360">
-    <cfRule type="duplicateValues" dxfId="1517" priority="2221"/>
+    <cfRule type="duplicateValues" dxfId="1494" priority="2221"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B360">
-    <cfRule type="duplicateValues" dxfId="1516" priority="2220"/>
+    <cfRule type="duplicateValues" dxfId="1493" priority="2220"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B361">
-    <cfRule type="duplicateValues" dxfId="1515" priority="2219"/>
+    <cfRule type="duplicateValues" dxfId="1492" priority="2219"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B361">
-    <cfRule type="duplicateValues" dxfId="1514" priority="2218"/>
+    <cfRule type="duplicateValues" dxfId="1491" priority="2218"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B363">
-    <cfRule type="duplicateValues" dxfId="1513" priority="2215"/>
+    <cfRule type="duplicateValues" dxfId="1490" priority="2215"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B363">
-    <cfRule type="duplicateValues" dxfId="1512" priority="2214"/>
+    <cfRule type="duplicateValues" dxfId="1489" priority="2214"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B365">
-    <cfRule type="duplicateValues" dxfId="1511" priority="2209"/>
+    <cfRule type="duplicateValues" dxfId="1488" priority="2209"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B365">
-    <cfRule type="duplicateValues" dxfId="1510" priority="2208"/>
+    <cfRule type="duplicateValues" dxfId="1487" priority="2208"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B366">
-    <cfRule type="duplicateValues" dxfId="1509" priority="2205"/>
+    <cfRule type="duplicateValues" dxfId="1486" priority="2205"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B366">
-    <cfRule type="duplicateValues" dxfId="1508" priority="2204"/>
+    <cfRule type="duplicateValues" dxfId="1485" priority="2204"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B367">
-    <cfRule type="duplicateValues" dxfId="1507" priority="2201"/>
+    <cfRule type="duplicateValues" dxfId="1484" priority="2201"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B367">
-    <cfRule type="duplicateValues" dxfId="1506" priority="2200"/>
+    <cfRule type="duplicateValues" dxfId="1483" priority="2200"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B368">
-    <cfRule type="duplicateValues" dxfId="1505" priority="2199"/>
+    <cfRule type="duplicateValues" dxfId="1482" priority="2199"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B368">
-    <cfRule type="duplicateValues" dxfId="1504" priority="2198"/>
+    <cfRule type="duplicateValues" dxfId="1481" priority="2198"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B370">
-    <cfRule type="duplicateValues" dxfId="1503" priority="2193"/>
+    <cfRule type="duplicateValues" dxfId="1480" priority="2193"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B370">
-    <cfRule type="duplicateValues" dxfId="1502" priority="2192"/>
+    <cfRule type="duplicateValues" dxfId="1479" priority="2192"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B371">
-    <cfRule type="duplicateValues" dxfId="1501" priority="2191"/>
+    <cfRule type="duplicateValues" dxfId="1478" priority="2191"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B371">
-    <cfRule type="duplicateValues" dxfId="1500" priority="2190"/>
+    <cfRule type="duplicateValues" dxfId="1477" priority="2190"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B374">
-    <cfRule type="duplicateValues" dxfId="1499" priority="2185"/>
+    <cfRule type="duplicateValues" dxfId="1476" priority="2185"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B374">
-    <cfRule type="duplicateValues" dxfId="1498" priority="2184"/>
+    <cfRule type="duplicateValues" dxfId="1475" priority="2184"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B375">
-    <cfRule type="duplicateValues" dxfId="1497" priority="2183"/>
+    <cfRule type="duplicateValues" dxfId="1474" priority="2183"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B375">
-    <cfRule type="duplicateValues" dxfId="1496" priority="2182"/>
+    <cfRule type="duplicateValues" dxfId="1473" priority="2182"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B376">
-    <cfRule type="duplicateValues" dxfId="1495" priority="2179"/>
+    <cfRule type="duplicateValues" dxfId="1472" priority="2179"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B376">
-    <cfRule type="duplicateValues" dxfId="1494" priority="2178"/>
+    <cfRule type="duplicateValues" dxfId="1471" priority="2178"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B377">
-    <cfRule type="duplicateValues" dxfId="1493" priority="2175"/>
+    <cfRule type="duplicateValues" dxfId="1470" priority="2175"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B377">
-    <cfRule type="duplicateValues" dxfId="1492" priority="2174"/>
+    <cfRule type="duplicateValues" dxfId="1469" priority="2174"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B381">
-    <cfRule type="duplicateValues" dxfId="1491" priority="2173"/>
+    <cfRule type="duplicateValues" dxfId="1468" priority="2173"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B381">
-    <cfRule type="duplicateValues" dxfId="1490" priority="2172"/>
+    <cfRule type="duplicateValues" dxfId="1467" priority="2172"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B382">
-    <cfRule type="duplicateValues" dxfId="1489" priority="2169"/>
+    <cfRule type="duplicateValues" dxfId="1466" priority="2169"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B382">
-    <cfRule type="duplicateValues" dxfId="1488" priority="2168"/>
+    <cfRule type="duplicateValues" dxfId="1465" priority="2168"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B383">
-    <cfRule type="duplicateValues" dxfId="1487" priority="2165"/>
+    <cfRule type="duplicateValues" dxfId="1464" priority="2165"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B383">
-    <cfRule type="duplicateValues" dxfId="1486" priority="2164"/>
+    <cfRule type="duplicateValues" dxfId="1463" priority="2164"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B385">
-    <cfRule type="duplicateValues" dxfId="1485" priority="2161"/>
+    <cfRule type="duplicateValues" dxfId="1462" priority="2161"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B385">
-    <cfRule type="duplicateValues" dxfId="1484" priority="2160"/>
+    <cfRule type="duplicateValues" dxfId="1461" priority="2160"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B386">
-    <cfRule type="duplicateValues" dxfId="1483" priority="2155"/>
+    <cfRule type="duplicateValues" dxfId="1460" priority="2155"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B386">
-    <cfRule type="duplicateValues" dxfId="1482" priority="2154"/>
+    <cfRule type="duplicateValues" dxfId="1459" priority="2154"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B387">
-    <cfRule type="duplicateValues" dxfId="1481" priority="2149"/>
+    <cfRule type="duplicateValues" dxfId="1458" priority="2149"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B387">
-    <cfRule type="duplicateValues" dxfId="1480" priority="2148"/>
+    <cfRule type="duplicateValues" dxfId="1457" priority="2148"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B388">
-    <cfRule type="duplicateValues" dxfId="1479" priority="2147"/>
+    <cfRule type="duplicateValues" dxfId="1456" priority="2147"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B388">
-    <cfRule type="duplicateValues" dxfId="1478" priority="2146"/>
+    <cfRule type="duplicateValues" dxfId="1455" priority="2146"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B392">
-    <cfRule type="duplicateValues" dxfId="1477" priority="2143"/>
+    <cfRule type="duplicateValues" dxfId="1454" priority="2143"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B392">
-    <cfRule type="duplicateValues" dxfId="1476" priority="2142"/>
+    <cfRule type="duplicateValues" dxfId="1453" priority="2142"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B393">
-    <cfRule type="duplicateValues" dxfId="1475" priority="2141"/>
+    <cfRule type="duplicateValues" dxfId="1452" priority="2141"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B393">
-    <cfRule type="duplicateValues" dxfId="1474" priority="2140"/>
+    <cfRule type="duplicateValues" dxfId="1451" priority="2140"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B394">
-    <cfRule type="duplicateValues" dxfId="1473" priority="2137"/>
+    <cfRule type="duplicateValues" dxfId="1450" priority="2137"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B394">
-    <cfRule type="duplicateValues" dxfId="1472" priority="2136"/>
+    <cfRule type="duplicateValues" dxfId="1449" priority="2136"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B395">
-    <cfRule type="duplicateValues" dxfId="1471" priority="2135"/>
+    <cfRule type="duplicateValues" dxfId="1448" priority="2135"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B395">
-    <cfRule type="duplicateValues" dxfId="1470" priority="2134"/>
+    <cfRule type="duplicateValues" dxfId="1447" priority="2134"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B398">
-    <cfRule type="duplicateValues" dxfId="1469" priority="2133"/>
+    <cfRule type="duplicateValues" dxfId="1446" priority="2133"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B398">
-    <cfRule type="duplicateValues" dxfId="1468" priority="2132"/>
+    <cfRule type="duplicateValues" dxfId="1445" priority="2132"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B399">
-    <cfRule type="duplicateValues" dxfId="1467" priority="2131"/>
+    <cfRule type="duplicateValues" dxfId="1444" priority="2131"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B399">
-    <cfRule type="duplicateValues" dxfId="1466" priority="2130"/>
+    <cfRule type="duplicateValues" dxfId="1443" priority="2130"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B400">
-    <cfRule type="duplicateValues" dxfId="1465" priority="2127"/>
+    <cfRule type="duplicateValues" dxfId="1442" priority="2127"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B400">
-    <cfRule type="duplicateValues" dxfId="1464" priority="2126"/>
+    <cfRule type="duplicateValues" dxfId="1441" priority="2126"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B402">
-    <cfRule type="duplicateValues" dxfId="1463" priority="2125"/>
+    <cfRule type="duplicateValues" dxfId="1440" priority="2125"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B402">
-    <cfRule type="duplicateValues" dxfId="1462" priority="2124"/>
+    <cfRule type="duplicateValues" dxfId="1439" priority="2124"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B403">
-    <cfRule type="duplicateValues" dxfId="1461" priority="2123"/>
+    <cfRule type="duplicateValues" dxfId="1438" priority="2123"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B403">
-    <cfRule type="duplicateValues" dxfId="1460" priority="2122"/>
+    <cfRule type="duplicateValues" dxfId="1437" priority="2122"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B404">
-    <cfRule type="duplicateValues" dxfId="1459" priority="2121"/>
+    <cfRule type="duplicateValues" dxfId="1436" priority="2121"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B404">
-    <cfRule type="duplicateValues" dxfId="1458" priority="2120"/>
+    <cfRule type="duplicateValues" dxfId="1435" priority="2120"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B405">
-    <cfRule type="duplicateValues" dxfId="1457" priority="2119"/>
+    <cfRule type="duplicateValues" dxfId="1434" priority="2119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B405">
-    <cfRule type="duplicateValues" dxfId="1456" priority="2118"/>
+    <cfRule type="duplicateValues" dxfId="1433" priority="2118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B406">
-    <cfRule type="duplicateValues" dxfId="1455" priority="2117"/>
+    <cfRule type="duplicateValues" dxfId="1432" priority="2117"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B406">
-    <cfRule type="duplicateValues" dxfId="1454" priority="2116"/>
+    <cfRule type="duplicateValues" dxfId="1431" priority="2116"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B407">
-    <cfRule type="duplicateValues" dxfId="1453" priority="2115"/>
+    <cfRule type="duplicateValues" dxfId="1430" priority="2115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B407">
-    <cfRule type="duplicateValues" dxfId="1452" priority="2114"/>
+    <cfRule type="duplicateValues" dxfId="1429" priority="2114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B408">
-    <cfRule type="duplicateValues" dxfId="1451" priority="2113"/>
+    <cfRule type="duplicateValues" dxfId="1428" priority="2113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B408">
-    <cfRule type="duplicateValues" dxfId="1450" priority="2112"/>
+    <cfRule type="duplicateValues" dxfId="1427" priority="2112"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B409">
-    <cfRule type="duplicateValues" dxfId="1449" priority="2111"/>
+    <cfRule type="duplicateValues" dxfId="1426" priority="2111"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B409">
-    <cfRule type="duplicateValues" dxfId="1448" priority="2110"/>
+    <cfRule type="duplicateValues" dxfId="1425" priority="2110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B410">
-    <cfRule type="duplicateValues" dxfId="1447" priority="2109"/>
+    <cfRule type="duplicateValues" dxfId="1424" priority="2109"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B410">
-    <cfRule type="duplicateValues" dxfId="1446" priority="2108"/>
+    <cfRule type="duplicateValues" dxfId="1423" priority="2108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B411">
-    <cfRule type="duplicateValues" dxfId="1445" priority="2107"/>
+    <cfRule type="duplicateValues" dxfId="1422" priority="2107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B411">
-    <cfRule type="duplicateValues" dxfId="1444" priority="2106"/>
+    <cfRule type="duplicateValues" dxfId="1421" priority="2106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B412">
-    <cfRule type="duplicateValues" dxfId="1443" priority="2103"/>
+    <cfRule type="duplicateValues" dxfId="1420" priority="2103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B412">
-    <cfRule type="duplicateValues" dxfId="1442" priority="2102"/>
+    <cfRule type="duplicateValues" dxfId="1419" priority="2102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B413">
-    <cfRule type="duplicateValues" dxfId="1441" priority="2099"/>
+    <cfRule type="duplicateValues" dxfId="1418" priority="2099"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B413">
-    <cfRule type="duplicateValues" dxfId="1440" priority="2098"/>
+    <cfRule type="duplicateValues" dxfId="1417" priority="2098"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B414">
-    <cfRule type="duplicateValues" dxfId="1439" priority="2097"/>
+    <cfRule type="duplicateValues" dxfId="1416" priority="2097"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B414">
-    <cfRule type="duplicateValues" dxfId="1438" priority="2096"/>
+    <cfRule type="duplicateValues" dxfId="1415" priority="2096"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B416">
-    <cfRule type="duplicateValues" dxfId="1437" priority="2087"/>
+    <cfRule type="duplicateValues" dxfId="1414" priority="2087"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B416">
-    <cfRule type="duplicateValues" dxfId="1436" priority="2086"/>
+    <cfRule type="duplicateValues" dxfId="1413" priority="2086"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B417">
-    <cfRule type="duplicateValues" dxfId="1435" priority="2085"/>
+    <cfRule type="duplicateValues" dxfId="1412" priority="2085"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B417">
-    <cfRule type="duplicateValues" dxfId="1434" priority="2084"/>
+    <cfRule type="duplicateValues" dxfId="1411" priority="2084"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B422">
-    <cfRule type="duplicateValues" dxfId="1433" priority="2081"/>
+    <cfRule type="duplicateValues" dxfId="1410" priority="2081"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B422">
-    <cfRule type="duplicateValues" dxfId="1432" priority="2080"/>
+    <cfRule type="duplicateValues" dxfId="1409" priority="2080"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B421">
-    <cfRule type="duplicateValues" dxfId="1431" priority="2079"/>
+    <cfRule type="duplicateValues" dxfId="1408" priority="2079"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B421">
-    <cfRule type="duplicateValues" dxfId="1430" priority="2078"/>
+    <cfRule type="duplicateValues" dxfId="1407" priority="2078"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B423">
-    <cfRule type="duplicateValues" dxfId="1429" priority="2075"/>
+    <cfRule type="duplicateValues" dxfId="1406" priority="2075"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B423">
-    <cfRule type="duplicateValues" dxfId="1428" priority="2074"/>
+    <cfRule type="duplicateValues" dxfId="1405" priority="2074"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B424">
-    <cfRule type="duplicateValues" dxfId="1427" priority="2073"/>
+    <cfRule type="duplicateValues" dxfId="1404" priority="2073"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B424">
-    <cfRule type="duplicateValues" dxfId="1426" priority="2072"/>
+    <cfRule type="duplicateValues" dxfId="1403" priority="2072"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B425">
-    <cfRule type="duplicateValues" dxfId="1425" priority="2071"/>
+    <cfRule type="duplicateValues" dxfId="1402" priority="2071"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B425">
-    <cfRule type="duplicateValues" dxfId="1424" priority="2070"/>
+    <cfRule type="duplicateValues" dxfId="1401" priority="2070"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B426">
-    <cfRule type="duplicateValues" dxfId="1423" priority="2069"/>
+    <cfRule type="duplicateValues" dxfId="1400" priority="2069"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B426">
-    <cfRule type="duplicateValues" dxfId="1422" priority="2068"/>
+    <cfRule type="duplicateValues" dxfId="1399" priority="2068"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B427">
-    <cfRule type="duplicateValues" dxfId="1421" priority="2067"/>
+    <cfRule type="duplicateValues" dxfId="1398" priority="2067"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B427">
-    <cfRule type="duplicateValues" dxfId="1420" priority="2066"/>
+    <cfRule type="duplicateValues" dxfId="1397" priority="2066"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B428">
-    <cfRule type="duplicateValues" dxfId="1419" priority="2065"/>
+    <cfRule type="duplicateValues" dxfId="1396" priority="2065"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B428">
-    <cfRule type="duplicateValues" dxfId="1418" priority="2064"/>
+    <cfRule type="duplicateValues" dxfId="1395" priority="2064"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B429">
-    <cfRule type="duplicateValues" dxfId="1417" priority="2063"/>
+    <cfRule type="duplicateValues" dxfId="1394" priority="2063"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B429">
-    <cfRule type="duplicateValues" dxfId="1416" priority="2062"/>
+    <cfRule type="duplicateValues" dxfId="1393" priority="2062"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B432">
-    <cfRule type="duplicateValues" dxfId="1415" priority="2059"/>
+    <cfRule type="duplicateValues" dxfId="1392" priority="2059"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B432">
-    <cfRule type="duplicateValues" dxfId="1414" priority="2058"/>
+    <cfRule type="duplicateValues" dxfId="1391" priority="2058"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B431">
-    <cfRule type="duplicateValues" dxfId="1413" priority="2057"/>
+    <cfRule type="duplicateValues" dxfId="1390" priority="2057"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B431">
-    <cfRule type="duplicateValues" dxfId="1412" priority="2056"/>
+    <cfRule type="duplicateValues" dxfId="1389" priority="2056"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B434">
-    <cfRule type="duplicateValues" dxfId="1411" priority="2055"/>
+    <cfRule type="duplicateValues" dxfId="1388" priority="2055"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B434">
-    <cfRule type="duplicateValues" dxfId="1410" priority="2054"/>
+    <cfRule type="duplicateValues" dxfId="1387" priority="2054"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B435">
-    <cfRule type="duplicateValues" dxfId="1409" priority="2051"/>
+    <cfRule type="duplicateValues" dxfId="1386" priority="2051"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B435">
-    <cfRule type="duplicateValues" dxfId="1408" priority="2050"/>
+    <cfRule type="duplicateValues" dxfId="1385" priority="2050"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B437">
-    <cfRule type="duplicateValues" dxfId="1407" priority="2047"/>
+    <cfRule type="duplicateValues" dxfId="1384" priority="2047"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B437">
-    <cfRule type="duplicateValues" dxfId="1406" priority="2046"/>
+    <cfRule type="duplicateValues" dxfId="1383" priority="2046"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B436">
-    <cfRule type="duplicateValues" dxfId="1405" priority="2045"/>
+    <cfRule type="duplicateValues" dxfId="1382" priority="2045"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B436">
-    <cfRule type="duplicateValues" dxfId="1404" priority="2044"/>
+    <cfRule type="duplicateValues" dxfId="1381" priority="2044"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B440">
-    <cfRule type="duplicateValues" dxfId="1403" priority="2043"/>
+    <cfRule type="duplicateValues" dxfId="1380" priority="2043"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B440">
-    <cfRule type="duplicateValues" dxfId="1402" priority="2042"/>
+    <cfRule type="duplicateValues" dxfId="1379" priority="2042"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B443">
-    <cfRule type="duplicateValues" dxfId="1401" priority="2039"/>
+    <cfRule type="duplicateValues" dxfId="1378" priority="2039"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B443">
-    <cfRule type="duplicateValues" dxfId="1400" priority="2038"/>
+    <cfRule type="duplicateValues" dxfId="1377" priority="2038"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B445">
-    <cfRule type="duplicateValues" dxfId="1399" priority="2037"/>
+    <cfRule type="duplicateValues" dxfId="1376" priority="2037"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B445">
-    <cfRule type="duplicateValues" dxfId="1398" priority="2036"/>
+    <cfRule type="duplicateValues" dxfId="1375" priority="2036"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B446">
-    <cfRule type="duplicateValues" dxfId="1397" priority="2033"/>
+    <cfRule type="duplicateValues" dxfId="1374" priority="2033"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B446">
-    <cfRule type="duplicateValues" dxfId="1396" priority="2032"/>
+    <cfRule type="duplicateValues" dxfId="1373" priority="2032"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B447">
-    <cfRule type="duplicateValues" dxfId="1395" priority="2031"/>
+    <cfRule type="duplicateValues" dxfId="1372" priority="2031"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B447">
-    <cfRule type="duplicateValues" dxfId="1394" priority="2030"/>
+    <cfRule type="duplicateValues" dxfId="1371" priority="2030"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B449">
-    <cfRule type="duplicateValues" dxfId="1393" priority="2029"/>
+    <cfRule type="duplicateValues" dxfId="1370" priority="2029"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B449">
-    <cfRule type="duplicateValues" dxfId="1392" priority="2028"/>
+    <cfRule type="duplicateValues" dxfId="1369" priority="2028"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B450">
-    <cfRule type="duplicateValues" dxfId="1391" priority="2027"/>
+    <cfRule type="duplicateValues" dxfId="1368" priority="2027"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B450">
-    <cfRule type="duplicateValues" dxfId="1390" priority="2026"/>
+    <cfRule type="duplicateValues" dxfId="1367" priority="2026"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B452">
-    <cfRule type="duplicateValues" dxfId="1389" priority="2025"/>
+    <cfRule type="duplicateValues" dxfId="1366" priority="2025"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B452">
-    <cfRule type="duplicateValues" dxfId="1388" priority="2024"/>
+    <cfRule type="duplicateValues" dxfId="1365" priority="2024"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B453">
-    <cfRule type="duplicateValues" dxfId="1387" priority="2021"/>
+    <cfRule type="duplicateValues" dxfId="1364" priority="2021"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B453">
-    <cfRule type="duplicateValues" dxfId="1386" priority="2020"/>
+    <cfRule type="duplicateValues" dxfId="1363" priority="2020"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B454">
-    <cfRule type="duplicateValues" dxfId="1385" priority="2015"/>
+    <cfRule type="duplicateValues" dxfId="1362" priority="2015"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B454">
-    <cfRule type="duplicateValues" dxfId="1384" priority="2014"/>
+    <cfRule type="duplicateValues" dxfId="1361" priority="2014"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B455">
-    <cfRule type="duplicateValues" dxfId="1383" priority="2013"/>
+    <cfRule type="duplicateValues" dxfId="1360" priority="2013"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B455">
-    <cfRule type="duplicateValues" dxfId="1382" priority="2012"/>
+    <cfRule type="duplicateValues" dxfId="1359" priority="2012"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B457">
-    <cfRule type="duplicateValues" dxfId="1381" priority="2009"/>
+    <cfRule type="duplicateValues" dxfId="1358" priority="2009"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B457">
-    <cfRule type="duplicateValues" dxfId="1380" priority="2008"/>
+    <cfRule type="duplicateValues" dxfId="1357" priority="2008"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B458">
-    <cfRule type="duplicateValues" dxfId="1379" priority="2007"/>
+    <cfRule type="duplicateValues" dxfId="1356" priority="2007"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B458">
-    <cfRule type="duplicateValues" dxfId="1378" priority="2006"/>
+    <cfRule type="duplicateValues" dxfId="1355" priority="2006"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B460">
-    <cfRule type="duplicateValues" dxfId="1377" priority="2005"/>
+    <cfRule type="duplicateValues" dxfId="1354" priority="2005"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B460">
-    <cfRule type="duplicateValues" dxfId="1376" priority="2004"/>
+    <cfRule type="duplicateValues" dxfId="1353" priority="2004"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B461">
-    <cfRule type="duplicateValues" dxfId="1375" priority="2003"/>
+    <cfRule type="duplicateValues" dxfId="1352" priority="2003"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B461">
-    <cfRule type="duplicateValues" dxfId="1374" priority="2002"/>
+    <cfRule type="duplicateValues" dxfId="1351" priority="2002"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B462">
-    <cfRule type="duplicateValues" dxfId="1373" priority="1999"/>
+    <cfRule type="duplicateValues" dxfId="1350" priority="1999"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B462">
-    <cfRule type="duplicateValues" dxfId="1372" priority="1998"/>
+    <cfRule type="duplicateValues" dxfId="1349" priority="1998"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B465">
-    <cfRule type="duplicateValues" dxfId="1371" priority="1995"/>
+    <cfRule type="duplicateValues" dxfId="1348" priority="1995"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B465">
-    <cfRule type="duplicateValues" dxfId="1370" priority="1994"/>
+    <cfRule type="duplicateValues" dxfId="1347" priority="1994"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B469">
-    <cfRule type="duplicateValues" dxfId="1369" priority="1993"/>
+    <cfRule type="duplicateValues" dxfId="1346" priority="1993"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B469">
-    <cfRule type="duplicateValues" dxfId="1368" priority="1992"/>
+    <cfRule type="duplicateValues" dxfId="1345" priority="1992"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B470">
-    <cfRule type="duplicateValues" dxfId="1367" priority="1991"/>
+    <cfRule type="duplicateValues" dxfId="1344" priority="1991"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B470">
-    <cfRule type="duplicateValues" dxfId="1366" priority="1990"/>
+    <cfRule type="duplicateValues" dxfId="1343" priority="1990"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B473">
-    <cfRule type="duplicateValues" dxfId="1365" priority="1987"/>
+    <cfRule type="duplicateValues" dxfId="1342" priority="1987"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B473">
-    <cfRule type="duplicateValues" dxfId="1364" priority="1986"/>
+    <cfRule type="duplicateValues" dxfId="1341" priority="1986"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B474">
-    <cfRule type="duplicateValues" dxfId="1363" priority="1985"/>
+    <cfRule type="duplicateValues" dxfId="1340" priority="1985"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B474">
-    <cfRule type="duplicateValues" dxfId="1362" priority="1984"/>
+    <cfRule type="duplicateValues" dxfId="1339" priority="1984"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B478">
-    <cfRule type="duplicateValues" dxfId="1361" priority="1979"/>
+    <cfRule type="duplicateValues" dxfId="1338" priority="1979"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B478">
-    <cfRule type="duplicateValues" dxfId="1360" priority="1978"/>
+    <cfRule type="duplicateValues" dxfId="1337" priority="1978"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B479">
-    <cfRule type="duplicateValues" dxfId="1359" priority="1975"/>
+    <cfRule type="duplicateValues" dxfId="1336" priority="1975"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B479">
-    <cfRule type="duplicateValues" dxfId="1358" priority="1974"/>
+    <cfRule type="duplicateValues" dxfId="1335" priority="1974"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B481">
-    <cfRule type="duplicateValues" dxfId="1357" priority="1967"/>
+    <cfRule type="duplicateValues" dxfId="1334" priority="1967"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B481">
-    <cfRule type="duplicateValues" dxfId="1356" priority="1966"/>
+    <cfRule type="duplicateValues" dxfId="1333" priority="1966"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B482">
-    <cfRule type="duplicateValues" dxfId="1355" priority="1965"/>
+    <cfRule type="duplicateValues" dxfId="1332" priority="1965"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B482">
-    <cfRule type="duplicateValues" dxfId="1354" priority="1964"/>
+    <cfRule type="duplicateValues" dxfId="1331" priority="1964"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B484">
-    <cfRule type="duplicateValues" dxfId="1353" priority="1963"/>
+    <cfRule type="duplicateValues" dxfId="1330" priority="1963"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B484">
-    <cfRule type="duplicateValues" dxfId="1352" priority="1962"/>
+    <cfRule type="duplicateValues" dxfId="1329" priority="1962"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B486">
-    <cfRule type="duplicateValues" dxfId="1351" priority="1953"/>
+    <cfRule type="duplicateValues" dxfId="1328" priority="1953"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B486">
-    <cfRule type="duplicateValues" dxfId="1350" priority="1952"/>
+    <cfRule type="duplicateValues" dxfId="1327" priority="1952"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B489">
-    <cfRule type="duplicateValues" dxfId="1349" priority="1949"/>
+    <cfRule type="duplicateValues" dxfId="1326" priority="1949"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B489">
-    <cfRule type="duplicateValues" dxfId="1348" priority="1948"/>
+    <cfRule type="duplicateValues" dxfId="1325" priority="1948"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B490">
-    <cfRule type="duplicateValues" dxfId="1347" priority="1947"/>
+    <cfRule type="duplicateValues" dxfId="1324" priority="1947"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B490">
-    <cfRule type="duplicateValues" dxfId="1346" priority="1946"/>
+    <cfRule type="duplicateValues" dxfId="1323" priority="1946"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B496">
-    <cfRule type="duplicateValues" dxfId="1345" priority="1931"/>
+    <cfRule type="duplicateValues" dxfId="1322" priority="1931"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B496">
-    <cfRule type="duplicateValues" dxfId="1344" priority="1930"/>
+    <cfRule type="duplicateValues" dxfId="1321" priority="1930"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B497">
-    <cfRule type="duplicateValues" dxfId="1343" priority="1929"/>
+    <cfRule type="duplicateValues" dxfId="1320" priority="1929"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B497">
-    <cfRule type="duplicateValues" dxfId="1342" priority="1928"/>
+    <cfRule type="duplicateValues" dxfId="1319" priority="1928"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B498">
-    <cfRule type="duplicateValues" dxfId="1341" priority="1925"/>
+    <cfRule type="duplicateValues" dxfId="1318" priority="1925"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B498">
-    <cfRule type="duplicateValues" dxfId="1340" priority="1924"/>
+    <cfRule type="duplicateValues" dxfId="1317" priority="1924"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B501">
-    <cfRule type="duplicateValues" dxfId="1339" priority="1919"/>
+    <cfRule type="duplicateValues" dxfId="1316" priority="1919"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B501">
-    <cfRule type="duplicateValues" dxfId="1338" priority="1918"/>
+    <cfRule type="duplicateValues" dxfId="1315" priority="1918"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B502">
-    <cfRule type="duplicateValues" dxfId="1337" priority="1917"/>
+    <cfRule type="duplicateValues" dxfId="1314" priority="1917"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B502:B503">
-    <cfRule type="duplicateValues" dxfId="1336" priority="1916"/>
+    <cfRule type="duplicateValues" dxfId="1313" priority="1916"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B503">
-    <cfRule type="duplicateValues" dxfId="1335" priority="1915"/>
+    <cfRule type="duplicateValues" dxfId="1312" priority="1915"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B503">
-    <cfRule type="duplicateValues" dxfId="1334" priority="1914"/>
+    <cfRule type="duplicateValues" dxfId="1311" priority="1914"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B504">
-    <cfRule type="duplicateValues" dxfId="1333" priority="1913"/>
+    <cfRule type="duplicateValues" dxfId="1310" priority="1913"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B504">
-    <cfRule type="duplicateValues" dxfId="1332" priority="1912"/>
+    <cfRule type="duplicateValues" dxfId="1309" priority="1912"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B508">
-    <cfRule type="duplicateValues" dxfId="1331" priority="1903"/>
+    <cfRule type="duplicateValues" dxfId="1308" priority="1903"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B508">
-    <cfRule type="duplicateValues" dxfId="1330" priority="1902"/>
+    <cfRule type="duplicateValues" dxfId="1307" priority="1902"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B509">
-    <cfRule type="duplicateValues" dxfId="1329" priority="1901"/>
+    <cfRule type="duplicateValues" dxfId="1306" priority="1901"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B509">
-    <cfRule type="duplicateValues" dxfId="1328" priority="1900"/>
+    <cfRule type="duplicateValues" dxfId="1305" priority="1900"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B510">
-    <cfRule type="duplicateValues" dxfId="1327" priority="1899"/>
+    <cfRule type="duplicateValues" dxfId="1304" priority="1899"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B510">
-    <cfRule type="duplicateValues" dxfId="1326" priority="1898"/>
+    <cfRule type="duplicateValues" dxfId="1303" priority="1898"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B512">
-    <cfRule type="duplicateValues" dxfId="1325" priority="1895"/>
+    <cfRule type="duplicateValues" dxfId="1302" priority="1895"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B512">
-    <cfRule type="duplicateValues" dxfId="1324" priority="1894"/>
+    <cfRule type="duplicateValues" dxfId="1301" priority="1894"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B513">
-    <cfRule type="duplicateValues" dxfId="1323" priority="1893"/>
+    <cfRule type="duplicateValues" dxfId="1300" priority="1893"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B513">
-    <cfRule type="duplicateValues" dxfId="1322" priority="1892"/>
+    <cfRule type="duplicateValues" dxfId="1299" priority="1892"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B515">
-    <cfRule type="duplicateValues" dxfId="1321" priority="1891"/>
+    <cfRule type="duplicateValues" dxfId="1298" priority="1891"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B515">
-    <cfRule type="duplicateValues" dxfId="1320" priority="1890"/>
+    <cfRule type="duplicateValues" dxfId="1297" priority="1890"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B516">
-    <cfRule type="duplicateValues" dxfId="1319" priority="1883"/>
+    <cfRule type="duplicateValues" dxfId="1296" priority="1883"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B516">
-    <cfRule type="duplicateValues" dxfId="1318" priority="1882"/>
+    <cfRule type="duplicateValues" dxfId="1295" priority="1882"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B517">
-    <cfRule type="duplicateValues" dxfId="1317" priority="1879"/>
+    <cfRule type="duplicateValues" dxfId="1294" priority="1879"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B517">
-    <cfRule type="duplicateValues" dxfId="1316" priority="1878"/>
+    <cfRule type="duplicateValues" dxfId="1293" priority="1878"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B518">
-    <cfRule type="duplicateValues" dxfId="1315" priority="1875"/>
+    <cfRule type="duplicateValues" dxfId="1292" priority="1875"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B518">
-    <cfRule type="duplicateValues" dxfId="1314" priority="1874"/>
+    <cfRule type="duplicateValues" dxfId="1291" priority="1874"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B522">
-    <cfRule type="duplicateValues" dxfId="1313" priority="1871"/>
+    <cfRule type="duplicateValues" dxfId="1290" priority="1871"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B522">
-    <cfRule type="duplicateValues" dxfId="1312" priority="1870"/>
+    <cfRule type="duplicateValues" dxfId="1289" priority="1870"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B520">
-    <cfRule type="duplicateValues" dxfId="1311" priority="1869"/>
+    <cfRule type="duplicateValues" dxfId="1288" priority="1869"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B520">
-    <cfRule type="duplicateValues" dxfId="1310" priority="1868"/>
+    <cfRule type="duplicateValues" dxfId="1287" priority="1868"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B521">
-    <cfRule type="duplicateValues" dxfId="1309" priority="1865"/>
+    <cfRule type="duplicateValues" dxfId="1286" priority="1865"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B521">
-    <cfRule type="duplicateValues" dxfId="1308" priority="1864"/>
+    <cfRule type="duplicateValues" dxfId="1285" priority="1864"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B523">
-    <cfRule type="duplicateValues" dxfId="1307" priority="1859"/>
+    <cfRule type="duplicateValues" dxfId="1284" priority="1859"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B523">
-    <cfRule type="duplicateValues" dxfId="1306" priority="1858"/>
+    <cfRule type="duplicateValues" dxfId="1283" priority="1858"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B527">
-    <cfRule type="duplicateValues" dxfId="1305" priority="1853"/>
+    <cfRule type="duplicateValues" dxfId="1282" priority="1853"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B527">
-    <cfRule type="duplicateValues" dxfId="1304" priority="1852"/>
+    <cfRule type="duplicateValues" dxfId="1281" priority="1852"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B526">
-    <cfRule type="duplicateValues" dxfId="1303" priority="1851"/>
+    <cfRule type="duplicateValues" dxfId="1280" priority="1851"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B526">
-    <cfRule type="duplicateValues" dxfId="1302" priority="1850"/>
+    <cfRule type="duplicateValues" dxfId="1279" priority="1850"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B525">
-    <cfRule type="duplicateValues" dxfId="1301" priority="1849"/>
+    <cfRule type="duplicateValues" dxfId="1278" priority="1849"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B525">
-    <cfRule type="duplicateValues" dxfId="1300" priority="1848"/>
+    <cfRule type="duplicateValues" dxfId="1277" priority="1848"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B530">
-    <cfRule type="duplicateValues" dxfId="1299" priority="1847"/>
+    <cfRule type="duplicateValues" dxfId="1276" priority="1847"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B530">
-    <cfRule type="duplicateValues" dxfId="1298" priority="1846"/>
+    <cfRule type="duplicateValues" dxfId="1275" priority="1846"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B536">
-    <cfRule type="duplicateValues" dxfId="1297" priority="1845"/>
+    <cfRule type="duplicateValues" dxfId="1274" priority="1845"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B536">
-    <cfRule type="duplicateValues" dxfId="1296" priority="1844"/>
+    <cfRule type="duplicateValues" dxfId="1273" priority="1844"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B538">
-    <cfRule type="duplicateValues" dxfId="1295" priority="1843"/>
+    <cfRule type="duplicateValues" dxfId="1272" priority="1843"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B538">
-    <cfRule type="duplicateValues" dxfId="1294" priority="1842"/>
+    <cfRule type="duplicateValues" dxfId="1271" priority="1842"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B540">
-    <cfRule type="duplicateValues" dxfId="1293" priority="1839"/>
+    <cfRule type="duplicateValues" dxfId="1270" priority="1839"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B540">
-    <cfRule type="duplicateValues" dxfId="1292" priority="1838"/>
+    <cfRule type="duplicateValues" dxfId="1269" priority="1838"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B543">
-    <cfRule type="duplicateValues" dxfId="1291" priority="1835"/>
+    <cfRule type="duplicateValues" dxfId="1268" priority="1835"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B543">
-    <cfRule type="duplicateValues" dxfId="1290" priority="1834"/>
+    <cfRule type="duplicateValues" dxfId="1267" priority="1834"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B541">
-    <cfRule type="duplicateValues" dxfId="1289" priority="1833"/>
+    <cfRule type="duplicateValues" dxfId="1266" priority="1833"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B541">
-    <cfRule type="duplicateValues" dxfId="1288" priority="1832"/>
+    <cfRule type="duplicateValues" dxfId="1265" priority="1832"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B542">
-    <cfRule type="duplicateValues" dxfId="1287" priority="1827"/>
+    <cfRule type="duplicateValues" dxfId="1264" priority="1827"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B542">
-    <cfRule type="duplicateValues" dxfId="1286" priority="1826"/>
+    <cfRule type="duplicateValues" dxfId="1263" priority="1826"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B544">
-    <cfRule type="duplicateValues" dxfId="1285" priority="1823"/>
+    <cfRule type="duplicateValues" dxfId="1262" priority="1823"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B544">
-    <cfRule type="duplicateValues" dxfId="1284" priority="1822"/>
+    <cfRule type="duplicateValues" dxfId="1261" priority="1822"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B545">
-    <cfRule type="duplicateValues" dxfId="1283" priority="1819"/>
+    <cfRule type="duplicateValues" dxfId="1260" priority="1819"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B545">
-    <cfRule type="duplicateValues" dxfId="1282" priority="1818"/>
+    <cfRule type="duplicateValues" dxfId="1259" priority="1818"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B546">
-    <cfRule type="duplicateValues" dxfId="1281" priority="1817"/>
+    <cfRule type="duplicateValues" dxfId="1258" priority="1817"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B546">
-    <cfRule type="duplicateValues" dxfId="1280" priority="1816"/>
+    <cfRule type="duplicateValues" dxfId="1257" priority="1816"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B547">
-    <cfRule type="duplicateValues" dxfId="1279" priority="1813"/>
+    <cfRule type="duplicateValues" dxfId="1256" priority="1813"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B547">
-    <cfRule type="duplicateValues" dxfId="1278" priority="1812"/>
+    <cfRule type="duplicateValues" dxfId="1255" priority="1812"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B549">
-    <cfRule type="duplicateValues" dxfId="1277" priority="1811"/>
+    <cfRule type="duplicateValues" dxfId="1254" priority="1811"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B549">
-    <cfRule type="duplicateValues" dxfId="1276" priority="1810"/>
+    <cfRule type="duplicateValues" dxfId="1253" priority="1810"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B551">
-    <cfRule type="duplicateValues" dxfId="1275" priority="1807"/>
+    <cfRule type="duplicateValues" dxfId="1252" priority="1807"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B551">
-    <cfRule type="duplicateValues" dxfId="1274" priority="1806"/>
+    <cfRule type="duplicateValues" dxfId="1251" priority="1806"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B552">
-    <cfRule type="duplicateValues" dxfId="1273" priority="1805"/>
+    <cfRule type="duplicateValues" dxfId="1250" priority="1805"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B552">
-    <cfRule type="duplicateValues" dxfId="1272" priority="1804"/>
+    <cfRule type="duplicateValues" dxfId="1249" priority="1804"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B553">
-    <cfRule type="duplicateValues" dxfId="1271" priority="1799"/>
+    <cfRule type="duplicateValues" dxfId="1248" priority="1799"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B553">
-    <cfRule type="duplicateValues" dxfId="1270" priority="1798"/>
+    <cfRule type="duplicateValues" dxfId="1247" priority="1798"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B554">
-    <cfRule type="duplicateValues" dxfId="1269" priority="1797"/>
+    <cfRule type="duplicateValues" dxfId="1246" priority="1797"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B554">
-    <cfRule type="duplicateValues" dxfId="1268" priority="1796"/>
+    <cfRule type="duplicateValues" dxfId="1245" priority="1796"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B555">
-    <cfRule type="duplicateValues" dxfId="1267" priority="1791"/>
+    <cfRule type="duplicateValues" dxfId="1244" priority="1791"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B555">
-    <cfRule type="duplicateValues" dxfId="1266" priority="1790"/>
+    <cfRule type="duplicateValues" dxfId="1243" priority="1790"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B556">
-    <cfRule type="duplicateValues" dxfId="1265" priority="1789"/>
+    <cfRule type="duplicateValues" dxfId="1242" priority="1789"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B556">
-    <cfRule type="duplicateValues" dxfId="1264" priority="1788"/>
+    <cfRule type="duplicateValues" dxfId="1241" priority="1788"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B557">
-    <cfRule type="duplicateValues" dxfId="1263" priority="1785"/>
+    <cfRule type="duplicateValues" dxfId="1240" priority="1785"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B557">
-    <cfRule type="duplicateValues" dxfId="1262" priority="1784"/>
+    <cfRule type="duplicateValues" dxfId="1239" priority="1784"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B558">
-    <cfRule type="duplicateValues" dxfId="1261" priority="1783"/>
+    <cfRule type="duplicateValues" dxfId="1238" priority="1783"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B558">
-    <cfRule type="duplicateValues" dxfId="1260" priority="1782"/>
+    <cfRule type="duplicateValues" dxfId="1237" priority="1782"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B562">
-    <cfRule type="duplicateValues" dxfId="1259" priority="1773"/>
+    <cfRule type="duplicateValues" dxfId="1236" priority="1773"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B562">
-    <cfRule type="duplicateValues" dxfId="1258" priority="1772"/>
+    <cfRule type="duplicateValues" dxfId="1235" priority="1772"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B564">
-    <cfRule type="duplicateValues" dxfId="1257" priority="1771"/>
+    <cfRule type="duplicateValues" dxfId="1234" priority="1771"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B564">
-    <cfRule type="duplicateValues" dxfId="1256" priority="1770"/>
+    <cfRule type="duplicateValues" dxfId="1233" priority="1770"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B563">
-    <cfRule type="duplicateValues" dxfId="1255" priority="1769"/>
+    <cfRule type="duplicateValues" dxfId="1232" priority="1769"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B563">
-    <cfRule type="duplicateValues" dxfId="1254" priority="1768"/>
+    <cfRule type="duplicateValues" dxfId="1231" priority="1768"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B565">
-    <cfRule type="duplicateValues" dxfId="1253" priority="1767"/>
+    <cfRule type="duplicateValues" dxfId="1230" priority="1767"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B565">
-    <cfRule type="duplicateValues" dxfId="1252" priority="1766"/>
+    <cfRule type="duplicateValues" dxfId="1229" priority="1766"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B566">
-    <cfRule type="duplicateValues" dxfId="1251" priority="1759"/>
+    <cfRule type="duplicateValues" dxfId="1228" priority="1759"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B566">
-    <cfRule type="duplicateValues" dxfId="1250" priority="1758"/>
+    <cfRule type="duplicateValues" dxfId="1227" priority="1758"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B569">
-    <cfRule type="duplicateValues" dxfId="1249" priority="1757"/>
+    <cfRule type="duplicateValues" dxfId="1226" priority="1757"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B569">
-    <cfRule type="duplicateValues" dxfId="1248" priority="1756"/>
+    <cfRule type="duplicateValues" dxfId="1225" priority="1756"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B567">
-    <cfRule type="duplicateValues" dxfId="1247" priority="1753"/>
+    <cfRule type="duplicateValues" dxfId="1224" priority="1753"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B567">
-    <cfRule type="duplicateValues" dxfId="1246" priority="1752"/>
+    <cfRule type="duplicateValues" dxfId="1223" priority="1752"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B568">
-    <cfRule type="duplicateValues" dxfId="1245" priority="1749"/>
+    <cfRule type="duplicateValues" dxfId="1222" priority="1749"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B568">
-    <cfRule type="duplicateValues" dxfId="1244" priority="1748"/>
+    <cfRule type="duplicateValues" dxfId="1221" priority="1748"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B571">
-    <cfRule type="duplicateValues" dxfId="1243" priority="1739"/>
+    <cfRule type="duplicateValues" dxfId="1220" priority="1739"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B572">
-    <cfRule type="duplicateValues" dxfId="1242" priority="1736"/>
+    <cfRule type="duplicateValues" dxfId="1219" priority="1736"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B572">
-    <cfRule type="duplicateValues" dxfId="1241" priority="1735"/>
+    <cfRule type="duplicateValues" dxfId="1218" priority="1735"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B575">
-    <cfRule type="duplicateValues" dxfId="1240" priority="1733"/>
+    <cfRule type="duplicateValues" dxfId="1217" priority="1733"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B575">
-    <cfRule type="duplicateValues" dxfId="1239" priority="1734"/>
+    <cfRule type="duplicateValues" dxfId="1216" priority="1734"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B577">
-    <cfRule type="duplicateValues" dxfId="1238" priority="1732"/>
+    <cfRule type="duplicateValues" dxfId="1215" priority="1732"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B577">
-    <cfRule type="duplicateValues" dxfId="1237" priority="1731"/>
+    <cfRule type="duplicateValues" dxfId="1214" priority="1731"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B578">
-    <cfRule type="duplicateValues" dxfId="1236" priority="1721"/>
+    <cfRule type="duplicateValues" dxfId="1213" priority="1721"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B578">
-    <cfRule type="duplicateValues" dxfId="1235" priority="1722"/>
+    <cfRule type="duplicateValues" dxfId="1212" priority="1722"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B579">
-    <cfRule type="duplicateValues" dxfId="1234" priority="1718"/>
+    <cfRule type="duplicateValues" dxfId="1211" priority="1718"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B580">
-    <cfRule type="duplicateValues" dxfId="1233" priority="1715"/>
+    <cfRule type="duplicateValues" dxfId="1210" priority="1715"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B581">
-    <cfRule type="duplicateValues" dxfId="1232" priority="1712"/>
+    <cfRule type="duplicateValues" dxfId="1209" priority="1712"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B581">
-    <cfRule type="duplicateValues" dxfId="1231" priority="1711"/>
+    <cfRule type="duplicateValues" dxfId="1208" priority="1711"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B582">
-    <cfRule type="duplicateValues" dxfId="1230" priority="1710"/>
+    <cfRule type="duplicateValues" dxfId="1207" priority="1710"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B582">
-    <cfRule type="duplicateValues" dxfId="1229" priority="1709"/>
+    <cfRule type="duplicateValues" dxfId="1206" priority="1709"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B583">
-    <cfRule type="duplicateValues" dxfId="1228" priority="1708"/>
+    <cfRule type="duplicateValues" dxfId="1205" priority="1708"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B583">
-    <cfRule type="duplicateValues" dxfId="1227" priority="1707"/>
+    <cfRule type="duplicateValues" dxfId="1204" priority="1707"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B584">
-    <cfRule type="duplicateValues" dxfId="1226" priority="1706"/>
+    <cfRule type="duplicateValues" dxfId="1203" priority="1706"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B584">
-    <cfRule type="duplicateValues" dxfId="1225" priority="1705"/>
+    <cfRule type="duplicateValues" dxfId="1202" priority="1705"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B587">
-    <cfRule type="duplicateValues" dxfId="1224" priority="1703"/>
+    <cfRule type="duplicateValues" dxfId="1201" priority="1703"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B587">
-    <cfRule type="duplicateValues" dxfId="1223" priority="1704"/>
+    <cfRule type="duplicateValues" dxfId="1200" priority="1704"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B586">
-    <cfRule type="duplicateValues" dxfId="1222" priority="1701"/>
+    <cfRule type="duplicateValues" dxfId="1199" priority="1701"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B586">
-    <cfRule type="duplicateValues" dxfId="1221" priority="1702"/>
+    <cfRule type="duplicateValues" dxfId="1198" priority="1702"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B589">
-    <cfRule type="duplicateValues" dxfId="1220" priority="1695"/>
+    <cfRule type="duplicateValues" dxfId="1197" priority="1695"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B589">
-    <cfRule type="duplicateValues" dxfId="1219" priority="1696"/>
+    <cfRule type="duplicateValues" dxfId="1196" priority="1696"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B591">
-    <cfRule type="duplicateValues" dxfId="1218" priority="1691"/>
+    <cfRule type="duplicateValues" dxfId="1195" priority="1691"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B591">
-    <cfRule type="duplicateValues" dxfId="1217" priority="1692"/>
+    <cfRule type="duplicateValues" dxfId="1194" priority="1692"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B592">
-    <cfRule type="duplicateValues" dxfId="1216" priority="1689"/>
+    <cfRule type="duplicateValues" dxfId="1193" priority="1689"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B592">
-    <cfRule type="duplicateValues" dxfId="1215" priority="1690"/>
+    <cfRule type="duplicateValues" dxfId="1192" priority="1690"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B593">
-    <cfRule type="duplicateValues" dxfId="1214" priority="1687"/>
+    <cfRule type="duplicateValues" dxfId="1191" priority="1687"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B593">
-    <cfRule type="duplicateValues" dxfId="1213" priority="1688"/>
+    <cfRule type="duplicateValues" dxfId="1190" priority="1688"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B594">
-    <cfRule type="duplicateValues" dxfId="1212" priority="1683"/>
+    <cfRule type="duplicateValues" dxfId="1189" priority="1683"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B594">
-    <cfRule type="duplicateValues" dxfId="1211" priority="1684"/>
+    <cfRule type="duplicateValues" dxfId="1188" priority="1684"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B595">
-    <cfRule type="duplicateValues" dxfId="1210" priority="1679"/>
+    <cfRule type="duplicateValues" dxfId="1187" priority="1679"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B595">
-    <cfRule type="duplicateValues" dxfId="1209" priority="1680"/>
+    <cfRule type="duplicateValues" dxfId="1186" priority="1680"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B596">
-    <cfRule type="duplicateValues" dxfId="1208" priority="1678"/>
+    <cfRule type="duplicateValues" dxfId="1185" priority="1678"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B601">
-    <cfRule type="duplicateValues" dxfId="1207" priority="1675"/>
+    <cfRule type="duplicateValues" dxfId="1184" priority="1675"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B602">
-    <cfRule type="duplicateValues" dxfId="1206" priority="1673"/>
+    <cfRule type="duplicateValues" dxfId="1183" priority="1673"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B602">
-    <cfRule type="duplicateValues" dxfId="1205" priority="1674"/>
+    <cfRule type="duplicateValues" dxfId="1182" priority="1674"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B603">
-    <cfRule type="duplicateValues" dxfId="1204" priority="1671"/>
+    <cfRule type="duplicateValues" dxfId="1181" priority="1671"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B603">
-    <cfRule type="duplicateValues" dxfId="1203" priority="1672"/>
+    <cfRule type="duplicateValues" dxfId="1180" priority="1672"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B604:B605">
-    <cfRule type="duplicateValues" dxfId="1202" priority="1667"/>
+    <cfRule type="duplicateValues" dxfId="1179" priority="1667"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B604:B605">
-    <cfRule type="duplicateValues" dxfId="1201" priority="1668"/>
+    <cfRule type="duplicateValues" dxfId="1178" priority="1668"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B606:B608">
-    <cfRule type="duplicateValues" dxfId="1200" priority="1665"/>
+    <cfRule type="duplicateValues" dxfId="1177" priority="1665"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B606:B608">
-    <cfRule type="duplicateValues" dxfId="1199" priority="1666"/>
+    <cfRule type="duplicateValues" dxfId="1176" priority="1666"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B609:B610">
-    <cfRule type="duplicateValues" dxfId="1198" priority="1659"/>
+    <cfRule type="duplicateValues" dxfId="1175" priority="1659"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B609:B610">
-    <cfRule type="duplicateValues" dxfId="1197" priority="1660"/>
+    <cfRule type="duplicateValues" dxfId="1174" priority="1660"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B611:B613">
-    <cfRule type="duplicateValues" dxfId="1196" priority="1658"/>
+    <cfRule type="duplicateValues" dxfId="1173" priority="1658"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B611:B613">
-    <cfRule type="duplicateValues" dxfId="1195" priority="1657"/>
+    <cfRule type="duplicateValues" dxfId="1172" priority="1657"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B614:B615">
-    <cfRule type="duplicateValues" dxfId="1194" priority="1655"/>
+    <cfRule type="duplicateValues" dxfId="1171" priority="1655"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B614:B615">
-    <cfRule type="duplicateValues" dxfId="1193" priority="1656"/>
+    <cfRule type="duplicateValues" dxfId="1170" priority="1656"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B616:B618">
-    <cfRule type="duplicateValues" dxfId="1192" priority="1649"/>
+    <cfRule type="duplicateValues" dxfId="1169" priority="1649"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B616:B618">
-    <cfRule type="duplicateValues" dxfId="1191" priority="1650"/>
+    <cfRule type="duplicateValues" dxfId="1168" priority="1650"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B619:B621">
-    <cfRule type="duplicateValues" dxfId="1190" priority="1647"/>
+    <cfRule type="duplicateValues" dxfId="1167" priority="1647"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B619:B621">
-    <cfRule type="duplicateValues" dxfId="1189" priority="1648"/>
+    <cfRule type="duplicateValues" dxfId="1166" priority="1648"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B624:B626">
-    <cfRule type="duplicateValues" dxfId="1188" priority="1645"/>
+    <cfRule type="duplicateValues" dxfId="1165" priority="1645"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B624:B626">
-    <cfRule type="duplicateValues" dxfId="1187" priority="1646"/>
+    <cfRule type="duplicateValues" dxfId="1164" priority="1646"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B627:B628">
-    <cfRule type="duplicateValues" dxfId="1186" priority="1640"/>
+    <cfRule type="duplicateValues" dxfId="1163" priority="1640"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B627:B628">
-    <cfRule type="duplicateValues" dxfId="1185" priority="1639"/>
+    <cfRule type="duplicateValues" dxfId="1162" priority="1639"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B629:B632">
-    <cfRule type="duplicateValues" dxfId="1184" priority="1636"/>
+    <cfRule type="duplicateValues" dxfId="1161" priority="1636"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B629:B632">
-    <cfRule type="duplicateValues" dxfId="1183" priority="1635"/>
+    <cfRule type="duplicateValues" dxfId="1160" priority="1635"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B633:B634">
-    <cfRule type="duplicateValues" dxfId="1182" priority="1632"/>
+    <cfRule type="duplicateValues" dxfId="1159" priority="1632"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B633:B634">
-    <cfRule type="duplicateValues" dxfId="1181" priority="1631"/>
+    <cfRule type="duplicateValues" dxfId="1158" priority="1631"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B635:B636">
-    <cfRule type="duplicateValues" dxfId="1180" priority="1629"/>
+    <cfRule type="duplicateValues" dxfId="1157" priority="1629"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B635:B636">
-    <cfRule type="duplicateValues" dxfId="1179" priority="1630"/>
+    <cfRule type="duplicateValues" dxfId="1156" priority="1630"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B637:B639">
-    <cfRule type="duplicateValues" dxfId="1178" priority="1626"/>
+    <cfRule type="duplicateValues" dxfId="1155" priority="1626"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B640:B642">
-    <cfRule type="duplicateValues" dxfId="1177" priority="1624"/>
+    <cfRule type="duplicateValues" dxfId="1154" priority="1624"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B640:B642">
-    <cfRule type="duplicateValues" dxfId="1176" priority="1625"/>
+    <cfRule type="duplicateValues" dxfId="1153" priority="1625"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B643:B644">
-    <cfRule type="duplicateValues" dxfId="1175" priority="1622"/>
+    <cfRule type="duplicateValues" dxfId="1152" priority="1622"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B643:B644">
-    <cfRule type="duplicateValues" dxfId="1174" priority="1623"/>
+    <cfRule type="duplicateValues" dxfId="1151" priority="1623"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D645:D647">
-    <cfRule type="duplicateValues" dxfId="1173" priority="1620"/>
+    <cfRule type="duplicateValues" dxfId="1150" priority="1620"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D645:D647">
-    <cfRule type="duplicateValues" dxfId="1172" priority="1621"/>
+    <cfRule type="duplicateValues" dxfId="1149" priority="1621"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B645:B647">
-    <cfRule type="duplicateValues" dxfId="1171" priority="1616"/>
+    <cfRule type="duplicateValues" dxfId="1148" priority="1616"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B645:B647">
-    <cfRule type="duplicateValues" dxfId="1170" priority="1617"/>
+    <cfRule type="duplicateValues" dxfId="1147" priority="1617"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B656:B657">
-    <cfRule type="duplicateValues" dxfId="1169" priority="1614"/>
+    <cfRule type="duplicateValues" dxfId="1146" priority="1614"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B656:B657">
-    <cfRule type="duplicateValues" dxfId="1168" priority="1615"/>
+    <cfRule type="duplicateValues" dxfId="1145" priority="1615"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B660:B662">
-    <cfRule type="duplicateValues" dxfId="1167" priority="1612"/>
+    <cfRule type="duplicateValues" dxfId="1144" priority="1612"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B660:B662">
-    <cfRule type="duplicateValues" dxfId="1166" priority="1613"/>
+    <cfRule type="duplicateValues" dxfId="1143" priority="1613"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B658:B659">
-    <cfRule type="duplicateValues" dxfId="1165" priority="1611"/>
+    <cfRule type="duplicateValues" dxfId="1142" priority="1611"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B658:B659">
-    <cfRule type="duplicateValues" dxfId="1164" priority="1610"/>
+    <cfRule type="duplicateValues" dxfId="1141" priority="1610"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B663:B665">
-    <cfRule type="duplicateValues" dxfId="1163" priority="1609"/>
+    <cfRule type="duplicateValues" dxfId="1140" priority="1609"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B663:B665">
-    <cfRule type="duplicateValues" dxfId="1162" priority="1608"/>
+    <cfRule type="duplicateValues" dxfId="1139" priority="1608"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B666:B667">
-    <cfRule type="duplicateValues" dxfId="1161" priority="1605"/>
+    <cfRule type="duplicateValues" dxfId="1138" priority="1605"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B666:B667">
-    <cfRule type="duplicateValues" dxfId="1160" priority="1604"/>
+    <cfRule type="duplicateValues" dxfId="1137" priority="1604"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B670:B672">
-    <cfRule type="duplicateValues" dxfId="1159" priority="1597"/>
+    <cfRule type="duplicateValues" dxfId="1136" priority="1597"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B670:B672">
-    <cfRule type="duplicateValues" dxfId="1158" priority="1596"/>
+    <cfRule type="duplicateValues" dxfId="1135" priority="1596"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677">
-    <cfRule type="duplicateValues" dxfId="1157" priority="1584"/>
+    <cfRule type="duplicateValues" dxfId="1134" priority="1584"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677">
-    <cfRule type="duplicateValues" dxfId="1156" priority="1585"/>
+    <cfRule type="duplicateValues" dxfId="1133" priority="1585"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B678">
-    <cfRule type="duplicateValues" dxfId="1155" priority="1582"/>
+    <cfRule type="duplicateValues" dxfId="1132" priority="1582"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B678">
-    <cfRule type="duplicateValues" dxfId="1154" priority="1583"/>
+    <cfRule type="duplicateValues" dxfId="1131" priority="1583"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B682:B684">
-    <cfRule type="duplicateValues" dxfId="1153" priority="1580"/>
+    <cfRule type="duplicateValues" dxfId="1130" priority="1580"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B682:B684">
-    <cfRule type="duplicateValues" dxfId="1152" priority="1581"/>
+    <cfRule type="duplicateValues" dxfId="1129" priority="1581"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B679:B681">
-    <cfRule type="duplicateValues" dxfId="1151" priority="1578"/>
+    <cfRule type="duplicateValues" dxfId="1128" priority="1578"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B679:B681">
-    <cfRule type="duplicateValues" dxfId="1150" priority="1579"/>
+    <cfRule type="duplicateValues" dxfId="1127" priority="1579"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B685:B686">
-    <cfRule type="duplicateValues" dxfId="1149" priority="1576"/>
+    <cfRule type="duplicateValues" dxfId="1126" priority="1576"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B685:B686">
-    <cfRule type="duplicateValues" dxfId="1148" priority="1577"/>
+    <cfRule type="duplicateValues" dxfId="1125" priority="1577"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B692:B693">
-    <cfRule type="duplicateValues" dxfId="1147" priority="1574"/>
+    <cfRule type="duplicateValues" dxfId="1124" priority="1574"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B692:B693">
-    <cfRule type="duplicateValues" dxfId="1146" priority="1575"/>
+    <cfRule type="duplicateValues" dxfId="1123" priority="1575"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B694">
-    <cfRule type="duplicateValues" dxfId="1145" priority="1570"/>
+    <cfRule type="duplicateValues" dxfId="1122" priority="1570"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B694">
-    <cfRule type="duplicateValues" dxfId="1144" priority="1571"/>
+    <cfRule type="duplicateValues" dxfId="1121" priority="1571"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B695:B697">
-    <cfRule type="duplicateValues" dxfId="1143" priority="1568"/>
+    <cfRule type="duplicateValues" dxfId="1120" priority="1568"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B695:B697">
-    <cfRule type="duplicateValues" dxfId="1142" priority="1569"/>
+    <cfRule type="duplicateValues" dxfId="1119" priority="1569"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B702:B705">
-    <cfRule type="duplicateValues" dxfId="1141" priority="1565"/>
+    <cfRule type="duplicateValues" dxfId="1118" priority="1565"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B702:B705">
-    <cfRule type="duplicateValues" dxfId="1140" priority="1564"/>
+    <cfRule type="duplicateValues" dxfId="1117" priority="1564"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B698:B701">
-    <cfRule type="duplicateValues" dxfId="1139" priority="1562"/>
+    <cfRule type="duplicateValues" dxfId="1116" priority="1562"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B698:B701">
-    <cfRule type="duplicateValues" dxfId="1138" priority="1563"/>
+    <cfRule type="duplicateValues" dxfId="1115" priority="1563"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B709:B710">
-    <cfRule type="duplicateValues" dxfId="1137" priority="1556"/>
+    <cfRule type="duplicateValues" dxfId="1114" priority="1556"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B709:B710">
-    <cfRule type="duplicateValues" dxfId="1136" priority="1557"/>
+    <cfRule type="duplicateValues" dxfId="1113" priority="1557"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B711">
-    <cfRule type="duplicateValues" dxfId="1135" priority="1551"/>
+    <cfRule type="duplicateValues" dxfId="1112" priority="1551"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B711">
-    <cfRule type="duplicateValues" dxfId="1134" priority="1550"/>
+    <cfRule type="duplicateValues" dxfId="1111" priority="1550"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B712:B713">
-    <cfRule type="duplicateValues" dxfId="1133" priority="1546"/>
+    <cfRule type="duplicateValues" dxfId="1110" priority="1546"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B712:B713">
-    <cfRule type="duplicateValues" dxfId="1132" priority="1547"/>
+    <cfRule type="duplicateValues" dxfId="1109" priority="1547"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B714:B715">
-    <cfRule type="duplicateValues" dxfId="1131" priority="1545"/>
+    <cfRule type="duplicateValues" dxfId="1108" priority="1545"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B714:B715">
-    <cfRule type="duplicateValues" dxfId="1130" priority="1544"/>
+    <cfRule type="duplicateValues" dxfId="1107" priority="1544"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B716:B718">
-    <cfRule type="duplicateValues" dxfId="1129" priority="1542"/>
+    <cfRule type="duplicateValues" dxfId="1106" priority="1542"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B716:B718">
-    <cfRule type="duplicateValues" dxfId="1128" priority="1543"/>
+    <cfRule type="duplicateValues" dxfId="1105" priority="1543"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B719:B720">
-    <cfRule type="duplicateValues" dxfId="1127" priority="1540"/>
+    <cfRule type="duplicateValues" dxfId="1104" priority="1540"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B719:B720">
-    <cfRule type="duplicateValues" dxfId="1126" priority="1541"/>
+    <cfRule type="duplicateValues" dxfId="1103" priority="1541"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B721">
-    <cfRule type="duplicateValues" dxfId="1125" priority="1538"/>
+    <cfRule type="duplicateValues" dxfId="1102" priority="1538"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B721">
-    <cfRule type="duplicateValues" dxfId="1124" priority="1539"/>
+    <cfRule type="duplicateValues" dxfId="1101" priority="1539"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B722">
-    <cfRule type="duplicateValues" dxfId="1123" priority="1536"/>
+    <cfRule type="duplicateValues" dxfId="1100" priority="1536"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B722">
-    <cfRule type="duplicateValues" dxfId="1122" priority="1537"/>
+    <cfRule type="duplicateValues" dxfId="1099" priority="1537"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B723">
-    <cfRule type="duplicateValues" dxfId="1121" priority="1530"/>
+    <cfRule type="duplicateValues" dxfId="1098" priority="1530"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B723">
-    <cfRule type="duplicateValues" dxfId="1120" priority="1531"/>
+    <cfRule type="duplicateValues" dxfId="1097" priority="1531"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B725">
-    <cfRule type="duplicateValues" dxfId="1119" priority="1526"/>
+    <cfRule type="duplicateValues" dxfId="1096" priority="1526"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B725">
-    <cfRule type="duplicateValues" dxfId="1118" priority="1527"/>
+    <cfRule type="duplicateValues" dxfId="1095" priority="1527"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B726">
-    <cfRule type="duplicateValues" dxfId="1117" priority="1524"/>
+    <cfRule type="duplicateValues" dxfId="1094" priority="1524"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B726">
-    <cfRule type="duplicateValues" dxfId="1116" priority="1525"/>
+    <cfRule type="duplicateValues" dxfId="1093" priority="1525"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B727">
-    <cfRule type="duplicateValues" dxfId="1115" priority="1522"/>
+    <cfRule type="duplicateValues" dxfId="1092" priority="1522"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B727">
-    <cfRule type="duplicateValues" dxfId="1114" priority="1523"/>
+    <cfRule type="duplicateValues" dxfId="1091" priority="1523"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B728">
-    <cfRule type="duplicateValues" dxfId="1113" priority="1521"/>
+    <cfRule type="duplicateValues" dxfId="1090" priority="1521"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B728">
-    <cfRule type="duplicateValues" dxfId="1112" priority="1520"/>
+    <cfRule type="duplicateValues" dxfId="1089" priority="1520"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B729">
-    <cfRule type="duplicateValues" dxfId="1111" priority="1518"/>
+    <cfRule type="duplicateValues" dxfId="1088" priority="1518"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B729">
-    <cfRule type="duplicateValues" dxfId="1110" priority="1519"/>
+    <cfRule type="duplicateValues" dxfId="1087" priority="1519"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B730">
-    <cfRule type="duplicateValues" dxfId="1109" priority="1516"/>
+    <cfRule type="duplicateValues" dxfId="1086" priority="1516"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B730">
-    <cfRule type="duplicateValues" dxfId="1108" priority="1517"/>
+    <cfRule type="duplicateValues" dxfId="1085" priority="1517"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B735">
-    <cfRule type="duplicateValues" dxfId="1105" priority="1510"/>
+    <cfRule type="duplicateValues" dxfId="1084" priority="1510"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B735">
-    <cfRule type="duplicateValues" dxfId="1104" priority="1511"/>
+    <cfRule type="duplicateValues" dxfId="1083" priority="1511"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B736">
-    <cfRule type="duplicateValues" dxfId="1103" priority="1508"/>
+    <cfRule type="duplicateValues" dxfId="1082" priority="1508"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B736">
-    <cfRule type="duplicateValues" dxfId="1102" priority="1509"/>
+    <cfRule type="duplicateValues" dxfId="1081" priority="1509"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B737">
-    <cfRule type="duplicateValues" dxfId="1101" priority="1504"/>
+    <cfRule type="duplicateValues" dxfId="1080" priority="1504"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B737">
-    <cfRule type="duplicateValues" dxfId="1100" priority="1505"/>
+    <cfRule type="duplicateValues" dxfId="1079" priority="1505"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B738">
-    <cfRule type="duplicateValues" dxfId="1099" priority="1501"/>
+    <cfRule type="duplicateValues" dxfId="1078" priority="1501"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B738">
-    <cfRule type="duplicateValues" dxfId="1098" priority="1500"/>
+    <cfRule type="duplicateValues" dxfId="1077" priority="1500"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B739">
-    <cfRule type="duplicateValues" dxfId="1097" priority="1497"/>
+    <cfRule type="duplicateValues" dxfId="1076" priority="1497"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B739">
-    <cfRule type="duplicateValues" dxfId="1096" priority="1496"/>
+    <cfRule type="duplicateValues" dxfId="1075" priority="1496"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B741">
-    <cfRule type="duplicateValues" dxfId="1095" priority="1494"/>
+    <cfRule type="duplicateValues" dxfId="1074" priority="1494"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B741">
-    <cfRule type="duplicateValues" dxfId="1094" priority="1495"/>
+    <cfRule type="duplicateValues" dxfId="1073" priority="1495"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B742">
-    <cfRule type="duplicateValues" dxfId="1093" priority="1490"/>
+    <cfRule type="duplicateValues" dxfId="1072" priority="1490"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B742">
-    <cfRule type="duplicateValues" dxfId="1092" priority="1491"/>
+    <cfRule type="duplicateValues" dxfId="1071" priority="1491"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B743">
-    <cfRule type="duplicateValues" dxfId="1091" priority="1484"/>
+    <cfRule type="duplicateValues" dxfId="1070" priority="1484"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B743">
-    <cfRule type="duplicateValues" dxfId="1090" priority="1485"/>
+    <cfRule type="duplicateValues" dxfId="1069" priority="1485"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B745">
-    <cfRule type="duplicateValues" dxfId="1086" priority="1475"/>
+    <cfRule type="duplicateValues" dxfId="1068" priority="1475"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B745">
-    <cfRule type="duplicateValues" dxfId="1085" priority="1476"/>
+    <cfRule type="duplicateValues" dxfId="1067" priority="1476"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B745">
-    <cfRule type="duplicateValues" dxfId="1084" priority="1474"/>
+    <cfRule type="duplicateValues" dxfId="1066" priority="1474"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B746">
-    <cfRule type="duplicateValues" dxfId="1083" priority="1472"/>
+    <cfRule type="duplicateValues" dxfId="1065" priority="1472"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B746">
-    <cfRule type="duplicateValues" dxfId="1082" priority="1473"/>
+    <cfRule type="duplicateValues" dxfId="1064" priority="1473"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B746">
-    <cfRule type="duplicateValues" dxfId="1081" priority="1471"/>
+    <cfRule type="duplicateValues" dxfId="1063" priority="1471"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B748">
-    <cfRule type="duplicateValues" dxfId="1077" priority="1466"/>
+    <cfRule type="duplicateValues" dxfId="1062" priority="1466"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B748">
-    <cfRule type="duplicateValues" dxfId="1076" priority="1467"/>
+    <cfRule type="duplicateValues" dxfId="1061" priority="1467"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B748">
-    <cfRule type="duplicateValues" dxfId="1075" priority="1465"/>
+    <cfRule type="duplicateValues" dxfId="1060" priority="1465"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B749">
-    <cfRule type="duplicateValues" dxfId="1074" priority="1460"/>
+    <cfRule type="duplicateValues" dxfId="1059" priority="1460"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B749">
-    <cfRule type="duplicateValues" dxfId="1073" priority="1461"/>
+    <cfRule type="duplicateValues" dxfId="1058" priority="1461"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B749">
-    <cfRule type="duplicateValues" dxfId="1072" priority="1459"/>
+    <cfRule type="duplicateValues" dxfId="1057" priority="1459"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B750">
-    <cfRule type="duplicateValues" dxfId="1071" priority="1455"/>
+    <cfRule type="duplicateValues" dxfId="1056" priority="1455"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B750">
-    <cfRule type="duplicateValues" dxfId="1070" priority="1454"/>
+    <cfRule type="duplicateValues" dxfId="1055" priority="1454"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B750">
-    <cfRule type="duplicateValues" dxfId="1069" priority="1453"/>
+    <cfRule type="duplicateValues" dxfId="1054" priority="1453"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B751">
-    <cfRule type="duplicateValues" dxfId="1068" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="1053" priority="1449"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B751">
-    <cfRule type="duplicateValues" dxfId="1067" priority="1448"/>
+    <cfRule type="duplicateValues" dxfId="1052" priority="1448"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B751">
-    <cfRule type="duplicateValues" dxfId="1066" priority="1447"/>
+    <cfRule type="duplicateValues" dxfId="1051" priority="1447"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B753">
-    <cfRule type="duplicateValues" dxfId="1065" priority="1436"/>
+    <cfRule type="duplicateValues" dxfId="1050" priority="1436"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B753">
-    <cfRule type="duplicateValues" dxfId="1064" priority="1437"/>
+    <cfRule type="duplicateValues" dxfId="1049" priority="1437"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B753">
-    <cfRule type="duplicateValues" dxfId="1063" priority="1435"/>
+    <cfRule type="duplicateValues" dxfId="1048" priority="1435"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B754">
-    <cfRule type="duplicateValues" dxfId="1062" priority="1433"/>
+    <cfRule type="duplicateValues" dxfId="1047" priority="1433"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B754">
-    <cfRule type="duplicateValues" dxfId="1061" priority="1434"/>
+    <cfRule type="duplicateValues" dxfId="1046" priority="1434"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B754">
-    <cfRule type="duplicateValues" dxfId="1060" priority="1432"/>
+    <cfRule type="duplicateValues" dxfId="1045" priority="1432"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B756">
-    <cfRule type="duplicateValues" dxfId="18" priority="1430"/>
+    <cfRule type="duplicateValues" dxfId="1044" priority="1430"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B756">
-    <cfRule type="duplicateValues" dxfId="1059" priority="1431"/>
+    <cfRule type="duplicateValues" dxfId="1043" priority="1431"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B756">
-    <cfRule type="duplicateValues" dxfId="1058" priority="1429"/>
+    <cfRule type="duplicateValues" dxfId="1042" priority="1429"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B758">
-    <cfRule type="duplicateValues" dxfId="1054" priority="1418"/>
+    <cfRule type="duplicateValues" dxfId="1041" priority="1418"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B758">
-    <cfRule type="duplicateValues" dxfId="1053" priority="1419"/>
+    <cfRule type="duplicateValues" dxfId="1040" priority="1419"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B758">
-    <cfRule type="duplicateValues" dxfId="1052" priority="1417"/>
+    <cfRule type="duplicateValues" dxfId="1039" priority="1417"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B759">
-    <cfRule type="duplicateValues" dxfId="1051" priority="1415"/>
+    <cfRule type="duplicateValues" dxfId="1038" priority="1415"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B759">
-    <cfRule type="duplicateValues" dxfId="1050" priority="1416"/>
+    <cfRule type="duplicateValues" dxfId="1037" priority="1416"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B759">
-    <cfRule type="duplicateValues" dxfId="1049" priority="1414"/>
+    <cfRule type="duplicateValues" dxfId="1036" priority="1414"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B760">
-    <cfRule type="duplicateValues" dxfId="1048" priority="1410"/>
+    <cfRule type="duplicateValues" dxfId="1035" priority="1410"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B760">
-    <cfRule type="duplicateValues" dxfId="1047" priority="1409"/>
+    <cfRule type="duplicateValues" dxfId="1034" priority="1409"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B760">
-    <cfRule type="duplicateValues" dxfId="1046" priority="1408"/>
+    <cfRule type="duplicateValues" dxfId="1033" priority="1408"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B762">
-    <cfRule type="duplicateValues" dxfId="1045" priority="1407"/>
+    <cfRule type="duplicateValues" dxfId="1032" priority="1407"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B762">
-    <cfRule type="duplicateValues" dxfId="1044" priority="1406"/>
+    <cfRule type="duplicateValues" dxfId="1031" priority="1406"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B762">
-    <cfRule type="duplicateValues" dxfId="1043" priority="1405"/>
+    <cfRule type="duplicateValues" dxfId="1030" priority="1405"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B763">
-    <cfRule type="duplicateValues" dxfId="1042" priority="1401"/>
+    <cfRule type="duplicateValues" dxfId="1029" priority="1401"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B763">
-    <cfRule type="duplicateValues" dxfId="1041" priority="1400"/>
+    <cfRule type="duplicateValues" dxfId="1028" priority="1400"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B763">
-    <cfRule type="duplicateValues" dxfId="1040" priority="1399"/>
+    <cfRule type="duplicateValues" dxfId="1027" priority="1399"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B764">
-    <cfRule type="duplicateValues" dxfId="1039" priority="1392"/>
+    <cfRule type="duplicateValues" dxfId="1026" priority="1392"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B764">
-    <cfRule type="duplicateValues" dxfId="1038" priority="1391"/>
+    <cfRule type="duplicateValues" dxfId="1025" priority="1391"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B764">
-    <cfRule type="duplicateValues" dxfId="1037" priority="1390"/>
+    <cfRule type="duplicateValues" dxfId="1024" priority="1390"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B765">
-    <cfRule type="duplicateValues" dxfId="1036" priority="1388"/>
+    <cfRule type="duplicateValues" dxfId="1023" priority="1388"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B765">
-    <cfRule type="duplicateValues" dxfId="1035" priority="1389"/>
+    <cfRule type="duplicateValues" dxfId="1022" priority="1389"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B765">
-    <cfRule type="duplicateValues" dxfId="1034" priority="1387"/>
+    <cfRule type="duplicateValues" dxfId="1021" priority="1387"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B766">
-    <cfRule type="duplicateValues" dxfId="1033" priority="1385"/>
+    <cfRule type="duplicateValues" dxfId="1020" priority="1385"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B766">
-    <cfRule type="duplicateValues" dxfId="1032" priority="1386"/>
+    <cfRule type="duplicateValues" dxfId="1019" priority="1386"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B766">
-    <cfRule type="duplicateValues" dxfId="1031" priority="1384"/>
+    <cfRule type="duplicateValues" dxfId="1018" priority="1384"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B768">
-    <cfRule type="duplicateValues" dxfId="1027" priority="1373"/>
+    <cfRule type="duplicateValues" dxfId="1017" priority="1373"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B768">
-    <cfRule type="duplicateValues" dxfId="1026" priority="1374"/>
+    <cfRule type="duplicateValues" dxfId="1016" priority="1374"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B768">
-    <cfRule type="duplicateValues" dxfId="1025" priority="1372"/>
+    <cfRule type="duplicateValues" dxfId="1015" priority="1372"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B770">
-    <cfRule type="duplicateValues" dxfId="1024" priority="1367"/>
+    <cfRule type="duplicateValues" dxfId="1014" priority="1367"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B770">
-    <cfRule type="duplicateValues" dxfId="1023" priority="1368"/>
+    <cfRule type="duplicateValues" dxfId="1013" priority="1368"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B770">
-    <cfRule type="duplicateValues" dxfId="1022" priority="1366"/>
+    <cfRule type="duplicateValues" dxfId="1012" priority="1366"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B769">
-    <cfRule type="duplicateValues" dxfId="1021" priority="1365"/>
+    <cfRule type="duplicateValues" dxfId="1011" priority="1365"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B769">
-    <cfRule type="duplicateValues" dxfId="1020" priority="1364"/>
+    <cfRule type="duplicateValues" dxfId="1010" priority="1364"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B769">
-    <cfRule type="duplicateValues" dxfId="1019" priority="1363"/>
+    <cfRule type="duplicateValues" dxfId="1009" priority="1363"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B771">
-    <cfRule type="duplicateValues" dxfId="1018" priority="1361"/>
+    <cfRule type="duplicateValues" dxfId="1008" priority="1361"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B771">
-    <cfRule type="duplicateValues" dxfId="1017" priority="1362"/>
+    <cfRule type="duplicateValues" dxfId="1007" priority="1362"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B771">
-    <cfRule type="duplicateValues" dxfId="1016" priority="1360"/>
+    <cfRule type="duplicateValues" dxfId="1006" priority="1360"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B773">
-    <cfRule type="duplicateValues" dxfId="1015" priority="1358"/>
+    <cfRule type="duplicateValues" dxfId="1005" priority="1358"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B773">
-    <cfRule type="duplicateValues" dxfId="1014" priority="1359"/>
+    <cfRule type="duplicateValues" dxfId="1004" priority="1359"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B773">
-    <cfRule type="duplicateValues" dxfId="1013" priority="1357"/>
+    <cfRule type="duplicateValues" dxfId="1003" priority="1357"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B774">
-    <cfRule type="duplicateValues" dxfId="1012" priority="1355"/>
+    <cfRule type="duplicateValues" dxfId="1002" priority="1355"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B774">
-    <cfRule type="duplicateValues" dxfId="1011" priority="1356"/>
+    <cfRule type="duplicateValues" dxfId="1001" priority="1356"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B774">
-    <cfRule type="duplicateValues" dxfId="1010" priority="1354"/>
+    <cfRule type="duplicateValues" dxfId="1000" priority="1354"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B776">
-    <cfRule type="duplicateValues" dxfId="1009" priority="1353"/>
+    <cfRule type="duplicateValues" dxfId="999" priority="1353"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B776">
-    <cfRule type="duplicateValues" dxfId="1008" priority="1352"/>
+    <cfRule type="duplicateValues" dxfId="998" priority="1352"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B776">
-    <cfRule type="duplicateValues" dxfId="1007" priority="1351"/>
+    <cfRule type="duplicateValues" dxfId="997" priority="1351"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B777">
-    <cfRule type="duplicateValues" dxfId="1006" priority="1349"/>
+    <cfRule type="duplicateValues" dxfId="996" priority="1349"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B777">
-    <cfRule type="duplicateValues" dxfId="1005" priority="1350"/>
+    <cfRule type="duplicateValues" dxfId="995" priority="1350"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B777">
-    <cfRule type="duplicateValues" dxfId="1004" priority="1348"/>
+    <cfRule type="duplicateValues" dxfId="994" priority="1348"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B778">
-    <cfRule type="duplicateValues" dxfId="1003" priority="1346"/>
+    <cfRule type="duplicateValues" dxfId="993" priority="1346"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B778">
-    <cfRule type="duplicateValues" dxfId="1002" priority="1347"/>
+    <cfRule type="duplicateValues" dxfId="992" priority="1347"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B778">
-    <cfRule type="duplicateValues" dxfId="1001" priority="1345"/>
+    <cfRule type="duplicateValues" dxfId="991" priority="1345"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B780">
-    <cfRule type="duplicateValues" dxfId="1000" priority="1343"/>
+    <cfRule type="duplicateValues" dxfId="990" priority="1343"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B780">
-    <cfRule type="duplicateValues" dxfId="999" priority="1344"/>
+    <cfRule type="duplicateValues" dxfId="989" priority="1344"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B780">
-    <cfRule type="duplicateValues" dxfId="998" priority="1342"/>
+    <cfRule type="duplicateValues" dxfId="988" priority="1342"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B781">
-    <cfRule type="duplicateValues" dxfId="997" priority="1337"/>
+    <cfRule type="duplicateValues" dxfId="987" priority="1337"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B781">
-    <cfRule type="duplicateValues" dxfId="996" priority="1338"/>
+    <cfRule type="duplicateValues" dxfId="986" priority="1338"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B781">
-    <cfRule type="duplicateValues" dxfId="995" priority="1336"/>
+    <cfRule type="duplicateValues" dxfId="985" priority="1336"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B782">
-    <cfRule type="duplicateValues" dxfId="994" priority="1334"/>
+    <cfRule type="duplicateValues" dxfId="984" priority="1334"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B782">
-    <cfRule type="duplicateValues" dxfId="993" priority="1335"/>
+    <cfRule type="duplicateValues" dxfId="983" priority="1335"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B782">
-    <cfRule type="duplicateValues" dxfId="992" priority="1333"/>
+    <cfRule type="duplicateValues" dxfId="982" priority="1333"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B784">
-    <cfRule type="duplicateValues" dxfId="991" priority="1331"/>
+    <cfRule type="duplicateValues" dxfId="981" priority="1331"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B784">
-    <cfRule type="duplicateValues" dxfId="990" priority="1332"/>
+    <cfRule type="duplicateValues" dxfId="980" priority="1332"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B784">
-    <cfRule type="duplicateValues" dxfId="989" priority="1330"/>
+    <cfRule type="duplicateValues" dxfId="979" priority="1330"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B785">
-    <cfRule type="duplicateValues" dxfId="988" priority="1325"/>
+    <cfRule type="duplicateValues" dxfId="978" priority="1325"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B785">
-    <cfRule type="duplicateValues" dxfId="987" priority="1326"/>
+    <cfRule type="duplicateValues" dxfId="977" priority="1326"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B785">
-    <cfRule type="duplicateValues" dxfId="986" priority="1324"/>
+    <cfRule type="duplicateValues" dxfId="976" priority="1324"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B786">
-    <cfRule type="duplicateValues" dxfId="985" priority="1317"/>
+    <cfRule type="duplicateValues" dxfId="975" priority="1317"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B786">
-    <cfRule type="duplicateValues" dxfId="984" priority="1316"/>
+    <cfRule type="duplicateValues" dxfId="974" priority="1316"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B786">
-    <cfRule type="duplicateValues" dxfId="983" priority="1315"/>
+    <cfRule type="duplicateValues" dxfId="973" priority="1315"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B787">
-    <cfRule type="duplicateValues" dxfId="982" priority="1314"/>
+    <cfRule type="duplicateValues" dxfId="972" priority="1314"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B787">
-    <cfRule type="duplicateValues" dxfId="981" priority="1313"/>
+    <cfRule type="duplicateValues" dxfId="971" priority="1313"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B787">
-    <cfRule type="duplicateValues" dxfId="980" priority="1312"/>
+    <cfRule type="duplicateValues" dxfId="970" priority="1312"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B789">
-    <cfRule type="duplicateValues" dxfId="979" priority="1311"/>
+    <cfRule type="duplicateValues" dxfId="969" priority="1311"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B789">
-    <cfRule type="duplicateValues" dxfId="978" priority="1310"/>
+    <cfRule type="duplicateValues" dxfId="968" priority="1310"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B789">
-    <cfRule type="duplicateValues" dxfId="977" priority="1309"/>
+    <cfRule type="duplicateValues" dxfId="967" priority="1309"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B788">
-    <cfRule type="duplicateValues" dxfId="976" priority="1308"/>
+    <cfRule type="duplicateValues" dxfId="966" priority="1308"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B788">
-    <cfRule type="duplicateValues" dxfId="975" priority="1307"/>
+    <cfRule type="duplicateValues" dxfId="965" priority="1307"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B788">
-    <cfRule type="duplicateValues" dxfId="974" priority="1306"/>
+    <cfRule type="duplicateValues" dxfId="964" priority="1306"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B791">
-    <cfRule type="duplicateValues" dxfId="973" priority="1304"/>
+    <cfRule type="duplicateValues" dxfId="963" priority="1304"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B791">
-    <cfRule type="duplicateValues" dxfId="972" priority="1305"/>
+    <cfRule type="duplicateValues" dxfId="962" priority="1305"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B791">
-    <cfRule type="duplicateValues" dxfId="971" priority="1303"/>
+    <cfRule type="duplicateValues" dxfId="961" priority="1303"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B793">
-    <cfRule type="duplicateValues" dxfId="970" priority="1295"/>
+    <cfRule type="duplicateValues" dxfId="960" priority="1295"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B793">
-    <cfRule type="duplicateValues" dxfId="969" priority="1296"/>
+    <cfRule type="duplicateValues" dxfId="959" priority="1296"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B793">
-    <cfRule type="duplicateValues" dxfId="968" priority="1294"/>
+    <cfRule type="duplicateValues" dxfId="958" priority="1294"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B794">
-    <cfRule type="duplicateValues" dxfId="967" priority="1289"/>
+    <cfRule type="duplicateValues" dxfId="957" priority="1289"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B794">
-    <cfRule type="duplicateValues" dxfId="966" priority="1290"/>
+    <cfRule type="duplicateValues" dxfId="956" priority="1290"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B794">
-    <cfRule type="duplicateValues" dxfId="965" priority="1288"/>
+    <cfRule type="duplicateValues" dxfId="955" priority="1288"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B796">
-    <cfRule type="duplicateValues" dxfId="964" priority="1283"/>
+    <cfRule type="duplicateValues" dxfId="954" priority="1283"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B796">
-    <cfRule type="duplicateValues" dxfId="963" priority="1284"/>
+    <cfRule type="duplicateValues" dxfId="953" priority="1284"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B796">
-    <cfRule type="duplicateValues" dxfId="962" priority="1282"/>
+    <cfRule type="duplicateValues" dxfId="952" priority="1282"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B795">
-    <cfRule type="duplicateValues" dxfId="961" priority="1281"/>
+    <cfRule type="duplicateValues" dxfId="951" priority="1281"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B795">
-    <cfRule type="duplicateValues" dxfId="960" priority="1280"/>
+    <cfRule type="duplicateValues" dxfId="950" priority="1280"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B795">
-    <cfRule type="duplicateValues" dxfId="959" priority="1279"/>
+    <cfRule type="duplicateValues" dxfId="949" priority="1279"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B797">
-    <cfRule type="duplicateValues" dxfId="958" priority="1274"/>
+    <cfRule type="duplicateValues" dxfId="948" priority="1274"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B797">
-    <cfRule type="duplicateValues" dxfId="957" priority="1275"/>
+    <cfRule type="duplicateValues" dxfId="947" priority="1275"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B797">
-    <cfRule type="duplicateValues" dxfId="956" priority="1273"/>
+    <cfRule type="duplicateValues" dxfId="946" priority="1273"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B799">
-    <cfRule type="duplicateValues" dxfId="955" priority="1272"/>
+    <cfRule type="duplicateValues" dxfId="945" priority="1272"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B799">
-    <cfRule type="duplicateValues" dxfId="954" priority="1271"/>
+    <cfRule type="duplicateValues" dxfId="944" priority="1271"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B799">
-    <cfRule type="duplicateValues" dxfId="953" priority="1270"/>
+    <cfRule type="duplicateValues" dxfId="943" priority="1270"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B800">
-    <cfRule type="duplicateValues" dxfId="952" priority="1268"/>
+    <cfRule type="duplicateValues" dxfId="942" priority="1268"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B800">
-    <cfRule type="duplicateValues" dxfId="951" priority="1269"/>
+    <cfRule type="duplicateValues" dxfId="941" priority="1269"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B800">
-    <cfRule type="duplicateValues" dxfId="950" priority="1267"/>
+    <cfRule type="duplicateValues" dxfId="940" priority="1267"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B801">
-    <cfRule type="duplicateValues" dxfId="949" priority="1259"/>
+    <cfRule type="duplicateValues" dxfId="939" priority="1259"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B801">
-    <cfRule type="duplicateValues" dxfId="948" priority="1260"/>
+    <cfRule type="duplicateValues" dxfId="938" priority="1260"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B801">
-    <cfRule type="duplicateValues" dxfId="947" priority="1258"/>
+    <cfRule type="duplicateValues" dxfId="937" priority="1258"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B752 D46 B573:B574 B46 B104:B106 B109:B111 B126 B131 B134 B137 B143:B147 B150:B152 B159:B160 D154 B169 B181 B188 B190 B199 D195 B212 B222:B224 B229 B231:B232 B239:B240 B242:B244 B251 B258:B261 B264:B269 B273 B278 B288:B289 B291 B295:B299 B306:B307 B324 B331 B333 B337:B338 B340:B341 B343 B348 B345:B346 B351 B364 B372:B373 B378:B380 B389:B390 B396:B397 B401 B420 B430 B433 B438:B439 B442 B444 B448 B451 B459 B463 B466 B475:B476 B480 B488 B492:B495 B507 B514 B519 B524 B528:B529 B531:B535 B537 B539 B560 B576 B590 B599:B600 B622:B623 B648:B655 B687:B691 B724 B732:B734 B740 B755 B772 B775 B779 B783 B790 B792 B798 B808 B824 B827 B835 B837:B838 B844:B845 B850:B852 B874 B877 B880 B893:B896 B907 B909 B911:B912 B916 B919 B924:B925 B929 B931 B933:B934 B945 B947 B966 B980 B996:B997 B999 B1001:B1002 B1011 B1019:B1048576 B1:B8 B11:B15 B18:B19 B22 B24 B30:B31 B34 B39:B41 B43 B48:B50 B53 B56:B58 B62:B64 B74:B94 B96:B102 B114:B119 B122 B124 B183:B184 B468">
-    <cfRule type="duplicateValues" dxfId="946" priority="2600"/>
+    <cfRule type="duplicateValues" dxfId="936" priority="2600"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B752 B573:B574 B231:B232 B239:B240 B242:B244 B251 B258:B261 B264:B269 B273 B278 B288:B289 B291 B295:B299 B306:B307 B324 B331 B333 B337:B338 B340:B341 B343 B348 B345:B346 B351 B364 B372:B373 B378:B380 B389:B390 B396:B397 B401 B420 B430 B433 B438:B439 B442 B444 B448 B451 B459 B463 B466 B475:B476 B480 B488 B492:B495 B507 B514 B519 B524 B528:B529 B531:B535 B537 B539 B560 B576 B590 B599:B600 B622:B623 B648:B655 B687:B691 B724 B732:B734 B740 B755 B772 B775 B779 B783 B790 B792 B798 B808 B824 B827 B835 B837:B838 B844:B845 B850:B852 B874 B877 B880 B893:B896 B907 B909 B911:B912 B916 B919 B924:B925 B929 B931 B933:B934 B945 B947 B966 B980 B996:B997 B999 B1001:B1002 B1011 B1019:B1048576 B1:B8 B11:B15 B18:B19 B22 B24 B30:B31 B34 B39:B41 B43 B46 B48:B50 B53 B56:B58 B62:B64 B74:B94 B96:B106 B108:B111 B114:B119 B122 B124:B126 B128:B152 B154:B155 B157 B159:B164 B166:B167 B169:B170 B179 B181 B183:B184 B186:B188 B190:B202 B204:B205 B209:B212 B214 B216:B217 B219:B220 B222:B229 B468">
-    <cfRule type="duplicateValues" dxfId="945" priority="2712"/>
+    <cfRule type="duplicateValues" dxfId="935" priority="2712"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B752 B755 B772 B775 B779 B783 B790 B792 B798 B808 B824 B827 B835 B837:B838 B844:B845 B850:B852 B874 B877 B880 B893:B896 B907 B909 B911:B912 B916 B919 B924:B925 B929 B931 B933:B934 B945 B947 B966 B980 B996:B997 B999 B1001:B1002 B1011 B1019:B1048576 B1:B8 B11:B15 B18:B19 B22 B24 B30:B31 B34 B39:B41 B43 B46 B48:B50 B53 B56:B58 B62:B64 B74:B94 B96:B106 B108:B111 B114:B119 B122 B124:B126 B128:B152 B154:B155 B157 B159:B164 B166:B167 B169:B170 B179 B181 B183:B184 B186:B188 B190:B202 B204:B205 B209:B212 B214 B216:B217 B219:B220 B222:B229 B231:B232 B237:B249 B251:B252 B255 B258:B261 B263:B269 B271 B273:B279 B281:B283 B286:B310 B312 B315 B317:B318 B320:B321 B324 B329:B353 B355:B361 B363:B368 B370:B383 B385:B390 B392:B414 B416:B417 B420:B440 B442:B455 B457:B463 B465:B466 B468:B470 B473:B476 B478:B482 B484 B486 B488:B490 B492:B498 B501:B504 B507:B510 B512:B547 B549 B551:B558 B560 B562:B569 B571:B584 B586:B587 B589:B596 B599:B730 B732:B743">
-    <cfRule type="duplicateValues" dxfId="944" priority="2798"/>
+    <cfRule type="duplicateValues" dxfId="934" priority="2798"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B802">
-    <cfRule type="duplicateValues" dxfId="943" priority="1252"/>
+    <cfRule type="duplicateValues" dxfId="933" priority="1252"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B802">
-    <cfRule type="duplicateValues" dxfId="942" priority="1253"/>
+    <cfRule type="duplicateValues" dxfId="932" priority="1253"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B802">
-    <cfRule type="duplicateValues" dxfId="941" priority="1254"/>
+    <cfRule type="duplicateValues" dxfId="931" priority="1254"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B803">
-    <cfRule type="duplicateValues" dxfId="940" priority="1247"/>
+    <cfRule type="duplicateValues" dxfId="930" priority="1247"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B803">
-    <cfRule type="duplicateValues" dxfId="939" priority="1246"/>
+    <cfRule type="duplicateValues" dxfId="929" priority="1246"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B803">
-    <cfRule type="duplicateValues" dxfId="938" priority="1248"/>
+    <cfRule type="duplicateValues" dxfId="928" priority="1248"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B804">
-    <cfRule type="duplicateValues" dxfId="937" priority="1243"/>
+    <cfRule type="duplicateValues" dxfId="927" priority="1243"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B804">
-    <cfRule type="duplicateValues" dxfId="936" priority="1244"/>
+    <cfRule type="duplicateValues" dxfId="926" priority="1244"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B804">
-    <cfRule type="duplicateValues" dxfId="935" priority="1245"/>
+    <cfRule type="duplicateValues" dxfId="925" priority="1245"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B805">
-    <cfRule type="duplicateValues" dxfId="934" priority="1238"/>
+    <cfRule type="duplicateValues" dxfId="924" priority="1238"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B805">
-    <cfRule type="duplicateValues" dxfId="933" priority="1239"/>
+    <cfRule type="duplicateValues" dxfId="923" priority="1239"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B805">
-    <cfRule type="duplicateValues" dxfId="932" priority="1237"/>
+    <cfRule type="duplicateValues" dxfId="922" priority="1237"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B806">
-    <cfRule type="duplicateValues" dxfId="931" priority="1231"/>
+    <cfRule type="duplicateValues" dxfId="921" priority="1231"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B806">
-    <cfRule type="duplicateValues" dxfId="930" priority="1232"/>
+    <cfRule type="duplicateValues" dxfId="920" priority="1232"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B806">
-    <cfRule type="duplicateValues" dxfId="929" priority="1233"/>
+    <cfRule type="duplicateValues" dxfId="919" priority="1233"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B807">
-    <cfRule type="duplicateValues" dxfId="928" priority="1229"/>
+    <cfRule type="duplicateValues" dxfId="918" priority="1229"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B807">
-    <cfRule type="duplicateValues" dxfId="927" priority="1230"/>
+    <cfRule type="duplicateValues" dxfId="917" priority="1230"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B807">
-    <cfRule type="duplicateValues" dxfId="926" priority="1228"/>
+    <cfRule type="duplicateValues" dxfId="916" priority="1228"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B809">
-    <cfRule type="duplicateValues" dxfId="925" priority="1223"/>
+    <cfRule type="duplicateValues" dxfId="915" priority="1223"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B809">
-    <cfRule type="duplicateValues" dxfId="924" priority="1224"/>
+    <cfRule type="duplicateValues" dxfId="914" priority="1224"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B810">
-    <cfRule type="duplicateValues" dxfId="923" priority="1221"/>
+    <cfRule type="duplicateValues" dxfId="913" priority="1221"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B810">
-    <cfRule type="duplicateValues" dxfId="922" priority="1220"/>
+    <cfRule type="duplicateValues" dxfId="912" priority="1220"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B810">
-    <cfRule type="duplicateValues" dxfId="921" priority="1222"/>
+    <cfRule type="duplicateValues" dxfId="911" priority="1222"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B811">
-    <cfRule type="duplicateValues" dxfId="920" priority="1214"/>
+    <cfRule type="duplicateValues" dxfId="910" priority="1214"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B811">
-    <cfRule type="duplicateValues" dxfId="919" priority="1215"/>
+    <cfRule type="duplicateValues" dxfId="909" priority="1215"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B811">
-    <cfRule type="duplicateValues" dxfId="918" priority="1216"/>
+    <cfRule type="duplicateValues" dxfId="908" priority="1216"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B812">
-    <cfRule type="duplicateValues" dxfId="917" priority="1211"/>
+    <cfRule type="duplicateValues" dxfId="907" priority="1211"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B812">
-    <cfRule type="duplicateValues" dxfId="916" priority="1212"/>
+    <cfRule type="duplicateValues" dxfId="906" priority="1212"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B812">
-    <cfRule type="duplicateValues" dxfId="915" priority="1213"/>
+    <cfRule type="duplicateValues" dxfId="905" priority="1213"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B813">
-    <cfRule type="duplicateValues" dxfId="914" priority="1205"/>
+    <cfRule type="duplicateValues" dxfId="904" priority="1205"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B813">
-    <cfRule type="duplicateValues" dxfId="913" priority="1206"/>
+    <cfRule type="duplicateValues" dxfId="903" priority="1206"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B813">
-    <cfRule type="duplicateValues" dxfId="912" priority="1207"/>
+    <cfRule type="duplicateValues" dxfId="902" priority="1207"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B814">
-    <cfRule type="duplicateValues" dxfId="911" priority="1190"/>
+    <cfRule type="duplicateValues" dxfId="901" priority="1190"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B814">
-    <cfRule type="duplicateValues" dxfId="910" priority="1191"/>
+    <cfRule type="duplicateValues" dxfId="900" priority="1191"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B814">
-    <cfRule type="duplicateValues" dxfId="909" priority="1192"/>
+    <cfRule type="duplicateValues" dxfId="899" priority="1192"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B815">
-    <cfRule type="duplicateValues" dxfId="908" priority="1184"/>
+    <cfRule type="duplicateValues" dxfId="898" priority="1184"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B815">
-    <cfRule type="duplicateValues" dxfId="907" priority="1185"/>
+    <cfRule type="duplicateValues" dxfId="897" priority="1185"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B815">
-    <cfRule type="duplicateValues" dxfId="906" priority="1186"/>
+    <cfRule type="duplicateValues" dxfId="896" priority="1186"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B816">
-    <cfRule type="duplicateValues" dxfId="905" priority="1178"/>
+    <cfRule type="duplicateValues" dxfId="895" priority="1178"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B816">
-    <cfRule type="duplicateValues" dxfId="904" priority="1179"/>
+    <cfRule type="duplicateValues" dxfId="894" priority="1179"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B816">
-    <cfRule type="duplicateValues" dxfId="903" priority="1180"/>
+    <cfRule type="duplicateValues" dxfId="893" priority="1180"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B817">
-    <cfRule type="duplicateValues" dxfId="902" priority="1176"/>
+    <cfRule type="duplicateValues" dxfId="892" priority="1176"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B817">
-    <cfRule type="duplicateValues" dxfId="901" priority="1177"/>
+    <cfRule type="duplicateValues" dxfId="891" priority="1177"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B817">
-    <cfRule type="duplicateValues" dxfId="900" priority="1175"/>
+    <cfRule type="duplicateValues" dxfId="890" priority="1175"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B818">
-    <cfRule type="duplicateValues" dxfId="899" priority="1166"/>
+    <cfRule type="duplicateValues" dxfId="889" priority="1166"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B818">
-    <cfRule type="duplicateValues" dxfId="898" priority="1167"/>
+    <cfRule type="duplicateValues" dxfId="888" priority="1167"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B818">
-    <cfRule type="duplicateValues" dxfId="897" priority="1168"/>
+    <cfRule type="duplicateValues" dxfId="887" priority="1168"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B819">
-    <cfRule type="duplicateValues" dxfId="896" priority="1158"/>
+    <cfRule type="duplicateValues" dxfId="886" priority="1158"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B819">
-    <cfRule type="duplicateValues" dxfId="895" priority="1157"/>
+    <cfRule type="duplicateValues" dxfId="885" priority="1157"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B819">
-    <cfRule type="duplicateValues" dxfId="894" priority="1159"/>
+    <cfRule type="duplicateValues" dxfId="884" priority="1159"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B820">
-    <cfRule type="duplicateValues" dxfId="893" priority="1155"/>
+    <cfRule type="duplicateValues" dxfId="883" priority="1155"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B820">
-    <cfRule type="duplicateValues" dxfId="892" priority="1154"/>
+    <cfRule type="duplicateValues" dxfId="882" priority="1154"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B820">
-    <cfRule type="duplicateValues" dxfId="891" priority="1156"/>
+    <cfRule type="duplicateValues" dxfId="881" priority="1156"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B821">
-    <cfRule type="duplicateValues" dxfId="890" priority="1149"/>
+    <cfRule type="duplicateValues" dxfId="880" priority="1149"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B821">
-    <cfRule type="duplicateValues" dxfId="889" priority="1150"/>
+    <cfRule type="duplicateValues" dxfId="879" priority="1150"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B821">
-    <cfRule type="duplicateValues" dxfId="888" priority="1148"/>
+    <cfRule type="duplicateValues" dxfId="878" priority="1148"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B822">
-    <cfRule type="duplicateValues" dxfId="887" priority="1142"/>
+    <cfRule type="duplicateValues" dxfId="877" priority="1142"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B822">
-    <cfRule type="duplicateValues" dxfId="886" priority="1143"/>
+    <cfRule type="duplicateValues" dxfId="876" priority="1143"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B822">
-    <cfRule type="duplicateValues" dxfId="885" priority="1144"/>
+    <cfRule type="duplicateValues" dxfId="875" priority="1144"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B823">
-    <cfRule type="duplicateValues" dxfId="884" priority="1139"/>
+    <cfRule type="duplicateValues" dxfId="874" priority="1139"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B823">
-    <cfRule type="duplicateValues" dxfId="883" priority="1140"/>
+    <cfRule type="duplicateValues" dxfId="873" priority="1140"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B823">
-    <cfRule type="duplicateValues" dxfId="882" priority="1141"/>
+    <cfRule type="duplicateValues" dxfId="872" priority="1141"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B825">
-    <cfRule type="duplicateValues" dxfId="881" priority="1136"/>
+    <cfRule type="duplicateValues" dxfId="871" priority="1136"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B825">
-    <cfRule type="duplicateValues" dxfId="880" priority="1137"/>
+    <cfRule type="duplicateValues" dxfId="870" priority="1137"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B825">
-    <cfRule type="duplicateValues" dxfId="879" priority="1138"/>
+    <cfRule type="duplicateValues" dxfId="869" priority="1138"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B826">
-    <cfRule type="duplicateValues" dxfId="878" priority="1133"/>
+    <cfRule type="duplicateValues" dxfId="868" priority="1133"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B826">
-    <cfRule type="duplicateValues" dxfId="877" priority="1134"/>
+    <cfRule type="duplicateValues" dxfId="867" priority="1134"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B826">
-    <cfRule type="duplicateValues" dxfId="876" priority="1135"/>
+    <cfRule type="duplicateValues" dxfId="866" priority="1135"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B828">
-    <cfRule type="duplicateValues" dxfId="875" priority="1132"/>
+    <cfRule type="duplicateValues" dxfId="865" priority="1132"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B828">
-    <cfRule type="duplicateValues" dxfId="874" priority="1131"/>
+    <cfRule type="duplicateValues" dxfId="864" priority="1131"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B828">
-    <cfRule type="duplicateValues" dxfId="873" priority="1130"/>
+    <cfRule type="duplicateValues" dxfId="863" priority="1130"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B829">
-    <cfRule type="duplicateValues" dxfId="872" priority="1127"/>
+    <cfRule type="duplicateValues" dxfId="862" priority="1127"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B829">
-    <cfRule type="duplicateValues" dxfId="871" priority="1128"/>
+    <cfRule type="duplicateValues" dxfId="861" priority="1128"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B829">
-    <cfRule type="duplicateValues" dxfId="870" priority="1129"/>
+    <cfRule type="duplicateValues" dxfId="860" priority="1129"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B830">
-    <cfRule type="duplicateValues" dxfId="869" priority="1124"/>
+    <cfRule type="duplicateValues" dxfId="859" priority="1124"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B830">
-    <cfRule type="duplicateValues" dxfId="868" priority="1125"/>
+    <cfRule type="duplicateValues" dxfId="858" priority="1125"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B830">
-    <cfRule type="duplicateValues" dxfId="867" priority="1126"/>
+    <cfRule type="duplicateValues" dxfId="857" priority="1126"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B833">
-    <cfRule type="duplicateValues" dxfId="866" priority="1122"/>
+    <cfRule type="duplicateValues" dxfId="856" priority="1122"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B833">
-    <cfRule type="duplicateValues" dxfId="865" priority="1123"/>
+    <cfRule type="duplicateValues" dxfId="855" priority="1123"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B833">
-    <cfRule type="duplicateValues" dxfId="864" priority="1121"/>
+    <cfRule type="duplicateValues" dxfId="854" priority="1121"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B831">
-    <cfRule type="duplicateValues" dxfId="863" priority="1119"/>
+    <cfRule type="duplicateValues" dxfId="853" priority="1119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B831">
-    <cfRule type="duplicateValues" dxfId="862" priority="1120"/>
+    <cfRule type="duplicateValues" dxfId="852" priority="1120"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B832">
-    <cfRule type="duplicateValues" dxfId="861" priority="1114"/>
+    <cfRule type="duplicateValues" dxfId="851" priority="1114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B832">
-    <cfRule type="duplicateValues" dxfId="860" priority="1115"/>
+    <cfRule type="duplicateValues" dxfId="850" priority="1115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B834">
-    <cfRule type="duplicateValues" dxfId="859" priority="1109"/>
+    <cfRule type="duplicateValues" dxfId="849" priority="1109"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B834">
-    <cfRule type="duplicateValues" dxfId="858" priority="1110"/>
+    <cfRule type="duplicateValues" dxfId="848" priority="1110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B834">
-    <cfRule type="duplicateValues" dxfId="857" priority="1108"/>
+    <cfRule type="duplicateValues" dxfId="847" priority="1108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B836">
-    <cfRule type="duplicateValues" dxfId="856" priority="1105"/>
+    <cfRule type="duplicateValues" dxfId="846" priority="1105"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B836">
-    <cfRule type="duplicateValues" dxfId="855" priority="1106"/>
+    <cfRule type="duplicateValues" dxfId="845" priority="1106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B836">
-    <cfRule type="duplicateValues" dxfId="854" priority="1107"/>
+    <cfRule type="duplicateValues" dxfId="844" priority="1107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B839">
-    <cfRule type="duplicateValues" dxfId="853" priority="1102"/>
+    <cfRule type="duplicateValues" dxfId="843" priority="1102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B839">
-    <cfRule type="duplicateValues" dxfId="852" priority="1103"/>
+    <cfRule type="duplicateValues" dxfId="842" priority="1103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B839">
-    <cfRule type="duplicateValues" dxfId="851" priority="1104"/>
+    <cfRule type="duplicateValues" dxfId="841" priority="1104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B840">
-    <cfRule type="duplicateValues" dxfId="850" priority="1099"/>
+    <cfRule type="duplicateValues" dxfId="840" priority="1099"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B840">
-    <cfRule type="duplicateValues" dxfId="849" priority="1100"/>
+    <cfRule type="duplicateValues" dxfId="839" priority="1100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B840">
-    <cfRule type="duplicateValues" dxfId="848" priority="1101"/>
+    <cfRule type="duplicateValues" dxfId="838" priority="1101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B841">
-    <cfRule type="duplicateValues" dxfId="847" priority="1096"/>
+    <cfRule type="duplicateValues" dxfId="837" priority="1096"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B841">
-    <cfRule type="duplicateValues" dxfId="846" priority="1097"/>
+    <cfRule type="duplicateValues" dxfId="836" priority="1097"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B841">
-    <cfRule type="duplicateValues" dxfId="845" priority="1098"/>
+    <cfRule type="duplicateValues" dxfId="835" priority="1098"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B842">
-    <cfRule type="duplicateValues" dxfId="844" priority="1084"/>
+    <cfRule type="duplicateValues" dxfId="834" priority="1084"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B842">
-    <cfRule type="duplicateValues" dxfId="843" priority="1085"/>
+    <cfRule type="duplicateValues" dxfId="833" priority="1085"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B842">
-    <cfRule type="duplicateValues" dxfId="842" priority="1086"/>
+    <cfRule type="duplicateValues" dxfId="832" priority="1086"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B843">
-    <cfRule type="duplicateValues" dxfId="841" priority="1079"/>
+    <cfRule type="duplicateValues" dxfId="831" priority="1079"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B843">
-    <cfRule type="duplicateValues" dxfId="840" priority="1080"/>
+    <cfRule type="duplicateValues" dxfId="830" priority="1080"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B846">
-    <cfRule type="duplicateValues" dxfId="839" priority="1073"/>
+    <cfRule type="duplicateValues" dxfId="829" priority="1073"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B846">
-    <cfRule type="duplicateValues" dxfId="838" priority="1074"/>
+    <cfRule type="duplicateValues" dxfId="828" priority="1074"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B846">
-    <cfRule type="duplicateValues" dxfId="837" priority="1075"/>
+    <cfRule type="duplicateValues" dxfId="827" priority="1075"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B847">
-    <cfRule type="duplicateValues" dxfId="836" priority="1067"/>
+    <cfRule type="duplicateValues" dxfId="826" priority="1067"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B847">
-    <cfRule type="duplicateValues" dxfId="835" priority="1068"/>
+    <cfRule type="duplicateValues" dxfId="825" priority="1068"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B847">
-    <cfRule type="duplicateValues" dxfId="834" priority="1069"/>
+    <cfRule type="duplicateValues" dxfId="824" priority="1069"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B848">
-    <cfRule type="duplicateValues" dxfId="833" priority="1064"/>
+    <cfRule type="duplicateValues" dxfId="823" priority="1064"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B848">
-    <cfRule type="duplicateValues" dxfId="832" priority="1065"/>
+    <cfRule type="duplicateValues" dxfId="822" priority="1065"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B848">
-    <cfRule type="duplicateValues" dxfId="831" priority="1066"/>
+    <cfRule type="duplicateValues" dxfId="821" priority="1066"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B849">
-    <cfRule type="duplicateValues" dxfId="830" priority="1058"/>
+    <cfRule type="duplicateValues" dxfId="820" priority="1058"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B849">
-    <cfRule type="duplicateValues" dxfId="829" priority="1059"/>
+    <cfRule type="duplicateValues" dxfId="819" priority="1059"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B849">
-    <cfRule type="duplicateValues" dxfId="828" priority="1060"/>
+    <cfRule type="duplicateValues" dxfId="818" priority="1060"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B853">
-    <cfRule type="duplicateValues" dxfId="827" priority="1049"/>
+    <cfRule type="duplicateValues" dxfId="817" priority="1049"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B853">
-    <cfRule type="duplicateValues" dxfId="826" priority="1050"/>
+    <cfRule type="duplicateValues" dxfId="816" priority="1050"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B853">
-    <cfRule type="duplicateValues" dxfId="825" priority="1051"/>
+    <cfRule type="duplicateValues" dxfId="815" priority="1051"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B854">
-    <cfRule type="duplicateValues" dxfId="824" priority="1046"/>
+    <cfRule type="duplicateValues" dxfId="814" priority="1046"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B854">
-    <cfRule type="duplicateValues" dxfId="823" priority="1047"/>
+    <cfRule type="duplicateValues" dxfId="813" priority="1047"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B854">
-    <cfRule type="duplicateValues" dxfId="822" priority="1048"/>
+    <cfRule type="duplicateValues" dxfId="812" priority="1048"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B855">
-    <cfRule type="duplicateValues" dxfId="821" priority="1040"/>
+    <cfRule type="duplicateValues" dxfId="811" priority="1040"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B855">
-    <cfRule type="duplicateValues" dxfId="820" priority="1041"/>
+    <cfRule type="duplicateValues" dxfId="810" priority="1041"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B855">
-    <cfRule type="duplicateValues" dxfId="819" priority="1042"/>
+    <cfRule type="duplicateValues" dxfId="809" priority="1042"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B856">
-    <cfRule type="duplicateValues" dxfId="818" priority="1031"/>
+    <cfRule type="duplicateValues" dxfId="808" priority="1031"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B856">
-    <cfRule type="duplicateValues" dxfId="817" priority="1032"/>
+    <cfRule type="duplicateValues" dxfId="807" priority="1032"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B856">
-    <cfRule type="duplicateValues" dxfId="816" priority="1033"/>
+    <cfRule type="duplicateValues" dxfId="806" priority="1033"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B857">
-    <cfRule type="duplicateValues" dxfId="815" priority="1028"/>
+    <cfRule type="duplicateValues" dxfId="805" priority="1028"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B857">
-    <cfRule type="duplicateValues" dxfId="814" priority="1029"/>
+    <cfRule type="duplicateValues" dxfId="804" priority="1029"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B857">
-    <cfRule type="duplicateValues" dxfId="813" priority="1030"/>
+    <cfRule type="duplicateValues" dxfId="803" priority="1030"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B858">
-    <cfRule type="duplicateValues" dxfId="812" priority="1022"/>
+    <cfRule type="duplicateValues" dxfId="802" priority="1022"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B858">
-    <cfRule type="duplicateValues" dxfId="811" priority="1023"/>
+    <cfRule type="duplicateValues" dxfId="801" priority="1023"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B858">
-    <cfRule type="duplicateValues" dxfId="810" priority="1024"/>
+    <cfRule type="duplicateValues" dxfId="800" priority="1024"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B859">
-    <cfRule type="duplicateValues" dxfId="809" priority="1020"/>
+    <cfRule type="duplicateValues" dxfId="799" priority="1020"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B859">
-    <cfRule type="duplicateValues" dxfId="808" priority="1021"/>
+    <cfRule type="duplicateValues" dxfId="798" priority="1021"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B859">
-    <cfRule type="duplicateValues" dxfId="807" priority="1019"/>
+    <cfRule type="duplicateValues" dxfId="797" priority="1019"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B860">
-    <cfRule type="duplicateValues" dxfId="806" priority="1016"/>
+    <cfRule type="duplicateValues" dxfId="796" priority="1016"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B860">
-    <cfRule type="duplicateValues" dxfId="805" priority="1017"/>
+    <cfRule type="duplicateValues" dxfId="795" priority="1017"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B860">
-    <cfRule type="duplicateValues" dxfId="804" priority="1018"/>
+    <cfRule type="duplicateValues" dxfId="794" priority="1018"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B861">
-    <cfRule type="duplicateValues" dxfId="803" priority="1014"/>
+    <cfRule type="duplicateValues" dxfId="793" priority="1014"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B861">
-    <cfRule type="duplicateValues" dxfId="802" priority="1013"/>
+    <cfRule type="duplicateValues" dxfId="792" priority="1013"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B861">
-    <cfRule type="duplicateValues" dxfId="801" priority="1015"/>
+    <cfRule type="duplicateValues" dxfId="791" priority="1015"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B862">
-    <cfRule type="duplicateValues" dxfId="800" priority="1004"/>
+    <cfRule type="duplicateValues" dxfId="790" priority="1004"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B862">
-    <cfRule type="duplicateValues" dxfId="799" priority="1005"/>
+    <cfRule type="duplicateValues" dxfId="789" priority="1005"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B862">
-    <cfRule type="duplicateValues" dxfId="798" priority="1006"/>
+    <cfRule type="duplicateValues" dxfId="788" priority="1006"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B863">
-    <cfRule type="duplicateValues" dxfId="797" priority="1001"/>
+    <cfRule type="duplicateValues" dxfId="787" priority="1001"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B863">
-    <cfRule type="duplicateValues" dxfId="796" priority="1002"/>
+    <cfRule type="duplicateValues" dxfId="786" priority="1002"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B863">
-    <cfRule type="duplicateValues" dxfId="795" priority="1003"/>
+    <cfRule type="duplicateValues" dxfId="785" priority="1003"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B864">
-    <cfRule type="duplicateValues" dxfId="794" priority="998"/>
+    <cfRule type="duplicateValues" dxfId="784" priority="998"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B864">
-    <cfRule type="duplicateValues" dxfId="793" priority="999"/>
+    <cfRule type="duplicateValues" dxfId="783" priority="999"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B864">
-    <cfRule type="duplicateValues" dxfId="792" priority="1000"/>
+    <cfRule type="duplicateValues" dxfId="782" priority="1000"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B865">
-    <cfRule type="duplicateValues" dxfId="791" priority="995"/>
+    <cfRule type="duplicateValues" dxfId="781" priority="995"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B865">
-    <cfRule type="duplicateValues" dxfId="790" priority="996"/>
+    <cfRule type="duplicateValues" dxfId="780" priority="996"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B865">
-    <cfRule type="duplicateValues" dxfId="789" priority="997"/>
+    <cfRule type="duplicateValues" dxfId="779" priority="997"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B866">
-    <cfRule type="duplicateValues" dxfId="788" priority="992"/>
+    <cfRule type="duplicateValues" dxfId="778" priority="992"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B866">
-    <cfRule type="duplicateValues" dxfId="787" priority="993"/>
+    <cfRule type="duplicateValues" dxfId="777" priority="993"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B866">
-    <cfRule type="duplicateValues" dxfId="786" priority="994"/>
+    <cfRule type="duplicateValues" dxfId="776" priority="994"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B867">
-    <cfRule type="duplicateValues" dxfId="785" priority="989"/>
+    <cfRule type="duplicateValues" dxfId="775" priority="989"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B867">
-    <cfRule type="duplicateValues" dxfId="784" priority="990"/>
+    <cfRule type="duplicateValues" dxfId="774" priority="990"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B867">
-    <cfRule type="duplicateValues" dxfId="783" priority="991"/>
+    <cfRule type="duplicateValues" dxfId="773" priority="991"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B868">
-    <cfRule type="duplicateValues" dxfId="782" priority="983"/>
+    <cfRule type="duplicateValues" dxfId="772" priority="983"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B868">
-    <cfRule type="duplicateValues" dxfId="781" priority="984"/>
+    <cfRule type="duplicateValues" dxfId="771" priority="984"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B868">
-    <cfRule type="duplicateValues" dxfId="780" priority="985"/>
+    <cfRule type="duplicateValues" dxfId="770" priority="985"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B869">
-    <cfRule type="duplicateValues" dxfId="779" priority="980"/>
+    <cfRule type="duplicateValues" dxfId="769" priority="980"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B869">
-    <cfRule type="duplicateValues" dxfId="778" priority="981"/>
+    <cfRule type="duplicateValues" dxfId="768" priority="981"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B869">
-    <cfRule type="duplicateValues" dxfId="777" priority="982"/>
+    <cfRule type="duplicateValues" dxfId="767" priority="982"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B870">
-    <cfRule type="duplicateValues" dxfId="776" priority="972"/>
+    <cfRule type="duplicateValues" dxfId="766" priority="972"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B870">
-    <cfRule type="duplicateValues" dxfId="775" priority="973"/>
+    <cfRule type="duplicateValues" dxfId="765" priority="973"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B871">
-    <cfRule type="duplicateValues" dxfId="774" priority="967"/>
+    <cfRule type="duplicateValues" dxfId="764" priority="967"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B871">
-    <cfRule type="duplicateValues" dxfId="773" priority="968"/>
+    <cfRule type="duplicateValues" dxfId="763" priority="968"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B872">
-    <cfRule type="duplicateValues" dxfId="772" priority="965"/>
+    <cfRule type="duplicateValues" dxfId="762" priority="965"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B872">
-    <cfRule type="duplicateValues" dxfId="771" priority="964"/>
+    <cfRule type="duplicateValues" dxfId="761" priority="964"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B872">
-    <cfRule type="duplicateValues" dxfId="770" priority="966"/>
+    <cfRule type="duplicateValues" dxfId="760" priority="966"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B873">
-    <cfRule type="duplicateValues" dxfId="769" priority="955"/>
+    <cfRule type="duplicateValues" dxfId="759" priority="955"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B873">
-    <cfRule type="duplicateValues" dxfId="768" priority="956"/>
+    <cfRule type="duplicateValues" dxfId="758" priority="956"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B873">
-    <cfRule type="duplicateValues" dxfId="767" priority="957"/>
+    <cfRule type="duplicateValues" dxfId="757" priority="957"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B875">
-    <cfRule type="duplicateValues" dxfId="766" priority="952"/>
+    <cfRule type="duplicateValues" dxfId="756" priority="952"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B875">
-    <cfRule type="duplicateValues" dxfId="765" priority="953"/>
+    <cfRule type="duplicateValues" dxfId="755" priority="953"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B875">
-    <cfRule type="duplicateValues" dxfId="764" priority="954"/>
+    <cfRule type="duplicateValues" dxfId="754" priority="954"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B876">
-    <cfRule type="duplicateValues" dxfId="763" priority="949"/>
+    <cfRule type="duplicateValues" dxfId="753" priority="949"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B876">
-    <cfRule type="duplicateValues" dxfId="762" priority="950"/>
+    <cfRule type="duplicateValues" dxfId="752" priority="950"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B876">
-    <cfRule type="duplicateValues" dxfId="761" priority="951"/>
+    <cfRule type="duplicateValues" dxfId="751" priority="951"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B878">
-    <cfRule type="duplicateValues" dxfId="760" priority="946"/>
+    <cfRule type="duplicateValues" dxfId="750" priority="946"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B878">
-    <cfRule type="duplicateValues" dxfId="759" priority="947"/>
+    <cfRule type="duplicateValues" dxfId="749" priority="947"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B878">
-    <cfRule type="duplicateValues" dxfId="758" priority="948"/>
+    <cfRule type="duplicateValues" dxfId="748" priority="948"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B879">
-    <cfRule type="duplicateValues" dxfId="757" priority="944"/>
+    <cfRule type="duplicateValues" dxfId="747" priority="944"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B879">
-    <cfRule type="duplicateValues" dxfId="756" priority="945"/>
+    <cfRule type="duplicateValues" dxfId="746" priority="945"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B881">
-    <cfRule type="duplicateValues" dxfId="755" priority="936"/>
+    <cfRule type="duplicateValues" dxfId="745" priority="936"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B881">
-    <cfRule type="duplicateValues" dxfId="754" priority="935"/>
+    <cfRule type="duplicateValues" dxfId="744" priority="935"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B881">
-    <cfRule type="duplicateValues" dxfId="753" priority="937"/>
+    <cfRule type="duplicateValues" dxfId="743" priority="937"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B882">
-    <cfRule type="duplicateValues" dxfId="752" priority="929"/>
+    <cfRule type="duplicateValues" dxfId="742" priority="929"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B882">
-    <cfRule type="duplicateValues" dxfId="751" priority="930"/>
+    <cfRule type="duplicateValues" dxfId="741" priority="930"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B882">
-    <cfRule type="duplicateValues" dxfId="750" priority="931"/>
+    <cfRule type="duplicateValues" dxfId="740" priority="931"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B883">
-    <cfRule type="duplicateValues" dxfId="749" priority="926"/>
+    <cfRule type="duplicateValues" dxfId="739" priority="926"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B883">
-    <cfRule type="duplicateValues" dxfId="748" priority="927"/>
+    <cfRule type="duplicateValues" dxfId="738" priority="927"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B883">
-    <cfRule type="duplicateValues" dxfId="747" priority="928"/>
+    <cfRule type="duplicateValues" dxfId="737" priority="928"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B884">
-    <cfRule type="duplicateValues" dxfId="746" priority="923"/>
+    <cfRule type="duplicateValues" dxfId="736" priority="923"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B884">
-    <cfRule type="duplicateValues" dxfId="745" priority="924"/>
+    <cfRule type="duplicateValues" dxfId="735" priority="924"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B884">
-    <cfRule type="duplicateValues" dxfId="744" priority="925"/>
+    <cfRule type="duplicateValues" dxfId="734" priority="925"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B885">
-    <cfRule type="duplicateValues" dxfId="743" priority="920"/>
+    <cfRule type="duplicateValues" dxfId="733" priority="920"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B885">
-    <cfRule type="duplicateValues" dxfId="742" priority="921"/>
+    <cfRule type="duplicateValues" dxfId="732" priority="921"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B885">
-    <cfRule type="duplicateValues" dxfId="741" priority="922"/>
+    <cfRule type="duplicateValues" dxfId="731" priority="922"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B886">
-    <cfRule type="duplicateValues" dxfId="740" priority="917"/>
+    <cfRule type="duplicateValues" dxfId="730" priority="917"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B886">
-    <cfRule type="duplicateValues" dxfId="739" priority="918"/>
+    <cfRule type="duplicateValues" dxfId="729" priority="918"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B886">
-    <cfRule type="duplicateValues" dxfId="738" priority="919"/>
+    <cfRule type="duplicateValues" dxfId="728" priority="919"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B887">
-    <cfRule type="duplicateValues" dxfId="737" priority="914"/>
+    <cfRule type="duplicateValues" dxfId="727" priority="914"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B887">
-    <cfRule type="duplicateValues" dxfId="736" priority="915"/>
+    <cfRule type="duplicateValues" dxfId="726" priority="915"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B887">
-    <cfRule type="duplicateValues" dxfId="735" priority="916"/>
+    <cfRule type="duplicateValues" dxfId="725" priority="916"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B888">
-    <cfRule type="duplicateValues" dxfId="734" priority="908"/>
+    <cfRule type="duplicateValues" dxfId="724" priority="908"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B888">
-    <cfRule type="duplicateValues" dxfId="733" priority="909"/>
+    <cfRule type="duplicateValues" dxfId="723" priority="909"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B888">
-    <cfRule type="duplicateValues" dxfId="732" priority="910"/>
+    <cfRule type="duplicateValues" dxfId="722" priority="910"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B889">
-    <cfRule type="duplicateValues" dxfId="731" priority="905"/>
+    <cfRule type="duplicateValues" dxfId="721" priority="905"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B889">
-    <cfRule type="duplicateValues" dxfId="730" priority="906"/>
+    <cfRule type="duplicateValues" dxfId="720" priority="906"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B889">
-    <cfRule type="duplicateValues" dxfId="729" priority="907"/>
+    <cfRule type="duplicateValues" dxfId="719" priority="907"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B890">
-    <cfRule type="duplicateValues" dxfId="728" priority="902"/>
+    <cfRule type="duplicateValues" dxfId="718" priority="902"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B890">
-    <cfRule type="duplicateValues" dxfId="727" priority="903"/>
+    <cfRule type="duplicateValues" dxfId="717" priority="903"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B890">
-    <cfRule type="duplicateValues" dxfId="726" priority="904"/>
+    <cfRule type="duplicateValues" dxfId="716" priority="904"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B891">
-    <cfRule type="duplicateValues" dxfId="725" priority="900"/>
+    <cfRule type="duplicateValues" dxfId="715" priority="900"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B891">
-    <cfRule type="duplicateValues" dxfId="724" priority="901"/>
+    <cfRule type="duplicateValues" dxfId="714" priority="901"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B892">
-    <cfRule type="duplicateValues" dxfId="723" priority="897"/>
+    <cfRule type="duplicateValues" dxfId="713" priority="897"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B892">
-    <cfRule type="duplicateValues" dxfId="722" priority="898"/>
+    <cfRule type="duplicateValues" dxfId="712" priority="898"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B892">
-    <cfRule type="duplicateValues" dxfId="721" priority="899"/>
+    <cfRule type="duplicateValues" dxfId="711" priority="899"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B897">
-    <cfRule type="duplicateValues" dxfId="720" priority="894"/>
+    <cfRule type="duplicateValues" dxfId="710" priority="894"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B897">
-    <cfRule type="duplicateValues" dxfId="719" priority="895"/>
+    <cfRule type="duplicateValues" dxfId="709" priority="895"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B897">
-    <cfRule type="duplicateValues" dxfId="718" priority="896"/>
+    <cfRule type="duplicateValues" dxfId="708" priority="896"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B898">
-    <cfRule type="duplicateValues" dxfId="717" priority="885"/>
+    <cfRule type="duplicateValues" dxfId="707" priority="885"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B898">
-    <cfRule type="duplicateValues" dxfId="716" priority="886"/>
+    <cfRule type="duplicateValues" dxfId="706" priority="886"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B898">
-    <cfRule type="duplicateValues" dxfId="715" priority="887"/>
+    <cfRule type="duplicateValues" dxfId="705" priority="887"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B899">
-    <cfRule type="duplicateValues" dxfId="714" priority="882"/>
+    <cfRule type="duplicateValues" dxfId="704" priority="882"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B899">
-    <cfRule type="duplicateValues" dxfId="713" priority="883"/>
+    <cfRule type="duplicateValues" dxfId="703" priority="883"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B899">
-    <cfRule type="duplicateValues" dxfId="712" priority="884"/>
+    <cfRule type="duplicateValues" dxfId="702" priority="884"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B900">
-    <cfRule type="duplicateValues" dxfId="711" priority="879"/>
+    <cfRule type="duplicateValues" dxfId="701" priority="879"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B900">
-    <cfRule type="duplicateValues" dxfId="710" priority="880"/>
+    <cfRule type="duplicateValues" dxfId="700" priority="880"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B900">
-    <cfRule type="duplicateValues" dxfId="709" priority="881"/>
+    <cfRule type="duplicateValues" dxfId="699" priority="881"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B901">
-    <cfRule type="duplicateValues" dxfId="708" priority="876"/>
+    <cfRule type="duplicateValues" dxfId="698" priority="876"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B901">
-    <cfRule type="duplicateValues" dxfId="707" priority="877"/>
+    <cfRule type="duplicateValues" dxfId="697" priority="877"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B901">
-    <cfRule type="duplicateValues" dxfId="706" priority="878"/>
+    <cfRule type="duplicateValues" dxfId="696" priority="878"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B902">
-    <cfRule type="duplicateValues" dxfId="705" priority="873"/>
+    <cfRule type="duplicateValues" dxfId="695" priority="873"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B902">
-    <cfRule type="duplicateValues" dxfId="704" priority="874"/>
+    <cfRule type="duplicateValues" dxfId="694" priority="874"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B902">
-    <cfRule type="duplicateValues" dxfId="703" priority="875"/>
+    <cfRule type="duplicateValues" dxfId="693" priority="875"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B903">
-    <cfRule type="duplicateValues" dxfId="702" priority="871"/>
+    <cfRule type="duplicateValues" dxfId="692" priority="871"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B903">
-    <cfRule type="duplicateValues" dxfId="701" priority="870"/>
+    <cfRule type="duplicateValues" dxfId="691" priority="870"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B903">
-    <cfRule type="duplicateValues" dxfId="700" priority="872"/>
+    <cfRule type="duplicateValues" dxfId="690" priority="872"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B904">
-    <cfRule type="duplicateValues" dxfId="699" priority="867"/>
+    <cfRule type="duplicateValues" dxfId="689" priority="867"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B904">
-    <cfRule type="duplicateValues" dxfId="698" priority="868"/>
+    <cfRule type="duplicateValues" dxfId="688" priority="868"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B904">
-    <cfRule type="duplicateValues" dxfId="697" priority="869"/>
+    <cfRule type="duplicateValues" dxfId="687" priority="869"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B905">
-    <cfRule type="duplicateValues" dxfId="696" priority="864"/>
+    <cfRule type="duplicateValues" dxfId="686" priority="864"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B905">
-    <cfRule type="duplicateValues" dxfId="695" priority="865"/>
+    <cfRule type="duplicateValues" dxfId="685" priority="865"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B905">
-    <cfRule type="duplicateValues" dxfId="694" priority="866"/>
+    <cfRule type="duplicateValues" dxfId="684" priority="866"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B906">
-    <cfRule type="duplicateValues" dxfId="693" priority="858"/>
+    <cfRule type="duplicateValues" dxfId="683" priority="858"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B906">
-    <cfRule type="duplicateValues" dxfId="692" priority="859"/>
+    <cfRule type="duplicateValues" dxfId="682" priority="859"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B906">
-    <cfRule type="duplicateValues" dxfId="691" priority="860"/>
+    <cfRule type="duplicateValues" dxfId="681" priority="860"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B908">
-    <cfRule type="duplicateValues" dxfId="690" priority="855"/>
+    <cfRule type="duplicateValues" dxfId="680" priority="855"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B908">
-    <cfRule type="duplicateValues" dxfId="689" priority="856"/>
+    <cfRule type="duplicateValues" dxfId="679" priority="856"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B908">
-    <cfRule type="duplicateValues" dxfId="688" priority="857"/>
+    <cfRule type="duplicateValues" dxfId="678" priority="857"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B910">
-    <cfRule type="duplicateValues" dxfId="687" priority="852"/>
+    <cfRule type="duplicateValues" dxfId="677" priority="852"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B910">
-    <cfRule type="duplicateValues" dxfId="686" priority="853"/>
+    <cfRule type="duplicateValues" dxfId="676" priority="853"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B910">
-    <cfRule type="duplicateValues" dxfId="685" priority="854"/>
+    <cfRule type="duplicateValues" dxfId="675" priority="854"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B913">
-    <cfRule type="duplicateValues" dxfId="684" priority="849"/>
+    <cfRule type="duplicateValues" dxfId="674" priority="849"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B913">
-    <cfRule type="duplicateValues" dxfId="683" priority="850"/>
+    <cfRule type="duplicateValues" dxfId="673" priority="850"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B913">
-    <cfRule type="duplicateValues" dxfId="682" priority="851"/>
+    <cfRule type="duplicateValues" dxfId="672" priority="851"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B914">
-    <cfRule type="duplicateValues" dxfId="681" priority="846"/>
+    <cfRule type="duplicateValues" dxfId="671" priority="846"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B914">
-    <cfRule type="duplicateValues" dxfId="680" priority="847"/>
+    <cfRule type="duplicateValues" dxfId="670" priority="847"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B914">
-    <cfRule type="duplicateValues" dxfId="679" priority="848"/>
+    <cfRule type="duplicateValues" dxfId="669" priority="848"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B915">
-    <cfRule type="duplicateValues" dxfId="678" priority="843"/>
+    <cfRule type="duplicateValues" dxfId="668" priority="843"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B915">
-    <cfRule type="duplicateValues" dxfId="677" priority="844"/>
+    <cfRule type="duplicateValues" dxfId="667" priority="844"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B915">
-    <cfRule type="duplicateValues" dxfId="676" priority="845"/>
+    <cfRule type="duplicateValues" dxfId="666" priority="845"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B917">
-    <cfRule type="duplicateValues" dxfId="675" priority="837"/>
+    <cfRule type="duplicateValues" dxfId="665" priority="837"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B917">
-    <cfRule type="duplicateValues" dxfId="674" priority="838"/>
+    <cfRule type="duplicateValues" dxfId="664" priority="838"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B917">
-    <cfRule type="duplicateValues" dxfId="673" priority="839"/>
+    <cfRule type="duplicateValues" dxfId="663" priority="839"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B918">
-    <cfRule type="duplicateValues" dxfId="672" priority="831"/>
+    <cfRule type="duplicateValues" dxfId="662" priority="831"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B918">
-    <cfRule type="duplicateValues" dxfId="671" priority="832"/>
+    <cfRule type="duplicateValues" dxfId="661" priority="832"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B918">
-    <cfRule type="duplicateValues" dxfId="670" priority="833"/>
+    <cfRule type="duplicateValues" dxfId="660" priority="833"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B920">
-    <cfRule type="duplicateValues" dxfId="669" priority="828"/>
+    <cfRule type="duplicateValues" dxfId="659" priority="828"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B920">
-    <cfRule type="duplicateValues" dxfId="668" priority="829"/>
+    <cfRule type="duplicateValues" dxfId="658" priority="829"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B920">
-    <cfRule type="duplicateValues" dxfId="667" priority="830"/>
+    <cfRule type="duplicateValues" dxfId="657" priority="830"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B921">
-    <cfRule type="duplicateValues" dxfId="666" priority="819"/>
+    <cfRule type="duplicateValues" dxfId="656" priority="819"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B921">
-    <cfRule type="duplicateValues" dxfId="665" priority="820"/>
+    <cfRule type="duplicateValues" dxfId="655" priority="820"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B921">
-    <cfRule type="duplicateValues" dxfId="664" priority="821"/>
+    <cfRule type="duplicateValues" dxfId="654" priority="821"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B922">
-    <cfRule type="duplicateValues" dxfId="663" priority="813"/>
+    <cfRule type="duplicateValues" dxfId="653" priority="813"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B922">
-    <cfRule type="duplicateValues" dxfId="662" priority="814"/>
+    <cfRule type="duplicateValues" dxfId="652" priority="814"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B922">
-    <cfRule type="duplicateValues" dxfId="661" priority="815"/>
+    <cfRule type="duplicateValues" dxfId="651" priority="815"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B923">
-    <cfRule type="duplicateValues" dxfId="660" priority="810"/>
+    <cfRule type="duplicateValues" dxfId="650" priority="810"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B923">
-    <cfRule type="duplicateValues" dxfId="659" priority="811"/>
+    <cfRule type="duplicateValues" dxfId="649" priority="811"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B923">
-    <cfRule type="duplicateValues" dxfId="658" priority="812"/>
+    <cfRule type="duplicateValues" dxfId="648" priority="812"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B926">
-    <cfRule type="duplicateValues" dxfId="657" priority="807"/>
+    <cfRule type="duplicateValues" dxfId="647" priority="807"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B926">
-    <cfRule type="duplicateValues" dxfId="656" priority="808"/>
+    <cfRule type="duplicateValues" dxfId="646" priority="808"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B926">
-    <cfRule type="duplicateValues" dxfId="655" priority="809"/>
+    <cfRule type="duplicateValues" dxfId="645" priority="809"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B927">
-    <cfRule type="duplicateValues" dxfId="654" priority="804"/>
+    <cfRule type="duplicateValues" dxfId="644" priority="804"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B927">
-    <cfRule type="duplicateValues" dxfId="653" priority="805"/>
+    <cfRule type="duplicateValues" dxfId="643" priority="805"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B927">
-    <cfRule type="duplicateValues" dxfId="652" priority="806"/>
+    <cfRule type="duplicateValues" dxfId="642" priority="806"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B928">
-    <cfRule type="duplicateValues" dxfId="651" priority="801"/>
+    <cfRule type="duplicateValues" dxfId="641" priority="801"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B928">
-    <cfRule type="duplicateValues" dxfId="650" priority="802"/>
+    <cfRule type="duplicateValues" dxfId="640" priority="802"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B928">
-    <cfRule type="duplicateValues" dxfId="649" priority="803"/>
+    <cfRule type="duplicateValues" dxfId="639" priority="803"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B930">
-    <cfRule type="duplicateValues" dxfId="648" priority="798"/>
+    <cfRule type="duplicateValues" dxfId="638" priority="798"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B930">
-    <cfRule type="duplicateValues" dxfId="647" priority="797"/>
+    <cfRule type="duplicateValues" dxfId="637" priority="797"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B930">
-    <cfRule type="duplicateValues" dxfId="646" priority="796"/>
+    <cfRule type="duplicateValues" dxfId="636" priority="796"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B932">
-    <cfRule type="duplicateValues" dxfId="645" priority="787"/>
+    <cfRule type="duplicateValues" dxfId="635" priority="787"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B932">
-    <cfRule type="duplicateValues" dxfId="644" priority="788"/>
+    <cfRule type="duplicateValues" dxfId="634" priority="788"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B932">
-    <cfRule type="duplicateValues" dxfId="643" priority="789"/>
+    <cfRule type="duplicateValues" dxfId="633" priority="789"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B937">
-    <cfRule type="duplicateValues" dxfId="642" priority="776"/>
+    <cfRule type="duplicateValues" dxfId="632" priority="776"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B937">
-    <cfRule type="duplicateValues" dxfId="641" priority="777"/>
+    <cfRule type="duplicateValues" dxfId="631" priority="777"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B937">
-    <cfRule type="duplicateValues" dxfId="640" priority="778"/>
+    <cfRule type="duplicateValues" dxfId="630" priority="778"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B935">
-    <cfRule type="duplicateValues" dxfId="639" priority="773"/>
+    <cfRule type="duplicateValues" dxfId="629" priority="773"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B935">
-    <cfRule type="duplicateValues" dxfId="638" priority="774"/>
+    <cfRule type="duplicateValues" dxfId="628" priority="774"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B935">
-    <cfRule type="duplicateValues" dxfId="637" priority="775"/>
+    <cfRule type="duplicateValues" dxfId="627" priority="775"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B936">
-    <cfRule type="duplicateValues" dxfId="636" priority="770"/>
+    <cfRule type="duplicateValues" dxfId="626" priority="770"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B936">
-    <cfRule type="duplicateValues" dxfId="635" priority="771"/>
+    <cfRule type="duplicateValues" dxfId="625" priority="771"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B936">
-    <cfRule type="duplicateValues" dxfId="634" priority="772"/>
+    <cfRule type="duplicateValues" dxfId="624" priority="772"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B938">
-    <cfRule type="duplicateValues" dxfId="633" priority="768"/>
+    <cfRule type="duplicateValues" dxfId="623" priority="768"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B938">
-    <cfRule type="duplicateValues" dxfId="632" priority="767"/>
+    <cfRule type="duplicateValues" dxfId="622" priority="767"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B938">
-    <cfRule type="duplicateValues" dxfId="631" priority="769"/>
+    <cfRule type="duplicateValues" dxfId="621" priority="769"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B939">
-    <cfRule type="duplicateValues" dxfId="630" priority="761"/>
+    <cfRule type="duplicateValues" dxfId="620" priority="761"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B939">
-    <cfRule type="duplicateValues" dxfId="629" priority="762"/>
+    <cfRule type="duplicateValues" dxfId="619" priority="762"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B939">
-    <cfRule type="duplicateValues" dxfId="628" priority="763"/>
+    <cfRule type="duplicateValues" dxfId="618" priority="763"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B940">
-    <cfRule type="duplicateValues" dxfId="627" priority="755"/>
+    <cfRule type="duplicateValues" dxfId="617" priority="755"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B940">
-    <cfRule type="duplicateValues" dxfId="626" priority="756"/>
+    <cfRule type="duplicateValues" dxfId="616" priority="756"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B940">
-    <cfRule type="duplicateValues" dxfId="625" priority="757"/>
+    <cfRule type="duplicateValues" dxfId="615" priority="757"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B942">
-    <cfRule type="duplicateValues" dxfId="624" priority="752"/>
+    <cfRule type="duplicateValues" dxfId="614" priority="752"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B942">
-    <cfRule type="duplicateValues" dxfId="623" priority="753"/>
+    <cfRule type="duplicateValues" dxfId="613" priority="753"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B942">
-    <cfRule type="duplicateValues" dxfId="622" priority="754"/>
+    <cfRule type="duplicateValues" dxfId="612" priority="754"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B941">
-    <cfRule type="duplicateValues" dxfId="621" priority="746"/>
+    <cfRule type="duplicateValues" dxfId="611" priority="746"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B941">
-    <cfRule type="duplicateValues" dxfId="620" priority="747"/>
+    <cfRule type="duplicateValues" dxfId="610" priority="747"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B941">
-    <cfRule type="duplicateValues" dxfId="619" priority="748"/>
+    <cfRule type="duplicateValues" dxfId="609" priority="748"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B943">
-    <cfRule type="duplicateValues" dxfId="618" priority="740"/>
+    <cfRule type="duplicateValues" dxfId="608" priority="740"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B943">
-    <cfRule type="duplicateValues" dxfId="617" priority="741"/>
+    <cfRule type="duplicateValues" dxfId="607" priority="741"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B943">
-    <cfRule type="duplicateValues" dxfId="616" priority="742"/>
+    <cfRule type="duplicateValues" dxfId="606" priority="742"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B944">
-    <cfRule type="duplicateValues" dxfId="615" priority="737"/>
+    <cfRule type="duplicateValues" dxfId="605" priority="737"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B944">
-    <cfRule type="duplicateValues" dxfId="614" priority="738"/>
+    <cfRule type="duplicateValues" dxfId="604" priority="738"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B944">
-    <cfRule type="duplicateValues" dxfId="613" priority="739"/>
+    <cfRule type="duplicateValues" dxfId="603" priority="739"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B946">
-    <cfRule type="duplicateValues" dxfId="612" priority="734"/>
+    <cfRule type="duplicateValues" dxfId="602" priority="734"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B946">
-    <cfRule type="duplicateValues" dxfId="611" priority="735"/>
+    <cfRule type="duplicateValues" dxfId="601" priority="735"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B946">
-    <cfRule type="duplicateValues" dxfId="610" priority="736"/>
+    <cfRule type="duplicateValues" dxfId="600" priority="736"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B948">
-    <cfRule type="duplicateValues" dxfId="609" priority="731"/>
+    <cfRule type="duplicateValues" dxfId="599" priority="731"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B948">
-    <cfRule type="duplicateValues" dxfId="608" priority="732"/>
+    <cfRule type="duplicateValues" dxfId="598" priority="732"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B948">
-    <cfRule type="duplicateValues" dxfId="607" priority="733"/>
+    <cfRule type="duplicateValues" dxfId="597" priority="733"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B950">
-    <cfRule type="duplicateValues" dxfId="606" priority="728"/>
+    <cfRule type="duplicateValues" dxfId="596" priority="728"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B950">
-    <cfRule type="duplicateValues" dxfId="605" priority="729"/>
+    <cfRule type="duplicateValues" dxfId="595" priority="729"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B950">
-    <cfRule type="duplicateValues" dxfId="604" priority="730"/>
+    <cfRule type="duplicateValues" dxfId="594" priority="730"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B951">
-    <cfRule type="duplicateValues" dxfId="603" priority="726"/>
+    <cfRule type="duplicateValues" dxfId="593" priority="726"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B951">
-    <cfRule type="duplicateValues" dxfId="602" priority="725"/>
+    <cfRule type="duplicateValues" dxfId="592" priority="725"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B951">
-    <cfRule type="duplicateValues" dxfId="601" priority="727"/>
+    <cfRule type="duplicateValues" dxfId="591" priority="727"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B953">
-    <cfRule type="duplicateValues" dxfId="600" priority="722"/>
+    <cfRule type="duplicateValues" dxfId="590" priority="722"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B953">
-    <cfRule type="duplicateValues" dxfId="599" priority="723"/>
+    <cfRule type="duplicateValues" dxfId="589" priority="723"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B953">
-    <cfRule type="duplicateValues" dxfId="598" priority="724"/>
+    <cfRule type="duplicateValues" dxfId="588" priority="724"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B952">
-    <cfRule type="duplicateValues" dxfId="597" priority="719"/>
+    <cfRule type="duplicateValues" dxfId="587" priority="719"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B952">
-    <cfRule type="duplicateValues" dxfId="596" priority="720"/>
+    <cfRule type="duplicateValues" dxfId="586" priority="720"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B952">
-    <cfRule type="duplicateValues" dxfId="595" priority="721"/>
+    <cfRule type="duplicateValues" dxfId="585" priority="721"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B954">
-    <cfRule type="duplicateValues" dxfId="594" priority="716"/>
+    <cfRule type="duplicateValues" dxfId="584" priority="716"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B954">
-    <cfRule type="duplicateValues" dxfId="593" priority="717"/>
+    <cfRule type="duplicateValues" dxfId="583" priority="717"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B954">
-    <cfRule type="duplicateValues" dxfId="592" priority="718"/>
+    <cfRule type="duplicateValues" dxfId="582" priority="718"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B955">
-    <cfRule type="duplicateValues" dxfId="591" priority="713"/>
+    <cfRule type="duplicateValues" dxfId="581" priority="713"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B955">
-    <cfRule type="duplicateValues" dxfId="590" priority="714"/>
+    <cfRule type="duplicateValues" dxfId="580" priority="714"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B955">
-    <cfRule type="duplicateValues" dxfId="589" priority="715"/>
+    <cfRule type="duplicateValues" dxfId="579" priority="715"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B956">
-    <cfRule type="duplicateValues" dxfId="588" priority="707"/>
+    <cfRule type="duplicateValues" dxfId="578" priority="707"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B956">
-    <cfRule type="duplicateValues" dxfId="587" priority="708"/>
+    <cfRule type="duplicateValues" dxfId="577" priority="708"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B956">
-    <cfRule type="duplicateValues" dxfId="586" priority="709"/>
+    <cfRule type="duplicateValues" dxfId="576" priority="709"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B957">
-    <cfRule type="duplicateValues" dxfId="585" priority="701"/>
+    <cfRule type="duplicateValues" dxfId="575" priority="701"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B957">
-    <cfRule type="duplicateValues" dxfId="584" priority="702"/>
+    <cfRule type="duplicateValues" dxfId="574" priority="702"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B957">
-    <cfRule type="duplicateValues" dxfId="583" priority="703"/>
+    <cfRule type="duplicateValues" dxfId="573" priority="703"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B958">
-    <cfRule type="duplicateValues" dxfId="582" priority="698"/>
+    <cfRule type="duplicateValues" dxfId="572" priority="698"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B958">
-    <cfRule type="duplicateValues" dxfId="581" priority="699"/>
+    <cfRule type="duplicateValues" dxfId="571" priority="699"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B958">
-    <cfRule type="duplicateValues" dxfId="580" priority="700"/>
+    <cfRule type="duplicateValues" dxfId="570" priority="700"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B959">
-    <cfRule type="duplicateValues" dxfId="579" priority="689"/>
+    <cfRule type="duplicateValues" dxfId="569" priority="689"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B959">
-    <cfRule type="duplicateValues" dxfId="578" priority="690"/>
+    <cfRule type="duplicateValues" dxfId="568" priority="690"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B959">
-    <cfRule type="duplicateValues" dxfId="577" priority="691"/>
+    <cfRule type="duplicateValues" dxfId="567" priority="691"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B960">
-    <cfRule type="duplicateValues" dxfId="576" priority="686"/>
+    <cfRule type="duplicateValues" dxfId="566" priority="686"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B960">
-    <cfRule type="duplicateValues" dxfId="575" priority="687"/>
+    <cfRule type="duplicateValues" dxfId="565" priority="687"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B960">
-    <cfRule type="duplicateValues" dxfId="574" priority="688"/>
+    <cfRule type="duplicateValues" dxfId="564" priority="688"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B961">
-    <cfRule type="duplicateValues" dxfId="573" priority="685"/>
+    <cfRule type="duplicateValues" dxfId="563" priority="685"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B961">
-    <cfRule type="duplicateValues" dxfId="572" priority="684"/>
+    <cfRule type="duplicateValues" dxfId="562" priority="684"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B961">
-    <cfRule type="duplicateValues" dxfId="571" priority="683"/>
+    <cfRule type="duplicateValues" dxfId="561" priority="683"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B962">
-    <cfRule type="duplicateValues" dxfId="570" priority="674"/>
+    <cfRule type="duplicateValues" dxfId="560" priority="674"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B962">
-    <cfRule type="duplicateValues" dxfId="569" priority="675"/>
+    <cfRule type="duplicateValues" dxfId="559" priority="675"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B962">
-    <cfRule type="duplicateValues" dxfId="568" priority="676"/>
+    <cfRule type="duplicateValues" dxfId="558" priority="676"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B963">
-    <cfRule type="duplicateValues" dxfId="567" priority="665"/>
+    <cfRule type="duplicateValues" dxfId="557" priority="665"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B963">
-    <cfRule type="duplicateValues" dxfId="566" priority="666"/>
+    <cfRule type="duplicateValues" dxfId="556" priority="666"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B963">
-    <cfRule type="duplicateValues" dxfId="565" priority="667"/>
+    <cfRule type="duplicateValues" dxfId="555" priority="667"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B964">
-    <cfRule type="duplicateValues" dxfId="564" priority="662"/>
+    <cfRule type="duplicateValues" dxfId="554" priority="662"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B964">
-    <cfRule type="duplicateValues" dxfId="563" priority="663"/>
+    <cfRule type="duplicateValues" dxfId="553" priority="663"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B964">
-    <cfRule type="duplicateValues" dxfId="562" priority="664"/>
+    <cfRule type="duplicateValues" dxfId="552" priority="664"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B965">
-    <cfRule type="duplicateValues" dxfId="561" priority="660"/>
+    <cfRule type="duplicateValues" dxfId="551" priority="660"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B965">
-    <cfRule type="duplicateValues" dxfId="560" priority="659"/>
+    <cfRule type="duplicateValues" dxfId="550" priority="659"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B965">
-    <cfRule type="duplicateValues" dxfId="559" priority="661"/>
+    <cfRule type="duplicateValues" dxfId="549" priority="661"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B949">
-    <cfRule type="duplicateValues" dxfId="558" priority="656"/>
+    <cfRule type="duplicateValues" dxfId="548" priority="656"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B949">
-    <cfRule type="duplicateValues" dxfId="557" priority="657"/>
+    <cfRule type="duplicateValues" dxfId="547" priority="657"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B949">
-    <cfRule type="duplicateValues" dxfId="556" priority="658"/>
+    <cfRule type="duplicateValues" dxfId="546" priority="658"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B967">
-    <cfRule type="duplicateValues" dxfId="555" priority="651"/>
+    <cfRule type="duplicateValues" dxfId="545" priority="651"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B967">
-    <cfRule type="duplicateValues" dxfId="554" priority="650"/>
+    <cfRule type="duplicateValues" dxfId="544" priority="650"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B967">
-    <cfRule type="duplicateValues" dxfId="553" priority="652"/>
+    <cfRule type="duplicateValues" dxfId="543" priority="652"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B968">
-    <cfRule type="duplicateValues" dxfId="552" priority="647"/>
+    <cfRule type="duplicateValues" dxfId="542" priority="647"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B968">
-    <cfRule type="duplicateValues" dxfId="551" priority="648"/>
+    <cfRule type="duplicateValues" dxfId="541" priority="648"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B968">
-    <cfRule type="duplicateValues" dxfId="550" priority="649"/>
+    <cfRule type="duplicateValues" dxfId="540" priority="649"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B969">
-    <cfRule type="duplicateValues" dxfId="549" priority="638"/>
+    <cfRule type="duplicateValues" dxfId="539" priority="638"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B969">
-    <cfRule type="duplicateValues" dxfId="548" priority="639"/>
+    <cfRule type="duplicateValues" dxfId="538" priority="639"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B969">
-    <cfRule type="duplicateValues" dxfId="547" priority="640"/>
+    <cfRule type="duplicateValues" dxfId="537" priority="640"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B970">
-    <cfRule type="duplicateValues" dxfId="546" priority="635"/>
+    <cfRule type="duplicateValues" dxfId="536" priority="635"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B970">
-    <cfRule type="duplicateValues" dxfId="545" priority="636"/>
+    <cfRule type="duplicateValues" dxfId="535" priority="636"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B970">
-    <cfRule type="duplicateValues" dxfId="544" priority="637"/>
+    <cfRule type="duplicateValues" dxfId="534" priority="637"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B971">
-    <cfRule type="duplicateValues" dxfId="543" priority="630"/>
+    <cfRule type="duplicateValues" dxfId="533" priority="630"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B971">
-    <cfRule type="duplicateValues" dxfId="542" priority="631"/>
+    <cfRule type="duplicateValues" dxfId="532" priority="631"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B971">
-    <cfRule type="duplicateValues" dxfId="541" priority="632"/>
+    <cfRule type="duplicateValues" dxfId="531" priority="632"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B972">
-    <cfRule type="duplicateValues" dxfId="540" priority="627"/>
+    <cfRule type="duplicateValues" dxfId="530" priority="627"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B972">
-    <cfRule type="duplicateValues" dxfId="539" priority="628"/>
+    <cfRule type="duplicateValues" dxfId="529" priority="628"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B972">
-    <cfRule type="duplicateValues" dxfId="538" priority="629"/>
+    <cfRule type="duplicateValues" dxfId="528" priority="629"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B973">
-    <cfRule type="duplicateValues" dxfId="537" priority="621"/>
+    <cfRule type="duplicateValues" dxfId="527" priority="621"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B973">
-    <cfRule type="duplicateValues" dxfId="536" priority="622"/>
+    <cfRule type="duplicateValues" dxfId="526" priority="622"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B973">
-    <cfRule type="duplicateValues" dxfId="535" priority="623"/>
+    <cfRule type="duplicateValues" dxfId="525" priority="623"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B974">
-    <cfRule type="duplicateValues" dxfId="534" priority="615"/>
+    <cfRule type="duplicateValues" dxfId="524" priority="615"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B974">
-    <cfRule type="duplicateValues" dxfId="533" priority="616"/>
+    <cfRule type="duplicateValues" dxfId="523" priority="616"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B974">
-    <cfRule type="duplicateValues" dxfId="532" priority="617"/>
+    <cfRule type="duplicateValues" dxfId="522" priority="617"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B976">
-    <cfRule type="duplicateValues" dxfId="531" priority="612"/>
+    <cfRule type="duplicateValues" dxfId="521" priority="612"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B976">
-    <cfRule type="duplicateValues" dxfId="530" priority="613"/>
+    <cfRule type="duplicateValues" dxfId="520" priority="613"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B976">
-    <cfRule type="duplicateValues" dxfId="529" priority="614"/>
+    <cfRule type="duplicateValues" dxfId="519" priority="614"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B975">
-    <cfRule type="duplicateValues" dxfId="528" priority="609"/>
+    <cfRule type="duplicateValues" dxfId="518" priority="609"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B975">
-    <cfRule type="duplicateValues" dxfId="527" priority="610"/>
+    <cfRule type="duplicateValues" dxfId="517" priority="610"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B975">
-    <cfRule type="duplicateValues" dxfId="526" priority="611"/>
+    <cfRule type="duplicateValues" dxfId="516" priority="611"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B978">
-    <cfRule type="duplicateValues" dxfId="525" priority="606"/>
+    <cfRule type="duplicateValues" dxfId="515" priority="606"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B978">
-    <cfRule type="duplicateValues" dxfId="524" priority="607"/>
+    <cfRule type="duplicateValues" dxfId="514" priority="607"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B978">
-    <cfRule type="duplicateValues" dxfId="523" priority="608"/>
+    <cfRule type="duplicateValues" dxfId="513" priority="608"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B977">
-    <cfRule type="duplicateValues" dxfId="522" priority="603"/>
+    <cfRule type="duplicateValues" dxfId="512" priority="603"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B977">
-    <cfRule type="duplicateValues" dxfId="521" priority="604"/>
+    <cfRule type="duplicateValues" dxfId="511" priority="604"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B977">
-    <cfRule type="duplicateValues" dxfId="520" priority="605"/>
+    <cfRule type="duplicateValues" dxfId="510" priority="605"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B979">
-    <cfRule type="duplicateValues" dxfId="519" priority="594"/>
+    <cfRule type="duplicateValues" dxfId="509" priority="594"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B979">
-    <cfRule type="duplicateValues" dxfId="518" priority="595"/>
+    <cfRule type="duplicateValues" dxfId="508" priority="595"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B979">
-    <cfRule type="duplicateValues" dxfId="517" priority="596"/>
+    <cfRule type="duplicateValues" dxfId="507" priority="596"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B981">
-    <cfRule type="duplicateValues" dxfId="516" priority="591"/>
+    <cfRule type="duplicateValues" dxfId="506" priority="591"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B981">
-    <cfRule type="duplicateValues" dxfId="515" priority="592"/>
+    <cfRule type="duplicateValues" dxfId="505" priority="592"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B981">
-    <cfRule type="duplicateValues" dxfId="514" priority="593"/>
+    <cfRule type="duplicateValues" dxfId="504" priority="593"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B982">
-    <cfRule type="duplicateValues" dxfId="513" priority="588"/>
+    <cfRule type="duplicateValues" dxfId="503" priority="588"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B982">
-    <cfRule type="duplicateValues" dxfId="512" priority="589"/>
+    <cfRule type="duplicateValues" dxfId="502" priority="589"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B982">
-    <cfRule type="duplicateValues" dxfId="511" priority="590"/>
+    <cfRule type="duplicateValues" dxfId="501" priority="590"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B983">
-    <cfRule type="duplicateValues" dxfId="510" priority="585"/>
+    <cfRule type="duplicateValues" dxfId="500" priority="585"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B983">
-    <cfRule type="duplicateValues" dxfId="509" priority="586"/>
+    <cfRule type="duplicateValues" dxfId="499" priority="586"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B983">
-    <cfRule type="duplicateValues" dxfId="508" priority="587"/>
+    <cfRule type="duplicateValues" dxfId="498" priority="587"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B984">
-    <cfRule type="duplicateValues" dxfId="507" priority="579"/>
+    <cfRule type="duplicateValues" dxfId="497" priority="579"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B984">
-    <cfRule type="duplicateValues" dxfId="506" priority="580"/>
+    <cfRule type="duplicateValues" dxfId="496" priority="580"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B984">
-    <cfRule type="duplicateValues" dxfId="505" priority="581"/>
+    <cfRule type="duplicateValues" dxfId="495" priority="581"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B985">
-    <cfRule type="duplicateValues" dxfId="504" priority="576"/>
+    <cfRule type="duplicateValues" dxfId="494" priority="576"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B985">
-    <cfRule type="duplicateValues" dxfId="503" priority="577"/>
+    <cfRule type="duplicateValues" dxfId="493" priority="577"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B985">
-    <cfRule type="duplicateValues" dxfId="502" priority="578"/>
+    <cfRule type="duplicateValues" dxfId="492" priority="578"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B986">
-    <cfRule type="duplicateValues" dxfId="501" priority="574"/>
+    <cfRule type="duplicateValues" dxfId="491" priority="574"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B986">
-    <cfRule type="duplicateValues" dxfId="500" priority="575"/>
+    <cfRule type="duplicateValues" dxfId="490" priority="575"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B987">
-    <cfRule type="duplicateValues" dxfId="499" priority="571"/>
+    <cfRule type="duplicateValues" dxfId="489" priority="571"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B987">
-    <cfRule type="duplicateValues" dxfId="498" priority="572"/>
+    <cfRule type="duplicateValues" dxfId="488" priority="572"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B987">
-    <cfRule type="duplicateValues" dxfId="497" priority="573"/>
+    <cfRule type="duplicateValues" dxfId="487" priority="573"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B988">
-    <cfRule type="duplicateValues" dxfId="496" priority="568"/>
+    <cfRule type="duplicateValues" dxfId="486" priority="568"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B988">
-    <cfRule type="duplicateValues" dxfId="495" priority="569"/>
+    <cfRule type="duplicateValues" dxfId="485" priority="569"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B988">
-    <cfRule type="duplicateValues" dxfId="494" priority="570"/>
+    <cfRule type="duplicateValues" dxfId="484" priority="570"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B989">
-    <cfRule type="duplicateValues" dxfId="493" priority="559"/>
+    <cfRule type="duplicateValues" dxfId="483" priority="559"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B989">
-    <cfRule type="duplicateValues" dxfId="492" priority="560"/>
+    <cfRule type="duplicateValues" dxfId="482" priority="560"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B989">
-    <cfRule type="duplicateValues" dxfId="491" priority="561"/>
+    <cfRule type="duplicateValues" dxfId="481" priority="561"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B991">
-    <cfRule type="duplicateValues" dxfId="490" priority="558"/>
+    <cfRule type="duplicateValues" dxfId="480" priority="558"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B991">
-    <cfRule type="duplicateValues" dxfId="489" priority="557"/>
+    <cfRule type="duplicateValues" dxfId="479" priority="557"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B991">
-    <cfRule type="duplicateValues" dxfId="488" priority="556"/>
+    <cfRule type="duplicateValues" dxfId="478" priority="556"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B990">
-    <cfRule type="duplicateValues" dxfId="487" priority="547"/>
+    <cfRule type="duplicateValues" dxfId="477" priority="547"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B990">
-    <cfRule type="duplicateValues" dxfId="486" priority="548"/>
+    <cfRule type="duplicateValues" dxfId="476" priority="548"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B990">
-    <cfRule type="duplicateValues" dxfId="485" priority="549"/>
+    <cfRule type="duplicateValues" dxfId="475" priority="549"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B992">
-    <cfRule type="duplicateValues" dxfId="484" priority="544"/>
+    <cfRule type="duplicateValues" dxfId="474" priority="544"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B992">
-    <cfRule type="duplicateValues" dxfId="483" priority="545"/>
+    <cfRule type="duplicateValues" dxfId="473" priority="545"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B992">
-    <cfRule type="duplicateValues" dxfId="482" priority="546"/>
+    <cfRule type="duplicateValues" dxfId="472" priority="546"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B993">
-    <cfRule type="duplicateValues" dxfId="481" priority="538"/>
+    <cfRule type="duplicateValues" dxfId="471" priority="538"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B993">
-    <cfRule type="duplicateValues" dxfId="480" priority="539"/>
+    <cfRule type="duplicateValues" dxfId="470" priority="539"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B993">
-    <cfRule type="duplicateValues" dxfId="479" priority="540"/>
+    <cfRule type="duplicateValues" dxfId="469" priority="540"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B994">
-    <cfRule type="duplicateValues" dxfId="478" priority="529"/>
+    <cfRule type="duplicateValues" dxfId="468" priority="529"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B994">
-    <cfRule type="duplicateValues" dxfId="477" priority="530"/>
+    <cfRule type="duplicateValues" dxfId="467" priority="530"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B994">
-    <cfRule type="duplicateValues" dxfId="476" priority="531"/>
+    <cfRule type="duplicateValues" dxfId="466" priority="531"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B995">
-    <cfRule type="duplicateValues" dxfId="475" priority="526"/>
+    <cfRule type="duplicateValues" dxfId="465" priority="526"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B995">
-    <cfRule type="duplicateValues" dxfId="474" priority="527"/>
+    <cfRule type="duplicateValues" dxfId="464" priority="527"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B995">
-    <cfRule type="duplicateValues" dxfId="473" priority="528"/>
+    <cfRule type="duplicateValues" dxfId="463" priority="528"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B998">
-    <cfRule type="duplicateValues" dxfId="472" priority="523"/>
+    <cfRule type="duplicateValues" dxfId="462" priority="523"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B998">
-    <cfRule type="duplicateValues" dxfId="471" priority="524"/>
+    <cfRule type="duplicateValues" dxfId="461" priority="524"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B998">
-    <cfRule type="duplicateValues" dxfId="470" priority="525"/>
+    <cfRule type="duplicateValues" dxfId="460" priority="525"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1000">
-    <cfRule type="duplicateValues" dxfId="469" priority="520"/>
+    <cfRule type="duplicateValues" dxfId="459" priority="520"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1000">
-    <cfRule type="duplicateValues" dxfId="468" priority="521"/>
+    <cfRule type="duplicateValues" dxfId="458" priority="521"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1000">
-    <cfRule type="duplicateValues" dxfId="467" priority="522"/>
+    <cfRule type="duplicateValues" dxfId="457" priority="522"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1003">
-    <cfRule type="duplicateValues" dxfId="466" priority="517"/>
+    <cfRule type="duplicateValues" dxfId="456" priority="517"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1003">
-    <cfRule type="duplicateValues" dxfId="465" priority="518"/>
+    <cfRule type="duplicateValues" dxfId="455" priority="518"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1003">
-    <cfRule type="duplicateValues" dxfId="464" priority="519"/>
+    <cfRule type="duplicateValues" dxfId="454" priority="519"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1004">
-    <cfRule type="duplicateValues" dxfId="463" priority="511"/>
+    <cfRule type="duplicateValues" dxfId="453" priority="511"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1004">
-    <cfRule type="duplicateValues" dxfId="462" priority="512"/>
+    <cfRule type="duplicateValues" dxfId="452" priority="512"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1004">
-    <cfRule type="duplicateValues" dxfId="461" priority="513"/>
+    <cfRule type="duplicateValues" dxfId="451" priority="513"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1006">
-    <cfRule type="duplicateValues" dxfId="460" priority="508"/>
+    <cfRule type="duplicateValues" dxfId="450" priority="508"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1006">
-    <cfRule type="duplicateValues" dxfId="459" priority="509"/>
+    <cfRule type="duplicateValues" dxfId="449" priority="509"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1006">
-    <cfRule type="duplicateValues" dxfId="458" priority="510"/>
+    <cfRule type="duplicateValues" dxfId="448" priority="510"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1005">
-    <cfRule type="duplicateValues" dxfId="457" priority="502"/>
+    <cfRule type="duplicateValues" dxfId="447" priority="502"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1005">
-    <cfRule type="duplicateValues" dxfId="456" priority="503"/>
+    <cfRule type="duplicateValues" dxfId="446" priority="503"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1005">
-    <cfRule type="duplicateValues" dxfId="455" priority="504"/>
+    <cfRule type="duplicateValues" dxfId="445" priority="504"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1007">
-    <cfRule type="duplicateValues" dxfId="454" priority="496"/>
+    <cfRule type="duplicateValues" dxfId="444" priority="496"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1007">
-    <cfRule type="duplicateValues" dxfId="453" priority="497"/>
+    <cfRule type="duplicateValues" dxfId="443" priority="497"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1007">
-    <cfRule type="duplicateValues" dxfId="452" priority="498"/>
+    <cfRule type="duplicateValues" dxfId="442" priority="498"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1008">
-    <cfRule type="duplicateValues" dxfId="451" priority="490"/>
+    <cfRule type="duplicateValues" dxfId="441" priority="490"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1008">
-    <cfRule type="duplicateValues" dxfId="450" priority="491"/>
+    <cfRule type="duplicateValues" dxfId="440" priority="491"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1008">
-    <cfRule type="duplicateValues" dxfId="449" priority="492"/>
+    <cfRule type="duplicateValues" dxfId="439" priority="492"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1009">
-    <cfRule type="duplicateValues" dxfId="448" priority="481"/>
+    <cfRule type="duplicateValues" dxfId="438" priority="481"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1009">
-    <cfRule type="duplicateValues" dxfId="447" priority="482"/>
+    <cfRule type="duplicateValues" dxfId="437" priority="482"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1009">
-    <cfRule type="duplicateValues" dxfId="446" priority="483"/>
+    <cfRule type="duplicateValues" dxfId="436" priority="483"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1010">
-    <cfRule type="duplicateValues" dxfId="445" priority="476"/>
+    <cfRule type="duplicateValues" dxfId="435" priority="476"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1010">
-    <cfRule type="duplicateValues" dxfId="444" priority="475"/>
+    <cfRule type="duplicateValues" dxfId="434" priority="475"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1010">
-    <cfRule type="duplicateValues" dxfId="443" priority="477"/>
+    <cfRule type="duplicateValues" dxfId="433" priority="477"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1012">
-    <cfRule type="duplicateValues" dxfId="442" priority="466"/>
+    <cfRule type="duplicateValues" dxfId="432" priority="466"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1012">
-    <cfRule type="duplicateValues" dxfId="441" priority="467"/>
+    <cfRule type="duplicateValues" dxfId="431" priority="467"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1012">
-    <cfRule type="duplicateValues" dxfId="440" priority="468"/>
+    <cfRule type="duplicateValues" dxfId="430" priority="468"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1013">
-    <cfRule type="duplicateValues" dxfId="439" priority="460"/>
+    <cfRule type="duplicateValues" dxfId="429" priority="460"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1013">
-    <cfRule type="duplicateValues" dxfId="438" priority="461"/>
+    <cfRule type="duplicateValues" dxfId="428" priority="461"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1013">
-    <cfRule type="duplicateValues" dxfId="437" priority="462"/>
+    <cfRule type="duplicateValues" dxfId="427" priority="462"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1014">
-    <cfRule type="duplicateValues" dxfId="436" priority="457"/>
+    <cfRule type="duplicateValues" dxfId="426" priority="457"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1014">
-    <cfRule type="duplicateValues" dxfId="435" priority="458"/>
+    <cfRule type="duplicateValues" dxfId="425" priority="458"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1014">
-    <cfRule type="duplicateValues" dxfId="434" priority="459"/>
+    <cfRule type="duplicateValues" dxfId="424" priority="459"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1015">
-    <cfRule type="duplicateValues" dxfId="433" priority="454"/>
+    <cfRule type="duplicateValues" dxfId="423" priority="454"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1015">
-    <cfRule type="duplicateValues" dxfId="432" priority="455"/>
+    <cfRule type="duplicateValues" dxfId="422" priority="455"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1015">
-    <cfRule type="duplicateValues" dxfId="431" priority="456"/>
+    <cfRule type="duplicateValues" dxfId="421" priority="456"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1016">
-    <cfRule type="duplicateValues" dxfId="430" priority="450"/>
+    <cfRule type="duplicateValues" dxfId="420" priority="450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1016">
-    <cfRule type="duplicateValues" dxfId="429" priority="449"/>
+    <cfRule type="duplicateValues" dxfId="419" priority="449"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1016">
-    <cfRule type="duplicateValues" dxfId="428" priority="448"/>
+    <cfRule type="duplicateValues" dxfId="418" priority="448"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1017">
-    <cfRule type="duplicateValues" dxfId="427" priority="446"/>
+    <cfRule type="duplicateValues" dxfId="417" priority="446"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1017">
-    <cfRule type="duplicateValues" dxfId="426" priority="445"/>
+    <cfRule type="duplicateValues" dxfId="416" priority="445"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1017">
-    <cfRule type="duplicateValues" dxfId="425" priority="447"/>
+    <cfRule type="duplicateValues" dxfId="415" priority="447"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1018">
-    <cfRule type="duplicateValues" dxfId="424" priority="442"/>
+    <cfRule type="duplicateValues" dxfId="414" priority="442"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1018">
-    <cfRule type="duplicateValues" dxfId="423" priority="443"/>
+    <cfRule type="duplicateValues" dxfId="413" priority="443"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1018">
-    <cfRule type="duplicateValues" dxfId="422" priority="444"/>
+    <cfRule type="duplicateValues" dxfId="412" priority="444"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9">
-    <cfRule type="duplicateValues" dxfId="421" priority="439"/>
+    <cfRule type="duplicateValues" dxfId="411" priority="439"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9">
-    <cfRule type="duplicateValues" dxfId="420" priority="440"/>
+    <cfRule type="duplicateValues" dxfId="410" priority="440"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9">
-    <cfRule type="duplicateValues" dxfId="419" priority="441"/>
+    <cfRule type="duplicateValues" dxfId="409" priority="441"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10">
-    <cfRule type="duplicateValues" dxfId="418" priority="436"/>
+    <cfRule type="duplicateValues" dxfId="408" priority="436"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10">
-    <cfRule type="duplicateValues" dxfId="417" priority="437"/>
+    <cfRule type="duplicateValues" dxfId="407" priority="437"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10">
-    <cfRule type="duplicateValues" dxfId="416" priority="438"/>
+    <cfRule type="duplicateValues" dxfId="406" priority="438"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
-    <cfRule type="duplicateValues" dxfId="415" priority="433"/>
+    <cfRule type="duplicateValues" dxfId="405" priority="433"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
-    <cfRule type="duplicateValues" dxfId="414" priority="434"/>
+    <cfRule type="duplicateValues" dxfId="404" priority="434"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
-    <cfRule type="duplicateValues" dxfId="413" priority="435"/>
+    <cfRule type="duplicateValues" dxfId="403" priority="435"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="412" priority="430"/>
+    <cfRule type="duplicateValues" dxfId="402" priority="430"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="411" priority="431"/>
+    <cfRule type="duplicateValues" dxfId="401" priority="431"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="410" priority="432"/>
+    <cfRule type="duplicateValues" dxfId="400" priority="432"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20">
-    <cfRule type="duplicateValues" dxfId="409" priority="427"/>
+    <cfRule type="duplicateValues" dxfId="399" priority="427"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20">
-    <cfRule type="duplicateValues" dxfId="408" priority="428"/>
+    <cfRule type="duplicateValues" dxfId="398" priority="428"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20">
-    <cfRule type="duplicateValues" dxfId="407" priority="429"/>
+    <cfRule type="duplicateValues" dxfId="397" priority="429"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="duplicateValues" dxfId="406" priority="424"/>
+    <cfRule type="duplicateValues" dxfId="396" priority="424"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="duplicateValues" dxfId="405" priority="425"/>
+    <cfRule type="duplicateValues" dxfId="395" priority="425"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="duplicateValues" dxfId="404" priority="426"/>
+    <cfRule type="duplicateValues" dxfId="394" priority="426"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="duplicateValues" dxfId="403" priority="421"/>
+    <cfRule type="duplicateValues" dxfId="393" priority="421"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="duplicateValues" dxfId="402" priority="422"/>
+    <cfRule type="duplicateValues" dxfId="392" priority="422"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="duplicateValues" dxfId="401" priority="423"/>
+    <cfRule type="duplicateValues" dxfId="391" priority="423"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="duplicateValues" dxfId="400" priority="418"/>
+    <cfRule type="duplicateValues" dxfId="390" priority="418"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="duplicateValues" dxfId="399" priority="419"/>
+    <cfRule type="duplicateValues" dxfId="389" priority="419"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="duplicateValues" dxfId="398" priority="420"/>
+    <cfRule type="duplicateValues" dxfId="388" priority="420"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="397" priority="415"/>
+    <cfRule type="duplicateValues" dxfId="387" priority="415"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="396" priority="416"/>
+    <cfRule type="duplicateValues" dxfId="386" priority="416"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="395" priority="417"/>
+    <cfRule type="duplicateValues" dxfId="385" priority="417"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27">
-    <cfRule type="duplicateValues" dxfId="394" priority="412"/>
+    <cfRule type="duplicateValues" dxfId="384" priority="412"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27">
-    <cfRule type="duplicateValues" dxfId="393" priority="413"/>
+    <cfRule type="duplicateValues" dxfId="383" priority="413"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27">
-    <cfRule type="duplicateValues" dxfId="392" priority="414"/>
+    <cfRule type="duplicateValues" dxfId="382" priority="414"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28">
-    <cfRule type="duplicateValues" dxfId="391" priority="409"/>
+    <cfRule type="duplicateValues" dxfId="381" priority="409"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28">
-    <cfRule type="duplicateValues" dxfId="390" priority="410"/>
+    <cfRule type="duplicateValues" dxfId="380" priority="410"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28">
-    <cfRule type="duplicateValues" dxfId="389" priority="411"/>
+    <cfRule type="duplicateValues" dxfId="379" priority="411"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29">
-    <cfRule type="duplicateValues" dxfId="388" priority="406"/>
+    <cfRule type="duplicateValues" dxfId="378" priority="406"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29">
-    <cfRule type="duplicateValues" dxfId="387" priority="407"/>
+    <cfRule type="duplicateValues" dxfId="377" priority="407"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29">
-    <cfRule type="duplicateValues" dxfId="386" priority="408"/>
+    <cfRule type="duplicateValues" dxfId="376" priority="408"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="385" priority="403"/>
+    <cfRule type="duplicateValues" dxfId="375" priority="403"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="384" priority="404"/>
+    <cfRule type="duplicateValues" dxfId="374" priority="404"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="383" priority="405"/>
+    <cfRule type="duplicateValues" dxfId="373" priority="405"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="382" priority="400"/>
+    <cfRule type="duplicateValues" dxfId="372" priority="400"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="381" priority="401"/>
+    <cfRule type="duplicateValues" dxfId="371" priority="401"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="380" priority="402"/>
+    <cfRule type="duplicateValues" dxfId="370" priority="402"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="379" priority="397"/>
+    <cfRule type="duplicateValues" dxfId="369" priority="397"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="378" priority="398"/>
+    <cfRule type="duplicateValues" dxfId="368" priority="398"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="377" priority="399"/>
+    <cfRule type="duplicateValues" dxfId="367" priority="399"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="376" priority="394"/>
+    <cfRule type="duplicateValues" dxfId="366" priority="394"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="375" priority="395"/>
+    <cfRule type="duplicateValues" dxfId="365" priority="395"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="374" priority="396"/>
+    <cfRule type="duplicateValues" dxfId="364" priority="396"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="373" priority="391"/>
+    <cfRule type="duplicateValues" dxfId="363" priority="391"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="372" priority="392"/>
+    <cfRule type="duplicateValues" dxfId="362" priority="392"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="371" priority="393"/>
+    <cfRule type="duplicateValues" dxfId="361" priority="393"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="370" priority="388"/>
+    <cfRule type="duplicateValues" dxfId="360" priority="388"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="369" priority="389"/>
+    <cfRule type="duplicateValues" dxfId="359" priority="389"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="368" priority="390"/>
+    <cfRule type="duplicateValues" dxfId="358" priority="390"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="367" priority="385"/>
+    <cfRule type="duplicateValues" dxfId="357" priority="385"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="366" priority="386"/>
+    <cfRule type="duplicateValues" dxfId="356" priority="386"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="365" priority="387"/>
+    <cfRule type="duplicateValues" dxfId="355" priority="387"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="364" priority="382"/>
+    <cfRule type="duplicateValues" dxfId="354" priority="382"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="363" priority="383"/>
+    <cfRule type="duplicateValues" dxfId="353" priority="383"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="362" priority="384"/>
+    <cfRule type="duplicateValues" dxfId="352" priority="384"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="361" priority="379"/>
+    <cfRule type="duplicateValues" dxfId="351" priority="379"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="360" priority="380"/>
+    <cfRule type="duplicateValues" dxfId="350" priority="380"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="359" priority="381"/>
+    <cfRule type="duplicateValues" dxfId="349" priority="381"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47">
-    <cfRule type="duplicateValues" dxfId="358" priority="376"/>
+    <cfRule type="duplicateValues" dxfId="348" priority="376"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47">
-    <cfRule type="duplicateValues" dxfId="357" priority="377"/>
+    <cfRule type="duplicateValues" dxfId="347" priority="377"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47">
-    <cfRule type="duplicateValues" dxfId="356" priority="378"/>
+    <cfRule type="duplicateValues" dxfId="346" priority="378"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="355" priority="373"/>
+    <cfRule type="duplicateValues" dxfId="345" priority="373"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="354" priority="374"/>
+    <cfRule type="duplicateValues" dxfId="344" priority="374"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="353" priority="375"/>
+    <cfRule type="duplicateValues" dxfId="343" priority="375"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="352" priority="370"/>
+    <cfRule type="duplicateValues" dxfId="342" priority="370"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="351" priority="371"/>
+    <cfRule type="duplicateValues" dxfId="341" priority="371"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="350" priority="372"/>
+    <cfRule type="duplicateValues" dxfId="340" priority="372"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="349" priority="364"/>
+    <cfRule type="duplicateValues" dxfId="339" priority="364"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="348" priority="365"/>
+    <cfRule type="duplicateValues" dxfId="338" priority="365"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="347" priority="366"/>
+    <cfRule type="duplicateValues" dxfId="337" priority="366"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55">
-    <cfRule type="duplicateValues" dxfId="346" priority="361"/>
+    <cfRule type="duplicateValues" dxfId="336" priority="361"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55">
-    <cfRule type="duplicateValues" dxfId="345" priority="362"/>
+    <cfRule type="duplicateValues" dxfId="335" priority="362"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55">
-    <cfRule type="duplicateValues" dxfId="344" priority="363"/>
+    <cfRule type="duplicateValues" dxfId="334" priority="363"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="343" priority="358"/>
+    <cfRule type="duplicateValues" dxfId="333" priority="358"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="342" priority="359"/>
+    <cfRule type="duplicateValues" dxfId="332" priority="359"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="341" priority="360"/>
+    <cfRule type="duplicateValues" dxfId="331" priority="360"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B60">
-    <cfRule type="duplicateValues" dxfId="340" priority="355"/>
+    <cfRule type="duplicateValues" dxfId="330" priority="355"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B60">
-    <cfRule type="duplicateValues" dxfId="339" priority="356"/>
+    <cfRule type="duplicateValues" dxfId="329" priority="356"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B60">
-    <cfRule type="duplicateValues" dxfId="338" priority="357"/>
+    <cfRule type="duplicateValues" dxfId="328" priority="357"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B61">
-    <cfRule type="duplicateValues" dxfId="337" priority="352"/>
+    <cfRule type="duplicateValues" dxfId="327" priority="352"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B61">
-    <cfRule type="duplicateValues" dxfId="336" priority="353"/>
+    <cfRule type="duplicateValues" dxfId="326" priority="353"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B61">
-    <cfRule type="duplicateValues" dxfId="335" priority="354"/>
+    <cfRule type="duplicateValues" dxfId="325" priority="354"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B65">
-    <cfRule type="duplicateValues" dxfId="334" priority="349"/>
+    <cfRule type="duplicateValues" dxfId="324" priority="349"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B65">
-    <cfRule type="duplicateValues" dxfId="333" priority="350"/>
+    <cfRule type="duplicateValues" dxfId="323" priority="350"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B65">
-    <cfRule type="duplicateValues" dxfId="332" priority="351"/>
+    <cfRule type="duplicateValues" dxfId="322" priority="351"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B66">
-    <cfRule type="duplicateValues" dxfId="331" priority="346"/>
+    <cfRule type="duplicateValues" dxfId="321" priority="346"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B66">
-    <cfRule type="duplicateValues" dxfId="330" priority="347"/>
+    <cfRule type="duplicateValues" dxfId="320" priority="347"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B66">
-    <cfRule type="duplicateValues" dxfId="329" priority="348"/>
+    <cfRule type="duplicateValues" dxfId="319" priority="348"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="328" priority="343"/>
+    <cfRule type="duplicateValues" dxfId="318" priority="343"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="327" priority="344"/>
+    <cfRule type="duplicateValues" dxfId="317" priority="344"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="326" priority="345"/>
+    <cfRule type="duplicateValues" dxfId="316" priority="345"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68">
-    <cfRule type="duplicateValues" dxfId="325" priority="340"/>
+    <cfRule type="duplicateValues" dxfId="315" priority="340"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68">
-    <cfRule type="duplicateValues" dxfId="324" priority="341"/>
+    <cfRule type="duplicateValues" dxfId="314" priority="341"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68">
-    <cfRule type="duplicateValues" dxfId="323" priority="342"/>
+    <cfRule type="duplicateValues" dxfId="313" priority="342"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="322" priority="337"/>
+    <cfRule type="duplicateValues" dxfId="312" priority="337"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="321" priority="338"/>
+    <cfRule type="duplicateValues" dxfId="311" priority="338"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="320" priority="339"/>
+    <cfRule type="duplicateValues" dxfId="310" priority="339"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70">
-    <cfRule type="duplicateValues" dxfId="319" priority="331"/>
+    <cfRule type="duplicateValues" dxfId="309" priority="331"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70">
-    <cfRule type="duplicateValues" dxfId="318" priority="332"/>
+    <cfRule type="duplicateValues" dxfId="308" priority="332"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70">
-    <cfRule type="duplicateValues" dxfId="317" priority="333"/>
+    <cfRule type="duplicateValues" dxfId="307" priority="333"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="316" priority="328"/>
+    <cfRule type="duplicateValues" dxfId="306" priority="328"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="315" priority="329"/>
+    <cfRule type="duplicateValues" dxfId="305" priority="329"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="314" priority="330"/>
+    <cfRule type="duplicateValues" dxfId="304" priority="330"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72">
-    <cfRule type="duplicateValues" dxfId="313" priority="325"/>
+    <cfRule type="duplicateValues" dxfId="303" priority="325"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72">
-    <cfRule type="duplicateValues" dxfId="312" priority="326"/>
+    <cfRule type="duplicateValues" dxfId="302" priority="326"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72">
-    <cfRule type="duplicateValues" dxfId="311" priority="327"/>
+    <cfRule type="duplicateValues" dxfId="301" priority="327"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B73">
-    <cfRule type="duplicateValues" dxfId="310" priority="322"/>
+    <cfRule type="duplicateValues" dxfId="300" priority="322"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B73">
-    <cfRule type="duplicateValues" dxfId="309" priority="323"/>
+    <cfRule type="duplicateValues" dxfId="299" priority="323"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B73">
-    <cfRule type="duplicateValues" dxfId="308" priority="324"/>
+    <cfRule type="duplicateValues" dxfId="298" priority="324"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B95">
-    <cfRule type="duplicateValues" dxfId="307" priority="319"/>
+    <cfRule type="duplicateValues" dxfId="297" priority="319"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B95">
-    <cfRule type="duplicateValues" dxfId="306" priority="320"/>
+    <cfRule type="duplicateValues" dxfId="296" priority="320"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B95">
-    <cfRule type="duplicateValues" dxfId="305" priority="321"/>
+    <cfRule type="duplicateValues" dxfId="295" priority="321"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107">
-    <cfRule type="duplicateValues" dxfId="304" priority="316"/>
+    <cfRule type="duplicateValues" dxfId="294" priority="316"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107">
-    <cfRule type="duplicateValues" dxfId="303" priority="317"/>
+    <cfRule type="duplicateValues" dxfId="293" priority="317"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107">
-    <cfRule type="duplicateValues" dxfId="302" priority="318"/>
+    <cfRule type="duplicateValues" dxfId="292" priority="318"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112">
-    <cfRule type="duplicateValues" dxfId="301" priority="310"/>
+    <cfRule type="duplicateValues" dxfId="291" priority="310"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112">
-    <cfRule type="duplicateValues" dxfId="300" priority="311"/>
+    <cfRule type="duplicateValues" dxfId="290" priority="311"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112">
-    <cfRule type="duplicateValues" dxfId="299" priority="312"/>
+    <cfRule type="duplicateValues" dxfId="289" priority="312"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B113">
-    <cfRule type="duplicateValues" dxfId="298" priority="307"/>
+    <cfRule type="duplicateValues" dxfId="288" priority="307"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B113">
-    <cfRule type="duplicateValues" dxfId="297" priority="308"/>
+    <cfRule type="duplicateValues" dxfId="287" priority="308"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B113">
-    <cfRule type="duplicateValues" dxfId="296" priority="309"/>
+    <cfRule type="duplicateValues" dxfId="286" priority="309"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B120">
-    <cfRule type="duplicateValues" dxfId="295" priority="304"/>
+    <cfRule type="duplicateValues" dxfId="285" priority="304"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B120">
-    <cfRule type="duplicateValues" dxfId="294" priority="305"/>
+    <cfRule type="duplicateValues" dxfId="284" priority="305"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B120">
-    <cfRule type="duplicateValues" dxfId="293" priority="306"/>
+    <cfRule type="duplicateValues" dxfId="283" priority="306"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B121">
-    <cfRule type="duplicateValues" dxfId="292" priority="298"/>
+    <cfRule type="duplicateValues" dxfId="282" priority="298"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B121">
-    <cfRule type="duplicateValues" dxfId="291" priority="299"/>
+    <cfRule type="duplicateValues" dxfId="281" priority="299"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B121">
-    <cfRule type="duplicateValues" dxfId="290" priority="300"/>
+    <cfRule type="duplicateValues" dxfId="280" priority="300"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B123">
-    <cfRule type="duplicateValues" dxfId="289" priority="295"/>
+    <cfRule type="duplicateValues" dxfId="279" priority="295"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B123">
-    <cfRule type="duplicateValues" dxfId="288" priority="296"/>
+    <cfRule type="duplicateValues" dxfId="278" priority="296"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B123">
-    <cfRule type="duplicateValues" dxfId="287" priority="297"/>
+    <cfRule type="duplicateValues" dxfId="277" priority="297"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B127">
-    <cfRule type="duplicateValues" dxfId="286" priority="292"/>
+    <cfRule type="duplicateValues" dxfId="276" priority="292"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B127">
-    <cfRule type="duplicateValues" dxfId="285" priority="293"/>
+    <cfRule type="duplicateValues" dxfId="275" priority="293"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B127">
-    <cfRule type="duplicateValues" dxfId="284" priority="294"/>
+    <cfRule type="duplicateValues" dxfId="274" priority="294"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B153">
-    <cfRule type="duplicateValues" dxfId="283" priority="289"/>
+    <cfRule type="duplicateValues" dxfId="273" priority="289"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B153">
-    <cfRule type="duplicateValues" dxfId="282" priority="290"/>
+    <cfRule type="duplicateValues" dxfId="272" priority="290"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B153">
-    <cfRule type="duplicateValues" dxfId="281" priority="291"/>
+    <cfRule type="duplicateValues" dxfId="271" priority="291"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B155">
-    <cfRule type="duplicateValues" dxfId="280" priority="288"/>
+    <cfRule type="duplicateValues" dxfId="270" priority="288"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B156">
-    <cfRule type="duplicateValues" dxfId="279" priority="285"/>
+    <cfRule type="duplicateValues" dxfId="269" priority="285"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B156">
-    <cfRule type="duplicateValues" dxfId="278" priority="286"/>
+    <cfRule type="duplicateValues" dxfId="268" priority="286"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B156">
-    <cfRule type="duplicateValues" dxfId="277" priority="287"/>
+    <cfRule type="duplicateValues" dxfId="267" priority="287"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B158">
-    <cfRule type="duplicateValues" dxfId="276" priority="282"/>
+    <cfRule type="duplicateValues" dxfId="266" priority="282"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B158">
-    <cfRule type="duplicateValues" dxfId="275" priority="283"/>
+    <cfRule type="duplicateValues" dxfId="265" priority="283"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B158">
-    <cfRule type="duplicateValues" dxfId="274" priority="284"/>
+    <cfRule type="duplicateValues" dxfId="264" priority="284"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B165">
-    <cfRule type="duplicateValues" dxfId="273" priority="279"/>
+    <cfRule type="duplicateValues" dxfId="263" priority="279"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B165">
-    <cfRule type="duplicateValues" dxfId="272" priority="280"/>
+    <cfRule type="duplicateValues" dxfId="262" priority="280"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B165">
-    <cfRule type="duplicateValues" dxfId="271" priority="281"/>
+    <cfRule type="duplicateValues" dxfId="261" priority="281"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B168">
-    <cfRule type="duplicateValues" dxfId="270" priority="276"/>
+    <cfRule type="duplicateValues" dxfId="260" priority="276"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B168">
-    <cfRule type="duplicateValues" dxfId="269" priority="277"/>
+    <cfRule type="duplicateValues" dxfId="259" priority="277"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B168">
-    <cfRule type="duplicateValues" dxfId="268" priority="278"/>
+    <cfRule type="duplicateValues" dxfId="258" priority="278"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171">
-    <cfRule type="duplicateValues" dxfId="267" priority="273"/>
+    <cfRule type="duplicateValues" dxfId="257" priority="273"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171">
-    <cfRule type="duplicateValues" dxfId="266" priority="274"/>
+    <cfRule type="duplicateValues" dxfId="256" priority="274"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171">
-    <cfRule type="duplicateValues" dxfId="265" priority="275"/>
+    <cfRule type="duplicateValues" dxfId="255" priority="275"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B172">
-    <cfRule type="duplicateValues" dxfId="264" priority="267"/>
+    <cfRule type="duplicateValues" dxfId="254" priority="267"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B172">
-    <cfRule type="duplicateValues" dxfId="263" priority="268"/>
+    <cfRule type="duplicateValues" dxfId="253" priority="268"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B172">
-    <cfRule type="duplicateValues" dxfId="262" priority="269"/>
+    <cfRule type="duplicateValues" dxfId="252" priority="269"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B173">
-    <cfRule type="duplicateValues" dxfId="261" priority="264"/>
+    <cfRule type="duplicateValues" dxfId="251" priority="264"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B173">
-    <cfRule type="duplicateValues" dxfId="260" priority="265"/>
+    <cfRule type="duplicateValues" dxfId="250" priority="265"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B173">
-    <cfRule type="duplicateValues" dxfId="259" priority="266"/>
+    <cfRule type="duplicateValues" dxfId="249" priority="266"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B174">
-    <cfRule type="duplicateValues" dxfId="258" priority="261"/>
+    <cfRule type="duplicateValues" dxfId="248" priority="261"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B174">
-    <cfRule type="duplicateValues" dxfId="257" priority="262"/>
+    <cfRule type="duplicateValues" dxfId="247" priority="262"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B174">
-    <cfRule type="duplicateValues" dxfId="256" priority="263"/>
+    <cfRule type="duplicateValues" dxfId="246" priority="263"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B175">
-    <cfRule type="duplicateValues" dxfId="255" priority="258"/>
+    <cfRule type="duplicateValues" dxfId="245" priority="258"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B175">
-    <cfRule type="duplicateValues" dxfId="254" priority="259"/>
+    <cfRule type="duplicateValues" dxfId="244" priority="259"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B175">
-    <cfRule type="duplicateValues" dxfId="253" priority="260"/>
+    <cfRule type="duplicateValues" dxfId="243" priority="260"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B176">
-    <cfRule type="duplicateValues" dxfId="252" priority="255"/>
+    <cfRule type="duplicateValues" dxfId="242" priority="255"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B176">
-    <cfRule type="duplicateValues" dxfId="251" priority="256"/>
+    <cfRule type="duplicateValues" dxfId="241" priority="256"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B176">
-    <cfRule type="duplicateValues" dxfId="250" priority="257"/>
+    <cfRule type="duplicateValues" dxfId="240" priority="257"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B177">
-    <cfRule type="duplicateValues" dxfId="249" priority="252"/>
+    <cfRule type="duplicateValues" dxfId="239" priority="252"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B177">
-    <cfRule type="duplicateValues" dxfId="248" priority="253"/>
+    <cfRule type="duplicateValues" dxfId="238" priority="253"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B177">
-    <cfRule type="duplicateValues" dxfId="247" priority="254"/>
+    <cfRule type="duplicateValues" dxfId="237" priority="254"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B178">
-    <cfRule type="duplicateValues" dxfId="246" priority="249"/>
+    <cfRule type="duplicateValues" dxfId="236" priority="249"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B178">
-    <cfRule type="duplicateValues" dxfId="245" priority="250"/>
+    <cfRule type="duplicateValues" dxfId="235" priority="250"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B178">
-    <cfRule type="duplicateValues" dxfId="244" priority="251"/>
+    <cfRule type="duplicateValues" dxfId="234" priority="251"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B180">
-    <cfRule type="duplicateValues" dxfId="243" priority="246"/>
+    <cfRule type="duplicateValues" dxfId="233" priority="246"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B180">
-    <cfRule type="duplicateValues" dxfId="242" priority="247"/>
+    <cfRule type="duplicateValues" dxfId="232" priority="247"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B180">
-    <cfRule type="duplicateValues" dxfId="241" priority="248"/>
+    <cfRule type="duplicateValues" dxfId="231" priority="248"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B182">
-    <cfRule type="duplicateValues" dxfId="240" priority="243"/>
+    <cfRule type="duplicateValues" dxfId="230" priority="243"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B182">
-    <cfRule type="duplicateValues" dxfId="239" priority="244"/>
+    <cfRule type="duplicateValues" dxfId="229" priority="244"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B182">
-    <cfRule type="duplicateValues" dxfId="238" priority="245"/>
+    <cfRule type="duplicateValues" dxfId="228" priority="245"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B185">
-    <cfRule type="duplicateValues" dxfId="237" priority="240"/>
+    <cfRule type="duplicateValues" dxfId="227" priority="240"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B185">
-    <cfRule type="duplicateValues" dxfId="236" priority="241"/>
+    <cfRule type="duplicateValues" dxfId="226" priority="241"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B185">
-    <cfRule type="duplicateValues" dxfId="235" priority="242"/>
+    <cfRule type="duplicateValues" dxfId="225" priority="242"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B189">
-    <cfRule type="duplicateValues" dxfId="234" priority="237"/>
+    <cfRule type="duplicateValues" dxfId="224" priority="237"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B189">
-    <cfRule type="duplicateValues" dxfId="233" priority="238"/>
+    <cfRule type="duplicateValues" dxfId="223" priority="238"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B189">
-    <cfRule type="duplicateValues" dxfId="232" priority="239"/>
+    <cfRule type="duplicateValues" dxfId="222" priority="239"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B203">
-    <cfRule type="duplicateValues" dxfId="231" priority="234"/>
+    <cfRule type="duplicateValues" dxfId="221" priority="234"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B203">
-    <cfRule type="duplicateValues" dxfId="230" priority="235"/>
+    <cfRule type="duplicateValues" dxfId="220" priority="235"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B203">
-    <cfRule type="duplicateValues" dxfId="229" priority="236"/>
+    <cfRule type="duplicateValues" dxfId="219" priority="236"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B206">
-    <cfRule type="duplicateValues" dxfId="228" priority="231"/>
+    <cfRule type="duplicateValues" dxfId="218" priority="231"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B206">
-    <cfRule type="duplicateValues" dxfId="227" priority="232"/>
+    <cfRule type="duplicateValues" dxfId="217" priority="232"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B206">
-    <cfRule type="duplicateValues" dxfId="226" priority="233"/>
+    <cfRule type="duplicateValues" dxfId="216" priority="233"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B207">
-    <cfRule type="duplicateValues" dxfId="225" priority="228"/>
+    <cfRule type="duplicateValues" dxfId="215" priority="228"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B207">
-    <cfRule type="duplicateValues" dxfId="224" priority="229"/>
+    <cfRule type="duplicateValues" dxfId="214" priority="229"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B207">
-    <cfRule type="duplicateValues" dxfId="223" priority="230"/>
+    <cfRule type="duplicateValues" dxfId="213" priority="230"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B208">
-    <cfRule type="duplicateValues" dxfId="222" priority="222"/>
+    <cfRule type="duplicateValues" dxfId="212" priority="222"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B208">
-    <cfRule type="duplicateValues" dxfId="221" priority="223"/>
+    <cfRule type="duplicateValues" dxfId="211" priority="223"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B208">
-    <cfRule type="duplicateValues" dxfId="220" priority="224"/>
+    <cfRule type="duplicateValues" dxfId="210" priority="224"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B213">
-    <cfRule type="duplicateValues" dxfId="219" priority="219"/>
+    <cfRule type="duplicateValues" dxfId="209" priority="219"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B213">
-    <cfRule type="duplicateValues" dxfId="218" priority="220"/>
+    <cfRule type="duplicateValues" dxfId="208" priority="220"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B213">
-    <cfRule type="duplicateValues" dxfId="217" priority="221"/>
+    <cfRule type="duplicateValues" dxfId="207" priority="221"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B215">
-    <cfRule type="duplicateValues" dxfId="216" priority="216"/>
+    <cfRule type="duplicateValues" dxfId="206" priority="216"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B215">
-    <cfRule type="duplicateValues" dxfId="215" priority="217"/>
+    <cfRule type="duplicateValues" dxfId="205" priority="217"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B215">
-    <cfRule type="duplicateValues" dxfId="214" priority="218"/>
+    <cfRule type="duplicateValues" dxfId="204" priority="218"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B218">
-    <cfRule type="duplicateValues" dxfId="213" priority="213"/>
+    <cfRule type="duplicateValues" dxfId="203" priority="213"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B218">
-    <cfRule type="duplicateValues" dxfId="212" priority="214"/>
+    <cfRule type="duplicateValues" dxfId="202" priority="214"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B218">
-    <cfRule type="duplicateValues" dxfId="211" priority="215"/>
+    <cfRule type="duplicateValues" dxfId="201" priority="215"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B221">
-    <cfRule type="duplicateValues" dxfId="210" priority="210"/>
+    <cfRule type="duplicateValues" dxfId="200" priority="210"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B221">
-    <cfRule type="duplicateValues" dxfId="209" priority="211"/>
+    <cfRule type="duplicateValues" dxfId="199" priority="211"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B221">
-    <cfRule type="duplicateValues" dxfId="208" priority="212"/>
+    <cfRule type="duplicateValues" dxfId="198" priority="212"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B230">
-    <cfRule type="duplicateValues" dxfId="207" priority="207"/>
+    <cfRule type="duplicateValues" dxfId="197" priority="207"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B230">
-    <cfRule type="duplicateValues" dxfId="206" priority="208"/>
+    <cfRule type="duplicateValues" dxfId="196" priority="208"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B230">
-    <cfRule type="duplicateValues" dxfId="205" priority="209"/>
+    <cfRule type="duplicateValues" dxfId="195" priority="209"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B234">
-    <cfRule type="duplicateValues" dxfId="204" priority="201"/>
+    <cfRule type="duplicateValues" dxfId="194" priority="201"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B234">
-    <cfRule type="duplicateValues" dxfId="203" priority="202"/>
+    <cfRule type="duplicateValues" dxfId="193" priority="202"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B234">
-    <cfRule type="duplicateValues" dxfId="202" priority="203"/>
+    <cfRule type="duplicateValues" dxfId="192" priority="203"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B233">
-    <cfRule type="duplicateValues" dxfId="201" priority="195"/>
+    <cfRule type="duplicateValues" dxfId="191" priority="195"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B233">
-    <cfRule type="duplicateValues" dxfId="200" priority="196"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="196"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B233">
-    <cfRule type="duplicateValues" dxfId="199" priority="197"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="197"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B236">
-    <cfRule type="duplicateValues" dxfId="198" priority="192"/>
+    <cfRule type="duplicateValues" dxfId="188" priority="192"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B236">
-    <cfRule type="duplicateValues" dxfId="197" priority="193"/>
+    <cfRule type="duplicateValues" dxfId="187" priority="193"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B236">
-    <cfRule type="duplicateValues" dxfId="196" priority="194"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="194"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B235">
-    <cfRule type="duplicateValues" dxfId="195" priority="189"/>
+    <cfRule type="duplicateValues" dxfId="185" priority="189"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B235">
-    <cfRule type="duplicateValues" dxfId="194" priority="190"/>
+    <cfRule type="duplicateValues" dxfId="184" priority="190"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B235">
-    <cfRule type="duplicateValues" dxfId="193" priority="191"/>
+    <cfRule type="duplicateValues" dxfId="183" priority="191"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B250">
-    <cfRule type="duplicateValues" dxfId="192" priority="186"/>
+    <cfRule type="duplicateValues" dxfId="182" priority="186"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B250">
-    <cfRule type="duplicateValues" dxfId="191" priority="187"/>
+    <cfRule type="duplicateValues" dxfId="181" priority="187"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B250">
-    <cfRule type="duplicateValues" dxfId="190" priority="188"/>
+    <cfRule type="duplicateValues" dxfId="180" priority="188"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B253">
-    <cfRule type="duplicateValues" dxfId="189" priority="183"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="183"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B253">
-    <cfRule type="duplicateValues" dxfId="188" priority="184"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="184"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B253">
-    <cfRule type="duplicateValues" dxfId="187" priority="185"/>
+    <cfRule type="duplicateValues" dxfId="177" priority="185"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B254">
-    <cfRule type="duplicateValues" dxfId="186" priority="180"/>
+    <cfRule type="duplicateValues" dxfId="176" priority="180"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B254">
-    <cfRule type="duplicateValues" dxfId="185" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="175" priority="181"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B254">
-    <cfRule type="duplicateValues" dxfId="184" priority="182"/>
+    <cfRule type="duplicateValues" dxfId="174" priority="182"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B256">
-    <cfRule type="duplicateValues" dxfId="183" priority="177"/>
+    <cfRule type="duplicateValues" dxfId="173" priority="177"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B256">
-    <cfRule type="duplicateValues" dxfId="182" priority="178"/>
+    <cfRule type="duplicateValues" dxfId="172" priority="178"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B256">
-    <cfRule type="duplicateValues" dxfId="181" priority="179"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="179"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B257">
-    <cfRule type="duplicateValues" dxfId="180" priority="174"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="174"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B257">
-    <cfRule type="duplicateValues" dxfId="179" priority="175"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="175"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B257">
-    <cfRule type="duplicateValues" dxfId="178" priority="176"/>
+    <cfRule type="duplicateValues" dxfId="168" priority="176"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B262">
-    <cfRule type="duplicateValues" dxfId="177" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="171"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B262">
-    <cfRule type="duplicateValues" dxfId="176" priority="172"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="172"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B262">
-    <cfRule type="duplicateValues" dxfId="175" priority="173"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="173"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B270">
-    <cfRule type="duplicateValues" dxfId="174" priority="168"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="168"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B270">
-    <cfRule type="duplicateValues" dxfId="173" priority="169"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="169"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B270">
-    <cfRule type="duplicateValues" dxfId="172" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="170"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B272">
-    <cfRule type="duplicateValues" dxfId="171" priority="166"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="166"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B272">
-    <cfRule type="duplicateValues" dxfId="170" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="165"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B272">
-    <cfRule type="duplicateValues" dxfId="169" priority="167"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="167"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B280">
-    <cfRule type="duplicateValues" dxfId="168" priority="162"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="162"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B280">
-    <cfRule type="duplicateValues" dxfId="167" priority="163"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="163"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B280">
-    <cfRule type="duplicateValues" dxfId="166" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="164"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B284">
-    <cfRule type="duplicateValues" dxfId="165" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="157"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B284">
-    <cfRule type="duplicateValues" dxfId="164" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="156"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B284">
-    <cfRule type="duplicateValues" dxfId="163" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="158"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B285">
-    <cfRule type="duplicateValues" dxfId="162" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="153"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B285">
-    <cfRule type="duplicateValues" dxfId="161" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="154"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B285">
-    <cfRule type="duplicateValues" dxfId="160" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="155"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B311">
-    <cfRule type="duplicateValues" dxfId="159" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="151"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B311">
-    <cfRule type="duplicateValues" dxfId="158" priority="150"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="150"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B311">
-    <cfRule type="duplicateValues" dxfId="157" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="152"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B313">
-    <cfRule type="duplicateValues" dxfId="156" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="145"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B313">
-    <cfRule type="duplicateValues" dxfId="155" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="144"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B313">
-    <cfRule type="duplicateValues" dxfId="154" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="146"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B314">
-    <cfRule type="duplicateValues" dxfId="153" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="139"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B314">
-    <cfRule type="duplicateValues" dxfId="152" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="138"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B314">
-    <cfRule type="duplicateValues" dxfId="151" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="140"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B316">
-    <cfRule type="duplicateValues" dxfId="150" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="135"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B316">
-    <cfRule type="duplicateValues" dxfId="149" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="136"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B316">
-    <cfRule type="duplicateValues" dxfId="148" priority="137"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="137"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B319">
-    <cfRule type="duplicateValues" dxfId="147" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="133"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B319">
-    <cfRule type="duplicateValues" dxfId="146" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="132"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B319">
-    <cfRule type="duplicateValues" dxfId="145" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="134"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B322">
-    <cfRule type="duplicateValues" dxfId="144" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="130"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B322">
-    <cfRule type="duplicateValues" dxfId="143" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="129"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B322">
-    <cfRule type="duplicateValues" dxfId="142" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="131"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B323">
-    <cfRule type="duplicateValues" dxfId="141" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="127"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B323">
-    <cfRule type="duplicateValues" dxfId="140" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="126"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B323">
-    <cfRule type="duplicateValues" dxfId="139" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="128"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B325">
-    <cfRule type="duplicateValues" dxfId="138" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="123"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B325">
-    <cfRule type="duplicateValues" dxfId="137" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="124"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B325">
-    <cfRule type="duplicateValues" dxfId="136" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="125"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B326">
-    <cfRule type="duplicateValues" dxfId="135" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="120"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B326">
-    <cfRule type="duplicateValues" dxfId="134" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="121"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B326">
-    <cfRule type="duplicateValues" dxfId="133" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="122"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B327">
-    <cfRule type="duplicateValues" dxfId="132" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="117"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B327">
-    <cfRule type="duplicateValues" dxfId="131" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B327">
-    <cfRule type="duplicateValues" dxfId="130" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B328">
-    <cfRule type="duplicateValues" dxfId="129" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B328">
-    <cfRule type="duplicateValues" dxfId="128" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B328">
-    <cfRule type="duplicateValues" dxfId="127" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="116"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B354">
-    <cfRule type="duplicateValues" dxfId="126" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="112"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B354">
-    <cfRule type="duplicateValues" dxfId="125" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="111"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B354">
-    <cfRule type="duplicateValues" dxfId="124" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B362">
-    <cfRule type="duplicateValues" dxfId="123" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="109"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B362">
-    <cfRule type="duplicateValues" dxfId="122" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B362">
-    <cfRule type="duplicateValues" dxfId="121" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B369">
-    <cfRule type="duplicateValues" dxfId="120" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B369">
-    <cfRule type="duplicateValues" dxfId="119" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="105"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B369">
-    <cfRule type="duplicateValues" dxfId="118" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B384">
-    <cfRule type="duplicateValues" dxfId="117" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B384">
-    <cfRule type="duplicateValues" dxfId="116" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B384">
-    <cfRule type="duplicateValues" dxfId="115" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B391">
-    <cfRule type="duplicateValues" dxfId="114" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B391">
-    <cfRule type="duplicateValues" dxfId="113" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="99"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B391">
-    <cfRule type="duplicateValues" dxfId="112" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B415">
-    <cfRule type="duplicateValues" dxfId="111" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="97"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B415">
-    <cfRule type="duplicateValues" dxfId="110" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B415">
-    <cfRule type="duplicateValues" dxfId="109" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="98"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B418">
-    <cfRule type="duplicateValues" dxfId="108" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="94"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B418">
-    <cfRule type="duplicateValues" dxfId="107" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="93"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B418">
-    <cfRule type="duplicateValues" dxfId="106" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="95"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B419">
-    <cfRule type="duplicateValues" dxfId="105" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B419">
-    <cfRule type="duplicateValues" dxfId="104" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="90"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B419">
-    <cfRule type="duplicateValues" dxfId="103" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="92"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B441">
-    <cfRule type="duplicateValues" dxfId="102" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B441">
-    <cfRule type="duplicateValues" dxfId="101" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B441">
-    <cfRule type="duplicateValues" dxfId="100" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="89"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B456">
-    <cfRule type="duplicateValues" dxfId="99" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B456">
-    <cfRule type="duplicateValues" dxfId="98" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B456">
-    <cfRule type="duplicateValues" dxfId="97" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B464">
-    <cfRule type="duplicateValues" dxfId="96" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B464">
-    <cfRule type="duplicateValues" dxfId="95" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B464">
-    <cfRule type="duplicateValues" dxfId="94" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B467">
-    <cfRule type="duplicateValues" dxfId="93" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B467">
-    <cfRule type="duplicateValues" dxfId="92" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B467">
-    <cfRule type="duplicateValues" dxfId="91" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B471">
-    <cfRule type="duplicateValues" dxfId="90" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B471">
-    <cfRule type="duplicateValues" dxfId="89" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B471">
-    <cfRule type="duplicateValues" dxfId="88" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B472">
-    <cfRule type="duplicateValues" dxfId="87" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B472">
-    <cfRule type="duplicateValues" dxfId="86" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B472">
-    <cfRule type="duplicateValues" dxfId="85" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B477">
-    <cfRule type="duplicateValues" dxfId="84" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B477">
-    <cfRule type="duplicateValues" dxfId="83" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B477">
-    <cfRule type="duplicateValues" dxfId="82" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B483">
-    <cfRule type="duplicateValues" dxfId="81" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B483">
-    <cfRule type="duplicateValues" dxfId="80" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B483">
-    <cfRule type="duplicateValues" dxfId="79" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B487">
-    <cfRule type="duplicateValues" dxfId="78" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B487">
-    <cfRule type="duplicateValues" dxfId="77" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B487">
-    <cfRule type="duplicateValues" dxfId="76" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B499">
-    <cfRule type="duplicateValues" dxfId="75" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B499">
-    <cfRule type="duplicateValues" dxfId="74" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B499">
-    <cfRule type="duplicateValues" dxfId="73" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B500">
-    <cfRule type="duplicateValues" dxfId="72" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B500">
-    <cfRule type="duplicateValues" dxfId="71" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B500">
-    <cfRule type="duplicateValues" dxfId="70" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B505">
-    <cfRule type="duplicateValues" dxfId="69" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B505">
-    <cfRule type="duplicateValues" dxfId="68" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B505">
-    <cfRule type="duplicateValues" dxfId="67" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B506">
-    <cfRule type="duplicateValues" dxfId="66" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B506">
-    <cfRule type="duplicateValues" dxfId="65" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B506">
-    <cfRule type="duplicateValues" dxfId="64" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B511">
-    <cfRule type="duplicateValues" dxfId="63" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B511">
-    <cfRule type="duplicateValues" dxfId="62" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B511">
-    <cfRule type="duplicateValues" dxfId="61" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B548">
-    <cfRule type="duplicateValues" dxfId="60" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B548">
-    <cfRule type="duplicateValues" dxfId="59" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B548">
-    <cfRule type="duplicateValues" dxfId="58" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B550">
-    <cfRule type="duplicateValues" dxfId="57" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B550">
-    <cfRule type="duplicateValues" dxfId="56" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B550">
-    <cfRule type="duplicateValues" dxfId="55" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B558">
-    <cfRule type="duplicateValues" dxfId="54" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B558">
-    <cfRule type="duplicateValues" dxfId="53" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B559">
-    <cfRule type="duplicateValues" dxfId="52" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B559">
-    <cfRule type="duplicateValues" dxfId="51" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B559">
-    <cfRule type="duplicateValues" dxfId="50" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B561">
-    <cfRule type="duplicateValues" dxfId="49" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B561">
-    <cfRule type="duplicateValues" dxfId="48" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B561">
-    <cfRule type="duplicateValues" dxfId="47" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B570">
-    <cfRule type="duplicateValues" dxfId="46" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B570">
-    <cfRule type="duplicateValues" dxfId="45" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B570">
-    <cfRule type="duplicateValues" dxfId="44" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B585">
-    <cfRule type="duplicateValues" dxfId="43" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B585">
-    <cfRule type="duplicateValues" dxfId="42" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B585">
-    <cfRule type="duplicateValues" dxfId="41" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B588">
-    <cfRule type="duplicateValues" dxfId="40" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B588">
-    <cfRule type="duplicateValues" dxfId="39" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B588">
-    <cfRule type="duplicateValues" dxfId="38" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B597">
-    <cfRule type="duplicateValues" dxfId="37" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B597">
-    <cfRule type="duplicateValues" dxfId="36" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B598">
-    <cfRule type="duplicateValues" dxfId="35" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B598">
-    <cfRule type="duplicateValues" dxfId="34" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B598">
-    <cfRule type="duplicateValues" dxfId="33" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B598">
-    <cfRule type="duplicateValues" dxfId="32" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B668:B669">
-    <cfRule type="duplicateValues" dxfId="31" priority="2799"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="2799"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B673:B674">
-    <cfRule type="duplicateValues" dxfId="30" priority="2800"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="2800"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B675:B676">
-    <cfRule type="duplicateValues" dxfId="29" priority="2801"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="2801"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B706:B708">
-    <cfRule type="duplicateValues" dxfId="28" priority="2802"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="2802"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D731">
-    <cfRule type="duplicateValues" dxfId="27" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B731">
-    <cfRule type="duplicateValues" dxfId="26" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B731">
-    <cfRule type="duplicateValues" dxfId="25" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B744">
-    <cfRule type="duplicateValues" dxfId="24" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B744">
-    <cfRule type="duplicateValues" dxfId="23" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B744">
-    <cfRule type="duplicateValues" dxfId="22" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B747">
-    <cfRule type="duplicateValues" dxfId="21" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B747">
-    <cfRule type="duplicateValues" dxfId="20" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B747">
-    <cfRule type="duplicateValues" dxfId="19" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B757">
-    <cfRule type="duplicateValues" dxfId="17" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B757">
-    <cfRule type="duplicateValues" dxfId="15" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B757">
-    <cfRule type="duplicateValues" dxfId="13" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B761">
-    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B761">
-    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B761">
-    <cfRule type="duplicateValues" dxfId="7" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B767">
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B767">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B767">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Spanish Dictionary.xlsx
+++ b/Spanish Dictionary.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2421" uniqueCount="2412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2520" uniqueCount="2511">
   <si>
     <t>Word / Expression</t>
   </si>
@@ -6996,9 +6996,6 @@
     <t>Pagamos a toca y tú pidiéndole a tu chica</t>
   </si>
   <si>
-    <t>We pay in full and you're asking your girl</t>
-  </si>
-  <si>
     <t>pahgahmos ah tokah ee toh peediéndoléh ah toh tchikah</t>
   </si>
   <si>
@@ -7035,9 +7032,6 @@
     <t>I do it hard, fast, and also spotless</t>
   </si>
   <si>
-    <t>loh agoh yah duroh rapidoh ee tambiénn empolutoh</t>
-  </si>
-  <si>
     <t>Más duro que yeso, más de uno lo discuto</t>
   </si>
   <si>
@@ -7252,6 +7246,309 @@
   </si>
   <si>
     <t>toh mamah déh tétah</t>
+  </si>
+  <si>
+    <t>no te sale</t>
+  </si>
+  <si>
+    <t>noh téh salé</t>
+  </si>
+  <si>
+    <t>It doesn't work for you</t>
+  </si>
+  <si>
+    <t>si entras aquí no sales</t>
+  </si>
+  <si>
+    <t>cee éntras aqui noh salés</t>
+  </si>
+  <si>
+    <t>If you enter here, you won't leave</t>
+  </si>
+  <si>
+    <t>Hablando</t>
+  </si>
+  <si>
+    <t>ablandoh</t>
+  </si>
+  <si>
+    <t>talking</t>
+  </si>
+  <si>
+    <t>ilegale</t>
+  </si>
+  <si>
+    <t>eelégaléh</t>
+  </si>
+  <si>
+    <t>illegal</t>
+  </si>
+  <si>
+    <t>Pegadizo</t>
+  </si>
+  <si>
+    <t>pégadisoh</t>
+  </si>
+  <si>
+    <t>catchy / memorable / easy to repeat</t>
+  </si>
+  <si>
+    <t>guitarrista</t>
+  </si>
+  <si>
+    <t>geetarristah</t>
+  </si>
+  <si>
+    <t>guitarist / guitar player</t>
+  </si>
+  <si>
+    <t>Para hacer</t>
+  </si>
+  <si>
+    <t>parah asér</t>
+  </si>
+  <si>
+    <t>to make / to do</t>
+  </si>
+  <si>
+    <t>un tema</t>
+  </si>
+  <si>
+    <t>own témah</t>
+  </si>
+  <si>
+    <t>a topic / subject</t>
+  </si>
+  <si>
+    <t>fumando</t>
+  </si>
+  <si>
+    <t>smoking</t>
+  </si>
+  <si>
+    <t>fumandoh</t>
+  </si>
+  <si>
+    <t>fumando uno de verdura</t>
+  </si>
+  <si>
+    <t>fumandoh ownoh dé vérdurah</t>
+  </si>
+  <si>
+    <t>smoking a marijuana joint</t>
+  </si>
+  <si>
+    <t>Yo hago mi escritura</t>
+  </si>
+  <si>
+    <t>yoh agoh mee éscreeturah</t>
+  </si>
+  <si>
+    <t>I do my writing</t>
+  </si>
+  <si>
+    <t>tú está fuera de cobertura</t>
+  </si>
+  <si>
+    <t>toh estah fuerah déh cobérturah</t>
+  </si>
+  <si>
+    <t>you're out of coverage</t>
+  </si>
+  <si>
+    <t>Tú dos meses duras</t>
+  </si>
+  <si>
+    <t>toh dohs mésés durahs</t>
+  </si>
+  <si>
+    <t>You last two months</t>
+  </si>
+  <si>
+    <t>La calle está loca</t>
+  </si>
+  <si>
+    <t>lah cahyéh estah lokah</t>
+  </si>
+  <si>
+    <t>The street is crazy</t>
+  </si>
+  <si>
+    <t>Pagamos a toca</t>
+  </si>
+  <si>
+    <t>pahgahmos ah tokah</t>
+  </si>
+  <si>
+    <t>we pay in cash</t>
+  </si>
+  <si>
+    <t>We pay in cash and you're asking your girl</t>
+  </si>
+  <si>
+    <t>tú pidiéndole a tu chica</t>
+  </si>
+  <si>
+    <t>toh peediéndoléh ah toh tchikah</t>
+  </si>
+  <si>
+    <t>You asking your girl</t>
+  </si>
+  <si>
+    <t>El capo</t>
+  </si>
+  <si>
+    <t>the boss</t>
+  </si>
+  <si>
+    <t>éhl kapoh</t>
+  </si>
+  <si>
+    <t>Tu coche</t>
+  </si>
+  <si>
+    <t>your car</t>
+  </si>
+  <si>
+    <t>toh kotchéh</t>
+  </si>
+  <si>
+    <t>Tu coche se cala</t>
+  </si>
+  <si>
+    <t>toh kotchéh séh kalah</t>
+  </si>
+  <si>
+    <t>Your car stalls</t>
+  </si>
+  <si>
+    <t>la tele</t>
+  </si>
+  <si>
+    <t>lah téléh</t>
+  </si>
+  <si>
+    <t>the TV</t>
+  </si>
+  <si>
+    <t>luego</t>
+  </si>
+  <si>
+    <t>luégoh</t>
+  </si>
+  <si>
+    <t>then / later</t>
+  </si>
+  <si>
+    <t>cuidado</t>
+  </si>
+  <si>
+    <t>quidadoh</t>
+  </si>
+  <si>
+    <t>watch out / careful / attention</t>
+  </si>
+  <si>
+    <t>mira</t>
+  </si>
+  <si>
+    <t>meerah</t>
+  </si>
+  <si>
+    <t>look</t>
+  </si>
+  <si>
+    <t>ya</t>
+  </si>
+  <si>
+    <t>yaah</t>
+  </si>
+  <si>
+    <t>already</t>
+  </si>
+  <si>
+    <t>fácil</t>
+  </si>
+  <si>
+    <t>faseel</t>
+  </si>
+  <si>
+    <t>easy</t>
+  </si>
+  <si>
+    <t>Lo hago ya duro</t>
+  </si>
+  <si>
+    <t>loh agoh yah duroh</t>
+  </si>
+  <si>
+    <t>también</t>
+  </si>
+  <si>
+    <t>tambiénn</t>
+  </si>
+  <si>
+    <t>also</t>
+  </si>
+  <si>
+    <t>rápido</t>
+  </si>
+  <si>
+    <t>fast</t>
+  </si>
+  <si>
+    <t>rahpidoh</t>
+  </si>
+  <si>
+    <t>impoluto</t>
+  </si>
+  <si>
+    <t>loh agoh yah duroh rahpidoh ee tambiénn eempolutoh</t>
+  </si>
+  <si>
+    <t>eempolutoh</t>
+  </si>
+  <si>
+    <t>unpolluted / clean / impeccable</t>
+  </si>
+  <si>
+    <t>I'm doing it hard now</t>
+  </si>
+  <si>
+    <t>yeso</t>
+  </si>
+  <si>
+    <t>yésoh</t>
+  </si>
+  <si>
+    <t>plaster / gypsum</t>
+  </si>
+  <si>
+    <t>espera</t>
+  </si>
+  <si>
+    <t>éspérah</t>
+  </si>
+  <si>
+    <t>wait</t>
+  </si>
+  <si>
+    <t>para</t>
+  </si>
+  <si>
+    <t>parah</t>
+  </si>
+  <si>
+    <t>stop</t>
+  </si>
+  <si>
+    <t>espera que lo cambie</t>
+  </si>
+  <si>
+    <t>éspérah kéh loh kambiéh</t>
+  </si>
+  <si>
+    <t>wait until he changes it</t>
   </si>
 </sst>
 </file>
@@ -7267,12 +7564,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -7287,7 +7590,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -7296,6 +7599,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -24270,7 +24576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:D819"/>
+  <dimension ref="B1:D852"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="1" customWidth="1"/>
@@ -32740,475 +33046,838 @@
     </row>
     <row r="777" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B777" s="1" t="s">
-        <v>2285</v>
+        <v>2410</v>
       </c>
       <c r="C777" s="1" t="s">
-        <v>2286</v>
+        <v>2411</v>
       </c>
       <c r="D777" s="1" t="s">
-        <v>2287</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="778" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B778" s="1" t="s">
-        <v>2288</v>
+        <v>2285</v>
       </c>
       <c r="C778" s="1" t="s">
-        <v>2306</v>
+        <v>2286</v>
       </c>
       <c r="D778" s="1" t="s">
-        <v>2289</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="779" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B779" s="1" t="s">
-        <v>2290</v>
+        <v>2413</v>
       </c>
       <c r="C779" s="1" t="s">
-        <v>2292</v>
+        <v>2414</v>
       </c>
       <c r="D779" s="1" t="s">
-        <v>2291</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="780" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B780" s="1" t="s">
-        <v>2293</v>
+        <v>2288</v>
       </c>
       <c r="C780" s="1" t="s">
-        <v>2295</v>
+        <v>2306</v>
       </c>
       <c r="D780" s="1" t="s">
-        <v>2294</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="781" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B781" s="1" t="s">
-        <v>2296</v>
+        <v>2290</v>
       </c>
       <c r="C781" s="1" t="s">
-        <v>2298</v>
+        <v>2292</v>
       </c>
       <c r="D781" s="1" t="s">
-        <v>2297</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="782" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B782" s="1" t="s">
-        <v>2299</v>
+        <v>2293</v>
       </c>
       <c r="C782" s="1" t="s">
-        <v>2301</v>
+        <v>2295</v>
       </c>
       <c r="D782" s="1" t="s">
-        <v>2300</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="783" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B783" s="1" t="s">
-        <v>2303</v>
+        <v>2416</v>
       </c>
       <c r="C783" s="1" t="s">
-        <v>2307</v>
+        <v>2417</v>
       </c>
       <c r="D783" s="1" t="s">
-        <v>2302</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="784" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B784" s="1" t="s">
-        <v>2304</v>
+        <v>2419</v>
       </c>
       <c r="C784" s="1" t="s">
-        <v>2305</v>
-      </c>
-      <c r="D784" s="1">
-        <v>40</v>
+        <v>2420</v>
+      </c>
+      <c r="D784" s="1" t="s">
+        <v>2421</v>
       </c>
     </row>
     <row r="785" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B785" s="1" t="s">
-        <v>2312</v>
+        <v>2296</v>
       </c>
       <c r="C785" s="1" t="s">
-        <v>2311</v>
+        <v>2298</v>
       </c>
       <c r="D785" s="1" t="s">
-        <v>2308</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="786" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B786" s="1" t="s">
-        <v>2309</v>
+        <v>2422</v>
       </c>
       <c r="C786" s="1" t="s">
-        <v>2310</v>
-      </c>
-      <c r="D786" s="1">
-        <v>17</v>
+        <v>2423</v>
+      </c>
+      <c r="D786" s="1" t="s">
+        <v>2424</v>
       </c>
     </row>
     <row r="787" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B787" s="1" t="s">
-        <v>2313</v>
+        <v>2299</v>
       </c>
       <c r="C787" s="1" t="s">
-        <v>2315</v>
+        <v>2301</v>
       </c>
       <c r="D787" s="1" t="s">
-        <v>2314</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="788" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B788" s="1" t="s">
-        <v>2316</v>
+        <v>2303</v>
       </c>
       <c r="C788" s="1" t="s">
-        <v>2318</v>
+        <v>2307</v>
       </c>
       <c r="D788" s="1" t="s">
-        <v>2317</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="789" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B789" s="1" t="s">
-        <v>2319</v>
+        <v>2304</v>
       </c>
       <c r="C789" s="1" t="s">
-        <v>2321</v>
-      </c>
-      <c r="D789" s="1" t="s">
-        <v>2320</v>
+        <v>2305</v>
+      </c>
+      <c r="D789" s="1">
+        <v>40</v>
       </c>
     </row>
     <row r="790" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B790" s="1" t="s">
-        <v>2322</v>
+        <v>2312</v>
       </c>
       <c r="C790" s="1" t="s">
-        <v>2324</v>
+        <v>2311</v>
       </c>
       <c r="D790" s="1" t="s">
-        <v>2323</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="791" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B791" s="1" t="s">
-        <v>2325</v>
+        <v>2425</v>
       </c>
       <c r="C791" s="1" t="s">
-        <v>2327</v>
+        <v>2426</v>
       </c>
       <c r="D791" s="1" t="s">
-        <v>2326</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="792" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B792" s="1" t="s">
-        <v>2328</v>
+        <v>2309</v>
       </c>
       <c r="C792" s="1" t="s">
-        <v>2330</v>
-      </c>
-      <c r="D792" s="1" t="s">
-        <v>2329</v>
+        <v>2310</v>
+      </c>
+      <c r="D792" s="1">
+        <v>17</v>
       </c>
     </row>
     <row r="793" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B793" s="1" t="s">
-        <v>2331</v>
+        <v>2313</v>
       </c>
       <c r="C793" s="1" t="s">
-        <v>2333</v>
+        <v>2315</v>
       </c>
       <c r="D793" s="1" t="s">
-        <v>2332</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="794" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B794" s="1" t="s">
-        <v>2334</v>
+        <v>2428</v>
       </c>
       <c r="C794" s="1" t="s">
-        <v>2336</v>
+        <v>2429</v>
       </c>
       <c r="D794" s="1" t="s">
-        <v>2335</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="795" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B795" s="1" t="s">
-        <v>2337</v>
+        <v>2431</v>
       </c>
       <c r="C795" s="1" t="s">
-        <v>2339</v>
+        <v>2432</v>
       </c>
       <c r="D795" s="1" t="s">
-        <v>2338</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="796" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B796" s="1" t="s">
-        <v>2340</v>
+        <v>2316</v>
       </c>
       <c r="C796" s="1" t="s">
-        <v>2342</v>
+        <v>2318</v>
       </c>
       <c r="D796" s="1" t="s">
-        <v>2341</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="797" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B797" s="1" t="s">
-        <v>2343</v>
+        <v>2434</v>
       </c>
       <c r="C797" s="1" t="s">
-        <v>2345</v>
+        <v>2436</v>
       </c>
       <c r="D797" s="1" t="s">
-        <v>2344</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="798" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B798" s="1" t="s">
-        <v>2346</v>
+        <v>2437</v>
       </c>
       <c r="C798" s="1" t="s">
-        <v>2348</v>
+        <v>2438</v>
       </c>
       <c r="D798" s="1" t="s">
-        <v>2347</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="799" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B799" s="1" t="s">
-        <v>2349</v>
+        <v>2440</v>
       </c>
       <c r="C799" s="1" t="s">
-        <v>2351</v>
+        <v>2441</v>
       </c>
       <c r="D799" s="1" t="s">
-        <v>2350</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="800" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B800" s="2" t="s">
-        <v>2352</v>
+      <c r="B800" s="1" t="s">
+        <v>2319</v>
       </c>
       <c r="C800" s="1" t="s">
-        <v>2354</v>
+        <v>2321</v>
       </c>
       <c r="D800" s="1" t="s">
-        <v>2353</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="801" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B801" s="1" t="s">
-        <v>2355</v>
+        <v>2443</v>
       </c>
       <c r="C801" s="1" t="s">
-        <v>2357</v>
+        <v>2444</v>
       </c>
       <c r="D801" s="1" t="s">
-        <v>2356</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="802" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B802" s="1" t="s">
-        <v>2358</v>
+        <v>2446</v>
       </c>
       <c r="C802" s="1" t="s">
-        <v>2365</v>
+        <v>2447</v>
       </c>
       <c r="D802" s="1" t="s">
-        <v>2359</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="803" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B803" s="1" t="s">
-        <v>2360</v>
+        <v>2322</v>
       </c>
       <c r="C803" s="1" t="s">
-        <v>2362</v>
+        <v>2324</v>
       </c>
       <c r="D803" s="1" t="s">
-        <v>2361</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="804" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B804" s="1" t="s">
-        <v>2363</v>
+        <v>2449</v>
       </c>
       <c r="C804" s="1" t="s">
-        <v>2366</v>
+        <v>2450</v>
       </c>
       <c r="D804" s="1" t="s">
-        <v>2364</v>
+        <v>2451</v>
       </c>
     </row>
     <row r="805" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B805" s="1" t="s">
-        <v>2369</v>
+        <v>2325</v>
       </c>
       <c r="C805" s="1" t="s">
-        <v>2368</v>
+        <v>2326</v>
       </c>
       <c r="D805" s="1" t="s">
-        <v>2367</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="806" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B806" s="1" t="s">
-        <v>2370</v>
+        <v>2452</v>
       </c>
       <c r="C806" s="1" t="s">
-        <v>2372</v>
+        <v>2453</v>
       </c>
       <c r="D806" s="1" t="s">
-        <v>2371</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="807" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B807" s="1" t="s">
-        <v>2373</v>
+        <v>2456</v>
       </c>
       <c r="C807" s="1" t="s">
-        <v>2375</v>
+        <v>2457</v>
       </c>
       <c r="D807" s="1" t="s">
-        <v>2374</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="808" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B808" s="1" t="s">
-        <v>2376</v>
+        <v>2327</v>
       </c>
       <c r="C808" s="1" t="s">
-        <v>2378</v>
+        <v>2329</v>
       </c>
       <c r="D808" s="1" t="s">
-        <v>2377</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="809" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B809" s="1" t="s">
-        <v>2381</v>
+        <v>2459</v>
       </c>
       <c r="C809" s="1" t="s">
-        <v>2380</v>
+        <v>2461</v>
       </c>
       <c r="D809" s="1" t="s">
-        <v>2379</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="810" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B810" s="1" t="s">
-        <v>2383</v>
+        <v>2330</v>
       </c>
       <c r="C810" s="1" t="s">
-        <v>2382</v>
+        <v>2332</v>
       </c>
       <c r="D810" s="1" t="s">
-        <v>2384</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="811" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B811" s="1" t="s">
-        <v>2385</v>
+        <v>2462</v>
       </c>
       <c r="C811" s="1" t="s">
-        <v>2387</v>
+        <v>2464</v>
       </c>
       <c r="D811" s="1" t="s">
-        <v>2386</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="812" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B812" s="1" t="s">
-        <v>2388</v>
+        <v>2465</v>
       </c>
       <c r="C812" s="1" t="s">
-        <v>2390</v>
+        <v>2466</v>
       </c>
       <c r="D812" s="1" t="s">
-        <v>2389</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="813" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B813" s="1" t="s">
-        <v>2391</v>
+        <v>2468</v>
       </c>
       <c r="C813" s="1" t="s">
-        <v>2393</v>
+        <v>2469</v>
       </c>
       <c r="D813" s="1" t="s">
-        <v>2392</v>
+        <v>2470</v>
       </c>
     </row>
     <row r="814" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B814" s="1" t="s">
-        <v>2394</v>
+        <v>2471</v>
       </c>
       <c r="C814" s="1" t="s">
-        <v>2396</v>
+        <v>2472</v>
       </c>
       <c r="D814" s="1" t="s">
-        <v>2395</v>
+        <v>2473</v>
       </c>
     </row>
     <row r="815" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B815" s="1" t="s">
-        <v>2397</v>
+        <v>2474</v>
       </c>
       <c r="C815" s="1" t="s">
-        <v>2398</v>
+        <v>2475</v>
       </c>
       <c r="D815" s="1" t="s">
-        <v>2399</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="816" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B816" s="1" t="s">
-        <v>2400</v>
+        <v>2333</v>
       </c>
       <c r="C816" s="1" t="s">
-        <v>2402</v>
+        <v>2335</v>
       </c>
       <c r="D816" s="1" t="s">
-        <v>2401</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="817" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B817" s="1" t="s">
-        <v>2403</v>
+        <v>2477</v>
       </c>
       <c r="C817" s="1" t="s">
-        <v>2404</v>
+        <v>2478</v>
       </c>
       <c r="D817" s="1" t="s">
-        <v>2405</v>
+        <v>2479</v>
       </c>
     </row>
     <row r="818" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B818" s="1" t="s">
-        <v>2406</v>
+        <v>2480</v>
       </c>
       <c r="C818" s="1" t="s">
-        <v>2407</v>
+        <v>2481</v>
       </c>
       <c r="D818" s="1" t="s">
-        <v>2408</v>
+        <v>2482</v>
       </c>
     </row>
     <row r="819" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B819" s="1" t="s">
+        <v>2483</v>
+      </c>
+      <c r="C819" s="1" t="s">
+        <v>2484</v>
+      </c>
+      <c r="D819" s="1" t="s">
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="820" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B820" s="1" t="s">
+        <v>2336</v>
+      </c>
+      <c r="C820" s="1" t="s">
+        <v>2495</v>
+      </c>
+      <c r="D820" s="1" t="s">
+        <v>2337</v>
+      </c>
+    </row>
+    <row r="821" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B821" s="1" t="s">
+        <v>2486</v>
+      </c>
+      <c r="C821" s="1" t="s">
+        <v>2487</v>
+      </c>
+      <c r="D821" s="1" t="s">
+        <v>2498</v>
+      </c>
+    </row>
+    <row r="822" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B822" s="1" t="s">
+        <v>2488</v>
+      </c>
+      <c r="C822" s="1" t="s">
+        <v>2489</v>
+      </c>
+      <c r="D822" s="1" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="823" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B823" s="1" t="s">
+        <v>2491</v>
+      </c>
+      <c r="C823" s="1" t="s">
+        <v>2493</v>
+      </c>
+      <c r="D823" s="1" t="s">
+        <v>2492</v>
+      </c>
+    </row>
+    <row r="824" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B824" s="1" t="s">
+        <v>2494</v>
+      </c>
+      <c r="C824" s="1" t="s">
+        <v>2496</v>
+      </c>
+      <c r="D824" s="1" t="s">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="825" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B825" s="1" t="s">
+        <v>2338</v>
+      </c>
+      <c r="C825" s="1" t="s">
+        <v>2340</v>
+      </c>
+      <c r="D825" s="1" t="s">
+        <v>2339</v>
+      </c>
+    </row>
+    <row r="826" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B826" s="1" t="s">
+        <v>2499</v>
+      </c>
+      <c r="C826" s="1" t="s">
+        <v>2500</v>
+      </c>
+      <c r="D826" s="1" t="s">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="827" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B827" s="1" t="s">
+        <v>2502</v>
+      </c>
+      <c r="C827" s="1" t="s">
+        <v>2503</v>
+      </c>
+      <c r="D827" s="1" t="s">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="828" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B828" s="1" t="s">
+        <v>2505</v>
+      </c>
+      <c r="C828" s="1" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D828" s="1" t="s">
+        <v>2507</v>
+      </c>
+    </row>
+    <row r="829" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B829" s="1" t="s">
+        <v>2341</v>
+      </c>
+      <c r="C829" s="1" t="s">
+        <v>2343</v>
+      </c>
+      <c r="D829" s="1" t="s">
+        <v>2342</v>
+      </c>
+    </row>
+    <row r="830" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B830" s="1" t="s">
+        <v>2344</v>
+      </c>
+      <c r="C830" s="1" t="s">
+        <v>2346</v>
+      </c>
+      <c r="D830" s="1" t="s">
+        <v>2345</v>
+      </c>
+    </row>
+    <row r="831" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B831" s="1" t="s">
+        <v>2508</v>
+      </c>
+      <c r="C831" s="1" t="s">
+        <v>2509</v>
+      </c>
+      <c r="D831" s="1" t="s">
+        <v>2510</v>
+      </c>
+    </row>
+    <row r="832" spans="2:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B832" s="4" t="s">
+        <v>2347</v>
+      </c>
+      <c r="C832" s="4" t="s">
+        <v>2349</v>
+      </c>
+      <c r="D832" s="4" t="s">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="833" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B833" s="2" t="s">
+        <v>2350</v>
+      </c>
+      <c r="C833" s="1" t="s">
+        <v>2352</v>
+      </c>
+      <c r="D833" s="1" t="s">
+        <v>2351</v>
+      </c>
+    </row>
+    <row r="834" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B834" s="1" t="s">
+        <v>2353</v>
+      </c>
+      <c r="C834" s="1" t="s">
+        <v>2355</v>
+      </c>
+      <c r="D834" s="1" t="s">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="835" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B835" s="1" t="s">
+        <v>2356</v>
+      </c>
+      <c r="C835" s="1" t="s">
+        <v>2363</v>
+      </c>
+      <c r="D835" s="1" t="s">
+        <v>2357</v>
+      </c>
+    </row>
+    <row r="836" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B836" s="1" t="s">
+        <v>2358</v>
+      </c>
+      <c r="C836" s="1" t="s">
+        <v>2360</v>
+      </c>
+      <c r="D836" s="1" t="s">
+        <v>2359</v>
+      </c>
+    </row>
+    <row r="837" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B837" s="1" t="s">
+        <v>2361</v>
+      </c>
+      <c r="C837" s="1" t="s">
+        <v>2364</v>
+      </c>
+      <c r="D837" s="1" t="s">
+        <v>2362</v>
+      </c>
+    </row>
+    <row r="838" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B838" s="1" t="s">
+        <v>2367</v>
+      </c>
+      <c r="C838" s="1" t="s">
+        <v>2366</v>
+      </c>
+      <c r="D838" s="1" t="s">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="839" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B839" s="1" t="s">
+        <v>2368</v>
+      </c>
+      <c r="C839" s="1" t="s">
+        <v>2370</v>
+      </c>
+      <c r="D839" s="1" t="s">
+        <v>2369</v>
+      </c>
+    </row>
+    <row r="840" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B840" s="1" t="s">
+        <v>2371</v>
+      </c>
+      <c r="C840" s="1" t="s">
+        <v>2373</v>
+      </c>
+      <c r="D840" s="1" t="s">
+        <v>2372</v>
+      </c>
+    </row>
+    <row r="841" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B841" s="1" t="s">
+        <v>2374</v>
+      </c>
+      <c r="C841" s="1" t="s">
+        <v>2376</v>
+      </c>
+      <c r="D841" s="1" t="s">
+        <v>2375</v>
+      </c>
+    </row>
+    <row r="842" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B842" s="1" t="s">
+        <v>2379</v>
+      </c>
+      <c r="C842" s="1" t="s">
+        <v>2378</v>
+      </c>
+      <c r="D842" s="1" t="s">
+        <v>2377</v>
+      </c>
+    </row>
+    <row r="843" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B843" s="1" t="s">
+        <v>2381</v>
+      </c>
+      <c r="C843" s="1" t="s">
+        <v>2380</v>
+      </c>
+      <c r="D843" s="1" t="s">
+        <v>2382</v>
+      </c>
+    </row>
+    <row r="844" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B844" s="1" t="s">
+        <v>2383</v>
+      </c>
+      <c r="C844" s="1" t="s">
+        <v>2385</v>
+      </c>
+      <c r="D844" s="1" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="845" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B845" s="1" t="s">
+        <v>2386</v>
+      </c>
+      <c r="C845" s="1" t="s">
+        <v>2388</v>
+      </c>
+      <c r="D845" s="1" t="s">
+        <v>2387</v>
+      </c>
+    </row>
+    <row r="846" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B846" s="1" t="s">
+        <v>2389</v>
+      </c>
+      <c r="C846" s="1" t="s">
+        <v>2391</v>
+      </c>
+      <c r="D846" s="1" t="s">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="847" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B847" s="1" t="s">
+        <v>2392</v>
+      </c>
+      <c r="C847" s="1" t="s">
+        <v>2394</v>
+      </c>
+      <c r="D847" s="1" t="s">
+        <v>2393</v>
+      </c>
+    </row>
+    <row r="848" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B848" s="1" t="s">
+        <v>2395</v>
+      </c>
+      <c r="C848" s="1" t="s">
+        <v>2396</v>
+      </c>
+      <c r="D848" s="1" t="s">
+        <v>2397</v>
+      </c>
+    </row>
+    <row r="849" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B849" s="1" t="s">
+        <v>2398</v>
+      </c>
+      <c r="C849" s="1" t="s">
+        <v>2400</v>
+      </c>
+      <c r="D849" s="1" t="s">
+        <v>2399</v>
+      </c>
+    </row>
+    <row r="850" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B850" s="1" t="s">
+        <v>2401</v>
+      </c>
+      <c r="C850" s="1" t="s">
+        <v>2402</v>
+      </c>
+      <c r="D850" s="1" t="s">
+        <v>2403</v>
+      </c>
+    </row>
+    <row r="851" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B851" s="1" t="s">
+        <v>2404</v>
+      </c>
+      <c r="C851" s="1" t="s">
+        <v>2405</v>
+      </c>
+      <c r="D851" s="1" t="s">
+        <v>2406</v>
+      </c>
+    </row>
+    <row r="852" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B852" s="1" t="s">
+        <v>2407</v>
+      </c>
+      <c r="C852" s="1" t="s">
         <v>2409</v>
       </c>
-      <c r="C819" s="1" t="s">
-        <v>2411</v>
-      </c>
-      <c r="D819" s="1" t="s">
-        <v>2410</v>
+      <c r="D852" s="1" t="s">
+        <v>2408</v>
       </c>
     </row>
   </sheetData>
@@ -35213,1768 +35882,1768 @@
   <conditionalFormatting sqref="B774">
     <cfRule type="duplicateValues" dxfId="1000" priority="1354"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B776">
+  <conditionalFormatting sqref="B776:B777">
     <cfRule type="duplicateValues" dxfId="999" priority="1353"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B776">
+  <conditionalFormatting sqref="B776:B777">
     <cfRule type="duplicateValues" dxfId="998" priority="1352"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B776">
+  <conditionalFormatting sqref="B776:B777">
     <cfRule type="duplicateValues" dxfId="997" priority="1351"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B777">
+  <conditionalFormatting sqref="B778:B779">
     <cfRule type="duplicateValues" dxfId="996" priority="1349"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B777">
+  <conditionalFormatting sqref="B778:B779">
     <cfRule type="duplicateValues" dxfId="995" priority="1350"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B777">
+  <conditionalFormatting sqref="B778:B779">
     <cfRule type="duplicateValues" dxfId="994" priority="1348"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B778">
+  <conditionalFormatting sqref="B780">
     <cfRule type="duplicateValues" dxfId="993" priority="1346"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B778">
+  <conditionalFormatting sqref="B780">
     <cfRule type="duplicateValues" dxfId="992" priority="1347"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B778">
+  <conditionalFormatting sqref="B780">
     <cfRule type="duplicateValues" dxfId="991" priority="1345"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B780">
+  <conditionalFormatting sqref="B782:B784">
     <cfRule type="duplicateValues" dxfId="990" priority="1343"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B780">
+  <conditionalFormatting sqref="B782:B784">
     <cfRule type="duplicateValues" dxfId="989" priority="1344"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B780">
+  <conditionalFormatting sqref="B782:B784">
     <cfRule type="duplicateValues" dxfId="988" priority="1342"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B781">
+  <conditionalFormatting sqref="B785:B786">
     <cfRule type="duplicateValues" dxfId="987" priority="1337"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B781">
+  <conditionalFormatting sqref="B785:B786">
     <cfRule type="duplicateValues" dxfId="986" priority="1338"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B781">
+  <conditionalFormatting sqref="B785:B786">
     <cfRule type="duplicateValues" dxfId="985" priority="1336"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B782">
+  <conditionalFormatting sqref="B787">
     <cfRule type="duplicateValues" dxfId="984" priority="1334"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B782">
+  <conditionalFormatting sqref="B787">
     <cfRule type="duplicateValues" dxfId="983" priority="1335"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B782">
+  <conditionalFormatting sqref="B787">
     <cfRule type="duplicateValues" dxfId="982" priority="1333"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B784">
+  <conditionalFormatting sqref="B789">
     <cfRule type="duplicateValues" dxfId="981" priority="1331"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B784">
+  <conditionalFormatting sqref="B789">
     <cfRule type="duplicateValues" dxfId="980" priority="1332"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B784">
+  <conditionalFormatting sqref="B789">
     <cfRule type="duplicateValues" dxfId="979" priority="1330"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B785">
+  <conditionalFormatting sqref="B790:B791">
     <cfRule type="duplicateValues" dxfId="978" priority="1325"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B785">
+  <conditionalFormatting sqref="B790:B791">
     <cfRule type="duplicateValues" dxfId="977" priority="1326"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B785">
+  <conditionalFormatting sqref="B790:B791">
     <cfRule type="duplicateValues" dxfId="976" priority="1324"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B786">
+  <conditionalFormatting sqref="B792">
     <cfRule type="duplicateValues" dxfId="975" priority="1317"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B786">
+  <conditionalFormatting sqref="B792">
     <cfRule type="duplicateValues" dxfId="974" priority="1316"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B786">
+  <conditionalFormatting sqref="B792">
     <cfRule type="duplicateValues" dxfId="973" priority="1315"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B787">
+  <conditionalFormatting sqref="B793:B795">
     <cfRule type="duplicateValues" dxfId="972" priority="1314"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B787">
+  <conditionalFormatting sqref="B793:B795">
     <cfRule type="duplicateValues" dxfId="971" priority="1313"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B787">
+  <conditionalFormatting sqref="B793:B795">
     <cfRule type="duplicateValues" dxfId="970" priority="1312"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B789">
+  <conditionalFormatting sqref="B800:B802">
     <cfRule type="duplicateValues" dxfId="969" priority="1311"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B789">
+  <conditionalFormatting sqref="B800:B802">
     <cfRule type="duplicateValues" dxfId="968" priority="1310"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B789">
+  <conditionalFormatting sqref="B800:B802">
     <cfRule type="duplicateValues" dxfId="967" priority="1309"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B788">
+  <conditionalFormatting sqref="B796:B799">
     <cfRule type="duplicateValues" dxfId="966" priority="1308"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B788">
+  <conditionalFormatting sqref="B796:B799">
     <cfRule type="duplicateValues" dxfId="965" priority="1307"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B788">
+  <conditionalFormatting sqref="B796:B799">
     <cfRule type="duplicateValues" dxfId="964" priority="1306"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B791">
+  <conditionalFormatting sqref="B805:B807">
     <cfRule type="duplicateValues" dxfId="963" priority="1304"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B791">
+  <conditionalFormatting sqref="B805:B807">
     <cfRule type="duplicateValues" dxfId="962" priority="1305"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B791">
+  <conditionalFormatting sqref="B805:B807">
     <cfRule type="duplicateValues" dxfId="961" priority="1303"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B793">
+  <conditionalFormatting sqref="B810:B815">
     <cfRule type="duplicateValues" dxfId="960" priority="1295"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B793">
+  <conditionalFormatting sqref="B810:B815">
     <cfRule type="duplicateValues" dxfId="959" priority="1296"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B793">
+  <conditionalFormatting sqref="B810:B815">
     <cfRule type="duplicateValues" dxfId="958" priority="1294"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B794">
+  <conditionalFormatting sqref="B816:B819">
     <cfRule type="duplicateValues" dxfId="957" priority="1289"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B794">
+  <conditionalFormatting sqref="B816:B819">
     <cfRule type="duplicateValues" dxfId="956" priority="1290"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B794">
+  <conditionalFormatting sqref="B816:B819">
     <cfRule type="duplicateValues" dxfId="955" priority="1288"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B796">
+  <conditionalFormatting sqref="B825:B828">
     <cfRule type="duplicateValues" dxfId="954" priority="1283"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B796">
+  <conditionalFormatting sqref="B825:B828">
     <cfRule type="duplicateValues" dxfId="953" priority="1284"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B796">
+  <conditionalFormatting sqref="B825:B828">
     <cfRule type="duplicateValues" dxfId="952" priority="1282"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B795">
+  <conditionalFormatting sqref="B820:B824">
     <cfRule type="duplicateValues" dxfId="951" priority="1281"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B795">
+  <conditionalFormatting sqref="B820:B824">
     <cfRule type="duplicateValues" dxfId="950" priority="1280"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B795">
+  <conditionalFormatting sqref="B820:B824">
     <cfRule type="duplicateValues" dxfId="949" priority="1279"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B797">
+  <conditionalFormatting sqref="B829">
     <cfRule type="duplicateValues" dxfId="948" priority="1274"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B797">
+  <conditionalFormatting sqref="B829">
     <cfRule type="duplicateValues" dxfId="947" priority="1275"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B797">
+  <conditionalFormatting sqref="B829">
     <cfRule type="duplicateValues" dxfId="946" priority="1273"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B799">
+  <conditionalFormatting sqref="B832">
     <cfRule type="duplicateValues" dxfId="945" priority="1272"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B799">
+  <conditionalFormatting sqref="B832">
     <cfRule type="duplicateValues" dxfId="944" priority="1271"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B799">
+  <conditionalFormatting sqref="B832">
     <cfRule type="duplicateValues" dxfId="943" priority="1270"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B800">
+  <conditionalFormatting sqref="B833">
     <cfRule type="duplicateValues" dxfId="942" priority="1268"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B800">
+  <conditionalFormatting sqref="B833">
     <cfRule type="duplicateValues" dxfId="941" priority="1269"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B800">
+  <conditionalFormatting sqref="B833">
     <cfRule type="duplicateValues" dxfId="940" priority="1267"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B801">
+  <conditionalFormatting sqref="B834">
     <cfRule type="duplicateValues" dxfId="939" priority="1259"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B801">
+  <conditionalFormatting sqref="B834">
     <cfRule type="duplicateValues" dxfId="938" priority="1260"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B801">
+  <conditionalFormatting sqref="B834">
     <cfRule type="duplicateValues" dxfId="937" priority="1258"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B752 D46 B573:B574 B46 B104:B106 B109:B111 B126 B131 B134 B137 B143:B147 B150:B152 B159:B160 D154 B169 B181 B188 B190 B199 D195 B212 B222:B224 B229 B231:B232 B239:B240 B242:B244 B251 B258:B261 B264:B269 B273 B278 B288:B289 B291 B295:B299 B306:B307 B324 B331 B333 B337:B338 B340:B341 B343 B348 B345:B346 B351 B364 B372:B373 B378:B380 B389:B390 B396:B397 B401 B420 B430 B433 B438:B439 B442 B444 B448 B451 B459 B463 B466 B475:B476 B480 B488 B492:B495 B507 B514 B519 B524 B528:B529 B531:B535 B537 B539 B560 B576 B590 B599:B600 B622:B623 B648:B655 B687:B691 B724 B732:B734 B740 B755 B772 B775 B779 B783 B790 B792 B798 B808 B824 B827 B835 B837:B838 B844:B845 B850:B852 B874 B877 B880 B893:B896 B907 B909 B911:B912 B916 B919 B924:B925 B929 B931 B933:B934 B945 B947 B966 B980 B996:B997 B999 B1001:B1002 B1011 B1019:B1048576 B1:B8 B11:B15 B18:B19 B22 B24 B30:B31 B34 B39:B41 B43 B48:B50 B53 B56:B58 B62:B64 B74:B94 B96:B102 B114:B119 B122 B124 B183:B184 B468">
+  <conditionalFormatting sqref="B841 B830:B831 B808:B809 B803:B804 B788 B781 B752 D46 B573:B574 B46 B104:B106 B109:B111 B126 B131 B134 B137 B143:B147 B150:B152 B159:B160 D154 B169 B181 B188 B190 B199 D195 B212 B222:B224 B229 B231:B232 B239:B240 B242:B244 B251 B258:B261 B264:B269 B273 B278 B288:B289 B291 B295:B299 B306:B307 B324 B331 B333 B337:B338 B340:B341 B343 B348 B345:B346 B351 B364 B372:B373 B378:B380 B389:B390 B396:B397 B401 B420 B430 B433 B438:B439 B442 B444 B448 B451 B459 B463 B466 B475:B476 B480 B488 B492:B495 B507 B514 B519 B524 B528:B529 B531:B535 B537 B539 B560 B576 B590 B599:B600 B622:B623 B648:B655 B687:B691 B724 B732:B734 B740 B755 B772 B775 B857 B860 B868 B870:B871 B877:B878 B883:B885 B907 B910 B913 B926:B929 B940 B942 B944:B945 B949 B952 B957:B958 B962 B964 B966:B967 B978 B980 B999 B1013 B1029:B1030 B1032 B1034:B1035 B1044 B1052:B1048576 B1:B8 B11:B15 B18:B19 B22 B24 B30:B31 B34 B39:B41 B43 B48:B50 B53 B56:B58 B62:B64 B74:B94 B96:B102 B114:B119 B122 B124 B183:B184 B468">
     <cfRule type="duplicateValues" dxfId="936" priority="2600"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B752 B573:B574 B231:B232 B239:B240 B242:B244 B251 B258:B261 B264:B269 B273 B278 B288:B289 B291 B295:B299 B306:B307 B324 B331 B333 B337:B338 B340:B341 B343 B348 B345:B346 B351 B364 B372:B373 B378:B380 B389:B390 B396:B397 B401 B420 B430 B433 B438:B439 B442 B444 B448 B451 B459 B463 B466 B475:B476 B480 B488 B492:B495 B507 B514 B519 B524 B528:B529 B531:B535 B537 B539 B560 B576 B590 B599:B600 B622:B623 B648:B655 B687:B691 B724 B732:B734 B740 B755 B772 B775 B779 B783 B790 B792 B798 B808 B824 B827 B835 B837:B838 B844:B845 B850:B852 B874 B877 B880 B893:B896 B907 B909 B911:B912 B916 B919 B924:B925 B929 B931 B933:B934 B945 B947 B966 B980 B996:B997 B999 B1001:B1002 B1011 B1019:B1048576 B1:B8 B11:B15 B18:B19 B22 B24 B30:B31 B34 B39:B41 B43 B46 B48:B50 B53 B56:B58 B62:B64 B74:B94 B96:B106 B108:B111 B114:B119 B122 B124:B126 B128:B152 B154:B155 B157 B159:B164 B166:B167 B169:B170 B179 B181 B183:B184 B186:B188 B190:B202 B204:B205 B209:B212 B214 B216:B217 B219:B220 B222:B229 B468">
+  <conditionalFormatting sqref="B841 B830:B831 B808:B809 B803:B804 B788 B781 B752 B573:B574 B231:B232 B239:B240 B242:B244 B251 B258:B261 B264:B269 B273 B278 B288:B289 B291 B295:B299 B306:B307 B324 B331 B333 B337:B338 B340:B341 B343 B348 B345:B346 B351 B364 B372:B373 B378:B380 B389:B390 B396:B397 B401 B420 B430 B433 B438:B439 B442 B444 B448 B451 B459 B463 B466 B475:B476 B480 B488 B492:B495 B507 B514 B519 B524 B528:B529 B531:B535 B537 B539 B560 B576 B590 B599:B600 B622:B623 B648:B655 B687:B691 B724 B732:B734 B740 B755 B772 B775 B857 B860 B868 B870:B871 B877:B878 B883:B885 B907 B910 B913 B926:B929 B940 B942 B944:B945 B949 B952 B957:B958 B962 B964 B966:B967 B978 B980 B999 B1013 B1029:B1030 B1032 B1034:B1035 B1044 B1052:B1048576 B1:B8 B11:B15 B18:B19 B22 B24 B30:B31 B34 B39:B41 B43 B46 B48:B50 B53 B56:B58 B62:B64 B74:B94 B96:B106 B108:B111 B114:B119 B122 B124:B126 B128:B152 B154:B155 B157 B159:B164 B166:B167 B169:B170 B179 B181 B183:B184 B186:B188 B190:B202 B204:B205 B209:B212 B214 B216:B217 B219:B220 B222:B229 B468">
     <cfRule type="duplicateValues" dxfId="935" priority="2712"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B752 B755 B772 B775 B779 B783 B790 B792 B798 B808 B824 B827 B835 B837:B838 B844:B845 B850:B852 B874 B877 B880 B893:B896 B907 B909 B911:B912 B916 B919 B924:B925 B929 B931 B933:B934 B945 B947 B966 B980 B996:B997 B999 B1001:B1002 B1011 B1019:B1048576 B1:B8 B11:B15 B18:B19 B22 B24 B30:B31 B34 B39:B41 B43 B46 B48:B50 B53 B56:B58 B62:B64 B74:B94 B96:B106 B108:B111 B114:B119 B122 B124:B126 B128:B152 B154:B155 B157 B159:B164 B166:B167 B169:B170 B179 B181 B183:B184 B186:B188 B190:B202 B204:B205 B209:B212 B214 B216:B217 B219:B220 B222:B229 B231:B232 B237:B249 B251:B252 B255 B258:B261 B263:B269 B271 B273:B279 B281:B283 B286:B310 B312 B315 B317:B318 B320:B321 B324 B329:B353 B355:B361 B363:B368 B370:B383 B385:B390 B392:B414 B416:B417 B420:B440 B442:B455 B457:B463 B465:B466 B468:B470 B473:B476 B478:B482 B484 B486 B488:B490 B492:B498 B501:B504 B507:B510 B512:B547 B549 B551:B558 B560 B562:B569 B571:B584 B586:B587 B589:B596 B599:B730 B732:B743">
+  <conditionalFormatting sqref="B841 B830:B831 B808:B809 B803:B804 B788 B781 B752 B755 B772 B775 B857 B860 B868 B870:B871 B877:B878 B883:B885 B907 B910 B913 B926:B929 B940 B942 B944:B945 B949 B952 B957:B958 B962 B964 B966:B967 B978 B980 B999 B1013 B1029:B1030 B1032 B1034:B1035 B1044 B1052:B1048576 B1:B8 B11:B15 B18:B19 B22 B24 B30:B31 B34 B39:B41 B43 B46 B48:B50 B53 B56:B58 B62:B64 B74:B94 B96:B106 B108:B111 B114:B119 B122 B124:B126 B128:B152 B154:B155 B157 B159:B164 B166:B167 B169:B170 B179 B181 B183:B184 B186:B188 B190:B202 B204:B205 B209:B212 B214 B216:B217 B219:B220 B222:B229 B231:B232 B237:B249 B251:B252 B255 B258:B261 B263:B269 B271 B273:B279 B281:B283 B286:B310 B312 B315 B317:B318 B320:B321 B324 B329:B353 B355:B361 B363:B368 B370:B383 B385:B390 B392:B414 B416:B417 B420:B440 B442:B455 B457:B463 B465:B466 B468:B470 B473:B476 B478:B482 B484 B486 B488:B490 B492:B498 B501:B504 B507:B510 B512:B547 B549 B551:B558 B560 B562:B569 B571:B584 B586:B587 B589:B596 B599:B730 B732:B743">
     <cfRule type="duplicateValues" dxfId="934" priority="2798"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B802">
+  <conditionalFormatting sqref="B835">
     <cfRule type="duplicateValues" dxfId="933" priority="1252"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B802">
+  <conditionalFormatting sqref="B835">
     <cfRule type="duplicateValues" dxfId="932" priority="1253"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B802">
+  <conditionalFormatting sqref="B835">
     <cfRule type="duplicateValues" dxfId="931" priority="1254"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B803">
+  <conditionalFormatting sqref="B836">
     <cfRule type="duplicateValues" dxfId="930" priority="1247"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B803">
+  <conditionalFormatting sqref="B836">
     <cfRule type="duplicateValues" dxfId="929" priority="1246"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B803">
+  <conditionalFormatting sqref="B836">
     <cfRule type="duplicateValues" dxfId="928" priority="1248"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B804">
+  <conditionalFormatting sqref="B837">
     <cfRule type="duplicateValues" dxfId="927" priority="1243"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B804">
+  <conditionalFormatting sqref="B837">
     <cfRule type="duplicateValues" dxfId="926" priority="1244"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B804">
+  <conditionalFormatting sqref="B837">
     <cfRule type="duplicateValues" dxfId="925" priority="1245"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B805">
+  <conditionalFormatting sqref="B838">
     <cfRule type="duplicateValues" dxfId="924" priority="1238"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B805">
+  <conditionalFormatting sqref="B838">
     <cfRule type="duplicateValues" dxfId="923" priority="1239"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B805">
+  <conditionalFormatting sqref="B838">
     <cfRule type="duplicateValues" dxfId="922" priority="1237"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B806">
+  <conditionalFormatting sqref="B839">
     <cfRule type="duplicateValues" dxfId="921" priority="1231"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B806">
+  <conditionalFormatting sqref="B839">
     <cfRule type="duplicateValues" dxfId="920" priority="1232"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B806">
+  <conditionalFormatting sqref="B839">
     <cfRule type="duplicateValues" dxfId="919" priority="1233"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B807">
+  <conditionalFormatting sqref="B840">
     <cfRule type="duplicateValues" dxfId="918" priority="1229"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B807">
+  <conditionalFormatting sqref="B840">
     <cfRule type="duplicateValues" dxfId="917" priority="1230"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B807">
+  <conditionalFormatting sqref="B840">
     <cfRule type="duplicateValues" dxfId="916" priority="1228"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B809">
+  <conditionalFormatting sqref="B842">
     <cfRule type="duplicateValues" dxfId="915" priority="1223"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B809">
+  <conditionalFormatting sqref="B842">
     <cfRule type="duplicateValues" dxfId="914" priority="1224"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B810">
+  <conditionalFormatting sqref="B843">
     <cfRule type="duplicateValues" dxfId="913" priority="1221"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B810">
+  <conditionalFormatting sqref="B843">
     <cfRule type="duplicateValues" dxfId="912" priority="1220"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B810">
+  <conditionalFormatting sqref="B843">
     <cfRule type="duplicateValues" dxfId="911" priority="1222"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B811">
+  <conditionalFormatting sqref="B844">
     <cfRule type="duplicateValues" dxfId="910" priority="1214"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B811">
+  <conditionalFormatting sqref="B844">
     <cfRule type="duplicateValues" dxfId="909" priority="1215"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B811">
+  <conditionalFormatting sqref="B844">
     <cfRule type="duplicateValues" dxfId="908" priority="1216"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B812">
+  <conditionalFormatting sqref="B845">
     <cfRule type="duplicateValues" dxfId="907" priority="1211"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B812">
+  <conditionalFormatting sqref="B845">
     <cfRule type="duplicateValues" dxfId="906" priority="1212"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B812">
+  <conditionalFormatting sqref="B845">
     <cfRule type="duplicateValues" dxfId="905" priority="1213"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B813">
+  <conditionalFormatting sqref="B846">
     <cfRule type="duplicateValues" dxfId="904" priority="1205"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B813">
+  <conditionalFormatting sqref="B846">
     <cfRule type="duplicateValues" dxfId="903" priority="1206"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B813">
+  <conditionalFormatting sqref="B846">
     <cfRule type="duplicateValues" dxfId="902" priority="1207"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B814">
+  <conditionalFormatting sqref="B847">
     <cfRule type="duplicateValues" dxfId="901" priority="1190"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B814">
+  <conditionalFormatting sqref="B847">
     <cfRule type="duplicateValues" dxfId="900" priority="1191"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B814">
+  <conditionalFormatting sqref="B847">
     <cfRule type="duplicateValues" dxfId="899" priority="1192"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B815">
+  <conditionalFormatting sqref="B848">
     <cfRule type="duplicateValues" dxfId="898" priority="1184"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B815">
+  <conditionalFormatting sqref="B848">
     <cfRule type="duplicateValues" dxfId="897" priority="1185"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B815">
+  <conditionalFormatting sqref="B848">
     <cfRule type="duplicateValues" dxfId="896" priority="1186"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B816">
+  <conditionalFormatting sqref="B849">
     <cfRule type="duplicateValues" dxfId="895" priority="1178"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B816">
+  <conditionalFormatting sqref="B849">
     <cfRule type="duplicateValues" dxfId="894" priority="1179"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B816">
+  <conditionalFormatting sqref="B849">
     <cfRule type="duplicateValues" dxfId="893" priority="1180"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B817">
+  <conditionalFormatting sqref="B850">
     <cfRule type="duplicateValues" dxfId="892" priority="1176"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B817">
+  <conditionalFormatting sqref="B850">
     <cfRule type="duplicateValues" dxfId="891" priority="1177"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B817">
+  <conditionalFormatting sqref="B850">
     <cfRule type="duplicateValues" dxfId="890" priority="1175"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B818">
+  <conditionalFormatting sqref="B851">
     <cfRule type="duplicateValues" dxfId="889" priority="1166"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B818">
+  <conditionalFormatting sqref="B851">
     <cfRule type="duplicateValues" dxfId="888" priority="1167"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B818">
+  <conditionalFormatting sqref="B851">
     <cfRule type="duplicateValues" dxfId="887" priority="1168"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B819">
+  <conditionalFormatting sqref="B852">
     <cfRule type="duplicateValues" dxfId="886" priority="1158"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B819">
+  <conditionalFormatting sqref="B852">
     <cfRule type="duplicateValues" dxfId="885" priority="1157"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B819">
+  <conditionalFormatting sqref="B852">
     <cfRule type="duplicateValues" dxfId="884" priority="1159"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B820">
+  <conditionalFormatting sqref="B853">
     <cfRule type="duplicateValues" dxfId="883" priority="1155"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B820">
+  <conditionalFormatting sqref="B853">
     <cfRule type="duplicateValues" dxfId="882" priority="1154"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B820">
+  <conditionalFormatting sqref="B853">
     <cfRule type="duplicateValues" dxfId="881" priority="1156"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B821">
+  <conditionalFormatting sqref="B854">
     <cfRule type="duplicateValues" dxfId="880" priority="1149"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B821">
+  <conditionalFormatting sqref="B854">
     <cfRule type="duplicateValues" dxfId="879" priority="1150"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B821">
+  <conditionalFormatting sqref="B854">
     <cfRule type="duplicateValues" dxfId="878" priority="1148"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B822">
+  <conditionalFormatting sqref="B855">
     <cfRule type="duplicateValues" dxfId="877" priority="1142"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B822">
+  <conditionalFormatting sqref="B855">
     <cfRule type="duplicateValues" dxfId="876" priority="1143"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B822">
+  <conditionalFormatting sqref="B855">
     <cfRule type="duplicateValues" dxfId="875" priority="1144"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B823">
+  <conditionalFormatting sqref="B856">
     <cfRule type="duplicateValues" dxfId="874" priority="1139"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B823">
+  <conditionalFormatting sqref="B856">
     <cfRule type="duplicateValues" dxfId="873" priority="1140"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B823">
+  <conditionalFormatting sqref="B856">
     <cfRule type="duplicateValues" dxfId="872" priority="1141"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B825">
+  <conditionalFormatting sqref="B858">
     <cfRule type="duplicateValues" dxfId="871" priority="1136"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B825">
+  <conditionalFormatting sqref="B858">
     <cfRule type="duplicateValues" dxfId="870" priority="1137"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B825">
+  <conditionalFormatting sqref="B858">
     <cfRule type="duplicateValues" dxfId="869" priority="1138"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B826">
+  <conditionalFormatting sqref="B859">
     <cfRule type="duplicateValues" dxfId="868" priority="1133"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B826">
+  <conditionalFormatting sqref="B859">
     <cfRule type="duplicateValues" dxfId="867" priority="1134"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B826">
+  <conditionalFormatting sqref="B859">
     <cfRule type="duplicateValues" dxfId="866" priority="1135"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B828">
+  <conditionalFormatting sqref="B861">
     <cfRule type="duplicateValues" dxfId="865" priority="1132"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B828">
+  <conditionalFormatting sqref="B861">
     <cfRule type="duplicateValues" dxfId="864" priority="1131"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B828">
+  <conditionalFormatting sqref="B861">
     <cfRule type="duplicateValues" dxfId="863" priority="1130"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B829">
+  <conditionalFormatting sqref="B862">
     <cfRule type="duplicateValues" dxfId="862" priority="1127"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B829">
+  <conditionalFormatting sqref="B862">
     <cfRule type="duplicateValues" dxfId="861" priority="1128"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B829">
+  <conditionalFormatting sqref="B862">
     <cfRule type="duplicateValues" dxfId="860" priority="1129"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B830">
+  <conditionalFormatting sqref="B863">
     <cfRule type="duplicateValues" dxfId="859" priority="1124"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B830">
+  <conditionalFormatting sqref="B863">
     <cfRule type="duplicateValues" dxfId="858" priority="1125"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B830">
+  <conditionalFormatting sqref="B863">
     <cfRule type="duplicateValues" dxfId="857" priority="1126"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B833">
+  <conditionalFormatting sqref="B866">
     <cfRule type="duplicateValues" dxfId="856" priority="1122"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B833">
+  <conditionalFormatting sqref="B866">
     <cfRule type="duplicateValues" dxfId="855" priority="1123"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B833">
+  <conditionalFormatting sqref="B866">
     <cfRule type="duplicateValues" dxfId="854" priority="1121"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B831">
+  <conditionalFormatting sqref="B864">
     <cfRule type="duplicateValues" dxfId="853" priority="1119"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B831">
+  <conditionalFormatting sqref="B864">
     <cfRule type="duplicateValues" dxfId="852" priority="1120"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B832">
+  <conditionalFormatting sqref="B865">
     <cfRule type="duplicateValues" dxfId="851" priority="1114"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B832">
+  <conditionalFormatting sqref="B865">
     <cfRule type="duplicateValues" dxfId="850" priority="1115"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B834">
+  <conditionalFormatting sqref="B867">
     <cfRule type="duplicateValues" dxfId="849" priority="1109"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B834">
+  <conditionalFormatting sqref="B867">
     <cfRule type="duplicateValues" dxfId="848" priority="1110"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B834">
+  <conditionalFormatting sqref="B867">
     <cfRule type="duplicateValues" dxfId="847" priority="1108"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B836">
+  <conditionalFormatting sqref="B869">
     <cfRule type="duplicateValues" dxfId="846" priority="1105"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B836">
+  <conditionalFormatting sqref="B869">
     <cfRule type="duplicateValues" dxfId="845" priority="1106"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B836">
+  <conditionalFormatting sqref="B869">
     <cfRule type="duplicateValues" dxfId="844" priority="1107"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B839">
+  <conditionalFormatting sqref="B872">
     <cfRule type="duplicateValues" dxfId="843" priority="1102"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B839">
+  <conditionalFormatting sqref="B872">
     <cfRule type="duplicateValues" dxfId="842" priority="1103"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B839">
+  <conditionalFormatting sqref="B872">
     <cfRule type="duplicateValues" dxfId="841" priority="1104"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B840">
+  <conditionalFormatting sqref="B873">
     <cfRule type="duplicateValues" dxfId="840" priority="1099"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B840">
+  <conditionalFormatting sqref="B873">
     <cfRule type="duplicateValues" dxfId="839" priority="1100"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B840">
+  <conditionalFormatting sqref="B873">
     <cfRule type="duplicateValues" dxfId="838" priority="1101"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B841">
+  <conditionalFormatting sqref="B874">
     <cfRule type="duplicateValues" dxfId="837" priority="1096"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B841">
+  <conditionalFormatting sqref="B874">
     <cfRule type="duplicateValues" dxfId="836" priority="1097"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B841">
+  <conditionalFormatting sqref="B874">
     <cfRule type="duplicateValues" dxfId="835" priority="1098"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B842">
+  <conditionalFormatting sqref="B875">
     <cfRule type="duplicateValues" dxfId="834" priority="1084"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B842">
+  <conditionalFormatting sqref="B875">
     <cfRule type="duplicateValues" dxfId="833" priority="1085"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B842">
+  <conditionalFormatting sqref="B875">
     <cfRule type="duplicateValues" dxfId="832" priority="1086"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B843">
+  <conditionalFormatting sqref="B876">
     <cfRule type="duplicateValues" dxfId="831" priority="1079"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B843">
+  <conditionalFormatting sqref="B876">
     <cfRule type="duplicateValues" dxfId="830" priority="1080"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B846">
+  <conditionalFormatting sqref="B879">
     <cfRule type="duplicateValues" dxfId="829" priority="1073"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B846">
+  <conditionalFormatting sqref="B879">
     <cfRule type="duplicateValues" dxfId="828" priority="1074"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B846">
+  <conditionalFormatting sqref="B879">
     <cfRule type="duplicateValues" dxfId="827" priority="1075"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B847">
+  <conditionalFormatting sqref="B880">
     <cfRule type="duplicateValues" dxfId="826" priority="1067"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B847">
+  <conditionalFormatting sqref="B880">
     <cfRule type="duplicateValues" dxfId="825" priority="1068"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B847">
+  <conditionalFormatting sqref="B880">
     <cfRule type="duplicateValues" dxfId="824" priority="1069"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B848">
+  <conditionalFormatting sqref="B881">
     <cfRule type="duplicateValues" dxfId="823" priority="1064"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B848">
+  <conditionalFormatting sqref="B881">
     <cfRule type="duplicateValues" dxfId="822" priority="1065"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B848">
+  <conditionalFormatting sqref="B881">
     <cfRule type="duplicateValues" dxfId="821" priority="1066"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B849">
+  <conditionalFormatting sqref="B882">
     <cfRule type="duplicateValues" dxfId="820" priority="1058"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B849">
+  <conditionalFormatting sqref="B882">
     <cfRule type="duplicateValues" dxfId="819" priority="1059"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B849">
+  <conditionalFormatting sqref="B882">
     <cfRule type="duplicateValues" dxfId="818" priority="1060"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B853">
+  <conditionalFormatting sqref="B886">
     <cfRule type="duplicateValues" dxfId="817" priority="1049"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B853">
+  <conditionalFormatting sqref="B886">
     <cfRule type="duplicateValues" dxfId="816" priority="1050"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B853">
+  <conditionalFormatting sqref="B886">
     <cfRule type="duplicateValues" dxfId="815" priority="1051"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B854">
+  <conditionalFormatting sqref="B887">
     <cfRule type="duplicateValues" dxfId="814" priority="1046"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B854">
+  <conditionalFormatting sqref="B887">
     <cfRule type="duplicateValues" dxfId="813" priority="1047"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B854">
+  <conditionalFormatting sqref="B887">
     <cfRule type="duplicateValues" dxfId="812" priority="1048"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B855">
+  <conditionalFormatting sqref="B888">
     <cfRule type="duplicateValues" dxfId="811" priority="1040"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B855">
+  <conditionalFormatting sqref="B888">
     <cfRule type="duplicateValues" dxfId="810" priority="1041"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B855">
+  <conditionalFormatting sqref="B888">
     <cfRule type="duplicateValues" dxfId="809" priority="1042"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B856">
+  <conditionalFormatting sqref="B889">
     <cfRule type="duplicateValues" dxfId="808" priority="1031"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B856">
+  <conditionalFormatting sqref="B889">
     <cfRule type="duplicateValues" dxfId="807" priority="1032"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B856">
+  <conditionalFormatting sqref="B889">
     <cfRule type="duplicateValues" dxfId="806" priority="1033"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B857">
+  <conditionalFormatting sqref="B890">
     <cfRule type="duplicateValues" dxfId="805" priority="1028"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B857">
+  <conditionalFormatting sqref="B890">
     <cfRule type="duplicateValues" dxfId="804" priority="1029"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B857">
+  <conditionalFormatting sqref="B890">
     <cfRule type="duplicateValues" dxfId="803" priority="1030"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B858">
+  <conditionalFormatting sqref="B891">
     <cfRule type="duplicateValues" dxfId="802" priority="1022"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B858">
+  <conditionalFormatting sqref="B891">
     <cfRule type="duplicateValues" dxfId="801" priority="1023"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B858">
+  <conditionalFormatting sqref="B891">
     <cfRule type="duplicateValues" dxfId="800" priority="1024"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B859">
+  <conditionalFormatting sqref="B892">
     <cfRule type="duplicateValues" dxfId="799" priority="1020"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B859">
+  <conditionalFormatting sqref="B892">
     <cfRule type="duplicateValues" dxfId="798" priority="1021"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B859">
+  <conditionalFormatting sqref="B892">
     <cfRule type="duplicateValues" dxfId="797" priority="1019"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B860">
+  <conditionalFormatting sqref="B893">
     <cfRule type="duplicateValues" dxfId="796" priority="1016"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B860">
+  <conditionalFormatting sqref="B893">
     <cfRule type="duplicateValues" dxfId="795" priority="1017"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B860">
+  <conditionalFormatting sqref="B893">
     <cfRule type="duplicateValues" dxfId="794" priority="1018"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B861">
+  <conditionalFormatting sqref="B894">
     <cfRule type="duplicateValues" dxfId="793" priority="1014"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B861">
+  <conditionalFormatting sqref="B894">
     <cfRule type="duplicateValues" dxfId="792" priority="1013"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B861">
+  <conditionalFormatting sqref="B894">
     <cfRule type="duplicateValues" dxfId="791" priority="1015"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B862">
+  <conditionalFormatting sqref="B895">
     <cfRule type="duplicateValues" dxfId="790" priority="1004"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B862">
+  <conditionalFormatting sqref="B895">
     <cfRule type="duplicateValues" dxfId="789" priority="1005"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B862">
+  <conditionalFormatting sqref="B895">
     <cfRule type="duplicateValues" dxfId="788" priority="1006"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B863">
+  <conditionalFormatting sqref="B896">
     <cfRule type="duplicateValues" dxfId="787" priority="1001"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B863">
+  <conditionalFormatting sqref="B896">
     <cfRule type="duplicateValues" dxfId="786" priority="1002"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B863">
+  <conditionalFormatting sqref="B896">
     <cfRule type="duplicateValues" dxfId="785" priority="1003"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B864">
+  <conditionalFormatting sqref="B897">
     <cfRule type="duplicateValues" dxfId="784" priority="998"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B864">
+  <conditionalFormatting sqref="B897">
     <cfRule type="duplicateValues" dxfId="783" priority="999"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B864">
+  <conditionalFormatting sqref="B897">
     <cfRule type="duplicateValues" dxfId="782" priority="1000"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B865">
+  <conditionalFormatting sqref="B898">
     <cfRule type="duplicateValues" dxfId="781" priority="995"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B865">
+  <conditionalFormatting sqref="B898">
     <cfRule type="duplicateValues" dxfId="780" priority="996"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B865">
+  <conditionalFormatting sqref="B898">
     <cfRule type="duplicateValues" dxfId="779" priority="997"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B866">
+  <conditionalFormatting sqref="B899">
     <cfRule type="duplicateValues" dxfId="778" priority="992"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B866">
+  <conditionalFormatting sqref="B899">
     <cfRule type="duplicateValues" dxfId="777" priority="993"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B866">
+  <conditionalFormatting sqref="B899">
     <cfRule type="duplicateValues" dxfId="776" priority="994"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B867">
+  <conditionalFormatting sqref="B900">
     <cfRule type="duplicateValues" dxfId="775" priority="989"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B867">
+  <conditionalFormatting sqref="B900">
     <cfRule type="duplicateValues" dxfId="774" priority="990"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B867">
+  <conditionalFormatting sqref="B900">
     <cfRule type="duplicateValues" dxfId="773" priority="991"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B868">
+  <conditionalFormatting sqref="B901">
     <cfRule type="duplicateValues" dxfId="772" priority="983"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B868">
+  <conditionalFormatting sqref="B901">
     <cfRule type="duplicateValues" dxfId="771" priority="984"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B868">
+  <conditionalFormatting sqref="B901">
     <cfRule type="duplicateValues" dxfId="770" priority="985"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B869">
+  <conditionalFormatting sqref="B902">
     <cfRule type="duplicateValues" dxfId="769" priority="980"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B869">
+  <conditionalFormatting sqref="B902">
     <cfRule type="duplicateValues" dxfId="768" priority="981"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B869">
+  <conditionalFormatting sqref="B902">
     <cfRule type="duplicateValues" dxfId="767" priority="982"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B870">
+  <conditionalFormatting sqref="B903">
     <cfRule type="duplicateValues" dxfId="766" priority="972"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B870">
+  <conditionalFormatting sqref="B903">
     <cfRule type="duplicateValues" dxfId="765" priority="973"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B871">
+  <conditionalFormatting sqref="B904">
     <cfRule type="duplicateValues" dxfId="764" priority="967"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B871">
+  <conditionalFormatting sqref="B904">
     <cfRule type="duplicateValues" dxfId="763" priority="968"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B872">
+  <conditionalFormatting sqref="B905">
     <cfRule type="duplicateValues" dxfId="762" priority="965"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B872">
+  <conditionalFormatting sqref="B905">
     <cfRule type="duplicateValues" dxfId="761" priority="964"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B872">
+  <conditionalFormatting sqref="B905">
     <cfRule type="duplicateValues" dxfId="760" priority="966"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B873">
+  <conditionalFormatting sqref="B906">
     <cfRule type="duplicateValues" dxfId="759" priority="955"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B873">
+  <conditionalFormatting sqref="B906">
     <cfRule type="duplicateValues" dxfId="758" priority="956"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B873">
+  <conditionalFormatting sqref="B906">
     <cfRule type="duplicateValues" dxfId="757" priority="957"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B875">
+  <conditionalFormatting sqref="B908">
     <cfRule type="duplicateValues" dxfId="756" priority="952"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B875">
+  <conditionalFormatting sqref="B908">
     <cfRule type="duplicateValues" dxfId="755" priority="953"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B875">
+  <conditionalFormatting sqref="B908">
     <cfRule type="duplicateValues" dxfId="754" priority="954"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B876">
+  <conditionalFormatting sqref="B909">
     <cfRule type="duplicateValues" dxfId="753" priority="949"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B876">
+  <conditionalFormatting sqref="B909">
     <cfRule type="duplicateValues" dxfId="752" priority="950"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B876">
+  <conditionalFormatting sqref="B909">
     <cfRule type="duplicateValues" dxfId="751" priority="951"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B878">
+  <conditionalFormatting sqref="B911">
     <cfRule type="duplicateValues" dxfId="750" priority="946"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B878">
+  <conditionalFormatting sqref="B911">
     <cfRule type="duplicateValues" dxfId="749" priority="947"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B878">
+  <conditionalFormatting sqref="B911">
     <cfRule type="duplicateValues" dxfId="748" priority="948"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B879">
+  <conditionalFormatting sqref="B912">
     <cfRule type="duplicateValues" dxfId="747" priority="944"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B879">
+  <conditionalFormatting sqref="B912">
     <cfRule type="duplicateValues" dxfId="746" priority="945"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B881">
+  <conditionalFormatting sqref="B914">
     <cfRule type="duplicateValues" dxfId="745" priority="936"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B881">
+  <conditionalFormatting sqref="B914">
     <cfRule type="duplicateValues" dxfId="744" priority="935"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B881">
+  <conditionalFormatting sqref="B914">
     <cfRule type="duplicateValues" dxfId="743" priority="937"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B882">
+  <conditionalFormatting sqref="B915">
     <cfRule type="duplicateValues" dxfId="742" priority="929"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B882">
+  <conditionalFormatting sqref="B915">
     <cfRule type="duplicateValues" dxfId="741" priority="930"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B882">
+  <conditionalFormatting sqref="B915">
     <cfRule type="duplicateValues" dxfId="740" priority="931"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B883">
+  <conditionalFormatting sqref="B916">
     <cfRule type="duplicateValues" dxfId="739" priority="926"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B883">
+  <conditionalFormatting sqref="B916">
     <cfRule type="duplicateValues" dxfId="738" priority="927"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B883">
+  <conditionalFormatting sqref="B916">
     <cfRule type="duplicateValues" dxfId="737" priority="928"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B884">
+  <conditionalFormatting sqref="B917">
     <cfRule type="duplicateValues" dxfId="736" priority="923"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B884">
+  <conditionalFormatting sqref="B917">
     <cfRule type="duplicateValues" dxfId="735" priority="924"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B884">
+  <conditionalFormatting sqref="B917">
     <cfRule type="duplicateValues" dxfId="734" priority="925"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B885">
+  <conditionalFormatting sqref="B918">
     <cfRule type="duplicateValues" dxfId="733" priority="920"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B885">
+  <conditionalFormatting sqref="B918">
     <cfRule type="duplicateValues" dxfId="732" priority="921"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B885">
+  <conditionalFormatting sqref="B918">
     <cfRule type="duplicateValues" dxfId="731" priority="922"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B886">
+  <conditionalFormatting sqref="B919">
     <cfRule type="duplicateValues" dxfId="730" priority="917"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B886">
+  <conditionalFormatting sqref="B919">
     <cfRule type="duplicateValues" dxfId="729" priority="918"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B886">
+  <conditionalFormatting sqref="B919">
     <cfRule type="duplicateValues" dxfId="728" priority="919"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B887">
+  <conditionalFormatting sqref="B920">
     <cfRule type="duplicateValues" dxfId="727" priority="914"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B887">
+  <conditionalFormatting sqref="B920">
     <cfRule type="duplicateValues" dxfId="726" priority="915"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B887">
+  <conditionalFormatting sqref="B920">
     <cfRule type="duplicateValues" dxfId="725" priority="916"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B888">
+  <conditionalFormatting sqref="B921">
     <cfRule type="duplicateValues" dxfId="724" priority="908"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B888">
+  <conditionalFormatting sqref="B921">
     <cfRule type="duplicateValues" dxfId="723" priority="909"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B888">
+  <conditionalFormatting sqref="B921">
     <cfRule type="duplicateValues" dxfId="722" priority="910"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B889">
+  <conditionalFormatting sqref="B922">
     <cfRule type="duplicateValues" dxfId="721" priority="905"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B889">
+  <conditionalFormatting sqref="B922">
     <cfRule type="duplicateValues" dxfId="720" priority="906"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B889">
+  <conditionalFormatting sqref="B922">
     <cfRule type="duplicateValues" dxfId="719" priority="907"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B890">
+  <conditionalFormatting sqref="B923">
     <cfRule type="duplicateValues" dxfId="718" priority="902"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B890">
+  <conditionalFormatting sqref="B923">
     <cfRule type="duplicateValues" dxfId="717" priority="903"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B890">
+  <conditionalFormatting sqref="B923">
     <cfRule type="duplicateValues" dxfId="716" priority="904"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B891">
+  <conditionalFormatting sqref="B924">
     <cfRule type="duplicateValues" dxfId="715" priority="900"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B891">
+  <conditionalFormatting sqref="B924">
     <cfRule type="duplicateValues" dxfId="714" priority="901"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B892">
+  <conditionalFormatting sqref="B925">
     <cfRule type="duplicateValues" dxfId="713" priority="897"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B892">
+  <conditionalFormatting sqref="B925">
     <cfRule type="duplicateValues" dxfId="712" priority="898"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B892">
+  <conditionalFormatting sqref="B925">
     <cfRule type="duplicateValues" dxfId="711" priority="899"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B897">
+  <conditionalFormatting sqref="B930">
     <cfRule type="duplicateValues" dxfId="710" priority="894"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B897">
+  <conditionalFormatting sqref="B930">
     <cfRule type="duplicateValues" dxfId="709" priority="895"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B897">
+  <conditionalFormatting sqref="B930">
     <cfRule type="duplicateValues" dxfId="708" priority="896"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B898">
+  <conditionalFormatting sqref="B931">
     <cfRule type="duplicateValues" dxfId="707" priority="885"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B898">
+  <conditionalFormatting sqref="B931">
     <cfRule type="duplicateValues" dxfId="706" priority="886"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B898">
+  <conditionalFormatting sqref="B931">
     <cfRule type="duplicateValues" dxfId="705" priority="887"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B899">
+  <conditionalFormatting sqref="B932">
     <cfRule type="duplicateValues" dxfId="704" priority="882"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B899">
+  <conditionalFormatting sqref="B932">
     <cfRule type="duplicateValues" dxfId="703" priority="883"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B899">
+  <conditionalFormatting sqref="B932">
     <cfRule type="duplicateValues" dxfId="702" priority="884"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B900">
+  <conditionalFormatting sqref="B933">
     <cfRule type="duplicateValues" dxfId="701" priority="879"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B900">
+  <conditionalFormatting sqref="B933">
     <cfRule type="duplicateValues" dxfId="700" priority="880"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B900">
+  <conditionalFormatting sqref="B933">
     <cfRule type="duplicateValues" dxfId="699" priority="881"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B901">
+  <conditionalFormatting sqref="B934">
     <cfRule type="duplicateValues" dxfId="698" priority="876"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B901">
+  <conditionalFormatting sqref="B934">
     <cfRule type="duplicateValues" dxfId="697" priority="877"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B901">
+  <conditionalFormatting sqref="B934">
     <cfRule type="duplicateValues" dxfId="696" priority="878"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B902">
+  <conditionalFormatting sqref="B935">
     <cfRule type="duplicateValues" dxfId="695" priority="873"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B902">
+  <conditionalFormatting sqref="B935">
     <cfRule type="duplicateValues" dxfId="694" priority="874"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B902">
+  <conditionalFormatting sqref="B935">
     <cfRule type="duplicateValues" dxfId="693" priority="875"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B903">
+  <conditionalFormatting sqref="B936">
     <cfRule type="duplicateValues" dxfId="692" priority="871"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B903">
+  <conditionalFormatting sqref="B936">
     <cfRule type="duplicateValues" dxfId="691" priority="870"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B903">
+  <conditionalFormatting sqref="B936">
     <cfRule type="duplicateValues" dxfId="690" priority="872"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B904">
+  <conditionalFormatting sqref="B937">
     <cfRule type="duplicateValues" dxfId="689" priority="867"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B904">
+  <conditionalFormatting sqref="B937">
     <cfRule type="duplicateValues" dxfId="688" priority="868"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B904">
+  <conditionalFormatting sqref="B937">
     <cfRule type="duplicateValues" dxfId="687" priority="869"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B905">
+  <conditionalFormatting sqref="B938">
     <cfRule type="duplicateValues" dxfId="686" priority="864"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B905">
+  <conditionalFormatting sqref="B938">
     <cfRule type="duplicateValues" dxfId="685" priority="865"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B905">
+  <conditionalFormatting sqref="B938">
     <cfRule type="duplicateValues" dxfId="684" priority="866"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B906">
+  <conditionalFormatting sqref="B939">
     <cfRule type="duplicateValues" dxfId="683" priority="858"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B906">
+  <conditionalFormatting sqref="B939">
     <cfRule type="duplicateValues" dxfId="682" priority="859"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B906">
+  <conditionalFormatting sqref="B939">
     <cfRule type="duplicateValues" dxfId="681" priority="860"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B908">
+  <conditionalFormatting sqref="B941">
     <cfRule type="duplicateValues" dxfId="680" priority="855"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B908">
+  <conditionalFormatting sqref="B941">
     <cfRule type="duplicateValues" dxfId="679" priority="856"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B908">
+  <conditionalFormatting sqref="B941">
     <cfRule type="duplicateValues" dxfId="678" priority="857"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B910">
+  <conditionalFormatting sqref="B943">
     <cfRule type="duplicateValues" dxfId="677" priority="852"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B910">
+  <conditionalFormatting sqref="B943">
     <cfRule type="duplicateValues" dxfId="676" priority="853"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B910">
+  <conditionalFormatting sqref="B943">
     <cfRule type="duplicateValues" dxfId="675" priority="854"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B913">
+  <conditionalFormatting sqref="B946">
     <cfRule type="duplicateValues" dxfId="674" priority="849"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B913">
+  <conditionalFormatting sqref="B946">
     <cfRule type="duplicateValues" dxfId="673" priority="850"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B913">
+  <conditionalFormatting sqref="B946">
     <cfRule type="duplicateValues" dxfId="672" priority="851"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B914">
+  <conditionalFormatting sqref="B947">
     <cfRule type="duplicateValues" dxfId="671" priority="846"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B914">
+  <conditionalFormatting sqref="B947">
     <cfRule type="duplicateValues" dxfId="670" priority="847"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B914">
+  <conditionalFormatting sqref="B947">
     <cfRule type="duplicateValues" dxfId="669" priority="848"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B915">
+  <conditionalFormatting sqref="B948">
     <cfRule type="duplicateValues" dxfId="668" priority="843"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B915">
+  <conditionalFormatting sqref="B948">
     <cfRule type="duplicateValues" dxfId="667" priority="844"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B915">
+  <conditionalFormatting sqref="B948">
     <cfRule type="duplicateValues" dxfId="666" priority="845"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B917">
+  <conditionalFormatting sqref="B950">
     <cfRule type="duplicateValues" dxfId="665" priority="837"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B917">
+  <conditionalFormatting sqref="B950">
     <cfRule type="duplicateValues" dxfId="664" priority="838"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B917">
+  <conditionalFormatting sqref="B950">
     <cfRule type="duplicateValues" dxfId="663" priority="839"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B918">
+  <conditionalFormatting sqref="B951">
     <cfRule type="duplicateValues" dxfId="662" priority="831"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B918">
+  <conditionalFormatting sqref="B951">
     <cfRule type="duplicateValues" dxfId="661" priority="832"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B918">
+  <conditionalFormatting sqref="B951">
     <cfRule type="duplicateValues" dxfId="660" priority="833"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B920">
+  <conditionalFormatting sqref="B953">
     <cfRule type="duplicateValues" dxfId="659" priority="828"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B920">
+  <conditionalFormatting sqref="B953">
     <cfRule type="duplicateValues" dxfId="658" priority="829"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B920">
+  <conditionalFormatting sqref="B953">
     <cfRule type="duplicateValues" dxfId="657" priority="830"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B921">
+  <conditionalFormatting sqref="B954">
     <cfRule type="duplicateValues" dxfId="656" priority="819"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B921">
+  <conditionalFormatting sqref="B954">
     <cfRule type="duplicateValues" dxfId="655" priority="820"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B921">
+  <conditionalFormatting sqref="B954">
     <cfRule type="duplicateValues" dxfId="654" priority="821"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B922">
+  <conditionalFormatting sqref="B955">
     <cfRule type="duplicateValues" dxfId="653" priority="813"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B922">
+  <conditionalFormatting sqref="B955">
     <cfRule type="duplicateValues" dxfId="652" priority="814"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B922">
+  <conditionalFormatting sqref="B955">
     <cfRule type="duplicateValues" dxfId="651" priority="815"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B923">
+  <conditionalFormatting sqref="B956">
     <cfRule type="duplicateValues" dxfId="650" priority="810"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B923">
+  <conditionalFormatting sqref="B956">
     <cfRule type="duplicateValues" dxfId="649" priority="811"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B923">
+  <conditionalFormatting sqref="B956">
     <cfRule type="duplicateValues" dxfId="648" priority="812"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B926">
+  <conditionalFormatting sqref="B959">
     <cfRule type="duplicateValues" dxfId="647" priority="807"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B926">
+  <conditionalFormatting sqref="B959">
     <cfRule type="duplicateValues" dxfId="646" priority="808"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B926">
+  <conditionalFormatting sqref="B959">
     <cfRule type="duplicateValues" dxfId="645" priority="809"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B927">
+  <conditionalFormatting sqref="B960">
     <cfRule type="duplicateValues" dxfId="644" priority="804"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B927">
+  <conditionalFormatting sqref="B960">
     <cfRule type="duplicateValues" dxfId="643" priority="805"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B927">
+  <conditionalFormatting sqref="B960">
     <cfRule type="duplicateValues" dxfId="642" priority="806"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B928">
+  <conditionalFormatting sqref="B961">
     <cfRule type="duplicateValues" dxfId="641" priority="801"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B928">
+  <conditionalFormatting sqref="B961">
     <cfRule type="duplicateValues" dxfId="640" priority="802"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B928">
+  <conditionalFormatting sqref="B961">
     <cfRule type="duplicateValues" dxfId="639" priority="803"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B930">
+  <conditionalFormatting sqref="B963">
     <cfRule type="duplicateValues" dxfId="638" priority="798"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B930">
+  <conditionalFormatting sqref="B963">
     <cfRule type="duplicateValues" dxfId="637" priority="797"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B930">
+  <conditionalFormatting sqref="B963">
     <cfRule type="duplicateValues" dxfId="636" priority="796"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B932">
+  <conditionalFormatting sqref="B965">
     <cfRule type="duplicateValues" dxfId="635" priority="787"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B932">
+  <conditionalFormatting sqref="B965">
     <cfRule type="duplicateValues" dxfId="634" priority="788"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B932">
+  <conditionalFormatting sqref="B965">
     <cfRule type="duplicateValues" dxfId="633" priority="789"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B937">
+  <conditionalFormatting sqref="B970">
     <cfRule type="duplicateValues" dxfId="632" priority="776"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B937">
+  <conditionalFormatting sqref="B970">
     <cfRule type="duplicateValues" dxfId="631" priority="777"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B937">
+  <conditionalFormatting sqref="B970">
     <cfRule type="duplicateValues" dxfId="630" priority="778"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B935">
+  <conditionalFormatting sqref="B968">
     <cfRule type="duplicateValues" dxfId="629" priority="773"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B935">
+  <conditionalFormatting sqref="B968">
     <cfRule type="duplicateValues" dxfId="628" priority="774"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B935">
+  <conditionalFormatting sqref="B968">
     <cfRule type="duplicateValues" dxfId="627" priority="775"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B936">
+  <conditionalFormatting sqref="B969">
     <cfRule type="duplicateValues" dxfId="626" priority="770"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B936">
+  <conditionalFormatting sqref="B969">
     <cfRule type="duplicateValues" dxfId="625" priority="771"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B936">
+  <conditionalFormatting sqref="B969">
     <cfRule type="duplicateValues" dxfId="624" priority="772"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B938">
+  <conditionalFormatting sqref="B971">
     <cfRule type="duplicateValues" dxfId="623" priority="768"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B938">
+  <conditionalFormatting sqref="B971">
     <cfRule type="duplicateValues" dxfId="622" priority="767"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B938">
+  <conditionalFormatting sqref="B971">
     <cfRule type="duplicateValues" dxfId="621" priority="769"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B939">
+  <conditionalFormatting sqref="B972">
     <cfRule type="duplicateValues" dxfId="620" priority="761"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B939">
+  <conditionalFormatting sqref="B972">
     <cfRule type="duplicateValues" dxfId="619" priority="762"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B939">
+  <conditionalFormatting sqref="B972">
     <cfRule type="duplicateValues" dxfId="618" priority="763"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B940">
+  <conditionalFormatting sqref="B973">
     <cfRule type="duplicateValues" dxfId="617" priority="755"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B940">
+  <conditionalFormatting sqref="B973">
     <cfRule type="duplicateValues" dxfId="616" priority="756"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B940">
+  <conditionalFormatting sqref="B973">
     <cfRule type="duplicateValues" dxfId="615" priority="757"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B942">
+  <conditionalFormatting sqref="B975">
     <cfRule type="duplicateValues" dxfId="614" priority="752"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B942">
+  <conditionalFormatting sqref="B975">
     <cfRule type="duplicateValues" dxfId="613" priority="753"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B942">
+  <conditionalFormatting sqref="B975">
     <cfRule type="duplicateValues" dxfId="612" priority="754"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B941">
+  <conditionalFormatting sqref="B974">
     <cfRule type="duplicateValues" dxfId="611" priority="746"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B941">
+  <conditionalFormatting sqref="B974">
     <cfRule type="duplicateValues" dxfId="610" priority="747"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B941">
+  <conditionalFormatting sqref="B974">
     <cfRule type="duplicateValues" dxfId="609" priority="748"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B943">
+  <conditionalFormatting sqref="B976">
     <cfRule type="duplicateValues" dxfId="608" priority="740"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B943">
+  <conditionalFormatting sqref="B976">
     <cfRule type="duplicateValues" dxfId="607" priority="741"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B943">
+  <conditionalFormatting sqref="B976">
     <cfRule type="duplicateValues" dxfId="606" priority="742"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B944">
+  <conditionalFormatting sqref="B977">
     <cfRule type="duplicateValues" dxfId="605" priority="737"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B944">
+  <conditionalFormatting sqref="B977">
     <cfRule type="duplicateValues" dxfId="604" priority="738"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B944">
+  <conditionalFormatting sqref="B977">
     <cfRule type="duplicateValues" dxfId="603" priority="739"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B946">
+  <conditionalFormatting sqref="B979">
     <cfRule type="duplicateValues" dxfId="602" priority="734"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B946">
+  <conditionalFormatting sqref="B979">
     <cfRule type="duplicateValues" dxfId="601" priority="735"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B946">
+  <conditionalFormatting sqref="B979">
     <cfRule type="duplicateValues" dxfId="600" priority="736"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B948">
+  <conditionalFormatting sqref="B981">
     <cfRule type="duplicateValues" dxfId="599" priority="731"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B948">
+  <conditionalFormatting sqref="B981">
     <cfRule type="duplicateValues" dxfId="598" priority="732"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B948">
+  <conditionalFormatting sqref="B981">
     <cfRule type="duplicateValues" dxfId="597" priority="733"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B950">
+  <conditionalFormatting sqref="B983">
     <cfRule type="duplicateValues" dxfId="596" priority="728"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B950">
+  <conditionalFormatting sqref="B983">
     <cfRule type="duplicateValues" dxfId="595" priority="729"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B950">
+  <conditionalFormatting sqref="B983">
     <cfRule type="duplicateValues" dxfId="594" priority="730"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B951">
+  <conditionalFormatting sqref="B984">
     <cfRule type="duplicateValues" dxfId="593" priority="726"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B951">
+  <conditionalFormatting sqref="B984">
     <cfRule type="duplicateValues" dxfId="592" priority="725"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B951">
+  <conditionalFormatting sqref="B984">
     <cfRule type="duplicateValues" dxfId="591" priority="727"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B953">
+  <conditionalFormatting sqref="B986">
     <cfRule type="duplicateValues" dxfId="590" priority="722"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B953">
+  <conditionalFormatting sqref="B986">
     <cfRule type="duplicateValues" dxfId="589" priority="723"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B953">
+  <conditionalFormatting sqref="B986">
     <cfRule type="duplicateValues" dxfId="588" priority="724"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B952">
+  <conditionalFormatting sqref="B985">
     <cfRule type="duplicateValues" dxfId="587" priority="719"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B952">
+  <conditionalFormatting sqref="B985">
     <cfRule type="duplicateValues" dxfId="586" priority="720"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B952">
+  <conditionalFormatting sqref="B985">
     <cfRule type="duplicateValues" dxfId="585" priority="721"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B954">
+  <conditionalFormatting sqref="B987">
     <cfRule type="duplicateValues" dxfId="584" priority="716"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B954">
+  <conditionalFormatting sqref="B987">
     <cfRule type="duplicateValues" dxfId="583" priority="717"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B954">
+  <conditionalFormatting sqref="B987">
     <cfRule type="duplicateValues" dxfId="582" priority="718"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B955">
+  <conditionalFormatting sqref="B988">
     <cfRule type="duplicateValues" dxfId="581" priority="713"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B955">
+  <conditionalFormatting sqref="B988">
     <cfRule type="duplicateValues" dxfId="580" priority="714"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B955">
+  <conditionalFormatting sqref="B988">
     <cfRule type="duplicateValues" dxfId="579" priority="715"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B956">
+  <conditionalFormatting sqref="B989">
     <cfRule type="duplicateValues" dxfId="578" priority="707"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B956">
+  <conditionalFormatting sqref="B989">
     <cfRule type="duplicateValues" dxfId="577" priority="708"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B956">
+  <conditionalFormatting sqref="B989">
     <cfRule type="duplicateValues" dxfId="576" priority="709"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B957">
+  <conditionalFormatting sqref="B990">
     <cfRule type="duplicateValues" dxfId="575" priority="701"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B957">
+  <conditionalFormatting sqref="B990">
     <cfRule type="duplicateValues" dxfId="574" priority="702"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B957">
+  <conditionalFormatting sqref="B990">
     <cfRule type="duplicateValues" dxfId="573" priority="703"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B958">
+  <conditionalFormatting sqref="B991">
     <cfRule type="duplicateValues" dxfId="572" priority="698"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B958">
+  <conditionalFormatting sqref="B991">
     <cfRule type="duplicateValues" dxfId="571" priority="699"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B958">
+  <conditionalFormatting sqref="B991">
     <cfRule type="duplicateValues" dxfId="570" priority="700"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B959">
+  <conditionalFormatting sqref="B992">
     <cfRule type="duplicateValues" dxfId="569" priority="689"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B959">
+  <conditionalFormatting sqref="B992">
     <cfRule type="duplicateValues" dxfId="568" priority="690"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B959">
+  <conditionalFormatting sqref="B992">
     <cfRule type="duplicateValues" dxfId="567" priority="691"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B960">
+  <conditionalFormatting sqref="B993">
     <cfRule type="duplicateValues" dxfId="566" priority="686"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B960">
+  <conditionalFormatting sqref="B993">
     <cfRule type="duplicateValues" dxfId="565" priority="687"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B960">
+  <conditionalFormatting sqref="B993">
     <cfRule type="duplicateValues" dxfId="564" priority="688"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B961">
+  <conditionalFormatting sqref="B994">
     <cfRule type="duplicateValues" dxfId="563" priority="685"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B961">
+  <conditionalFormatting sqref="B994">
     <cfRule type="duplicateValues" dxfId="562" priority="684"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B961">
+  <conditionalFormatting sqref="B994">
     <cfRule type="duplicateValues" dxfId="561" priority="683"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B962">
+  <conditionalFormatting sqref="B995">
     <cfRule type="duplicateValues" dxfId="560" priority="674"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B962">
+  <conditionalFormatting sqref="B995">
     <cfRule type="duplicateValues" dxfId="559" priority="675"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B962">
+  <conditionalFormatting sqref="B995">
     <cfRule type="duplicateValues" dxfId="558" priority="676"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B963">
+  <conditionalFormatting sqref="B996">
     <cfRule type="duplicateValues" dxfId="557" priority="665"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B963">
+  <conditionalFormatting sqref="B996">
     <cfRule type="duplicateValues" dxfId="556" priority="666"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B963">
+  <conditionalFormatting sqref="B996">
     <cfRule type="duplicateValues" dxfId="555" priority="667"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B964">
+  <conditionalFormatting sqref="B997">
     <cfRule type="duplicateValues" dxfId="554" priority="662"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B964">
+  <conditionalFormatting sqref="B997">
     <cfRule type="duplicateValues" dxfId="553" priority="663"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B964">
+  <conditionalFormatting sqref="B997">
     <cfRule type="duplicateValues" dxfId="552" priority="664"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B965">
+  <conditionalFormatting sqref="B998">
     <cfRule type="duplicateValues" dxfId="551" priority="660"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B965">
+  <conditionalFormatting sqref="B998">
     <cfRule type="duplicateValues" dxfId="550" priority="659"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B965">
+  <conditionalFormatting sqref="B998">
     <cfRule type="duplicateValues" dxfId="549" priority="661"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B949">
+  <conditionalFormatting sqref="B982">
     <cfRule type="duplicateValues" dxfId="548" priority="656"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B949">
+  <conditionalFormatting sqref="B982">
     <cfRule type="duplicateValues" dxfId="547" priority="657"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B949">
+  <conditionalFormatting sqref="B982">
     <cfRule type="duplicateValues" dxfId="546" priority="658"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B967">
+  <conditionalFormatting sqref="B1000">
     <cfRule type="duplicateValues" dxfId="545" priority="651"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B967">
+  <conditionalFormatting sqref="B1000">
     <cfRule type="duplicateValues" dxfId="544" priority="650"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B967">
+  <conditionalFormatting sqref="B1000">
     <cfRule type="duplicateValues" dxfId="543" priority="652"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B968">
+  <conditionalFormatting sqref="B1001">
     <cfRule type="duplicateValues" dxfId="542" priority="647"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B968">
+  <conditionalFormatting sqref="B1001">
     <cfRule type="duplicateValues" dxfId="541" priority="648"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B968">
+  <conditionalFormatting sqref="B1001">
     <cfRule type="duplicateValues" dxfId="540" priority="649"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B969">
+  <conditionalFormatting sqref="B1002">
     <cfRule type="duplicateValues" dxfId="539" priority="638"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B969">
+  <conditionalFormatting sqref="B1002">
     <cfRule type="duplicateValues" dxfId="538" priority="639"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B969">
+  <conditionalFormatting sqref="B1002">
     <cfRule type="duplicateValues" dxfId="537" priority="640"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B970">
+  <conditionalFormatting sqref="B1003">
     <cfRule type="duplicateValues" dxfId="536" priority="635"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B970">
+  <conditionalFormatting sqref="B1003">
     <cfRule type="duplicateValues" dxfId="535" priority="636"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B970">
+  <conditionalFormatting sqref="B1003">
     <cfRule type="duplicateValues" dxfId="534" priority="637"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B971">
+  <conditionalFormatting sqref="B1004">
     <cfRule type="duplicateValues" dxfId="533" priority="630"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B971">
+  <conditionalFormatting sqref="B1004">
     <cfRule type="duplicateValues" dxfId="532" priority="631"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B971">
+  <conditionalFormatting sqref="B1004">
     <cfRule type="duplicateValues" dxfId="531" priority="632"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B972">
+  <conditionalFormatting sqref="B1005">
     <cfRule type="duplicateValues" dxfId="530" priority="627"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B972">
+  <conditionalFormatting sqref="B1005">
     <cfRule type="duplicateValues" dxfId="529" priority="628"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B972">
+  <conditionalFormatting sqref="B1005">
     <cfRule type="duplicateValues" dxfId="528" priority="629"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B973">
+  <conditionalFormatting sqref="B1006">
     <cfRule type="duplicateValues" dxfId="527" priority="621"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B973">
+  <conditionalFormatting sqref="B1006">
     <cfRule type="duplicateValues" dxfId="526" priority="622"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B973">
+  <conditionalFormatting sqref="B1006">
     <cfRule type="duplicateValues" dxfId="525" priority="623"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B974">
+  <conditionalFormatting sqref="B1007">
     <cfRule type="duplicateValues" dxfId="524" priority="615"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B974">
+  <conditionalFormatting sqref="B1007">
     <cfRule type="duplicateValues" dxfId="523" priority="616"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B974">
+  <conditionalFormatting sqref="B1007">
     <cfRule type="duplicateValues" dxfId="522" priority="617"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B976">
+  <conditionalFormatting sqref="B1009">
     <cfRule type="duplicateValues" dxfId="521" priority="612"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B976">
+  <conditionalFormatting sqref="B1009">
     <cfRule type="duplicateValues" dxfId="520" priority="613"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B976">
+  <conditionalFormatting sqref="B1009">
     <cfRule type="duplicateValues" dxfId="519" priority="614"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B975">
+  <conditionalFormatting sqref="B1008">
     <cfRule type="duplicateValues" dxfId="518" priority="609"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B975">
+  <conditionalFormatting sqref="B1008">
     <cfRule type="duplicateValues" dxfId="517" priority="610"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B975">
+  <conditionalFormatting sqref="B1008">
     <cfRule type="duplicateValues" dxfId="516" priority="611"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B978">
+  <conditionalFormatting sqref="B1011">
     <cfRule type="duplicateValues" dxfId="515" priority="606"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B978">
+  <conditionalFormatting sqref="B1011">
     <cfRule type="duplicateValues" dxfId="514" priority="607"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B978">
+  <conditionalFormatting sqref="B1011">
     <cfRule type="duplicateValues" dxfId="513" priority="608"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B977">
+  <conditionalFormatting sqref="B1010">
     <cfRule type="duplicateValues" dxfId="512" priority="603"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B977">
+  <conditionalFormatting sqref="B1010">
     <cfRule type="duplicateValues" dxfId="511" priority="604"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B977">
+  <conditionalFormatting sqref="B1010">
     <cfRule type="duplicateValues" dxfId="510" priority="605"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B979">
+  <conditionalFormatting sqref="B1012">
     <cfRule type="duplicateValues" dxfId="509" priority="594"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B979">
+  <conditionalFormatting sqref="B1012">
     <cfRule type="duplicateValues" dxfId="508" priority="595"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B979">
+  <conditionalFormatting sqref="B1012">
     <cfRule type="duplicateValues" dxfId="507" priority="596"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B981">
+  <conditionalFormatting sqref="B1014">
     <cfRule type="duplicateValues" dxfId="506" priority="591"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B981">
+  <conditionalFormatting sqref="B1014">
     <cfRule type="duplicateValues" dxfId="505" priority="592"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B981">
+  <conditionalFormatting sqref="B1014">
     <cfRule type="duplicateValues" dxfId="504" priority="593"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B982">
+  <conditionalFormatting sqref="B1015">
     <cfRule type="duplicateValues" dxfId="503" priority="588"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B982">
+  <conditionalFormatting sqref="B1015">
     <cfRule type="duplicateValues" dxfId="502" priority="589"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B982">
+  <conditionalFormatting sqref="B1015">
     <cfRule type="duplicateValues" dxfId="501" priority="590"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B983">
+  <conditionalFormatting sqref="B1016">
     <cfRule type="duplicateValues" dxfId="500" priority="585"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B983">
+  <conditionalFormatting sqref="B1016">
     <cfRule type="duplicateValues" dxfId="499" priority="586"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B983">
+  <conditionalFormatting sqref="B1016">
     <cfRule type="duplicateValues" dxfId="498" priority="587"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B984">
+  <conditionalFormatting sqref="B1017">
     <cfRule type="duplicateValues" dxfId="497" priority="579"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B984">
+  <conditionalFormatting sqref="B1017">
     <cfRule type="duplicateValues" dxfId="496" priority="580"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B984">
+  <conditionalFormatting sqref="B1017">
     <cfRule type="duplicateValues" dxfId="495" priority="581"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B985">
+  <conditionalFormatting sqref="B1018">
     <cfRule type="duplicateValues" dxfId="494" priority="576"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B985">
+  <conditionalFormatting sqref="B1018">
     <cfRule type="duplicateValues" dxfId="493" priority="577"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B985">
+  <conditionalFormatting sqref="B1018">
     <cfRule type="duplicateValues" dxfId="492" priority="578"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B986">
+  <conditionalFormatting sqref="B1019">
     <cfRule type="duplicateValues" dxfId="491" priority="574"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B986">
+  <conditionalFormatting sqref="B1019">
     <cfRule type="duplicateValues" dxfId="490" priority="575"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B987">
+  <conditionalFormatting sqref="B1020">
     <cfRule type="duplicateValues" dxfId="489" priority="571"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B987">
+  <conditionalFormatting sqref="B1020">
     <cfRule type="duplicateValues" dxfId="488" priority="572"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B987">
+  <conditionalFormatting sqref="B1020">
     <cfRule type="duplicateValues" dxfId="487" priority="573"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B988">
+  <conditionalFormatting sqref="B1021">
     <cfRule type="duplicateValues" dxfId="486" priority="568"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B988">
+  <conditionalFormatting sqref="B1021">
     <cfRule type="duplicateValues" dxfId="485" priority="569"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B988">
+  <conditionalFormatting sqref="B1021">
     <cfRule type="duplicateValues" dxfId="484" priority="570"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B989">
+  <conditionalFormatting sqref="B1022">
     <cfRule type="duplicateValues" dxfId="483" priority="559"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B989">
+  <conditionalFormatting sqref="B1022">
     <cfRule type="duplicateValues" dxfId="482" priority="560"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B989">
+  <conditionalFormatting sqref="B1022">
     <cfRule type="duplicateValues" dxfId="481" priority="561"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B991">
+  <conditionalFormatting sqref="B1024">
     <cfRule type="duplicateValues" dxfId="480" priority="558"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B991">
+  <conditionalFormatting sqref="B1024">
     <cfRule type="duplicateValues" dxfId="479" priority="557"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B991">
+  <conditionalFormatting sqref="B1024">
     <cfRule type="duplicateValues" dxfId="478" priority="556"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B990">
+  <conditionalFormatting sqref="B1023">
     <cfRule type="duplicateValues" dxfId="477" priority="547"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B990">
+  <conditionalFormatting sqref="B1023">
     <cfRule type="duplicateValues" dxfId="476" priority="548"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B990">
+  <conditionalFormatting sqref="B1023">
     <cfRule type="duplicateValues" dxfId="475" priority="549"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B992">
+  <conditionalFormatting sqref="B1025">
     <cfRule type="duplicateValues" dxfId="474" priority="544"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B992">
+  <conditionalFormatting sqref="B1025">
     <cfRule type="duplicateValues" dxfId="473" priority="545"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B992">
+  <conditionalFormatting sqref="B1025">
     <cfRule type="duplicateValues" dxfId="472" priority="546"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B993">
+  <conditionalFormatting sqref="B1026">
     <cfRule type="duplicateValues" dxfId="471" priority="538"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B993">
+  <conditionalFormatting sqref="B1026">
     <cfRule type="duplicateValues" dxfId="470" priority="539"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B993">
+  <conditionalFormatting sqref="B1026">
     <cfRule type="duplicateValues" dxfId="469" priority="540"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B994">
+  <conditionalFormatting sqref="B1027">
     <cfRule type="duplicateValues" dxfId="468" priority="529"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B994">
+  <conditionalFormatting sqref="B1027">
     <cfRule type="duplicateValues" dxfId="467" priority="530"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B994">
+  <conditionalFormatting sqref="B1027">
     <cfRule type="duplicateValues" dxfId="466" priority="531"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B995">
+  <conditionalFormatting sqref="B1028">
     <cfRule type="duplicateValues" dxfId="465" priority="526"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B995">
+  <conditionalFormatting sqref="B1028">
     <cfRule type="duplicateValues" dxfId="464" priority="527"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B995">
+  <conditionalFormatting sqref="B1028">
     <cfRule type="duplicateValues" dxfId="463" priority="528"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B998">
+  <conditionalFormatting sqref="B1031">
     <cfRule type="duplicateValues" dxfId="462" priority="523"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B998">
+  <conditionalFormatting sqref="B1031">
     <cfRule type="duplicateValues" dxfId="461" priority="524"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B998">
+  <conditionalFormatting sqref="B1031">
     <cfRule type="duplicateValues" dxfId="460" priority="525"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1000">
+  <conditionalFormatting sqref="B1033">
     <cfRule type="duplicateValues" dxfId="459" priority="520"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1000">
+  <conditionalFormatting sqref="B1033">
     <cfRule type="duplicateValues" dxfId="458" priority="521"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1000">
+  <conditionalFormatting sqref="B1033">
     <cfRule type="duplicateValues" dxfId="457" priority="522"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1003">
+  <conditionalFormatting sqref="B1036">
     <cfRule type="duplicateValues" dxfId="456" priority="517"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1003">
+  <conditionalFormatting sqref="B1036">
     <cfRule type="duplicateValues" dxfId="455" priority="518"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1003">
+  <conditionalFormatting sqref="B1036">
     <cfRule type="duplicateValues" dxfId="454" priority="519"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1004">
+  <conditionalFormatting sqref="B1037">
     <cfRule type="duplicateValues" dxfId="453" priority="511"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1004">
+  <conditionalFormatting sqref="B1037">
     <cfRule type="duplicateValues" dxfId="452" priority="512"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1004">
+  <conditionalFormatting sqref="B1037">
     <cfRule type="duplicateValues" dxfId="451" priority="513"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1006">
+  <conditionalFormatting sqref="B1039">
     <cfRule type="duplicateValues" dxfId="450" priority="508"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1006">
+  <conditionalFormatting sqref="B1039">
     <cfRule type="duplicateValues" dxfId="449" priority="509"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1006">
+  <conditionalFormatting sqref="B1039">
     <cfRule type="duplicateValues" dxfId="448" priority="510"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1005">
+  <conditionalFormatting sqref="B1038">
     <cfRule type="duplicateValues" dxfId="447" priority="502"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1005">
+  <conditionalFormatting sqref="B1038">
     <cfRule type="duplicateValues" dxfId="446" priority="503"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1005">
+  <conditionalFormatting sqref="B1038">
     <cfRule type="duplicateValues" dxfId="445" priority="504"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1007">
+  <conditionalFormatting sqref="B1040">
     <cfRule type="duplicateValues" dxfId="444" priority="496"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1007">
+  <conditionalFormatting sqref="B1040">
     <cfRule type="duplicateValues" dxfId="443" priority="497"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1007">
+  <conditionalFormatting sqref="B1040">
     <cfRule type="duplicateValues" dxfId="442" priority="498"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1008">
+  <conditionalFormatting sqref="B1041">
     <cfRule type="duplicateValues" dxfId="441" priority="490"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1008">
+  <conditionalFormatting sqref="B1041">
     <cfRule type="duplicateValues" dxfId="440" priority="491"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1008">
+  <conditionalFormatting sqref="B1041">
     <cfRule type="duplicateValues" dxfId="439" priority="492"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1009">
+  <conditionalFormatting sqref="B1042">
     <cfRule type="duplicateValues" dxfId="438" priority="481"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1009">
+  <conditionalFormatting sqref="B1042">
     <cfRule type="duplicateValues" dxfId="437" priority="482"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1009">
+  <conditionalFormatting sqref="B1042">
     <cfRule type="duplicateValues" dxfId="436" priority="483"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1010">
+  <conditionalFormatting sqref="B1043">
     <cfRule type="duplicateValues" dxfId="435" priority="476"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1010">
+  <conditionalFormatting sqref="B1043">
     <cfRule type="duplicateValues" dxfId="434" priority="475"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1010">
+  <conditionalFormatting sqref="B1043">
     <cfRule type="duplicateValues" dxfId="433" priority="477"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1012">
+  <conditionalFormatting sqref="B1045">
     <cfRule type="duplicateValues" dxfId="432" priority="466"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1012">
+  <conditionalFormatting sqref="B1045">
     <cfRule type="duplicateValues" dxfId="431" priority="467"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1012">
+  <conditionalFormatting sqref="B1045">
     <cfRule type="duplicateValues" dxfId="430" priority="468"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1013">
+  <conditionalFormatting sqref="B1046">
     <cfRule type="duplicateValues" dxfId="429" priority="460"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1013">
+  <conditionalFormatting sqref="B1046">
     <cfRule type="duplicateValues" dxfId="428" priority="461"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1013">
+  <conditionalFormatting sqref="B1046">
     <cfRule type="duplicateValues" dxfId="427" priority="462"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1014">
+  <conditionalFormatting sqref="B1047">
     <cfRule type="duplicateValues" dxfId="426" priority="457"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1014">
+  <conditionalFormatting sqref="B1047">
     <cfRule type="duplicateValues" dxfId="425" priority="458"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1014">
+  <conditionalFormatting sqref="B1047">
     <cfRule type="duplicateValues" dxfId="424" priority="459"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1015">
+  <conditionalFormatting sqref="B1048">
     <cfRule type="duplicateValues" dxfId="423" priority="454"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1015">
+  <conditionalFormatting sqref="B1048">
     <cfRule type="duplicateValues" dxfId="422" priority="455"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1015">
+  <conditionalFormatting sqref="B1048">
     <cfRule type="duplicateValues" dxfId="421" priority="456"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1016">
+  <conditionalFormatting sqref="B1049">
     <cfRule type="duplicateValues" dxfId="420" priority="450"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1016">
+  <conditionalFormatting sqref="B1049">
     <cfRule type="duplicateValues" dxfId="419" priority="449"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1016">
+  <conditionalFormatting sqref="B1049">
     <cfRule type="duplicateValues" dxfId="418" priority="448"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1017">
+  <conditionalFormatting sqref="B1050">
     <cfRule type="duplicateValues" dxfId="417" priority="446"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1017">
+  <conditionalFormatting sqref="B1050">
     <cfRule type="duplicateValues" dxfId="416" priority="445"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1017">
+  <conditionalFormatting sqref="B1050">
     <cfRule type="duplicateValues" dxfId="415" priority="447"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1018">
+  <conditionalFormatting sqref="B1051">
     <cfRule type="duplicateValues" dxfId="414" priority="442"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1018">
+  <conditionalFormatting sqref="B1051">
     <cfRule type="duplicateValues" dxfId="413" priority="443"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1018">
+  <conditionalFormatting sqref="B1051">
     <cfRule type="duplicateValues" dxfId="412" priority="444"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9">

--- a/Spanish Dictionary.xlsx
+++ b/Spanish Dictionary.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2520" uniqueCount="2511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2646" uniqueCount="2636">
   <si>
     <t>Word / Expression</t>
   </si>
@@ -6861,9 +6861,6 @@
     <t>péléléh</t>
   </si>
   <si>
-    <t>dummy, weak easily manipulated person</t>
-  </si>
-  <si>
     <t>Hombre, no te sale</t>
   </si>
   <si>
@@ -6963,9 +6960,6 @@
     <t>To make a song that doesn't even get played at the party</t>
   </si>
   <si>
-    <t>parah asér own témah kéh noh suénah ni én lah fiéstah</t>
-  </si>
-  <si>
     <t>Yo hago mi escritura fumando uno de verdura</t>
   </si>
   <si>
@@ -7062,9 +7056,6 @@
     <t>Dime dónde para', para ir a buscarte, y cogerte aparte</t>
   </si>
   <si>
-    <t>Tell me where you're staying, so I can come find you and we can go off on our own.</t>
-  </si>
-  <si>
     <t>deeméh dondéh parah parah eer ah buscartéh ee kokhértéh aparté</t>
   </si>
   <si>
@@ -7095,9 +7086,6 @@
     <t>El que te lo brega o el que por ti se pega</t>
   </si>
   <si>
-    <t>The one who works hard for you or the one who sticks for you</t>
-  </si>
-  <si>
     <t>éhl kéh téh loh brégah oh éhl kéh por ti séh pégah</t>
   </si>
   <si>
@@ -7107,18 +7095,12 @@
     <t>Where are you hiding? Where are you from your group?</t>
   </si>
   <si>
-    <t>dondéh estah éskondioh ee kién-és toh kolégah?</t>
-  </si>
-  <si>
     <t>dondéh estah éskondioh dondéh éh toh grupoh?</t>
   </si>
   <si>
     <t>To see how I spit it out, and then I don't worry</t>
   </si>
   <si>
-    <t>parah vér komoh loh éskupoh ee luégoh noh méh préokupoh</t>
-  </si>
-  <si>
     <t>Para ver cómo lo escupo, y luego no me preocupo</t>
   </si>
   <si>
@@ -7128,9 +7110,6 @@
     <t>You have a gun but it doesn't shoot</t>
   </si>
   <si>
-    <t>toh tiéné ownah peestolah péroh noh deesparah</t>
-  </si>
-  <si>
     <t>Eladio dijo "no hay chaleco para la cara"</t>
   </si>
   <si>
@@ -7152,15 +7131,9 @@
     <t>Wait, now I see that I'm doing what I want</t>
   </si>
   <si>
-    <t>éspérah ahorah véoh kéh estoy asiéndoh loh kéh kiérah</t>
-  </si>
-  <si>
     <t>Espera, ahora veo que estoy haciendo lo que quiera</t>
   </si>
   <si>
-    <t>ee toh aprétadoh kon entéréhs déh deskérah</t>
-  </si>
-  <si>
     <t>Y tú apretado con interés de disquera</t>
   </si>
   <si>
@@ -7182,27 +7155,18 @@
     <t>You fool, you think it's so easy to name the letter L</t>
   </si>
   <si>
-    <t>péléléh téh krées kéh éhs muyy fasel nombrar á lah élé</t>
-  </si>
-  <si>
     <t>Si sabemos que tú no llega' a los nivele'</t>
   </si>
   <si>
     <t>If we know that you don't reach the levels</t>
   </si>
   <si>
-    <t>cee sabémos kéh toh noh yégah á lohs nebéléh</t>
-  </si>
-  <si>
     <t>Y nosotros os pusimos a vosotro' los chele', los primero' chele'</t>
   </si>
   <si>
     <t>And we called you 'the whites', the first 'whites'</t>
   </si>
   <si>
-    <t>ee nosotrohs ohs pusimohs ah vosotroh lohs tchéléh lohs preeméroh tchéléh</t>
-  </si>
-  <si>
     <t>Cuando me ven de frente ya me dicen "para"</t>
   </si>
   <si>
@@ -7470,9 +7434,6 @@
     <t>fácil</t>
   </si>
   <si>
-    <t>faseel</t>
-  </si>
-  <si>
     <t>easy</t>
   </si>
   <si>
@@ -7549,6 +7510,420 @@
   </si>
   <si>
     <t>wait until he changes it</t>
+  </si>
+  <si>
+    <t>Dime dónde para'</t>
+  </si>
+  <si>
+    <t>deeméh dondéh parah</t>
+  </si>
+  <si>
+    <t>Tell me where it stops</t>
+  </si>
+  <si>
+    <t>para ir a buscarte</t>
+  </si>
+  <si>
+    <t>parah eer ah buscartéh</t>
+  </si>
+  <si>
+    <t>to go find you</t>
+  </si>
+  <si>
+    <t>y cogerte aparte</t>
+  </si>
+  <si>
+    <t>and take you apart</t>
+  </si>
+  <si>
+    <t>ee kokhértéh aparté</t>
+  </si>
+  <si>
+    <t>Tell me where you're staying, so I can come find you and take you apart</t>
+  </si>
+  <si>
+    <t>A mí no interesa</t>
+  </si>
+  <si>
+    <t>ah mee noh eentérésah</t>
+  </si>
+  <si>
+    <t>I'm not interested</t>
+  </si>
+  <si>
+    <t>Tener que grabarte</t>
+  </si>
+  <si>
+    <t>ténér kéh grabartéh</t>
+  </si>
+  <si>
+    <t>having to record you</t>
+  </si>
+  <si>
+    <t>si eres un desastre</t>
+  </si>
+  <si>
+    <t>cee-érés own désastréh</t>
+  </si>
+  <si>
+    <t>if you are a disaster</t>
+  </si>
+  <si>
+    <t>un desastre</t>
+  </si>
+  <si>
+    <t>own désastréh</t>
+  </si>
+  <si>
+    <t>a disaster</t>
+  </si>
+  <si>
+    <t>¿quién es tu colega?</t>
+  </si>
+  <si>
+    <t>dondéh estah éskondioh ee kiénne-és toh kolégah?</t>
+  </si>
+  <si>
+    <t>kiénne-és toh kolégah?</t>
+  </si>
+  <si>
+    <t>who is your colleague?</t>
+  </si>
+  <si>
+    <t>¿Dónde e' tu grupo?</t>
+  </si>
+  <si>
+    <t>dondéh éh toh grupoh?</t>
+  </si>
+  <si>
+    <t>Where is your group?</t>
+  </si>
+  <si>
+    <t>parah béhr komoh loh éskupoh ee luégoh noh méh préokupoh</t>
+  </si>
+  <si>
+    <t>Para ver cómo lo escupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parah béhr komoh loh éskupoh </t>
+  </si>
+  <si>
+    <t>To see how I spit it out</t>
+  </si>
+  <si>
+    <t>y luego no me preocupo</t>
+  </si>
+  <si>
+    <t>ee luégoh noh méh préokupoh</t>
+  </si>
+  <si>
+    <t>and then I don't worry</t>
+  </si>
+  <si>
+    <t>una pistola</t>
+  </si>
+  <si>
+    <t>a gun</t>
+  </si>
+  <si>
+    <t>ownah pee-stolah</t>
+  </si>
+  <si>
+    <t>toh tiéné ownah pee-stolah péroh noh deesparah</t>
+  </si>
+  <si>
+    <t>no hay chaleco para la cara</t>
+  </si>
+  <si>
+    <t>There's no vest for the face</t>
+  </si>
+  <si>
+    <t>la cara</t>
+  </si>
+  <si>
+    <t>lah karah</t>
+  </si>
+  <si>
+    <t>noh ahyy tchalekoh parah lah karah</t>
+  </si>
+  <si>
+    <t>the face</t>
+  </si>
+  <si>
+    <t>Entonces</t>
+  </si>
+  <si>
+    <t>éntonséhs</t>
+  </si>
+  <si>
+    <t>so</t>
+  </si>
+  <si>
+    <t>te haremos</t>
+  </si>
+  <si>
+    <t>téh arémos</t>
+  </si>
+  <si>
+    <t>we will make you</t>
+  </si>
+  <si>
+    <t>Te raja</t>
+  </si>
+  <si>
+    <t>téh rakhah</t>
+  </si>
+  <si>
+    <t>It cuts you</t>
+  </si>
+  <si>
+    <t>ahora</t>
+  </si>
+  <si>
+    <t>ahorah</t>
+  </si>
+  <si>
+    <t>now</t>
+  </si>
+  <si>
+    <t>estoy haciendo</t>
+  </si>
+  <si>
+    <t>éspérah ahorah véoh kéh éhstoy asiéndoh loh kéh kiérah</t>
+  </si>
+  <si>
+    <t>éhstoy asiéndoh</t>
+  </si>
+  <si>
+    <t>I'm doing</t>
+  </si>
+  <si>
+    <t>estoy haciendo lo que quiera</t>
+  </si>
+  <si>
+    <t>I'm doing whatever I want</t>
+  </si>
+  <si>
+    <t>éhstoy asiéndoh loh kéh kiérah</t>
+  </si>
+  <si>
+    <t>estoy</t>
+  </si>
+  <si>
+    <t>éhstoy</t>
+  </si>
+  <si>
+    <t>I'm</t>
+  </si>
+  <si>
+    <t>con</t>
+  </si>
+  <si>
+    <t>with</t>
+  </si>
+  <si>
+    <t>kon</t>
+  </si>
+  <si>
+    <t>interés</t>
+  </si>
+  <si>
+    <t>ee toh aprétadoh kon ein-téréhs déh deskérah</t>
+  </si>
+  <si>
+    <t>ein-téréhs</t>
+  </si>
+  <si>
+    <t>interest</t>
+  </si>
+  <si>
+    <t>Y yo tranquilo hasta el día que me muera</t>
+  </si>
+  <si>
+    <t>ee yoh tranquiloh astah él diah kéh mé muérah</t>
+  </si>
+  <si>
+    <t>And I will be calm until the day I die</t>
+  </si>
+  <si>
+    <t>hasta que me oye</t>
+  </si>
+  <si>
+    <t>astah kéh méh ohyéh</t>
+  </si>
+  <si>
+    <t>until you hear me</t>
+  </si>
+  <si>
+    <t>te crees que es muy fácil</t>
+  </si>
+  <si>
+    <t>you think it's very easy</t>
+  </si>
+  <si>
+    <t>téh krées kéh éhs muyy faceel</t>
+  </si>
+  <si>
+    <t>péléléh téh krées kéh éhs muyy faceel nombrar á lah élé</t>
+  </si>
+  <si>
+    <t>nombrar</t>
+  </si>
+  <si>
+    <t>to name / to mention</t>
+  </si>
+  <si>
+    <t>Si sabemos</t>
+  </si>
+  <si>
+    <t>cee sabéhmos</t>
+  </si>
+  <si>
+    <t>If we know</t>
+  </si>
+  <si>
+    <t>que tú no llega' a los niveles</t>
+  </si>
+  <si>
+    <t>that you don't reach the levels</t>
+  </si>
+  <si>
+    <t>los niveles</t>
+  </si>
+  <si>
+    <t>kéh toh noh yégah á lohs neebéléhs</t>
+  </si>
+  <si>
+    <t>cee sabéhmos kéh toh noh yégah á lohs neebéléh</t>
+  </si>
+  <si>
+    <t>lohs neebéléhs</t>
+  </si>
+  <si>
+    <t>the levels</t>
+  </si>
+  <si>
+    <t>nosotros</t>
+  </si>
+  <si>
+    <t>us</t>
+  </si>
+  <si>
+    <t>nohsotrohs</t>
+  </si>
+  <si>
+    <t>nosotros os pusimos</t>
+  </si>
+  <si>
+    <t>nohsotrohs ohs pusimohs</t>
+  </si>
+  <si>
+    <t>we put you</t>
+  </si>
+  <si>
+    <t>ee nohsotrohs ohs pusimohs ah bohsotroh lohs tchéléh lohs preeméroh tchéléh</t>
+  </si>
+  <si>
+    <t>vosotros</t>
+  </si>
+  <si>
+    <t>you all</t>
+  </si>
+  <si>
+    <t>bohsotroh</t>
+  </si>
+  <si>
+    <t>los cheles</t>
+  </si>
+  <si>
+    <t>lohs tchéléhs</t>
+  </si>
+  <si>
+    <t>people with fair skin or blonde hair</t>
+  </si>
+  <si>
+    <t>Cuando me ven</t>
+  </si>
+  <si>
+    <t>quandoh méh bén</t>
+  </si>
+  <si>
+    <t>When they see me</t>
+  </si>
+  <si>
+    <t>de frente</t>
+  </si>
+  <si>
+    <t>déh fréntéh</t>
+  </si>
+  <si>
+    <t>head-on</t>
+  </si>
+  <si>
+    <t>atacar de frente</t>
+  </si>
+  <si>
+    <t>ahtah-kar déh fréntéh</t>
+  </si>
+  <si>
+    <t>to attack head-on</t>
+  </si>
+  <si>
+    <t>ni</t>
+  </si>
+  <si>
+    <t>nee</t>
+  </si>
+  <si>
+    <t>parah asér own témah kéh noh suénah nee én lah fiéstah</t>
+  </si>
+  <si>
+    <t>neither</t>
+  </si>
+  <si>
+    <t>la fiesta</t>
+  </si>
+  <si>
+    <t>lah fiéstah</t>
+  </si>
+  <si>
+    <t>the party</t>
+  </si>
+  <si>
+    <t>faceel</t>
+  </si>
+  <si>
+    <t>El que te lo brega</t>
+  </si>
+  <si>
+    <t>éhl kéh téh loh brégah</t>
+  </si>
+  <si>
+    <t>The one who gives you trouble</t>
+  </si>
+  <si>
+    <t>el que por ti se pega</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> éhl kéh por ti séh pégah</t>
+  </si>
+  <si>
+    <t>the one who sticks for you</t>
+  </si>
+  <si>
+    <t>The one who gives you trouble or the one who sticks for you</t>
+  </si>
+  <si>
+    <t>pero no dispara</t>
+  </si>
+  <si>
+    <t>péroh noh deesparah</t>
+  </si>
+  <si>
+    <t>but it doesn't shoot</t>
+  </si>
+  <si>
+    <t>you fool / wimp / weak character</t>
   </si>
 </sst>
 </file>
@@ -7564,18 +7939,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -7590,7 +7959,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -7601,64 +7970,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1667">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1662">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -24576,7 +24892,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:D852"/>
+  <dimension ref="B1:D894"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="1" customWidth="1"/>
@@ -33030,158 +33346,158 @@
         <v>2280</v>
       </c>
       <c r="D775" s="1" t="s">
-        <v>2281</v>
+        <v>2635</v>
       </c>
     </row>
     <row r="776" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B776" s="1" t="s">
+        <v>2281</v>
+      </c>
+      <c r="C776" s="1" t="s">
+        <v>2283</v>
+      </c>
+      <c r="D776" s="1" t="s">
         <v>2282</v>
-      </c>
-      <c r="C776" s="1" t="s">
-        <v>2284</v>
-      </c>
-      <c r="D776" s="1" t="s">
-        <v>2283</v>
       </c>
     </row>
     <row r="777" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B777" s="1" t="s">
-        <v>2410</v>
+        <v>2398</v>
       </c>
       <c r="C777" s="1" t="s">
-        <v>2411</v>
+        <v>2399</v>
       </c>
       <c r="D777" s="1" t="s">
-        <v>2412</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="778" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B778" s="1" t="s">
+        <v>2284</v>
+      </c>
+      <c r="C778" s="1" t="s">
         <v>2285</v>
       </c>
-      <c r="C778" s="1" t="s">
+      <c r="D778" s="1" t="s">
         <v>2286</v>
-      </c>
-      <c r="D778" s="1" t="s">
-        <v>2287</v>
       </c>
     </row>
     <row r="779" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B779" s="1" t="s">
-        <v>2413</v>
+        <v>2401</v>
       </c>
       <c r="C779" s="1" t="s">
-        <v>2414</v>
+        <v>2402</v>
       </c>
       <c r="D779" s="1" t="s">
-        <v>2415</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="780" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B780" s="1" t="s">
+        <v>2287</v>
+      </c>
+      <c r="C780" s="1" t="s">
+        <v>2305</v>
+      </c>
+      <c r="D780" s="1" t="s">
         <v>2288</v>
-      </c>
-      <c r="C780" s="1" t="s">
-        <v>2306</v>
-      </c>
-      <c r="D780" s="1" t="s">
-        <v>2289</v>
       </c>
     </row>
     <row r="781" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B781" s="1" t="s">
+        <v>2289</v>
+      </c>
+      <c r="C781" s="1" t="s">
+        <v>2291</v>
+      </c>
+      <c r="D781" s="1" t="s">
         <v>2290</v>
-      </c>
-      <c r="C781" s="1" t="s">
-        <v>2292</v>
-      </c>
-      <c r="D781" s="1" t="s">
-        <v>2291</v>
       </c>
     </row>
     <row r="782" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B782" s="1" t="s">
+        <v>2292</v>
+      </c>
+      <c r="C782" s="1" t="s">
+        <v>2294</v>
+      </c>
+      <c r="D782" s="1" t="s">
         <v>2293</v>
-      </c>
-      <c r="C782" s="1" t="s">
-        <v>2295</v>
-      </c>
-      <c r="D782" s="1" t="s">
-        <v>2294</v>
       </c>
     </row>
     <row r="783" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B783" s="1" t="s">
-        <v>2416</v>
+        <v>2404</v>
       </c>
       <c r="C783" s="1" t="s">
-        <v>2417</v>
+        <v>2405</v>
       </c>
       <c r="D783" s="1" t="s">
-        <v>2418</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="784" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B784" s="1" t="s">
-        <v>2419</v>
+        <v>2407</v>
       </c>
       <c r="C784" s="1" t="s">
-        <v>2420</v>
+        <v>2408</v>
       </c>
       <c r="D784" s="1" t="s">
-        <v>2421</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="785" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B785" s="1" t="s">
+        <v>2295</v>
+      </c>
+      <c r="C785" s="1" t="s">
+        <v>2297</v>
+      </c>
+      <c r="D785" s="1" t="s">
         <v>2296</v>
-      </c>
-      <c r="C785" s="1" t="s">
-        <v>2298</v>
-      </c>
-      <c r="D785" s="1" t="s">
-        <v>2297</v>
       </c>
     </row>
     <row r="786" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B786" s="1" t="s">
-        <v>2422</v>
+        <v>2410</v>
       </c>
       <c r="C786" s="1" t="s">
-        <v>2423</v>
+        <v>2411</v>
       </c>
       <c r="D786" s="1" t="s">
-        <v>2424</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="787" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B787" s="1" t="s">
+        <v>2298</v>
+      </c>
+      <c r="C787" s="1" t="s">
+        <v>2300</v>
+      </c>
+      <c r="D787" s="1" t="s">
         <v>2299</v>
-      </c>
-      <c r="C787" s="1" t="s">
-        <v>2301</v>
-      </c>
-      <c r="D787" s="1" t="s">
-        <v>2300</v>
       </c>
     </row>
     <row r="788" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B788" s="1" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="C788" s="1" t="s">
-        <v>2307</v>
+        <v>2306</v>
       </c>
       <c r="D788" s="1" t="s">
-        <v>2302</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="789" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B789" s="1" t="s">
+        <v>2303</v>
+      </c>
+      <c r="C789" s="1" t="s">
         <v>2304</v>
-      </c>
-      <c r="C789" s="1" t="s">
-        <v>2305</v>
       </c>
       <c r="D789" s="1">
         <v>40</v>
@@ -33189,32 +33505,32 @@
     </row>
     <row r="790" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B790" s="1" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
       <c r="C790" s="1" t="s">
-        <v>2311</v>
+        <v>2310</v>
       </c>
       <c r="D790" s="1" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="791" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B791" s="1" t="s">
-        <v>2425</v>
+        <v>2413</v>
       </c>
       <c r="C791" s="1" t="s">
-        <v>2426</v>
+        <v>2414</v>
       </c>
       <c r="D791" s="1" t="s">
-        <v>2427</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="792" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B792" s="1" t="s">
+        <v>2308</v>
+      </c>
+      <c r="C792" s="1" t="s">
         <v>2309</v>
-      </c>
-      <c r="C792" s="1" t="s">
-        <v>2310</v>
       </c>
       <c r="D792" s="1">
         <v>17</v>
@@ -33222,5665 +33538,6112 @@
     </row>
     <row r="793" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B793" s="1" t="s">
+        <v>2312</v>
+      </c>
+      <c r="C793" s="1" t="s">
+        <v>2619</v>
+      </c>
+      <c r="D793" s="1" t="s">
         <v>2313</v>
-      </c>
-      <c r="C793" s="1" t="s">
-        <v>2315</v>
-      </c>
-      <c r="D793" s="1" t="s">
-        <v>2314</v>
       </c>
     </row>
     <row r="794" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B794" s="1" t="s">
-        <v>2428</v>
+        <v>2416</v>
       </c>
       <c r="C794" s="1" t="s">
-        <v>2429</v>
+        <v>2417</v>
       </c>
       <c r="D794" s="1" t="s">
-        <v>2430</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="795" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B795" s="1" t="s">
-        <v>2431</v>
+        <v>2419</v>
       </c>
       <c r="C795" s="1" t="s">
-        <v>2432</v>
+        <v>2420</v>
       </c>
       <c r="D795" s="1" t="s">
-        <v>2433</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="796" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B796" s="1" t="s">
-        <v>2316</v>
+        <v>2617</v>
       </c>
       <c r="C796" s="1" t="s">
-        <v>2318</v>
+        <v>2618</v>
       </c>
       <c r="D796" s="1" t="s">
-        <v>2317</v>
+        <v>2620</v>
       </c>
     </row>
     <row r="797" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B797" s="1" t="s">
-        <v>2434</v>
+        <v>2621</v>
       </c>
       <c r="C797" s="1" t="s">
-        <v>2436</v>
+        <v>2622</v>
       </c>
       <c r="D797" s="1" t="s">
-        <v>2435</v>
+        <v>2623</v>
       </c>
     </row>
     <row r="798" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B798" s="1" t="s">
-        <v>2437</v>
+        <v>2314</v>
       </c>
       <c r="C798" s="1" t="s">
-        <v>2438</v>
+        <v>2316</v>
       </c>
       <c r="D798" s="1" t="s">
-        <v>2439</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="799" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B799" s="1" t="s">
-        <v>2440</v>
+        <v>2422</v>
       </c>
       <c r="C799" s="1" t="s">
-        <v>2441</v>
+        <v>2424</v>
       </c>
       <c r="D799" s="1" t="s">
-        <v>2442</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="800" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B800" s="1" t="s">
-        <v>2319</v>
+        <v>2425</v>
       </c>
       <c r="C800" s="1" t="s">
-        <v>2321</v>
+        <v>2426</v>
       </c>
       <c r="D800" s="1" t="s">
-        <v>2320</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="801" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B801" s="1" t="s">
-        <v>2443</v>
+        <v>2428</v>
       </c>
       <c r="C801" s="1" t="s">
-        <v>2444</v>
+        <v>2429</v>
       </c>
       <c r="D801" s="1" t="s">
-        <v>2445</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="802" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B802" s="1" t="s">
-        <v>2446</v>
+        <v>2317</v>
       </c>
       <c r="C802" s="1" t="s">
-        <v>2447</v>
+        <v>2319</v>
       </c>
       <c r="D802" s="1" t="s">
-        <v>2448</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="803" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B803" s="1" t="s">
-        <v>2322</v>
+        <v>2431</v>
       </c>
       <c r="C803" s="1" t="s">
-        <v>2324</v>
+        <v>2432</v>
       </c>
       <c r="D803" s="1" t="s">
-        <v>2323</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="804" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B804" s="1" t="s">
-        <v>2449</v>
+        <v>2434</v>
       </c>
       <c r="C804" s="1" t="s">
-        <v>2450</v>
+        <v>2435</v>
       </c>
       <c r="D804" s="1" t="s">
-        <v>2451</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="805" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B805" s="1" t="s">
-        <v>2325</v>
+        <v>2320</v>
       </c>
       <c r="C805" s="1" t="s">
-        <v>2326</v>
+        <v>2322</v>
       </c>
       <c r="D805" s="1" t="s">
-        <v>2455</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="806" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B806" s="1" t="s">
-        <v>2452</v>
+        <v>2437</v>
       </c>
       <c r="C806" s="1" t="s">
-        <v>2453</v>
+        <v>2438</v>
       </c>
       <c r="D806" s="1" t="s">
-        <v>2454</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="807" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B807" s="1" t="s">
-        <v>2456</v>
+        <v>2323</v>
       </c>
       <c r="C807" s="1" t="s">
-        <v>2457</v>
+        <v>2324</v>
       </c>
       <c r="D807" s="1" t="s">
-        <v>2458</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="808" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B808" s="1" t="s">
-        <v>2327</v>
+        <v>2440</v>
       </c>
       <c r="C808" s="1" t="s">
-        <v>2329</v>
+        <v>2441</v>
       </c>
       <c r="D808" s="1" t="s">
-        <v>2328</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="809" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B809" s="1" t="s">
-        <v>2459</v>
+        <v>2444</v>
       </c>
       <c r="C809" s="1" t="s">
-        <v>2461</v>
+        <v>2445</v>
       </c>
       <c r="D809" s="1" t="s">
-        <v>2460</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="810" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B810" s="1" t="s">
-        <v>2330</v>
+        <v>2325</v>
       </c>
       <c r="C810" s="1" t="s">
-        <v>2332</v>
+        <v>2327</v>
       </c>
       <c r="D810" s="1" t="s">
-        <v>2331</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="811" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B811" s="1" t="s">
-        <v>2462</v>
+        <v>2447</v>
       </c>
       <c r="C811" s="1" t="s">
-        <v>2464</v>
+        <v>2449</v>
       </c>
       <c r="D811" s="1" t="s">
-        <v>2463</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="812" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B812" s="1" t="s">
-        <v>2465</v>
+        <v>2328</v>
       </c>
       <c r="C812" s="1" t="s">
-        <v>2466</v>
+        <v>2330</v>
       </c>
       <c r="D812" s="1" t="s">
-        <v>2467</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="813" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B813" s="1" t="s">
-        <v>2468</v>
+        <v>2450</v>
       </c>
       <c r="C813" s="1" t="s">
-        <v>2469</v>
+        <v>2452</v>
       </c>
       <c r="D813" s="1" t="s">
-        <v>2470</v>
+        <v>2451</v>
       </c>
     </row>
     <row r="814" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B814" s="1" t="s">
-        <v>2471</v>
+        <v>2453</v>
       </c>
       <c r="C814" s="1" t="s">
-        <v>2472</v>
+        <v>2454</v>
       </c>
       <c r="D814" s="1" t="s">
-        <v>2473</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="815" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B815" s="1" t="s">
-        <v>2474</v>
+        <v>2456</v>
       </c>
       <c r="C815" s="1" t="s">
-        <v>2475</v>
+        <v>2457</v>
       </c>
       <c r="D815" s="1" t="s">
-        <v>2476</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="816" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B816" s="1" t="s">
-        <v>2333</v>
+        <v>2459</v>
       </c>
       <c r="C816" s="1" t="s">
-        <v>2335</v>
+        <v>2460</v>
       </c>
       <c r="D816" s="1" t="s">
-        <v>2334</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="817" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B817" s="1" t="s">
-        <v>2477</v>
+        <v>2462</v>
       </c>
       <c r="C817" s="1" t="s">
-        <v>2478</v>
+        <v>2463</v>
       </c>
       <c r="D817" s="1" t="s">
-        <v>2479</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="818" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B818" s="1" t="s">
-        <v>2480</v>
+        <v>2331</v>
       </c>
       <c r="C818" s="1" t="s">
-        <v>2481</v>
+        <v>2333</v>
       </c>
       <c r="D818" s="1" t="s">
-        <v>2482</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="819" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B819" s="1" t="s">
-        <v>2483</v>
+        <v>2465</v>
       </c>
       <c r="C819" s="1" t="s">
-        <v>2484</v>
+        <v>2466</v>
       </c>
       <c r="D819" s="1" t="s">
-        <v>2485</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="820" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B820" s="1" t="s">
-        <v>2336</v>
+        <v>2468</v>
       </c>
       <c r="C820" s="1" t="s">
-        <v>2495</v>
+        <v>2469</v>
       </c>
       <c r="D820" s="1" t="s">
-        <v>2337</v>
+        <v>2470</v>
       </c>
     </row>
     <row r="821" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B821" s="1" t="s">
-        <v>2486</v>
+        <v>2471</v>
       </c>
       <c r="C821" s="1" t="s">
-        <v>2487</v>
+        <v>2624</v>
       </c>
       <c r="D821" s="1" t="s">
-        <v>2498</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="822" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B822" s="1" t="s">
-        <v>2488</v>
+        <v>2334</v>
       </c>
       <c r="C822" s="1" t="s">
-        <v>2489</v>
+        <v>2482</v>
       </c>
       <c r="D822" s="1" t="s">
-        <v>2490</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="823" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B823" s="1" t="s">
-        <v>2491</v>
+        <v>2473</v>
       </c>
       <c r="C823" s="1" t="s">
-        <v>2493</v>
+        <v>2474</v>
       </c>
       <c r="D823" s="1" t="s">
-        <v>2492</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="824" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B824" s="1" t="s">
-        <v>2494</v>
+        <v>2475</v>
       </c>
       <c r="C824" s="1" t="s">
-        <v>2496</v>
+        <v>2476</v>
       </c>
       <c r="D824" s="1" t="s">
-        <v>2497</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="825" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B825" s="1" t="s">
-        <v>2338</v>
+        <v>2478</v>
       </c>
       <c r="C825" s="1" t="s">
-        <v>2340</v>
+        <v>2480</v>
       </c>
       <c r="D825" s="1" t="s">
-        <v>2339</v>
+        <v>2479</v>
       </c>
     </row>
     <row r="826" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B826" s="1" t="s">
-        <v>2499</v>
+        <v>2481</v>
       </c>
       <c r="C826" s="1" t="s">
-        <v>2500</v>
+        <v>2483</v>
       </c>
       <c r="D826" s="1" t="s">
-        <v>2501</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="827" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B827" s="1" t="s">
-        <v>2502</v>
+        <v>2336</v>
       </c>
       <c r="C827" s="1" t="s">
-        <v>2503</v>
+        <v>2338</v>
       </c>
       <c r="D827" s="1" t="s">
-        <v>2504</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="828" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B828" s="1" t="s">
-        <v>2505</v>
+        <v>2486</v>
       </c>
       <c r="C828" s="1" t="s">
-        <v>2506</v>
+        <v>2487</v>
       </c>
       <c r="D828" s="1" t="s">
-        <v>2507</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="829" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B829" s="1" t="s">
-        <v>2341</v>
+        <v>2489</v>
       </c>
       <c r="C829" s="1" t="s">
-        <v>2343</v>
+        <v>2490</v>
       </c>
       <c r="D829" s="1" t="s">
-        <v>2342</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="830" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B830" s="1" t="s">
-        <v>2344</v>
+        <v>2492</v>
       </c>
       <c r="C830" s="1" t="s">
-        <v>2346</v>
+        <v>2493</v>
       </c>
       <c r="D830" s="1" t="s">
-        <v>2345</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="831" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B831" s="1" t="s">
+        <v>2339</v>
+      </c>
+      <c r="C831" s="1" t="s">
+        <v>2341</v>
+      </c>
+      <c r="D831" s="1" t="s">
+        <v>2340</v>
+      </c>
+    </row>
+    <row r="832" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B832" s="1" t="s">
+        <v>2342</v>
+      </c>
+      <c r="C832" s="1" t="s">
+        <v>2344</v>
+      </c>
+      <c r="D832" s="1" t="s">
+        <v>2343</v>
+      </c>
+    </row>
+    <row r="833" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B833" s="1" t="s">
+        <v>2495</v>
+      </c>
+      <c r="C833" s="1" t="s">
+        <v>2496</v>
+      </c>
+      <c r="D833" s="1" t="s">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="834" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B834" s="3" t="s">
+        <v>2345</v>
+      </c>
+      <c r="C834" s="3" t="s">
+        <v>2346</v>
+      </c>
+      <c r="D834" s="3" t="s">
+        <v>2507</v>
+      </c>
+    </row>
+    <row r="835" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B835" s="3" t="s">
+        <v>2498</v>
+      </c>
+      <c r="C835" s="3" t="s">
+        <v>2499</v>
+      </c>
+      <c r="D835" s="3" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="836" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B836" s="3" t="s">
+        <v>2501</v>
+      </c>
+      <c r="C836" s="3" t="s">
+        <v>2502</v>
+      </c>
+      <c r="D836" s="3" t="s">
+        <v>2503</v>
+      </c>
+    </row>
+    <row r="837" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B837" s="3" t="s">
+        <v>2504</v>
+      </c>
+      <c r="C837" s="3" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D837" s="3" t="s">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="838" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B838" s="2" t="s">
+        <v>2347</v>
+      </c>
+      <c r="C838" s="1" t="s">
+        <v>2349</v>
+      </c>
+      <c r="D838" s="1" t="s">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="839" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B839" s="2" t="s">
         <v>2508</v>
       </c>
-      <c r="C831" s="1" t="s">
+      <c r="C839" s="1" t="s">
         <v>2509</v>
       </c>
-      <c r="D831" s="1" t="s">
+      <c r="D839" s="1" t="s">
         <v>2510</v>
-      </c>
-    </row>
-    <row r="832" spans="2:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B832" s="4" t="s">
-        <v>2347</v>
-      </c>
-      <c r="C832" s="4" t="s">
-        <v>2349</v>
-      </c>
-      <c r="D832" s="4" t="s">
-        <v>2348</v>
-      </c>
-    </row>
-    <row r="833" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B833" s="2" t="s">
-        <v>2350</v>
-      </c>
-      <c r="C833" s="1" t="s">
-        <v>2352</v>
-      </c>
-      <c r="D833" s="1" t="s">
-        <v>2351</v>
-      </c>
-    </row>
-    <row r="834" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B834" s="1" t="s">
-        <v>2353</v>
-      </c>
-      <c r="C834" s="1" t="s">
-        <v>2355</v>
-      </c>
-      <c r="D834" s="1" t="s">
-        <v>2354</v>
-      </c>
-    </row>
-    <row r="835" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B835" s="1" t="s">
-        <v>2356</v>
-      </c>
-      <c r="C835" s="1" t="s">
-        <v>2363</v>
-      </c>
-      <c r="D835" s="1" t="s">
-        <v>2357</v>
-      </c>
-    </row>
-    <row r="836" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B836" s="1" t="s">
-        <v>2358</v>
-      </c>
-      <c r="C836" s="1" t="s">
-        <v>2360</v>
-      </c>
-      <c r="D836" s="1" t="s">
-        <v>2359</v>
-      </c>
-    </row>
-    <row r="837" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B837" s="1" t="s">
-        <v>2361</v>
-      </c>
-      <c r="C837" s="1" t="s">
-        <v>2364</v>
-      </c>
-      <c r="D837" s="1" t="s">
-        <v>2362</v>
-      </c>
-    </row>
-    <row r="838" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B838" s="1" t="s">
-        <v>2367</v>
-      </c>
-      <c r="C838" s="1" t="s">
-        <v>2366</v>
-      </c>
-      <c r="D838" s="1" t="s">
-        <v>2365</v>
-      </c>
-    </row>
-    <row r="839" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B839" s="1" t="s">
-        <v>2368</v>
-      </c>
-      <c r="C839" s="1" t="s">
-        <v>2370</v>
-      </c>
-      <c r="D839" s="1" t="s">
-        <v>2369</v>
       </c>
     </row>
     <row r="840" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B840" s="1" t="s">
-        <v>2371</v>
+        <v>2350</v>
       </c>
       <c r="C840" s="1" t="s">
-        <v>2373</v>
+        <v>2352</v>
       </c>
       <c r="D840" s="1" t="s">
-        <v>2372</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="841" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B841" s="1" t="s">
-        <v>2374</v>
+        <v>2511</v>
       </c>
       <c r="C841" s="1" t="s">
-        <v>2376</v>
+        <v>2512</v>
       </c>
       <c r="D841" s="1" t="s">
-        <v>2375</v>
+        <v>2513</v>
       </c>
     </row>
     <row r="842" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B842" s="1" t="s">
-        <v>2379</v>
+        <v>2514</v>
       </c>
       <c r="C842" s="1" t="s">
-        <v>2378</v>
+        <v>2515</v>
       </c>
       <c r="D842" s="1" t="s">
-        <v>2377</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="843" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B843" s="1" t="s">
-        <v>2381</v>
+        <v>2517</v>
       </c>
       <c r="C843" s="1" t="s">
-        <v>2380</v>
+        <v>2518</v>
       </c>
       <c r="D843" s="1" t="s">
-        <v>2382</v>
+        <v>2519</v>
       </c>
     </row>
     <row r="844" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B844" s="1" t="s">
-        <v>2383</v>
+        <v>2353</v>
       </c>
       <c r="C844" s="1" t="s">
-        <v>2385</v>
+        <v>2521</v>
       </c>
       <c r="D844" s="1" t="s">
-        <v>2384</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="845" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B845" s="1" t="s">
-        <v>2386</v>
+        <v>2520</v>
       </c>
       <c r="C845" s="1" t="s">
-        <v>2388</v>
+        <v>2522</v>
       </c>
       <c r="D845" s="1" t="s">
-        <v>2387</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="846" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B846" s="1" t="s">
-        <v>2389</v>
+        <v>2355</v>
       </c>
       <c r="C846" s="1" t="s">
-        <v>2391</v>
+        <v>2356</v>
       </c>
       <c r="D846" s="1" t="s">
-        <v>2390</v>
+        <v>2631</v>
       </c>
     </row>
     <row r="847" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B847" s="1" t="s">
-        <v>2392</v>
+        <v>2625</v>
       </c>
       <c r="C847" s="1" t="s">
-        <v>2394</v>
+        <v>2626</v>
       </c>
       <c r="D847" s="1" t="s">
-        <v>2393</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="848" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B848" s="1" t="s">
-        <v>2395</v>
+        <v>2628</v>
       </c>
       <c r="C848" s="1" t="s">
-        <v>2396</v>
+        <v>2629</v>
       </c>
       <c r="D848" s="1" t="s">
-        <v>2397</v>
+        <v>2630</v>
       </c>
     </row>
     <row r="849" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B849" s="1" t="s">
-        <v>2398</v>
+        <v>2357</v>
       </c>
       <c r="C849" s="1" t="s">
-        <v>2400</v>
+        <v>2359</v>
       </c>
       <c r="D849" s="1" t="s">
-        <v>2399</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="850" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B850" s="1" t="s">
-        <v>2401</v>
+        <v>2524</v>
       </c>
       <c r="C850" s="1" t="s">
-        <v>2402</v>
+        <v>2525</v>
       </c>
       <c r="D850" s="1" t="s">
-        <v>2403</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="851" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B851" s="1" t="s">
-        <v>2404</v>
+        <v>2361</v>
       </c>
       <c r="C851" s="1" t="s">
-        <v>2405</v>
+        <v>2527</v>
       </c>
       <c r="D851" s="1" t="s">
-        <v>2406</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="852" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B852" s="1" t="s">
-        <v>2407</v>
+        <v>2528</v>
       </c>
       <c r="C852" s="1" t="s">
-        <v>2409</v>
+        <v>2529</v>
       </c>
       <c r="D852" s="1" t="s">
-        <v>2408</v>
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="853" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B853" s="1" t="s">
+        <v>2531</v>
+      </c>
+      <c r="C853" s="1" t="s">
+        <v>2532</v>
+      </c>
+      <c r="D853" s="1" t="s">
+        <v>2533</v>
+      </c>
+    </row>
+    <row r="854" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B854" s="1" t="s">
+        <v>2362</v>
+      </c>
+      <c r="C854" s="1" t="s">
+        <v>2537</v>
+      </c>
+      <c r="D854" s="1" t="s">
+        <v>2363</v>
+      </c>
+    </row>
+    <row r="855" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B855" s="1" t="s">
+        <v>2632</v>
+      </c>
+      <c r="C855" s="1" t="s">
+        <v>2633</v>
+      </c>
+      <c r="D855" s="1" t="s">
+        <v>2634</v>
+      </c>
+    </row>
+    <row r="856" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B856" s="1" t="s">
+        <v>2534</v>
+      </c>
+      <c r="C856" s="1" t="s">
+        <v>2536</v>
+      </c>
+      <c r="D856" s="1" t="s">
+        <v>2535</v>
+      </c>
+    </row>
+    <row r="857" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B857" s="1" t="s">
+        <v>2364</v>
+      </c>
+      <c r="C857" s="1" t="s">
+        <v>2366</v>
+      </c>
+      <c r="D857" s="1" t="s">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="858" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B858" s="1" t="s">
+        <v>2538</v>
+      </c>
+      <c r="C858" s="1" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D858" s="1" t="s">
+        <v>2539</v>
+      </c>
+    </row>
+    <row r="859" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B859" s="1" t="s">
+        <v>2540</v>
+      </c>
+      <c r="C859" s="1" t="s">
+        <v>2541</v>
+      </c>
+      <c r="D859" s="1" t="s">
+        <v>2543</v>
+      </c>
+    </row>
+    <row r="860" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B860" s="1" t="s">
+        <v>2367</v>
+      </c>
+      <c r="C860" s="1" t="s">
+        <v>2369</v>
+      </c>
+      <c r="D860" s="1" t="s">
+        <v>2368</v>
+      </c>
+    </row>
+    <row r="861" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B861" s="1" t="s">
+        <v>2544</v>
+      </c>
+      <c r="C861" s="1" t="s">
+        <v>2545</v>
+      </c>
+      <c r="D861" s="1" t="s">
+        <v>2546</v>
+      </c>
+    </row>
+    <row r="862" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B862" s="1" t="s">
+        <v>2547</v>
+      </c>
+      <c r="C862" s="1" t="s">
+        <v>2548</v>
+      </c>
+      <c r="D862" s="1" t="s">
+        <v>2549</v>
+      </c>
+    </row>
+    <row r="863" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B863" s="1" t="s">
+        <v>2550</v>
+      </c>
+      <c r="C863" s="1" t="s">
+        <v>2551</v>
+      </c>
+      <c r="D863" s="1" t="s">
+        <v>2552</v>
+      </c>
+    </row>
+    <row r="864" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B864" s="1" t="s">
+        <v>2371</v>
+      </c>
+      <c r="C864" s="1" t="s">
+        <v>2557</v>
+      </c>
+      <c r="D864" s="1" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="865" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B865" s="1" t="s">
+        <v>2553</v>
+      </c>
+      <c r="C865" s="1" t="s">
+        <v>2554</v>
+      </c>
+      <c r="D865" s="1" t="s">
+        <v>2555</v>
+      </c>
+    </row>
+    <row r="866" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B866" s="1" t="s">
+        <v>2556</v>
+      </c>
+      <c r="C866" s="1" t="s">
+        <v>2558</v>
+      </c>
+      <c r="D866" s="1" t="s">
+        <v>2559</v>
+      </c>
+    </row>
+    <row r="867" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B867" s="1" t="s">
+        <v>2560</v>
+      </c>
+      <c r="C867" s="1" t="s">
+        <v>2562</v>
+      </c>
+      <c r="D867" s="1" t="s">
+        <v>2561</v>
+      </c>
+    </row>
+    <row r="868" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B868" s="1" t="s">
+        <v>2563</v>
+      </c>
+      <c r="C868" s="1" t="s">
+        <v>2564</v>
+      </c>
+      <c r="D868" s="1" t="s">
+        <v>2565</v>
+      </c>
+    </row>
+    <row r="869" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B869" s="1" t="s">
+        <v>2372</v>
+      </c>
+      <c r="C869" s="1" t="s">
+        <v>2570</v>
+      </c>
+      <c r="D869" s="1" t="s">
+        <v>2373</v>
+      </c>
+    </row>
+    <row r="870" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B870" s="1" t="s">
+        <v>2566</v>
+      </c>
+      <c r="C870" s="1" t="s">
+        <v>2568</v>
+      </c>
+      <c r="D870" s="1" t="s">
+        <v>2567</v>
+      </c>
+    </row>
+    <row r="871" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B871" s="1" t="s">
+        <v>2569</v>
+      </c>
+      <c r="C871" s="1" t="s">
+        <v>2571</v>
+      </c>
+      <c r="D871" s="1" t="s">
+        <v>2572</v>
+      </c>
+    </row>
+    <row r="872" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B872" s="1" t="s">
+        <v>2374</v>
+      </c>
+      <c r="C872" s="1" t="s">
+        <v>2376</v>
+      </c>
+      <c r="D872" s="1" t="s">
+        <v>2375</v>
+      </c>
+    </row>
+    <row r="873" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B873" s="1" t="s">
+        <v>2573</v>
+      </c>
+      <c r="C873" s="1" t="s">
+        <v>2574</v>
+      </c>
+      <c r="D873" s="1" t="s">
+        <v>2575</v>
+      </c>
+    </row>
+    <row r="874" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B874" s="1" t="s">
+        <v>2576</v>
+      </c>
+      <c r="C874" s="1" t="s">
+        <v>2577</v>
+      </c>
+      <c r="D874" s="1" t="s">
+        <v>2578</v>
+      </c>
+    </row>
+    <row r="875" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B875" s="1" t="s">
+        <v>2377</v>
+      </c>
+      <c r="C875" s="1" t="s">
+        <v>2582</v>
+      </c>
+      <c r="D875" s="1" t="s">
+        <v>2378</v>
+      </c>
+    </row>
+    <row r="876" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B876" s="1" t="s">
+        <v>2579</v>
+      </c>
+      <c r="C876" s="1" t="s">
+        <v>2581</v>
+      </c>
+      <c r="D876" s="1" t="s">
+        <v>2580</v>
+      </c>
+    </row>
+    <row r="877" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B877" s="1" t="s">
+        <v>2583</v>
+      </c>
+      <c r="C877" s="1" t="s">
+        <v>2583</v>
+      </c>
+      <c r="D877" s="1" t="s">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="878" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B878" s="1" t="s">
+        <v>2379</v>
+      </c>
+      <c r="C878" s="1" t="s">
+        <v>2592</v>
+      </c>
+      <c r="D878" s="1" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="879" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B879" s="1" t="s">
+        <v>2585</v>
+      </c>
+      <c r="C879" s="1" t="s">
+        <v>2586</v>
+      </c>
+      <c r="D879" s="1" t="s">
+        <v>2587</v>
+      </c>
+    </row>
+    <row r="880" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B880" s="1" t="s">
+        <v>2588</v>
+      </c>
+      <c r="C880" s="1" t="s">
+        <v>2591</v>
+      </c>
+      <c r="D880" s="1" t="s">
+        <v>2589</v>
+      </c>
+    </row>
+    <row r="881" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B881" s="1" t="s">
+        <v>2590</v>
+      </c>
+      <c r="C881" s="1" t="s">
+        <v>2593</v>
+      </c>
+      <c r="D881" s="1" t="s">
+        <v>2594</v>
+      </c>
+    </row>
+    <row r="882" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B882" s="1" t="s">
+        <v>2381</v>
+      </c>
+      <c r="C882" s="1" t="s">
+        <v>2601</v>
+      </c>
+      <c r="D882" s="1" t="s">
+        <v>2382</v>
+      </c>
+    </row>
+    <row r="883" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B883" s="1" t="s">
+        <v>2595</v>
+      </c>
+      <c r="C883" s="1" t="s">
+        <v>2597</v>
+      </c>
+      <c r="D883" s="1" t="s">
+        <v>2596</v>
+      </c>
+    </row>
+    <row r="884" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B884" s="1" t="s">
+        <v>2598</v>
+      </c>
+      <c r="C884" s="1" t="s">
+        <v>2599</v>
+      </c>
+      <c r="D884" s="1" t="s">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="885" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B885" s="1" t="s">
+        <v>2602</v>
+      </c>
+      <c r="C885" s="1" t="s">
+        <v>2604</v>
+      </c>
+      <c r="D885" s="1" t="s">
+        <v>2603</v>
+      </c>
+    </row>
+    <row r="886" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B886" s="1" t="s">
+        <v>2605</v>
+      </c>
+      <c r="C886" s="1" t="s">
+        <v>2606</v>
+      </c>
+      <c r="D886" s="1" t="s">
+        <v>2607</v>
+      </c>
+    </row>
+    <row r="887" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B887" s="1" t="s">
+        <v>2383</v>
+      </c>
+      <c r="C887" s="1" t="s">
+        <v>2384</v>
+      </c>
+      <c r="D887" s="1" t="s">
+        <v>2385</v>
+      </c>
+    </row>
+    <row r="888" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B888" s="1" t="s">
+        <v>2608</v>
+      </c>
+      <c r="C888" s="1" t="s">
+        <v>2609</v>
+      </c>
+      <c r="D888" s="1" t="s">
+        <v>2610</v>
+      </c>
+    </row>
+    <row r="889" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B889" s="1" t="s">
+        <v>2611</v>
+      </c>
+      <c r="C889" s="1" t="s">
+        <v>2612</v>
+      </c>
+      <c r="D889" s="1" t="s">
+        <v>2613</v>
+      </c>
+    </row>
+    <row r="890" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B890" s="1" t="s">
+        <v>2614</v>
+      </c>
+      <c r="C890" s="1" t="s">
+        <v>2615</v>
+      </c>
+      <c r="D890" s="1" t="s">
+        <v>2616</v>
+      </c>
+    </row>
+    <row r="891" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B891" s="1" t="s">
+        <v>2386</v>
+      </c>
+      <c r="C891" s="1" t="s">
+        <v>2388</v>
+      </c>
+      <c r="D891" s="1" t="s">
+        <v>2387</v>
+      </c>
+    </row>
+    <row r="892" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B892" s="1" t="s">
+        <v>2389</v>
+      </c>
+      <c r="C892" s="1" t="s">
+        <v>2390</v>
+      </c>
+      <c r="D892" s="1" t="s">
+        <v>2391</v>
+      </c>
+    </row>
+    <row r="893" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B893" s="1" t="s">
+        <v>2392</v>
+      </c>
+      <c r="C893" s="1" t="s">
+        <v>2393</v>
+      </c>
+      <c r="D893" s="1" t="s">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="894" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B894" s="1" t="s">
+        <v>2395</v>
+      </c>
+      <c r="C894" s="1" t="s">
+        <v>2397</v>
+      </c>
+      <c r="D894" s="1" t="s">
+        <v>2396</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B108">
-    <cfRule type="duplicateValues" dxfId="1666" priority="2507"/>
+    <cfRule type="duplicateValues" dxfId="1661" priority="2507"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B125">
-    <cfRule type="duplicateValues" dxfId="1665" priority="2506"/>
+    <cfRule type="duplicateValues" dxfId="1660" priority="2506"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B132">
-    <cfRule type="duplicateValues" dxfId="1664" priority="2505"/>
+    <cfRule type="duplicateValues" dxfId="1659" priority="2505"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B128">
-    <cfRule type="duplicateValues" dxfId="1663" priority="2504"/>
+    <cfRule type="duplicateValues" dxfId="1658" priority="2504"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B129">
-    <cfRule type="duplicateValues" dxfId="1662" priority="2503"/>
+    <cfRule type="duplicateValues" dxfId="1657" priority="2503"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B130">
-    <cfRule type="duplicateValues" dxfId="1661" priority="2502"/>
+    <cfRule type="duplicateValues" dxfId="1656" priority="2502"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B133">
-    <cfRule type="duplicateValues" dxfId="1660" priority="2501"/>
+    <cfRule type="duplicateValues" dxfId="1655" priority="2501"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B135">
-    <cfRule type="duplicateValues" dxfId="1659" priority="2500"/>
+    <cfRule type="duplicateValues" dxfId="1654" priority="2500"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B136">
-    <cfRule type="duplicateValues" dxfId="1658" priority="2499"/>
+    <cfRule type="duplicateValues" dxfId="1653" priority="2499"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B138">
-    <cfRule type="duplicateValues" dxfId="1657" priority="2498"/>
+    <cfRule type="duplicateValues" dxfId="1652" priority="2498"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B139">
-    <cfRule type="duplicateValues" dxfId="1656" priority="2497"/>
+    <cfRule type="duplicateValues" dxfId="1651" priority="2497"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B140">
-    <cfRule type="duplicateValues" dxfId="1655" priority="2496"/>
+    <cfRule type="duplicateValues" dxfId="1650" priority="2496"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B141">
-    <cfRule type="duplicateValues" dxfId="1654" priority="2495"/>
+    <cfRule type="duplicateValues" dxfId="1649" priority="2495"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B142">
-    <cfRule type="duplicateValues" dxfId="1653" priority="2494"/>
+    <cfRule type="duplicateValues" dxfId="1648" priority="2494"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B148">
-    <cfRule type="duplicateValues" dxfId="1652" priority="2493"/>
+    <cfRule type="duplicateValues" dxfId="1647" priority="2493"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B149">
-    <cfRule type="duplicateValues" dxfId="1651" priority="2492"/>
+    <cfRule type="duplicateValues" dxfId="1646" priority="2492"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B154">
-    <cfRule type="duplicateValues" dxfId="1650" priority="2490"/>
+    <cfRule type="duplicateValues" dxfId="1645" priority="2490"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B155">
-    <cfRule type="duplicateValues" dxfId="1649" priority="2489"/>
+    <cfRule type="duplicateValues" dxfId="1644" priority="2489"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B157">
-    <cfRule type="duplicateValues" dxfId="1648" priority="2487"/>
+    <cfRule type="duplicateValues" dxfId="1643" priority="2487"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B161">
-    <cfRule type="duplicateValues" dxfId="1647" priority="2486"/>
+    <cfRule type="duplicateValues" dxfId="1642" priority="2486"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B162">
-    <cfRule type="duplicateValues" dxfId="1646" priority="2485"/>
+    <cfRule type="duplicateValues" dxfId="1641" priority="2485"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B163">
-    <cfRule type="duplicateValues" dxfId="1645" priority="2484"/>
+    <cfRule type="duplicateValues" dxfId="1640" priority="2484"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B164">
-    <cfRule type="duplicateValues" dxfId="1644" priority="2483"/>
+    <cfRule type="duplicateValues" dxfId="1639" priority="2483"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B166">
-    <cfRule type="duplicateValues" dxfId="1643" priority="2481"/>
+    <cfRule type="duplicateValues" dxfId="1638" priority="2481"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B167">
-    <cfRule type="duplicateValues" dxfId="1642" priority="2480"/>
+    <cfRule type="duplicateValues" dxfId="1637" priority="2480"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B170">
-    <cfRule type="duplicateValues" dxfId="1641" priority="2479"/>
+    <cfRule type="duplicateValues" dxfId="1636" priority="2479"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B179">
-    <cfRule type="duplicateValues" dxfId="1640" priority="2473"/>
+    <cfRule type="duplicateValues" dxfId="1635" priority="2473"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B186">
-    <cfRule type="duplicateValues" dxfId="1639" priority="2472"/>
+    <cfRule type="duplicateValues" dxfId="1634" priority="2472"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B187">
-    <cfRule type="duplicateValues" dxfId="1638" priority="2471"/>
+    <cfRule type="duplicateValues" dxfId="1633" priority="2471"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B191">
-    <cfRule type="duplicateValues" dxfId="1637" priority="2469"/>
+    <cfRule type="duplicateValues" dxfId="1632" priority="2469"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B192">
-    <cfRule type="duplicateValues" dxfId="1636" priority="2468"/>
+    <cfRule type="duplicateValues" dxfId="1631" priority="2468"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B193">
-    <cfRule type="duplicateValues" dxfId="1635" priority="2467"/>
+    <cfRule type="duplicateValues" dxfId="1630" priority="2467"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B194">
-    <cfRule type="duplicateValues" dxfId="1634" priority="2466"/>
+    <cfRule type="duplicateValues" dxfId="1629" priority="2466"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B196">
-    <cfRule type="duplicateValues" dxfId="1633" priority="2465"/>
+    <cfRule type="duplicateValues" dxfId="1628" priority="2465"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B197">
-    <cfRule type="duplicateValues" dxfId="1632" priority="2464"/>
+    <cfRule type="duplicateValues" dxfId="1627" priority="2464"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B198">
-    <cfRule type="duplicateValues" dxfId="1631" priority="2463"/>
+    <cfRule type="duplicateValues" dxfId="1626" priority="2463"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B200">
-    <cfRule type="duplicateValues" dxfId="1630" priority="2462"/>
+    <cfRule type="duplicateValues" dxfId="1625" priority="2462"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B201">
-    <cfRule type="duplicateValues" dxfId="1629" priority="2461"/>
+    <cfRule type="duplicateValues" dxfId="1624" priority="2461"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B202">
-    <cfRule type="duplicateValues" dxfId="1628" priority="2460"/>
+    <cfRule type="duplicateValues" dxfId="1623" priority="2460"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B204">
-    <cfRule type="duplicateValues" dxfId="1627" priority="2459"/>
+    <cfRule type="duplicateValues" dxfId="1622" priority="2459"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B205">
-    <cfRule type="duplicateValues" dxfId="1626" priority="2458"/>
+    <cfRule type="duplicateValues" dxfId="1621" priority="2458"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B209">
-    <cfRule type="duplicateValues" dxfId="1625" priority="2454"/>
+    <cfRule type="duplicateValues" dxfId="1620" priority="2454"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B210">
-    <cfRule type="duplicateValues" dxfId="1624" priority="2453"/>
+    <cfRule type="duplicateValues" dxfId="1619" priority="2453"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B211">
-    <cfRule type="duplicateValues" dxfId="1623" priority="2452"/>
+    <cfRule type="duplicateValues" dxfId="1618" priority="2452"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B214">
-    <cfRule type="duplicateValues" dxfId="1622" priority="2451"/>
+    <cfRule type="duplicateValues" dxfId="1617" priority="2451"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B216">
-    <cfRule type="duplicateValues" dxfId="1621" priority="2449"/>
+    <cfRule type="duplicateValues" dxfId="1616" priority="2449"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B217">
-    <cfRule type="duplicateValues" dxfId="1620" priority="2448"/>
+    <cfRule type="duplicateValues" dxfId="1615" priority="2448"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B219">
-    <cfRule type="duplicateValues" dxfId="1619" priority="2447"/>
+    <cfRule type="duplicateValues" dxfId="1614" priority="2447"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B220">
-    <cfRule type="duplicateValues" dxfId="1618" priority="2446"/>
+    <cfRule type="duplicateValues" dxfId="1613" priority="2446"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B225">
-    <cfRule type="duplicateValues" dxfId="1617" priority="2444"/>
+    <cfRule type="duplicateValues" dxfId="1612" priority="2444"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B226">
-    <cfRule type="duplicateValues" dxfId="1616" priority="2443"/>
+    <cfRule type="duplicateValues" dxfId="1611" priority="2443"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B227">
-    <cfRule type="duplicateValues" dxfId="1615" priority="2442"/>
+    <cfRule type="duplicateValues" dxfId="1610" priority="2442"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B228">
-    <cfRule type="duplicateValues" dxfId="1614" priority="2441"/>
+    <cfRule type="duplicateValues" dxfId="1609" priority="2441"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B237">
-    <cfRule type="duplicateValues" dxfId="1613" priority="2431"/>
+    <cfRule type="duplicateValues" dxfId="1608" priority="2431"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B237">
-    <cfRule type="duplicateValues" dxfId="1612" priority="2430"/>
+    <cfRule type="duplicateValues" dxfId="1607" priority="2430"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B238">
-    <cfRule type="duplicateValues" dxfId="1611" priority="2429"/>
+    <cfRule type="duplicateValues" dxfId="1606" priority="2429"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B238">
-    <cfRule type="duplicateValues" dxfId="1610" priority="2428"/>
+    <cfRule type="duplicateValues" dxfId="1605" priority="2428"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B241">
-    <cfRule type="duplicateValues" dxfId="1609" priority="2427"/>
+    <cfRule type="duplicateValues" dxfId="1604" priority="2427"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B241">
-    <cfRule type="duplicateValues" dxfId="1608" priority="2426"/>
+    <cfRule type="duplicateValues" dxfId="1603" priority="2426"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B245">
-    <cfRule type="duplicateValues" dxfId="1607" priority="2425"/>
+    <cfRule type="duplicateValues" dxfId="1602" priority="2425"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B245">
-    <cfRule type="duplicateValues" dxfId="1606" priority="2424"/>
+    <cfRule type="duplicateValues" dxfId="1601" priority="2424"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B246">
-    <cfRule type="duplicateValues" dxfId="1605" priority="2423"/>
+    <cfRule type="duplicateValues" dxfId="1600" priority="2423"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B246">
-    <cfRule type="duplicateValues" dxfId="1604" priority="2422"/>
+    <cfRule type="duplicateValues" dxfId="1599" priority="2422"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B247">
-    <cfRule type="duplicateValues" dxfId="1603" priority="2421"/>
+    <cfRule type="duplicateValues" dxfId="1598" priority="2421"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B247">
-    <cfRule type="duplicateValues" dxfId="1602" priority="2420"/>
+    <cfRule type="duplicateValues" dxfId="1597" priority="2420"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B248">
-    <cfRule type="duplicateValues" dxfId="1601" priority="2419"/>
+    <cfRule type="duplicateValues" dxfId="1596" priority="2419"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B248">
-    <cfRule type="duplicateValues" dxfId="1600" priority="2418"/>
+    <cfRule type="duplicateValues" dxfId="1595" priority="2418"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B249">
-    <cfRule type="duplicateValues" dxfId="1599" priority="2417"/>
+    <cfRule type="duplicateValues" dxfId="1594" priority="2417"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B249">
-    <cfRule type="duplicateValues" dxfId="1598" priority="2416"/>
+    <cfRule type="duplicateValues" dxfId="1593" priority="2416"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B252">
-    <cfRule type="duplicateValues" dxfId="1597" priority="2411"/>
+    <cfRule type="duplicateValues" dxfId="1592" priority="2411"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B252">
-    <cfRule type="duplicateValues" dxfId="1596" priority="2410"/>
+    <cfRule type="duplicateValues" dxfId="1591" priority="2410"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B255">
-    <cfRule type="duplicateValues" dxfId="1595" priority="2407"/>
+    <cfRule type="duplicateValues" dxfId="1590" priority="2407"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B255">
-    <cfRule type="duplicateValues" dxfId="1594" priority="2406"/>
+    <cfRule type="duplicateValues" dxfId="1589" priority="2406"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B263">
-    <cfRule type="duplicateValues" dxfId="1593" priority="2403"/>
+    <cfRule type="duplicateValues" dxfId="1588" priority="2403"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B263">
-    <cfRule type="duplicateValues" dxfId="1592" priority="2402"/>
+    <cfRule type="duplicateValues" dxfId="1587" priority="2402"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B271">
-    <cfRule type="duplicateValues" dxfId="1591" priority="2399"/>
+    <cfRule type="duplicateValues" dxfId="1586" priority="2399"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B271">
-    <cfRule type="duplicateValues" dxfId="1590" priority="2398"/>
+    <cfRule type="duplicateValues" dxfId="1585" priority="2398"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B274">
-    <cfRule type="duplicateValues" dxfId="1589" priority="2395"/>
+    <cfRule type="duplicateValues" dxfId="1584" priority="2395"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B274">
-    <cfRule type="duplicateValues" dxfId="1588" priority="2394"/>
+    <cfRule type="duplicateValues" dxfId="1583" priority="2394"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B275">
-    <cfRule type="duplicateValues" dxfId="1587" priority="2393"/>
+    <cfRule type="duplicateValues" dxfId="1582" priority="2393"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B275">
-    <cfRule type="duplicateValues" dxfId="1586" priority="2392"/>
+    <cfRule type="duplicateValues" dxfId="1581" priority="2392"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B276">
-    <cfRule type="duplicateValues" dxfId="1585" priority="2391"/>
+    <cfRule type="duplicateValues" dxfId="1580" priority="2391"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B276">
-    <cfRule type="duplicateValues" dxfId="1584" priority="2390"/>
+    <cfRule type="duplicateValues" dxfId="1579" priority="2390"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B277">
-    <cfRule type="duplicateValues" dxfId="1583" priority="2387"/>
+    <cfRule type="duplicateValues" dxfId="1578" priority="2387"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B277">
-    <cfRule type="duplicateValues" dxfId="1582" priority="2386"/>
+    <cfRule type="duplicateValues" dxfId="1577" priority="2386"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B279">
-    <cfRule type="duplicateValues" dxfId="1581" priority="2385"/>
+    <cfRule type="duplicateValues" dxfId="1576" priority="2385"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B279">
-    <cfRule type="duplicateValues" dxfId="1580" priority="2384"/>
+    <cfRule type="duplicateValues" dxfId="1575" priority="2384"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B281">
-    <cfRule type="duplicateValues" dxfId="1579" priority="2379"/>
+    <cfRule type="duplicateValues" dxfId="1574" priority="2379"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B281">
-    <cfRule type="duplicateValues" dxfId="1578" priority="2378"/>
+    <cfRule type="duplicateValues" dxfId="1573" priority="2378"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B282">
-    <cfRule type="duplicateValues" dxfId="1577" priority="2377"/>
+    <cfRule type="duplicateValues" dxfId="1572" priority="2377"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B282">
-    <cfRule type="duplicateValues" dxfId="1576" priority="2376"/>
+    <cfRule type="duplicateValues" dxfId="1571" priority="2376"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B283">
-    <cfRule type="duplicateValues" dxfId="1575" priority="2375"/>
+    <cfRule type="duplicateValues" dxfId="1570" priority="2375"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B283">
-    <cfRule type="duplicateValues" dxfId="1574" priority="2374"/>
+    <cfRule type="duplicateValues" dxfId="1569" priority="2374"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B286">
-    <cfRule type="duplicateValues" dxfId="1573" priority="2369"/>
+    <cfRule type="duplicateValues" dxfId="1568" priority="2369"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B287">
-    <cfRule type="duplicateValues" dxfId="1572" priority="2366"/>
+    <cfRule type="duplicateValues" dxfId="1567" priority="2366"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B287">
-    <cfRule type="duplicateValues" dxfId="1571" priority="2365"/>
+    <cfRule type="duplicateValues" dxfId="1566" priority="2365"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B290">
-    <cfRule type="duplicateValues" dxfId="1570" priority="2364"/>
+    <cfRule type="duplicateValues" dxfId="1565" priority="2364"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B290">
-    <cfRule type="duplicateValues" dxfId="1569" priority="2363"/>
+    <cfRule type="duplicateValues" dxfId="1564" priority="2363"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B292">
-    <cfRule type="duplicateValues" dxfId="1568" priority="2362"/>
+    <cfRule type="duplicateValues" dxfId="1563" priority="2362"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B292">
-    <cfRule type="duplicateValues" dxfId="1567" priority="2361"/>
+    <cfRule type="duplicateValues" dxfId="1562" priority="2361"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B293">
-    <cfRule type="duplicateValues" dxfId="1566" priority="2358"/>
+    <cfRule type="duplicateValues" dxfId="1561" priority="2358"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B293">
-    <cfRule type="duplicateValues" dxfId="1565" priority="2357"/>
+    <cfRule type="duplicateValues" dxfId="1560" priority="2357"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B294">
-    <cfRule type="duplicateValues" dxfId="1564" priority="2356"/>
+    <cfRule type="duplicateValues" dxfId="1559" priority="2356"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B294">
-    <cfRule type="duplicateValues" dxfId="1563" priority="2355"/>
+    <cfRule type="duplicateValues" dxfId="1558" priority="2355"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B300">
-    <cfRule type="duplicateValues" dxfId="1562" priority="2354"/>
+    <cfRule type="duplicateValues" dxfId="1557" priority="2354"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B300">
-    <cfRule type="duplicateValues" dxfId="1561" priority="2353"/>
+    <cfRule type="duplicateValues" dxfId="1556" priority="2353"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B301">
-    <cfRule type="duplicateValues" dxfId="1560" priority="2352"/>
+    <cfRule type="duplicateValues" dxfId="1555" priority="2352"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B301">
-    <cfRule type="duplicateValues" dxfId="1559" priority="2351"/>
+    <cfRule type="duplicateValues" dxfId="1554" priority="2351"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B302">
-    <cfRule type="duplicateValues" dxfId="1558" priority="2348"/>
+    <cfRule type="duplicateValues" dxfId="1553" priority="2348"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B302">
-    <cfRule type="duplicateValues" dxfId="1557" priority="2347"/>
+    <cfRule type="duplicateValues" dxfId="1552" priority="2347"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B303">
-    <cfRule type="duplicateValues" dxfId="1556" priority="2346"/>
+    <cfRule type="duplicateValues" dxfId="1551" priority="2346"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B303">
-    <cfRule type="duplicateValues" dxfId="1555" priority="2345"/>
+    <cfRule type="duplicateValues" dxfId="1550" priority="2345"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B304">
-    <cfRule type="duplicateValues" dxfId="1554" priority="2344"/>
+    <cfRule type="duplicateValues" dxfId="1549" priority="2344"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B304">
-    <cfRule type="duplicateValues" dxfId="1553" priority="2343"/>
+    <cfRule type="duplicateValues" dxfId="1548" priority="2343"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B305">
-    <cfRule type="duplicateValues" dxfId="1552" priority="2342"/>
+    <cfRule type="duplicateValues" dxfId="1547" priority="2342"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B305">
-    <cfRule type="duplicateValues" dxfId="1551" priority="2341"/>
+    <cfRule type="duplicateValues" dxfId="1546" priority="2341"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B308">
-    <cfRule type="duplicateValues" dxfId="1550" priority="2337"/>
+    <cfRule type="duplicateValues" dxfId="1545" priority="2337"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B308">
-    <cfRule type="duplicateValues" dxfId="1549" priority="2336"/>
+    <cfRule type="duplicateValues" dxfId="1544" priority="2336"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B309">
-    <cfRule type="duplicateValues" dxfId="1548" priority="2335"/>
+    <cfRule type="duplicateValues" dxfId="1543" priority="2335"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B309">
-    <cfRule type="duplicateValues" dxfId="1547" priority="2334"/>
+    <cfRule type="duplicateValues" dxfId="1542" priority="2334"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B310">
-    <cfRule type="duplicateValues" dxfId="1546" priority="2333"/>
+    <cfRule type="duplicateValues" dxfId="1541" priority="2333"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B310">
-    <cfRule type="duplicateValues" dxfId="1545" priority="2332"/>
+    <cfRule type="duplicateValues" dxfId="1540" priority="2332"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B312">
-    <cfRule type="duplicateValues" dxfId="1544" priority="2327"/>
+    <cfRule type="duplicateValues" dxfId="1539" priority="2327"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B312">
-    <cfRule type="duplicateValues" dxfId="1543" priority="2326"/>
+    <cfRule type="duplicateValues" dxfId="1538" priority="2326"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B315">
-    <cfRule type="duplicateValues" dxfId="1542" priority="2319"/>
+    <cfRule type="duplicateValues" dxfId="1537" priority="2319"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B315">
-    <cfRule type="duplicateValues" dxfId="1541" priority="2318"/>
+    <cfRule type="duplicateValues" dxfId="1536" priority="2318"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B317">
-    <cfRule type="duplicateValues" dxfId="1540" priority="2311"/>
+    <cfRule type="duplicateValues" dxfId="1535" priority="2311"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B317">
-    <cfRule type="duplicateValues" dxfId="1539" priority="2310"/>
+    <cfRule type="duplicateValues" dxfId="1534" priority="2310"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B318">
-    <cfRule type="duplicateValues" dxfId="1538" priority="2309"/>
+    <cfRule type="duplicateValues" dxfId="1533" priority="2309"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B318">
-    <cfRule type="duplicateValues" dxfId="1537" priority="2308"/>
+    <cfRule type="duplicateValues" dxfId="1532" priority="2308"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B320">
-    <cfRule type="duplicateValues" dxfId="1536" priority="2301"/>
+    <cfRule type="duplicateValues" dxfId="1531" priority="2301"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B320">
-    <cfRule type="duplicateValues" dxfId="1535" priority="2300"/>
+    <cfRule type="duplicateValues" dxfId="1530" priority="2300"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B321">
-    <cfRule type="duplicateValues" dxfId="1534" priority="2299"/>
+    <cfRule type="duplicateValues" dxfId="1529" priority="2299"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B321">
-    <cfRule type="duplicateValues" dxfId="1533" priority="2298"/>
+    <cfRule type="duplicateValues" dxfId="1528" priority="2298"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B329">
-    <cfRule type="duplicateValues" dxfId="1532" priority="2279"/>
+    <cfRule type="duplicateValues" dxfId="1527" priority="2279"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B329">
-    <cfRule type="duplicateValues" dxfId="1531" priority="2278"/>
+    <cfRule type="duplicateValues" dxfId="1526" priority="2278"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B330">
-    <cfRule type="duplicateValues" dxfId="1530" priority="2275"/>
+    <cfRule type="duplicateValues" dxfId="1525" priority="2275"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B330">
-    <cfRule type="duplicateValues" dxfId="1529" priority="2274"/>
+    <cfRule type="duplicateValues" dxfId="1524" priority="2274"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B332">
-    <cfRule type="duplicateValues" dxfId="1528" priority="2273"/>
+    <cfRule type="duplicateValues" dxfId="1523" priority="2273"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B332">
-    <cfRule type="duplicateValues" dxfId="1527" priority="2272"/>
+    <cfRule type="duplicateValues" dxfId="1522" priority="2272"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B334">
-    <cfRule type="duplicateValues" dxfId="1526" priority="2271"/>
+    <cfRule type="duplicateValues" dxfId="1521" priority="2271"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B334">
-    <cfRule type="duplicateValues" dxfId="1525" priority="2270"/>
+    <cfRule type="duplicateValues" dxfId="1520" priority="2270"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B335">
-    <cfRule type="duplicateValues" dxfId="1524" priority="2269"/>
+    <cfRule type="duplicateValues" dxfId="1519" priority="2269"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B335">
-    <cfRule type="duplicateValues" dxfId="1523" priority="2268"/>
+    <cfRule type="duplicateValues" dxfId="1518" priority="2268"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B336">
-    <cfRule type="duplicateValues" dxfId="1522" priority="2265"/>
+    <cfRule type="duplicateValues" dxfId="1517" priority="2265"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B336">
-    <cfRule type="duplicateValues" dxfId="1521" priority="2264"/>
+    <cfRule type="duplicateValues" dxfId="1516" priority="2264"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B339">
-    <cfRule type="duplicateValues" dxfId="1520" priority="2263"/>
+    <cfRule type="duplicateValues" dxfId="1515" priority="2263"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B339">
-    <cfRule type="duplicateValues" dxfId="1519" priority="2262"/>
+    <cfRule type="duplicateValues" dxfId="1514" priority="2262"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B342">
-    <cfRule type="duplicateValues" dxfId="1518" priority="2259"/>
+    <cfRule type="duplicateValues" dxfId="1513" priority="2259"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B342">
-    <cfRule type="duplicateValues" dxfId="1517" priority="2258"/>
+    <cfRule type="duplicateValues" dxfId="1512" priority="2258"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B344">
-    <cfRule type="duplicateValues" dxfId="1516" priority="2253"/>
+    <cfRule type="duplicateValues" dxfId="1511" priority="2253"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B344">
-    <cfRule type="duplicateValues" dxfId="1515" priority="2252"/>
+    <cfRule type="duplicateValues" dxfId="1510" priority="2252"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B347">
-    <cfRule type="duplicateValues" dxfId="1514" priority="2251"/>
+    <cfRule type="duplicateValues" dxfId="1509" priority="2251"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B347">
-    <cfRule type="duplicateValues" dxfId="1513" priority="2250"/>
+    <cfRule type="duplicateValues" dxfId="1508" priority="2250"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B349">
-    <cfRule type="duplicateValues" dxfId="1512" priority="2249"/>
+    <cfRule type="duplicateValues" dxfId="1507" priority="2249"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B349">
-    <cfRule type="duplicateValues" dxfId="1511" priority="2248"/>
+    <cfRule type="duplicateValues" dxfId="1506" priority="2248"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B350">
-    <cfRule type="duplicateValues" dxfId="1510" priority="2245"/>
+    <cfRule type="duplicateValues" dxfId="1505" priority="2245"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B350">
-    <cfRule type="duplicateValues" dxfId="1509" priority="2244"/>
+    <cfRule type="duplicateValues" dxfId="1504" priority="2244"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B352">
-    <cfRule type="duplicateValues" dxfId="1508" priority="2241"/>
+    <cfRule type="duplicateValues" dxfId="1503" priority="2241"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B352">
-    <cfRule type="duplicateValues" dxfId="1507" priority="2240"/>
+    <cfRule type="duplicateValues" dxfId="1502" priority="2240"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B353">
-    <cfRule type="duplicateValues" dxfId="1506" priority="2237"/>
+    <cfRule type="duplicateValues" dxfId="1501" priority="2237"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B353">
-    <cfRule type="duplicateValues" dxfId="1505" priority="2236"/>
+    <cfRule type="duplicateValues" dxfId="1500" priority="2236"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B355">
-    <cfRule type="duplicateValues" dxfId="1504" priority="2233"/>
+    <cfRule type="duplicateValues" dxfId="1499" priority="2233"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B355">
-    <cfRule type="duplicateValues" dxfId="1503" priority="2232"/>
+    <cfRule type="duplicateValues" dxfId="1498" priority="2232"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B356">
-    <cfRule type="duplicateValues" dxfId="1502" priority="2231"/>
+    <cfRule type="duplicateValues" dxfId="1497" priority="2231"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B356">
-    <cfRule type="duplicateValues" dxfId="1501" priority="2230"/>
+    <cfRule type="duplicateValues" dxfId="1496" priority="2230"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B357">
-    <cfRule type="duplicateValues" dxfId="1500" priority="2229"/>
+    <cfRule type="duplicateValues" dxfId="1495" priority="2229"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B357">
-    <cfRule type="duplicateValues" dxfId="1499" priority="2228"/>
+    <cfRule type="duplicateValues" dxfId="1494" priority="2228"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B358">
-    <cfRule type="duplicateValues" dxfId="1498" priority="2225"/>
+    <cfRule type="duplicateValues" dxfId="1493" priority="2225"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B358">
-    <cfRule type="duplicateValues" dxfId="1497" priority="2224"/>
+    <cfRule type="duplicateValues" dxfId="1492" priority="2224"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B359">
-    <cfRule type="duplicateValues" dxfId="1496" priority="2223"/>
+    <cfRule type="duplicateValues" dxfId="1491" priority="2223"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B359">
-    <cfRule type="duplicateValues" dxfId="1495" priority="2222"/>
+    <cfRule type="duplicateValues" dxfId="1490" priority="2222"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B360">
-    <cfRule type="duplicateValues" dxfId="1494" priority="2221"/>
+    <cfRule type="duplicateValues" dxfId="1489" priority="2221"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B360">
-    <cfRule type="duplicateValues" dxfId="1493" priority="2220"/>
+    <cfRule type="duplicateValues" dxfId="1488" priority="2220"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B361">
-    <cfRule type="duplicateValues" dxfId="1492" priority="2219"/>
+    <cfRule type="duplicateValues" dxfId="1487" priority="2219"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B361">
-    <cfRule type="duplicateValues" dxfId="1491" priority="2218"/>
+    <cfRule type="duplicateValues" dxfId="1486" priority="2218"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B363">
-    <cfRule type="duplicateValues" dxfId="1490" priority="2215"/>
+    <cfRule type="duplicateValues" dxfId="1485" priority="2215"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B363">
-    <cfRule type="duplicateValues" dxfId="1489" priority="2214"/>
+    <cfRule type="duplicateValues" dxfId="1484" priority="2214"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B365">
-    <cfRule type="duplicateValues" dxfId="1488" priority="2209"/>
+    <cfRule type="duplicateValues" dxfId="1483" priority="2209"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B365">
-    <cfRule type="duplicateValues" dxfId="1487" priority="2208"/>
+    <cfRule type="duplicateValues" dxfId="1482" priority="2208"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B366">
-    <cfRule type="duplicateValues" dxfId="1486" priority="2205"/>
+    <cfRule type="duplicateValues" dxfId="1481" priority="2205"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B366">
-    <cfRule type="duplicateValues" dxfId="1485" priority="2204"/>
+    <cfRule type="duplicateValues" dxfId="1480" priority="2204"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B367">
-    <cfRule type="duplicateValues" dxfId="1484" priority="2201"/>
+    <cfRule type="duplicateValues" dxfId="1479" priority="2201"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B367">
-    <cfRule type="duplicateValues" dxfId="1483" priority="2200"/>
+    <cfRule type="duplicateValues" dxfId="1478" priority="2200"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B368">
-    <cfRule type="duplicateValues" dxfId="1482" priority="2199"/>
+    <cfRule type="duplicateValues" dxfId="1477" priority="2199"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B368">
-    <cfRule type="duplicateValues" dxfId="1481" priority="2198"/>
+    <cfRule type="duplicateValues" dxfId="1476" priority="2198"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B370">
-    <cfRule type="duplicateValues" dxfId="1480" priority="2193"/>
+    <cfRule type="duplicateValues" dxfId="1475" priority="2193"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B370">
-    <cfRule type="duplicateValues" dxfId="1479" priority="2192"/>
+    <cfRule type="duplicateValues" dxfId="1474" priority="2192"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B371">
-    <cfRule type="duplicateValues" dxfId="1478" priority="2191"/>
+    <cfRule type="duplicateValues" dxfId="1473" priority="2191"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B371">
-    <cfRule type="duplicateValues" dxfId="1477" priority="2190"/>
+    <cfRule type="duplicateValues" dxfId="1472" priority="2190"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B374">
-    <cfRule type="duplicateValues" dxfId="1476" priority="2185"/>
+    <cfRule type="duplicateValues" dxfId="1471" priority="2185"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B374">
-    <cfRule type="duplicateValues" dxfId="1475" priority="2184"/>
+    <cfRule type="duplicateValues" dxfId="1470" priority="2184"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B375">
-    <cfRule type="duplicateValues" dxfId="1474" priority="2183"/>
+    <cfRule type="duplicateValues" dxfId="1469" priority="2183"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B375">
-    <cfRule type="duplicateValues" dxfId="1473" priority="2182"/>
+    <cfRule type="duplicateValues" dxfId="1468" priority="2182"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B376">
-    <cfRule type="duplicateValues" dxfId="1472" priority="2179"/>
+    <cfRule type="duplicateValues" dxfId="1467" priority="2179"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B376">
-    <cfRule type="duplicateValues" dxfId="1471" priority="2178"/>
+    <cfRule type="duplicateValues" dxfId="1466" priority="2178"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B377">
-    <cfRule type="duplicateValues" dxfId="1470" priority="2175"/>
+    <cfRule type="duplicateValues" dxfId="1465" priority="2175"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B377">
-    <cfRule type="duplicateValues" dxfId="1469" priority="2174"/>
+    <cfRule type="duplicateValues" dxfId="1464" priority="2174"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B381">
-    <cfRule type="duplicateValues" dxfId="1468" priority="2173"/>
+    <cfRule type="duplicateValues" dxfId="1463" priority="2173"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B381">
-    <cfRule type="duplicateValues" dxfId="1467" priority="2172"/>
+    <cfRule type="duplicateValues" dxfId="1462" priority="2172"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B382">
-    <cfRule type="duplicateValues" dxfId="1466" priority="2169"/>
+    <cfRule type="duplicateValues" dxfId="1461" priority="2169"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B382">
-    <cfRule type="duplicateValues" dxfId="1465" priority="2168"/>
+    <cfRule type="duplicateValues" dxfId="1460" priority="2168"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B383">
-    <cfRule type="duplicateValues" dxfId="1464" priority="2165"/>
+    <cfRule type="duplicateValues" dxfId="1459" priority="2165"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B383">
-    <cfRule type="duplicateValues" dxfId="1463" priority="2164"/>
+    <cfRule type="duplicateValues" dxfId="1458" priority="2164"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B385">
-    <cfRule type="duplicateValues" dxfId="1462" priority="2161"/>
+    <cfRule type="duplicateValues" dxfId="1457" priority="2161"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B385">
-    <cfRule type="duplicateValues" dxfId="1461" priority="2160"/>
+    <cfRule type="duplicateValues" dxfId="1456" priority="2160"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B386">
-    <cfRule type="duplicateValues" dxfId="1460" priority="2155"/>
+    <cfRule type="duplicateValues" dxfId="1455" priority="2155"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B386">
-    <cfRule type="duplicateValues" dxfId="1459" priority="2154"/>
+    <cfRule type="duplicateValues" dxfId="1454" priority="2154"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B387">
-    <cfRule type="duplicateValues" dxfId="1458" priority="2149"/>
+    <cfRule type="duplicateValues" dxfId="1453" priority="2149"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B387">
-    <cfRule type="duplicateValues" dxfId="1457" priority="2148"/>
+    <cfRule type="duplicateValues" dxfId="1452" priority="2148"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B388">
-    <cfRule type="duplicateValues" dxfId="1456" priority="2147"/>
+    <cfRule type="duplicateValues" dxfId="1451" priority="2147"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B388">
-    <cfRule type="duplicateValues" dxfId="1455" priority="2146"/>
+    <cfRule type="duplicateValues" dxfId="1450" priority="2146"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B392">
-    <cfRule type="duplicateValues" dxfId="1454" priority="2143"/>
+    <cfRule type="duplicateValues" dxfId="1449" priority="2143"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B392">
-    <cfRule type="duplicateValues" dxfId="1453" priority="2142"/>
+    <cfRule type="duplicateValues" dxfId="1448" priority="2142"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B393">
-    <cfRule type="duplicateValues" dxfId="1452" priority="2141"/>
+    <cfRule type="duplicateValues" dxfId="1447" priority="2141"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B393">
-    <cfRule type="duplicateValues" dxfId="1451" priority="2140"/>
+    <cfRule type="duplicateValues" dxfId="1446" priority="2140"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B394">
-    <cfRule type="duplicateValues" dxfId="1450" priority="2137"/>
+    <cfRule type="duplicateValues" dxfId="1445" priority="2137"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B394">
-    <cfRule type="duplicateValues" dxfId="1449" priority="2136"/>
+    <cfRule type="duplicateValues" dxfId="1444" priority="2136"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B395">
-    <cfRule type="duplicateValues" dxfId="1448" priority="2135"/>
+    <cfRule type="duplicateValues" dxfId="1443" priority="2135"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B395">
-    <cfRule type="duplicateValues" dxfId="1447" priority="2134"/>
+    <cfRule type="duplicateValues" dxfId="1442" priority="2134"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B398">
-    <cfRule type="duplicateValues" dxfId="1446" priority="2133"/>
+    <cfRule type="duplicateValues" dxfId="1441" priority="2133"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B398">
-    <cfRule type="duplicateValues" dxfId="1445" priority="2132"/>
+    <cfRule type="duplicateValues" dxfId="1440" priority="2132"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B399">
-    <cfRule type="duplicateValues" dxfId="1444" priority="2131"/>
+    <cfRule type="duplicateValues" dxfId="1439" priority="2131"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B399">
-    <cfRule type="duplicateValues" dxfId="1443" priority="2130"/>
+    <cfRule type="duplicateValues" dxfId="1438" priority="2130"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B400">
-    <cfRule type="duplicateValues" dxfId="1442" priority="2127"/>
+    <cfRule type="duplicateValues" dxfId="1437" priority="2127"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B400">
-    <cfRule type="duplicateValues" dxfId="1441" priority="2126"/>
+    <cfRule type="duplicateValues" dxfId="1436" priority="2126"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B402">
-    <cfRule type="duplicateValues" dxfId="1440" priority="2125"/>
+    <cfRule type="duplicateValues" dxfId="1435" priority="2125"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B402">
-    <cfRule type="duplicateValues" dxfId="1439" priority="2124"/>
+    <cfRule type="duplicateValues" dxfId="1434" priority="2124"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B403">
-    <cfRule type="duplicateValues" dxfId="1438" priority="2123"/>
+    <cfRule type="duplicateValues" dxfId="1433" priority="2123"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B403">
-    <cfRule type="duplicateValues" dxfId="1437" priority="2122"/>
+    <cfRule type="duplicateValues" dxfId="1432" priority="2122"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B404">
-    <cfRule type="duplicateValues" dxfId="1436" priority="2121"/>
+    <cfRule type="duplicateValues" dxfId="1431" priority="2121"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B404">
-    <cfRule type="duplicateValues" dxfId="1435" priority="2120"/>
+    <cfRule type="duplicateValues" dxfId="1430" priority="2120"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B405">
-    <cfRule type="duplicateValues" dxfId="1434" priority="2119"/>
+    <cfRule type="duplicateValues" dxfId="1429" priority="2119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B405">
-    <cfRule type="duplicateValues" dxfId="1433" priority="2118"/>
+    <cfRule type="duplicateValues" dxfId="1428" priority="2118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B406">
-    <cfRule type="duplicateValues" dxfId="1432" priority="2117"/>
+    <cfRule type="duplicateValues" dxfId="1427" priority="2117"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B406">
-    <cfRule type="duplicateValues" dxfId="1431" priority="2116"/>
+    <cfRule type="duplicateValues" dxfId="1426" priority="2116"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B407">
-    <cfRule type="duplicateValues" dxfId="1430" priority="2115"/>
+    <cfRule type="duplicateValues" dxfId="1425" priority="2115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B407">
-    <cfRule type="duplicateValues" dxfId="1429" priority="2114"/>
+    <cfRule type="duplicateValues" dxfId="1424" priority="2114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B408">
-    <cfRule type="duplicateValues" dxfId="1428" priority="2113"/>
+    <cfRule type="duplicateValues" dxfId="1423" priority="2113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B408">
-    <cfRule type="duplicateValues" dxfId="1427" priority="2112"/>
+    <cfRule type="duplicateValues" dxfId="1422" priority="2112"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B409">
-    <cfRule type="duplicateValues" dxfId="1426" priority="2111"/>
+    <cfRule type="duplicateValues" dxfId="1421" priority="2111"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B409">
-    <cfRule type="duplicateValues" dxfId="1425" priority="2110"/>
+    <cfRule type="duplicateValues" dxfId="1420" priority="2110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B410">
-    <cfRule type="duplicateValues" dxfId="1424" priority="2109"/>
+    <cfRule type="duplicateValues" dxfId="1419" priority="2109"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B410">
-    <cfRule type="duplicateValues" dxfId="1423" priority="2108"/>
+    <cfRule type="duplicateValues" dxfId="1418" priority="2108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B411">
-    <cfRule type="duplicateValues" dxfId="1422" priority="2107"/>
+    <cfRule type="duplicateValues" dxfId="1417" priority="2107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B411">
-    <cfRule type="duplicateValues" dxfId="1421" priority="2106"/>
+    <cfRule type="duplicateValues" dxfId="1416" priority="2106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B412">
-    <cfRule type="duplicateValues" dxfId="1420" priority="2103"/>
+    <cfRule type="duplicateValues" dxfId="1415" priority="2103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B412">
-    <cfRule type="duplicateValues" dxfId="1419" priority="2102"/>
+    <cfRule type="duplicateValues" dxfId="1414" priority="2102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B413">
-    <cfRule type="duplicateValues" dxfId="1418" priority="2099"/>
+    <cfRule type="duplicateValues" dxfId="1413" priority="2099"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B413">
-    <cfRule type="duplicateValues" dxfId="1417" priority="2098"/>
+    <cfRule type="duplicateValues" dxfId="1412" priority="2098"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B414">
-    <cfRule type="duplicateValues" dxfId="1416" priority="2097"/>
+    <cfRule type="duplicateValues" dxfId="1411" priority="2097"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B414">
-    <cfRule type="duplicateValues" dxfId="1415" priority="2096"/>
+    <cfRule type="duplicateValues" dxfId="1410" priority="2096"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B416">
-    <cfRule type="duplicateValues" dxfId="1414" priority="2087"/>
+    <cfRule type="duplicateValues" dxfId="1409" priority="2087"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B416">
-    <cfRule type="duplicateValues" dxfId="1413" priority="2086"/>
+    <cfRule type="duplicateValues" dxfId="1408" priority="2086"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B417">
-    <cfRule type="duplicateValues" dxfId="1412" priority="2085"/>
+    <cfRule type="duplicateValues" dxfId="1407" priority="2085"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B417">
-    <cfRule type="duplicateValues" dxfId="1411" priority="2084"/>
+    <cfRule type="duplicateValues" dxfId="1406" priority="2084"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B422">
-    <cfRule type="duplicateValues" dxfId="1410" priority="2081"/>
+    <cfRule type="duplicateValues" dxfId="1405" priority="2081"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B422">
-    <cfRule type="duplicateValues" dxfId="1409" priority="2080"/>
+    <cfRule type="duplicateValues" dxfId="1404" priority="2080"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B421">
-    <cfRule type="duplicateValues" dxfId="1408" priority="2079"/>
+    <cfRule type="duplicateValues" dxfId="1403" priority="2079"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B421">
-    <cfRule type="duplicateValues" dxfId="1407" priority="2078"/>
+    <cfRule type="duplicateValues" dxfId="1402" priority="2078"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B423">
-    <cfRule type="duplicateValues" dxfId="1406" priority="2075"/>
+    <cfRule type="duplicateValues" dxfId="1401" priority="2075"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B423">
-    <cfRule type="duplicateValues" dxfId="1405" priority="2074"/>
+    <cfRule type="duplicateValues" dxfId="1400" priority="2074"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B424">
-    <cfRule type="duplicateValues" dxfId="1404" priority="2073"/>
+    <cfRule type="duplicateValues" dxfId="1399" priority="2073"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B424">
-    <cfRule type="duplicateValues" dxfId="1403" priority="2072"/>
+    <cfRule type="duplicateValues" dxfId="1398" priority="2072"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B425">
-    <cfRule type="duplicateValues" dxfId="1402" priority="2071"/>
+    <cfRule type="duplicateValues" dxfId="1397" priority="2071"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B425">
-    <cfRule type="duplicateValues" dxfId="1401" priority="2070"/>
+    <cfRule type="duplicateValues" dxfId="1396" priority="2070"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B426">
-    <cfRule type="duplicateValues" dxfId="1400" priority="2069"/>
+    <cfRule type="duplicateValues" dxfId="1395" priority="2069"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B426">
-    <cfRule type="duplicateValues" dxfId="1399" priority="2068"/>
+    <cfRule type="duplicateValues" dxfId="1394" priority="2068"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B427">
-    <cfRule type="duplicateValues" dxfId="1398" priority="2067"/>
+    <cfRule type="duplicateValues" dxfId="1393" priority="2067"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B427">
-    <cfRule type="duplicateValues" dxfId="1397" priority="2066"/>
+    <cfRule type="duplicateValues" dxfId="1392" priority="2066"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B428">
-    <cfRule type="duplicateValues" dxfId="1396" priority="2065"/>
+    <cfRule type="duplicateValues" dxfId="1391" priority="2065"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B428">
-    <cfRule type="duplicateValues" dxfId="1395" priority="2064"/>
+    <cfRule type="duplicateValues" dxfId="1390" priority="2064"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B429">
-    <cfRule type="duplicateValues" dxfId="1394" priority="2063"/>
+    <cfRule type="duplicateValues" dxfId="1389" priority="2063"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B429">
-    <cfRule type="duplicateValues" dxfId="1393" priority="2062"/>
+    <cfRule type="duplicateValues" dxfId="1388" priority="2062"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B432">
-    <cfRule type="duplicateValues" dxfId="1392" priority="2059"/>
+    <cfRule type="duplicateValues" dxfId="1387" priority="2059"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B432">
-    <cfRule type="duplicateValues" dxfId="1391" priority="2058"/>
+    <cfRule type="duplicateValues" dxfId="1386" priority="2058"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B431">
-    <cfRule type="duplicateValues" dxfId="1390" priority="2057"/>
+    <cfRule type="duplicateValues" dxfId="1385" priority="2057"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B431">
-    <cfRule type="duplicateValues" dxfId="1389" priority="2056"/>
+    <cfRule type="duplicateValues" dxfId="1384" priority="2056"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B434">
-    <cfRule type="duplicateValues" dxfId="1388" priority="2055"/>
+    <cfRule type="duplicateValues" dxfId="1383" priority="2055"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B434">
-    <cfRule type="duplicateValues" dxfId="1387" priority="2054"/>
+    <cfRule type="duplicateValues" dxfId="1382" priority="2054"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B435">
-    <cfRule type="duplicateValues" dxfId="1386" priority="2051"/>
+    <cfRule type="duplicateValues" dxfId="1381" priority="2051"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B435">
-    <cfRule type="duplicateValues" dxfId="1385" priority="2050"/>
+    <cfRule type="duplicateValues" dxfId="1380" priority="2050"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B437">
-    <cfRule type="duplicateValues" dxfId="1384" priority="2047"/>
+    <cfRule type="duplicateValues" dxfId="1379" priority="2047"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B437">
-    <cfRule type="duplicateValues" dxfId="1383" priority="2046"/>
+    <cfRule type="duplicateValues" dxfId="1378" priority="2046"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B436">
-    <cfRule type="duplicateValues" dxfId="1382" priority="2045"/>
+    <cfRule type="duplicateValues" dxfId="1377" priority="2045"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B436">
-    <cfRule type="duplicateValues" dxfId="1381" priority="2044"/>
+    <cfRule type="duplicateValues" dxfId="1376" priority="2044"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B440">
-    <cfRule type="duplicateValues" dxfId="1380" priority="2043"/>
+    <cfRule type="duplicateValues" dxfId="1375" priority="2043"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B440">
-    <cfRule type="duplicateValues" dxfId="1379" priority="2042"/>
+    <cfRule type="duplicateValues" dxfId="1374" priority="2042"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B443">
-    <cfRule type="duplicateValues" dxfId="1378" priority="2039"/>
+    <cfRule type="duplicateValues" dxfId="1373" priority="2039"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B443">
-    <cfRule type="duplicateValues" dxfId="1377" priority="2038"/>
+    <cfRule type="duplicateValues" dxfId="1372" priority="2038"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B445">
-    <cfRule type="duplicateValues" dxfId="1376" priority="2037"/>
+    <cfRule type="duplicateValues" dxfId="1371" priority="2037"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B445">
-    <cfRule type="duplicateValues" dxfId="1375" priority="2036"/>
+    <cfRule type="duplicateValues" dxfId="1370" priority="2036"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B446">
-    <cfRule type="duplicateValues" dxfId="1374" priority="2033"/>
+    <cfRule type="duplicateValues" dxfId="1369" priority="2033"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B446">
-    <cfRule type="duplicateValues" dxfId="1373" priority="2032"/>
+    <cfRule type="duplicateValues" dxfId="1368" priority="2032"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B447">
-    <cfRule type="duplicateValues" dxfId="1372" priority="2031"/>
+    <cfRule type="duplicateValues" dxfId="1367" priority="2031"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B447">
-    <cfRule type="duplicateValues" dxfId="1371" priority="2030"/>
+    <cfRule type="duplicateValues" dxfId="1366" priority="2030"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B449">
-    <cfRule type="duplicateValues" dxfId="1370" priority="2029"/>
+    <cfRule type="duplicateValues" dxfId="1365" priority="2029"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B449">
-    <cfRule type="duplicateValues" dxfId="1369" priority="2028"/>
+    <cfRule type="duplicateValues" dxfId="1364" priority="2028"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B450">
-    <cfRule type="duplicateValues" dxfId="1368" priority="2027"/>
+    <cfRule type="duplicateValues" dxfId="1363" priority="2027"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B450">
-    <cfRule type="duplicateValues" dxfId="1367" priority="2026"/>
+    <cfRule type="duplicateValues" dxfId="1362" priority="2026"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B452">
-    <cfRule type="duplicateValues" dxfId="1366" priority="2025"/>
+    <cfRule type="duplicateValues" dxfId="1361" priority="2025"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B452">
-    <cfRule type="duplicateValues" dxfId="1365" priority="2024"/>
+    <cfRule type="duplicateValues" dxfId="1360" priority="2024"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B453">
-    <cfRule type="duplicateValues" dxfId="1364" priority="2021"/>
+    <cfRule type="duplicateValues" dxfId="1359" priority="2021"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B453">
-    <cfRule type="duplicateValues" dxfId="1363" priority="2020"/>
+    <cfRule type="duplicateValues" dxfId="1358" priority="2020"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B454">
-    <cfRule type="duplicateValues" dxfId="1362" priority="2015"/>
+    <cfRule type="duplicateValues" dxfId="1357" priority="2015"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B454">
-    <cfRule type="duplicateValues" dxfId="1361" priority="2014"/>
+    <cfRule type="duplicateValues" dxfId="1356" priority="2014"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B455">
-    <cfRule type="duplicateValues" dxfId="1360" priority="2013"/>
+    <cfRule type="duplicateValues" dxfId="1355" priority="2013"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B455">
-    <cfRule type="duplicateValues" dxfId="1359" priority="2012"/>
+    <cfRule type="duplicateValues" dxfId="1354" priority="2012"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B457">
-    <cfRule type="duplicateValues" dxfId="1358" priority="2009"/>
+    <cfRule type="duplicateValues" dxfId="1353" priority="2009"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B457">
-    <cfRule type="duplicateValues" dxfId="1357" priority="2008"/>
+    <cfRule type="duplicateValues" dxfId="1352" priority="2008"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B458">
-    <cfRule type="duplicateValues" dxfId="1356" priority="2007"/>
+    <cfRule type="duplicateValues" dxfId="1351" priority="2007"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B458">
-    <cfRule type="duplicateValues" dxfId="1355" priority="2006"/>
+    <cfRule type="duplicateValues" dxfId="1350" priority="2006"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B460">
-    <cfRule type="duplicateValues" dxfId="1354" priority="2005"/>
+    <cfRule type="duplicateValues" dxfId="1349" priority="2005"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B460">
-    <cfRule type="duplicateValues" dxfId="1353" priority="2004"/>
+    <cfRule type="duplicateValues" dxfId="1348" priority="2004"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B461">
-    <cfRule type="duplicateValues" dxfId="1352" priority="2003"/>
+    <cfRule type="duplicateValues" dxfId="1347" priority="2003"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B461">
-    <cfRule type="duplicateValues" dxfId="1351" priority="2002"/>
+    <cfRule type="duplicateValues" dxfId="1346" priority="2002"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B462">
-    <cfRule type="duplicateValues" dxfId="1350" priority="1999"/>
+    <cfRule type="duplicateValues" dxfId="1345" priority="1999"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B462">
-    <cfRule type="duplicateValues" dxfId="1349" priority="1998"/>
+    <cfRule type="duplicateValues" dxfId="1344" priority="1998"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B465">
-    <cfRule type="duplicateValues" dxfId="1348" priority="1995"/>
+    <cfRule type="duplicateValues" dxfId="1343" priority="1995"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B465">
-    <cfRule type="duplicateValues" dxfId="1347" priority="1994"/>
+    <cfRule type="duplicateValues" dxfId="1342" priority="1994"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B469">
-    <cfRule type="duplicateValues" dxfId="1346" priority="1993"/>
+    <cfRule type="duplicateValues" dxfId="1341" priority="1993"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B469">
-    <cfRule type="duplicateValues" dxfId="1345" priority="1992"/>
+    <cfRule type="duplicateValues" dxfId="1340" priority="1992"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B470">
-    <cfRule type="duplicateValues" dxfId="1344" priority="1991"/>
+    <cfRule type="duplicateValues" dxfId="1339" priority="1991"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B470">
-    <cfRule type="duplicateValues" dxfId="1343" priority="1990"/>
+    <cfRule type="duplicateValues" dxfId="1338" priority="1990"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B473">
-    <cfRule type="duplicateValues" dxfId="1342" priority="1987"/>
+    <cfRule type="duplicateValues" dxfId="1337" priority="1987"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B473">
-    <cfRule type="duplicateValues" dxfId="1341" priority="1986"/>
+    <cfRule type="duplicateValues" dxfId="1336" priority="1986"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B474">
-    <cfRule type="duplicateValues" dxfId="1340" priority="1985"/>
+    <cfRule type="duplicateValues" dxfId="1335" priority="1985"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B474">
-    <cfRule type="duplicateValues" dxfId="1339" priority="1984"/>
+    <cfRule type="duplicateValues" dxfId="1334" priority="1984"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B478">
-    <cfRule type="duplicateValues" dxfId="1338" priority="1979"/>
+    <cfRule type="duplicateValues" dxfId="1333" priority="1979"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B478">
-    <cfRule type="duplicateValues" dxfId="1337" priority="1978"/>
+    <cfRule type="duplicateValues" dxfId="1332" priority="1978"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B479">
-    <cfRule type="duplicateValues" dxfId="1336" priority="1975"/>
+    <cfRule type="duplicateValues" dxfId="1331" priority="1975"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B479">
-    <cfRule type="duplicateValues" dxfId="1335" priority="1974"/>
+    <cfRule type="duplicateValues" dxfId="1330" priority="1974"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B481">
-    <cfRule type="duplicateValues" dxfId="1334" priority="1967"/>
+    <cfRule type="duplicateValues" dxfId="1329" priority="1967"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B481">
-    <cfRule type="duplicateValues" dxfId="1333" priority="1966"/>
+    <cfRule type="duplicateValues" dxfId="1328" priority="1966"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B482">
-    <cfRule type="duplicateValues" dxfId="1332" priority="1965"/>
+    <cfRule type="duplicateValues" dxfId="1327" priority="1965"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B482">
-    <cfRule type="duplicateValues" dxfId="1331" priority="1964"/>
+    <cfRule type="duplicateValues" dxfId="1326" priority="1964"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B484">
-    <cfRule type="duplicateValues" dxfId="1330" priority="1963"/>
+    <cfRule type="duplicateValues" dxfId="1325" priority="1963"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B484">
-    <cfRule type="duplicateValues" dxfId="1329" priority="1962"/>
+    <cfRule type="duplicateValues" dxfId="1324" priority="1962"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B486">
-    <cfRule type="duplicateValues" dxfId="1328" priority="1953"/>
+    <cfRule type="duplicateValues" dxfId="1323" priority="1953"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B486">
-    <cfRule type="duplicateValues" dxfId="1327" priority="1952"/>
+    <cfRule type="duplicateValues" dxfId="1322" priority="1952"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B489">
-    <cfRule type="duplicateValues" dxfId="1326" priority="1949"/>
+    <cfRule type="duplicateValues" dxfId="1321" priority="1949"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B489">
-    <cfRule type="duplicateValues" dxfId="1325" priority="1948"/>
+    <cfRule type="duplicateValues" dxfId="1320" priority="1948"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B490">
-    <cfRule type="duplicateValues" dxfId="1324" priority="1947"/>
+    <cfRule type="duplicateValues" dxfId="1319" priority="1947"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B490">
-    <cfRule type="duplicateValues" dxfId="1323" priority="1946"/>
+    <cfRule type="duplicateValues" dxfId="1318" priority="1946"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B496">
-    <cfRule type="duplicateValues" dxfId="1322" priority="1931"/>
+    <cfRule type="duplicateValues" dxfId="1317" priority="1931"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B496">
-    <cfRule type="duplicateValues" dxfId="1321" priority="1930"/>
+    <cfRule type="duplicateValues" dxfId="1316" priority="1930"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B497">
-    <cfRule type="duplicateValues" dxfId="1320" priority="1929"/>
+    <cfRule type="duplicateValues" dxfId="1315" priority="1929"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B497">
-    <cfRule type="duplicateValues" dxfId="1319" priority="1928"/>
+    <cfRule type="duplicateValues" dxfId="1314" priority="1928"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B498">
-    <cfRule type="duplicateValues" dxfId="1318" priority="1925"/>
+    <cfRule type="duplicateValues" dxfId="1313" priority="1925"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B498">
-    <cfRule type="duplicateValues" dxfId="1317" priority="1924"/>
+    <cfRule type="duplicateValues" dxfId="1312" priority="1924"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B501">
-    <cfRule type="duplicateValues" dxfId="1316" priority="1919"/>
+    <cfRule type="duplicateValues" dxfId="1311" priority="1919"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B501">
-    <cfRule type="duplicateValues" dxfId="1315" priority="1918"/>
+    <cfRule type="duplicateValues" dxfId="1310" priority="1918"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B502">
-    <cfRule type="duplicateValues" dxfId="1314" priority="1917"/>
+    <cfRule type="duplicateValues" dxfId="1309" priority="1917"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B502:B503">
-    <cfRule type="duplicateValues" dxfId="1313" priority="1916"/>
+    <cfRule type="duplicateValues" dxfId="1308" priority="1916"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B503">
-    <cfRule type="duplicateValues" dxfId="1312" priority="1915"/>
+    <cfRule type="duplicateValues" dxfId="1307" priority="1915"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B503">
-    <cfRule type="duplicateValues" dxfId="1311" priority="1914"/>
+    <cfRule type="duplicateValues" dxfId="1306" priority="1914"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B504">
-    <cfRule type="duplicateValues" dxfId="1310" priority="1913"/>
+    <cfRule type="duplicateValues" dxfId="1305" priority="1913"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B504">
-    <cfRule type="duplicateValues" dxfId="1309" priority="1912"/>
+    <cfRule type="duplicateValues" dxfId="1304" priority="1912"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B508">
-    <cfRule type="duplicateValues" dxfId="1308" priority="1903"/>
+    <cfRule type="duplicateValues" dxfId="1303" priority="1903"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B508">
-    <cfRule type="duplicateValues" dxfId="1307" priority="1902"/>
+    <cfRule type="duplicateValues" dxfId="1302" priority="1902"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B509">
-    <cfRule type="duplicateValues" dxfId="1306" priority="1901"/>
+    <cfRule type="duplicateValues" dxfId="1301" priority="1901"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B509">
-    <cfRule type="duplicateValues" dxfId="1305" priority="1900"/>
+    <cfRule type="duplicateValues" dxfId="1300" priority="1900"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B510">
-    <cfRule type="duplicateValues" dxfId="1304" priority="1899"/>
+    <cfRule type="duplicateValues" dxfId="1299" priority="1899"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B510">
-    <cfRule type="duplicateValues" dxfId="1303" priority="1898"/>
+    <cfRule type="duplicateValues" dxfId="1298" priority="1898"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B512">
-    <cfRule type="duplicateValues" dxfId="1302" priority="1895"/>
+    <cfRule type="duplicateValues" dxfId="1297" priority="1895"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B512">
-    <cfRule type="duplicateValues" dxfId="1301" priority="1894"/>
+    <cfRule type="duplicateValues" dxfId="1296" priority="1894"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B513">
-    <cfRule type="duplicateValues" dxfId="1300" priority="1893"/>
+    <cfRule type="duplicateValues" dxfId="1295" priority="1893"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B513">
-    <cfRule type="duplicateValues" dxfId="1299" priority="1892"/>
+    <cfRule type="duplicateValues" dxfId="1294" priority="1892"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B515">
-    <cfRule type="duplicateValues" dxfId="1298" priority="1891"/>
+    <cfRule type="duplicateValues" dxfId="1293" priority="1891"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B515">
-    <cfRule type="duplicateValues" dxfId="1297" priority="1890"/>
+    <cfRule type="duplicateValues" dxfId="1292" priority="1890"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B516">
-    <cfRule type="duplicateValues" dxfId="1296" priority="1883"/>
+    <cfRule type="duplicateValues" dxfId="1291" priority="1883"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B516">
-    <cfRule type="duplicateValues" dxfId="1295" priority="1882"/>
+    <cfRule type="duplicateValues" dxfId="1290" priority="1882"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B517">
-    <cfRule type="duplicateValues" dxfId="1294" priority="1879"/>
+    <cfRule type="duplicateValues" dxfId="1289" priority="1879"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B517">
-    <cfRule type="duplicateValues" dxfId="1293" priority="1878"/>
+    <cfRule type="duplicateValues" dxfId="1288" priority="1878"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B518">
-    <cfRule type="duplicateValues" dxfId="1292" priority="1875"/>
+    <cfRule type="duplicateValues" dxfId="1287" priority="1875"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B518">
-    <cfRule type="duplicateValues" dxfId="1291" priority="1874"/>
+    <cfRule type="duplicateValues" dxfId="1286" priority="1874"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B522">
-    <cfRule type="duplicateValues" dxfId="1290" priority="1871"/>
+    <cfRule type="duplicateValues" dxfId="1285" priority="1871"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B522">
-    <cfRule type="duplicateValues" dxfId="1289" priority="1870"/>
+    <cfRule type="duplicateValues" dxfId="1284" priority="1870"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B520">
-    <cfRule type="duplicateValues" dxfId="1288" priority="1869"/>
+    <cfRule type="duplicateValues" dxfId="1283" priority="1869"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B520">
-    <cfRule type="duplicateValues" dxfId="1287" priority="1868"/>
+    <cfRule type="duplicateValues" dxfId="1282" priority="1868"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B521">
-    <cfRule type="duplicateValues" dxfId="1286" priority="1865"/>
+    <cfRule type="duplicateValues" dxfId="1281" priority="1865"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B521">
-    <cfRule type="duplicateValues" dxfId="1285" priority="1864"/>
+    <cfRule type="duplicateValues" dxfId="1280" priority="1864"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B523">
-    <cfRule type="duplicateValues" dxfId="1284" priority="1859"/>
+    <cfRule type="duplicateValues" dxfId="1279" priority="1859"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B523">
-    <cfRule type="duplicateValues" dxfId="1283" priority="1858"/>
+    <cfRule type="duplicateValues" dxfId="1278" priority="1858"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B527">
-    <cfRule type="duplicateValues" dxfId="1282" priority="1853"/>
+    <cfRule type="duplicateValues" dxfId="1277" priority="1853"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B527">
-    <cfRule type="duplicateValues" dxfId="1281" priority="1852"/>
+    <cfRule type="duplicateValues" dxfId="1276" priority="1852"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B526">
-    <cfRule type="duplicateValues" dxfId="1280" priority="1851"/>
+    <cfRule type="duplicateValues" dxfId="1275" priority="1851"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B526">
-    <cfRule type="duplicateValues" dxfId="1279" priority="1850"/>
+    <cfRule type="duplicateValues" dxfId="1274" priority="1850"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B525">
-    <cfRule type="duplicateValues" dxfId="1278" priority="1849"/>
+    <cfRule type="duplicateValues" dxfId="1273" priority="1849"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B525">
-    <cfRule type="duplicateValues" dxfId="1277" priority="1848"/>
+    <cfRule type="duplicateValues" dxfId="1272" priority="1848"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B530">
-    <cfRule type="duplicateValues" dxfId="1276" priority="1847"/>
+    <cfRule type="duplicateValues" dxfId="1271" priority="1847"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B530">
-    <cfRule type="duplicateValues" dxfId="1275" priority="1846"/>
+    <cfRule type="duplicateValues" dxfId="1270" priority="1846"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B536">
-    <cfRule type="duplicateValues" dxfId="1274" priority="1845"/>
+    <cfRule type="duplicateValues" dxfId="1269" priority="1845"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B536">
-    <cfRule type="duplicateValues" dxfId="1273" priority="1844"/>
+    <cfRule type="duplicateValues" dxfId="1268" priority="1844"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B538">
-    <cfRule type="duplicateValues" dxfId="1272" priority="1843"/>
+    <cfRule type="duplicateValues" dxfId="1267" priority="1843"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B538">
-    <cfRule type="duplicateValues" dxfId="1271" priority="1842"/>
+    <cfRule type="duplicateValues" dxfId="1266" priority="1842"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B540">
-    <cfRule type="duplicateValues" dxfId="1270" priority="1839"/>
+    <cfRule type="duplicateValues" dxfId="1265" priority="1839"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B540">
-    <cfRule type="duplicateValues" dxfId="1269" priority="1838"/>
+    <cfRule type="duplicateValues" dxfId="1264" priority="1838"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B543">
-    <cfRule type="duplicateValues" dxfId="1268" priority="1835"/>
+    <cfRule type="duplicateValues" dxfId="1263" priority="1835"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B543">
-    <cfRule type="duplicateValues" dxfId="1267" priority="1834"/>
+    <cfRule type="duplicateValues" dxfId="1262" priority="1834"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B541">
-    <cfRule type="duplicateValues" dxfId="1266" priority="1833"/>
+    <cfRule type="duplicateValues" dxfId="1261" priority="1833"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B541">
-    <cfRule type="duplicateValues" dxfId="1265" priority="1832"/>
+    <cfRule type="duplicateValues" dxfId="1260" priority="1832"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B542">
-    <cfRule type="duplicateValues" dxfId="1264" priority="1827"/>
+    <cfRule type="duplicateValues" dxfId="1259" priority="1827"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B542">
-    <cfRule type="duplicateValues" dxfId="1263" priority="1826"/>
+    <cfRule type="duplicateValues" dxfId="1258" priority="1826"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B544">
-    <cfRule type="duplicateValues" dxfId="1262" priority="1823"/>
+    <cfRule type="duplicateValues" dxfId="1257" priority="1823"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B544">
-    <cfRule type="duplicateValues" dxfId="1261" priority="1822"/>
+    <cfRule type="duplicateValues" dxfId="1256" priority="1822"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B545">
-    <cfRule type="duplicateValues" dxfId="1260" priority="1819"/>
+    <cfRule type="duplicateValues" dxfId="1255" priority="1819"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B545">
-    <cfRule type="duplicateValues" dxfId="1259" priority="1818"/>
+    <cfRule type="duplicateValues" dxfId="1254" priority="1818"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B546">
-    <cfRule type="duplicateValues" dxfId="1258" priority="1817"/>
+    <cfRule type="duplicateValues" dxfId="1253" priority="1817"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B546">
-    <cfRule type="duplicateValues" dxfId="1257" priority="1816"/>
+    <cfRule type="duplicateValues" dxfId="1252" priority="1816"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B547">
-    <cfRule type="duplicateValues" dxfId="1256" priority="1813"/>
+    <cfRule type="duplicateValues" dxfId="1251" priority="1813"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B547">
-    <cfRule type="duplicateValues" dxfId="1255" priority="1812"/>
+    <cfRule type="duplicateValues" dxfId="1250" priority="1812"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B549">
-    <cfRule type="duplicateValues" dxfId="1254" priority="1811"/>
+    <cfRule type="duplicateValues" dxfId="1249" priority="1811"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B549">
-    <cfRule type="duplicateValues" dxfId="1253" priority="1810"/>
+    <cfRule type="duplicateValues" dxfId="1248" priority="1810"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B551">
-    <cfRule type="duplicateValues" dxfId="1252" priority="1807"/>
+    <cfRule type="duplicateValues" dxfId="1247" priority="1807"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B551">
-    <cfRule type="duplicateValues" dxfId="1251" priority="1806"/>
+    <cfRule type="duplicateValues" dxfId="1246" priority="1806"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B552">
-    <cfRule type="duplicateValues" dxfId="1250" priority="1805"/>
+    <cfRule type="duplicateValues" dxfId="1245" priority="1805"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B552">
-    <cfRule type="duplicateValues" dxfId="1249" priority="1804"/>
+    <cfRule type="duplicateValues" dxfId="1244" priority="1804"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B553">
-    <cfRule type="duplicateValues" dxfId="1248" priority="1799"/>
+    <cfRule type="duplicateValues" dxfId="1243" priority="1799"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B553">
-    <cfRule type="duplicateValues" dxfId="1247" priority="1798"/>
+    <cfRule type="duplicateValues" dxfId="1242" priority="1798"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B554">
-    <cfRule type="duplicateValues" dxfId="1246" priority="1797"/>
+    <cfRule type="duplicateValues" dxfId="1241" priority="1797"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B554">
-    <cfRule type="duplicateValues" dxfId="1245" priority="1796"/>
+    <cfRule type="duplicateValues" dxfId="1240" priority="1796"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B555">
-    <cfRule type="duplicateValues" dxfId="1244" priority="1791"/>
+    <cfRule type="duplicateValues" dxfId="1239" priority="1791"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B555">
-    <cfRule type="duplicateValues" dxfId="1243" priority="1790"/>
+    <cfRule type="duplicateValues" dxfId="1238" priority="1790"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B556">
-    <cfRule type="duplicateValues" dxfId="1242" priority="1789"/>
+    <cfRule type="duplicateValues" dxfId="1237" priority="1789"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B556">
-    <cfRule type="duplicateValues" dxfId="1241" priority="1788"/>
+    <cfRule type="duplicateValues" dxfId="1236" priority="1788"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B557">
-    <cfRule type="duplicateValues" dxfId="1240" priority="1785"/>
+    <cfRule type="duplicateValues" dxfId="1235" priority="1785"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B557">
-    <cfRule type="duplicateValues" dxfId="1239" priority="1784"/>
+    <cfRule type="duplicateValues" dxfId="1234" priority="1784"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B558">
-    <cfRule type="duplicateValues" dxfId="1238" priority="1783"/>
+    <cfRule type="duplicateValues" dxfId="1233" priority="1783"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B558">
-    <cfRule type="duplicateValues" dxfId="1237" priority="1782"/>
+    <cfRule type="duplicateValues" dxfId="1232" priority="1782"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B562">
-    <cfRule type="duplicateValues" dxfId="1236" priority="1773"/>
+    <cfRule type="duplicateValues" dxfId="1231" priority="1773"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B562">
-    <cfRule type="duplicateValues" dxfId="1235" priority="1772"/>
+    <cfRule type="duplicateValues" dxfId="1230" priority="1772"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B564">
-    <cfRule type="duplicateValues" dxfId="1234" priority="1771"/>
+    <cfRule type="duplicateValues" dxfId="1229" priority="1771"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B564">
-    <cfRule type="duplicateValues" dxfId="1233" priority="1770"/>
+    <cfRule type="duplicateValues" dxfId="1228" priority="1770"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B563">
-    <cfRule type="duplicateValues" dxfId="1232" priority="1769"/>
+    <cfRule type="duplicateValues" dxfId="1227" priority="1769"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B563">
-    <cfRule type="duplicateValues" dxfId="1231" priority="1768"/>
+    <cfRule type="duplicateValues" dxfId="1226" priority="1768"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B565">
-    <cfRule type="duplicateValues" dxfId="1230" priority="1767"/>
+    <cfRule type="duplicateValues" dxfId="1225" priority="1767"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B565">
-    <cfRule type="duplicateValues" dxfId="1229" priority="1766"/>
+    <cfRule type="duplicateValues" dxfId="1224" priority="1766"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B566">
-    <cfRule type="duplicateValues" dxfId="1228" priority="1759"/>
+    <cfRule type="duplicateValues" dxfId="1223" priority="1759"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B566">
-    <cfRule type="duplicateValues" dxfId="1227" priority="1758"/>
+    <cfRule type="duplicateValues" dxfId="1222" priority="1758"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B569">
-    <cfRule type="duplicateValues" dxfId="1226" priority="1757"/>
+    <cfRule type="duplicateValues" dxfId="1221" priority="1757"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B569">
-    <cfRule type="duplicateValues" dxfId="1225" priority="1756"/>
+    <cfRule type="duplicateValues" dxfId="1220" priority="1756"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B567">
-    <cfRule type="duplicateValues" dxfId="1224" priority="1753"/>
+    <cfRule type="duplicateValues" dxfId="1219" priority="1753"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B567">
-    <cfRule type="duplicateValues" dxfId="1223" priority="1752"/>
+    <cfRule type="duplicateValues" dxfId="1218" priority="1752"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B568">
-    <cfRule type="duplicateValues" dxfId="1222" priority="1749"/>
+    <cfRule type="duplicateValues" dxfId="1217" priority="1749"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B568">
-    <cfRule type="duplicateValues" dxfId="1221" priority="1748"/>
+    <cfRule type="duplicateValues" dxfId="1216" priority="1748"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B571">
-    <cfRule type="duplicateValues" dxfId="1220" priority="1739"/>
+    <cfRule type="duplicateValues" dxfId="1215" priority="1739"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B572">
-    <cfRule type="duplicateValues" dxfId="1219" priority="1736"/>
+    <cfRule type="duplicateValues" dxfId="1214" priority="1736"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B572">
-    <cfRule type="duplicateValues" dxfId="1218" priority="1735"/>
+    <cfRule type="duplicateValues" dxfId="1213" priority="1735"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B575">
-    <cfRule type="duplicateValues" dxfId="1217" priority="1733"/>
+    <cfRule type="duplicateValues" dxfId="1212" priority="1733"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B575">
-    <cfRule type="duplicateValues" dxfId="1216" priority="1734"/>
+    <cfRule type="duplicateValues" dxfId="1211" priority="1734"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B577">
-    <cfRule type="duplicateValues" dxfId="1215" priority="1732"/>
+    <cfRule type="duplicateValues" dxfId="1210" priority="1732"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B577">
-    <cfRule type="duplicateValues" dxfId="1214" priority="1731"/>
+    <cfRule type="duplicateValues" dxfId="1209" priority="1731"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B578">
-    <cfRule type="duplicateValues" dxfId="1213" priority="1721"/>
+    <cfRule type="duplicateValues" dxfId="1208" priority="1721"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B578">
-    <cfRule type="duplicateValues" dxfId="1212" priority="1722"/>
+    <cfRule type="duplicateValues" dxfId="1207" priority="1722"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B579">
-    <cfRule type="duplicateValues" dxfId="1211" priority="1718"/>
+    <cfRule type="duplicateValues" dxfId="1206" priority="1718"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B580">
-    <cfRule type="duplicateValues" dxfId="1210" priority="1715"/>
+    <cfRule type="duplicateValues" dxfId="1205" priority="1715"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B581">
-    <cfRule type="duplicateValues" dxfId="1209" priority="1712"/>
+    <cfRule type="duplicateValues" dxfId="1204" priority="1712"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B581">
-    <cfRule type="duplicateValues" dxfId="1208" priority="1711"/>
+    <cfRule type="duplicateValues" dxfId="1203" priority="1711"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B582">
-    <cfRule type="duplicateValues" dxfId="1207" priority="1710"/>
+    <cfRule type="duplicateValues" dxfId="1202" priority="1710"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B582">
-    <cfRule type="duplicateValues" dxfId="1206" priority="1709"/>
+    <cfRule type="duplicateValues" dxfId="1201" priority="1709"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B583">
-    <cfRule type="duplicateValues" dxfId="1205" priority="1708"/>
+    <cfRule type="duplicateValues" dxfId="1200" priority="1708"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B583">
-    <cfRule type="duplicateValues" dxfId="1204" priority="1707"/>
+    <cfRule type="duplicateValues" dxfId="1199" priority="1707"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B584">
-    <cfRule type="duplicateValues" dxfId="1203" priority="1706"/>
+    <cfRule type="duplicateValues" dxfId="1198" priority="1706"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B584">
-    <cfRule type="duplicateValues" dxfId="1202" priority="1705"/>
+    <cfRule type="duplicateValues" dxfId="1197" priority="1705"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B587">
-    <cfRule type="duplicateValues" dxfId="1201" priority="1703"/>
+    <cfRule type="duplicateValues" dxfId="1196" priority="1703"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B587">
-    <cfRule type="duplicateValues" dxfId="1200" priority="1704"/>
+    <cfRule type="duplicateValues" dxfId="1195" priority="1704"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B586">
-    <cfRule type="duplicateValues" dxfId="1199" priority="1701"/>
+    <cfRule type="duplicateValues" dxfId="1194" priority="1701"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B586">
-    <cfRule type="duplicateValues" dxfId="1198" priority="1702"/>
+    <cfRule type="duplicateValues" dxfId="1193" priority="1702"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B589">
-    <cfRule type="duplicateValues" dxfId="1197" priority="1695"/>
+    <cfRule type="duplicateValues" dxfId="1192" priority="1695"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B589">
-    <cfRule type="duplicateValues" dxfId="1196" priority="1696"/>
+    <cfRule type="duplicateValues" dxfId="1191" priority="1696"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B591">
-    <cfRule type="duplicateValues" dxfId="1195" priority="1691"/>
+    <cfRule type="duplicateValues" dxfId="1190" priority="1691"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B591">
-    <cfRule type="duplicateValues" dxfId="1194" priority="1692"/>
+    <cfRule type="duplicateValues" dxfId="1189" priority="1692"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B592">
-    <cfRule type="duplicateValues" dxfId="1193" priority="1689"/>
+    <cfRule type="duplicateValues" dxfId="1188" priority="1689"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B592">
-    <cfRule type="duplicateValues" dxfId="1192" priority="1690"/>
+    <cfRule type="duplicateValues" dxfId="1187" priority="1690"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B593">
-    <cfRule type="duplicateValues" dxfId="1191" priority="1687"/>
+    <cfRule type="duplicateValues" dxfId="1186" priority="1687"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B593">
-    <cfRule type="duplicateValues" dxfId="1190" priority="1688"/>
+    <cfRule type="duplicateValues" dxfId="1185" priority="1688"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B594">
-    <cfRule type="duplicateValues" dxfId="1189" priority="1683"/>
+    <cfRule type="duplicateValues" dxfId="1184" priority="1683"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B594">
-    <cfRule type="duplicateValues" dxfId="1188" priority="1684"/>
+    <cfRule type="duplicateValues" dxfId="1183" priority="1684"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B595">
-    <cfRule type="duplicateValues" dxfId="1187" priority="1679"/>
+    <cfRule type="duplicateValues" dxfId="1182" priority="1679"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B595">
-    <cfRule type="duplicateValues" dxfId="1186" priority="1680"/>
+    <cfRule type="duplicateValues" dxfId="1181" priority="1680"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B596">
-    <cfRule type="duplicateValues" dxfId="1185" priority="1678"/>
+    <cfRule type="duplicateValues" dxfId="1180" priority="1678"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B601">
-    <cfRule type="duplicateValues" dxfId="1184" priority="1675"/>
+    <cfRule type="duplicateValues" dxfId="1179" priority="1675"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B602">
-    <cfRule type="duplicateValues" dxfId="1183" priority="1673"/>
+    <cfRule type="duplicateValues" dxfId="1178" priority="1673"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B602">
-    <cfRule type="duplicateValues" dxfId="1182" priority="1674"/>
+    <cfRule type="duplicateValues" dxfId="1177" priority="1674"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B603">
-    <cfRule type="duplicateValues" dxfId="1181" priority="1671"/>
+    <cfRule type="duplicateValues" dxfId="1176" priority="1671"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B603">
-    <cfRule type="duplicateValues" dxfId="1180" priority="1672"/>
+    <cfRule type="duplicateValues" dxfId="1175" priority="1672"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B604:B605">
-    <cfRule type="duplicateValues" dxfId="1179" priority="1667"/>
+    <cfRule type="duplicateValues" dxfId="1174" priority="1667"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B604:B605">
-    <cfRule type="duplicateValues" dxfId="1178" priority="1668"/>
+    <cfRule type="duplicateValues" dxfId="1173" priority="1668"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B606:B608">
-    <cfRule type="duplicateValues" dxfId="1177" priority="1665"/>
+    <cfRule type="duplicateValues" dxfId="1172" priority="1665"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B606:B608">
-    <cfRule type="duplicateValues" dxfId="1176" priority="1666"/>
+    <cfRule type="duplicateValues" dxfId="1171" priority="1666"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B609:B610">
-    <cfRule type="duplicateValues" dxfId="1175" priority="1659"/>
+    <cfRule type="duplicateValues" dxfId="1170" priority="1659"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B609:B610">
-    <cfRule type="duplicateValues" dxfId="1174" priority="1660"/>
+    <cfRule type="duplicateValues" dxfId="1169" priority="1660"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B611:B613">
-    <cfRule type="duplicateValues" dxfId="1173" priority="1658"/>
+    <cfRule type="duplicateValues" dxfId="1168" priority="1658"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B611:B613">
-    <cfRule type="duplicateValues" dxfId="1172" priority="1657"/>
+    <cfRule type="duplicateValues" dxfId="1167" priority="1657"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B614:B615">
-    <cfRule type="duplicateValues" dxfId="1171" priority="1655"/>
+    <cfRule type="duplicateValues" dxfId="1166" priority="1655"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B614:B615">
-    <cfRule type="duplicateValues" dxfId="1170" priority="1656"/>
+    <cfRule type="duplicateValues" dxfId="1165" priority="1656"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B616:B618">
-    <cfRule type="duplicateValues" dxfId="1169" priority="1649"/>
+    <cfRule type="duplicateValues" dxfId="1164" priority="1649"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B616:B618">
-    <cfRule type="duplicateValues" dxfId="1168" priority="1650"/>
+    <cfRule type="duplicateValues" dxfId="1163" priority="1650"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B619:B621">
-    <cfRule type="duplicateValues" dxfId="1167" priority="1647"/>
+    <cfRule type="duplicateValues" dxfId="1162" priority="1647"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B619:B621">
-    <cfRule type="duplicateValues" dxfId="1166" priority="1648"/>
+    <cfRule type="duplicateValues" dxfId="1161" priority="1648"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B624:B626">
-    <cfRule type="duplicateValues" dxfId="1165" priority="1645"/>
+    <cfRule type="duplicateValues" dxfId="1160" priority="1645"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B624:B626">
-    <cfRule type="duplicateValues" dxfId="1164" priority="1646"/>
+    <cfRule type="duplicateValues" dxfId="1159" priority="1646"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B627:B628">
-    <cfRule type="duplicateValues" dxfId="1163" priority="1640"/>
+    <cfRule type="duplicateValues" dxfId="1158" priority="1640"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B627:B628">
-    <cfRule type="duplicateValues" dxfId="1162" priority="1639"/>
+    <cfRule type="duplicateValues" dxfId="1157" priority="1639"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B629:B632">
-    <cfRule type="duplicateValues" dxfId="1161" priority="1636"/>
+    <cfRule type="duplicateValues" dxfId="1156" priority="1636"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B629:B632">
-    <cfRule type="duplicateValues" dxfId="1160" priority="1635"/>
+    <cfRule type="duplicateValues" dxfId="1155" priority="1635"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B633:B634">
-    <cfRule type="duplicateValues" dxfId="1159" priority="1632"/>
+    <cfRule type="duplicateValues" dxfId="1154" priority="1632"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B633:B634">
-    <cfRule type="duplicateValues" dxfId="1158" priority="1631"/>
+    <cfRule type="duplicateValues" dxfId="1153" priority="1631"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B635:B636">
-    <cfRule type="duplicateValues" dxfId="1157" priority="1629"/>
+    <cfRule type="duplicateValues" dxfId="1152" priority="1629"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B635:B636">
-    <cfRule type="duplicateValues" dxfId="1156" priority="1630"/>
+    <cfRule type="duplicateValues" dxfId="1151" priority="1630"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B637:B639">
-    <cfRule type="duplicateValues" dxfId="1155" priority="1626"/>
+    <cfRule type="duplicateValues" dxfId="1150" priority="1626"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B640:B642">
-    <cfRule type="duplicateValues" dxfId="1154" priority="1624"/>
+    <cfRule type="duplicateValues" dxfId="1149" priority="1624"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B640:B642">
-    <cfRule type="duplicateValues" dxfId="1153" priority="1625"/>
+    <cfRule type="duplicateValues" dxfId="1148" priority="1625"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B643:B644">
-    <cfRule type="duplicateValues" dxfId="1152" priority="1622"/>
+    <cfRule type="duplicateValues" dxfId="1147" priority="1622"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B643:B644">
-    <cfRule type="duplicateValues" dxfId="1151" priority="1623"/>
+    <cfRule type="duplicateValues" dxfId="1146" priority="1623"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D645:D647">
-    <cfRule type="duplicateValues" dxfId="1150" priority="1620"/>
+    <cfRule type="duplicateValues" dxfId="1145" priority="1620"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D645:D647">
-    <cfRule type="duplicateValues" dxfId="1149" priority="1621"/>
+    <cfRule type="duplicateValues" dxfId="1144" priority="1621"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B645:B647">
-    <cfRule type="duplicateValues" dxfId="1148" priority="1616"/>
+    <cfRule type="duplicateValues" dxfId="1143" priority="1616"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B645:B647">
-    <cfRule type="duplicateValues" dxfId="1147" priority="1617"/>
+    <cfRule type="duplicateValues" dxfId="1142" priority="1617"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B656:B657">
-    <cfRule type="duplicateValues" dxfId="1146" priority="1614"/>
+    <cfRule type="duplicateValues" dxfId="1141" priority="1614"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B656:B657">
-    <cfRule type="duplicateValues" dxfId="1145" priority="1615"/>
+    <cfRule type="duplicateValues" dxfId="1140" priority="1615"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B660:B662">
-    <cfRule type="duplicateValues" dxfId="1144" priority="1612"/>
+    <cfRule type="duplicateValues" dxfId="1139" priority="1612"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B660:B662">
-    <cfRule type="duplicateValues" dxfId="1143" priority="1613"/>
+    <cfRule type="duplicateValues" dxfId="1138" priority="1613"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B658:B659">
-    <cfRule type="duplicateValues" dxfId="1142" priority="1611"/>
+    <cfRule type="duplicateValues" dxfId="1137" priority="1611"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B658:B659">
-    <cfRule type="duplicateValues" dxfId="1141" priority="1610"/>
+    <cfRule type="duplicateValues" dxfId="1136" priority="1610"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B663:B665">
-    <cfRule type="duplicateValues" dxfId="1140" priority="1609"/>
+    <cfRule type="duplicateValues" dxfId="1135" priority="1609"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B663:B665">
-    <cfRule type="duplicateValues" dxfId="1139" priority="1608"/>
+    <cfRule type="duplicateValues" dxfId="1134" priority="1608"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B666:B667">
-    <cfRule type="duplicateValues" dxfId="1138" priority="1605"/>
+    <cfRule type="duplicateValues" dxfId="1133" priority="1605"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B666:B667">
-    <cfRule type="duplicateValues" dxfId="1137" priority="1604"/>
+    <cfRule type="duplicateValues" dxfId="1132" priority="1604"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B670:B672">
-    <cfRule type="duplicateValues" dxfId="1136" priority="1597"/>
+    <cfRule type="duplicateValues" dxfId="1131" priority="1597"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B670:B672">
-    <cfRule type="duplicateValues" dxfId="1135" priority="1596"/>
+    <cfRule type="duplicateValues" dxfId="1130" priority="1596"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677">
-    <cfRule type="duplicateValues" dxfId="1134" priority="1584"/>
+    <cfRule type="duplicateValues" dxfId="1129" priority="1584"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677">
-    <cfRule type="duplicateValues" dxfId="1133" priority="1585"/>
+    <cfRule type="duplicateValues" dxfId="1128" priority="1585"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B678">
-    <cfRule type="duplicateValues" dxfId="1132" priority="1582"/>
+    <cfRule type="duplicateValues" dxfId="1127" priority="1582"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B678">
-    <cfRule type="duplicateValues" dxfId="1131" priority="1583"/>
+    <cfRule type="duplicateValues" dxfId="1126" priority="1583"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B682:B684">
-    <cfRule type="duplicateValues" dxfId="1130" priority="1580"/>
+    <cfRule type="duplicateValues" dxfId="1125" priority="1580"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B682:B684">
-    <cfRule type="duplicateValues" dxfId="1129" priority="1581"/>
+    <cfRule type="duplicateValues" dxfId="1124" priority="1581"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B679:B681">
-    <cfRule type="duplicateValues" dxfId="1128" priority="1578"/>
+    <cfRule type="duplicateValues" dxfId="1123" priority="1578"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B679:B681">
-    <cfRule type="duplicateValues" dxfId="1127" priority="1579"/>
+    <cfRule type="duplicateValues" dxfId="1122" priority="1579"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B685:B686">
-    <cfRule type="duplicateValues" dxfId="1126" priority="1576"/>
+    <cfRule type="duplicateValues" dxfId="1121" priority="1576"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B685:B686">
-    <cfRule type="duplicateValues" dxfId="1125" priority="1577"/>
+    <cfRule type="duplicateValues" dxfId="1120" priority="1577"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B692:B693">
-    <cfRule type="duplicateValues" dxfId="1124" priority="1574"/>
+    <cfRule type="duplicateValues" dxfId="1119" priority="1574"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B692:B693">
-    <cfRule type="duplicateValues" dxfId="1123" priority="1575"/>
+    <cfRule type="duplicateValues" dxfId="1118" priority="1575"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B694">
-    <cfRule type="duplicateValues" dxfId="1122" priority="1570"/>
+    <cfRule type="duplicateValues" dxfId="1117" priority="1570"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B694">
-    <cfRule type="duplicateValues" dxfId="1121" priority="1571"/>
+    <cfRule type="duplicateValues" dxfId="1116" priority="1571"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B695:B697">
-    <cfRule type="duplicateValues" dxfId="1120" priority="1568"/>
+    <cfRule type="duplicateValues" dxfId="1115" priority="1568"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B695:B697">
-    <cfRule type="duplicateValues" dxfId="1119" priority="1569"/>
+    <cfRule type="duplicateValues" dxfId="1114" priority="1569"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B702:B705">
-    <cfRule type="duplicateValues" dxfId="1118" priority="1565"/>
+    <cfRule type="duplicateValues" dxfId="1113" priority="1565"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B702:B705">
-    <cfRule type="duplicateValues" dxfId="1117" priority="1564"/>
+    <cfRule type="duplicateValues" dxfId="1112" priority="1564"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B698:B701">
-    <cfRule type="duplicateValues" dxfId="1116" priority="1562"/>
+    <cfRule type="duplicateValues" dxfId="1111" priority="1562"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B698:B701">
-    <cfRule type="duplicateValues" dxfId="1115" priority="1563"/>
+    <cfRule type="duplicateValues" dxfId="1110" priority="1563"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B709:B710">
-    <cfRule type="duplicateValues" dxfId="1114" priority="1556"/>
+    <cfRule type="duplicateValues" dxfId="1109" priority="1556"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B709:B710">
-    <cfRule type="duplicateValues" dxfId="1113" priority="1557"/>
+    <cfRule type="duplicateValues" dxfId="1108" priority="1557"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B711">
-    <cfRule type="duplicateValues" dxfId="1112" priority="1551"/>
+    <cfRule type="duplicateValues" dxfId="1107" priority="1551"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B711">
-    <cfRule type="duplicateValues" dxfId="1111" priority="1550"/>
+    <cfRule type="duplicateValues" dxfId="1106" priority="1550"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B712:B713">
-    <cfRule type="duplicateValues" dxfId="1110" priority="1546"/>
+    <cfRule type="duplicateValues" dxfId="1105" priority="1546"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B712:B713">
-    <cfRule type="duplicateValues" dxfId="1109" priority="1547"/>
+    <cfRule type="duplicateValues" dxfId="1104" priority="1547"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B714:B715">
-    <cfRule type="duplicateValues" dxfId="1108" priority="1545"/>
+    <cfRule type="duplicateValues" dxfId="1103" priority="1545"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B714:B715">
-    <cfRule type="duplicateValues" dxfId="1107" priority="1544"/>
+    <cfRule type="duplicateValues" dxfId="1102" priority="1544"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B716:B718">
-    <cfRule type="duplicateValues" dxfId="1106" priority="1542"/>
+    <cfRule type="duplicateValues" dxfId="1101" priority="1542"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B716:B718">
-    <cfRule type="duplicateValues" dxfId="1105" priority="1543"/>
+    <cfRule type="duplicateValues" dxfId="1100" priority="1543"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B719:B720">
-    <cfRule type="duplicateValues" dxfId="1104" priority="1540"/>
+    <cfRule type="duplicateValues" dxfId="1099" priority="1540"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B719:B720">
-    <cfRule type="duplicateValues" dxfId="1103" priority="1541"/>
+    <cfRule type="duplicateValues" dxfId="1098" priority="1541"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B721">
-    <cfRule type="duplicateValues" dxfId="1102" priority="1538"/>
+    <cfRule type="duplicateValues" dxfId="1097" priority="1538"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B721">
-    <cfRule type="duplicateValues" dxfId="1101" priority="1539"/>
+    <cfRule type="duplicateValues" dxfId="1096" priority="1539"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B722">
-    <cfRule type="duplicateValues" dxfId="1100" priority="1536"/>
+    <cfRule type="duplicateValues" dxfId="1095" priority="1536"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B722">
-    <cfRule type="duplicateValues" dxfId="1099" priority="1537"/>
+    <cfRule type="duplicateValues" dxfId="1094" priority="1537"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B723">
-    <cfRule type="duplicateValues" dxfId="1098" priority="1530"/>
+    <cfRule type="duplicateValues" dxfId="1093" priority="1530"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B723">
-    <cfRule type="duplicateValues" dxfId="1097" priority="1531"/>
+    <cfRule type="duplicateValues" dxfId="1092" priority="1531"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B725">
-    <cfRule type="duplicateValues" dxfId="1096" priority="1526"/>
+    <cfRule type="duplicateValues" dxfId="1091" priority="1526"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B725">
-    <cfRule type="duplicateValues" dxfId="1095" priority="1527"/>
+    <cfRule type="duplicateValues" dxfId="1090" priority="1527"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B726">
-    <cfRule type="duplicateValues" dxfId="1094" priority="1524"/>
+    <cfRule type="duplicateValues" dxfId="1089" priority="1524"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B726">
-    <cfRule type="duplicateValues" dxfId="1093" priority="1525"/>
+    <cfRule type="duplicateValues" dxfId="1088" priority="1525"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B727">
-    <cfRule type="duplicateValues" dxfId="1092" priority="1522"/>
+    <cfRule type="duplicateValues" dxfId="1087" priority="1522"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B727">
-    <cfRule type="duplicateValues" dxfId="1091" priority="1523"/>
+    <cfRule type="duplicateValues" dxfId="1086" priority="1523"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B728">
-    <cfRule type="duplicateValues" dxfId="1090" priority="1521"/>
+    <cfRule type="duplicateValues" dxfId="1085" priority="1521"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B728">
-    <cfRule type="duplicateValues" dxfId="1089" priority="1520"/>
+    <cfRule type="duplicateValues" dxfId="1084" priority="1520"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B729">
-    <cfRule type="duplicateValues" dxfId="1088" priority="1518"/>
+    <cfRule type="duplicateValues" dxfId="1083" priority="1518"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B729">
-    <cfRule type="duplicateValues" dxfId="1087" priority="1519"/>
+    <cfRule type="duplicateValues" dxfId="1082" priority="1519"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B730">
-    <cfRule type="duplicateValues" dxfId="1086" priority="1516"/>
+    <cfRule type="duplicateValues" dxfId="1081" priority="1516"/>
   </conditionalFormatting>
   <c